--- a/data/germany/p6_deployment/data_preparation/df_constructed.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_constructed.xlsx
@@ -525,57 +525,57 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
@@ -779,37 +779,37 @@
       </c>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="n">
-        <v>1.386219336219341</v>
+        <v>-13994968.13371813</v>
       </c>
       <c r="U2" t="n">
         <v>1.307371332371336</v>
       </c>
       <c r="V2" t="n">
+        <v>-0.4036070289359763</v>
+      </c>
+      <c r="W2" t="n">
+        <v>-4.856144148249413</v>
+      </c>
+      <c r="X2" t="n">
+        <v>-4193764.608016253</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>-0.5896945646945648</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>-8.366329175210737</v>
+      </c>
+      <c r="AA2" t="n">
         <v>-9.377958152958144</v>
       </c>
-      <c r="W2" t="n">
-        <v>-13994968.13371813</v>
-      </c>
-      <c r="X2" t="n">
-        <v>-0.4036070289359763</v>
-      </c>
-      <c r="Y2" t="n">
+      <c r="AB2" t="n">
         <v>-10.07853535353534</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AC2" t="n">
         <v>-1.594049517733708</v>
       </c>
-      <c r="AA2" t="n">
-        <v>-0.5896945646945648</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>-8.366329175210737</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>-4193764.608016253</v>
-      </c>
       <c r="AD2" t="n">
-        <v>-4.856144148249413</v>
+        <v>1.386219336219341</v>
       </c>
       <c r="AE2" t="n">
         <v>2.042059220019745</v>
@@ -1769,37 +1769,37 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9051948051948671</v>
+        <v>-1520649.350649351</v>
       </c>
       <c r="U11" t="n">
         <v>2.415584415584412</v>
       </c>
       <c r="V11" t="n">
+        <v>-0.230265103753172</v>
+      </c>
+      <c r="W11" t="n">
+        <v>-2.054266748652182</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-511996.1037427941</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>-0.07142857142857162</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>-3.333470192043251</v>
+      </c>
+      <c r="AA11" t="n">
         <v>-2.728571428571428</v>
       </c>
-      <c r="W11" t="n">
-        <v>-1520649.350649351</v>
-      </c>
-      <c r="X11" t="n">
-        <v>-0.230265103753172</v>
-      </c>
-      <c r="Y11" t="n">
+      <c r="AB11" t="n">
         <v>-4.963636363636382</v>
       </c>
-      <c r="Z11" t="n">
+      <c r="AC11" t="n">
         <v>0.4995336425950256</v>
       </c>
-      <c r="AA11" t="n">
-        <v>-0.07142857142857162</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>-3.333470192043251</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>-511996.1037427941</v>
-      </c>
       <c r="AD11" t="n">
-        <v>-2.054266748652182</v>
+        <v>-0.9051948051948671</v>
       </c>
       <c r="AE11" t="n">
         <v>-0.5918010606225685</v>
@@ -2437,37 +2437,37 @@
         <v>3</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5957653457653578</v>
+        <v>20477311.57731158</v>
       </c>
       <c r="U17" t="n">
         <v>1.253729603729603</v>
       </c>
       <c r="V17" t="n">
+        <v>0.4897894275611663</v>
+      </c>
+      <c r="W17" t="n">
+        <v>7.873451518288476</v>
+      </c>
+      <c r="X17" t="n">
+        <v>30268860.95310687</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.5293706293706295</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>8.819984906397934</v>
+      </c>
+      <c r="AA17" t="n">
         <v>5.122144522144509</v>
       </c>
-      <c r="W17" t="n">
-        <v>20477311.57731158</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0.4897894275611663</v>
-      </c>
-      <c r="Y17" t="n">
+      <c r="AB17" t="n">
         <v>4.910023310023305</v>
       </c>
-      <c r="Z17" t="n">
+      <c r="AC17" t="n">
         <v>-0.9577051169442825</v>
       </c>
-      <c r="AA17" t="n">
-        <v>0.5293706293706295</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>8.819984906397934</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>30268860.95310687</v>
-      </c>
       <c r="AD17" t="n">
-        <v>7.873451518288476</v>
+        <v>0.5957653457653578</v>
       </c>
       <c r="AE17" t="n">
         <v>-1.420749500097319</v>
@@ -3006,37 +3006,37 @@
         <v>-1</v>
       </c>
       <c r="T22" t="n">
-        <v>0.012337662337643</v>
+        <v>-7344080.086580085</v>
       </c>
       <c r="U22" t="n">
         <v>-1.63463203463203</v>
       </c>
       <c r="V22" t="n">
+        <v>-0.4320534125167992</v>
+      </c>
+      <c r="W22" t="n">
+        <v>-6.568198738305384</v>
+      </c>
+      <c r="X22" t="n">
+        <v>-4508584.188538115</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>-0.6969696969696966</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>-6.910317638687815</v>
+      </c>
+      <c r="AA22" t="n">
         <v>-8.457575757575754</v>
       </c>
-      <c r="W22" t="n">
-        <v>-7344080.086580085</v>
-      </c>
-      <c r="X22" t="n">
-        <v>-0.4320534125167992</v>
-      </c>
-      <c r="Y22" t="n">
+      <c r="AB22" t="n">
         <v>-6.20930735930736</v>
       </c>
-      <c r="Z22" t="n">
+      <c r="AC22" t="n">
         <v>-0.5932105431798789</v>
       </c>
-      <c r="AA22" t="n">
-        <v>-0.6969696969696966</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>-6.910317638687815</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>-4508584.188538115</v>
-      </c>
       <c r="AD22" t="n">
-        <v>-6.568198738305384</v>
+        <v>0.012337662337643</v>
       </c>
       <c r="AE22" t="n">
         <v>0.9483970991142385</v>
@@ -3992,37 +3992,37 @@
       </c>
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="n">
-        <v>2.795454545454533</v>
+        <v>-5617424.242424244</v>
       </c>
       <c r="U31" t="n">
         <v>0.5025252525252561</v>
       </c>
       <c r="V31" t="n">
+        <v>-0.5175264550264551</v>
+      </c>
+      <c r="W31" t="n">
+        <v>-7.633377425044088</v>
+      </c>
+      <c r="X31" t="n">
+        <v>-3627911.430776014</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>-0.5681818181818177</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-7.385030864197532</v>
+      </c>
+      <c r="AA31" t="n">
         <v>-7.199494949494948</v>
       </c>
-      <c r="W31" t="n">
-        <v>-5617424.242424244</v>
-      </c>
-      <c r="X31" t="n">
-        <v>-0.5175264550264551</v>
-      </c>
-      <c r="Y31" t="n">
+      <c r="AB31" t="n">
         <v>-8.967171717171723</v>
       </c>
-      <c r="Z31" t="n">
+      <c r="AC31" t="n">
         <v>-2.010141093474402</v>
       </c>
-      <c r="AA31" t="n">
-        <v>-0.5681818181818177</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>-7.385030864197532</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>-3627911.430776014</v>
-      </c>
       <c r="AD31" t="n">
-        <v>-7.633377425044088</v>
+        <v>2.795454545454533</v>
       </c>
       <c r="AE31" t="n">
         <v>-2.067405202821874</v>

--- a/data/germany/p6_deployment/data_preparation/df_constructed.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_constructed.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF42"/>
+  <dimension ref="A1:BF33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -525,84 +525,84 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_goal_attempts</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts_against</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days_against</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals_against</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_ball_possession</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_ball_possession_against</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_shots_on_goal</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_shots_on_goal_against</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals_against</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_fouls</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_fouls_against</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_points</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_points_against</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days_against</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts_against</t>
-        </is>
-      </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_away</t>
@@ -620,97 +620,97 @@
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
           <t>dif_sum_pot_player_miss</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_start</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_miss</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_rat_player_sub</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
         </is>
       </c>
       <c r="BF1" s="1" t="inlineStr">
@@ -722,42 +722,42 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>W67CmLPh</t>
+          <t>zuzbQnCF</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45531.65625</v>
+        <v>45527.64583333334</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">schlager d 
+          <t xml:space="preserve">dankert b 
   ger </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">preussenstadion
-  munster </t>
+          <t xml:space="preserve">borussia park
+  monchengladbach </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>zedZaSL7</t>
+          <t>88HSzjDr</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>nJQmYp1B</t>
+          <t>4jcj2zMd</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>59</v>
       </c>
       <c r="H2" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>20242025</v>
@@ -769,23 +769,31 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>dfb pokal</t>
+          <t>bundesliga</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>8E86CPuD</t>
+          <t>GzfvcwRj</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>M5BRZDsC</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
+          <t>hAcTWKKN</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>-19</v>
+      </c>
+      <c r="P2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>-9</v>
+      </c>
+      <c r="R2" t="n">
+        <v>-3</v>
+      </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
@@ -805,41 +813,51 @@
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="n">
-        <v>76</v>
-      </c>
+      <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="n">
-        <v>-4.559642857142862</v>
-      </c>
-      <c r="AS2" t="inlineStr"/>
+      <c r="AO2" t="n">
+        <v>-6.13494949494951</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>-0.684242424242484</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>-5.948686868686863</v>
+      </c>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="n">
+        <v>-29872264.42431086</v>
+      </c>
       <c r="AT2" t="n">
-        <v>-0.6717460317459825</v>
+        <v>-0.5298989898989896</v>
       </c>
       <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="inlineStr"/>
+      <c r="AV2" t="n">
+        <v>2.45863764693803</v>
+      </c>
       <c r="AW2" t="n">
-        <v>-4660730.158730159</v>
+        <v>-0.4946688226134863</v>
       </c>
       <c r="AX2" t="n">
-        <v>-7.30119047619047</v>
+        <v>-0.4451515151515117</v>
       </c>
       <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="inlineStr"/>
-      <c r="BA2" t="inlineStr"/>
+      <c r="AZ2" t="n">
+        <v>-23346757.57575758</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>-5.671401322656251</v>
+      </c>
       <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="n">
-        <v>1.166706349206347</v>
-      </c>
-      <c r="BD2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="n">
+        <v>-6.342584462638811</v>
+      </c>
       <c r="BE2" t="n">
-        <v>-0.2807539682539684</v>
+        <v>0.0286693017127817</v>
       </c>
       <c r="BF2" t="n">
         <v>0</v>
@@ -848,42 +866,42 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>AuVMGZvJ</t>
+          <t>pAXo2Kvn</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45529.52083333334</v>
+        <v>45523.65625</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">welz t 
+          <t xml:space="preserve">zwayer f 
   ger </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">millerntor stadion
-  hamburg </t>
+          <t xml:space="preserve">eintracht stadion
+  braunschweig </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ILyJuN3g</t>
+          <t>QqLCC3il</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>KWixEVWi</t>
+          <t>8vndvXTk</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>59</v>
       </c>
       <c r="H3" t="n">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
         <v>20242025</v>
@@ -895,31 +913,27 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>bundesliga</t>
+          <t>dfb pokal</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>QTAUlvUP</t>
+          <t>txZLBQVC</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>lGJdeemM</t>
+          <t>pfoInmcq</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
-      </c>
-      <c r="P3" t="n">
-        <v>3</v>
-      </c>
+        <v>-4</v>
+      </c>
+      <c r="P3" t="inlineStr"/>
       <c r="Q3" t="n">
-        <v>4</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1</v>
-      </c>
+        <v>-2</v>
+      </c>
+      <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
         <v>0</v>
       </c>
@@ -943,47 +957,47 @@
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="inlineStr"/>
-      <c r="AN3" t="n">
-        <v>0.2045454545454568</v>
-      </c>
-      <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="inlineStr"/>
-      <c r="AQ3" t="inlineStr"/>
-      <c r="AR3" t="n">
-        <v>-2.274352548036759</v>
-      </c>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="n">
+        <v>-9.648318903318909</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.121976911976901</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>-9.887279942279932</v>
+      </c>
+      <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="n">
-        <v>-2.88636363636364</v>
+        <v>-4433682.637329254</v>
       </c>
       <c r="AT3" t="n">
-        <v>2.892376775271543</v>
+        <v>-0.5472077922077923</v>
       </c>
       <c r="AU3" t="inlineStr"/>
-      <c r="AV3" t="inlineStr"/>
+      <c r="AV3" t="n">
+        <v>-1.113380963230583</v>
+      </c>
       <c r="AW3" t="n">
-        <v>-541607.9260651632</v>
+        <v>-0.4218284347231716</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.576754385964918</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>-1.406060606060606</v>
-      </c>
+        <v>1.164985569985571</v>
+      </c>
+      <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="n">
-        <v>-2182803.03030303</v>
+        <v>-14207630.59163059</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>-8.262956688257432</v>
       </c>
       <c r="BB3" t="inlineStr"/>
-      <c r="BC3" t="n">
-        <v>-1.536654135338345</v>
-      </c>
+      <c r="BC3" t="inlineStr"/>
       <c r="BD3" t="n">
-        <v>-2.36818181818181</v>
+        <v>-5.240819689917444</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.750992605973806</v>
       </c>
       <c r="BF3" t="n">
         <v>0</v>
@@ -992,42 +1006,42 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>t0w6KHuf</t>
+          <t>EkP2bxvB</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45529.4375</v>
+        <v>45523.54166666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">fritz m 
+          <t xml:space="preserve">willenborg f 
   ger </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">volkswagen arena
-  wolfsburg </t>
+          <t xml:space="preserve">stadion oberwerth
+  koblenz </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>p8wBsqZt</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>nwkTahLL</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>nVp0wiqd</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>59</v>
       </c>
       <c r="H4" t="n">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>20242025</v>
@@ -1039,31 +1053,19 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>f3ddUIXs</t>
-        </is>
-      </c>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>CQTUFgPk</t>
-        </is>
-      </c>
-      <c r="O4" t="n">
-        <v>-43</v>
-      </c>
-      <c r="P4" t="n">
-        <v>-5</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>-14</v>
-      </c>
-      <c r="R4" t="n">
-        <v>-2</v>
-      </c>
+          <t>vZA6VYpf</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
         <v>0</v>
       </c>
@@ -1087,48 +1089,24 @@
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr"/>
-      <c r="AN4" t="n">
-        <v>-1.989090909090908</v>
-      </c>
+      <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="n">
-        <v>-4.041575302716609</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>-5.508181818181825</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>1.230031369596588</v>
-      </c>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
       <c r="AU4" t="inlineStr"/>
       <c r="AV4" t="inlineStr"/>
-      <c r="AW4" t="n">
-        <v>-20163448.18330824</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>-4.770465681661321</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>1.74909090909091</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>-24898636.36363636</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>-1.403636363636364</v>
-      </c>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr"/>
+      <c r="BA4" t="inlineStr"/>
       <c r="BB4" t="inlineStr"/>
-      <c r="BC4" t="n">
-        <v>0.2246566597653583</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>-4.585454545454539</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>-0.926336972206538</v>
-      </c>
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="inlineStr"/>
       <c r="BF4" t="n">
         <v>0</v>
       </c>
@@ -1136,42 +1114,42 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>SxFxJ44k</t>
+          <t>06NAdG8N</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45528.5625</v>
+        <v>45523.54166666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">zwayer f 
+          <t xml:space="preserve">petersen m 
   ger </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">signal iduna park
-  dortmund </t>
+          <t xml:space="preserve">stadion der freundschaft
+  cottbus </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>nP1i5US1</t>
+          <t>6g44VD52</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>8vndvXTk</t>
+          <t>Ig1f1fy3</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>59</v>
       </c>
       <c r="H5" t="n">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>20242025</v>
@@ -1183,30 +1161,26 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Q1njn0Vm</t>
-        </is>
-      </c>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>pfoInmcq</t>
+          <t>xzRzG0VI</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>18</v>
+        <v>-3</v>
       </c>
       <c r="P5" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="Q5" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1227,54 +1201,28 @@
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="n">
-        <v>76.98111111111112</v>
-      </c>
+      <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="n">
-        <v>0.8932323232323256</v>
-      </c>
+      <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr"/>
-      <c r="AR5" t="n">
-        <v>5.78627781575149</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>2.573434343434343</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>-0.170637199058234</v>
-      </c>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
       <c r="AU5" t="inlineStr"/>
       <c r="AV5" t="inlineStr"/>
-      <c r="AW5" t="n">
-        <v>15016953.70053923</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>3.780325624667739</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>1.649898989898986</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>12926297.97979798</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>0.6154545454545459</v>
-      </c>
+      <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr"/>
+      <c r="BA5" t="inlineStr"/>
       <c r="BB5" t="inlineStr"/>
-      <c r="BC5" t="n">
-        <v>0.7602329687856049</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>1.927979797979802</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>0.5898779144831778</v>
-      </c>
+      <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="inlineStr"/>
+      <c r="BE5" t="inlineStr"/>
       <c r="BF5" t="n">
         <v>0</v>
       </c>
@@ -1282,42 +1230,42 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>YZZcMwBs</t>
+          <t>Sff03OL7</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45528.4375</v>
+        <v>45523.54166666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">petersen m 
+          <t xml:space="preserve">heft f 
   ger </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">wwk arena
-  augsburg </t>
+          <t xml:space="preserve">bieberer berg stadion
+  offenbach am main </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>fTVNku3I</t>
+          <t>YJURlaIO</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ig1f1fy3</t>
+          <t>YFuz2RLm</t>
         </is>
       </c>
       <c r="G6" t="n">
         <v>59</v>
       </c>
       <c r="H6" t="n">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>20242025</v>
@@ -1329,31 +1277,19 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>hAcTWKKN</t>
-        </is>
-      </c>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>xzRzG0VI</t>
-        </is>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2</v>
-      </c>
-      <c r="R6" t="n">
-        <v>-1</v>
-      </c>
+          <t>8E8qmw3d</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
         <v>0</v>
       </c>
@@ -1377,48 +1313,24 @@
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="inlineStr"/>
       <c r="AM6" t="inlineStr"/>
-      <c r="AN6" t="n">
-        <v>-0.7684848484848459</v>
-      </c>
+      <c r="AN6" t="inlineStr"/>
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr"/>
-      <c r="AR6" t="n">
-        <v>2.705774502956999</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>1.167474747474756</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>-0.5707879093319832</v>
-      </c>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
       <c r="AU6" t="inlineStr"/>
       <c r="AV6" t="inlineStr"/>
-      <c r="AW6" t="n">
-        <v>1456325.053307676</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>2.773008876770319</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>2.875757575757575</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>1841237.373737372</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>0.2805050505050504</v>
-      </c>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr"/>
+      <c r="BA6" t="inlineStr"/>
       <c r="BB6" t="inlineStr"/>
-      <c r="BC6" t="n">
-        <v>-0.9624418424189578</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>1.380606060606056</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>0.02797986402105423</v>
-      </c>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="inlineStr"/>
       <c r="BF6" t="n">
         <v>0</v>
       </c>
@@ -1426,42 +1338,42 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2FREIeA6</t>
+          <t>vXAKoaf5</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45528.4375</v>
+        <v>45522.54166666666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">dingert c 
+          <t xml:space="preserve">kampka r 
   ger </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">mewa arena
-  mainz </t>
+          <t xml:space="preserve">rudolf harbig stadion
+  dresden </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>EuakNmc1</t>
+          <t>zL1YsOi1</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>pzHW4oaE</t>
+          <t>ne1oL3y7</t>
         </is>
       </c>
       <c r="G7" t="n">
         <v>59</v>
       </c>
       <c r="H7" t="n">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>20242025</v>
@@ -1473,30 +1385,26 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>f3ddUIXs</t>
-        </is>
-      </c>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>l0fHXMdE</t>
+          <t>AoL97rX8</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>-2</v>
+        <v>4</v>
       </c>
       <c r="P7" t="n">
-        <v>-4</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
         <v>2</v>
       </c>
       <c r="R7" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1521,48 +1429,24 @@
       <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="inlineStr"/>
       <c r="AM7" t="inlineStr"/>
-      <c r="AN7" t="n">
-        <v>-1.263636363636369</v>
-      </c>
+      <c r="AN7" t="inlineStr"/>
       <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr"/>
-      <c r="AR7" t="n">
-        <v>-1.434459336747679</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>-1.38181818181819</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>1.060416893683453</v>
-      </c>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
       <c r="AU7" t="inlineStr"/>
       <c r="AV7" t="inlineStr"/>
-      <c r="AW7" t="n">
-        <v>-597797.2558207102</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>0.4833356035014873</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>-1.472727272727269</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>-1682727.272727272</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>-0.02727272727272734</v>
-      </c>
+      <c r="AW7" t="inlineStr"/>
+      <c r="AX7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr"/>
+      <c r="BA7" t="inlineStr"/>
       <c r="BB7" t="inlineStr"/>
-      <c r="BC7" t="n">
-        <v>-0.8075991609458448</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>0.3363636363636289</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>0.02194571573862203</v>
-      </c>
+      <c r="BC7" t="inlineStr"/>
+      <c r="BD7" t="inlineStr"/>
+      <c r="BE7" t="inlineStr"/>
       <c r="BF7" t="n">
         <v>0</v>
       </c>
@@ -1570,42 +1454,42 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>dfO6OQtS</t>
+          <t>pzHxyrtm</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45528.4375</v>
+        <v>45522.54166666666</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">aytekin d 
+          <t xml:space="preserve">braun r 
   ger </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">red bull arena
-  leipzig </t>
+          <t xml:space="preserve">stadion am lotter kreuz
+  lotte </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>KbS1suSm</t>
+          <t>hjNlCFPB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>8Y2m6ADe</t>
+          <t>EB3q7jbk</t>
         </is>
       </c>
       <c r="G8" t="n">
         <v>59</v>
       </c>
       <c r="H8" t="n">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>20242025</v>
@@ -1617,31 +1501,19 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>UgdQz0fK</t>
-        </is>
-      </c>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>xzRzG0VI</t>
-        </is>
-      </c>
-      <c r="O8" t="n">
-        <v>9</v>
-      </c>
-      <c r="P8" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>5</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2</v>
-      </c>
+          <t>tO31cZrF</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
         <v>0</v>
       </c>
@@ -1665,48 +1537,24 @@
       <c r="AK8" t="inlineStr"/>
       <c r="AL8" t="inlineStr"/>
       <c r="AM8" t="inlineStr"/>
-      <c r="AN8" t="n">
-        <v>-3.321313131313129</v>
-      </c>
+      <c r="AN8" t="inlineStr"/>
       <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr"/>
-      <c r="AR8" t="n">
-        <v>6.213338187365665</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>7.015589225589238</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>2.027617338801576</v>
-      </c>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
       <c r="AU8" t="inlineStr"/>
       <c r="AV8" t="inlineStr"/>
-      <c r="AW8" t="n">
-        <v>14982179.99021489</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>7.699864814924894</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>0.4905050505050497</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>25519476.01010101</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>0.8125757575757577</v>
-      </c>
+      <c r="AW8" t="inlineStr"/>
+      <c r="AX8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr"/>
+      <c r="BA8" t="inlineStr"/>
       <c r="BB8" t="inlineStr"/>
-      <c r="BC8" t="n">
-        <v>-1.563333908442605</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>8.87616161616161</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>0.6605013439395591</v>
-      </c>
+      <c r="BC8" t="inlineStr"/>
+      <c r="BD8" t="inlineStr"/>
+      <c r="BE8" t="inlineStr"/>
       <c r="BF8" t="n">
         <v>0</v>
       </c>
@@ -1714,42 +1562,42 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>GbeXvnR8</t>
+          <t>dCPKovw8</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45528.4375</v>
+        <v>45522.54166666666</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">schlager d 
+          <t xml:space="preserve">burda m 
   ger </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">europa park stadion
-  freiburg </t>
+          <t xml:space="preserve">hansch arena
+  meppen </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>fiEQZ7C7</t>
+          <t>rXqBh2xP</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>nJQmYp1B</t>
+          <t>v9k3aY5F</t>
         </is>
       </c>
       <c r="G9" t="n">
         <v>59</v>
       </c>
       <c r="H9" t="n">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>20242025</v>
@@ -1761,31 +1609,19 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>v9WoiHGP</t>
-        </is>
-      </c>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>M5BRZDsC</t>
-        </is>
-      </c>
-      <c r="O9" t="n">
-        <v>-9</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>3</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1</v>
-      </c>
+          <t>EDRZkDzS</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
         <v>0</v>
       </c>
@@ -1806,96 +1642,72 @@
       <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="inlineStr"/>
       <c r="AJ9" t="n">
-        <v>76</v>
+        <v>71.2</v>
       </c>
       <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="inlineStr"/>
-      <c r="AN9" t="n">
-        <v>2.990909090909092</v>
-      </c>
+      <c r="AN9" t="inlineStr"/>
       <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr"/>
-      <c r="AR9" t="n">
-        <v>1.716102756892241</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>-0.4181818181818215</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>2.394676274018366</v>
-      </c>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
       <c r="AU9" t="inlineStr"/>
       <c r="AV9" t="inlineStr"/>
-      <c r="AW9" t="n">
-        <v>-514226.086048454</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>0.8320144110275862</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>-1.254545454545479</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>-2633636.36363636</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>0.2181818181818176</v>
-      </c>
+      <c r="AW9" t="inlineStr"/>
+      <c r="AX9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr"/>
+      <c r="BA9" t="inlineStr"/>
       <c r="BB9" t="inlineStr"/>
-      <c r="BC9" t="n">
-        <v>0.2097263993316645</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>-1.900000000000006</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>0.1311883876357562</v>
-      </c>
+      <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="inlineStr"/>
       <c r="BF9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>O48oHrZ1</t>
+          <t>KSwfVwAO</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45528.4375</v>
+        <v>45522.4375</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">sather a 
+          <t xml:space="preserve">kampka r 
   ger </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">prezero arena
-  sinsheim </t>
+          <t xml:space="preserve">millerntor stadion
+  hamburg </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>hQAtP9Sl</t>
+          <t>WrbkcjCd</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>63WsD2ei</t>
+          <t>S0hPB9rA</t>
         </is>
       </c>
       <c r="G10" t="n">
         <v>59</v>
       </c>
       <c r="H10" t="n">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
         <v>20242025</v>
@@ -1907,31 +1719,19 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>KUx4Q7x1</t>
-        </is>
-      </c>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>A15eUM4C</t>
-        </is>
-      </c>
-      <c r="O10" t="n">
-        <v>1</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
+          <t>AoL97rX8</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
         <v>0</v>
       </c>
@@ -1955,48 +1755,24 @@
       <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="inlineStr"/>
       <c r="AM10" t="inlineStr"/>
-      <c r="AN10" t="n">
-        <v>1.506060606060601</v>
-      </c>
+      <c r="AN10" t="inlineStr"/>
       <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr"/>
-      <c r="AR10" t="n">
-        <v>4.897245226593043</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>6.896969696969705</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>-0.3796813894640252</v>
-      </c>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
       <c r="AU10" t="inlineStr"/>
       <c r="AV10" t="inlineStr"/>
-      <c r="AW10" t="n">
-        <v>3813832.671957672</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>6.600882792730616</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>-1.018181818181802</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>7180757.575757575</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>0.742424242424242</v>
-      </c>
+      <c r="AW10" t="inlineStr"/>
+      <c r="AX10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr"/>
+      <c r="BA10" t="inlineStr"/>
       <c r="BB10" t="inlineStr"/>
-      <c r="BC10" t="n">
-        <v>-0.8442575339314509</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>6.257575757575736</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>0.3518806073153895</v>
-      </c>
+      <c r="BC10" t="inlineStr"/>
+      <c r="BD10" t="inlineStr"/>
+      <c r="BE10" t="inlineStr"/>
       <c r="BF10" t="n">
         <v>0</v>
       </c>
@@ -2004,42 +1780,42 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>zuzbQnCF</t>
+          <t>YV3TqwPH</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45527.64583333334</v>
+        <v>45522.4375</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">dankert b 
+          <t xml:space="preserve">haslberger w 
   ger </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">borussia park
-  monchengladbach </t>
+          <t xml:space="preserve">stadion am panzenberg
+  bremen </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>88HSzjDr</t>
+          <t>tW75B1ei</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>4jcj2zMd</t>
+          <t>G2Op923t</t>
         </is>
       </c>
       <c r="G11" t="n">
         <v>59</v>
       </c>
       <c r="H11" t="n">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>20242025</v>
@@ -2051,31 +1827,19 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>GzfvcwRj</t>
-        </is>
-      </c>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>hAcTWKKN</t>
-        </is>
-      </c>
-      <c r="O11" t="n">
-        <v>-19</v>
-      </c>
-      <c r="P11" t="n">
-        <v>-3</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>-9</v>
-      </c>
-      <c r="R11" t="n">
-        <v>-3</v>
-      </c>
+          <t>0AI1QUJH</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
         <v>0</v>
       </c>
@@ -2095,52 +1859,30 @@
       <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="inlineStr"/>
       <c r="AI11" t="inlineStr"/>
-      <c r="AJ11" t="inlineStr"/>
+      <c r="AJ11" t="n">
+        <v>67</v>
+      </c>
       <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="inlineStr"/>
       <c r="AM11" t="inlineStr"/>
-      <c r="AN11" t="n">
-        <v>-0.4451515151515117</v>
-      </c>
+      <c r="AN11" t="inlineStr"/>
       <c r="AO11" t="inlineStr"/>
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr"/>
-      <c r="AR11" t="n">
-        <v>-6.342584462638811</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>-6.13494949494951</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>2.45863764693803</v>
-      </c>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="inlineStr"/>
       <c r="AU11" t="inlineStr"/>
       <c r="AV11" t="inlineStr"/>
-      <c r="AW11" t="n">
-        <v>-29872264.42431086</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>-5.671401322656251</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>-0.684242424242484</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>-23346757.57575758</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>-0.5298989898989896</v>
-      </c>
+      <c r="AW11" t="inlineStr"/>
+      <c r="AX11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr"/>
+      <c r="BA11" t="inlineStr"/>
       <c r="BB11" t="inlineStr"/>
-      <c r="BC11" t="n">
-        <v>0.0286693017127817</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>-5.948686868686863</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>-0.4946688226134863</v>
-      </c>
+      <c r="BC11" t="inlineStr"/>
+      <c r="BD11" t="inlineStr"/>
+      <c r="BE11" t="inlineStr"/>
       <c r="BF11" t="n">
         <v>0</v>
       </c>
@@ -2148,32 +1890,32 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>pAXo2Kvn</t>
+          <t>tvOIPExA</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45523.65625</v>
+        <v>45522.4375</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">zwayer f 
+          <t xml:space="preserve">burda m 
   ger </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">eintracht stadion
-  braunschweig </t>
+          <t xml:space="preserve">hardtwaldstadion
+  sandhausen </t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>QqLCC3il</t>
+          <t>UZxEj1R4</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>8vndvXTk</t>
+          <t>WG9pOTse</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2198,14 +1940,10 @@
           <t>dfb pokal</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>txZLBQVC</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>pfoInmcq</t>
+          <t>EDRZkDzS</t>
         </is>
       </c>
       <c r="O12" t="n">
@@ -2239,48 +1977,24 @@
       <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="inlineStr"/>
       <c r="AM12" t="inlineStr"/>
-      <c r="AN12" t="n">
-        <v>1.164985569985571</v>
-      </c>
+      <c r="AN12" t="inlineStr"/>
       <c r="AO12" t="inlineStr"/>
       <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr"/>
-      <c r="AR12" t="n">
-        <v>-5.240819689917444</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>-9.648318903318909</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>-1.113380963230583</v>
-      </c>
+      <c r="AR12" t="inlineStr"/>
+      <c r="AS12" t="inlineStr"/>
+      <c r="AT12" t="inlineStr"/>
       <c r="AU12" t="inlineStr"/>
       <c r="AV12" t="inlineStr"/>
-      <c r="AW12" t="n">
-        <v>-4433682.637329254</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>-8.262956688257432</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>1.121976911976901</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>-14207630.59163059</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>-0.5472077922077923</v>
-      </c>
+      <c r="AW12" t="inlineStr"/>
+      <c r="AX12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr"/>
+      <c r="BA12" t="inlineStr"/>
       <c r="BB12" t="inlineStr"/>
-      <c r="BC12" t="n">
-        <v>1.750992605973806</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>-9.887279942279932</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>-0.4218284347231716</v>
-      </c>
+      <c r="BC12" t="inlineStr"/>
+      <c r="BD12" t="inlineStr"/>
+      <c r="BE12" t="inlineStr"/>
       <c r="BF12" t="n">
         <v>0</v>
       </c>
@@ -2288,32 +2002,32 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>06NAdG8N</t>
+          <t>jFMCm08e</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45523.54166666666</v>
+        <v>45522.4375</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">petersen m 
+          <t xml:space="preserve">aytekin d 
   ger </t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadion der freundschaft
-  cottbus </t>
+          <t xml:space="preserve">jahnstadion regensburg
+  regensburg </t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>6g44VD52</t>
+          <t>UiCmEP56</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ig1f1fy3</t>
+          <t>8Y2m6ADe</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2338,24 +2052,24 @@
           <t>dfb pokal</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>t0ZPdkUl</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr">
         <is>
           <t>xzRzG0VI</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>-3</v>
-      </c>
-      <c r="P13" t="n">
-        <v>-1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="P13" t="inlineStr"/>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
-      <c r="R13" t="n">
-        <v>-1</v>
-      </c>
+      <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
         <v>0</v>
       </c>
@@ -2404,11 +2118,11 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Sff03OL7</t>
+          <t>t2AoZLAa</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45523.54166666666</v>
+        <v>45522.4375</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2418,18 +2132,18 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">bieberer berg stadion
-  offenbach am main </t>
+          <t xml:space="preserve">friedrich ebert stadium
+  hildesheim </t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>YJURlaIO</t>
+          <t>E3xs5mIe</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>YFuz2RLm</t>
+          <t>6in2Eknb</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2512,32 +2226,32 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>EkP2bxvB</t>
+          <t>l0ueP5rR</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45523.54166666666</v>
+        <v>45522.4375</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">willenborg f 
+          <t xml:space="preserve">haslberger w 
   ger </t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadion oberwerth
-  koblenz </t>
+          <t xml:space="preserve">ostseestadion
+  rostock </t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>p8wBsqZt</t>
+          <t>KIHmtCkL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>nwkTahLL</t>
+          <t>2y0u8Wrq</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2562,16 +2276,28 @@
           <t>dfb pokal</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>UyNNTYWE</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>vZA6VYpf</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
+          <t>0AI1QUJH</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>-7</v>
+      </c>
+      <c r="P15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>-3</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
@@ -2596,23 +2322,47 @@
       <c r="AL15" t="inlineStr"/>
       <c r="AM15" t="inlineStr"/>
       <c r="AN15" t="inlineStr"/>
-      <c r="AO15" t="inlineStr"/>
-      <c r="AP15" t="inlineStr"/>
-      <c r="AQ15" t="inlineStr"/>
+      <c r="AO15" t="n">
+        <v>-2.515873015873012</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>-0.5937950937951371</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>-5.057864357864361</v>
+      </c>
       <c r="AR15" t="inlineStr"/>
-      <c r="AS15" t="inlineStr"/>
-      <c r="AT15" t="inlineStr"/>
+      <c r="AS15" t="n">
+        <v>-630832.411212642</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>-0.07301587301587298</v>
+      </c>
       <c r="AU15" t="inlineStr"/>
-      <c r="AV15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr"/>
-      <c r="AX15" t="inlineStr"/>
+      <c r="AV15" t="n">
+        <v>0.3381612675581209</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>-0.2286778021658702</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>2.539682539682538</v>
+      </c>
       <c r="AY15" t="inlineStr"/>
-      <c r="AZ15" t="inlineStr"/>
-      <c r="BA15" t="inlineStr"/>
+      <c r="AZ15" t="n">
+        <v>-1437914.862914863</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>-3.590488579108211</v>
+      </c>
       <c r="BB15" t="inlineStr"/>
       <c r="BC15" t="inlineStr"/>
-      <c r="BD15" t="inlineStr"/>
-      <c r="BE15" t="inlineStr"/>
+      <c r="BD15" t="n">
+        <v>-2.249002855655363</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>-0.3369713751251808</v>
+      </c>
       <c r="BF15" t="n">
         <v>0</v>
       </c>
@@ -2620,32 +2370,32 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>pzHxyrtm</t>
+          <t>AiJ3kset</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>45522.54166666666</v>
+        <v>45522.33333333334</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">braun r 
+          <t xml:space="preserve">jollenbeck m 
   ger </t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadion am lotter kreuz
-  lotte </t>
+          <t xml:space="preserve">friedrich ludwig jahn sportpark
+  berlin </t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>hjNlCFPB</t>
+          <t>UNr2EUfd</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>EB3q7jbk</t>
+          <t>fTVNku3I</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2673,7 +2423,7 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>tO31cZrF</t>
+          <t>2VSFgl3c</t>
         </is>
       </c>
       <c r="O16" t="inlineStr"/>
@@ -2728,32 +2478,32 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>dCPKovw8</t>
+          <t>6q2yrHgU</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>45522.54166666666</v>
+        <v>45522.33333333334</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">burda m 
+          <t xml:space="preserve">braun r 
   ger </t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">hansch arena
-  meppen </t>
+          <t xml:space="preserve">ludwigspark stadion
+  saarbrucken </t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>rXqBh2xP</t>
+          <t>fLbhmJ5l</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>v9k3aY5F</t>
+          <t>6FDqshzF</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2781,12 +2531,16 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>EDRZkDzS</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr"/>
+          <t>tO31cZrF</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>1</v>
+      </c>
       <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
         <v>0</v>
@@ -2808,7 +2562,7 @@
       <c r="AH17" t="inlineStr"/>
       <c r="AI17" t="inlineStr"/>
       <c r="AJ17" t="n">
-        <v>71.2</v>
+        <v>66</v>
       </c>
       <c r="AK17" t="inlineStr"/>
       <c r="AL17" t="inlineStr"/>
@@ -2838,45 +2592,45 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>vXAKoaf5</t>
+          <t>fcxqFy2l</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>45522.54166666666</v>
+        <v>45521.64583333334</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">kampka r 
+          <t xml:space="preserve">schlager d 
   ger </t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">rudolf harbig stadion
-  dresden </t>
+          <t xml:space="preserve">bayarena
+  leverkusen </t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>zL1YsOi1</t>
+          <t>4jcj2zMd</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ne1oL3y7</t>
+          <t>nJQmYp1B</t>
         </is>
       </c>
       <c r="G18" t="n">
         <v>59</v>
       </c>
       <c r="H18" t="n">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="I18" t="n">
         <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>20242025</v>
+        <v>2024</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -2885,26 +2639,30 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr"/>
+          <t>super cup</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2BYSk4KO</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>AoL97rX8</t>
+          <t>M5BRZDsC</t>
         </is>
       </c>
       <c r="O18" t="n">
+        <v>27</v>
+      </c>
+      <c r="P18" t="n">
         <v>4</v>
       </c>
-      <c r="P18" t="n">
-        <v>1</v>
-      </c>
       <c r="Q18" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -2930,23 +2688,47 @@
       <c r="AL18" t="inlineStr"/>
       <c r="AM18" t="inlineStr"/>
       <c r="AN18" t="inlineStr"/>
-      <c r="AO18" t="inlineStr"/>
-      <c r="AP18" t="inlineStr"/>
-      <c r="AQ18" t="inlineStr"/>
+      <c r="AO18" t="n">
+        <v>5.13333333333334</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0.7535353535353693</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>4.878787878787875</v>
+      </c>
       <c r="AR18" t="inlineStr"/>
-      <c r="AS18" t="inlineStr"/>
-      <c r="AT18" t="inlineStr"/>
+      <c r="AS18" t="n">
+        <v>30827197.30905896</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0.5272727272727271</v>
+      </c>
       <c r="AU18" t="inlineStr"/>
-      <c r="AV18" t="inlineStr"/>
-      <c r="AW18" t="inlineStr"/>
-      <c r="AX18" t="inlineStr"/>
+      <c r="AV18" t="n">
+        <v>-1.175290510982194</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0.5169583326203877</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1.23030303030303</v>
+      </c>
       <c r="AY18" t="inlineStr"/>
-      <c r="AZ18" t="inlineStr"/>
-      <c r="BA18" t="inlineStr"/>
+      <c r="AZ18" t="n">
+        <v>19594646.46464647</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>8.734170473794975</v>
+      </c>
       <c r="BB18" t="inlineStr"/>
       <c r="BC18" t="inlineStr"/>
-      <c r="BD18" t="inlineStr"/>
-      <c r="BE18" t="inlineStr"/>
+      <c r="BD18" t="n">
+        <v>7.566349990589131</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>-1.531745561202083</v>
+      </c>
       <c r="BF18" t="n">
         <v>0</v>
       </c>
@@ -2954,32 +2736,32 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>t2AoZLAa</t>
+          <t>CpiTEcOi</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>45522.4375</v>
+        <v>45521.54166666666</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">heft f 
+          <t xml:space="preserve">bacher m 
   ger </t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">friedrich ebert stadium
-  hildesheim </t>
+          <t xml:space="preserve">schuco arena
+  bielefeld </t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>E3xs5mIe</t>
+          <t>pp38UXK8</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>6in2Eknb</t>
+          <t>dfNCCCzS</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3007,13 +2789,21 @@
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>8E8qmw3d</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
+          <t>zyLSrbZQ</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>3</v>
+      </c>
+      <c r="P19" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>-1</v>
+      </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
@@ -3062,32 +2852,32 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>l0ueP5rR</t>
+          <t>8CpxDyg4</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>45522.4375</v>
+        <v>45521.54166666666</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">haslberger w 
+          <t xml:space="preserve">siebert d 
   ger </t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">ostseestadion
-  rostock </t>
+          <t xml:space="preserve">stadion lohmuhle
+  lubeck </t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>KIHmtCkL</t>
+          <t>I1Vk6k3R</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2y0u8Wrq</t>
+          <t>nP1i5US1</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3112,28 +2902,16 @@
           <t>dfb pokal</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>UyNNTYWE</t>
-        </is>
-      </c>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0AI1QUJH</t>
-        </is>
-      </c>
-      <c r="O20" t="n">
-        <v>-7</v>
-      </c>
-      <c r="P20" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>-3</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
+          <t>MDhPV0RQ</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
         <v>0</v>
       </c>
@@ -3157,48 +2935,24 @@
       <c r="AK20" t="inlineStr"/>
       <c r="AL20" t="inlineStr"/>
       <c r="AM20" t="inlineStr"/>
-      <c r="AN20" t="n">
-        <v>2.539682539682538</v>
-      </c>
+      <c r="AN20" t="inlineStr"/>
       <c r="AO20" t="inlineStr"/>
       <c r="AP20" t="inlineStr"/>
       <c r="AQ20" t="inlineStr"/>
-      <c r="AR20" t="n">
-        <v>-2.249002855655363</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>-2.515873015873012</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>0.3381612675581209</v>
-      </c>
+      <c r="AR20" t="inlineStr"/>
+      <c r="AS20" t="inlineStr"/>
+      <c r="AT20" t="inlineStr"/>
       <c r="AU20" t="inlineStr"/>
       <c r="AV20" t="inlineStr"/>
-      <c r="AW20" t="n">
-        <v>-630832.411212642</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>-3.590488579108211</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>-0.5937950937951371</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>-1437914.862914863</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>-0.07301587301587298</v>
-      </c>
+      <c r="AW20" t="inlineStr"/>
+      <c r="AX20" t="inlineStr"/>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr"/>
+      <c r="BA20" t="inlineStr"/>
       <c r="BB20" t="inlineStr"/>
-      <c r="BC20" t="n">
-        <v>-0.3369713751251808</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>-5.057864357864361</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>-0.2286778021658702</v>
-      </c>
+      <c r="BC20" t="inlineStr"/>
+      <c r="BD20" t="inlineStr"/>
+      <c r="BE20" t="inlineStr"/>
       <c r="BF20" t="n">
         <v>0</v>
       </c>
@@ -3206,32 +2960,32 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>YV3TqwPH</t>
+          <t>hzyf0b9b</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>45522.4375</v>
+        <v>45521.54166666666</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">haslberger w 
+          <t xml:space="preserve">sather a 
   ger </t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadion am panzenberg
-  bremen </t>
+          <t xml:space="preserve">new tivoli
+  aachen </t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>tW75B1ei</t>
+          <t>j3PKcB4E</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>G2Op923t</t>
+          <t>63WsD2ei</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3259,7 +3013,7 @@
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0AI1QUJH</t>
+          <t>A15eUM4C</t>
         </is>
       </c>
       <c r="O21" t="inlineStr"/>
@@ -3285,9 +3039,7 @@
       <c r="AG21" t="inlineStr"/>
       <c r="AH21" t="inlineStr"/>
       <c r="AI21" t="inlineStr"/>
-      <c r="AJ21" t="n">
-        <v>67</v>
-      </c>
+      <c r="AJ21" t="inlineStr"/>
       <c r="AK21" t="inlineStr"/>
       <c r="AL21" t="inlineStr"/>
       <c r="AM21" t="inlineStr"/>
@@ -3316,32 +3068,32 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>KSwfVwAO</t>
+          <t>8QPARz8c</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>45522.4375</v>
+        <v>45521.4375</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">kampka r 
+          <t xml:space="preserve">welz t 
   ger </t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">millerntor stadion
-  hamburg </t>
+          <t xml:space="preserve">ms technologie arena
+  villingen schwenningen </t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>WrbkcjCd</t>
+          <t>lKLJUxeT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>S0hPB9rA</t>
+          <t>KWixEVWi</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3369,7 +3121,7 @@
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
-          <t>AoL97rX8</t>
+          <t>lGJdeemM</t>
         </is>
       </c>
       <c r="O22" t="inlineStr"/>
@@ -3424,32 +3176,32 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>tvOIPExA</t>
+          <t>f1nnRRDE</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>45522.4375</v>
+        <v>45521.4375</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">burda m 
+          <t xml:space="preserve">dingert c 
   ger </t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">hardtwaldstadion
-  sandhausen </t>
+          <t xml:space="preserve">stadion an der bremer bruck
+  osnabruck </t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>UZxEj1R4</t>
+          <t>88Xgj1Y5</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>WG9pOTse</t>
+          <t>fiEQZ7C7</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3474,20 +3226,28 @@
           <t>dfb pokal</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>lxrr7DgN</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>EDRZkDzS</t>
+          <t>l0fHXMdE</t>
         </is>
       </c>
       <c r="O23" t="n">
-        <v>-4</v>
-      </c>
-      <c r="P23" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q23" t="n">
-        <v>-2</v>
-      </c>
-      <c r="R23" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="R23" t="n">
+        <v>-1</v>
+      </c>
       <c r="S23" t="n">
         <v>0</v>
       </c>
@@ -3512,23 +3272,47 @@
       <c r="AL23" t="inlineStr"/>
       <c r="AM23" t="inlineStr"/>
       <c r="AN23" t="inlineStr"/>
-      <c r="AO23" t="inlineStr"/>
-      <c r="AP23" t="inlineStr"/>
-      <c r="AQ23" t="inlineStr"/>
+      <c r="AO23" t="n">
+        <v>-8.536363636363632</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>-0.2303030303030198</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>-6.271212121212116</v>
+      </c>
       <c r="AR23" t="inlineStr"/>
-      <c r="AS23" t="inlineStr"/>
-      <c r="AT23" t="inlineStr"/>
+      <c r="AS23" t="n">
+        <v>-4060136.67850181</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>-0.7090909090909085</v>
+      </c>
       <c r="AU23" t="inlineStr"/>
-      <c r="AV23" t="inlineStr"/>
-      <c r="AW23" t="inlineStr"/>
-      <c r="AX23" t="inlineStr"/>
+      <c r="AV23" t="n">
+        <v>-0.4176127819548583</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>-0.4119423558897246</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>-1.751515151515147</v>
+      </c>
       <c r="AY23" t="inlineStr"/>
-      <c r="AZ23" t="inlineStr"/>
-      <c r="BA23" t="inlineStr"/>
+      <c r="AZ23" t="n">
+        <v>-7719469.696969695</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>-6.725136104149286</v>
+      </c>
       <c r="BB23" t="inlineStr"/>
       <c r="BC23" t="inlineStr"/>
-      <c r="BD23" t="inlineStr"/>
-      <c r="BE23" t="inlineStr"/>
+      <c r="BD23" t="n">
+        <v>-6.363708576998064</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>1.088263018657749</v>
+      </c>
       <c r="BF23" t="n">
         <v>0</v>
       </c>
@@ -3536,32 +3320,32 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>jFMCm08e</t>
+          <t>MZjh9ghT</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>45522.4375</v>
+        <v>45521.4375</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">aytekin d 
+          <t xml:space="preserve">zwayer f 
   ger </t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">jahnstadion regensburg
-  regensburg </t>
+          <t xml:space="preserve">stadion an der hafenstrasse
+  essen </t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>UiCmEP56</t>
+          <t>EB0xsr77</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>8Y2m6ADe</t>
+          <t>KbS1suSm</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3586,23 +3370,15 @@
           <t>dfb pokal</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>t0ZPdkUl</t>
-        </is>
-      </c>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
-          <t>xzRzG0VI</t>
-        </is>
-      </c>
-      <c r="O24" t="n">
-        <v>1</v>
-      </c>
+          <t>pfoInmcq</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="n">
         <v>0</v>
@@ -3652,32 +3428,32 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>AiJ3kset</t>
+          <t>tbKZHNz1</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>45522.33333333334</v>
+        <v>45521.4375</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">jollenbeck m 
+          <t xml:space="preserve">schroder r 
   ger </t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">friedrich ludwig jahn sportpark
-  berlin </t>
+          <t xml:space="preserve">audi sportpark
+  ingolstadt </t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>UNr2EUfd</t>
+          <t>ne5QkLtB</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>fTVNku3I</t>
+          <t>naWckLmC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3705,12 +3481,16 @@
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2VSFgl3c</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr"/>
+          <t>4bJLk19p</t>
+        </is>
+      </c>
+      <c r="O25" t="n">
+        <v>-5</v>
+      </c>
       <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
+      <c r="Q25" t="n">
+        <v>-2</v>
+      </c>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="n">
         <v>0</v>
@@ -3760,32 +3540,32 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>6q2yrHgU</t>
+          <t>vyk5gjdE</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>45522.33333333334</v>
+        <v>45521.4375</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">braun r 
+          <t xml:space="preserve">dingert c 
   ger </t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">ludwigspark stadion
-  saarbrucken </t>
+          <t xml:space="preserve">volksstadion greifswald
+  greifswald </t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>fLbhmJ5l</t>
+          <t>Q1yNyI5t</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>6FDqshzF</t>
+          <t>pzHW4oaE</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3813,16 +3593,12 @@
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
-          <t>tO31cZrF</t>
-        </is>
-      </c>
-      <c r="O26" t="n">
-        <v>1</v>
-      </c>
+          <t>l0fHXMdE</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="n">
         <v>0</v>
@@ -3843,9 +3619,7 @@
       <c r="AG26" t="inlineStr"/>
       <c r="AH26" t="inlineStr"/>
       <c r="AI26" t="inlineStr"/>
-      <c r="AJ26" t="n">
-        <v>66</v>
-      </c>
+      <c r="AJ26" t="inlineStr"/>
       <c r="AK26" t="inlineStr"/>
       <c r="AL26" t="inlineStr"/>
       <c r="AM26" t="inlineStr"/>
@@ -3874,45 +3648,45 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>fcxqFy2l</t>
+          <t>bF2q76Mr</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>45521.64583333334</v>
+        <v>45521.4375</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">schlager d 
+          <t xml:space="preserve">stieler t 
   ger </t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">bayarena
-  leverkusen </t>
+          <t xml:space="preserve">ostalb arena
+  aalen </t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>4jcj2zMd</t>
+          <t>Oh2C15j0</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>nJQmYp1B</t>
+          <t>0Ija0Ej9</t>
         </is>
       </c>
       <c r="G27" t="n">
         <v>59</v>
       </c>
       <c r="H27" t="n">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="I27" t="n">
         <v>1</v>
       </c>
       <c r="J27" t="n">
-        <v>2024</v>
+        <v>20242025</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -3921,31 +3695,23 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>super cup</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>2BYSk4KO</t>
-        </is>
-      </c>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
-          <t>M5BRZDsC</t>
+          <t>SQrxFAMl</t>
         </is>
       </c>
       <c r="O27" t="n">
-        <v>27</v>
-      </c>
-      <c r="P27" t="n">
-        <v>4</v>
-      </c>
+        <v>-1</v>
+      </c>
+      <c r="P27" t="inlineStr"/>
       <c r="Q27" t="n">
-        <v>18</v>
-      </c>
-      <c r="R27" t="n">
-        <v>3</v>
-      </c>
+        <v>-1</v>
+      </c>
+      <c r="R27" t="inlineStr"/>
       <c r="S27" t="n">
         <v>0</v>
       </c>
@@ -3969,48 +3735,24 @@
       <c r="AK27" t="inlineStr"/>
       <c r="AL27" t="inlineStr"/>
       <c r="AM27" t="inlineStr"/>
-      <c r="AN27" t="n">
-        <v>1.23030303030303</v>
-      </c>
+      <c r="AN27" t="inlineStr"/>
       <c r="AO27" t="inlineStr"/>
       <c r="AP27" t="inlineStr"/>
       <c r="AQ27" t="inlineStr"/>
-      <c r="AR27" t="n">
-        <v>7.566349990589131</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>5.13333333333334</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>-1.175290510982194</v>
-      </c>
+      <c r="AR27" t="inlineStr"/>
+      <c r="AS27" t="inlineStr"/>
+      <c r="AT27" t="inlineStr"/>
       <c r="AU27" t="inlineStr"/>
       <c r="AV27" t="inlineStr"/>
-      <c r="AW27" t="n">
-        <v>30827197.30905896</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>8.734170473794975</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>0.7535353535353693</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>19594646.46464647</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>0.5272727272727271</v>
-      </c>
+      <c r="AW27" t="inlineStr"/>
+      <c r="AX27" t="inlineStr"/>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr"/>
+      <c r="BA27" t="inlineStr"/>
       <c r="BB27" t="inlineStr"/>
-      <c r="BC27" t="n">
-        <v>-1.531745561202083</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>4.878787878787875</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>0.5169583326203877</v>
-      </c>
+      <c r="BC27" t="inlineStr"/>
+      <c r="BD27" t="inlineStr"/>
+      <c r="BE27" t="inlineStr"/>
       <c r="BF27" t="n">
         <v>0</v>
       </c>
@@ -4018,32 +3760,32 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>8CpxDyg4</t>
+          <t>Kj4sifWp</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>45521.54166666666</v>
+        <v>45521.33333333334</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">siebert d 
+          <t xml:space="preserve">hempel r 
   ger </t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadion lohmuhle
-  lubeck </t>
+          <t xml:space="preserve">bruchwegstadion
+  mainz </t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>I1Vk6k3R</t>
+          <t>WzEYqEyg</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>nP1i5US1</t>
+          <t>CCQGbik8</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4071,7 +3813,7 @@
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
-          <t>MDhPV0RQ</t>
+          <t>pdPRS0me</t>
         </is>
       </c>
       <c r="O28" t="inlineStr"/>
@@ -4126,32 +3868,32 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>hzyf0b9b</t>
+          <t>0K2qBFNG</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>45521.54166666666</v>
+        <v>45521.33333333334</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">sather a 
+          <t xml:space="preserve">schlager d 
   ger </t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">new tivoli
-  aachen </t>
+          <t xml:space="preserve">erzgebirgsstadion
+  aue </t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>j3PKcB4E</t>
+          <t>vsXIDreP</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>63WsD2ei</t>
+          <t>88HSzjDr</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4179,12 +3921,16 @@
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
-          <t>A15eUM4C</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr"/>
+          <t>M5BRZDsC</t>
+        </is>
+      </c>
+      <c r="O29" t="n">
+        <v>-3</v>
+      </c>
       <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
+      <c r="Q29" t="n">
+        <v>-2</v>
+      </c>
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="n">
         <v>0</v>
@@ -4234,32 +3980,32 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>CpiTEcOi</t>
+          <t>lONsG15D</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>45521.54166666666</v>
+        <v>45520.65625</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">bacher m 
+          <t xml:space="preserve">fritz m 
   ger </t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">schuco arena
-  bielefeld </t>
+          <t xml:space="preserve">donaustadion
+  ulm </t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>pp38UXK8</t>
+          <t>tbC3EcQn</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>dfNCCCzS</t>
+          <t>nVp0wiqd</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4284,24 +4030,24 @@
           <t>dfb pokal</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>QevvB2nf</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>zyLSrbZQ</t>
+          <t>CQTUFgPk</t>
         </is>
       </c>
       <c r="O30" t="n">
-        <v>3</v>
-      </c>
-      <c r="P30" t="n">
         <v>-2</v>
       </c>
+      <c r="P30" t="inlineStr"/>
       <c r="Q30" t="n">
-        <v>1</v>
-      </c>
-      <c r="R30" t="n">
         <v>-1</v>
       </c>
+      <c r="R30" t="inlineStr"/>
       <c r="S30" t="n">
         <v>0</v>
       </c>
@@ -4350,32 +4096,32 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>tbKZHNz1</t>
+          <t>EF8gXauC</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>45521.4375</v>
+        <v>45520.54166666666</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">schroder r 
+          <t xml:space="preserve">fritz m 
   ger </t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">audi sportpark
-  ingolstadt </t>
+          <t xml:space="preserve">flyeralarm arena
+  wurzburger </t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>ne5QkLtB</t>
+          <t>nVM1YUFj</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>naWckLmC</t>
+          <t>hQAtP9Sl</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4403,15 +4149,15 @@
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
-          <t>4bJLk19p</t>
+          <t>CQTUFgPk</t>
         </is>
       </c>
       <c r="O31" t="n">
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="n">
@@ -4462,32 +4208,32 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>vyk5gjdE</t>
+          <t>hIsO3XFj</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>45521.4375</v>
+        <v>45520.54166666666</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">dingert c 
+          <t xml:space="preserve">willenborg f 
   ger </t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">volksstadion greifswald
-  greifswald </t>
+          <t xml:space="preserve">brita arena
+  wiesbaden </t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Q1yNyI5t</t>
+          <t>ObxFt3lm</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>pzHW4oaE</t>
+          <t>EuakNmc1</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4512,15 +4258,23 @@
           <t>dfb pokal</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>QTAUlvUP</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>l0fHXMdE</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr"/>
+          <t>vZA6VYpf</t>
+        </is>
+      </c>
+      <c r="O32" t="n">
+        <v>-4</v>
+      </c>
       <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
+      <c r="Q32" t="n">
+        <v>-2</v>
+      </c>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="n">
         <v>0</v>
@@ -4546,56 +4300,80 @@
       <c r="AL32" t="inlineStr"/>
       <c r="AM32" t="inlineStr"/>
       <c r="AN32" t="inlineStr"/>
-      <c r="AO32" t="inlineStr"/>
-      <c r="AP32" t="inlineStr"/>
-      <c r="AQ32" t="inlineStr"/>
+      <c r="AO32" t="n">
+        <v>-7.22727272727272</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>2.738636363636346</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>-9.025000000000006</v>
+      </c>
       <c r="AR32" t="inlineStr"/>
-      <c r="AS32" t="inlineStr"/>
-      <c r="AT32" t="inlineStr"/>
+      <c r="AS32" t="n">
+        <v>-3581285.962301588</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>-0.5727272727272723</v>
+      </c>
       <c r="AU32" t="inlineStr"/>
-      <c r="AV32" t="inlineStr"/>
-      <c r="AW32" t="inlineStr"/>
-      <c r="AX32" t="inlineStr"/>
+      <c r="AV32" t="n">
+        <v>-2.321775793650772</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>-0.5224206349206351</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>0.4568181818181891</v>
+      </c>
       <c r="AY32" t="inlineStr"/>
-      <c r="AZ32" t="inlineStr"/>
-      <c r="BA32" t="inlineStr"/>
+      <c r="AZ32" t="n">
+        <v>-5601534.090909092</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>-7.431249999999977</v>
+      </c>
       <c r="BB32" t="inlineStr"/>
       <c r="BC32" t="inlineStr"/>
-      <c r="BD32" t="inlineStr"/>
-      <c r="BE32" t="inlineStr"/>
+      <c r="BD32" t="n">
+        <v>-7.606001984126991</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>-1.994196428571424</v>
+      </c>
       <c r="BF32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>bF2q76Mr</t>
+          <t>pWQQJq6l</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>45521.4375</v>
+        <v>45520.54166666666</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">stieler t 
+          <t xml:space="preserve">aytekin d 
   ger </t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">ostalb arena
-  aalen </t>
+          <t xml:space="preserve">leuna chemie stadion
+  halle </t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Oh2C15j0</t>
+          <t>boX3cIQa</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0Ija0Ej9</t>
+          <t>ILyJuN3g</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4623,16 +4401,12 @@
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
-          <t>SQrxFAMl</t>
-        </is>
-      </c>
-      <c r="O33" t="n">
-        <v>-1</v>
-      </c>
+          <t>QHesBmSQ</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="n">
-        <v>-1</v>
-      </c>
+      <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="n">
         <v>0</v>
@@ -4679,1062 +4453,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>8QPARz8c</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="n">
-        <v>45521.4375</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">welz t 
-  ger </t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ms technologie arena
-  villingen schwenningen </t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>lKLJUxeT</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>KWixEVWi</t>
-        </is>
-      </c>
-      <c r="G34" t="n">
-        <v>59</v>
-      </c>
-      <c r="H34" t="n">
-        <v>593</v>
-      </c>
-      <c r="I34" t="n">
-        <v>1</v>
-      </c>
-      <c r="J34" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>lGJdeemM</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
-      <c r="W34" t="inlineStr"/>
-      <c r="X34" t="inlineStr"/>
-      <c r="Y34" t="inlineStr"/>
-      <c r="Z34" t="inlineStr"/>
-      <c r="AA34" t="inlineStr"/>
-      <c r="AB34" t="inlineStr"/>
-      <c r="AC34" t="inlineStr"/>
-      <c r="AD34" t="inlineStr"/>
-      <c r="AE34" t="inlineStr"/>
-      <c r="AF34" t="inlineStr"/>
-      <c r="AG34" t="inlineStr"/>
-      <c r="AH34" t="inlineStr"/>
-      <c r="AI34" t="inlineStr"/>
-      <c r="AJ34" t="inlineStr"/>
-      <c r="AK34" t="inlineStr"/>
-      <c r="AL34" t="inlineStr"/>
-      <c r="AM34" t="inlineStr"/>
-      <c r="AN34" t="inlineStr"/>
-      <c r="AO34" t="inlineStr"/>
-      <c r="AP34" t="inlineStr"/>
-      <c r="AQ34" t="inlineStr"/>
-      <c r="AR34" t="inlineStr"/>
-      <c r="AS34" t="inlineStr"/>
-      <c r="AT34" t="inlineStr"/>
-      <c r="AU34" t="inlineStr"/>
-      <c r="AV34" t="inlineStr"/>
-      <c r="AW34" t="inlineStr"/>
-      <c r="AX34" t="inlineStr"/>
-      <c r="AY34" t="inlineStr"/>
-      <c r="AZ34" t="inlineStr"/>
-      <c r="BA34" t="inlineStr"/>
-      <c r="BB34" t="inlineStr"/>
-      <c r="BC34" t="inlineStr"/>
-      <c r="BD34" t="inlineStr"/>
-      <c r="BE34" t="inlineStr"/>
-      <c r="BF34" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>f1nnRRDE</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="n">
-        <v>45521.4375</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dingert c 
-  ger </t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadion an der bremer bruck
-  osnabruck </t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>88Xgj1Y5</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>fiEQZ7C7</t>
-        </is>
-      </c>
-      <c r="G35" t="n">
-        <v>59</v>
-      </c>
-      <c r="H35" t="n">
-        <v>593</v>
-      </c>
-      <c r="I35" t="n">
-        <v>1</v>
-      </c>
-      <c r="J35" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>lxrr7DgN</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>l0fHXMdE</t>
-        </is>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>1</v>
-      </c>
-      <c r="R35" t="n">
-        <v>-1</v>
-      </c>
-      <c r="S35" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
-      <c r="W35" t="inlineStr"/>
-      <c r="X35" t="inlineStr"/>
-      <c r="Y35" t="inlineStr"/>
-      <c r="Z35" t="inlineStr"/>
-      <c r="AA35" t="inlineStr"/>
-      <c r="AB35" t="inlineStr"/>
-      <c r="AC35" t="inlineStr"/>
-      <c r="AD35" t="inlineStr"/>
-      <c r="AE35" t="inlineStr"/>
-      <c r="AF35" t="inlineStr"/>
-      <c r="AG35" t="inlineStr"/>
-      <c r="AH35" t="inlineStr"/>
-      <c r="AI35" t="inlineStr"/>
-      <c r="AJ35" t="inlineStr"/>
-      <c r="AK35" t="inlineStr"/>
-      <c r="AL35" t="inlineStr"/>
-      <c r="AM35" t="inlineStr"/>
-      <c r="AN35" t="n">
-        <v>-1.751515151515147</v>
-      </c>
-      <c r="AO35" t="inlineStr"/>
-      <c r="AP35" t="inlineStr"/>
-      <c r="AQ35" t="inlineStr"/>
-      <c r="AR35" t="n">
-        <v>-6.363708576998064</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>-8.536363636363632</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>-0.4176127819548583</v>
-      </c>
-      <c r="AU35" t="inlineStr"/>
-      <c r="AV35" t="inlineStr"/>
-      <c r="AW35" t="n">
-        <v>-4060136.67850181</v>
-      </c>
-      <c r="AX35" t="n">
-        <v>-6.725136104149286</v>
-      </c>
-      <c r="AY35" t="n">
-        <v>-0.2303030303030198</v>
-      </c>
-      <c r="AZ35" t="n">
-        <v>-7719469.696969695</v>
-      </c>
-      <c r="BA35" t="n">
-        <v>-0.7090909090909085</v>
-      </c>
-      <c r="BB35" t="inlineStr"/>
-      <c r="BC35" t="n">
-        <v>1.088263018657749</v>
-      </c>
-      <c r="BD35" t="n">
-        <v>-6.271212121212116</v>
-      </c>
-      <c r="BE35" t="n">
-        <v>-0.4119423558897246</v>
-      </c>
-      <c r="BF35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>MZjh9ghT</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="n">
-        <v>45521.4375</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">zwayer f 
-  ger </t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadion an der hafenstrasse
-  essen </t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>EB0xsr77</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>KbS1suSm</t>
-        </is>
-      </c>
-      <c r="G36" t="n">
-        <v>59</v>
-      </c>
-      <c r="H36" t="n">
-        <v>593</v>
-      </c>
-      <c r="I36" t="n">
-        <v>1</v>
-      </c>
-      <c r="J36" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>pfoInmcq</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
-      <c r="W36" t="inlineStr"/>
-      <c r="X36" t="inlineStr"/>
-      <c r="Y36" t="inlineStr"/>
-      <c r="Z36" t="inlineStr"/>
-      <c r="AA36" t="inlineStr"/>
-      <c r="AB36" t="inlineStr"/>
-      <c r="AC36" t="inlineStr"/>
-      <c r="AD36" t="inlineStr"/>
-      <c r="AE36" t="inlineStr"/>
-      <c r="AF36" t="inlineStr"/>
-      <c r="AG36" t="inlineStr"/>
-      <c r="AH36" t="inlineStr"/>
-      <c r="AI36" t="inlineStr"/>
-      <c r="AJ36" t="inlineStr"/>
-      <c r="AK36" t="inlineStr"/>
-      <c r="AL36" t="inlineStr"/>
-      <c r="AM36" t="inlineStr"/>
-      <c r="AN36" t="inlineStr"/>
-      <c r="AO36" t="inlineStr"/>
-      <c r="AP36" t="inlineStr"/>
-      <c r="AQ36" t="inlineStr"/>
-      <c r="AR36" t="inlineStr"/>
-      <c r="AS36" t="inlineStr"/>
-      <c r="AT36" t="inlineStr"/>
-      <c r="AU36" t="inlineStr"/>
-      <c r="AV36" t="inlineStr"/>
-      <c r="AW36" t="inlineStr"/>
-      <c r="AX36" t="inlineStr"/>
-      <c r="AY36" t="inlineStr"/>
-      <c r="AZ36" t="inlineStr"/>
-      <c r="BA36" t="inlineStr"/>
-      <c r="BB36" t="inlineStr"/>
-      <c r="BC36" t="inlineStr"/>
-      <c r="BD36" t="inlineStr"/>
-      <c r="BE36" t="inlineStr"/>
-      <c r="BF36" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>Kj4sifWp</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="n">
-        <v>45521.33333333334</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hempel r 
-  ger </t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bruchwegstadion
-  mainz </t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>WzEYqEyg</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>CCQGbik8</t>
-        </is>
-      </c>
-      <c r="G37" t="n">
-        <v>59</v>
-      </c>
-      <c r="H37" t="n">
-        <v>593</v>
-      </c>
-      <c r="I37" t="n">
-        <v>1</v>
-      </c>
-      <c r="J37" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>pdPRS0me</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr"/>
-      <c r="S37" t="n">
-        <v>0</v>
-      </c>
-      <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr"/>
-      <c r="W37" t="inlineStr"/>
-      <c r="X37" t="inlineStr"/>
-      <c r="Y37" t="inlineStr"/>
-      <c r="Z37" t="inlineStr"/>
-      <c r="AA37" t="inlineStr"/>
-      <c r="AB37" t="inlineStr"/>
-      <c r="AC37" t="inlineStr"/>
-      <c r="AD37" t="inlineStr"/>
-      <c r="AE37" t="inlineStr"/>
-      <c r="AF37" t="inlineStr"/>
-      <c r="AG37" t="inlineStr"/>
-      <c r="AH37" t="inlineStr"/>
-      <c r="AI37" t="inlineStr"/>
-      <c r="AJ37" t="inlineStr"/>
-      <c r="AK37" t="inlineStr"/>
-      <c r="AL37" t="inlineStr"/>
-      <c r="AM37" t="inlineStr"/>
-      <c r="AN37" t="inlineStr"/>
-      <c r="AO37" t="inlineStr"/>
-      <c r="AP37" t="inlineStr"/>
-      <c r="AQ37" t="inlineStr"/>
-      <c r="AR37" t="inlineStr"/>
-      <c r="AS37" t="inlineStr"/>
-      <c r="AT37" t="inlineStr"/>
-      <c r="AU37" t="inlineStr"/>
-      <c r="AV37" t="inlineStr"/>
-      <c r="AW37" t="inlineStr"/>
-      <c r="AX37" t="inlineStr"/>
-      <c r="AY37" t="inlineStr"/>
-      <c r="AZ37" t="inlineStr"/>
-      <c r="BA37" t="inlineStr"/>
-      <c r="BB37" t="inlineStr"/>
-      <c r="BC37" t="inlineStr"/>
-      <c r="BD37" t="inlineStr"/>
-      <c r="BE37" t="inlineStr"/>
-      <c r="BF37" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>0K2qBFNG</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="n">
-        <v>45521.33333333334</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">schlager d 
-  ger </t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">erzgebirgsstadion
-  aue </t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>vsXIDreP</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>88HSzjDr</t>
-        </is>
-      </c>
-      <c r="G38" t="n">
-        <v>59</v>
-      </c>
-      <c r="H38" t="n">
-        <v>593</v>
-      </c>
-      <c r="I38" t="n">
-        <v>1</v>
-      </c>
-      <c r="J38" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>M5BRZDsC</t>
-        </is>
-      </c>
-      <c r="O38" t="n">
-        <v>-3</v>
-      </c>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="n">
-        <v>-2</v>
-      </c>
-      <c r="R38" t="inlineStr"/>
-      <c r="S38" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr"/>
-      <c r="W38" t="inlineStr"/>
-      <c r="X38" t="inlineStr"/>
-      <c r="Y38" t="inlineStr"/>
-      <c r="Z38" t="inlineStr"/>
-      <c r="AA38" t="inlineStr"/>
-      <c r="AB38" t="inlineStr"/>
-      <c r="AC38" t="inlineStr"/>
-      <c r="AD38" t="inlineStr"/>
-      <c r="AE38" t="inlineStr"/>
-      <c r="AF38" t="inlineStr"/>
-      <c r="AG38" t="inlineStr"/>
-      <c r="AH38" t="inlineStr"/>
-      <c r="AI38" t="inlineStr"/>
-      <c r="AJ38" t="inlineStr"/>
-      <c r="AK38" t="inlineStr"/>
-      <c r="AL38" t="inlineStr"/>
-      <c r="AM38" t="inlineStr"/>
-      <c r="AN38" t="inlineStr"/>
-      <c r="AO38" t="inlineStr"/>
-      <c r="AP38" t="inlineStr"/>
-      <c r="AQ38" t="inlineStr"/>
-      <c r="AR38" t="inlineStr"/>
-      <c r="AS38" t="inlineStr"/>
-      <c r="AT38" t="inlineStr"/>
-      <c r="AU38" t="inlineStr"/>
-      <c r="AV38" t="inlineStr"/>
-      <c r="AW38" t="inlineStr"/>
-      <c r="AX38" t="inlineStr"/>
-      <c r="AY38" t="inlineStr"/>
-      <c r="AZ38" t="inlineStr"/>
-      <c r="BA38" t="inlineStr"/>
-      <c r="BB38" t="inlineStr"/>
-      <c r="BC38" t="inlineStr"/>
-      <c r="BD38" t="inlineStr"/>
-      <c r="BE38" t="inlineStr"/>
-      <c r="BF38" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>lONsG15D</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="n">
-        <v>45520.65625</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fritz m 
-  ger </t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">donaustadion
-  ulm </t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>tbC3EcQn</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>nVp0wiqd</t>
-        </is>
-      </c>
-      <c r="G39" t="n">
-        <v>59</v>
-      </c>
-      <c r="H39" t="n">
-        <v>593</v>
-      </c>
-      <c r="I39" t="n">
-        <v>1</v>
-      </c>
-      <c r="J39" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>QevvB2nf</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>CQTUFgPk</t>
-        </is>
-      </c>
-      <c r="O39" t="n">
-        <v>-2</v>
-      </c>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="n">
-        <v>-1</v>
-      </c>
-      <c r="R39" t="inlineStr"/>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr"/>
-      <c r="V39" t="inlineStr"/>
-      <c r="W39" t="inlineStr"/>
-      <c r="X39" t="inlineStr"/>
-      <c r="Y39" t="inlineStr"/>
-      <c r="Z39" t="inlineStr"/>
-      <c r="AA39" t="inlineStr"/>
-      <c r="AB39" t="inlineStr"/>
-      <c r="AC39" t="inlineStr"/>
-      <c r="AD39" t="inlineStr"/>
-      <c r="AE39" t="inlineStr"/>
-      <c r="AF39" t="inlineStr"/>
-      <c r="AG39" t="inlineStr"/>
-      <c r="AH39" t="inlineStr"/>
-      <c r="AI39" t="inlineStr"/>
-      <c r="AJ39" t="inlineStr"/>
-      <c r="AK39" t="inlineStr"/>
-      <c r="AL39" t="inlineStr"/>
-      <c r="AM39" t="inlineStr"/>
-      <c r="AN39" t="inlineStr"/>
-      <c r="AO39" t="inlineStr"/>
-      <c r="AP39" t="inlineStr"/>
-      <c r="AQ39" t="inlineStr"/>
-      <c r="AR39" t="inlineStr"/>
-      <c r="AS39" t="inlineStr"/>
-      <c r="AT39" t="inlineStr"/>
-      <c r="AU39" t="inlineStr"/>
-      <c r="AV39" t="inlineStr"/>
-      <c r="AW39" t="inlineStr"/>
-      <c r="AX39" t="inlineStr"/>
-      <c r="AY39" t="inlineStr"/>
-      <c r="AZ39" t="inlineStr"/>
-      <c r="BA39" t="inlineStr"/>
-      <c r="BB39" t="inlineStr"/>
-      <c r="BC39" t="inlineStr"/>
-      <c r="BD39" t="inlineStr"/>
-      <c r="BE39" t="inlineStr"/>
-      <c r="BF39" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>hIsO3XFj</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="n">
-        <v>45520.54166666666</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">willenborg f 
-  ger </t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">brita arena
-  wiesbaden </t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>ObxFt3lm</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>EuakNmc1</t>
-        </is>
-      </c>
-      <c r="G40" t="n">
-        <v>59</v>
-      </c>
-      <c r="H40" t="n">
-        <v>593</v>
-      </c>
-      <c r="I40" t="n">
-        <v>1</v>
-      </c>
-      <c r="J40" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>QTAUlvUP</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>vZA6VYpf</t>
-        </is>
-      </c>
-      <c r="O40" t="n">
-        <v>-4</v>
-      </c>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="n">
-        <v>-2</v>
-      </c>
-      <c r="R40" t="inlineStr"/>
-      <c r="S40" t="n">
-        <v>0</v>
-      </c>
-      <c r="T40" t="inlineStr"/>
-      <c r="U40" t="inlineStr"/>
-      <c r="V40" t="inlineStr"/>
-      <c r="W40" t="inlineStr"/>
-      <c r="X40" t="inlineStr"/>
-      <c r="Y40" t="inlineStr"/>
-      <c r="Z40" t="inlineStr"/>
-      <c r="AA40" t="inlineStr"/>
-      <c r="AB40" t="inlineStr"/>
-      <c r="AC40" t="inlineStr"/>
-      <c r="AD40" t="inlineStr"/>
-      <c r="AE40" t="inlineStr"/>
-      <c r="AF40" t="inlineStr"/>
-      <c r="AG40" t="inlineStr"/>
-      <c r="AH40" t="inlineStr"/>
-      <c r="AI40" t="inlineStr"/>
-      <c r="AJ40" t="inlineStr"/>
-      <c r="AK40" t="inlineStr"/>
-      <c r="AL40" t="inlineStr"/>
-      <c r="AM40" t="inlineStr"/>
-      <c r="AN40" t="n">
-        <v>0.4568181818181891</v>
-      </c>
-      <c r="AO40" t="inlineStr"/>
-      <c r="AP40" t="inlineStr"/>
-      <c r="AQ40" t="inlineStr"/>
-      <c r="AR40" t="n">
-        <v>-7.606001984126991</v>
-      </c>
-      <c r="AS40" t="n">
-        <v>-7.22727272727272</v>
-      </c>
-      <c r="AT40" t="n">
-        <v>-2.321775793650772</v>
-      </c>
-      <c r="AU40" t="inlineStr"/>
-      <c r="AV40" t="inlineStr"/>
-      <c r="AW40" t="n">
-        <v>-3581285.962301588</v>
-      </c>
-      <c r="AX40" t="n">
-        <v>-7.431249999999977</v>
-      </c>
-      <c r="AY40" t="n">
-        <v>2.738636363636346</v>
-      </c>
-      <c r="AZ40" t="n">
-        <v>-5601534.090909092</v>
-      </c>
-      <c r="BA40" t="n">
-        <v>-0.5727272727272723</v>
-      </c>
-      <c r="BB40" t="inlineStr"/>
-      <c r="BC40" t="n">
-        <v>-1.994196428571424</v>
-      </c>
-      <c r="BD40" t="n">
-        <v>-9.025000000000006</v>
-      </c>
-      <c r="BE40" t="n">
-        <v>-0.5224206349206351</v>
-      </c>
-      <c r="BF40" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>pWQQJq6l</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="n">
-        <v>45520.54166666666</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">aytekin d 
-  ger </t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">leuna chemie stadion
-  halle </t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>boX3cIQa</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>ILyJuN3g</t>
-        </is>
-      </c>
-      <c r="G41" t="n">
-        <v>59</v>
-      </c>
-      <c r="H41" t="n">
-        <v>593</v>
-      </c>
-      <c r="I41" t="n">
-        <v>1</v>
-      </c>
-      <c r="J41" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>QHesBmSQ</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr"/>
-      <c r="S41" t="n">
-        <v>0</v>
-      </c>
-      <c r="T41" t="inlineStr"/>
-      <c r="U41" t="inlineStr"/>
-      <c r="V41" t="inlineStr"/>
-      <c r="W41" t="inlineStr"/>
-      <c r="X41" t="inlineStr"/>
-      <c r="Y41" t="inlineStr"/>
-      <c r="Z41" t="inlineStr"/>
-      <c r="AA41" t="inlineStr"/>
-      <c r="AB41" t="inlineStr"/>
-      <c r="AC41" t="inlineStr"/>
-      <c r="AD41" t="inlineStr"/>
-      <c r="AE41" t="inlineStr"/>
-      <c r="AF41" t="inlineStr"/>
-      <c r="AG41" t="inlineStr"/>
-      <c r="AH41" t="inlineStr"/>
-      <c r="AI41" t="inlineStr"/>
-      <c r="AJ41" t="inlineStr"/>
-      <c r="AK41" t="inlineStr"/>
-      <c r="AL41" t="inlineStr"/>
-      <c r="AM41" t="inlineStr"/>
-      <c r="AN41" t="inlineStr"/>
-      <c r="AO41" t="inlineStr"/>
-      <c r="AP41" t="inlineStr"/>
-      <c r="AQ41" t="inlineStr"/>
-      <c r="AR41" t="inlineStr"/>
-      <c r="AS41" t="inlineStr"/>
-      <c r="AT41" t="inlineStr"/>
-      <c r="AU41" t="inlineStr"/>
-      <c r="AV41" t="inlineStr"/>
-      <c r="AW41" t="inlineStr"/>
-      <c r="AX41" t="inlineStr"/>
-      <c r="AY41" t="inlineStr"/>
-      <c r="AZ41" t="inlineStr"/>
-      <c r="BA41" t="inlineStr"/>
-      <c r="BB41" t="inlineStr"/>
-      <c r="BC41" t="inlineStr"/>
-      <c r="BD41" t="inlineStr"/>
-      <c r="BE41" t="inlineStr"/>
-      <c r="BF41" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="inlineStr">
-        <is>
-          <t>EF8gXauC</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="n">
-        <v>45520.54166666666</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fritz m 
-  ger </t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">flyeralarm arena
-  wurzburger </t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>nVM1YUFj</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>hQAtP9Sl</t>
-        </is>
-      </c>
-      <c r="G42" t="n">
-        <v>59</v>
-      </c>
-      <c r="H42" t="n">
-        <v>593</v>
-      </c>
-      <c r="I42" t="n">
-        <v>1</v>
-      </c>
-      <c r="J42" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>CQTUFgPk</t>
-        </is>
-      </c>
-      <c r="O42" t="n">
-        <v>-1</v>
-      </c>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="n">
-        <v>-1</v>
-      </c>
-      <c r="R42" t="inlineStr"/>
-      <c r="S42" t="n">
-        <v>0</v>
-      </c>
-      <c r="T42" t="inlineStr"/>
-      <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr"/>
-      <c r="W42" t="inlineStr"/>
-      <c r="X42" t="inlineStr"/>
-      <c r="Y42" t="inlineStr"/>
-      <c r="Z42" t="inlineStr"/>
-      <c r="AA42" t="inlineStr"/>
-      <c r="AB42" t="inlineStr"/>
-      <c r="AC42" t="inlineStr"/>
-      <c r="AD42" t="inlineStr"/>
-      <c r="AE42" t="inlineStr"/>
-      <c r="AF42" t="inlineStr"/>
-      <c r="AG42" t="inlineStr"/>
-      <c r="AH42" t="inlineStr"/>
-      <c r="AI42" t="inlineStr"/>
-      <c r="AJ42" t="inlineStr"/>
-      <c r="AK42" t="inlineStr"/>
-      <c r="AL42" t="inlineStr"/>
-      <c r="AM42" t="inlineStr"/>
-      <c r="AN42" t="inlineStr"/>
-      <c r="AO42" t="inlineStr"/>
-      <c r="AP42" t="inlineStr"/>
-      <c r="AQ42" t="inlineStr"/>
-      <c r="AR42" t="inlineStr"/>
-      <c r="AS42" t="inlineStr"/>
-      <c r="AT42" t="inlineStr"/>
-      <c r="AU42" t="inlineStr"/>
-      <c r="AV42" t="inlineStr"/>
-      <c r="AW42" t="inlineStr"/>
-      <c r="AX42" t="inlineStr"/>
-      <c r="AY42" t="inlineStr"/>
-      <c r="AZ42" t="inlineStr"/>
-      <c r="BA42" t="inlineStr"/>
-      <c r="BB42" t="inlineStr"/>
-      <c r="BC42" t="inlineStr"/>
-      <c r="BD42" t="inlineStr"/>
-      <c r="BE42" t="inlineStr"/>
-      <c r="BF42" t="n">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/germany/p6_deployment/data_preparation/df_constructed.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_constructed.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF33"/>
+  <dimension ref="A1:BF41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -525,84 +525,84 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_n_matches_last_days</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days_against</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_goal_attempts</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts_against</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days_against</t>
-        </is>
-      </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_ball_possession</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession_against</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points_against</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_expected_goals_(xg)</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_expected_goals_(xg)_against</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls_against</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goals</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goals_against</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession_against</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls_against</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points_against</t>
-        </is>
-      </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_away</t>
@@ -620,92 +620,92 @@
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
           <t>dif_sum_rat_player_miss</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
         </is>
       </c>
       <c r="BE1" s="1" t="inlineStr">
@@ -722,32 +722,32 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>zuzbQnCF</t>
+          <t>AuVMGZvJ</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45527.64583333334</v>
+        <v>45529.52083333334</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">dankert b 
+          <t xml:space="preserve">welz t 
   ger </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">borussia park
-  monchengladbach </t>
+          <t xml:space="preserve">millerntor stadion
+  hamburg </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>88HSzjDr</t>
+          <t>ILyJuN3g</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>4jcj2zMd</t>
+          <t>KWixEVWi</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -774,25 +774,25 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>GzfvcwRj</t>
+          <t>QTAUlvUP</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>hAcTWKKN</t>
+          <t>lGJdeemM</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>-19</v>
+        <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="Q2" t="n">
-        <v>-9</v>
+        <v>4</v>
       </c>
       <c r="R2" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -816,48 +816,48 @@
       <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
+      <c r="AM2" t="n">
+        <v>0.1156569526170586</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>-1.638383838383845</v>
+      </c>
       <c r="AO2" t="n">
-        <v>-6.13494949494951</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>-0.684242424242484</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="n">
-        <v>-5.948686868686863</v>
-      </c>
-      <c r="AR2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>-2.777007906995749</v>
+      </c>
       <c r="AS2" t="n">
-        <v>-29872264.42431086</v>
+        <v>3.026754102193905</v>
       </c>
       <c r="AT2" t="n">
-        <v>-0.5298989898989896</v>
+        <v>-0.0157828282828234</v>
       </c>
       <c r="AU2" t="inlineStr"/>
       <c r="AV2" t="n">
-        <v>2.45863764693803</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>-0.4946688226134863</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>-0.4451515151515117</v>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+        <v>-2.219696969696955</v>
+      </c>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="n">
+        <v>-705962.203686299</v>
+      </c>
       <c r="AZ2" t="n">
-        <v>-23346757.57575758</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>-5.671401322656251</v>
-      </c>
+        <v>-2141126.893939394</v>
+      </c>
+      <c r="BA2" t="inlineStr"/>
       <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="n">
-        <v>-6.342584462638811</v>
-      </c>
+      <c r="BC2" t="n">
+        <v>-2.892045454545453</v>
+      </c>
+      <c r="BD2" t="inlineStr"/>
       <c r="BE2" t="n">
-        <v>0.0286693017127817</v>
+        <v>-1.094057380770767</v>
       </c>
       <c r="BF2" t="n">
         <v>0</v>
@@ -866,42 +866,42 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>pAXo2Kvn</t>
+          <t>t0w6KHuf</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45523.65625</v>
+        <v>45529.4375</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">zwayer f 
+          <t xml:space="preserve">fritz m 
   ger </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">eintracht stadion
-  braunschweig </t>
+          <t xml:space="preserve">volkswagen arena
+  wolfsburg </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>QqLCC3il</t>
+          <t>nwkTahLL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>8vndvXTk</t>
+          <t>nVp0wiqd</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>59</v>
       </c>
       <c r="H3" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>20242025</v>
@@ -913,27 +913,31 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>dfb pokal</t>
+          <t>bundesliga</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>txZLBQVC</t>
+          <t>f3ddUIXs</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>pfoInmcq</t>
+          <t>CQTUFgPk</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>-4</v>
-      </c>
-      <c r="P3" t="inlineStr"/>
+        <v>-43</v>
+      </c>
+      <c r="P3" t="n">
+        <v>-5</v>
+      </c>
       <c r="Q3" t="n">
+        <v>-14</v>
+      </c>
+      <c r="R3" t="n">
         <v>-2</v>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
         <v>0</v>
       </c>
@@ -956,48 +960,48 @@
       <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="inlineStr"/>
-      <c r="AM3" t="inlineStr"/>
-      <c r="AN3" t="inlineStr"/>
+      <c r="AM3" t="n">
+        <v>-5.265642893052785</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1.619318181818187</v>
+      </c>
       <c r="AO3" t="n">
-        <v>-9.648318903318909</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>1.121976911976901</v>
-      </c>
+        <v>-1.540909090909091</v>
+      </c>
+      <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="n">
-        <v>-9.887279942279932</v>
-      </c>
-      <c r="AR3" t="inlineStr"/>
+        <v>-0.956070445175851</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>-4.969508455447738</v>
+      </c>
       <c r="AS3" t="n">
-        <v>-4433682.637329254</v>
+        <v>1.119034818394823</v>
       </c>
       <c r="AT3" t="n">
-        <v>-0.5472077922077923</v>
+        <v>-1.797727272727272</v>
       </c>
       <c r="AU3" t="inlineStr"/>
       <c r="AV3" t="n">
-        <v>-1.113380963230583</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>-0.4218284347231716</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>1.164985569985571</v>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+        <v>-5.106818181818198</v>
+      </c>
+      <c r="AW3" t="inlineStr"/>
+      <c r="AX3" t="inlineStr"/>
+      <c r="AY3" t="n">
+        <v>-20119036.47813281</v>
+      </c>
       <c r="AZ3" t="n">
-        <v>-14207630.59163059</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>-8.262956688257432</v>
-      </c>
+        <v>-32226818.18181818</v>
+      </c>
+      <c r="BA3" t="inlineStr"/>
       <c r="BB3" t="inlineStr"/>
-      <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="n">
-        <v>-5.240819689917444</v>
-      </c>
+      <c r="BC3" t="n">
+        <v>-6.378977272727269</v>
+      </c>
+      <c r="BD3" t="inlineStr"/>
       <c r="BE3" t="n">
-        <v>1.750992605973806</v>
+        <v>-0.4879570416076362</v>
       </c>
       <c r="BF3" t="n">
         <v>0</v>
@@ -1006,42 +1010,42 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>EkP2bxvB</t>
+          <t>SxFxJ44k</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45523.54166666666</v>
+        <v>45528.5625</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">willenborg f 
+          <t xml:space="preserve">zwayer f 
   ger </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadion oberwerth
-  koblenz </t>
+          <t xml:space="preserve">signal iduna park
+  dortmund </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>p8wBsqZt</t>
+          <t>nP1i5US1</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>nwkTahLL</t>
+          <t>8vndvXTk</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>59</v>
       </c>
       <c r="H4" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>20242025</v>
@@ -1053,19 +1057,31 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Q1njn0Vm</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>vZA6VYpf</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
+          <t>pfoInmcq</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>18</v>
+      </c>
+      <c r="P4" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>20</v>
+      </c>
+      <c r="R4" t="n">
+        <v>3</v>
+      </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
@@ -1085,28 +1101,54 @@
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
+      <c r="AJ4" t="n">
+        <v>76.91875</v>
+      </c>
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="inlineStr"/>
-      <c r="AN4" t="inlineStr"/>
-      <c r="AO4" t="inlineStr"/>
+      <c r="AM4" t="n">
+        <v>4.036753760515353</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1.392297979798002</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0.592992424242424</v>
+      </c>
       <c r="AP4" t="inlineStr"/>
-      <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="inlineStr"/>
-      <c r="AS4" t="inlineStr"/>
-      <c r="AT4" t="inlineStr"/>
+      <c r="AQ4" t="n">
+        <v>0.5623828468787837</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>5.698715301511356</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0.2525122898043151</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1.551957070707072</v>
+      </c>
       <c r="AU4" t="inlineStr"/>
-      <c r="AV4" t="inlineStr"/>
+      <c r="AV4" t="n">
+        <v>1.808522727272717</v>
+      </c>
       <c r="AW4" t="inlineStr"/>
       <c r="AX4" t="inlineStr"/>
-      <c r="AY4" t="inlineStr"/>
-      <c r="AZ4" t="inlineStr"/>
+      <c r="AY4" t="n">
+        <v>13919978.9774612</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>13085628.15656566</v>
+      </c>
       <c r="BA4" t="inlineStr"/>
       <c r="BB4" t="inlineStr"/>
-      <c r="BC4" t="inlineStr"/>
+      <c r="BC4" t="n">
+        <v>3.075568181818184</v>
+      </c>
       <c r="BD4" t="inlineStr"/>
-      <c r="BE4" t="inlineStr"/>
+      <c r="BE4" t="n">
+        <v>0.2518000172557109</v>
+      </c>
       <c r="BF4" t="n">
         <v>0</v>
       </c>
@@ -1114,42 +1156,42 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>06NAdG8N</t>
+          <t>GbeXvnR8</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45523.54166666666</v>
+        <v>45528.4375</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">petersen m 
+          <t xml:space="preserve">schlager d 
   ger </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadion der freundschaft
-  cottbus </t>
+          <t xml:space="preserve">europa park stadion
+  freiburg </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>6g44VD52</t>
+          <t>fiEQZ7C7</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ig1f1fy3</t>
+          <t>nJQmYp1B</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>59</v>
       </c>
       <c r="H5" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>20242025</v>
@@ -1161,26 +1203,30 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>v9WoiHGP</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>xzRzG0VI</t>
+          <t>M5BRZDsC</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>-3</v>
+        <v>-9</v>
       </c>
       <c r="P5" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1201,71 +1247,97 @@
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr"/>
+      <c r="AJ5" t="n">
+        <v>76.29545454545455</v>
+      </c>
       <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="inlineStr"/>
+      <c r="AM5" t="n">
+        <v>0.9069622936417261</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>-0.8409090909090651</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0.1477272727272725</v>
+      </c>
       <c r="AP5" t="inlineStr"/>
-      <c r="AQ5" t="inlineStr"/>
-      <c r="AR5" t="inlineStr"/>
-      <c r="AS5" t="inlineStr"/>
-      <c r="AT5" t="inlineStr"/>
+      <c r="AQ5" t="n">
+        <v>0.2041750662889106</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>2.325698928026597</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>2.228974042897107</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>2.801136363636363</v>
+      </c>
       <c r="AU5" t="inlineStr"/>
-      <c r="AV5" t="inlineStr"/>
+      <c r="AV5" t="n">
+        <v>-1.9375</v>
+      </c>
       <c r="AW5" t="inlineStr"/>
       <c r="AX5" t="inlineStr"/>
-      <c r="AY5" t="inlineStr"/>
-      <c r="AZ5" t="inlineStr"/>
+      <c r="AY5" t="n">
+        <v>722051.8574515991</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>-3393749.999999998</v>
+      </c>
       <c r="BA5" t="inlineStr"/>
       <c r="BB5" t="inlineStr"/>
-      <c r="BC5" t="inlineStr"/>
+      <c r="BC5" t="n">
+        <v>-0.8522727272727337</v>
+      </c>
       <c r="BD5" t="inlineStr"/>
-      <c r="BE5" t="inlineStr"/>
+      <c r="BE5" t="n">
+        <v>0.7822921207003013</v>
+      </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Sff03OL7</t>
+          <t>YZZcMwBs</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45523.54166666666</v>
+        <v>45528.4375</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">heft f 
+          <t xml:space="preserve">petersen m 
   ger </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">bieberer berg stadion
-  offenbach am main </t>
+          <t xml:space="preserve">wwk arena
+  augsburg </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>YJURlaIO</t>
+          <t>fTVNku3I</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>YFuz2RLm</t>
+          <t>Ig1f1fy3</t>
         </is>
       </c>
       <c r="G6" t="n">
         <v>59</v>
       </c>
       <c r="H6" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>20242025</v>
@@ -1277,19 +1349,31 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>hAcTWKKN</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>8E8qmw3d</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
+          <t>xzRzG0VI</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-1</v>
+      </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
@@ -1312,25 +1396,49 @@
       <c r="AJ6" t="inlineStr"/>
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="inlineStr"/>
-      <c r="AM6" t="inlineStr"/>
-      <c r="AN6" t="inlineStr"/>
-      <c r="AO6" t="inlineStr"/>
+      <c r="AM6" t="n">
+        <v>2.33589577792057</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>2.212500000000034</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0.2828914141414141</v>
+      </c>
       <c r="AP6" t="inlineStr"/>
-      <c r="AQ6" t="inlineStr"/>
-      <c r="AR6" t="inlineStr"/>
-      <c r="AS6" t="inlineStr"/>
-      <c r="AT6" t="inlineStr"/>
+      <c r="AQ6" t="n">
+        <v>-0.07282682992065093</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>2.610843873620979</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>-0.4970342393987721</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>-0.5107323232323218</v>
+      </c>
       <c r="AU6" t="inlineStr"/>
-      <c r="AV6" t="inlineStr"/>
+      <c r="AV6" t="n">
+        <v>1.195328282828285</v>
+      </c>
       <c r="AW6" t="inlineStr"/>
       <c r="AX6" t="inlineStr"/>
-      <c r="AY6" t="inlineStr"/>
-      <c r="AZ6" t="inlineStr"/>
+      <c r="AY6" t="n">
+        <v>1288042.074948674</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>1747755.681818182</v>
+      </c>
       <c r="BA6" t="inlineStr"/>
       <c r="BB6" t="inlineStr"/>
-      <c r="BC6" t="inlineStr"/>
+      <c r="BC6" t="n">
+        <v>1.294570707070704</v>
+      </c>
       <c r="BD6" t="inlineStr"/>
-      <c r="BE6" t="inlineStr"/>
+      <c r="BE6" t="n">
+        <v>-0.9499159109070447</v>
+      </c>
       <c r="BF6" t="n">
         <v>0</v>
       </c>
@@ -1338,42 +1446,42 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>vXAKoaf5</t>
+          <t>2FREIeA6</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45522.54166666666</v>
+        <v>45528.4375</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">kampka r 
+          <t xml:space="preserve">dingert c 
   ger </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">rudolf harbig stadion
-  dresden </t>
+          <t xml:space="preserve">mewa arena
+  mainz </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>zL1YsOi1</t>
+          <t>EuakNmc1</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ne1oL3y7</t>
+          <t>pzHW4oaE</t>
         </is>
       </c>
       <c r="G7" t="n">
         <v>59</v>
       </c>
       <c r="H7" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>20242025</v>
@@ -1385,26 +1493,30 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>f3ddUIXs</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>AoL97rX8</t>
+          <t>l0fHXMdE</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="P7" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="Q7" t="n">
         <v>2</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1428,25 +1540,49 @@
       <c r="AJ7" t="inlineStr"/>
       <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="inlineStr"/>
-      <c r="AM7" t="inlineStr"/>
-      <c r="AN7" t="inlineStr"/>
-      <c r="AO7" t="inlineStr"/>
+      <c r="AM7" t="n">
+        <v>0.5059537998074859</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>-1.738636363636374</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>-0.02840909090909083</v>
+      </c>
       <c r="AP7" t="inlineStr"/>
-      <c r="AQ7" t="inlineStr"/>
-      <c r="AR7" t="inlineStr"/>
-      <c r="AS7" t="inlineStr"/>
-      <c r="AT7" t="inlineStr"/>
+      <c r="AQ7" t="n">
+        <v>0.01135992154298782</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>-1.443412085467301</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1.103360756964861</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>-1.08522727272727</v>
+      </c>
       <c r="AU7" t="inlineStr"/>
-      <c r="AV7" t="inlineStr"/>
+      <c r="AV7" t="n">
+        <v>0.09659090909090651</v>
+      </c>
       <c r="AW7" t="inlineStr"/>
       <c r="AX7" t="inlineStr"/>
-      <c r="AY7" t="inlineStr"/>
-      <c r="AZ7" t="inlineStr"/>
+      <c r="AY7" t="n">
+        <v>-778248.7809196906</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>-1543750.000000001</v>
+      </c>
       <c r="BA7" t="inlineStr"/>
       <c r="BB7" t="inlineStr"/>
-      <c r="BC7" t="inlineStr"/>
+      <c r="BC7" t="n">
+        <v>-1.261363636363626</v>
+      </c>
       <c r="BD7" t="inlineStr"/>
-      <c r="BE7" t="inlineStr"/>
+      <c r="BE7" t="n">
+        <v>-0.7354042374959171</v>
+      </c>
       <c r="BF7" t="n">
         <v>0</v>
       </c>
@@ -1454,42 +1590,42 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>pzHxyrtm</t>
+          <t>dfO6OQtS</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45522.54166666666</v>
+        <v>45528.4375</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">braun r 
+          <t xml:space="preserve">aytekin d 
   ger </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadion am lotter kreuz
-  lotte </t>
+          <t xml:space="preserve">red bull arena
+  leipzig </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>hjNlCFPB</t>
+          <t>KbS1suSm</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>EB3q7jbk</t>
+          <t>8Y2m6ADe</t>
         </is>
       </c>
       <c r="G8" t="n">
         <v>59</v>
       </c>
       <c r="H8" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>20242025</v>
@@ -1501,19 +1637,31 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>UgdQz0fK</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>tO31cZrF</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
+          <t>xzRzG0VI</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>9</v>
+      </c>
+      <c r="P8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>5</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2</v>
+      </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
@@ -1536,25 +1684,49 @@
       <c r="AJ8" t="inlineStr"/>
       <c r="AK8" t="inlineStr"/>
       <c r="AL8" t="inlineStr"/>
-      <c r="AM8" t="inlineStr"/>
-      <c r="AN8" t="inlineStr"/>
-      <c r="AO8" t="inlineStr"/>
+      <c r="AM8" t="n">
+        <v>8.236640068894786</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>-0.04682940516272538</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0.8395342312008975</v>
+      </c>
       <c r="AP8" t="inlineStr"/>
-      <c r="AQ8" t="inlineStr"/>
-      <c r="AR8" t="inlineStr"/>
-      <c r="AS8" t="inlineStr"/>
-      <c r="AT8" t="inlineStr"/>
+      <c r="AQ8" t="n">
+        <v>0.6429461838977482</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>6.30097730338602</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>2.605883522624111</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>-3.129138608305279</v>
+      </c>
       <c r="AU8" t="inlineStr"/>
-      <c r="AV8" t="inlineStr"/>
+      <c r="AV8" t="n">
+        <v>8.576304713804703</v>
+      </c>
       <c r="AW8" t="inlineStr"/>
       <c r="AX8" t="inlineStr"/>
-      <c r="AY8" t="inlineStr"/>
-      <c r="AZ8" t="inlineStr"/>
+      <c r="AY8" t="n">
+        <v>15364059.94967243</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>25517239.05723906</v>
+      </c>
       <c r="BA8" t="inlineStr"/>
       <c r="BB8" t="inlineStr"/>
-      <c r="BC8" t="inlineStr"/>
+      <c r="BC8" t="n">
+        <v>7.009048821548816</v>
+      </c>
       <c r="BD8" t="inlineStr"/>
-      <c r="BE8" t="inlineStr"/>
+      <c r="BE8" t="n">
+        <v>-2.081720870715433</v>
+      </c>
       <c r="BF8" t="n">
         <v>0</v>
       </c>
@@ -1562,42 +1734,42 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>dCPKovw8</t>
+          <t>O48oHrZ1</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45522.54166666666</v>
+        <v>45528.4375</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">burda m 
+          <t xml:space="preserve">sather a 
   ger </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">hansch arena
-  meppen </t>
+          <t xml:space="preserve">prezero arena
+  sinsheim </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>rXqBh2xP</t>
+          <t>hQAtP9Sl</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>v9k3aY5F</t>
+          <t>63WsD2ei</t>
         </is>
       </c>
       <c r="G9" t="n">
         <v>59</v>
       </c>
       <c r="H9" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>20242025</v>
@@ -1609,19 +1781,31 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>KUx4Q7x1</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>EDRZkDzS</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
+          <t>A15eUM4C</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>1</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
@@ -1641,30 +1825,52 @@
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="inlineStr"/>
-      <c r="AJ9" t="n">
-        <v>71.2</v>
-      </c>
+      <c r="AJ9" t="inlineStr"/>
       <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="inlineStr"/>
-      <c r="AM9" t="inlineStr"/>
-      <c r="AN9" t="inlineStr"/>
-      <c r="AO9" t="inlineStr"/>
+      <c r="AM9" t="n">
+        <v>6.578316703090238</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>-0.5151515151514729</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0.7032828282828283</v>
+      </c>
       <c r="AP9" t="inlineStr"/>
-      <c r="AQ9" t="inlineStr"/>
-      <c r="AR9" t="inlineStr"/>
-      <c r="AS9" t="inlineStr"/>
-      <c r="AT9" t="inlineStr"/>
+      <c r="AQ9" t="n">
+        <v>0.3777749022314238</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>5.277859251591138</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>-1.176205692623256</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1.209595959595962</v>
+      </c>
       <c r="AU9" t="inlineStr"/>
-      <c r="AV9" t="inlineStr"/>
+      <c r="AV9" t="n">
+        <v>6.184343434343432</v>
+      </c>
       <c r="AW9" t="inlineStr"/>
       <c r="AX9" t="inlineStr"/>
-      <c r="AY9" t="inlineStr"/>
-      <c r="AZ9" t="inlineStr"/>
+      <c r="AY9" t="n">
+        <v>4021058.958884479</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>6916919.191919191</v>
+      </c>
       <c r="BA9" t="inlineStr"/>
       <c r="BB9" t="inlineStr"/>
-      <c r="BC9" t="inlineStr"/>
+      <c r="BC9" t="n">
+        <v>6.37373737373737</v>
+      </c>
       <c r="BD9" t="inlineStr"/>
-      <c r="BE9" t="inlineStr"/>
+      <c r="BE9" t="n">
+        <v>-0.5843523550724683</v>
+      </c>
       <c r="BF9" t="n">
         <v>0</v>
       </c>
@@ -1672,42 +1878,42 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>KSwfVwAO</t>
+          <t>zuzbQnCF</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45522.4375</v>
+        <v>45527.64583333334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">kampka r 
+          <t xml:space="preserve">dankert b 
   ger </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">millerntor stadion
-  hamburg </t>
+          <t xml:space="preserve">borussia park
+  monchengladbach </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>WrbkcjCd</t>
+          <t>88HSzjDr</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>S0hPB9rA</t>
+          <t>4jcj2zMd</t>
         </is>
       </c>
       <c r="G10" t="n">
         <v>59</v>
       </c>
       <c r="H10" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>20242025</v>
@@ -1719,19 +1925,31 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>GzfvcwRj</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>AoL97rX8</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
+          <t>hAcTWKKN</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>-19</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-9</v>
+      </c>
+      <c r="R10" t="n">
+        <v>-3</v>
+      </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
@@ -1754,25 +1972,49 @@
       <c r="AJ10" t="inlineStr"/>
       <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="inlineStr"/>
-      <c r="AM10" t="inlineStr"/>
-      <c r="AN10" t="inlineStr"/>
-      <c r="AO10" t="inlineStr"/>
+      <c r="AM10" t="n">
+        <v>-5.442586561168511</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>-0.3699635241302133</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>-0.6130050505050506</v>
+      </c>
       <c r="AP10" t="inlineStr"/>
-      <c r="AQ10" t="inlineStr"/>
-      <c r="AR10" t="inlineStr"/>
-      <c r="AS10" t="inlineStr"/>
-      <c r="AT10" t="inlineStr"/>
+      <c r="AQ10" t="n">
+        <v>-0.3756549882336493</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>-5.418769419396909</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>2.367444642980985</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>-0.4003998316498318</v>
+      </c>
       <c r="AU10" t="inlineStr"/>
-      <c r="AV10" t="inlineStr"/>
+      <c r="AV10" t="n">
+        <v>-6.19309764309763</v>
+      </c>
       <c r="AW10" t="inlineStr"/>
       <c r="AX10" t="inlineStr"/>
-      <c r="AY10" t="inlineStr"/>
-      <c r="AZ10" t="inlineStr"/>
+      <c r="AY10" t="n">
+        <v>-24906213.52613665</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>-26871254.91021325</v>
+      </c>
       <c r="BA10" t="inlineStr"/>
       <c r="BB10" t="inlineStr"/>
-      <c r="BC10" t="inlineStr"/>
+      <c r="BC10" t="n">
+        <v>-6.247516835016825</v>
+      </c>
       <c r="BD10" t="inlineStr"/>
-      <c r="BE10" t="inlineStr"/>
+      <c r="BE10" t="n">
+        <v>0.1611833402951852</v>
+      </c>
       <c r="BF10" t="n">
         <v>0</v>
       </c>
@@ -1780,32 +2022,32 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>YV3TqwPH</t>
+          <t>pAXo2Kvn</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45522.4375</v>
+        <v>45523.65625</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">haslberger w 
+          <t xml:space="preserve">zwayer f 
   ger </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadion am panzenberg
-  bremen </t>
+          <t xml:space="preserve">eintracht stadion
+  braunschweig </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>tW75B1ei</t>
+          <t>QqLCC3il</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>G2Op923t</t>
+          <t>8vndvXTk</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,15 +2072,23 @@
           <t>dfb pokal</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>txZLBQVC</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0AI1QUJH</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr"/>
+          <t>pfoInmcq</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>-4</v>
+      </c>
       <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
+      <c r="Q11" t="n">
+        <v>-2</v>
+      </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
         <v>0</v>
@@ -1859,30 +2109,52 @@
       <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="inlineStr"/>
       <c r="AI11" t="inlineStr"/>
-      <c r="AJ11" t="n">
-        <v>67</v>
-      </c>
+      <c r="AJ11" t="inlineStr"/>
       <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="inlineStr"/>
-      <c r="AM11" t="inlineStr"/>
-      <c r="AN11" t="inlineStr"/>
-      <c r="AO11" t="inlineStr"/>
+      <c r="AM11" t="n">
+        <v>-7.984203580754468</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1.119570707070693</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>-0.6092803030303031</v>
+      </c>
       <c r="AP11" t="inlineStr"/>
-      <c r="AQ11" t="inlineStr"/>
-      <c r="AR11" t="inlineStr"/>
-      <c r="AS11" t="inlineStr"/>
-      <c r="AT11" t="inlineStr"/>
+      <c r="AQ11" t="n">
+        <v>-0.4284405658196293</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>-5.106294619123574</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>-0.9816890990846048</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>1.398547979797979</v>
+      </c>
       <c r="AU11" t="inlineStr"/>
-      <c r="AV11" t="inlineStr"/>
+      <c r="AV11" t="n">
+        <v>-10.14261363636363</v>
+      </c>
       <c r="AW11" t="inlineStr"/>
       <c r="AX11" t="inlineStr"/>
-      <c r="AY11" t="inlineStr"/>
-      <c r="AZ11" t="inlineStr"/>
+      <c r="AY11" t="n">
+        <v>-4445658.919364197</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>-14224826.38888889</v>
+      </c>
       <c r="BA11" t="inlineStr"/>
       <c r="BB11" t="inlineStr"/>
-      <c r="BC11" t="inlineStr"/>
+      <c r="BC11" t="n">
+        <v>-9.53125</v>
+      </c>
       <c r="BD11" t="inlineStr"/>
-      <c r="BE11" t="inlineStr"/>
+      <c r="BE11" t="n">
+        <v>1.414473628366817</v>
+      </c>
       <c r="BF11" t="n">
         <v>0</v>
       </c>
@@ -1890,32 +2162,32 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>tvOIPExA</t>
+          <t>06NAdG8N</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45522.4375</v>
+        <v>45523.54166666666</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">burda m 
+          <t xml:space="preserve">petersen m 
   ger </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">hardtwaldstadion
-  sandhausen </t>
+          <t xml:space="preserve">stadion der freundschaft
+  cottbus </t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>UZxEj1R4</t>
+          <t>6g44VD52</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>WG9pOTse</t>
+          <t>Ig1f1fy3</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1943,17 +2215,21 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>EDRZkDzS</t>
+          <t>xzRzG0VI</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>-4</v>
-      </c>
-      <c r="P12" t="inlineStr"/>
+        <v>-3</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q12" t="n">
-        <v>-2</v>
-      </c>
-      <c r="R12" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-1</v>
+      </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
@@ -2002,32 +2278,32 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>jFMCm08e</t>
+          <t>EkP2bxvB</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45522.4375</v>
+        <v>45523.54166666666</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">aytekin d 
+          <t xml:space="preserve">willenborg f 
   ger </t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">jahnstadion regensburg
-  regensburg </t>
+          <t xml:space="preserve">stadion oberwerth
+  koblenz </t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>UiCmEP56</t>
+          <t>p8wBsqZt</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>8Y2m6ADe</t>
+          <t>nwkTahLL</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2052,23 +2328,15 @@
           <t>dfb pokal</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>t0ZPdkUl</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>xzRzG0VI</t>
-        </is>
-      </c>
-      <c r="O13" t="n">
-        <v>1</v>
-      </c>
+          <t>vZA6VYpf</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
         <v>0</v>
@@ -2118,11 +2386,11 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>t2AoZLAa</t>
+          <t>Sff03OL7</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45522.4375</v>
+        <v>45523.54166666666</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2132,18 +2400,18 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">friedrich ebert stadium
-  hildesheim </t>
+          <t xml:space="preserve">bieberer berg stadion
+  offenbach am main </t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>E3xs5mIe</t>
+          <t>YJURlaIO</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>6in2Eknb</t>
+          <t>YFuz2RLm</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2226,32 +2494,32 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>l0ueP5rR</t>
+          <t>vXAKoaf5</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45522.4375</v>
+        <v>45522.54166666666</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">haslberger w 
+          <t xml:space="preserve">hartmann r 
   ger </t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">ostseestadion
-  rostock </t>
+          <t xml:space="preserve">rudolf harbig stadion
+  dresden </t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>KIHmtCkL</t>
+          <t>zL1YsOi1</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2y0u8Wrq</t>
+          <t>ne1oL3y7</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2276,27 +2544,23 @@
           <t>dfb pokal</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>UyNNTYWE</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>0AI1QUJH</t>
+          <t>OzPMRhK3</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>-7</v>
+        <v>4</v>
       </c>
       <c r="P15" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3</v>
+        <v>2</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -2322,47 +2586,23 @@
       <c r="AL15" t="inlineStr"/>
       <c r="AM15" t="inlineStr"/>
       <c r="AN15" t="inlineStr"/>
-      <c r="AO15" t="n">
-        <v>-2.515873015873012</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>-0.5937950937951371</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>-5.057864357864361</v>
-      </c>
+      <c r="AO15" t="inlineStr"/>
+      <c r="AP15" t="inlineStr"/>
+      <c r="AQ15" t="inlineStr"/>
       <c r="AR15" t="inlineStr"/>
-      <c r="AS15" t="n">
-        <v>-630832.411212642</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>-0.07301587301587298</v>
-      </c>
+      <c r="AS15" t="inlineStr"/>
+      <c r="AT15" t="inlineStr"/>
       <c r="AU15" t="inlineStr"/>
-      <c r="AV15" t="n">
-        <v>0.3381612675581209</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>-0.2286778021658702</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>2.539682539682538</v>
-      </c>
+      <c r="AV15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr"/>
+      <c r="AX15" t="inlineStr"/>
       <c r="AY15" t="inlineStr"/>
-      <c r="AZ15" t="n">
-        <v>-1437914.862914863</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>-3.590488579108211</v>
-      </c>
+      <c r="AZ15" t="inlineStr"/>
+      <c r="BA15" t="inlineStr"/>
       <c r="BB15" t="inlineStr"/>
       <c r="BC15" t="inlineStr"/>
-      <c r="BD15" t="n">
-        <v>-2.249002855655363</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>-0.3369713751251808</v>
-      </c>
+      <c r="BD15" t="inlineStr"/>
+      <c r="BE15" t="inlineStr"/>
       <c r="BF15" t="n">
         <v>0</v>
       </c>
@@ -2370,32 +2610,32 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>AiJ3kset</t>
+          <t>dCPKovw8</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>45522.33333333334</v>
+        <v>45522.54166666666</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">jollenbeck m 
+          <t xml:space="preserve">burda m 
   ger </t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">friedrich ludwig jahn sportpark
-  berlin </t>
+          <t xml:space="preserve">hansch arena
+  meppen </t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>UNr2EUfd</t>
+          <t>rXqBh2xP</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>fTVNku3I</t>
+          <t>v9k3aY5F</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2423,7 +2663,7 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2VSFgl3c</t>
+          <t>EDRZkDzS</t>
         </is>
       </c>
       <c r="O16" t="inlineStr"/>
@@ -2449,7 +2689,9 @@
       <c r="AG16" t="inlineStr"/>
       <c r="AH16" t="inlineStr"/>
       <c r="AI16" t="inlineStr"/>
-      <c r="AJ16" t="inlineStr"/>
+      <c r="AJ16" t="n">
+        <v>71.2</v>
+      </c>
       <c r="AK16" t="inlineStr"/>
       <c r="AL16" t="inlineStr"/>
       <c r="AM16" t="inlineStr"/>
@@ -2478,32 +2720,32 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>6q2yrHgU</t>
+          <t>pzHxyrtm</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>45522.33333333334</v>
+        <v>45522.54166666666</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">braun r 
+          <t xml:space="preserve">hartmann r 
   ger </t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ludwigspark stadion
-  saarbrucken </t>
+          <t xml:space="preserve">stadion am lotter kreuz
+  lotte </t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>fLbhmJ5l</t>
+          <t>hjNlCFPB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>6FDqshzF</t>
+          <t>EB3q7jbk</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2531,16 +2773,12 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>tO31cZrF</t>
-        </is>
-      </c>
-      <c r="O17" t="n">
-        <v>1</v>
-      </c>
+          <t>OzPMRhK3</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
         <v>0</v>
@@ -2562,7 +2800,7 @@
       <c r="AH17" t="inlineStr"/>
       <c r="AI17" t="inlineStr"/>
       <c r="AJ17" t="n">
-        <v>66</v>
+        <v>67.81818181818181</v>
       </c>
       <c r="AK17" t="inlineStr"/>
       <c r="AL17" t="inlineStr"/>
@@ -2592,45 +2830,45 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>fcxqFy2l</t>
+          <t>KSwfVwAO</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>45521.64583333334</v>
+        <v>45522.4375</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">schlager d 
+          <t xml:space="preserve">kampka r 
   ger </t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">bayarena
-  leverkusen </t>
+          <t xml:space="preserve">millerntor stadion
+  hamburg </t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>4jcj2zMd</t>
+          <t>WrbkcjCd</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>nJQmYp1B</t>
+          <t>S0hPB9rA</t>
         </is>
       </c>
       <c r="G18" t="n">
         <v>59</v>
       </c>
       <c r="H18" t="n">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="I18" t="n">
         <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>2024</v>
+        <v>20242025</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -2639,31 +2877,19 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>super cup</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>2BYSk4KO</t>
-        </is>
-      </c>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>M5BRZDsC</t>
-        </is>
-      </c>
-      <c r="O18" t="n">
-        <v>27</v>
-      </c>
-      <c r="P18" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>18</v>
-      </c>
-      <c r="R18" t="n">
-        <v>3</v>
-      </c>
+          <t>AoL97rX8</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
         <v>0</v>
       </c>
@@ -2688,47 +2914,23 @@
       <c r="AL18" t="inlineStr"/>
       <c r="AM18" t="inlineStr"/>
       <c r="AN18" t="inlineStr"/>
-      <c r="AO18" t="n">
-        <v>5.13333333333334</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>0.7535353535353693</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>4.878787878787875</v>
-      </c>
+      <c r="AO18" t="inlineStr"/>
+      <c r="AP18" t="inlineStr"/>
+      <c r="AQ18" t="inlineStr"/>
       <c r="AR18" t="inlineStr"/>
-      <c r="AS18" t="n">
-        <v>30827197.30905896</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>0.5272727272727271</v>
-      </c>
+      <c r="AS18" t="inlineStr"/>
+      <c r="AT18" t="inlineStr"/>
       <c r="AU18" t="inlineStr"/>
-      <c r="AV18" t="n">
-        <v>-1.175290510982194</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>0.5169583326203877</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>1.23030303030303</v>
-      </c>
+      <c r="AV18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr"/>
+      <c r="AX18" t="inlineStr"/>
       <c r="AY18" t="inlineStr"/>
-      <c r="AZ18" t="n">
-        <v>19594646.46464647</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>8.734170473794975</v>
-      </c>
+      <c r="AZ18" t="inlineStr"/>
+      <c r="BA18" t="inlineStr"/>
       <c r="BB18" t="inlineStr"/>
       <c r="BC18" t="inlineStr"/>
-      <c r="BD18" t="n">
-        <v>7.566349990589131</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>-1.531745561202083</v>
-      </c>
+      <c r="BD18" t="inlineStr"/>
+      <c r="BE18" t="inlineStr"/>
       <c r="BF18" t="n">
         <v>0</v>
       </c>
@@ -2736,32 +2938,32 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>CpiTEcOi</t>
+          <t>tvOIPExA</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>45521.54166666666</v>
+        <v>45522.4375</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">bacher m 
+          <t xml:space="preserve">bauer t 
   ger </t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">schuco arena
-  bielefeld </t>
+          <t xml:space="preserve">hardtwaldstadion
+  sandhausen </t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>pp38UXK8</t>
+          <t>UZxEj1R4</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>dfNCCCzS</t>
+          <t>WG9pOTse</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2789,21 +2991,17 @@
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>zyLSrbZQ</t>
+          <t>4fX0k7gg</t>
         </is>
       </c>
       <c r="O19" t="n">
-        <v>3</v>
-      </c>
-      <c r="P19" t="n">
+        <v>-4</v>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="n">
         <v>-2</v>
       </c>
-      <c r="Q19" t="n">
-        <v>1</v>
-      </c>
-      <c r="R19" t="n">
-        <v>-1</v>
-      </c>
+      <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
         <v>0</v>
       </c>
@@ -2823,7 +3021,9 @@
       <c r="AG19" t="inlineStr"/>
       <c r="AH19" t="inlineStr"/>
       <c r="AI19" t="inlineStr"/>
-      <c r="AJ19" t="inlineStr"/>
+      <c r="AJ19" t="n">
+        <v>71.27272727272727</v>
+      </c>
       <c r="AK19" t="inlineStr"/>
       <c r="AL19" t="inlineStr"/>
       <c r="AM19" t="inlineStr"/>
@@ -2852,32 +3052,32 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>8CpxDyg4</t>
+          <t>jFMCm08e</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>45521.54166666666</v>
+        <v>45522.4375</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">siebert d 
+          <t xml:space="preserve">aytekin d 
   ger </t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadion lohmuhle
-  lubeck </t>
+          <t xml:space="preserve">jahnstadion regensburg
+  regensburg </t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>I1Vk6k3R</t>
+          <t>UiCmEP56</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>nP1i5US1</t>
+          <t>8Y2m6ADe</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2902,15 +3102,23 @@
           <t>dfb pokal</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>zyLSrbZQ</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>MDhPV0RQ</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr"/>
+          <t>xzRzG0VI</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>1</v>
+      </c>
       <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
         <v>0</v>
@@ -2960,32 +3168,32 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>hzyf0b9b</t>
+          <t>t2AoZLAa</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>45521.54166666666</v>
+        <v>45522.4375</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">sather a 
+          <t xml:space="preserve">bauer t 
   ger </t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">new tivoli
-  aachen </t>
+          <t xml:space="preserve">friedrich ebert stadium
+  hildesheim </t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>j3PKcB4E</t>
+          <t>E3xs5mIe</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>63WsD2ei</t>
+          <t>6in2Eknb</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,7 +3221,7 @@
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
-          <t>A15eUM4C</t>
+          <t>4fX0k7gg</t>
         </is>
       </c>
       <c r="O21" t="inlineStr"/>
@@ -3068,32 +3276,32 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>8QPARz8c</t>
+          <t>l0ueP5rR</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>45521.4375</v>
+        <v>45522.4375</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">welz t 
+          <t xml:space="preserve">haslberger w 
   ger </t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ms technologie arena
-  villingen schwenningen </t>
+          <t xml:space="preserve">ostseestadion
+  rostock </t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>lKLJUxeT</t>
+          <t>KIHmtCkL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>KWixEVWi</t>
+          <t>2y0u8Wrq</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3118,16 +3326,28 @@
           <t>dfb pokal</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>UyNNTYWE</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>lGJdeemM</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
+          <t>0AI1QUJH</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>-7</v>
+      </c>
+      <c r="P22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-3</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
       <c r="S22" t="n">
         <v>0</v>
       </c>
@@ -3150,25 +3370,49 @@
       <c r="AJ22" t="inlineStr"/>
       <c r="AK22" t="inlineStr"/>
       <c r="AL22" t="inlineStr"/>
-      <c r="AM22" t="inlineStr"/>
-      <c r="AN22" t="inlineStr"/>
-      <c r="AO22" t="inlineStr"/>
+      <c r="AM22" t="n">
+        <v>-3.090937185960072</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>-0.6417171717172039</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>-0.06111111111111112</v>
+      </c>
       <c r="AP22" t="inlineStr"/>
-      <c r="AQ22" t="inlineStr"/>
-      <c r="AR22" t="inlineStr"/>
-      <c r="AS22" t="inlineStr"/>
-      <c r="AT22" t="inlineStr"/>
+      <c r="AQ22" t="n">
+        <v>-0.2372570011986488</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>-2.584352991980765</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>-0.07085842625892269</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>2.770707070707072</v>
+      </c>
       <c r="AU22" t="inlineStr"/>
-      <c r="AV22" t="inlineStr"/>
+      <c r="AV22" t="n">
+        <v>-5.147272727272735</v>
+      </c>
       <c r="AW22" t="inlineStr"/>
       <c r="AX22" t="inlineStr"/>
-      <c r="AY22" t="inlineStr"/>
-      <c r="AZ22" t="inlineStr"/>
+      <c r="AY22" t="n">
+        <v>-585126.7028783718</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>-1469656.565656566</v>
+      </c>
       <c r="BA22" t="inlineStr"/>
       <c r="BB22" t="inlineStr"/>
-      <c r="BC22" t="inlineStr"/>
+      <c r="BC22" t="n">
+        <v>-2.49686868686868</v>
+      </c>
       <c r="BD22" t="inlineStr"/>
-      <c r="BE22" t="inlineStr"/>
+      <c r="BE22" t="n">
+        <v>-1.038607418304213</v>
+      </c>
       <c r="BF22" t="n">
         <v>0</v>
       </c>
@@ -3176,32 +3420,32 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>f1nnRRDE</t>
+          <t>YV3TqwPH</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>45521.4375</v>
+        <v>45522.4375</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">dingert c 
+          <t xml:space="preserve">haslberger w 
   ger </t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadion an der bremer bruck
-  osnabruck </t>
+          <t xml:space="preserve">stadion am panzenberg
+  bremen </t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>88Xgj1Y5</t>
+          <t>tW75B1ei</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>fiEQZ7C7</t>
+          <t>G2Op923t</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3226,28 +3470,16 @@
           <t>dfb pokal</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>lxrr7DgN</t>
-        </is>
-      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>l0fHXMdE</t>
-        </is>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1</v>
-      </c>
-      <c r="R23" t="n">
-        <v>-1</v>
-      </c>
+          <t>0AI1QUJH</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
       <c r="S23" t="n">
         <v>0</v>
       </c>
@@ -3267,52 +3499,30 @@
       <c r="AG23" t="inlineStr"/>
       <c r="AH23" t="inlineStr"/>
       <c r="AI23" t="inlineStr"/>
-      <c r="AJ23" t="inlineStr"/>
+      <c r="AJ23" t="n">
+        <v>67</v>
+      </c>
       <c r="AK23" t="inlineStr"/>
       <c r="AL23" t="inlineStr"/>
       <c r="AM23" t="inlineStr"/>
       <c r="AN23" t="inlineStr"/>
-      <c r="AO23" t="n">
-        <v>-8.536363636363632</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>-0.2303030303030198</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>-6.271212121212116</v>
-      </c>
+      <c r="AO23" t="inlineStr"/>
+      <c r="AP23" t="inlineStr"/>
+      <c r="AQ23" t="inlineStr"/>
       <c r="AR23" t="inlineStr"/>
-      <c r="AS23" t="n">
-        <v>-4060136.67850181</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>-0.7090909090909085</v>
-      </c>
+      <c r="AS23" t="inlineStr"/>
+      <c r="AT23" t="inlineStr"/>
       <c r="AU23" t="inlineStr"/>
-      <c r="AV23" t="n">
-        <v>-0.4176127819548583</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>-0.4119423558897246</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>-1.751515151515147</v>
-      </c>
+      <c r="AV23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr"/>
+      <c r="AX23" t="inlineStr"/>
       <c r="AY23" t="inlineStr"/>
-      <c r="AZ23" t="n">
-        <v>-7719469.696969695</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>-6.725136104149286</v>
-      </c>
+      <c r="AZ23" t="inlineStr"/>
+      <c r="BA23" t="inlineStr"/>
       <c r="BB23" t="inlineStr"/>
       <c r="BC23" t="inlineStr"/>
-      <c r="BD23" t="n">
-        <v>-6.363708576998064</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>1.088263018657749</v>
-      </c>
+      <c r="BD23" t="inlineStr"/>
+      <c r="BE23" t="inlineStr"/>
       <c r="BF23" t="n">
         <v>0</v>
       </c>
@@ -3320,32 +3530,32 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>MZjh9ghT</t>
+          <t>AiJ3kset</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>45521.4375</v>
+        <v>45522.33333333334</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">zwayer f 
+          <t xml:space="preserve">jollenbeck m 
   ger </t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadion an der hafenstrasse
-  essen </t>
+          <t xml:space="preserve">friedrich ludwig jahn sportpark
+  berlin </t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>EB0xsr77</t>
+          <t>UNr2EUfd</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>KbS1suSm</t>
+          <t>fTVNku3I</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3373,7 +3583,7 @@
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
-          <t>pfoInmcq</t>
+          <t>2VSFgl3c</t>
         </is>
       </c>
       <c r="O24" t="inlineStr"/>
@@ -3428,32 +3638,32 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>tbKZHNz1</t>
+          <t>6q2yrHgU</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>45521.4375</v>
+        <v>45522.33333333334</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">schroder r 
+          <t xml:space="preserve">winter n 
   ger </t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">audi sportpark
-  ingolstadt </t>
+          <t xml:space="preserve">ludwigspark stadion
+  saarbrucken </t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ne5QkLtB</t>
+          <t>fLbhmJ5l</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>naWckLmC</t>
+          <t>6FDqshzF</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3478,18 +3688,22 @@
           <t>dfb pokal</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>trS1MB7T</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>4bJLk19p</t>
+          <t>txZLBQVC</t>
         </is>
       </c>
       <c r="O25" t="n">
-        <v>-5</v>
+        <v>1</v>
       </c>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="n">
@@ -3511,7 +3725,9 @@
       <c r="AG25" t="inlineStr"/>
       <c r="AH25" t="inlineStr"/>
       <c r="AI25" t="inlineStr"/>
-      <c r="AJ25" t="inlineStr"/>
+      <c r="AJ25" t="n">
+        <v>66</v>
+      </c>
       <c r="AK25" t="inlineStr"/>
       <c r="AL25" t="inlineStr"/>
       <c r="AM25" t="inlineStr"/>
@@ -3540,45 +3756,45 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>vyk5gjdE</t>
+          <t>fcxqFy2l</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>45521.4375</v>
+        <v>45521.64583333334</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">dingert c 
+          <t xml:space="preserve">schlager d 
   ger </t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">volksstadion greifswald
-  greifswald </t>
+          <t xml:space="preserve">bayarena
+  leverkusen </t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Q1yNyI5t</t>
+          <t>4jcj2zMd</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>pzHW4oaE</t>
+          <t>nJQmYp1B</t>
         </is>
       </c>
       <c r="G26" t="n">
         <v>59</v>
       </c>
       <c r="H26" t="n">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="I26" t="n">
         <v>1</v>
       </c>
       <c r="J26" t="n">
-        <v>20242025</v>
+        <v>2024</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -3587,19 +3803,31 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr"/>
+          <t>super cup</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>2BYSk4KO</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>l0fHXMdE</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
+          <t>M5BRZDsC</t>
+        </is>
+      </c>
+      <c r="O26" t="n">
+        <v>27</v>
+      </c>
+      <c r="P26" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>18</v>
+      </c>
+      <c r="R26" t="n">
+        <v>3</v>
+      </c>
       <c r="S26" t="n">
         <v>0</v>
       </c>
@@ -3622,25 +3850,49 @@
       <c r="AJ26" t="inlineStr"/>
       <c r="AK26" t="inlineStr"/>
       <c r="AL26" t="inlineStr"/>
-      <c r="AM26" t="inlineStr"/>
-      <c r="AN26" t="inlineStr"/>
-      <c r="AO26" t="inlineStr"/>
+      <c r="AM26" t="n">
+        <v>8.242324016219186</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>0.2550645342312521</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0.5727272727272728</v>
+      </c>
       <c r="AP26" t="inlineStr"/>
-      <c r="AQ26" t="inlineStr"/>
-      <c r="AR26" t="inlineStr"/>
-      <c r="AS26" t="inlineStr"/>
-      <c r="AT26" t="inlineStr"/>
+      <c r="AQ26" t="n">
+        <v>0.4082341149453561</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>7.3451830247418</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>-0.7672245501765076</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>1.120664983164986</v>
+      </c>
       <c r="AU26" t="inlineStr"/>
-      <c r="AV26" t="inlineStr"/>
+      <c r="AV26" t="n">
+        <v>5.119360269360257</v>
+      </c>
       <c r="AW26" t="inlineStr"/>
       <c r="AX26" t="inlineStr"/>
-      <c r="AY26" t="inlineStr"/>
-      <c r="AZ26" t="inlineStr"/>
+      <c r="AY26" t="n">
+        <v>26160895.69407915</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>23143041.52637487</v>
+      </c>
       <c r="BA26" t="inlineStr"/>
       <c r="BB26" t="inlineStr"/>
-      <c r="BC26" t="inlineStr"/>
+      <c r="BC26" t="n">
+        <v>5.216329966329951</v>
+      </c>
       <c r="BD26" t="inlineStr"/>
-      <c r="BE26" t="inlineStr"/>
+      <c r="BE26" t="n">
+        <v>-1.110478339568729</v>
+      </c>
       <c r="BF26" t="n">
         <v>0</v>
       </c>
@@ -3648,32 +3900,32 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bF2q76Mr</t>
+          <t>8CpxDyg4</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>45521.4375</v>
+        <v>45521.54166666666</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">stieler t 
+          <t xml:space="preserve">siebert d 
   ger </t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">ostalb arena
-  aalen </t>
+          <t xml:space="preserve">stadion lohmuhle
+  lubeck </t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Oh2C15j0</t>
+          <t>I1Vk6k3R</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0Ija0Ej9</t>
+          <t>nP1i5US1</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3701,16 +3953,12 @@
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
-          <t>SQrxFAMl</t>
-        </is>
-      </c>
-      <c r="O27" t="n">
-        <v>-1</v>
-      </c>
+          <t>MDhPV0RQ</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="n">
-        <v>-1</v>
-      </c>
+      <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="n">
         <v>0</v>
@@ -3760,32 +4008,32 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Kj4sifWp</t>
+          <t>hzyf0b9b</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>45521.33333333334</v>
+        <v>45521.54166666666</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">hempel r 
+          <t xml:space="preserve">sather a 
   ger </t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">bruchwegstadion
-  mainz </t>
+          <t xml:space="preserve">new tivoli
+  aachen </t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>WzEYqEyg</t>
+          <t>j3PKcB4E</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CCQGbik8</t>
+          <t>63WsD2ei</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3813,7 +4061,7 @@
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
-          <t>pdPRS0me</t>
+          <t>A15eUM4C</t>
         </is>
       </c>
       <c r="O28" t="inlineStr"/>
@@ -3868,32 +4116,32 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>0K2qBFNG</t>
+          <t>CpiTEcOi</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>45521.33333333334</v>
+        <v>45521.54166666666</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">schlager d 
+          <t xml:space="preserve">bacher m 
   ger </t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">erzgebirgsstadion
-  aue </t>
+          <t xml:space="preserve">schuco arena
+  bielefeld </t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>vsXIDreP</t>
+          <t>pp38UXK8</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>88HSzjDr</t>
+          <t>dfNCCCzS</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3921,17 +4169,21 @@
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
-          <t>M5BRZDsC</t>
+          <t>zyLSrbZQ</t>
         </is>
       </c>
       <c r="O29" t="n">
-        <v>-3</v>
-      </c>
-      <c r="P29" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="P29" t="n">
+        <v>-2</v>
+      </c>
       <c r="Q29" t="n">
-        <v>-2</v>
-      </c>
-      <c r="R29" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="R29" t="n">
+        <v>-1</v>
+      </c>
       <c r="S29" t="n">
         <v>0</v>
       </c>
@@ -3980,32 +4232,32 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>lONsG15D</t>
+          <t>8QPARz8c</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>45520.65625</v>
+        <v>45521.4375</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">fritz m 
+          <t xml:space="preserve">welz t 
   ger </t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">donaustadion
-  ulm </t>
+          <t xml:space="preserve">ms technologie arena
+  villingen schwenningen </t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>tbC3EcQn</t>
+          <t>lKLJUxeT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>nVp0wiqd</t>
+          <t>KWixEVWi</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4030,23 +4282,15 @@
           <t>dfb pokal</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>QevvB2nf</t>
-        </is>
-      </c>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
-          <t>CQTUFgPk</t>
-        </is>
-      </c>
-      <c r="O30" t="n">
-        <v>-2</v>
-      </c>
+          <t>lGJdeemM</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="n">
-        <v>-1</v>
-      </c>
+      <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="n">
         <v>0</v>
@@ -4096,32 +4340,32 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>EF8gXauC</t>
+          <t>MZjh9ghT</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>45520.54166666666</v>
+        <v>45521.4375</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">fritz m 
+          <t xml:space="preserve">zwayer f 
   ger </t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">flyeralarm arena
-  wurzburger </t>
+          <t xml:space="preserve">stadion an der hafenstrasse
+  essen </t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>nVM1YUFj</t>
+          <t>EB0xsr77</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>hQAtP9Sl</t>
+          <t>KbS1suSm</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4149,16 +4393,12 @@
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
-          <t>CQTUFgPk</t>
-        </is>
-      </c>
-      <c r="O31" t="n">
-        <v>-1</v>
-      </c>
+          <t>pfoInmcq</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="n">
-        <v>-1</v>
-      </c>
+      <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="n">
         <v>0</v>
@@ -4208,32 +4448,32 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>hIsO3XFj</t>
+          <t>vyk5gjdE</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>45520.54166666666</v>
+        <v>45521.4375</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">willenborg f 
+          <t xml:space="preserve">dingert c 
   ger </t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">brita arena
-  wiesbaden </t>
+          <t xml:space="preserve">volksstadion greifswald
+  greifswald </t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ObxFt3lm</t>
+          <t>Q1yNyI5t</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>EuakNmc1</t>
+          <t>pzHW4oaE</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4258,23 +4498,15 @@
           <t>dfb pokal</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>QTAUlvUP</t>
-        </is>
-      </c>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
-          <t>vZA6VYpf</t>
-        </is>
-      </c>
-      <c r="O32" t="n">
-        <v>-4</v>
-      </c>
+          <t>l0fHXMdE</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="n">
-        <v>-2</v>
-      </c>
+      <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="n">
         <v>0</v>
@@ -4300,80 +4532,56 @@
       <c r="AL32" t="inlineStr"/>
       <c r="AM32" t="inlineStr"/>
       <c r="AN32" t="inlineStr"/>
-      <c r="AO32" t="n">
-        <v>-7.22727272727272</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>2.738636363636346</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>-9.025000000000006</v>
-      </c>
+      <c r="AO32" t="inlineStr"/>
+      <c r="AP32" t="inlineStr"/>
+      <c r="AQ32" t="inlineStr"/>
       <c r="AR32" t="inlineStr"/>
-      <c r="AS32" t="n">
-        <v>-3581285.962301588</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>-0.5727272727272723</v>
-      </c>
+      <c r="AS32" t="inlineStr"/>
+      <c r="AT32" t="inlineStr"/>
       <c r="AU32" t="inlineStr"/>
-      <c r="AV32" t="n">
-        <v>-2.321775793650772</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>-0.5224206349206351</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>0.4568181818181891</v>
-      </c>
+      <c r="AV32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr"/>
+      <c r="AX32" t="inlineStr"/>
       <c r="AY32" t="inlineStr"/>
-      <c r="AZ32" t="n">
-        <v>-5601534.090909092</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>-7.431249999999977</v>
-      </c>
+      <c r="AZ32" t="inlineStr"/>
+      <c r="BA32" t="inlineStr"/>
       <c r="BB32" t="inlineStr"/>
       <c r="BC32" t="inlineStr"/>
-      <c r="BD32" t="n">
-        <v>-7.606001984126991</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>-1.994196428571424</v>
-      </c>
+      <c r="BD32" t="inlineStr"/>
+      <c r="BE32" t="inlineStr"/>
       <c r="BF32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>pWQQJq6l</t>
+          <t>tbKZHNz1</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>45520.54166666666</v>
+        <v>45521.4375</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">aytekin d 
+          <t xml:space="preserve">lechner f 
   ger </t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">leuna chemie stadion
-  halle </t>
+          <t xml:space="preserve">audi sportpark
+  ingolstadt </t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>boX3cIQa</t>
+          <t>ne5QkLtB</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>ILyJuN3g</t>
+          <t>naWckLmC</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4401,12 +4609,16 @@
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
-          <t>QHesBmSQ</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr"/>
+          <t>8E86CPuD</t>
+        </is>
+      </c>
+      <c r="O33" t="n">
+        <v>-5</v>
+      </c>
       <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
+      <c r="Q33" t="n">
+        <v>-2</v>
+      </c>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="n">
         <v>0</v>
@@ -4453,6 +4665,974 @@
         <v>0</v>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>bF2q76Mr</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>45521.4375</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">winter n 
+  ger </t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ostalb arena
+  aalen </t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Oh2C15j0</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>59</v>
+      </c>
+      <c r="H34" t="n">
+        <v>593</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>txZLBQVC</t>
+        </is>
+      </c>
+      <c r="O34" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr"/>
+      <c r="AC34" t="inlineStr"/>
+      <c r="AD34" t="inlineStr"/>
+      <c r="AE34" t="inlineStr"/>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="inlineStr"/>
+      <c r="AH34" t="inlineStr"/>
+      <c r="AI34" t="inlineStr"/>
+      <c r="AJ34" t="n">
+        <v>67.625</v>
+      </c>
+      <c r="AK34" t="inlineStr"/>
+      <c r="AL34" t="inlineStr"/>
+      <c r="AM34" t="inlineStr"/>
+      <c r="AN34" t="inlineStr"/>
+      <c r="AO34" t="inlineStr"/>
+      <c r="AP34" t="inlineStr"/>
+      <c r="AQ34" t="inlineStr"/>
+      <c r="AR34" t="inlineStr"/>
+      <c r="AS34" t="inlineStr"/>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AU34" t="inlineStr"/>
+      <c r="AV34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr"/>
+      <c r="AX34" t="inlineStr"/>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr"/>
+      <c r="BA34" t="inlineStr"/>
+      <c r="BB34" t="inlineStr"/>
+      <c r="BC34" t="inlineStr"/>
+      <c r="BD34" t="inlineStr"/>
+      <c r="BE34" t="inlineStr"/>
+      <c r="BF34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>f1nnRRDE</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>45521.4375</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dingert c 
+  ger </t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadion an der bremer bruck
+  osnabruck </t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>88Xgj1Y5</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>59</v>
+      </c>
+      <c r="H35" t="n">
+        <v>593</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>lxrr7DgN</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>l0fHXMdE</t>
+        </is>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1</v>
+      </c>
+      <c r="R35" t="n">
+        <v>-1</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr"/>
+      <c r="AB35" t="inlineStr"/>
+      <c r="AC35" t="inlineStr"/>
+      <c r="AD35" t="inlineStr"/>
+      <c r="AE35" t="inlineStr"/>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="inlineStr"/>
+      <c r="AH35" t="inlineStr"/>
+      <c r="AI35" t="inlineStr"/>
+      <c r="AJ35" t="inlineStr"/>
+      <c r="AK35" t="inlineStr"/>
+      <c r="AL35" t="inlineStr"/>
+      <c r="AM35" t="n">
+        <v>-6.924171839497106</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>-0.1715909090908951</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>-0.6931818181818179</v>
+      </c>
+      <c r="AP35" t="inlineStr"/>
+      <c r="AQ35" t="n">
+        <v>-0.4614915345428789</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>-6.793228138784983</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>-0.4664409741140503</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>-1.542424242424239</v>
+      </c>
+      <c r="AU35" t="inlineStr"/>
+      <c r="AV35" t="n">
+        <v>-6.260984848484853</v>
+      </c>
+      <c r="AW35" t="inlineStr"/>
+      <c r="AX35" t="inlineStr"/>
+      <c r="AY35" t="n">
+        <v>-5011078.11957682</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>-7351805.555555555</v>
+      </c>
+      <c r="BA35" t="inlineStr"/>
+      <c r="BB35" t="inlineStr"/>
+      <c r="BC35" t="n">
+        <v>-8.372474747474726</v>
+      </c>
+      <c r="BD35" t="inlineStr"/>
+      <c r="BE35" t="n">
+        <v>0.7741011773596647</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>0K2qBFNG</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>45521.33333333334</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">schlager d 
+  ger </t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">erzgebirgsstadion
+  aue </t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>vsXIDreP</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>59</v>
+      </c>
+      <c r="H36" t="n">
+        <v>593</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>M5BRZDsC</t>
+        </is>
+      </c>
+      <c r="O36" t="n">
+        <v>-3</v>
+      </c>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="n">
+        <v>-2</v>
+      </c>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr"/>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr"/>
+      <c r="AB36" t="inlineStr"/>
+      <c r="AC36" t="inlineStr"/>
+      <c r="AD36" t="inlineStr"/>
+      <c r="AE36" t="inlineStr"/>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="inlineStr"/>
+      <c r="AH36" t="inlineStr"/>
+      <c r="AI36" t="inlineStr"/>
+      <c r="AJ36" t="inlineStr"/>
+      <c r="AK36" t="inlineStr"/>
+      <c r="AL36" t="inlineStr"/>
+      <c r="AM36" t="inlineStr"/>
+      <c r="AN36" t="inlineStr"/>
+      <c r="AO36" t="inlineStr"/>
+      <c r="AP36" t="inlineStr"/>
+      <c r="AQ36" t="inlineStr"/>
+      <c r="AR36" t="inlineStr"/>
+      <c r="AS36" t="inlineStr"/>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AU36" t="inlineStr"/>
+      <c r="AV36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr"/>
+      <c r="AX36" t="inlineStr"/>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr"/>
+      <c r="BA36" t="inlineStr"/>
+      <c r="BB36" t="inlineStr"/>
+      <c r="BC36" t="inlineStr"/>
+      <c r="BD36" t="inlineStr"/>
+      <c r="BE36" t="inlineStr"/>
+      <c r="BF36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>Kj4sifWp</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>45521.33333333334</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lechner f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bruchwegstadion
+  mainz </t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>WzEYqEyg</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>CCQGbik8</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>59</v>
+      </c>
+      <c r="H37" t="n">
+        <v>593</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1</v>
+      </c>
+      <c r="J37" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>8E86CPuD</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="inlineStr"/>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr"/>
+      <c r="AB37" t="inlineStr"/>
+      <c r="AC37" t="inlineStr"/>
+      <c r="AD37" t="inlineStr"/>
+      <c r="AE37" t="inlineStr"/>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="inlineStr"/>
+      <c r="AH37" t="inlineStr"/>
+      <c r="AI37" t="inlineStr"/>
+      <c r="AJ37" t="n">
+        <v>67</v>
+      </c>
+      <c r="AK37" t="inlineStr"/>
+      <c r="AL37" t="inlineStr"/>
+      <c r="AM37" t="inlineStr"/>
+      <c r="AN37" t="inlineStr"/>
+      <c r="AO37" t="inlineStr"/>
+      <c r="AP37" t="inlineStr"/>
+      <c r="AQ37" t="inlineStr"/>
+      <c r="AR37" t="inlineStr"/>
+      <c r="AS37" t="inlineStr"/>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AU37" t="inlineStr"/>
+      <c r="AV37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr"/>
+      <c r="AX37" t="inlineStr"/>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr"/>
+      <c r="BA37" t="inlineStr"/>
+      <c r="BB37" t="inlineStr"/>
+      <c r="BC37" t="inlineStr"/>
+      <c r="BD37" t="inlineStr"/>
+      <c r="BE37" t="inlineStr"/>
+      <c r="BF37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>lONsG15D</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>45520.65625</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fritz m 
+  ger </t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">donaustadion
+  ulm </t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>tbC3EcQn</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>59</v>
+      </c>
+      <c r="H38" t="n">
+        <v>593</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J38" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>zyLSrbZQ</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>CQTUFgPk</t>
+        </is>
+      </c>
+      <c r="O38" t="n">
+        <v>-2</v>
+      </c>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr"/>
+      <c r="X38" t="inlineStr"/>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr"/>
+      <c r="AB38" t="inlineStr"/>
+      <c r="AC38" t="inlineStr"/>
+      <c r="AD38" t="inlineStr"/>
+      <c r="AE38" t="inlineStr"/>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="inlineStr"/>
+      <c r="AH38" t="inlineStr"/>
+      <c r="AI38" t="inlineStr"/>
+      <c r="AJ38" t="inlineStr"/>
+      <c r="AK38" t="inlineStr"/>
+      <c r="AL38" t="inlineStr"/>
+      <c r="AM38" t="n">
+        <v>-12.8859176515069</v>
+      </c>
+      <c r="AN38" t="inlineStr"/>
+      <c r="AO38" t="inlineStr"/>
+      <c r="AP38" t="inlineStr"/>
+      <c r="AQ38" t="n">
+        <v>-1.206357280924643</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>-16.49309692163132</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>0.6258056517281716</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AU38" t="inlineStr"/>
+      <c r="AV38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr"/>
+      <c r="AX38" t="inlineStr"/>
+      <c r="AY38" t="n">
+        <v>-27515071.72873668</v>
+      </c>
+      <c r="AZ38" t="inlineStr"/>
+      <c r="BA38" t="inlineStr"/>
+      <c r="BB38" t="inlineStr"/>
+      <c r="BC38" t="inlineStr"/>
+      <c r="BD38" t="inlineStr"/>
+      <c r="BE38" t="n">
+        <v>-3.240410242090732</v>
+      </c>
+      <c r="BF38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>EF8gXauC</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>45520.54166666666</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fritz m 
+  ger </t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">flyeralarm arena
+  wurzburger </t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>nVM1YUFj</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>59</v>
+      </c>
+      <c r="H39" t="n">
+        <v>593</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1</v>
+      </c>
+      <c r="J39" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>CQTUFgPk</t>
+        </is>
+      </c>
+      <c r="O39" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="inlineStr"/>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr"/>
+      <c r="AB39" t="inlineStr"/>
+      <c r="AC39" t="inlineStr"/>
+      <c r="AD39" t="inlineStr"/>
+      <c r="AE39" t="inlineStr"/>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="inlineStr"/>
+      <c r="AH39" t="inlineStr"/>
+      <c r="AI39" t="inlineStr"/>
+      <c r="AJ39" t="inlineStr"/>
+      <c r="AK39" t="inlineStr"/>
+      <c r="AL39" t="inlineStr"/>
+      <c r="AM39" t="inlineStr"/>
+      <c r="AN39" t="inlineStr"/>
+      <c r="AO39" t="inlineStr"/>
+      <c r="AP39" t="inlineStr"/>
+      <c r="AQ39" t="inlineStr"/>
+      <c r="AR39" t="inlineStr"/>
+      <c r="AS39" t="inlineStr"/>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AU39" t="inlineStr"/>
+      <c r="AV39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr"/>
+      <c r="AX39" t="inlineStr"/>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr"/>
+      <c r="BA39" t="inlineStr"/>
+      <c r="BB39" t="inlineStr"/>
+      <c r="BC39" t="inlineStr"/>
+      <c r="BD39" t="inlineStr"/>
+      <c r="BE39" t="inlineStr"/>
+      <c r="BF39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>hIsO3XFj</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>45520.54166666666</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">willenborg f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brita arena
+  wiesbaden </t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>ObxFt3lm</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>59</v>
+      </c>
+      <c r="H40" t="n">
+        <v>593</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J40" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>QTAUlvUP</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>vZA6VYpf</t>
+        </is>
+      </c>
+      <c r="O40" t="n">
+        <v>-4</v>
+      </c>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="n">
+        <v>-2</v>
+      </c>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr"/>
+      <c r="X40" t="inlineStr"/>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr"/>
+      <c r="AB40" t="inlineStr"/>
+      <c r="AC40" t="inlineStr"/>
+      <c r="AD40" t="inlineStr"/>
+      <c r="AE40" t="inlineStr"/>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="inlineStr"/>
+      <c r="AH40" t="inlineStr"/>
+      <c r="AI40" t="inlineStr"/>
+      <c r="AJ40" t="inlineStr"/>
+      <c r="AK40" t="inlineStr"/>
+      <c r="AL40" t="inlineStr"/>
+      <c r="AM40" t="n">
+        <v>-7.646656295093791</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>2.418904958677672</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>-0.5852272727272725</v>
+      </c>
+      <c r="AP40" t="inlineStr"/>
+      <c r="AQ40" t="n">
+        <v>-0.5003720238095237</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>-7.660454996392488</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>-1.312894570707044</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>0.3032024793388395</v>
+      </c>
+      <c r="AU40" t="inlineStr"/>
+      <c r="AV40" t="n">
+        <v>-8.790805785123979</v>
+      </c>
+      <c r="AW40" t="inlineStr"/>
+      <c r="AX40" t="inlineStr"/>
+      <c r="AY40" t="n">
+        <v>-3649653.905122655</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>-5679183.88429752</v>
+      </c>
+      <c r="BA40" t="inlineStr"/>
+      <c r="BB40" t="inlineStr"/>
+      <c r="BC40" t="n">
+        <v>-7.321797520661164</v>
+      </c>
+      <c r="BD40" t="inlineStr"/>
+      <c r="BE40" t="n">
+        <v>-1.822792658730155</v>
+      </c>
+      <c r="BF40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>pWQQJq6l</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>45520.54166666666</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aytekin d 
+  ger </t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">leuna chemie stadion
+  halle </t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>boX3cIQa</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>59</v>
+      </c>
+      <c r="H41" t="n">
+        <v>593</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1</v>
+      </c>
+      <c r="J41" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>QHesBmSQ</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr"/>
+      <c r="X41" t="inlineStr"/>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr"/>
+      <c r="AB41" t="inlineStr"/>
+      <c r="AC41" t="inlineStr"/>
+      <c r="AD41" t="inlineStr"/>
+      <c r="AE41" t="inlineStr"/>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="inlineStr"/>
+      <c r="AH41" t="inlineStr"/>
+      <c r="AI41" t="inlineStr"/>
+      <c r="AJ41" t="inlineStr"/>
+      <c r="AK41" t="inlineStr"/>
+      <c r="AL41" t="inlineStr"/>
+      <c r="AM41" t="inlineStr"/>
+      <c r="AN41" t="inlineStr"/>
+      <c r="AO41" t="inlineStr"/>
+      <c r="AP41" t="inlineStr"/>
+      <c r="AQ41" t="inlineStr"/>
+      <c r="AR41" t="inlineStr"/>
+      <c r="AS41" t="inlineStr"/>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AU41" t="inlineStr"/>
+      <c r="AV41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr"/>
+      <c r="AX41" t="inlineStr"/>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr"/>
+      <c r="BA41" t="inlineStr"/>
+      <c r="BB41" t="inlineStr"/>
+      <c r="BC41" t="inlineStr"/>
+      <c r="BD41" t="inlineStr"/>
+      <c r="BE41" t="inlineStr"/>
+      <c r="BF41" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/germany/p6_deployment/data_preparation/df_constructed.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_constructed.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE21"/>
+  <dimension ref="A1:BE19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -525,84 +525,84 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_expected_goals_(xg)</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals_against</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points_against</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days_against</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession_against</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_fouls</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_fouls_against</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days_against</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts_against</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession_against</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points_against</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals_against</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
-        </is>
-      </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
@@ -615,97 +615,97 @@
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_age_player_miss</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_start</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
         </is>
       </c>
       <c r="BE1" s="1" t="inlineStr">
@@ -792,67 +792,103 @@
       <c r="S2" t="n">
         <v>0</v>
       </c>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
+      <c r="T2" t="n">
+        <v>-0.2833333333333333</v>
+      </c>
+      <c r="U2" t="n">
+        <v>-1.413333333333334</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="W2" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>77</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>73.84848484848484</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.8056037886573624</v>
+      </c>
       <c r="AM2" t="n">
+        <v>1.336026936026936</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>-0.3500116268221021</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>5.189274310676581</v>
+      </c>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="n">
+        <v>23887475.50089946</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>6.791297154994481</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>32729595.95959596</v>
+      </c>
+      <c r="AT2" t="n">
         <v>-2.372025498269949</v>
       </c>
-      <c r="AN2" t="n">
-        <v>0.8056037886573624</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>23887475.50089946</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>-0.1077441077441073</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>1.336026936026936</v>
-      </c>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="n">
-        <v>7.400673400673412</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>6.791297154994481</v>
-      </c>
+      <c r="AU2" t="inlineStr"/>
       <c r="AV2" t="inlineStr"/>
       <c r="AW2" t="n">
-        <v>5.189274310676581</v>
+        <v>6.556228956228935</v>
       </c>
       <c r="AX2" t="n">
-        <v>32729595.95959596</v>
+        <v>1.250505050505069</v>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr"/>
       <c r="BA2" t="n">
-        <v>6.556228956228935</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>-0.3500116268221021</v>
-      </c>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="n">
-        <v>1.250505050505069</v>
-      </c>
+        <v>-0.1077441077441073</v>
+      </c>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="n">
+        <v>7.400673400673412</v>
+      </c>
+      <c r="BD2" t="inlineStr"/>
       <c r="BE2" t="n">
         <v>0</v>
       </c>
@@ -935,67 +971,103 @@
       <c r="S3" t="n">
         <v>0</v>
       </c>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
+      <c r="T3" t="n">
+        <v>-0.5899999999999999</v>
+      </c>
+      <c r="U3" t="n">
+        <v>-2.326666666666666</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="W3" t="n">
+        <v>-2.25</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.9166666666666667</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>-1.583333333333333</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>-0.8333333333333357</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.8333333333333357</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>2.083333333333333</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>-1.833333333333333</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>-0.4166666666666661</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>74.33333333333333</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>78.04848484848485</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>-0.1518165995797576</v>
+      </c>
       <c r="AM3" t="n">
+        <v>-0.4143265993265994</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>3.124671843750786</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>-1.790724475329739</v>
+      </c>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="n">
+        <v>-1934217.10368092</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>-5.41000727829676</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>-2081893.939393939</v>
+      </c>
+      <c r="AT3" t="n">
         <v>-0.861722108301052</v>
       </c>
-      <c r="AN3" t="n">
-        <v>-0.1518165995797576</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>-1934217.10368092</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>0.4179629629629638</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>-0.4143265993265994</v>
-      </c>
-      <c r="AR3" t="inlineStr"/>
-      <c r="AS3" t="inlineStr"/>
-      <c r="AT3" t="n">
-        <v>-2.063956228956243</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>-5.41000727829676</v>
-      </c>
+      <c r="AU3" t="inlineStr"/>
       <c r="AV3" t="inlineStr"/>
       <c r="AW3" t="n">
-        <v>-1.790724475329739</v>
+        <v>-1.46648148148148</v>
       </c>
       <c r="AX3" t="n">
-        <v>-2081893.939393939</v>
+        <v>1.042272727272689</v>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr"/>
       <c r="BA3" t="n">
-        <v>-1.46648148148148</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>3.124671843750786</v>
-      </c>
-      <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="n">
-        <v>1.042272727272689</v>
-      </c>
+        <v>0.4179629629629638</v>
+      </c>
+      <c r="BB3" t="inlineStr"/>
+      <c r="BC3" t="n">
+        <v>-2.063956228956243</v>
+      </c>
+      <c r="BD3" t="inlineStr"/>
       <c r="BE3" t="n">
         <v>0</v>
       </c>
@@ -1079,92 +1151,102 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>1</v>
+        <v>1.665</v>
       </c>
       <c r="U4" t="n">
-        <v>11</v>
-      </c>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
+        <v>-0.2350000000000001</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.25</v>
+      </c>
       <c r="X4" t="n">
-        <v>-2</v>
+        <v>1.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>4</v>
+        <v>-0.75</v>
       </c>
       <c r="Z4" t="n">
-        <v>-21</v>
+        <v>2</v>
       </c>
       <c r="AA4" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>-0.75</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
+        <v>0.75</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>-3</v>
+      </c>
       <c r="AF4" t="n">
         <v>-1</v>
       </c>
       <c r="AG4" t="n">
-        <v>1</v>
+        <v>5.75</v>
       </c>
       <c r="AH4" t="n">
-        <v>-5</v>
+        <v>5.75</v>
       </c>
       <c r="AI4" t="n">
-        <v>2</v>
+        <v>-6</v>
       </c>
       <c r="AJ4" t="n">
-        <v>75.09999999999999</v>
-      </c>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
+        <v>74.05</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>76.86363636363637</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.01812614007391233</v>
+      </c>
       <c r="AM4" t="n">
+        <v>-0.02097147950089129</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>-1.727029481040791</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1.94337948835188</v>
+      </c>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="n">
+        <v>15839869.36198489</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>2.759818151255416</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>5029254.307783723</v>
+      </c>
+      <c r="AT4" t="n">
         <v>-3.316519808731073</v>
       </c>
-      <c r="AN4" t="n">
-        <v>0.01812614007391233</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>15839869.36198489</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>0.7681639928698729</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>-0.02097147950089129</v>
-      </c>
-      <c r="AR4" t="inlineStr"/>
-      <c r="AS4" t="inlineStr"/>
-      <c r="AT4" t="n">
-        <v>0.4562388591800186</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>2.759818151255416</v>
-      </c>
+      <c r="AU4" t="inlineStr"/>
       <c r="AV4" t="inlineStr"/>
       <c r="AW4" t="n">
-        <v>1.94337948835188</v>
+        <v>1.106809269162198</v>
       </c>
       <c r="AX4" t="n">
-        <v>5029254.307783723</v>
+        <v>2.350656565656578</v>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr"/>
       <c r="BA4" t="n">
-        <v>1.106809269162198</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>-1.727029481040791</v>
-      </c>
-      <c r="BC4" t="inlineStr"/>
-      <c r="BD4" t="n">
-        <v>2.350656565656578</v>
-      </c>
+        <v>0.7681639928698729</v>
+      </c>
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="n">
+        <v>0.4562388591800186</v>
+      </c>
+      <c r="BD4" t="inlineStr"/>
       <c r="BE4" t="n">
         <v>0</v>
       </c>
@@ -1172,7 +1254,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>AgAeVYgC</t>
+          <t>0OYDmG9t</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -1180,24 +1262,24 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">petersen m 
+          <t xml:space="preserve">burda m 
   ger </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">deutsche bank park
-  frankfurt </t>
+          <t xml:space="preserve">weserstadion
+  bremen </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>8vndvXTk</t>
+          <t>Ig1f1fy3</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>hQAtP9Sl</t>
+          <t>nP1i5US1</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1224,90 +1306,126 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>SQrxFAMl</t>
+          <t>tnTvQd1l</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>KUx4Q7x1</t>
+          <t>IkCftsQm</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>3</v>
+        <v>-19</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="Q5" t="n">
-        <v>4</v>
+        <v>-3</v>
       </c>
       <c r="R5" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr"/>
+      <c r="T5" t="n">
+        <v>1.853333333333333</v>
+      </c>
+      <c r="U5" t="n">
+        <v>-0.5100000000000002</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.6666666666666665</v>
+      </c>
+      <c r="W5" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>-0.8333333333333334</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>-19.83333333333334</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>19.83333333333334</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>3.833333333333333</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>-3.333333333333334</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>8.666666666666668</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>74.47407407407407</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>74.36363636363636</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>-0.8243009217416943</v>
+      </c>
       <c r="AM5" t="n">
-        <v>-1.077976760082038</v>
+        <v>-1.124242424242424</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.001042207419917007</v>
+        <v>-0.1707883394903931</v>
       </c>
       <c r="AO5" t="n">
-        <v>83588.77251060028</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>-2.342289562289562</v>
-      </c>
+        <v>-9.162783824437469</v>
+      </c>
+      <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="n">
-        <v>-0.1315151515151511</v>
-      </c>
-      <c r="AR5" t="inlineStr"/>
-      <c r="AS5" t="inlineStr"/>
+        <v>-17387515.68374617</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>-8.01548829803977</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>-24596666.66666666</v>
+      </c>
       <c r="AT5" t="n">
-        <v>2.52343434343436</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>0.8463784088861672</v>
-      </c>
+        <v>0.5684801571277092</v>
+      </c>
+      <c r="AU5" t="inlineStr"/>
       <c r="AV5" t="inlineStr"/>
       <c r="AW5" t="n">
-        <v>-0.2893557348510996</v>
+        <v>-6.787878787878782</v>
       </c>
       <c r="AX5" t="n">
-        <v>6644723.905723901</v>
+        <v>-1.47939393939393</v>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="n">
-        <v>1.825117845117845</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>-0.6155437017975771</v>
-      </c>
-      <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="n">
-        <v>-2.338316498316516</v>
-      </c>
+        <v>0.6242424242424178</v>
+      </c>
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="n">
+        <v>-7.127272727272725</v>
+      </c>
+      <c r="BD5" t="inlineStr"/>
       <c r="BE5" t="n">
         <v>0</v>
       </c>
@@ -1315,7 +1433,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>QVJwrCwI</t>
+          <t>U3QUqY85</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -1323,24 +1441,24 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">storks s 
+          <t xml:space="preserve">badstubner f 
   ger </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">holstein stadion
-  kiel </t>
+          <t xml:space="preserve">vonovia ruhrstadion
+  bochum </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>63WsD2ei</t>
+          <t>8Y2m6ADe</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>nwkTahLL</t>
+          <t>88HSzjDr</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1367,86 +1485,126 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>SfKt2E6n</t>
+          <t>zyLSrbZQ</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>f3ddUIXs</t>
+          <t>M5BRZDsC</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>-2</v>
-      </c>
-      <c r="P6" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-4</v>
+      </c>
       <c r="Q6" t="n">
+        <v>7</v>
+      </c>
+      <c r="R6" t="n">
         <v>-1</v>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
         <v>0</v>
       </c>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr"/>
+      <c r="T6" t="n">
+        <v>-1.043333333333333</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.423333333333333</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>75.79545454545455</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>74.45454545454545</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>-0.2155674138457826</v>
+      </c>
       <c r="AM6" t="n">
-        <v>2.3578166935051</v>
+        <v>-0.2682471776589426</v>
       </c>
       <c r="AN6" t="n">
-        <v>-0.2364803312629402</v>
+        <v>3.499878116006126</v>
       </c>
       <c r="AO6" t="n">
-        <v>-6998787.79905682</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>-0.2021548821548826</v>
-      </c>
+        <v>-2.43574116693344</v>
+      </c>
+      <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="n">
-        <v>-0.4826262626262625</v>
-      </c>
-      <c r="AR6" t="inlineStr"/>
-      <c r="AS6" t="inlineStr"/>
+        <v>-4332638.692938169</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>-5.105190739287195</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>-4911360.962566844</v>
+      </c>
       <c r="AT6" t="n">
-        <v>-6.896228956228953</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>-7.265292538915745</v>
-      </c>
+        <v>-1.262473170254196</v>
+      </c>
+      <c r="AU6" t="inlineStr"/>
       <c r="AV6" t="inlineStr"/>
       <c r="AW6" t="n">
-        <v>-7.062239858906537</v>
+        <v>-2.131875618934444</v>
       </c>
       <c r="AX6" t="n">
-        <v>-8879589.225589225</v>
+        <v>-2.211051693404642</v>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr"/>
       <c r="BA6" t="n">
-        <v>-7.11232323232322</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>0.9633124376964943</v>
-      </c>
-      <c r="BC6" t="inlineStr"/>
-      <c r="BD6" t="n">
-        <v>-0.5230976430976284</v>
-      </c>
+        <v>2.715218855218854</v>
+      </c>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="n">
+        <v>-3.187023172905526</v>
+      </c>
+      <c r="BD6" t="inlineStr"/>
       <c r="BE6" t="n">
         <v>0</v>
       </c>
@@ -1454,7 +1612,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>0OYDmG9t</t>
+          <t>QVJwrCwI</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -1462,24 +1620,24 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">burda m 
+          <t xml:space="preserve">storks s 
   ger </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">weserstadion
-  bremen </t>
+          <t xml:space="preserve">holstein stadion
+  kiel </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ig1f1fy3</t>
+          <t>63WsD2ei</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>nP1i5US1</t>
+          <t>nwkTahLL</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1506,90 +1664,122 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>tnTvQd1l</t>
+          <t>SfKt2E6n</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>IkCftsQm</t>
+          <t>f3ddUIXs</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>-19</v>
-      </c>
-      <c r="P7" t="n">
-        <v>-3</v>
-      </c>
+        <v>-2</v>
+      </c>
+      <c r="P7" t="inlineStr"/>
       <c r="Q7" t="n">
-        <v>-3</v>
-      </c>
-      <c r="R7" t="n">
-        <v>-3</v>
-      </c>
+        <v>-1</v>
+      </c>
+      <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
         <v>0</v>
       </c>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr"/>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="inlineStr"/>
-      <c r="AJ7" t="inlineStr"/>
-      <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="inlineStr"/>
+      <c r="T7" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>-20</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>71.09090909090909</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>79.18181818181819</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>-0.2364803312629402</v>
+      </c>
       <c r="AM7" t="n">
-        <v>0.5684801571277092</v>
+        <v>-0.4826262626262625</v>
       </c>
       <c r="AN7" t="n">
-        <v>-0.8243009217416943</v>
+        <v>0.9633124376964943</v>
       </c>
       <c r="AO7" t="n">
-        <v>-17387515.68374617</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>0.6242424242424178</v>
-      </c>
+        <v>-7.062239858906537</v>
+      </c>
+      <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="n">
-        <v>-1.124242424242424</v>
-      </c>
-      <c r="AR7" t="inlineStr"/>
-      <c r="AS7" t="inlineStr"/>
+        <v>-6998787.79905682</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>-7.265292538915745</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>-8879589.225589225</v>
+      </c>
       <c r="AT7" t="n">
-        <v>-7.127272727272725</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>-8.01548829803977</v>
-      </c>
+        <v>2.3578166935051</v>
+      </c>
+      <c r="AU7" t="inlineStr"/>
       <c r="AV7" t="inlineStr"/>
       <c r="AW7" t="n">
-        <v>-9.162783824437469</v>
+        <v>-7.11232323232322</v>
       </c>
       <c r="AX7" t="n">
-        <v>-24596666.66666666</v>
+        <v>-0.5230976430976284</v>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr"/>
       <c r="BA7" t="n">
-        <v>-6.787878787878782</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>-0.1707883394903931</v>
-      </c>
-      <c r="BC7" t="inlineStr"/>
-      <c r="BD7" t="n">
-        <v>-1.47939393939393</v>
-      </c>
+        <v>-0.2021548821548826</v>
+      </c>
+      <c r="BB7" t="inlineStr"/>
+      <c r="BC7" t="n">
+        <v>-6.896228956228953</v>
+      </c>
+      <c r="BD7" t="inlineStr"/>
       <c r="BE7" t="n">
         <v>0</v>
       </c>
@@ -1597,7 +1787,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>61DvZGfm</t>
+          <t>AgAeVYgC</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -1605,24 +1795,24 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">hempel r 
+          <t xml:space="preserve">petersen m 
   ger </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">mhparena
-  stuttgart </t>
+          <t xml:space="preserve">deutsche bank park
+  frankfurt </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>nJQmYp1B</t>
+          <t>8vndvXTk</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>EuakNmc1</t>
+          <t>hQAtP9Sl</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1649,90 +1839,126 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>hAcTWKKN</t>
+          <t>SQrxFAMl</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>vZA6VYpf</t>
+          <t>KUx4Q7x1</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q8" t="n">
         <v>4</v>
       </c>
-      <c r="Q8" t="n">
-        <v>7</v>
-      </c>
       <c r="R8" t="n">
+        <v>3</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-1.733333333333334</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.793333333333333</v>
+      </c>
+      <c r="V8" t="n">
+        <v>-3.166666666666667</v>
+      </c>
+      <c r="W8" t="n">
+        <v>3</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-2.666666666666667</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-11.83333333333334</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>11.83333333333334</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>-2.166666666666667</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="AF8" t="n">
         <v>2</v>
       </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr"/>
-      <c r="AE8" t="inlineStr"/>
-      <c r="AF8" t="inlineStr"/>
-      <c r="AG8" t="inlineStr"/>
-      <c r="AH8" t="inlineStr"/>
-      <c r="AI8" t="inlineStr"/>
-      <c r="AJ8" t="inlineStr"/>
-      <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="inlineStr"/>
+      <c r="AG8" t="n">
+        <v>-3.666666666666667</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.6666666666666661</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>80.07070707070706</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>70.45454545454545</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.001042207419917007</v>
+      </c>
       <c r="AM8" t="n">
-        <v>-2.316984126984124</v>
+        <v>-0.1315151515151511</v>
       </c>
       <c r="AN8" t="n">
-        <v>-0.2438624338624338</v>
+        <v>-0.6155437017975771</v>
       </c>
       <c r="AO8" t="n">
-        <v>934490.0793650793</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>-1.381818181818179</v>
-      </c>
+        <v>-0.2893557348510996</v>
+      </c>
+      <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="n">
-        <v>-0.05575757575757545</v>
-      </c>
-      <c r="AR8" t="inlineStr"/>
-      <c r="AS8" t="inlineStr"/>
+        <v>83588.77251060028</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0.8463784088861672</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>6644723.905723903</v>
+      </c>
       <c r="AT8" t="n">
-        <v>0.8400000000000034</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>-0.7899470899470913</v>
-      </c>
+        <v>-1.077976760082038</v>
+      </c>
+      <c r="AU8" t="inlineStr"/>
       <c r="AV8" t="inlineStr"/>
       <c r="AW8" t="n">
-        <v>-1.298994708994684</v>
+        <v>1.825117845117845</v>
       </c>
       <c r="AX8" t="n">
-        <v>5140060.606060603</v>
+        <v>-2.338316498316516</v>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr"/>
       <c r="BA8" t="n">
-        <v>1.714545454545458</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>-1.924708994709</v>
-      </c>
-      <c r="BC8" t="inlineStr"/>
-      <c r="BD8" t="n">
-        <v>1.363636363636346</v>
-      </c>
+        <v>-2.342289562289562</v>
+      </c>
+      <c r="BB8" t="inlineStr"/>
+      <c r="BC8" t="n">
+        <v>2.52343434343436</v>
+      </c>
+      <c r="BD8" t="inlineStr"/>
       <c r="BE8" t="n">
         <v>0</v>
       </c>
@@ -1740,7 +1966,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>U3QUqY85</t>
+          <t>61DvZGfm</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -1748,24 +1974,24 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">badstubner f 
+          <t xml:space="preserve">hempel r 
   ger </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">vonovia ruhrstadion
-  bochum </t>
+          <t xml:space="preserve">mhparena
+  stuttgart </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>8Y2m6ADe</t>
+          <t>nJQmYp1B</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>88HSzjDr</t>
+          <t>EuakNmc1</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1792,90 +2018,126 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>zyLSrbZQ</t>
+          <t>hAcTWKKN</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>M5BRZDsC</t>
+          <t>vZA6VYpf</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P9" t="n">
-        <v>-4</v>
+        <v>4</v>
       </c>
       <c r="Q9" t="n">
         <v>7</v>
       </c>
       <c r="R9" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr"/>
-      <c r="AE9" t="inlineStr"/>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="inlineStr"/>
-      <c r="AH9" t="inlineStr"/>
-      <c r="AI9" t="inlineStr"/>
-      <c r="AJ9" t="inlineStr"/>
-      <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="inlineStr"/>
+      <c r="T9" t="n">
+        <v>0.7566666666666666</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.2866666666666668</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="W9" t="n">
+        <v>-0.3333333333333334</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>4.416666666666664</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-4.416666666666664</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>-4.25</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>-3.666666666666666</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>79.15824915824916</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>73.90606060606061</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>-0.2438624338624338</v>
+      </c>
       <c r="AM9" t="n">
-        <v>-1.262473170254196</v>
+        <v>-0.05575757575757545</v>
       </c>
       <c r="AN9" t="n">
-        <v>-0.2155674138457826</v>
+        <v>-1.924708994709</v>
       </c>
       <c r="AO9" t="n">
-        <v>-4332638.692938169</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>2.715218855218854</v>
-      </c>
+        <v>-1.298994708994684</v>
+      </c>
+      <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="n">
-        <v>-0.2682471776589426</v>
-      </c>
-      <c r="AR9" t="inlineStr"/>
-      <c r="AS9" t="inlineStr"/>
+        <v>934490.0793650793</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>-0.7899470899470913</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>5140060.606060603</v>
+      </c>
       <c r="AT9" t="n">
-        <v>-3.187023172905526</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>-5.105190739287195</v>
-      </c>
+        <v>-2.316984126984124</v>
+      </c>
+      <c r="AU9" t="inlineStr"/>
       <c r="AV9" t="inlineStr"/>
       <c r="AW9" t="n">
-        <v>-2.43574116693344</v>
+        <v>1.714545454545458</v>
       </c>
       <c r="AX9" t="n">
-        <v>-4911360.962566844</v>
+        <v>1.363636363636346</v>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr"/>
       <c r="BA9" t="n">
-        <v>-2.131875618934444</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>3.499878116006126</v>
-      </c>
-      <c r="BC9" t="inlineStr"/>
-      <c r="BD9" t="n">
-        <v>-2.211051693404642</v>
-      </c>
+        <v>-1.381818181818179</v>
+      </c>
+      <c r="BB9" t="inlineStr"/>
+      <c r="BC9" t="n">
+        <v>0.8400000000000034</v>
+      </c>
+      <c r="BD9" t="inlineStr"/>
       <c r="BE9" t="n">
         <v>0</v>
       </c>
@@ -1958,67 +2220,103 @@
       <c r="S10" t="n">
         <v>0</v>
       </c>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr"/>
-      <c r="AE10" t="inlineStr"/>
-      <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="inlineStr"/>
-      <c r="AH10" t="inlineStr"/>
-      <c r="AI10" t="inlineStr"/>
-      <c r="AJ10" t="inlineStr"/>
-      <c r="AK10" t="inlineStr"/>
-      <c r="AL10" t="inlineStr"/>
+      <c r="T10" t="n">
+        <v>0.1016666666666666</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-0.3233333333333335</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.9999999999999998</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>-11</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.333333333333333</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>3.666666666666668</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>2.333333333333332</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>-2.333333333333334</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>3.666666666666666</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>73.63636363636364</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>69.05454545454546</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0.4717739396801184</v>
+      </c>
       <c r="AM10" t="n">
+        <v>0.6141414141414141</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1.172395763967081</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>6.970296413336072</v>
+      </c>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="n">
+        <v>3901532.419010489</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>4.830097586962566</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>6122772.166105499</v>
+      </c>
+      <c r="AT10" t="n">
         <v>-1.720902396893962</v>
       </c>
-      <c r="AN10" t="n">
-        <v>0.4717739396801184</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>3901532.419010489</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>1.064309764309765</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>0.6141414141414141</v>
-      </c>
-      <c r="AR10" t="inlineStr"/>
-      <c r="AS10" t="inlineStr"/>
-      <c r="AT10" t="n">
-        <v>5.108193041526391</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>4.830097586962566</v>
-      </c>
+      <c r="AU10" t="inlineStr"/>
       <c r="AV10" t="inlineStr"/>
       <c r="AW10" t="n">
-        <v>6.970296413336072</v>
+        <v>5.783726150392837</v>
       </c>
       <c r="AX10" t="n">
-        <v>6122772.166105499</v>
+        <v>-0.2384960718294167</v>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr"/>
       <c r="BA10" t="n">
-        <v>5.783726150392837</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>1.172395763967081</v>
-      </c>
-      <c r="BC10" t="inlineStr"/>
-      <c r="BD10" t="n">
-        <v>-0.2384960718294167</v>
-      </c>
+        <v>1.064309764309765</v>
+      </c>
+      <c r="BB10" t="inlineStr"/>
+      <c r="BC10" t="n">
+        <v>5.108193041526391</v>
+      </c>
+      <c r="BD10" t="inlineStr"/>
       <c r="BE10" t="n">
         <v>0</v>
       </c>
@@ -2026,42 +2324,42 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>6u6i5pie</t>
+          <t>AuVMGZvJ</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45532.54166666666</v>
+        <v>45529.52083333334</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">stieler t 
+          <t xml:space="preserve">michel f 
   ger </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ernst abbe sportfeld
-  jena </t>
+          <t xml:space="preserve">millerntor stadion
+  hamburg </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>APNl8MIn</t>
+          <t>ILyJuN3g</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>4jcj2zMd</t>
+          <t>KWixEVWi</t>
         </is>
       </c>
       <c r="G11" t="n">
         <v>59</v>
       </c>
       <c r="H11" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>20242025</v>
@@ -2073,64 +2371,130 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>02hM7hzd</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>GzfvcwRj</t>
+          <t>4ljanukM</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="P11" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="P11" t="n">
+        <v>3</v>
+      </c>
       <c r="Q11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="R11" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr"/>
-      <c r="AE11" t="inlineStr"/>
-      <c r="AF11" t="inlineStr"/>
-      <c r="AG11" t="inlineStr"/>
-      <c r="AH11" t="inlineStr"/>
-      <c r="AI11" t="inlineStr"/>
-      <c r="AJ11" t="inlineStr"/>
+      <c r="T11" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-0.2999999999999999</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>-4.75</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>-9</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>-9.25</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>66.90000000000001</v>
+      </c>
       <c r="AK11" t="n">
-        <v>75.27043771043772</v>
-      </c>
-      <c r="AL11" t="inlineStr"/>
-      <c r="AM11" t="inlineStr"/>
-      <c r="AN11" t="inlineStr"/>
-      <c r="AO11" t="inlineStr"/>
+        <v>72.42424242424244</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>-1.282593056715857</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>-2.481887589343728</v>
+      </c>
       <c r="AP11" t="inlineStr"/>
-      <c r="AQ11" t="inlineStr"/>
-      <c r="AR11" t="inlineStr"/>
-      <c r="AS11" t="inlineStr"/>
-      <c r="AT11" t="inlineStr"/>
+      <c r="AQ11" t="n">
+        <v>-616302.3298988212</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0.2097674742411613</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>-2073807.519640853</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>2.663215910145738</v>
+      </c>
       <c r="AU11" t="inlineStr"/>
       <c r="AV11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr"/>
-      <c r="AX11" t="inlineStr"/>
+      <c r="AW11" t="n">
+        <v>-2.883641975308649</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>-1.692648709315336</v>
+      </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr"/>
-      <c r="BA11" t="inlineStr"/>
+      <c r="BA11" t="n">
+        <v>0.03417508417508586</v>
+      </c>
       <c r="BB11" t="inlineStr"/>
-      <c r="BC11" t="inlineStr"/>
+      <c r="BC11" t="n">
+        <v>-2.138075196408522</v>
+      </c>
       <c r="BD11" t="inlineStr"/>
       <c r="BE11" t="n">
         <v>0</v>
@@ -2139,42 +2503,42 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>W67CmLPh</t>
+          <t>t0w6KHuf</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45531.65625</v>
+        <v>45529.4375</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">stieler t 
+          <t xml:space="preserve">jablonski s 
   ger </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">preussenstadion
-  munster </t>
+          <t xml:space="preserve">volkswagen arena
+  wolfsburg </t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>zedZaSL7</t>
+          <t>nwkTahLL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>nJQmYp1B</t>
+          <t>nVp0wiqd</t>
         </is>
       </c>
       <c r="G12" t="n">
         <v>59</v>
       </c>
       <c r="H12" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>20242025</v>
@@ -2186,108 +2550,130 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>dfb pokal</t>
+          <t>bundesliga</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>pdPRS0me</t>
+          <t>rFNN7oyi</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>GzfvcwRj</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
+          <t>K6A2elS9</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>-43</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>-14</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-2</v>
+      </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>-7</v>
+        <v>0.09999999999999964</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>-1.24</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.3333333333333335</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>-1.5</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Y12" t="n">
-        <v>-3</v>
+        <v>-1.25</v>
       </c>
       <c r="Z12" t="n">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>15</v>
+        <v>0.25</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.5</v>
+        <v>2.083333333333336</v>
       </c>
       <c r="AC12" t="n">
-        <v>-1</v>
+        <v>-2.083333333333336</v>
       </c>
       <c r="AD12" t="n">
-        <v>-0.8399999999999999</v>
+        <v>1.583333333333333</v>
       </c>
       <c r="AE12" t="n">
-        <v>-2.2</v>
+        <v>-5.083333333333334</v>
       </c>
       <c r="AF12" t="n">
-        <v>-2</v>
+        <v>2.666666666666666</v>
       </c>
       <c r="AG12" t="n">
-        <v>-3</v>
+        <v>4.166666666666666</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AJ12" t="inlineStr"/>
+        <v>-9.5</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>71.90909090909092</v>
+      </c>
       <c r="AK12" t="n">
-        <v>77.66127946127946</v>
-      </c>
-      <c r="AL12" t="inlineStr"/>
+        <v>76.12121212121211</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>-1.003795402958817</v>
+      </c>
       <c r="AM12" t="n">
-        <v>-0.9073544973544756</v>
+        <v>-1.465858585858586</v>
       </c>
       <c r="AN12" t="n">
-        <v>-0.250793650793651</v>
+        <v>-0.4936465524424847</v>
       </c>
       <c r="AO12" t="n">
-        <v>-4306326.719576719</v>
+        <v>-5.014741481017893</v>
       </c>
       <c r="AP12" t="inlineStr"/>
-      <c r="AQ12" t="inlineStr"/>
-      <c r="AR12" t="inlineStr"/>
-      <c r="AS12" t="inlineStr"/>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AU12" t="n">
-        <v>-7.465608465608454</v>
-      </c>
+      <c r="AQ12" t="n">
+        <v>-21566201.81850506</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>-5.151239129495949</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>-30603441.07744108</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>1.444759143978416</v>
+      </c>
+      <c r="AU12" t="inlineStr"/>
       <c r="AV12" t="inlineStr"/>
       <c r="AW12" t="n">
-        <v>-4.368730158730173</v>
-      </c>
-      <c r="AX12" t="inlineStr"/>
+        <v>-6.165454545454537</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.751380471380457</v>
+      </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr"/>
-      <c r="BA12" t="inlineStr"/>
-      <c r="BB12" t="n">
-        <v>1.369603174603178</v>
-      </c>
-      <c r="BC12" t="inlineStr"/>
+      <c r="BA12" t="n">
+        <v>-1.690774410774409</v>
+      </c>
+      <c r="BB12" t="inlineStr"/>
+      <c r="BC12" t="n">
+        <v>-5.056296296296296</v>
+      </c>
       <c r="BD12" t="inlineStr"/>
       <c r="BE12" t="n">
         <v>0</v>
@@ -2296,32 +2682,32 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>AuVMGZvJ</t>
+          <t>SxFxJ44k</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45529.52083333334</v>
+        <v>45528.5625</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">michel f 
+          <t xml:space="preserve">exner f 
   ger </t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">millerntor stadion
-  hamburg </t>
+          <t xml:space="preserve">signal iduna park
+  dortmund </t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ILyJuN3g</t>
+          <t>nP1i5US1</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>KWixEVWi</t>
+          <t>8vndvXTk</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2348,90 +2734,126 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>02hM7hzd</t>
+          <t>AgnJojCs</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>4ljanukM</t>
+          <t>UgdQz0fK</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="P13" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>20</v>
+      </c>
+      <c r="R13" t="n">
         <v>3</v>
       </c>
-      <c r="Q13" t="n">
-        <v>4</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1</v>
-      </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr"/>
-      <c r="AB13" t="inlineStr"/>
-      <c r="AC13" t="inlineStr"/>
-      <c r="AD13" t="inlineStr"/>
-      <c r="AE13" t="inlineStr"/>
-      <c r="AF13" t="inlineStr"/>
-      <c r="AG13" t="inlineStr"/>
-      <c r="AH13" t="inlineStr"/>
-      <c r="AI13" t="inlineStr"/>
-      <c r="AJ13" t="inlineStr"/>
-      <c r="AK13" t="inlineStr"/>
-      <c r="AL13" t="inlineStr"/>
+      <c r="T13" t="n">
+        <v>2.983333333333333</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-1.053333333333333</v>
+      </c>
+      <c r="V13" t="n">
+        <v>2.916666666666667</v>
+      </c>
+      <c r="W13" t="n">
+        <v>-0.8333333333333334</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>14.33333333333334</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>-14.33333333333334</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.166666666666666</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>2.916666666666666</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>73.28888888888889</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>77.49261363636363</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0.5887959500652995</v>
+      </c>
       <c r="AM13" t="n">
-        <v>2.663215910145738</v>
+        <v>0.6220875420875418</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>1.012322413282174</v>
       </c>
       <c r="AO13" t="n">
-        <v>-616302.3298988212</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>0.03417508417508586</v>
-      </c>
+        <v>6.089137869927342</v>
+      </c>
+      <c r="AP13" t="inlineStr"/>
       <c r="AQ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR13" t="inlineStr"/>
-      <c r="AS13" t="inlineStr"/>
+        <v>14395037.90038078</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>3.681469396902813</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>13971404.04040404</v>
+      </c>
       <c r="AT13" t="n">
-        <v>-2.138075196408522</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>0.2097674742411613</v>
-      </c>
+        <v>0.0361077902718705</v>
+      </c>
+      <c r="AU13" t="inlineStr"/>
       <c r="AV13" t="inlineStr"/>
       <c r="AW13" t="n">
-        <v>-2.481887589343728</v>
+        <v>3.123703703703697</v>
       </c>
       <c r="AX13" t="n">
-        <v>-2073807.519640853</v>
+        <v>1.509966329966318</v>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr"/>
       <c r="BA13" t="n">
-        <v>-2.883641975308649</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>-1.282593056715857</v>
-      </c>
-      <c r="BC13" t="inlineStr"/>
-      <c r="BD13" t="n">
-        <v>-1.692648709315336</v>
-      </c>
+        <v>1.24936026936027</v>
+      </c>
+      <c r="BB13" t="inlineStr"/>
+      <c r="BC13" t="n">
+        <v>1.999124579124583</v>
+      </c>
+      <c r="BD13" t="inlineStr"/>
       <c r="BE13" t="n">
         <v>0</v>
       </c>
@@ -2439,32 +2861,32 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>t0w6KHuf</t>
+          <t>YZZcMwBs</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45529.4375</v>
+        <v>45528.4375</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">jablonski s 
+          <t xml:space="preserve">osmers h 
   ger </t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">volkswagen arena
-  wolfsburg </t>
+          <t xml:space="preserve">wwk arena
+  augsburg </t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>nwkTahLL</t>
+          <t>fTVNku3I</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>nVp0wiqd</t>
+          <t>Ig1f1fy3</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2491,90 +2913,126 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>rFNN7oyi</t>
+          <t>CCww5Qfo</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>K6A2elS9</t>
+          <t>4fuCGs9P</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>-43</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="Q14" t="n">
-        <v>-14</v>
+        <v>2</v>
       </c>
       <c r="R14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr"/>
-      <c r="AB14" t="inlineStr"/>
-      <c r="AC14" t="inlineStr"/>
-      <c r="AD14" t="inlineStr"/>
-      <c r="AE14" t="inlineStr"/>
-      <c r="AF14" t="inlineStr"/>
-      <c r="AG14" t="inlineStr"/>
-      <c r="AH14" t="inlineStr"/>
-      <c r="AI14" t="inlineStr"/>
-      <c r="AJ14" t="inlineStr"/>
-      <c r="AK14" t="inlineStr"/>
-      <c r="AL14" t="inlineStr"/>
+      <c r="T14" t="n">
+        <v>-0.8866666666666665</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.9200000000000002</v>
+      </c>
+      <c r="V14" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.833333333333333</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>-4.166666666666664</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>4.166666666666664</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>5.166666666666667</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>-6.916666666666666</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>-2.666666666666666</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>74.33333333333333</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>76.34545454545456</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>-0.01740099719706656</v>
+      </c>
       <c r="AM14" t="n">
-        <v>1.444759143978416</v>
+        <v>0.2446296296296298</v>
       </c>
       <c r="AN14" t="n">
-        <v>-1.003795402958817</v>
+        <v>-0.9231956735725717</v>
       </c>
       <c r="AO14" t="n">
-        <v>-21566201.81850506</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>-1.690774410774409</v>
-      </c>
+        <v>2.667000363259277</v>
+      </c>
+      <c r="AP14" t="inlineStr"/>
       <c r="AQ14" t="n">
-        <v>-1.465858585858586</v>
-      </c>
-      <c r="AR14" t="inlineStr"/>
-      <c r="AS14" t="inlineStr"/>
+        <v>1326521.147215446</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>2.329199280040243</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>1557878.787878787</v>
+      </c>
       <c r="AT14" t="n">
-        <v>-5.056296296296296</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>-5.151239129495949</v>
-      </c>
+        <v>-0.4686628107314164</v>
+      </c>
+      <c r="AU14" t="inlineStr"/>
       <c r="AV14" t="inlineStr"/>
       <c r="AW14" t="n">
-        <v>-5.014741481017893</v>
+        <v>1.129360269360262</v>
       </c>
       <c r="AX14" t="n">
-        <v>-30603441.07744108</v>
+        <v>2.483484848484864</v>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr"/>
       <c r="BA14" t="n">
-        <v>-6.165454545454537</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>-0.4936465524424847</v>
-      </c>
-      <c r="BC14" t="inlineStr"/>
-      <c r="BD14" t="n">
-        <v>1.751380471380457</v>
-      </c>
+        <v>-0.6134175084175055</v>
+      </c>
+      <c r="BB14" t="inlineStr"/>
+      <c r="BC14" t="n">
+        <v>1.151077441077433</v>
+      </c>
+      <c r="BD14" t="inlineStr"/>
       <c r="BE14" t="n">
         <v>0</v>
       </c>
@@ -2582,32 +3040,32 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>SxFxJ44k</t>
+          <t>GbeXvnR8</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45528.5625</v>
+        <v>45528.4375</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">exner f 
+          <t xml:space="preserve">stieler t 
   ger </t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">signal iduna park
-  dortmund </t>
+          <t xml:space="preserve">europa park stadion
+  freiburg </t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>nP1i5US1</t>
+          <t>fiEQZ7C7</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>8vndvXTk</t>
+          <t>nJQmYp1B</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2634,100 +3092,134 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>AgnJojCs</t>
+          <t>lxrr7DgN</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>UgdQz0fK</t>
+          <t>GzfvcwRj</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>18</v>
+        <v>-9</v>
       </c>
       <c r="P15" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="R15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
-      <c r="AA15" t="inlineStr"/>
-      <c r="AB15" t="inlineStr"/>
-      <c r="AC15" t="inlineStr"/>
-      <c r="AD15" t="inlineStr"/>
-      <c r="AE15" t="inlineStr"/>
-      <c r="AF15" t="inlineStr"/>
-      <c r="AG15" t="inlineStr"/>
-      <c r="AH15" t="inlineStr"/>
-      <c r="AI15" t="inlineStr"/>
-      <c r="AJ15" t="inlineStr"/>
+      <c r="T15" t="n">
+        <v>-0.2324999999999997</v>
+      </c>
+      <c r="U15" t="n">
+        <v>-0.7333333333333335</v>
+      </c>
+      <c r="V15" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="W15" t="n">
+        <v>-0.08333333333333326</v>
+      </c>
+      <c r="X15" t="n">
+        <v>-0.9166666666666667</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>-10.58333333333334</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>10.58333333333334</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0.08333333333333304</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>-5.75</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>-2.916666666666666</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>-0.5833333333333339</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>74.91515151515151</v>
+      </c>
       <c r="AK15" t="n">
-        <v>67.625</v>
-      </c>
-      <c r="AL15" t="inlineStr"/>
+        <v>79.5</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0.1940002179361446</v>
+      </c>
       <c r="AM15" t="n">
-        <v>0.0361077902718705</v>
+        <v>0.1773063973063975</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.5887959500652995</v>
+        <v>0.7688939740656089</v>
       </c>
       <c r="AO15" t="n">
-        <v>14395037.90038078</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>1.24936026936027</v>
-      </c>
+        <v>2.248723439032361</v>
+      </c>
+      <c r="AP15" t="inlineStr"/>
       <c r="AQ15" t="n">
-        <v>0.6220875420875418</v>
-      </c>
-      <c r="AR15" t="inlineStr"/>
-      <c r="AS15" t="inlineStr"/>
+        <v>559290.9023767142</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0.8225736745244916</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>-3379656.565656563</v>
+      </c>
       <c r="AT15" t="n">
-        <v>1.999124579124583</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>3.681469396902813</v>
-      </c>
+        <v>1.909991222016373</v>
+      </c>
+      <c r="AU15" t="inlineStr"/>
       <c r="AV15" t="inlineStr"/>
       <c r="AW15" t="n">
-        <v>6.089137869927342</v>
+        <v>-0.8235016835016893</v>
       </c>
       <c r="AX15" t="n">
-        <v>13971404.04040404</v>
+        <v>-0.920202020201998</v>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr"/>
       <c r="BA15" t="n">
-        <v>3.123703703703697</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>1.012322413282174</v>
-      </c>
-      <c r="BC15" t="inlineStr"/>
-      <c r="BD15" t="n">
-        <v>1.509966329966318</v>
-      </c>
+        <v>2.804107744107746</v>
+      </c>
+      <c r="BB15" t="inlineStr"/>
+      <c r="BC15" t="n">
+        <v>-2.066734006734023</v>
+      </c>
+      <c r="BD15" t="inlineStr"/>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>O48oHrZ1</t>
+          <t>dfO6OQtS</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -2735,24 +3227,24 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">bacher m 
+          <t xml:space="preserve">heft f 
   ger </t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">prezero arena
-  sinsheim </t>
+          <t xml:space="preserve">red bull arena
+  leipzig </t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>hQAtP9Sl</t>
+          <t>KbS1suSm</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>63WsD2ei</t>
+          <t>8Y2m6ADe</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2779,90 +3271,126 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>lEwgk7go</t>
+          <t>0KMe4S4D</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>A15eUM4C</t>
+          <t>8f6APkLc</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="P16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
-      <c r="AA16" t="inlineStr"/>
-      <c r="AB16" t="inlineStr"/>
-      <c r="AC16" t="inlineStr"/>
-      <c r="AD16" t="inlineStr"/>
-      <c r="AE16" t="inlineStr"/>
-      <c r="AF16" t="inlineStr"/>
-      <c r="AG16" t="inlineStr"/>
-      <c r="AH16" t="inlineStr"/>
-      <c r="AI16" t="inlineStr"/>
-      <c r="AJ16" t="inlineStr"/>
-      <c r="AK16" t="inlineStr"/>
-      <c r="AL16" t="inlineStr"/>
+      <c r="T16" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="U16" t="n">
+        <v>-0.7408333333333335</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.3999999999999999</v>
+      </c>
+      <c r="W16" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.5333333333333334</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>-0.8666666666666667</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.7999999999999998</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>-13.33333333333334</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>13.33333333333334</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>-0.2666666666666666</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>-3.533333333333334</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>-5.666666666666666</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>-6.933333333333333</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>-1.666666666666668</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>-6.066666666666665</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>78.27272727272727</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>74.15909090909091</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0.6375699862373709</v>
+      </c>
       <c r="AM16" t="n">
-        <v>-1.091873649620851</v>
+        <v>0.8589542483660131</v>
       </c>
       <c r="AN16" t="n">
-        <v>0.3935584378679007</v>
+        <v>-1.96347699614963</v>
       </c>
       <c r="AO16" t="n">
-        <v>4095505.271553065</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>1.288888888888888</v>
-      </c>
+        <v>6.393027361330624</v>
+      </c>
+      <c r="AP16" t="inlineStr"/>
       <c r="AQ16" t="n">
-        <v>0.7215488215488215</v>
-      </c>
-      <c r="AR16" t="inlineStr"/>
-      <c r="AS16" t="inlineStr"/>
+        <v>15752223.35181688</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>7.997767862138915</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>25412431.66963755</v>
+      </c>
       <c r="AT16" t="n">
-        <v>6.157239057239039</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>6.560130493421198</v>
-      </c>
+        <v>2.246797163067868</v>
+      </c>
+      <c r="AU16" t="inlineStr"/>
       <c r="AV16" t="inlineStr"/>
       <c r="AW16" t="n">
-        <v>5.364783465721246</v>
+        <v>7.141437908496727</v>
       </c>
       <c r="AX16" t="n">
-        <v>7083569.023569024</v>
+        <v>0.2308496732026413</v>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr"/>
       <c r="BA16" t="n">
-        <v>6.450168350168354</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>-0.485300488955648</v>
-      </c>
-      <c r="BC16" t="inlineStr"/>
-      <c r="BD16" t="n">
-        <v>-0.4659932659932622</v>
-      </c>
+        <v>-3.037979797979794</v>
+      </c>
+      <c r="BB16" t="inlineStr"/>
+      <c r="BC16" t="n">
+        <v>8.741770647653013</v>
+      </c>
+      <c r="BD16" t="inlineStr"/>
       <c r="BE16" t="n">
         <v>0</v>
       </c>
@@ -2870,7 +3398,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>GbeXvnR8</t>
+          <t>2FREIeA6</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -2878,24 +3406,24 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">stieler t 
+          <t xml:space="preserve">benen l 
   ger </t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">europa park stadion
-  freiburg </t>
+          <t xml:space="preserve">mewa arena
+  mainz </t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>fiEQZ7C7</t>
+          <t>EuakNmc1</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>nJQmYp1B</t>
+          <t>pzHW4oaE</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2922,100 +3450,134 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>lxrr7DgN</t>
+          <t>QTAUlvUP</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>GzfvcwRj</t>
+          <t>hpYJ6izc</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>-9</v>
+        <v>-2</v>
       </c>
       <c r="P17" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Q17" t="n">
         <v>2</v>
       </c>
-      <c r="Q17" t="n">
-        <v>3</v>
-      </c>
       <c r="R17" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
-      <c r="AA17" t="inlineStr"/>
-      <c r="AB17" t="inlineStr"/>
-      <c r="AC17" t="inlineStr"/>
-      <c r="AD17" t="inlineStr"/>
-      <c r="AE17" t="inlineStr"/>
-      <c r="AF17" t="inlineStr"/>
-      <c r="AG17" t="inlineStr"/>
-      <c r="AH17" t="inlineStr"/>
-      <c r="AI17" t="inlineStr"/>
-      <c r="AJ17" t="inlineStr"/>
+      <c r="T17" t="n">
+        <v>1.163333333333334</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.6333333333333331</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.9166666666666667</v>
+      </c>
+      <c r="W17" t="n">
+        <v>-0.08333333333333337</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>-0.5833333333333334</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>-6.166666666666664</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>6.166666666666664</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>-1.583333333333333</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0.666666666666667</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>5.583333333333334</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.083333333333334</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>74.12121212121212</v>
+      </c>
       <c r="AK17" t="n">
-        <v>80</v>
-      </c>
-      <c r="AL17" t="inlineStr"/>
+        <v>73.27272727272727</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0.02288214497596641</v>
+      </c>
       <c r="AM17" t="n">
-        <v>1.909991222016373</v>
+        <v>-0.04141414141414201</v>
       </c>
       <c r="AN17" t="n">
-        <v>0.1940002179361446</v>
+        <v>-0.7958079982565103</v>
       </c>
       <c r="AO17" t="n">
-        <v>559290.9023767142</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>2.804107744107746</v>
-      </c>
+        <v>-1.428488189071729</v>
+      </c>
+      <c r="AP17" t="inlineStr"/>
       <c r="AQ17" t="n">
-        <v>0.1773063973063975</v>
-      </c>
-      <c r="AR17" t="inlineStr"/>
-      <c r="AS17" t="inlineStr"/>
+        <v>-680417.2584238378</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0.5610608647221937</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>-1634949.494949494</v>
+      </c>
       <c r="AT17" t="n">
-        <v>-2.066734006734023</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>0.8225736745244916</v>
-      </c>
+        <v>0.9297764338381853</v>
+      </c>
+      <c r="AU17" t="inlineStr"/>
       <c r="AV17" t="inlineStr"/>
       <c r="AW17" t="n">
-        <v>2.248723439032361</v>
+        <v>-1.343569023569032</v>
       </c>
       <c r="AX17" t="n">
-        <v>-3379656.565656563</v>
+        <v>-1.743097643097656</v>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr"/>
       <c r="BA17" t="n">
-        <v>-0.8235016835016893</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>0.7688939740656089</v>
-      </c>
-      <c r="BC17" t="inlineStr"/>
-      <c r="BD17" t="n">
-        <v>-0.920202020201998</v>
-      </c>
+        <v>-1.144848484848492</v>
+      </c>
+      <c r="BB17" t="inlineStr"/>
+      <c r="BC17" t="n">
+        <v>0.1688215488215405</v>
+      </c>
+      <c r="BD17" t="inlineStr"/>
       <c r="BE17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>2FREIeA6</t>
+          <t>O48oHrZ1</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -3023,24 +3585,24 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">benen l 
+          <t xml:space="preserve">bacher m 
   ger </t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">mewa arena
-  mainz </t>
+          <t xml:space="preserve">prezero arena
+  sinsheim </t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>EuakNmc1</t>
+          <t>hQAtP9Sl</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>pzHW4oaE</t>
+          <t>63WsD2ei</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3067,90 +3629,126 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>QTAUlvUP</t>
+          <t>lEwgk7go</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>hpYJ6izc</t>
+          <t>A15eUM4C</t>
         </is>
       </c>
       <c r="O18" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="P18" t="n">
-        <v>-4</v>
+        <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
-      <c r="AA18" t="inlineStr"/>
-      <c r="AB18" t="inlineStr"/>
-      <c r="AC18" t="inlineStr"/>
-      <c r="AD18" t="inlineStr"/>
-      <c r="AE18" t="inlineStr"/>
-      <c r="AF18" t="inlineStr"/>
-      <c r="AG18" t="inlineStr"/>
-      <c r="AH18" t="inlineStr"/>
-      <c r="AI18" t="inlineStr"/>
-      <c r="AJ18" t="inlineStr"/>
-      <c r="AK18" t="inlineStr"/>
-      <c r="AL18" t="inlineStr"/>
+      <c r="T18" t="n">
+        <v>0.9033333333333335</v>
+      </c>
+      <c r="U18" t="n">
+        <v>-0.3116666666666668</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>3.333333333333334</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>-1.666666666666666</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>-5.666666666666667</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>-1.333333333333332</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>7.666666666666668</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>-6.666666666666666</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>80.6909090909091</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>68.59090909090909</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0.3935584378679007</v>
+      </c>
       <c r="AM18" t="n">
-        <v>0.9297764338381853</v>
+        <v>0.7215488215488215</v>
       </c>
       <c r="AN18" t="n">
-        <v>0.02288214497596641</v>
+        <v>-0.485300488955648</v>
       </c>
       <c r="AO18" t="n">
-        <v>-680417.2584238378</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>-1.144848484848492</v>
-      </c>
+        <v>5.364783465721246</v>
+      </c>
+      <c r="AP18" t="inlineStr"/>
       <c r="AQ18" t="n">
-        <v>-0.04141414141414201</v>
-      </c>
-      <c r="AR18" t="inlineStr"/>
-      <c r="AS18" t="inlineStr"/>
+        <v>4095505.271553065</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>6.560130493421198</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>7083569.023569024</v>
+      </c>
       <c r="AT18" t="n">
-        <v>0.1688215488215405</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>0.5610608647221937</v>
-      </c>
+        <v>-1.091873649620851</v>
+      </c>
+      <c r="AU18" t="inlineStr"/>
       <c r="AV18" t="inlineStr"/>
       <c r="AW18" t="n">
-        <v>-1.428488189071729</v>
+        <v>6.450168350168354</v>
       </c>
       <c r="AX18" t="n">
-        <v>-1634949.494949494</v>
+        <v>-0.4659932659932622</v>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr"/>
       <c r="BA18" t="n">
-        <v>-1.343569023569032</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>-0.7958079982565103</v>
-      </c>
-      <c r="BC18" t="inlineStr"/>
-      <c r="BD18" t="n">
-        <v>-1.743097643097656</v>
-      </c>
+        <v>1.288888888888888</v>
+      </c>
+      <c r="BB18" t="inlineStr"/>
+      <c r="BC18" t="n">
+        <v>6.157239057239039</v>
+      </c>
+      <c r="BD18" t="inlineStr"/>
       <c r="BE18" t="n">
         <v>0</v>
       </c>
@@ -3158,32 +3756,32 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>dfO6OQtS</t>
+          <t>zuzbQnCF</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>45528.4375</v>
+        <v>45527.64583333334</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">heft f 
+          <t xml:space="preserve">stieler t 
   ger </t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">red bull arena
-  leipzig </t>
+          <t xml:space="preserve">borussia park
+  monchengladbach </t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>KbS1suSm</t>
+          <t>88HSzjDr</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>8Y2m6ADe</t>
+          <t>4jcj2zMd</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3210,377 +3808,135 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>0KMe4S4D</t>
+          <t>rPfNaCdg</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>8f6APkLc</t>
+          <t>GzfvcwRj</t>
         </is>
       </c>
       <c r="O19" t="n">
-        <v>9</v>
+        <v>-19</v>
       </c>
       <c r="P19" t="n">
-        <v>4</v>
+        <v>-3</v>
       </c>
       <c r="Q19" t="n">
-        <v>5</v>
+        <v>-9</v>
       </c>
       <c r="R19" t="n">
+        <v>-3</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>-1.899166666666666</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.425</v>
+      </c>
+      <c r="V19" t="n">
+        <v>-3.666666666666667</v>
+      </c>
+      <c r="W19" t="n">
+        <v>-0.1666666666666667</v>
+      </c>
+      <c r="X19" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>-6.583333333333336</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>6.583333333333336</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>-3.083333333333333</v>
+      </c>
+      <c r="AE19" t="n">
         <v>2</v>
       </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
-      <c r="X19" t="inlineStr"/>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
-      <c r="AA19" t="inlineStr"/>
-      <c r="AB19" t="inlineStr"/>
-      <c r="AC19" t="inlineStr"/>
-      <c r="AD19" t="inlineStr"/>
-      <c r="AE19" t="inlineStr"/>
-      <c r="AF19" t="inlineStr"/>
-      <c r="AG19" t="inlineStr"/>
-      <c r="AH19" t="inlineStr"/>
-      <c r="AI19" t="inlineStr"/>
-      <c r="AJ19" t="inlineStr"/>
-      <c r="AK19" t="inlineStr"/>
-      <c r="AL19" t="inlineStr"/>
+      <c r="AF19" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>-4.333333333333334</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>4.166666666666666</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>76.89562289562288</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>74.19949494949495</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>-0.4401287124655007</v>
+      </c>
       <c r="AM19" t="n">
-        <v>2.246797163067868</v>
+        <v>-0.5697355912061792</v>
       </c>
       <c r="AN19" t="n">
-        <v>0.6375699862373709</v>
+        <v>0.1906283611842952</v>
       </c>
       <c r="AO19" t="n">
-        <v>15752223.35181688</v>
+        <v>-5.900665682749064</v>
       </c>
       <c r="AP19" t="n">
-        <v>-3.037979797979794</v>
+        <v>8225000</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.8589542483660131</v>
-      </c>
-      <c r="AR19" t="inlineStr"/>
-      <c r="AS19" t="inlineStr"/>
+        <v>-27259454.0208636</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>-5.652395274107135</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>-25530325.01485443</v>
+      </c>
       <c r="AT19" t="n">
-        <v>8.741770647653013</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>7.997767862138915</v>
-      </c>
-      <c r="AV19" t="inlineStr"/>
+        <v>2.332195815917402</v>
+      </c>
+      <c r="AU19" t="inlineStr"/>
+      <c r="AV19" t="n">
+        <v>231</v>
+      </c>
       <c r="AW19" t="n">
-        <v>6.393027361330624</v>
+        <v>-6.116371558724481</v>
       </c>
       <c r="AX19" t="n">
-        <v>25412431.66963755</v>
-      </c>
-      <c r="AY19" t="inlineStr"/>
+        <v>-0.370454545454578</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>199</v>
+      </c>
       <c r="AZ19" t="inlineStr"/>
       <c r="BA19" t="n">
-        <v>7.141437908496727</v>
+        <v>-0.4454030501089328</v>
       </c>
       <c r="BB19" t="n">
-        <v>-1.96347699614963</v>
-      </c>
-      <c r="BC19" t="inlineStr"/>
-      <c r="BD19" t="n">
-        <v>0.2308496732026413</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>-6.010986333927505</v>
+      </c>
+      <c r="BD19" t="inlineStr"/>
       <c r="BE19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>YZZcMwBs</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>45528.4375</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">osmers h 
-  ger </t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">wwk arena
-  augsburg </t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>fTVNku3I</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Ig1f1fy3</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
-        <v>59</v>
-      </c>
-      <c r="H20" t="n">
-        <v>591</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>CCww5Qfo</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>4fuCGs9P</t>
-        </is>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>2</v>
-      </c>
-      <c r="R20" t="n">
-        <v>-1</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
-      <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="inlineStr"/>
-      <c r="AA20" t="inlineStr"/>
-      <c r="AB20" t="inlineStr"/>
-      <c r="AC20" t="inlineStr"/>
-      <c r="AD20" t="inlineStr"/>
-      <c r="AE20" t="inlineStr"/>
-      <c r="AF20" t="inlineStr"/>
-      <c r="AG20" t="inlineStr"/>
-      <c r="AH20" t="inlineStr"/>
-      <c r="AI20" t="inlineStr"/>
-      <c r="AJ20" t="inlineStr"/>
-      <c r="AK20" t="inlineStr"/>
-      <c r="AL20" t="inlineStr"/>
-      <c r="AM20" t="n">
-        <v>-0.4686628107314164</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>-0.01740099719706656</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>1326521.147215446</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>-0.6134175084175055</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>0.2446296296296298</v>
-      </c>
-      <c r="AR20" t="inlineStr"/>
-      <c r="AS20" t="inlineStr"/>
-      <c r="AT20" t="n">
-        <v>1.151077441077433</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>2.329199280040243</v>
-      </c>
-      <c r="AV20" t="inlineStr"/>
-      <c r="AW20" t="n">
-        <v>2.667000363259277</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>1557878.787878787</v>
-      </c>
-      <c r="AY20" t="inlineStr"/>
-      <c r="AZ20" t="inlineStr"/>
-      <c r="BA20" t="n">
-        <v>1.129360269360262</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>-0.9231956735725717</v>
-      </c>
-      <c r="BC20" t="inlineStr"/>
-      <c r="BD20" t="n">
-        <v>2.483484848484864</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>zuzbQnCF</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>45527.64583333334</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stieler t 
-  ger </t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">borussia park
-  monchengladbach </t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>88HSzjDr</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>4jcj2zMd</t>
-        </is>
-      </c>
-      <c r="G21" t="n">
-        <v>59</v>
-      </c>
-      <c r="H21" t="n">
-        <v>591</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>rPfNaCdg</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>GzfvcwRj</t>
-        </is>
-      </c>
-      <c r="O21" t="n">
-        <v>-19</v>
-      </c>
-      <c r="P21" t="n">
-        <v>-3</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>-9</v>
-      </c>
-      <c r="R21" t="n">
-        <v>-3</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr"/>
-      <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="inlineStr"/>
-      <c r="Z21" t="inlineStr"/>
-      <c r="AA21" t="inlineStr"/>
-      <c r="AB21" t="inlineStr"/>
-      <c r="AC21" t="inlineStr"/>
-      <c r="AD21" t="inlineStr"/>
-      <c r="AE21" t="inlineStr"/>
-      <c r="AF21" t="inlineStr"/>
-      <c r="AG21" t="inlineStr"/>
-      <c r="AH21" t="inlineStr"/>
-      <c r="AI21" t="inlineStr"/>
-      <c r="AJ21" t="inlineStr"/>
-      <c r="AK21" t="inlineStr"/>
-      <c r="AL21" t="inlineStr"/>
-      <c r="AM21" t="n">
-        <v>2.332195815917402</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>-0.4401287124655007</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>-27259454.0208636</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>-0.4454030501089328</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>-0.5697355912061792</v>
-      </c>
-      <c r="AR21" t="inlineStr"/>
-      <c r="AS21" t="inlineStr"/>
-      <c r="AT21" t="n">
-        <v>-6.010986333927505</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>-5.652395274107135</v>
-      </c>
-      <c r="AV21" t="inlineStr"/>
-      <c r="AW21" t="n">
-        <v>-5.900665682749064</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>-25530325.01485443</v>
-      </c>
-      <c r="AY21" t="inlineStr"/>
-      <c r="AZ21" t="inlineStr"/>
-      <c r="BA21" t="n">
-        <v>-6.116371558724481</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>0.1906283611842952</v>
-      </c>
-      <c r="BC21" t="inlineStr"/>
-      <c r="BD21" t="n">
-        <v>-0.370454545454578</v>
-      </c>
-      <c r="BE21" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_preparation/df_constructed.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_constructed.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE7"/>
+  <dimension ref="A1:BE12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -525,84 +525,84 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_goals</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals_against</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_n_matches_last_days</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_n_matches_last_days_against</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_expected_goals_(xg)</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_expected_goals_(xg)_against</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_ball_possession</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_ball_possession_against</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_points</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_points_against</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls_against</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts_against</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals_against</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls_against</t>
-        </is>
-      </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
@@ -620,92 +620,92 @@
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_rat_player_sub</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_pot_player_sub</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
         </is>
       </c>
       <c r="BE1" s="1" t="inlineStr">
@@ -717,32 +717,32 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>SxFxJ44k</t>
+          <t>2T6mXfPa</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45528.5625</v>
+        <v>45536.52083333334</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zwayer f 
+          <t xml:space="preserve">welz t 
   ger </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">signal iduna park
-  dortmund </t>
+          <t xml:space="preserve">allianz arena
+  munich </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>nP1i5US1</t>
+          <t>nVp0wiqd</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>8vndvXTk</t>
+          <t>fiEQZ7C7</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -769,140 +769,90 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>AgnJojCs</t>
+          <t>QevvB2nf</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>UgdQz0fK</t>
+          <t>GzfvcwRj</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="P2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q2" t="n">
         <v>20</v>
       </c>
       <c r="R2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
-      <c r="T2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>2.983333333333333</v>
-      </c>
-      <c r="W2" t="n">
-        <v>-1.053333333333333</v>
-      </c>
-      <c r="X2" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>14.33333333333334</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>-14.33333333333334</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>-1.75</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>2.916666666666666</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>2.916666666666667</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>-0.8333333333333334</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1.166666666666666</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>73.28888888888889</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>77.49261363636363</v>
-      </c>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="n">
-        <v>1.012322413282174</v>
+        <v>-0.4441035709033194</v>
       </c>
       <c r="AM2" t="n">
-        <v>6.089137869927342</v>
+        <v>0.7828081673577365</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.6220875420875418</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>2.5</v>
-      </c>
+        <v>1.335669191919192</v>
+      </c>
+      <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="n">
-        <v>1.509966329966318</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>1.24936026936027</v>
-      </c>
+        <v>32665549.24242424</v>
+      </c>
+      <c r="AQ2" t="inlineStr"/>
       <c r="AR2" t="n">
-        <v>13971404.04040404</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>14395037.90038078</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>3</v>
-      </c>
+        <v>-0.001957070707071296</v>
+      </c>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
       <c r="AV2" t="n">
-        <v>3.681469396902813</v>
+        <v>7.365214646464651</v>
       </c>
       <c r="AW2" t="n">
-        <v>22</v>
+        <v>23636442.67370012</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>2</v>
-      </c>
+        <v>6.576388888888872</v>
+      </c>
+      <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="n">
-        <v>0.5887959500652995</v>
+        <v>-2.222727105095004</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.999124579124583</v>
+        <v>1.229924242424261</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.0361077902718705</v>
+        <v>5.05822230339389</v>
       </c>
       <c r="BC2" t="n">
-        <v>27425000</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>3.123703703703697</v>
-      </c>
+        <v>6.776570443514714</v>
+      </c>
+      <c r="BD2" t="inlineStr"/>
       <c r="BE2" t="n">
         <v>0</v>
       </c>
@@ -910,32 +860,32 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2FREIeA6</t>
+          <t>W8b4TCOO</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45528.4375</v>
+        <v>45536.4375</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">osmers h 
+          <t xml:space="preserve">stegemann s 
   ger </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">mewa arena
-  mainz </t>
+          <t xml:space="preserve">voith arena
+  heidenheim </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>EuakNmc1</t>
+          <t>KWixEVWi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>pzHW4oaE</t>
+          <t>fTVNku3I</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -962,22 +912,22 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>QTAUlvUP</t>
+          <t>lli2SfLl</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>hpYJ6izc</t>
+          <t>4fuCGs9P</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="P3" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="Q3" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="R3" t="n">
         <v>-1</v>
@@ -985,111 +935,67 @@
       <c r="S3" t="n">
         <v>0</v>
       </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.163333333333334</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0.6333333333333331</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-1.583333333333333</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.666666666666667</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>-6.166666666666664</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>6.166666666666664</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0.4166666666666667</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>-0.5833333333333334</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.083333333333334</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0.9166666666666667</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>-0.08333333333333337</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>5.583333333333334</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>74.12121212121212</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>73.27272727272727</v>
-      </c>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="n">
-        <v>-0.7958079982565103</v>
+        <v>3.122819833675091</v>
       </c>
       <c r="AM3" t="n">
-        <v>-1.428488189071729</v>
+        <v>-0.1696718121060228</v>
       </c>
       <c r="AN3" t="n">
-        <v>-0.04141414141414201</v>
+        <v>-0.3962436868686867</v>
       </c>
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="n">
-        <v>-1.743097643097656</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>-1.144848484848492</v>
-      </c>
+        <v>-1990785.984848485</v>
+      </c>
+      <c r="AQ3" t="inlineStr"/>
       <c r="AR3" t="n">
-        <v>-1634949.494949494</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>-680417.2584238378</v>
-      </c>
+        <v>0.4663194444444443</v>
+      </c>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
       <c r="AU3" t="inlineStr"/>
       <c r="AV3" t="n">
-        <v>0.5610608647221937</v>
+        <v>-2.061805555555566</v>
       </c>
       <c r="AW3" t="n">
-        <v>-229</v>
-      </c>
-      <c r="AX3" t="inlineStr"/>
-      <c r="AY3" t="n">
-        <v>-229</v>
-      </c>
+        <v>-1992049.702855624</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>-1.413888888888891</v>
+      </c>
+      <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="n">
-        <v>0.02288214497596641</v>
+        <v>-0.8104025056327657</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.1688215488215405</v>
+        <v>1.088162878787841</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.9297764338381853</v>
+        <v>-1.87742357392851</v>
       </c>
       <c r="BC3" t="n">
-        <v>-25300000</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>-1.343569023569032</v>
-      </c>
+        <v>-5.437775507265641</v>
+      </c>
+      <c r="BD3" t="inlineStr"/>
       <c r="BE3" t="n">
         <v>0</v>
       </c>
@@ -1097,11 +1003,11 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>dfO6OQtS</t>
+          <t>AVR8vwXP</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45528.4375</v>
+        <v>45535.5625</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1111,18 +1017,18 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">red bull arena
-  leipzig </t>
+          <t xml:space="preserve">bayarena
+  leverkusen </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>KbS1suSm</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>8Y2m6ADe</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1149,7 +1055,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0KMe4S4D</t>
+          <t>M5BRZDsC</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -1158,131 +1064,107 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>9</v>
+        <v>-2</v>
       </c>
       <c r="P4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
+      </c>
+      <c r="V4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="W4" t="n">
+        <v>2</v>
+      </c>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="n">
+        <v>-21</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AI4" t="n">
         <v>4</v>
       </c>
-      <c r="Q4" t="n">
-        <v>5</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0.7999999999999998</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="W4" t="n">
-        <v>-0.7408333333333335</v>
-      </c>
-      <c r="X4" t="n">
-        <v>-0.2666666666666666</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>-3.533333333333334</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>-13.33333333333334</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>13.33333333333334</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0.5333333333333334</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>-0.8666666666666667</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>-1.666666666666668</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>-6.066666666666665</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0.3999999999999999</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>-5.666666666666666</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>-6.933333333333333</v>
-      </c>
       <c r="AJ4" t="n">
-        <v>78.27272727272727</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>74.15909090909091</v>
-      </c>
+        <v>75.09999999999999</v>
+      </c>
+      <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="n">
-        <v>-1.96347699614963</v>
+        <v>-1.703678188565682</v>
       </c>
       <c r="AM4" t="n">
-        <v>6.393027361330624</v>
+        <v>-0.01504158027327374</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.8589542483660131</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>-2.916666666666657</v>
-      </c>
+        <v>-0.008080808080808133</v>
+      </c>
+      <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="n">
-        <v>0.2308496732026413</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>-3.037979797979794</v>
-      </c>
+        <v>5738117.283950619</v>
+      </c>
+      <c r="AQ4" t="inlineStr"/>
       <c r="AR4" t="n">
-        <v>25412431.66963755</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>15752223.35181688</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>-6.583333333333332</v>
-      </c>
+        <v>0.7580387205387211</v>
+      </c>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
       <c r="AV4" t="n">
-        <v>7.997767862138915</v>
+        <v>0.5240319865319805</v>
       </c>
       <c r="AW4" t="n">
-        <v>81</v>
+        <v>14904659.0151398</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>112</v>
-      </c>
+        <v>1.21986531986532</v>
+      </c>
+      <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="n">
-        <v>0.6375699862373709</v>
+        <v>-3.256647387470707</v>
       </c>
       <c r="BA4" t="n">
-        <v>8.741770647653013</v>
+        <v>2.306705948372638</v>
       </c>
       <c r="BB4" t="n">
-        <v>2.246797163067868</v>
+        <v>1.722677819265598</v>
       </c>
       <c r="BC4" t="n">
-        <v>60350000</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>7.141437908496727</v>
-      </c>
+        <v>2.625030756942238</v>
+      </c>
+      <c r="BD4" t="inlineStr"/>
       <c r="BE4" t="n">
         <v>0</v>
       </c>
@@ -1290,32 +1172,32 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>YZZcMwBs</t>
+          <t>U3QUqY85</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45528.4375</v>
+        <v>45535.4375</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stegemann s 
+          <t xml:space="preserve">schroder r 
   ger </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">wwk arena
-  augsburg </t>
+          <t xml:space="preserve">vonovia ruhrstadion
+  bochum </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>fTVNku3I</t>
+          <t>8Y2m6ADe</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ig1f1fy3</t>
+          <t>88HSzjDr</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1342,22 +1224,22 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>CCww5Qfo</t>
+          <t>pfoInmcq</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>4fuCGs9P</t>
+          <t>hAcTWKKN</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="P5" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="Q5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="R5" t="n">
         <v>-1</v>
@@ -1365,117 +1247,67 @@
       <c r="S5" t="n">
         <v>0</v>
       </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>-0.8866666666666665</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0.9200000000000002</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-5.5</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>5.166666666666667</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>-4.166666666666664</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>4.166666666666664</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>-2.666666666666666</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.833333333333333</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>-6.916666666666666</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>74.33333333333333</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>76.34545454545456</v>
-      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="n">
-        <v>-0.9231956735725717</v>
+        <v>3.186373731732711</v>
       </c>
       <c r="AM5" t="n">
-        <v>2.667000363259277</v>
+        <v>-0.2172706953575567</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.2446296296296298</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>1</v>
-      </c>
+        <v>-0.2895342312008979</v>
+      </c>
+      <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="n">
-        <v>2.483484848484864</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>-0.6134175084175055</v>
-      </c>
+        <v>-5105757.225028058</v>
+      </c>
+      <c r="AQ5" t="inlineStr"/>
       <c r="AR5" t="n">
-        <v>1557878.787878787</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>1326521.147215446</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>-0.8333333333333321</v>
-      </c>
+        <v>2.642599607182941</v>
+      </c>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
       <c r="AV5" t="n">
-        <v>2.329199280040243</v>
+        <v>-3.271689113355777</v>
       </c>
       <c r="AW5" t="n">
-        <v>64</v>
+        <v>-4293902.806739619</v>
       </c>
       <c r="AX5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>66</v>
-      </c>
+        <v>-2.303858024691351</v>
+      </c>
+      <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="n">
-        <v>-0.01740099719706656</v>
+        <v>-1.138384139353121</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.151077441077433</v>
+        <v>-2.149565095398458</v>
       </c>
       <c r="BB5" t="n">
-        <v>-0.4686628107314164</v>
+        <v>-2.65491420065635</v>
       </c>
       <c r="BC5" t="n">
-        <v>-3600000</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>1.129360269360262</v>
-      </c>
+        <v>-4.881280258590039</v>
+      </c>
+      <c r="BD5" t="inlineStr"/>
       <c r="BE5" t="n">
         <v>0</v>
       </c>
@@ -1483,32 +1315,32 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>O48oHrZ1</t>
+          <t>0OYDmG9t</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45528.4375</v>
+        <v>45535.4375</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">stieler t 
+          <t xml:space="preserve">zwayer f 
   ger </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">prezero arena
-  sinsheim </t>
+          <t xml:space="preserve">weserstadion
+  bremen </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>hQAtP9Sl</t>
+          <t>Ig1f1fy3</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>63WsD2ei</t>
+          <t>nP1i5US1</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1535,140 +1367,90 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>lEwgk7go</t>
+          <t>2VSFgl3c</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>A15eUM4C</t>
+          <t>UgdQz0fK</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>-19</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
-      <c r="T6" t="n">
-        <v>1</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0.9033333333333335</v>
-      </c>
-      <c r="W6" t="n">
-        <v>-0.3116666666666668</v>
-      </c>
-      <c r="X6" t="n">
-        <v>3.333333333333334</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>-1.666666666666666</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>-1.333333333333333</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>7.666666666666668</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>-6.666666666666666</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>-5.666666666666667</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>-1.333333333333332</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>80.6909090909091</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>68.59090909090909</v>
-      </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="n">
-        <v>-0.485300488955648</v>
+        <v>-0.02856035983234406</v>
       </c>
       <c r="AM6" t="n">
-        <v>5.364783465721246</v>
+        <v>-0.8015544926494629</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.7215488215488215</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>-1.285714285714278</v>
-      </c>
+        <v>-1.142613636363637</v>
+      </c>
+      <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="n">
-        <v>-0.4659932659932622</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1.288888888888888</v>
-      </c>
+        <v>-25128693.18181818</v>
+      </c>
+      <c r="AQ6" t="inlineStr"/>
       <c r="AR6" t="n">
-        <v>7083569.023569024</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>4</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>4095505.271553065</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>-2.904761904761905</v>
-      </c>
+        <v>0.5761363636363619</v>
+      </c>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
       <c r="AV6" t="n">
-        <v>6.560130493421198</v>
+        <v>-7.118749999999991</v>
       </c>
       <c r="AW6" t="n">
-        <v>305</v>
+        <v>-17385962.19392124</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.4285714285714286</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>341</v>
-      </c>
+        <v>-6.902840909090912</v>
+      </c>
+      <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="n">
-        <v>0.3935584378679007</v>
+        <v>0.5327903007598991</v>
       </c>
       <c r="BA6" t="n">
-        <v>6.157239057239039</v>
+        <v>-1.482386363636351</v>
       </c>
       <c r="BB6" t="n">
-        <v>-1.091873649620851</v>
+        <v>-8.988607277865384</v>
       </c>
       <c r="BC6" t="n">
-        <v>42250000</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>6.450168350168354</v>
-      </c>
+        <v>-7.943548412404624</v>
+      </c>
+      <c r="BD6" t="inlineStr"/>
       <c r="BE6" t="n">
         <v>0</v>
       </c>
@@ -1676,32 +1458,32 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>GbeXvnR8</t>
+          <t>QVJwrCwI</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45528.4375</v>
+        <v>45535.4375</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">welz t 
+          <t xml:space="preserve">storks s 
   ger </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">europa park stadion
-  freiburg </t>
+          <t xml:space="preserve">holstein stadion
+  kiel </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>fiEQZ7C7</t>
+          <t>63WsD2ei</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>nJQmYp1B</t>
+          <t>nwkTahLL</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1728,142 +1510,825 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>lxrr7DgN</t>
+          <t>KUx4Q7x1</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>GzfvcwRj</t>
+          <t>f3ddUIXs</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>-9</v>
-      </c>
-      <c r="P7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="n">
+        <v>0.9931639636530925</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>-0.2319369680239243</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>-0.4796969696969695</v>
+      </c>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="n">
+        <v>-8890104.377104376</v>
+      </c>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="n">
+        <v>-0.1991245791245788</v>
+      </c>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr"/>
+      <c r="AV7" t="n">
+        <v>-6.93208754208753</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>-6966625.927363698</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>-7.116868686868685</v>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="n">
+        <v>2.186201690821264</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>-0.5158249158249077</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>-6.912198642742112</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>-7.196666666666658</v>
+      </c>
+      <c r="BD7" t="inlineStr"/>
+      <c r="BE7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>61DvZGfm</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45535.4375</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">osmers h 
+  ger </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mhparena
+  stuttgart </t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>59</v>
+      </c>
+      <c r="H8" t="n">
+        <v>591</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>YZPE6Sx7</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>hpYJ6izc</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>5</v>
+      </c>
+      <c r="P8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>7</v>
+      </c>
+      <c r="R8" t="n">
         <v>2</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="n">
+        <v>-1.866914682539679</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>-0.2390376984126981</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>-0.07588383838383805</v>
+      </c>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="n">
+        <v>5087209.595959593</v>
+      </c>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="n">
+        <v>-1.474621212121214</v>
+      </c>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
+      <c r="AV8" t="n">
+        <v>0.90347222222222</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>979817.0882936511</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>1.6532196969697</v>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="n">
+        <v>-2.078422619047643</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>1.374242424242368</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>-1.273363095238096</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>-0.8065476190476062</v>
+      </c>
+      <c r="BD8" t="inlineStr"/>
+      <c r="BE8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>AgAeVYgC</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45535.4375</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stieler t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">deutsche bank park
+  frankfurt </t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>59</v>
+      </c>
+      <c r="H9" t="n">
+        <v>591</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>IkCftsQm</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>A15eUM4C</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
         <v>3</v>
       </c>
-      <c r="R7" t="n">
+      <c r="P9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>4</v>
+      </c>
+      <c r="R9" t="n">
+        <v>3</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="n">
+        <v>-0.7738923958738191</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>-0.01053608843856479</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>-0.1264204545454541</v>
+      </c>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="n">
+        <v>6646772.411616158</v>
+      </c>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="n">
+        <v>-2.389646464646464</v>
+      </c>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="n">
+        <v>2.617282196969697</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>28889.87627547048</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1.853235479797988</v>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="n">
+        <v>-1.038929235968709</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>-2.293734217171703</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>-0.3447359137036017</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0.9283481793833914</v>
+      </c>
+      <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>djSMofvg</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45534.64583333334</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">siebert d 
+  ger </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadion an der alten forsterei
+  berlin </t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>59</v>
+      </c>
+      <c r="H10" t="n">
+        <v>591</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>vZA6VYpf</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0jdIgO6t</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>5</v>
+      </c>
+      <c r="P10" t="n">
         <v>1</v>
       </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>-0.2324999999999997</v>
-      </c>
-      <c r="W7" t="n">
-        <v>-0.7333333333333335</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-1.75</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0.08333333333333304</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>-10.58333333333334</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>10.58333333333334</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>-0.9166666666666667</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.083333333333333</v>
-      </c>
-      <c r="AD7" t="n">
+      <c r="Q10" t="n">
+        <v>8</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="n">
+        <v>1.084987459843244</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0.463121401783444</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0.6195075757575756</v>
+      </c>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="n">
+        <v>6108409.792368125</v>
+      </c>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="n">
+        <v>1.100862794612794</v>
+      </c>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="n">
+        <v>5.096282267115612</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>3838965.955107677</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>5.791533389450052</v>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="n">
+        <v>-1.766098248085967</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>-0.1428942199775634</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>6.898806906810108</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>4.834310716404545</v>
+      </c>
+      <c r="BD10" t="inlineStr"/>
+      <c r="BE10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>AuVMGZvJ</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45529.52083333334</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jablonski s 
+  ger </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">millerntor stadion
+  hamburg </t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>59</v>
+      </c>
+      <c r="H11" t="n">
+        <v>591</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>02hM7hzd</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>4ljanukM</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>1</v>
+      </c>
+      <c r="P11" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q11" t="n">
         <v>4</v>
       </c>
-      <c r="AE7" t="n">
-        <v>-0.5833333333333339</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>-0.75</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>-0.08333333333333326</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>-5.75</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>-2.916666666666666</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>74.91515151515151</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>79.5</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0.7688939740656089</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>2.248723439032361</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>0.1773063973063975</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>-2.38095238095238</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>-0.920202020201998</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>2.804107744107746</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>-3379656.565656563</v>
-      </c>
-      <c r="AS7" t="n">
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="n">
+        <v>-1.282593056715857</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>-1100000</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>-2073807.519640853</v>
+      </c>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="n">
+        <v>0.03417508417508586</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>-70</v>
+      </c>
+      <c r="AT11" t="n">
         <v>-1</v>
       </c>
-      <c r="AT7" t="n">
-        <v>559290.9023767142</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>1.547619047619047</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>0.8225736745244916</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>-67</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>-0.2857142857142858</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>-84</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>0.1940002179361446</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>-2.066734006734023</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>1.909991222016373</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>-12325000</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>-0.8235016835016893</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>1</v>
+      <c r="AU11" t="inlineStr"/>
+      <c r="AV11" t="n">
+        <v>-2.138075196408522</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>-616302.3298988212</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>-2.883641975308649</v>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="n">
+        <v>2.663215910145738</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>-1.692648709315336</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>-2.481887589343728</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>0.2097674742411613</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>-66</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>t0w6KHuf</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45529.4375</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">siebert d 
+  ger </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">volkswagen arena
+  wolfsburg </t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>59</v>
+      </c>
+      <c r="H12" t="n">
+        <v>591</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>rFNN7oyi</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>K6A2elS9</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>-43</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>-14</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-2</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr"/>
+      <c r="AK12" t="inlineStr"/>
+      <c r="AL12" t="n">
+        <v>-0.4936465524424811</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>-1.003795402958817</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>-1.465858585858586</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>-77525000</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>-30603441.07744108</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>-1.690774410774409</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>-325</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>-4.833333333333343</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>-5.056296296296296</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>-21566201.81850507</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>-6.165454545454537</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0.1666666666666679</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1.444759143978416</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>1.751380471380457</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>-5.014741481017907</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>-5.151239129495977</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>-281</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/data_preparation/df_constructed.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_constructed.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE12"/>
+  <dimension ref="A1:BE10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -525,84 +525,84 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_points</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points_against</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days_against</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls_against</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_goals</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goals_against</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days_against</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts_against</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_expected_goals_(xg)</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_expected_goals_(xg)_against</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_ball_possession</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_ball_possession_against</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points_against</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls_against</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts_against</t>
-        </is>
-      </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
@@ -615,97 +615,97 @@
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_age_player_sub</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
         </is>
       </c>
       <c r="BE1" s="1" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>QevvB2nf</t>
+          <t>f3ddUIXs</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -811,48 +811,48 @@
       <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="n">
-        <v>-0.4441035709033194</v>
+        <v>-0.1072601010100982</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.7828081673577365</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1.335669191919192</v>
-      </c>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="n">
-        <v>32665549.24242424</v>
-      </c>
-      <c r="AQ2" t="inlineStr"/>
+        <v>0.8218458137710389</v>
+      </c>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="n">
+        <v>33450871.21212121</v>
+      </c>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="n">
+        <v>6.646464646464636</v>
+      </c>
       <c r="AR2" t="n">
-        <v>-0.001957070707071296</v>
-      </c>
-      <c r="AS2" t="inlineStr"/>
+        <v>-2.116631047485271</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1.203598484848499</v>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AU2" t="inlineStr"/>
       <c r="AV2" t="n">
-        <v>7.365214646464651</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>23636442.67370012</v>
-      </c>
+        <v>6.70966102328353</v>
+      </c>
+      <c r="AW2" t="inlineStr"/>
       <c r="AX2" t="n">
-        <v>6.576388888888872</v>
-      </c>
-      <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="n">
-        <v>-2.222727105095004</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>1.229924242424261</v>
-      </c>
+        <v>5.220971451973583</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>23618378.25977181</v>
+      </c>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
       <c r="BB2" t="n">
-        <v>5.05822230339389</v>
+        <v>7.494381313131314</v>
       </c>
       <c r="BC2" t="n">
-        <v>6.776570443514714</v>
-      </c>
-      <c r="BD2" t="inlineStr"/>
+        <v>-0.2250853049076262</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>1.333775252525253</v>
+      </c>
       <c r="BE2" t="n">
         <v>0</v>
       </c>
@@ -912,7 +912,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lli2SfLl</t>
+          <t>0jdIgO6t</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -954,48 +954,48 @@
       <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="n">
-        <v>3.122819833675091</v>
+        <v>0.5012152777777743</v>
       </c>
       <c r="AM3" t="n">
         <v>-0.1696718121060228</v>
       </c>
-      <c r="AN3" t="n">
-        <v>-0.3962436868686867</v>
-      </c>
-      <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="n">
-        <v>-1990785.984848485</v>
-      </c>
-      <c r="AQ3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="n">
+        <v>-2087713.068181818</v>
+      </c>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="n">
+        <v>-1.460763888888891</v>
+      </c>
       <c r="AR3" t="n">
-        <v>0.4663194444444443</v>
-      </c>
-      <c r="AS3" t="inlineStr"/>
+        <v>-0.6915450320877881</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>1.164630681818153</v>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AU3" t="inlineStr"/>
       <c r="AV3" t="n">
-        <v>-2.061805555555566</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>-1992049.702855624</v>
-      </c>
+        <v>-5.383947795625431</v>
+      </c>
+      <c r="AW3" t="inlineStr"/>
       <c r="AX3" t="n">
-        <v>-1.413888888888891</v>
-      </c>
-      <c r="AY3" t="inlineStr"/>
-      <c r="AZ3" t="n">
-        <v>-0.8104025056327657</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>1.088162878787841</v>
-      </c>
+        <v>-1.859359751177195</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>-1996585.913173085</v>
+      </c>
+      <c r="AZ3" t="inlineStr"/>
+      <c r="BA3" t="inlineStr"/>
       <c r="BB3" t="n">
-        <v>-1.87742357392851</v>
+        <v>-2.130271464646469</v>
       </c>
       <c r="BC3" t="n">
-        <v>-5.437775507265641</v>
-      </c>
-      <c r="BD3" t="inlineStr"/>
+        <v>3.030508325738584</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>-0.3962436868686867</v>
+      </c>
       <c r="BE3" t="n">
         <v>0</v>
       </c>
@@ -1079,92 +1079,92 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB4" t="n">
         <v>-1</v>
       </c>
-      <c r="U4" t="n">
+      <c r="AC4" t="n">
         <v>1</v>
       </c>
-      <c r="V4" t="n">
-        <v>-5</v>
-      </c>
-      <c r="W4" t="n">
-        <v>2</v>
-      </c>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="n">
+      <c r="AD4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="n">
         <v>-21</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AI4" t="n">
         <v>21</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>4</v>
       </c>
       <c r="AJ4" t="n">
         <v>75.09999999999999</v>
       </c>
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="n">
-        <v>-1.703678188565682</v>
+        <v>0.7580387205387211</v>
       </c>
       <c r="AM4" t="n">
         <v>-0.01504158027327374</v>
       </c>
-      <c r="AN4" t="n">
-        <v>-0.008080808080808133</v>
-      </c>
-      <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="n">
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="n">
         <v>5738117.283950619</v>
       </c>
-      <c r="AQ4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="n">
+        <v>1.21986531986532</v>
+      </c>
       <c r="AR4" t="n">
-        <v>0.7580387205387211</v>
-      </c>
-      <c r="AS4" t="inlineStr"/>
+        <v>-3.256647387470707</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>2.306705948372638</v>
+      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AU4" t="inlineStr"/>
       <c r="AV4" t="n">
+        <v>2.625030756942238</v>
+      </c>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="n">
+        <v>1.722677819265598</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>14904659.0151398</v>
+      </c>
+      <c r="AZ4" t="inlineStr"/>
+      <c r="BA4" t="inlineStr"/>
+      <c r="BB4" t="n">
         <v>0.5240319865319805</v>
       </c>
-      <c r="AW4" t="n">
-        <v>14904659.0151398</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1.21986531986532</v>
-      </c>
-      <c r="AY4" t="inlineStr"/>
-      <c r="AZ4" t="n">
-        <v>-3.256647387470707</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>2.306705948372638</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>1.722677819265598</v>
-      </c>
       <c r="BC4" t="n">
-        <v>2.625030756942238</v>
-      </c>
-      <c r="BD4" t="inlineStr"/>
+        <v>-1.703678188565682</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>-0.008080808080808133</v>
+      </c>
       <c r="BE4" t="n">
         <v>0</v>
       </c>
@@ -1266,48 +1266,48 @@
       <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="n">
-        <v>3.186373731732711</v>
+        <v>2.642599607182941</v>
       </c>
       <c r="AM5" t="n">
         <v>-0.2172706953575567</v>
       </c>
-      <c r="AN5" t="n">
-        <v>-0.2895342312008979</v>
-      </c>
-      <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="n">
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="n">
         <v>-5105757.225028058</v>
       </c>
-      <c r="AQ5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="n">
+        <v>-2.303858024691351</v>
+      </c>
       <c r="AR5" t="n">
-        <v>2.642599607182941</v>
-      </c>
-      <c r="AS5" t="inlineStr"/>
+        <v>-1.138384139353121</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>-2.149565095398458</v>
+      </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AU5" t="inlineStr"/>
       <c r="AV5" t="n">
+        <v>-4.881280258590039</v>
+      </c>
+      <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="n">
+        <v>-2.65491420065635</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>-4293902.806739619</v>
+      </c>
+      <c r="AZ5" t="inlineStr"/>
+      <c r="BA5" t="inlineStr"/>
+      <c r="BB5" t="n">
         <v>-3.271689113355777</v>
       </c>
-      <c r="AW5" t="n">
-        <v>-4293902.806739619</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>-2.303858024691351</v>
-      </c>
-      <c r="AY5" t="inlineStr"/>
-      <c r="AZ5" t="n">
-        <v>-1.138384139353121</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>-2.149565095398458</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>-2.65491420065635</v>
-      </c>
       <c r="BC5" t="n">
-        <v>-4.881280258590039</v>
-      </c>
-      <c r="BD5" t="inlineStr"/>
+        <v>3.186373731732711</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>-0.2895342312008979</v>
+      </c>
       <c r="BE5" t="n">
         <v>0</v>
       </c>
@@ -1409,48 +1409,48 @@
       <c r="AJ6" t="inlineStr"/>
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="n">
-        <v>-0.02856035983234406</v>
+        <v>0.5761363636363619</v>
       </c>
       <c r="AM6" t="n">
         <v>-0.8015544926494629</v>
       </c>
-      <c r="AN6" t="n">
-        <v>-1.142613636363637</v>
-      </c>
-      <c r="AO6" t="inlineStr"/>
-      <c r="AP6" t="n">
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="n">
         <v>-25128693.18181818</v>
       </c>
-      <c r="AQ6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="n">
+        <v>-6.902840909090912</v>
+      </c>
       <c r="AR6" t="n">
-        <v>0.5761363636363619</v>
-      </c>
-      <c r="AS6" t="inlineStr"/>
+        <v>0.5327903007598991</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>-1.482386363636351</v>
+      </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AU6" t="inlineStr"/>
       <c r="AV6" t="n">
+        <v>-7.943548412404638</v>
+      </c>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="n">
+        <v>-8.988607277865384</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>-17385962.19392124</v>
+      </c>
+      <c r="AZ6" t="inlineStr"/>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="n">
         <v>-7.118749999999991</v>
       </c>
-      <c r="AW6" t="n">
-        <v>-17385962.19392124</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>-6.902840909090912</v>
-      </c>
-      <c r="AY6" t="inlineStr"/>
-      <c r="AZ6" t="n">
-        <v>0.5327903007598991</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>-1.482386363636351</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>-8.988607277865384</v>
-      </c>
       <c r="BC6" t="n">
-        <v>-7.943548412404624</v>
-      </c>
-      <c r="BD6" t="inlineStr"/>
+        <v>-0.02856035983234406</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>-1.142613636363637</v>
+      </c>
       <c r="BE6" t="n">
         <v>0</v>
       </c>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">storks s 
+          <t xml:space="preserve">siebert d 
   ger </t>
         </is>
       </c>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>f3ddUIXs</t>
+          <t>K6A2elS9</t>
         </is>
       </c>
       <c r="O7" t="n">
@@ -1548,48 +1548,48 @@
       <c r="AJ7" t="inlineStr"/>
       <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="n">
-        <v>0.9931639636530925</v>
+        <v>-0.1119949494949495</v>
       </c>
       <c r="AM7" t="n">
-        <v>-0.2319369680239243</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>-0.4796969696969695</v>
-      </c>
-      <c r="AO7" t="inlineStr"/>
-      <c r="AP7" t="n">
-        <v>-8890104.377104376</v>
-      </c>
-      <c r="AQ7" t="inlineStr"/>
+        <v>-0.241524327122153</v>
+      </c>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="n">
+        <v>-8917360.164141413</v>
+      </c>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="n">
+        <v>-7.103535353535349</v>
+      </c>
       <c r="AR7" t="n">
-        <v>-0.1991245791245788</v>
-      </c>
-      <c r="AS7" t="inlineStr"/>
+        <v>2.095403079710167</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>-0.3722253787878742</v>
+      </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AU7" t="inlineStr"/>
       <c r="AV7" t="n">
-        <v>-6.93208754208753</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>-6966625.927363698</v>
-      </c>
+        <v>-7.191032608695664</v>
+      </c>
+      <c r="AW7" t="inlineStr"/>
       <c r="AX7" t="n">
-        <v>-7.116868686868685</v>
-      </c>
-      <c r="AY7" t="inlineStr"/>
-      <c r="AZ7" t="n">
-        <v>2.186201690821264</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>-0.5158249158249077</v>
-      </c>
+        <v>-7.030556633885439</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>-7109841.054175293</v>
+      </c>
+      <c r="AZ7" t="inlineStr"/>
+      <c r="BA7" t="inlineStr"/>
       <c r="BB7" t="n">
-        <v>-6.912198642742112</v>
+        <v>-6.956960227272717</v>
       </c>
       <c r="BC7" t="n">
-        <v>-7.196666666666658</v>
-      </c>
-      <c r="BD7" t="inlineStr"/>
+        <v>0.8511052881297445</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>-0.4834816919191918</v>
+      </c>
       <c r="BE7" t="n">
         <v>0</v>
       </c>
@@ -1691,48 +1691,48 @@
       <c r="AJ8" t="inlineStr"/>
       <c r="AK8" t="inlineStr"/>
       <c r="AL8" t="n">
-        <v>-1.866914682539679</v>
+        <v>-1.474621212121214</v>
       </c>
       <c r="AM8" t="n">
         <v>-0.2390376984126981</v>
       </c>
-      <c r="AN8" t="n">
-        <v>-0.07588383838383805</v>
-      </c>
-      <c r="AO8" t="inlineStr"/>
-      <c r="AP8" t="n">
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="n">
         <v>5087209.595959593</v>
       </c>
-      <c r="AQ8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="n">
+        <v>1.6532196969697</v>
+      </c>
       <c r="AR8" t="n">
-        <v>-1.474621212121214</v>
-      </c>
-      <c r="AS8" t="inlineStr"/>
+        <v>-2.078422619047615</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>1.374242424242368</v>
+      </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AU8" t="inlineStr"/>
       <c r="AV8" t="n">
+        <v>-0.8065476190476062</v>
+      </c>
+      <c r="AW8" t="inlineStr"/>
+      <c r="AX8" t="n">
+        <v>-1.273363095238096</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>979817.0882936502</v>
+      </c>
+      <c r="AZ8" t="inlineStr"/>
+      <c r="BA8" t="inlineStr"/>
+      <c r="BB8" t="n">
         <v>0.90347222222222</v>
       </c>
-      <c r="AW8" t="n">
-        <v>979817.0882936511</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>1.6532196969697</v>
-      </c>
-      <c r="AY8" t="inlineStr"/>
-      <c r="AZ8" t="n">
-        <v>-2.078422619047643</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>1.374242424242368</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>-1.273363095238096</v>
-      </c>
       <c r="BC8" t="n">
-        <v>-0.8065476190476062</v>
-      </c>
-      <c r="BD8" t="inlineStr"/>
+        <v>-1.866914682539683</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>-0.07588383838383805</v>
+      </c>
       <c r="BE8" t="n">
         <v>0</v>
       </c>
@@ -1834,48 +1834,48 @@
       <c r="AJ9" t="inlineStr"/>
       <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="n">
-        <v>-0.7738923958738191</v>
+        <v>-2.389646464646464</v>
       </c>
       <c r="AM9" t="n">
         <v>-0.01053608843856479</v>
       </c>
-      <c r="AN9" t="n">
-        <v>-0.1264204545454541</v>
-      </c>
-      <c r="AO9" t="inlineStr"/>
-      <c r="AP9" t="n">
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="n">
         <v>6646772.411616158</v>
       </c>
-      <c r="AQ9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="n">
+        <v>1.853235479797988</v>
+      </c>
       <c r="AR9" t="n">
-        <v>-2.389646464646464</v>
-      </c>
-      <c r="AS9" t="inlineStr"/>
+        <v>-1.038929235968709</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>-2.293734217171703</v>
+      </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AU9" t="inlineStr"/>
       <c r="AV9" t="n">
+        <v>0.9283481793833914</v>
+      </c>
+      <c r="AW9" t="inlineStr"/>
+      <c r="AX9" t="n">
+        <v>-0.3447359137036017</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>28889.87627547048</v>
+      </c>
+      <c r="AZ9" t="inlineStr"/>
+      <c r="BA9" t="inlineStr"/>
+      <c r="BB9" t="n">
         <v>2.617282196969697</v>
       </c>
-      <c r="AW9" t="n">
-        <v>28889.87627547048</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>1.853235479797988</v>
-      </c>
-      <c r="AY9" t="inlineStr"/>
-      <c r="AZ9" t="n">
-        <v>-1.038929235968709</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>-2.293734217171703</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>-0.3447359137036017</v>
-      </c>
       <c r="BC9" t="n">
-        <v>0.9283481793833914</v>
-      </c>
-      <c r="BD9" t="inlineStr"/>
+        <v>-0.7738923958738155</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>-0.1264204545454541</v>
+      </c>
       <c r="BE9" t="n">
         <v>0</v>
       </c>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">siebert d 
+          <t xml:space="preserve">jablonski s 
   ger </t>
         </is>
       </c>
@@ -1940,7 +1940,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0jdIgO6t</t>
+          <t>4ljanukM</t>
         </is>
       </c>
       <c r="O10" t="n">
@@ -1977,357 +1977,49 @@
       <c r="AJ10" t="inlineStr"/>
       <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="n">
-        <v>1.084987459843244</v>
+        <v>1.125946969696972</v>
       </c>
       <c r="AM10" t="n">
         <v>0.463121401783444</v>
       </c>
-      <c r="AN10" t="n">
-        <v>0.6195075757575756</v>
-      </c>
-      <c r="AO10" t="inlineStr"/>
-      <c r="AP10" t="n">
-        <v>6108409.792368125</v>
-      </c>
-      <c r="AQ10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="n">
+        <v>6115112.373737373</v>
+      </c>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="n">
+        <v>5.790669191919179</v>
+      </c>
       <c r="AR10" t="n">
-        <v>1.100862794612794</v>
-      </c>
-      <c r="AS10" t="inlineStr"/>
+        <v>-1.414131621279296</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>-0.1720075757575614</v>
+      </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AU10" t="inlineStr"/>
       <c r="AV10" t="n">
-        <v>5.096282267115612</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>3838965.955107677</v>
-      </c>
+        <v>4.587136981413451</v>
+      </c>
+      <c r="AW10" t="inlineStr"/>
       <c r="AX10" t="n">
-        <v>5.791533389450052</v>
-      </c>
-      <c r="AY10" t="inlineStr"/>
-      <c r="AZ10" t="n">
-        <v>-1.766098248085967</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>-0.1428942199775634</v>
-      </c>
+        <v>6.641650671996487</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>3742126.338364293</v>
+      </c>
+      <c r="AZ10" t="inlineStr"/>
+      <c r="BA10" t="inlineStr"/>
       <c r="BB10" t="n">
-        <v>6.898806906810108</v>
+        <v>5.044520202020209</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.834310716404545</v>
-      </c>
-      <c r="BD10" t="inlineStr"/>
+        <v>1.254099769484451</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0.6195075757575756</v>
+      </c>
       <c r="BE10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>AuVMGZvJ</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45529.52083333334</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jablonski s 
-  ger </t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">millerntor stadion
-  hamburg </t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>ILyJuN3g</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>KWixEVWi</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>59</v>
-      </c>
-      <c r="H11" t="n">
-        <v>591</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>02hM7hzd</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>4ljanukM</t>
-        </is>
-      </c>
-      <c r="O11" t="n">
-        <v>1</v>
-      </c>
-      <c r="P11" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>4</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr"/>
-      <c r="AE11" t="inlineStr"/>
-      <c r="AF11" t="inlineStr"/>
-      <c r="AG11" t="inlineStr"/>
-      <c r="AH11" t="inlineStr"/>
-      <c r="AI11" t="inlineStr"/>
-      <c r="AJ11" t="inlineStr"/>
-      <c r="AK11" t="inlineStr"/>
-      <c r="AL11" t="n">
-        <v>-1.282593056715857</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>-1100000</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>-2073807.519640853</v>
-      </c>
-      <c r="AQ11" t="inlineStr"/>
-      <c r="AR11" t="n">
-        <v>0.03417508417508586</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>-70</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AU11" t="inlineStr"/>
-      <c r="AV11" t="n">
-        <v>-2.138075196408522</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>-616302.3298988212</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>-2.883641975308649</v>
-      </c>
-      <c r="AY11" t="inlineStr"/>
-      <c r="AZ11" t="n">
-        <v>2.663215910145738</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>-1.692648709315336</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>-2.481887589343728</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>0.2097674742411613</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>-66</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>t0w6KHuf</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45529.4375</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">siebert d 
-  ger </t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">volkswagen arena
-  wolfsburg </t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>nwkTahLL</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>nVp0wiqd</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>59</v>
-      </c>
-      <c r="H12" t="n">
-        <v>591</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>rFNN7oyi</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>K6A2elS9</t>
-        </is>
-      </c>
-      <c r="O12" t="n">
-        <v>-43</v>
-      </c>
-      <c r="P12" t="n">
-        <v>-5</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>-14</v>
-      </c>
-      <c r="R12" t="n">
-        <v>-2</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr"/>
-      <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="inlineStr"/>
-      <c r="AE12" t="inlineStr"/>
-      <c r="AF12" t="inlineStr"/>
-      <c r="AG12" t="inlineStr"/>
-      <c r="AH12" t="inlineStr"/>
-      <c r="AI12" t="inlineStr"/>
-      <c r="AJ12" t="inlineStr"/>
-      <c r="AK12" t="inlineStr"/>
-      <c r="AL12" t="n">
-        <v>-0.4936465524424811</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>-1.003795402958817</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>-1.465858585858586</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>-77525000</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>-30603441.07744108</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>-1.690774410774409</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>-325</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>-4.833333333333343</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>-5.056296296296296</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>-21566201.81850507</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>-6.165454545454537</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>0.1666666666666679</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>1.444759143978416</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>1.751380471380457</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>-5.014741481017907</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>-5.151239129495977</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>-281</v>
-      </c>
-      <c r="BE12" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_preparation/df_constructed.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_constructed.xlsx
@@ -525,84 +525,84 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_ball_possession</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession_against</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_points</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_points_against</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts_against</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals_against</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_n_matches_last_days</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_n_matches_last_days_against</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_fouls</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_fouls_against</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals_against</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts_against</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession_against</t>
-        </is>
-      </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
@@ -615,97 +615,97 @@
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_age_player_start</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_int_rep_player_sub</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
         </is>
       </c>
       <c r="BE1" s="1" t="inlineStr">
@@ -811,48 +811,48 @@
       <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="n">
+        <v>-0.2250853049076262</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1.333775252525253</v>
+      </c>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="n">
         <v>-0.1072601010100982</v>
       </c>
-      <c r="AM2" t="n">
+      <c r="AQ2" t="n">
+        <v>1.203598484848499</v>
+      </c>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="n">
+        <v>23618378.25977181</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>7.494381313131314</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>6.646464646464636</v>
+      </c>
+      <c r="AX2" t="n">
         <v>0.8218458137710389</v>
       </c>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="n">
+      <c r="AY2" t="n">
+        <v>6.70966102328353</v>
+      </c>
+      <c r="AZ2" t="n">
         <v>33450871.21212121</v>
       </c>
-      <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="n">
-        <v>6.646464646464636</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>-2.116631047485271</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>1.203598484848499</v>
-      </c>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="n">
-        <v>6.70966102328353</v>
-      </c>
-      <c r="AW2" t="inlineStr"/>
-      <c r="AX2" t="n">
-        <v>5.220971451973583</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>23618378.25977181</v>
-      </c>
-      <c r="AZ2" t="inlineStr"/>
       <c r="BA2" t="inlineStr"/>
       <c r="BB2" t="n">
-        <v>7.494381313131314</v>
+        <v>-2.116631047485271</v>
       </c>
       <c r="BC2" t="n">
-        <v>-0.2250853049076262</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>1.333775252525253</v>
-      </c>
+        <v>5.220971451973583</v>
+      </c>
+      <c r="BD2" t="inlineStr"/>
       <c r="BE2" t="n">
         <v>0</v>
       </c>
@@ -954,48 +954,48 @@
       <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="n">
+        <v>3.030508325738584</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>-0.3962436868686867</v>
+      </c>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="n">
         <v>0.5012152777777743</v>
       </c>
-      <c r="AM3" t="n">
+      <c r="AQ3" t="n">
+        <v>1.164630681818153</v>
+      </c>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="n">
+        <v>-1996585.913173085</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>-2.130271464646469</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>-1.460763888888891</v>
+      </c>
+      <c r="AX3" t="n">
         <v>-0.1696718121060228</v>
       </c>
-      <c r="AN3" t="inlineStr"/>
-      <c r="AO3" t="n">
+      <c r="AY3" t="n">
+        <v>-5.383947795625431</v>
+      </c>
+      <c r="AZ3" t="n">
         <v>-2087713.068181818</v>
       </c>
-      <c r="AP3" t="inlineStr"/>
-      <c r="AQ3" t="n">
-        <v>-1.460763888888891</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>-0.6915450320877881</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>1.164630681818153</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AU3" t="inlineStr"/>
-      <c r="AV3" t="n">
-        <v>-5.383947795625431</v>
-      </c>
-      <c r="AW3" t="inlineStr"/>
-      <c r="AX3" t="n">
-        <v>-1.859359751177195</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>-1996585.913173085</v>
-      </c>
-      <c r="AZ3" t="inlineStr"/>
       <c r="BA3" t="inlineStr"/>
       <c r="BB3" t="n">
-        <v>-2.130271464646469</v>
+        <v>-0.6915450320877881</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.030508325738584</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>-0.3962436868686867</v>
-      </c>
+        <v>-1.859359751177195</v>
+      </c>
+      <c r="BD3" t="inlineStr"/>
       <c r="BE3" t="n">
         <v>0</v>
       </c>
@@ -1079,24 +1079,24 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>-21</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>11</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="AA4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AB4" t="n">
         <v>-1</v>
@@ -1104,67 +1104,67 @@
       <c r="AC4" t="n">
         <v>1</v>
       </c>
-      <c r="AD4" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>2</v>
+      </c>
       <c r="AH4" t="n">
-        <v>-21</v>
+        <v>1</v>
       </c>
       <c r="AI4" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="AJ4" t="n">
         <v>75.09999999999999</v>
       </c>
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="n">
+        <v>-1.703678188565682</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>-0.008080808080808133</v>
+      </c>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="n">
         <v>0.7580387205387211</v>
       </c>
-      <c r="AM4" t="n">
+      <c r="AQ4" t="n">
+        <v>2.306705948372638</v>
+      </c>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="n">
+        <v>14904659.0151398</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0.5240319865319805</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.21986531986532</v>
+      </c>
+      <c r="AX4" t="n">
         <v>-0.01504158027327374</v>
       </c>
-      <c r="AN4" t="inlineStr"/>
-      <c r="AO4" t="n">
+      <c r="AY4" t="n">
+        <v>2.625030756942238</v>
+      </c>
+      <c r="AZ4" t="n">
         <v>5738117.283950619</v>
       </c>
-      <c r="AP4" t="inlineStr"/>
-      <c r="AQ4" t="n">
-        <v>1.21986531986532</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>-3.256647387470707</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>2.306705948372638</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AU4" t="inlineStr"/>
-      <c r="AV4" t="n">
-        <v>2.625030756942238</v>
-      </c>
-      <c r="AW4" t="inlineStr"/>
-      <c r="AX4" t="n">
-        <v>1.722677819265598</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>14904659.0151398</v>
-      </c>
-      <c r="AZ4" t="inlineStr"/>
       <c r="BA4" t="inlineStr"/>
       <c r="BB4" t="n">
-        <v>0.5240319865319805</v>
+        <v>-3.256647387470707</v>
       </c>
       <c r="BC4" t="n">
-        <v>-1.703678188565682</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>-0.008080808080808133</v>
-      </c>
+        <v>1.722677819265598</v>
+      </c>
+      <c r="BD4" t="inlineStr"/>
       <c r="BE4" t="n">
         <v>0</v>
       </c>
@@ -1266,48 +1266,48 @@
       <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="n">
+        <v>3.186373731732711</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>-0.2895342312008979</v>
+      </c>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="n">
         <v>2.642599607182941</v>
       </c>
-      <c r="AM5" t="n">
+      <c r="AQ5" t="n">
+        <v>-2.149565095398458</v>
+      </c>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="n">
+        <v>-4293902.806739619</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>-3.271689113355777</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>-2.303858024691351</v>
+      </c>
+      <c r="AX5" t="n">
         <v>-0.2172706953575567</v>
       </c>
-      <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="n">
+      <c r="AY5" t="n">
+        <v>-4.881280258590039</v>
+      </c>
+      <c r="AZ5" t="n">
         <v>-5105757.225028058</v>
       </c>
-      <c r="AP5" t="inlineStr"/>
-      <c r="AQ5" t="n">
-        <v>-2.303858024691351</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>-1.138384139353121</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>-2.149565095398458</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AU5" t="inlineStr"/>
-      <c r="AV5" t="n">
-        <v>-4.881280258590039</v>
-      </c>
-      <c r="AW5" t="inlineStr"/>
-      <c r="AX5" t="n">
-        <v>-2.65491420065635</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>-4293902.806739619</v>
-      </c>
-      <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="inlineStr"/>
       <c r="BB5" t="n">
-        <v>-3.271689113355777</v>
+        <v>-1.138384139353121</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.186373731732711</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>-0.2895342312008979</v>
-      </c>
+        <v>-2.65491420065635</v>
+      </c>
+      <c r="BD5" t="inlineStr"/>
       <c r="BE5" t="n">
         <v>0</v>
       </c>
@@ -1409,48 +1409,48 @@
       <c r="AJ6" t="inlineStr"/>
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="n">
+        <v>-0.02856035983234406</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>-1.142613636363637</v>
+      </c>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="n">
         <v>0.5761363636363619</v>
       </c>
-      <c r="AM6" t="n">
+      <c r="AQ6" t="n">
+        <v>-1.482386363636351</v>
+      </c>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="n">
+        <v>-17385962.19392124</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>-7.118749999999991</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>-6.902840909090912</v>
+      </c>
+      <c r="AX6" t="n">
         <v>-0.8015544926494629</v>
       </c>
-      <c r="AN6" t="inlineStr"/>
-      <c r="AO6" t="n">
+      <c r="AY6" t="n">
+        <v>-7.943548412404638</v>
+      </c>
+      <c r="AZ6" t="n">
         <v>-25128693.18181818</v>
       </c>
-      <c r="AP6" t="inlineStr"/>
-      <c r="AQ6" t="n">
-        <v>-6.902840909090912</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>0.5327903007598991</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>-1.482386363636351</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AU6" t="inlineStr"/>
-      <c r="AV6" t="n">
-        <v>-7.943548412404638</v>
-      </c>
-      <c r="AW6" t="inlineStr"/>
-      <c r="AX6" t="n">
-        <v>-8.988607277865384</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>-17385962.19392124</v>
-      </c>
-      <c r="AZ6" t="inlineStr"/>
       <c r="BA6" t="inlineStr"/>
       <c r="BB6" t="n">
-        <v>-7.118749999999991</v>
+        <v>0.5327903007598991</v>
       </c>
       <c r="BC6" t="n">
-        <v>-0.02856035983234406</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>-1.142613636363637</v>
-      </c>
+        <v>-8.988607277865384</v>
+      </c>
+      <c r="BD6" t="inlineStr"/>
       <c r="BE6" t="n">
         <v>0</v>
       </c>
@@ -1548,48 +1548,48 @@
       <c r="AJ7" t="inlineStr"/>
       <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="n">
+        <v>0.8511052881297445</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>-0.4834816919191918</v>
+      </c>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="n">
         <v>-0.1119949494949495</v>
       </c>
-      <c r="AM7" t="n">
+      <c r="AQ7" t="n">
+        <v>-0.3722253787878742</v>
+      </c>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="n">
+        <v>-7109841.054175293</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>-6.956960227272717</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>-7.103535353535349</v>
+      </c>
+      <c r="AX7" t="n">
         <v>-0.241524327122153</v>
       </c>
-      <c r="AN7" t="inlineStr"/>
-      <c r="AO7" t="n">
+      <c r="AY7" t="n">
+        <v>-7.191032608695664</v>
+      </c>
+      <c r="AZ7" t="n">
         <v>-8917360.164141413</v>
       </c>
-      <c r="AP7" t="inlineStr"/>
-      <c r="AQ7" t="n">
-        <v>-7.103535353535349</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>2.095403079710167</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>-0.3722253787878742</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AU7" t="inlineStr"/>
-      <c r="AV7" t="n">
-        <v>-7.191032608695664</v>
-      </c>
-      <c r="AW7" t="inlineStr"/>
-      <c r="AX7" t="n">
-        <v>-7.030556633885439</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>-7109841.054175293</v>
-      </c>
-      <c r="AZ7" t="inlineStr"/>
       <c r="BA7" t="inlineStr"/>
       <c r="BB7" t="n">
-        <v>-6.956960227272717</v>
+        <v>2.095403079710167</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.8511052881297445</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>-0.4834816919191918</v>
-      </c>
+        <v>-7.030556633885439</v>
+      </c>
+      <c r="BD7" t="inlineStr"/>
       <c r="BE7" t="n">
         <v>0</v>
       </c>
@@ -1691,48 +1691,48 @@
       <c r="AJ8" t="inlineStr"/>
       <c r="AK8" t="inlineStr"/>
       <c r="AL8" t="n">
+        <v>-1.866914682539683</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>-0.07588383838383805</v>
+      </c>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="n">
         <v>-1.474621212121214</v>
       </c>
-      <c r="AM8" t="n">
+      <c r="AQ8" t="n">
+        <v>1.374242424242368</v>
+      </c>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="n">
+        <v>979817.0882936502</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0.90347222222222</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>1.6532196969697</v>
+      </c>
+      <c r="AX8" t="n">
         <v>-0.2390376984126981</v>
       </c>
-      <c r="AN8" t="inlineStr"/>
-      <c r="AO8" t="n">
+      <c r="AY8" t="n">
+        <v>-0.8065476190476062</v>
+      </c>
+      <c r="AZ8" t="n">
         <v>5087209.595959593</v>
       </c>
-      <c r="AP8" t="inlineStr"/>
-      <c r="AQ8" t="n">
-        <v>1.6532196969697</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>-2.078422619047615</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>1.374242424242368</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AU8" t="inlineStr"/>
-      <c r="AV8" t="n">
-        <v>-0.8065476190476062</v>
-      </c>
-      <c r="AW8" t="inlineStr"/>
-      <c r="AX8" t="n">
-        <v>-1.273363095238096</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>979817.0882936502</v>
-      </c>
-      <c r="AZ8" t="inlineStr"/>
       <c r="BA8" t="inlineStr"/>
       <c r="BB8" t="n">
-        <v>0.90347222222222</v>
+        <v>-2.078422619047615</v>
       </c>
       <c r="BC8" t="n">
-        <v>-1.866914682539683</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>-0.07588383838383805</v>
-      </c>
+        <v>-1.273363095238096</v>
+      </c>
+      <c r="BD8" t="inlineStr"/>
       <c r="BE8" t="n">
         <v>0</v>
       </c>
@@ -1834,48 +1834,48 @@
       <c r="AJ9" t="inlineStr"/>
       <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="n">
+        <v>-0.7738923958738155</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>-0.1264204545454541</v>
+      </c>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="n">
         <v>-2.389646464646464</v>
       </c>
-      <c r="AM9" t="n">
+      <c r="AQ9" t="n">
+        <v>-2.293734217171703</v>
+      </c>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="n">
+        <v>28889.87627547048</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>2.617282196969697</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1.853235479797988</v>
+      </c>
+      <c r="AX9" t="n">
         <v>-0.01053608843856479</v>
       </c>
-      <c r="AN9" t="inlineStr"/>
-      <c r="AO9" t="n">
+      <c r="AY9" t="n">
+        <v>0.9283481793833914</v>
+      </c>
+      <c r="AZ9" t="n">
         <v>6646772.411616158</v>
       </c>
-      <c r="AP9" t="inlineStr"/>
-      <c r="AQ9" t="n">
-        <v>1.853235479797988</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>-1.038929235968709</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>-2.293734217171703</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AU9" t="inlineStr"/>
-      <c r="AV9" t="n">
-        <v>0.9283481793833914</v>
-      </c>
-      <c r="AW9" t="inlineStr"/>
-      <c r="AX9" t="n">
-        <v>-0.3447359137036017</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>28889.87627547048</v>
-      </c>
-      <c r="AZ9" t="inlineStr"/>
       <c r="BA9" t="inlineStr"/>
       <c r="BB9" t="n">
-        <v>2.617282196969697</v>
+        <v>-1.038929235968709</v>
       </c>
       <c r="BC9" t="n">
-        <v>-0.7738923958738155</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>-0.1264204545454541</v>
-      </c>
+        <v>-0.3447359137036017</v>
+      </c>
+      <c r="BD9" t="inlineStr"/>
       <c r="BE9" t="n">
         <v>0</v>
       </c>
@@ -1977,48 +1977,48 @@
       <c r="AJ10" t="inlineStr"/>
       <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="n">
+        <v>1.254099769484451</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0.6195075757575756</v>
+      </c>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="n">
         <v>1.125946969696972</v>
       </c>
-      <c r="AM10" t="n">
+      <c r="AQ10" t="n">
+        <v>-0.1720075757575614</v>
+      </c>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="n">
+        <v>3742126.338364293</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>5.044520202020209</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>5.790669191919179</v>
+      </c>
+      <c r="AX10" t="n">
         <v>0.463121401783444</v>
       </c>
-      <c r="AN10" t="inlineStr"/>
-      <c r="AO10" t="n">
+      <c r="AY10" t="n">
+        <v>4.587136981413451</v>
+      </c>
+      <c r="AZ10" t="n">
         <v>6115112.373737373</v>
       </c>
-      <c r="AP10" t="inlineStr"/>
-      <c r="AQ10" t="n">
-        <v>5.790669191919179</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>-1.414131621279296</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>-0.1720075757575614</v>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AU10" t="inlineStr"/>
-      <c r="AV10" t="n">
-        <v>4.587136981413451</v>
-      </c>
-      <c r="AW10" t="inlineStr"/>
-      <c r="AX10" t="n">
-        <v>6.641650671996487</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>3742126.338364293</v>
-      </c>
-      <c r="AZ10" t="inlineStr"/>
       <c r="BA10" t="inlineStr"/>
       <c r="BB10" t="n">
-        <v>5.044520202020209</v>
+        <v>-1.414131621279296</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.254099769484451</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>0.6195075757575756</v>
-      </c>
+        <v>6.641650671996487</v>
+      </c>
+      <c r="BD10" t="inlineStr"/>
       <c r="BE10" t="n">
         <v>0</v>
       </c>

--- a/data/germany/p6_deployment/data_preparation/df_constructed.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_constructed.xlsx
@@ -535,74 +535,74 @@
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_fouls</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls_against</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_points</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_points_against</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals_against</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days_against</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_expected_goals_(xg)</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_expected_goals_(xg)_against</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts_against</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals_against</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days_against</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls_against</t>
-        </is>
-      </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
@@ -615,92 +615,92 @@
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_age_player_sub</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_int_rep_player_start</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_miss</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
         </is>
       </c>
       <c r="BD1" s="1" t="inlineStr">
@@ -810,48 +810,48 @@
       <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="n">
-        <v>-0.2250853049076262</v>
-      </c>
+      <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="n">
-        <v>1.333775252525253</v>
-      </c>
-      <c r="AN2" t="inlineStr"/>
+        <v>5.096331319262319</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0.8184757146045434</v>
+      </c>
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="n">
-        <v>-0.1072601010100982</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>1.203598484848499</v>
-      </c>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="inlineStr"/>
+        <v>-0.1485569985569981</v>
+      </c>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="n">
+        <v>-0.226684792910298</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>7.383189033189041</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>6.362193362193366</v>
+      </c>
       <c r="AU2" t="n">
-        <v>23618378.25977181</v>
+        <v>6.727282666065534</v>
       </c>
       <c r="AV2" t="n">
-        <v>7.494381313131314</v>
+        <v>31118852.81385281</v>
       </c>
       <c r="AW2" t="n">
-        <v>6.646464646464636</v>
+        <v>1.290548340548341</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.8218458137710389</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>6.70966102328353</v>
-      </c>
+        <v>23603044.54178003</v>
+      </c>
+      <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="n">
-        <v>33450871.21212121</v>
-      </c>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="n">
-        <v>-2.116631047485271</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>5.220971451973583</v>
-      </c>
+        <v>1.232683982683994</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>-2.127510312772245</v>
+      </c>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
       <c r="BD2" t="inlineStr"/>
       <c r="BE2" t="n">
         <v>0</v>
@@ -953,48 +953,48 @@
       <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="n">
-        <v>3.030508325738584</v>
-      </c>
+      <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="n">
-        <v>-0.3962436868686867</v>
-      </c>
-      <c r="AN3" t="inlineStr"/>
+        <v>-1.859359751177195</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>-0.1696718121060228</v>
+      </c>
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="n">
         <v>0.5012152777777743</v>
       </c>
-      <c r="AQ3" t="n">
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="n">
+        <v>3.030508325738584</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>-2.130271464646469</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>-1.460763888888891</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>-5.383947795625431</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>-2087713.068181818</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>-0.3962436868686867</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>-1996585.913173085</v>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="n">
         <v>1.164630681818153</v>
       </c>
-      <c r="AR3" t="inlineStr"/>
-      <c r="AS3" t="inlineStr"/>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AU3" t="n">
-        <v>-1996585.913173085</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>-2.130271464646469</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>-1.460763888888891</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>-0.1696718121060228</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>-5.383947795625431</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>-2087713.068181818</v>
-      </c>
-      <c r="BA3" t="inlineStr"/>
-      <c r="BB3" t="n">
+      <c r="BA3" t="n">
         <v>-0.6915450320877881</v>
       </c>
-      <c r="BC3" t="n">
-        <v>-1.859359751177195</v>
-      </c>
+      <c r="BB3" t="inlineStr"/>
+      <c r="BC3" t="inlineStr"/>
       <c r="BD3" t="inlineStr"/>
       <c r="BE3" t="n">
         <v>0</v>
@@ -1085,18 +1085,22 @@
         <v>21</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
       <c r="Z4" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="AA4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AB4" t="n">
         <v>-1</v>
@@ -1106,64 +1110,60 @@
       </c>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>2</v>
-      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="AI4" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="AJ4" t="n">
         <v>75.09999999999999</v>
       </c>
       <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="n">
-        <v>-1.703678188565682</v>
-      </c>
+      <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="n">
-        <v>-0.008080808080808133</v>
-      </c>
-      <c r="AN4" t="inlineStr"/>
+        <v>2.114992897242516</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0.02214647089452959</v>
+      </c>
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="n">
-        <v>0.7580387205387211</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>2.306705948372638</v>
-      </c>
-      <c r="AR4" t="inlineStr"/>
-      <c r="AS4" t="inlineStr"/>
-      <c r="AT4" t="inlineStr"/>
+        <v>0.8429924242424249</v>
+      </c>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="n">
+        <v>-1.693165142311102</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0.3559929653679603</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1.064393939393938</v>
+      </c>
       <c r="AU4" t="n">
-        <v>14904659.0151398</v>
+        <v>2.84461743559666</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.5240319865319805</v>
+        <v>4426932.269119769</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.21986531986532</v>
+        <v>-0.03062094155844131</v>
       </c>
       <c r="AX4" t="n">
-        <v>-0.01504158027327374</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>2.625030756942238</v>
-      </c>
+        <v>16829768.68946056</v>
+      </c>
+      <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="n">
-        <v>5738117.283950619</v>
-      </c>
-      <c r="BA4" t="inlineStr"/>
-      <c r="BB4" t="n">
-        <v>-3.256647387470707</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>1.722677819265598</v>
-      </c>
+        <v>2.156631042568534</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>-2.964555189569751</v>
+      </c>
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="inlineStr"/>
       <c r="BD4" t="inlineStr"/>
       <c r="BE4" t="n">
         <v>0</v>
@@ -1265,48 +1265,48 @@
       <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="n">
-        <v>3.186373731732711</v>
-      </c>
+      <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="n">
-        <v>-0.2895342312008979</v>
-      </c>
-      <c r="AN5" t="inlineStr"/>
+        <v>-2.401616347619253</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>-0.2094089894623838</v>
+      </c>
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="n">
-        <v>2.642599607182941</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>-2.149565095398458</v>
-      </c>
-      <c r="AR5" t="inlineStr"/>
-      <c r="AS5" t="inlineStr"/>
-      <c r="AT5" t="inlineStr"/>
+        <v>2.503358986692316</v>
+      </c>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="n">
+        <v>3.538782753121588</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>-3.179174683341358</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>-2.210207231040556</v>
+      </c>
       <c r="AU5" t="n">
-        <v>-4293902.806739619</v>
+        <v>-5.050709995587823</v>
       </c>
       <c r="AV5" t="n">
-        <v>-3.271689113355777</v>
+        <v>-4924003.07639891</v>
       </c>
       <c r="AW5" t="n">
-        <v>-2.303858024691351</v>
+        <v>-0.2849527016193685</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.2172706953575567</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>-4.881280258590039</v>
-      </c>
+        <v>-4269502.420584014</v>
+      </c>
+      <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="n">
-        <v>-5105757.225028058</v>
-      </c>
-      <c r="BA5" t="inlineStr"/>
-      <c r="BB5" t="n">
-        <v>-1.138384139353121</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>-2.65491420065635</v>
-      </c>
+        <v>-2.266808962642301</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>-0.9395091617304843</v>
+      </c>
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="inlineStr"/>
       <c r="BD5" t="inlineStr"/>
       <c r="BE5" t="n">
         <v>0</v>
@@ -1408,48 +1408,48 @@
       <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="inlineStr"/>
       <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="n">
-        <v>-0.02856035983234406</v>
-      </c>
+      <c r="AL6" t="inlineStr"/>
       <c r="AM6" t="n">
-        <v>-1.142613636363637</v>
-      </c>
-      <c r="AN6" t="inlineStr"/>
+        <v>-8.842138476290586</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>-0.8118956106470048</v>
+      </c>
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="n">
-        <v>0.5761363636363619</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>-1.482386363636351</v>
-      </c>
-      <c r="AR6" t="inlineStr"/>
-      <c r="AS6" t="inlineStr"/>
-      <c r="AT6" t="inlineStr"/>
+        <v>0.7623376623376608</v>
+      </c>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="n">
+        <v>0.03779609669954453</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>-7.200649350649343</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>-6.798051948051963</v>
+      </c>
       <c r="AU6" t="n">
-        <v>-17385962.19392124</v>
+        <v>-7.958301360208452</v>
       </c>
       <c r="AV6" t="n">
-        <v>-7.118749999999991</v>
+        <v>-25500324.67532468</v>
       </c>
       <c r="AW6" t="n">
-        <v>-6.902840909090912</v>
+        <v>-1.15</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.8015544926494629</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>-7.943548412404638</v>
-      </c>
+        <v>-17834328.81686237</v>
+      </c>
+      <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="n">
-        <v>-25128693.18181818</v>
-      </c>
-      <c r="BA6" t="inlineStr"/>
-      <c r="BB6" t="n">
-        <v>0.5327903007598991</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>-8.988607277865384</v>
-      </c>
+        <v>-1.616233766233762</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0.7606889151541623</v>
+      </c>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="inlineStr"/>
       <c r="BD6" t="inlineStr"/>
       <c r="BE6" t="n">
         <v>0</v>
@@ -1547,48 +1547,48 @@
       <c r="AI7" t="inlineStr"/>
       <c r="AJ7" t="inlineStr"/>
       <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="n">
-        <v>0.8511052881297445</v>
-      </c>
+      <c r="AL7" t="inlineStr"/>
       <c r="AM7" t="n">
-        <v>-0.4834816919191918</v>
-      </c>
-      <c r="AN7" t="inlineStr"/>
+        <v>-6.868331608005505</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>-0.2427632083429183</v>
+      </c>
       <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="n">
-        <v>-0.1119949494949495</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>-0.3722253787878742</v>
-      </c>
-      <c r="AR7" t="inlineStr"/>
-      <c r="AS7" t="inlineStr"/>
-      <c r="AT7" t="inlineStr"/>
+        <v>0.08010261343595104</v>
+      </c>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="n">
+        <v>0.7218292308871987</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>-7.179222783389449</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>-7.305515472182151</v>
+      </c>
       <c r="AU7" t="n">
-        <v>-7109841.054175293</v>
+        <v>-7.119085959665654</v>
       </c>
       <c r="AV7" t="n">
-        <v>-6.956960227272717</v>
+        <v>-9326396.705146704</v>
       </c>
       <c r="AW7" t="n">
-        <v>-7.103535353535349</v>
+        <v>-0.4939133397466731</v>
       </c>
       <c r="AX7" t="n">
-        <v>-0.241524327122153</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>-7.191032608695664</v>
-      </c>
+        <v>-6882742.336668966</v>
+      </c>
+      <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="n">
-        <v>-8917360.164141413</v>
-      </c>
-      <c r="BA7" t="inlineStr"/>
-      <c r="BB7" t="n">
-        <v>2.095403079710167</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>-7.030556633885439</v>
-      </c>
+        <v>-0.1199875741542655</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>2.078473659995439</v>
+      </c>
+      <c r="BB7" t="inlineStr"/>
+      <c r="BC7" t="inlineStr"/>
       <c r="BD7" t="inlineStr"/>
       <c r="BE7" t="n">
         <v>0</v>
@@ -1690,48 +1690,48 @@
       <c r="AI8" t="inlineStr"/>
       <c r="AJ8" t="inlineStr"/>
       <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="n">
-        <v>-1.866914682539683</v>
-      </c>
+      <c r="AL8" t="inlineStr"/>
       <c r="AM8" t="n">
-        <v>-0.07588383838383805</v>
-      </c>
-      <c r="AN8" t="inlineStr"/>
+        <v>-1.307164115646273</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>-0.250439342403628</v>
+      </c>
       <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="n">
-        <v>-1.474621212121214</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>1.374242424242368</v>
-      </c>
-      <c r="AR8" t="inlineStr"/>
-      <c r="AS8" t="inlineStr"/>
-      <c r="AT8" t="inlineStr"/>
+        <v>-1.363663419913419</v>
+      </c>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="n">
+        <v>-2.002625425170066</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0.8020111832611718</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>1.69396645021645</v>
+      </c>
       <c r="AU8" t="n">
-        <v>979817.0882936502</v>
+        <v>-0.7108134920635081</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.90347222222222</v>
+        <v>5092120.310245306</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.6532196969697</v>
+        <v>-0.0670364357864357</v>
       </c>
       <c r="AX8" t="n">
-        <v>-0.2390376984126981</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>-0.8065476190476062</v>
-      </c>
+        <v>1021023.419784582</v>
+      </c>
+      <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="n">
-        <v>5087209.595959593</v>
-      </c>
-      <c r="BA8" t="inlineStr"/>
-      <c r="BB8" t="n">
-        <v>-2.078422619047615</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>-1.273363095238096</v>
-      </c>
+        <v>1.622375541125479</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>-2.424581916099783</v>
+      </c>
+      <c r="BB8" t="inlineStr"/>
+      <c r="BC8" t="inlineStr"/>
       <c r="BD8" t="inlineStr"/>
       <c r="BE8" t="n">
         <v>0</v>
@@ -1833,48 +1833,48 @@
       <c r="AI9" t="inlineStr"/>
       <c r="AJ9" t="inlineStr"/>
       <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="n">
-        <v>-0.7738923958738155</v>
-      </c>
+      <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="n">
-        <v>-0.1264204545454541</v>
-      </c>
-      <c r="AN9" t="inlineStr"/>
+        <v>-0.1244260782463016</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>-0.001203575529094669</v>
+      </c>
       <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="n">
-        <v>-2.389646464646464</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>-2.293734217171703</v>
-      </c>
-      <c r="AR9" t="inlineStr"/>
-      <c r="AS9" t="inlineStr"/>
-      <c r="AT9" t="inlineStr"/>
+        <v>-2.565079365079363</v>
+      </c>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="n">
+        <v>-0.679241369594088</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>2.719895382395379</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1.66488095238094</v>
+      </c>
       <c r="AU9" t="n">
-        <v>28889.87627547048</v>
+        <v>0.9101673604050688</v>
       </c>
       <c r="AV9" t="n">
-        <v>2.617282196969697</v>
+        <v>6486859.668109665</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.853235479797988</v>
+        <v>-0.1516955266955264</v>
       </c>
       <c r="AX9" t="n">
-        <v>-0.01053608843856479</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>0.9283481793833914</v>
-      </c>
+        <v>125028.5977628697</v>
+      </c>
+      <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="n">
-        <v>6646772.411616158</v>
-      </c>
-      <c r="BA9" t="inlineStr"/>
-      <c r="BB9" t="n">
-        <v>-1.038929235968709</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>-0.3447359137036017</v>
-      </c>
+        <v>-2.410732323232367</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>-1.121521367717719</v>
+      </c>
+      <c r="BB9" t="inlineStr"/>
+      <c r="BC9" t="inlineStr"/>
       <c r="BD9" t="inlineStr"/>
       <c r="BE9" t="n">
         <v>0</v>
@@ -1977,48 +1977,62 @@
       <c r="AJ10" t="inlineStr"/>
       <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="n">
-        <v>1.254099769484451</v>
+        <v>30</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.6195075757575756</v>
-      </c>
-      <c r="AN10" t="inlineStr"/>
-      <c r="AO10" t="inlineStr"/>
+        <v>6.540874217726753</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0.4538847766413965</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
       <c r="AP10" t="n">
-        <v>1.125946969696972</v>
+        <v>1.14502164502165</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-0.1720075757575614</v>
-      </c>
-      <c r="AR10" t="inlineStr"/>
-      <c r="AS10" t="inlineStr"/>
-      <c r="AT10" t="inlineStr"/>
+        <v>22725000</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1.179923686484511</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>5.018095238095242</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>5.798614718614715</v>
+      </c>
       <c r="AU10" t="n">
-        <v>3742126.338364293</v>
+        <v>4.581510207439194</v>
       </c>
       <c r="AV10" t="n">
-        <v>5.044520202020209</v>
+        <v>6127317.46031746</v>
       </c>
       <c r="AW10" t="n">
-        <v>5.790669191919179</v>
+        <v>0.6170995670995669</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.463121401783444</v>
+        <v>3598837.638564198</v>
       </c>
       <c r="AY10" t="n">
-        <v>4.587136981413451</v>
+        <v>-1</v>
       </c>
       <c r="AZ10" t="n">
-        <v>6115112.373737373</v>
-      </c>
-      <c r="BA10" t="inlineStr"/>
+        <v>-0.3444011544011119</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>-1.113201736072</v>
+      </c>
       <c r="BB10" t="n">
-        <v>-1.414131621279296</v>
+        <v>-11</v>
       </c>
       <c r="BC10" t="n">
-        <v>6.641650671996487</v>
-      </c>
-      <c r="BD10" t="inlineStr"/>
+        <v>25</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0.6666666666666667</v>
+      </c>
       <c r="BE10" t="n">
         <v>0</v>
       </c>

--- a/data/germany/p6_deployment/data_preparation/df_constructed.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_constructed.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE10"/>
+  <dimension ref="A1:BE16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -525,84 +525,84 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_goals</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals_against</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_ball_possession</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_ball_possession_against</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days_against</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points_against</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts_against</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_fouls</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_fouls_against</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points_against</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals_against</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days_against</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts_against</t>
-        </is>
-      </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
@@ -615,97 +615,97 @@
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
           <t>dif_sum_rat_player_miss</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>dif_n_player_miss</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
         </is>
       </c>
       <c r="BE1" s="1" t="inlineStr">
@@ -717,32 +717,32 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2T6mXfPa</t>
+          <t>x4pn9lxH</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45536.52083333334</v>
+        <v>45549.5625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">welz t 
+          <t xml:space="preserve">siebert d 
   ger </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">allianz arena
-  munich </t>
+          <t xml:space="preserve">holstein stadion
+  kiel </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>nVp0wiqd</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>fiEQZ7C7</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -769,26 +769,22 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>f3ddUIXs</t>
+          <t>KUx4Q7x1</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>GzfvcwRj</t>
+          <t>K6A2elS9</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>30</v>
-      </c>
-      <c r="P2" t="n">
-        <v>4</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
-        <v>20</v>
-      </c>
-      <c r="R2" t="n">
-        <v>2</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
         <v>0</v>
       </c>
@@ -796,10 +792,18 @@
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
+      <c r="X2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1</v>
+      </c>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr"/>
@@ -808,47 +812,51 @@
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="n">
-        <v>5.096331319262319</v>
-      </c>
+      <c r="AJ2" t="n">
+        <v>75.85714285714286</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>-11.80158636941357</v>
+      </c>
+      <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="n">
-        <v>0.8184757146045434</v>
-      </c>
-      <c r="AO2" t="inlineStr"/>
+        <v>-12.11989738656405</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>-12.10543343968118</v>
+      </c>
       <c r="AP2" t="n">
-        <v>-0.1485569985569981</v>
-      </c>
-      <c r="AQ2" t="inlineStr"/>
+        <v>-13.19512586179253</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>-1.909443642776976</v>
+      </c>
       <c r="AR2" t="n">
-        <v>-0.226684792910298</v>
+        <v>-1.273813838497206</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.383189033189041</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>6.362193362193366</v>
-      </c>
+        <v>-1.734038800705466</v>
+      </c>
+      <c r="AT2" t="inlineStr"/>
       <c r="AU2" t="n">
-        <v>6.727282666065534</v>
+        <v>0.28875554374644</v>
       </c>
       <c r="AV2" t="n">
-        <v>31118852.81385281</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>1.290548340548341</v>
-      </c>
+        <v>3.499445758702478</v>
+      </c>
+      <c r="AW2" t="inlineStr"/>
       <c r="AX2" t="n">
-        <v>23603044.54178003</v>
+        <v>-38228119.28811929</v>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="n">
-        <v>1.232683982683994</v>
+        <v>1.541069424402764</v>
       </c>
       <c r="BA2" t="n">
-        <v>-2.127510312772245</v>
+        <v>-28283278.51125773</v>
       </c>
       <c r="BB2" t="inlineStr"/>
       <c r="BC2" t="inlineStr"/>
@@ -860,32 +868,32 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>W8b4TCOO</t>
+          <t>UwsvBA74</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45536.4375</v>
+        <v>45549.4375</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stegemann s 
+          <t xml:space="preserve">jollenbeck m 
   ger </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">voith arena
-  heidenheim </t>
+          <t xml:space="preserve">borussia park
+  monchengladbach </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>KWixEVWi</t>
+          <t>88HSzjDr</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>fTVNku3I</t>
+          <t>nJQmYp1B</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -912,86 +920,122 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0jdIgO6t</t>
+          <t>M5BRZDsC</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>4fuCGs9P</t>
+          <t>GzfvcwRj</t>
         </is>
       </c>
       <c r="O3" t="n">
+        <v>-10</v>
+      </c>
+      <c r="P3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>-0.6666666666666665</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V3" t="n">
+        <v>-22</v>
+      </c>
+      <c r="W3" t="n">
+        <v>22</v>
+      </c>
+      <c r="X3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.295</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>14.33333333333333</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>6.333333333333334</v>
+      </c>
+      <c r="AH3" t="n">
         <v>-3</v>
       </c>
-      <c r="P3" t="n">
-        <v>-3</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>-1</v>
-      </c>
-      <c r="R3" t="n">
-        <v>-1</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
-      <c r="AM3" t="n">
-        <v>-1.859359751177195</v>
-      </c>
+      <c r="AI3" t="n">
+        <v>-2.666666666666666</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1.458458445544508</v>
+      </c>
+      <c r="AM3" t="inlineStr"/>
       <c r="AN3" t="n">
-        <v>-0.1696718121060228</v>
-      </c>
-      <c r="AO3" t="inlineStr"/>
+        <v>-0.8270514670514615</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>2.576866467410767</v>
+      </c>
       <c r="AP3" t="n">
-        <v>0.5012152777777743</v>
-      </c>
-      <c r="AQ3" t="inlineStr"/>
+        <v>-0.4858393458393664</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0.06186628186628207</v>
+      </c>
       <c r="AR3" t="n">
-        <v>3.030508325738584</v>
+        <v>0.02440794014020531</v>
       </c>
       <c r="AS3" t="n">
-        <v>-2.130271464646469</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>-1.460763888888891</v>
-      </c>
+        <v>1.002881192881201</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
       <c r="AU3" t="n">
-        <v>-5.383947795625431</v>
+        <v>-1.112301271640106</v>
       </c>
       <c r="AV3" t="n">
-        <v>-2087713.068181818</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>-0.3962436868686867</v>
-      </c>
+        <v>1.305944623463404</v>
+      </c>
+      <c r="AW3" t="inlineStr"/>
       <c r="AX3" t="n">
-        <v>-1996585.913173085</v>
+        <v>-2874699.855699852</v>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="n">
-        <v>1.164630681818153</v>
+        <v>-0.2846079846079874</v>
       </c>
       <c r="BA3" t="n">
-        <v>-0.6915450320877881</v>
+        <v>819042.2811255194</v>
       </c>
       <c r="BB3" t="inlineStr"/>
       <c r="BC3" t="inlineStr"/>
@@ -1003,32 +1047,32 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>AVR8vwXP</t>
+          <t>r7j4bXNb</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45535.5625</v>
+        <v>45549.4375</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">brand b 
+          <t xml:space="preserve">welz t 
   ger </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">bayarena
-  leverkusen </t>
+          <t xml:space="preserve">prezero arena
+  sinsheim </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>4jcj2zMd</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>KbS1suSm</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1055,112 +1099,122 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>M5BRZDsC</t>
+          <t>KUx4Q7x1</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>8f6APkLc</t>
+          <t>hAcTWKKN</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>-2</v>
+        <v>-12</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1</v>
+        <v>-6</v>
       </c>
       <c r="R4" t="n">
+        <v>-3</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
         <v>1</v>
       </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>-21</v>
-      </c>
       <c r="U4" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="V4" t="n">
-        <v>1</v>
+        <v>-10.5</v>
       </c>
       <c r="W4" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
         <v>-1</v>
       </c>
       <c r="AC4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
+        <v>-0.08000000000000007</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>2</v>
+      </c>
       <c r="AH4" t="n">
-        <v>-2</v>
+        <v>2.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="AJ4" t="n">
-        <v>75.09999999999999</v>
-      </c>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="n">
-        <v>2.114992897242516</v>
-      </c>
+        <v>68.55555555555556</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>76.45454545454545</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>-7.60610961776014</v>
+      </c>
+      <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="n">
-        <v>0.02214647089452959</v>
-      </c>
-      <c r="AO4" t="inlineStr"/>
+        <v>-5.625617784992784</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>-6.476403690593486</v>
+      </c>
       <c r="AP4" t="n">
-        <v>0.8429924242424249</v>
-      </c>
-      <c r="AQ4" t="inlineStr"/>
+        <v>-6.107611832611838</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>-0.2333040223665224</v>
+      </c>
       <c r="AR4" t="n">
-        <v>-1.693165142311102</v>
+        <v>-0.3968940738350679</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.3559929653679603</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>1.064393939393938</v>
-      </c>
+        <v>1.127353896103894</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
       <c r="AU4" t="n">
-        <v>2.84461743559666</v>
+        <v>1.043426066078606</v>
       </c>
       <c r="AV4" t="n">
-        <v>4426932.269119769</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>-0.03062094155844131</v>
-      </c>
+        <v>3.626985029848555</v>
+      </c>
+      <c r="AW4" t="inlineStr"/>
       <c r="AX4" t="n">
-        <v>16829768.68946056</v>
+        <v>-24439114.80880231</v>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="n">
-        <v>2.156631042568534</v>
+        <v>0.7724454365079509</v>
       </c>
       <c r="BA4" t="n">
-        <v>-2.964555189569751</v>
+        <v>-30668135.40699548</v>
       </c>
       <c r="BB4" t="inlineStr"/>
       <c r="BC4" t="inlineStr"/>
@@ -1172,32 +1226,32 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>U3QUqY85</t>
+          <t>tI0qkTpo</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45535.4375</v>
+        <v>45549.4375</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">schroder r 
+          <t xml:space="preserve">zwayer f 
   ger </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">vonovia ruhrstadion
-  bochum </t>
+          <t xml:space="preserve">volkswagen arena
+  wolfsburg </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>8Y2m6ADe</t>
+          <t>nwkTahLL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>88HSzjDr</t>
+          <t>8vndvXTk</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1224,86 +1278,122 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>pfoInmcq</t>
+          <t>f3ddUIXs</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>hAcTWKKN</t>
+          <t>UgdQz0fK</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="P5" t="n">
-        <v>-4</v>
+        <v>3</v>
       </c>
       <c r="Q5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R5" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="n">
-        <v>-2.401616347619253</v>
-      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V5" t="n">
+        <v>-10</v>
+      </c>
+      <c r="W5" t="n">
+        <v>10</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>83</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>74.7625</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>2.051179243280416</v>
+      </c>
+      <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="n">
-        <v>-0.2094089894623838</v>
-      </c>
-      <c r="AO5" t="inlineStr"/>
+        <v>-1.623412698412693</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>-0.3849087062187806</v>
+      </c>
       <c r="AP5" t="n">
-        <v>2.503358986692316</v>
-      </c>
-      <c r="AQ5" t="inlineStr"/>
+        <v>-0.9736111111110972</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>-0.08432539682539719</v>
+      </c>
       <c r="AR5" t="n">
-        <v>3.538782753121588</v>
+        <v>-0.1320036928855173</v>
       </c>
       <c r="AS5" t="n">
-        <v>-3.179174683341358</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>-2.210207231040556</v>
-      </c>
+        <v>1.003968253968253</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
       <c r="AU5" t="n">
-        <v>-5.050709995587823</v>
+        <v>0.7194099732674424</v>
       </c>
       <c r="AV5" t="n">
-        <v>-4924003.07639891</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>-0.2849527016193685</v>
-      </c>
+        <v>-0.3161953856503033</v>
+      </c>
+      <c r="AW5" t="inlineStr"/>
       <c r="AX5" t="n">
-        <v>-4269502.420584014</v>
+        <v>-4319126.984126983</v>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="n">
-        <v>-2.266808962642301</v>
+        <v>3.099206349206412</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0.9395091617304843</v>
+        <v>2644260.788281403</v>
       </c>
       <c r="BB5" t="inlineStr"/>
       <c r="BC5" t="inlineStr"/>
@@ -1315,32 +1405,32 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>0OYDmG9t</t>
+          <t>WSMotj8U</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45535.4375</v>
+        <v>45549.4375</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">zwayer f 
+          <t xml:space="preserve">dankert b 
   ger </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">weserstadion
-  bremen </t>
+          <t xml:space="preserve">red bull arena
+  leipzig </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ig1f1fy3</t>
+          <t>KbS1suSm</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>nP1i5US1</t>
+          <t>pzHW4oaE</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1367,86 +1457,122 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2VSFgl3c</t>
+          <t>pfoInmcq</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>UgdQz0fK</t>
+          <t>0jdIgO6t</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>-19</v>
+        <v>2</v>
       </c>
       <c r="P6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>4</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="V6" t="n">
+        <v>5</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-5</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.3699999999999999</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-0.04000000000000004</v>
+      </c>
+      <c r="AD6" t="n">
         <v>-3</v>
       </c>
-      <c r="Q6" t="n">
-        <v>-3</v>
-      </c>
-      <c r="R6" t="n">
-        <v>-3</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr"/>
-      <c r="AM6" t="n">
-        <v>-8.842138476290586</v>
-      </c>
+      <c r="AE6" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>71.375</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>3.466652554702563</v>
+      </c>
+      <c r="AM6" t="inlineStr"/>
       <c r="AN6" t="n">
-        <v>-0.8118956106470048</v>
-      </c>
-      <c r="AO6" t="inlineStr"/>
+        <v>5.671332371332369</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>5.372542276684968</v>
+      </c>
       <c r="AP6" t="n">
-        <v>0.7623376623376608</v>
-      </c>
-      <c r="AQ6" t="inlineStr"/>
+        <v>4.470976430976435</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0.4686291486291487</v>
+      </c>
       <c r="AR6" t="n">
-        <v>0.03779609669954453</v>
+        <v>0.2995150634722392</v>
       </c>
       <c r="AS6" t="n">
-        <v>-7.200649350649343</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>-6.798051948051963</v>
-      </c>
+        <v>-2.152121212121216</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
       <c r="AU6" t="n">
-        <v>-7.958301360208452</v>
+        <v>-1.761292499377657</v>
       </c>
       <c r="AV6" t="n">
-        <v>-25500324.67532468</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>-1.15</v>
-      </c>
+        <v>0.5985209513405039</v>
+      </c>
+      <c r="AW6" t="inlineStr"/>
       <c r="AX6" t="n">
-        <v>-17834328.81686237</v>
+        <v>20578981.24098124</v>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="n">
-        <v>-1.616233766233762</v>
+        <v>-2.168898508898508</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.7606889151541623</v>
+        <v>13508688.70672328</v>
       </c>
       <c r="BB6" t="inlineStr"/>
       <c r="BC6" t="inlineStr"/>
@@ -1458,32 +1584,32 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>QVJwrCwI</t>
+          <t>vZqDdBhB</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45535.4375</v>
+        <v>45549.4375</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">siebert d 
+          <t xml:space="preserve">brand b 
   ger </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">holstein stadion
-  kiel </t>
+          <t xml:space="preserve">europa park stadion
+  freiburg </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>63WsD2ei</t>
+          <t>fiEQZ7C7</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>nwkTahLL</t>
+          <t>8Y2m6ADe</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1510,82 +1636,122 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>KUx4Q7x1</t>
+          <t>YZPE6Sx7</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>K6A2elS9</t>
+          <t>8f6APkLc</t>
         </is>
       </c>
       <c r="O7" t="n">
+        <v>5</v>
+      </c>
+      <c r="P7" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" t="n">
+        <v>3</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>-17</v>
+      </c>
+      <c r="W7" t="n">
+        <v>17</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-0.9299999999999999</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>-11.5</v>
+      </c>
+      <c r="AI7" t="n">
         <v>-2</v>
       </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr"/>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="inlineStr"/>
-      <c r="AJ7" t="inlineStr"/>
-      <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="inlineStr"/>
-      <c r="AM7" t="n">
-        <v>-6.868331608005505</v>
-      </c>
+      <c r="AJ7" t="n">
+        <v>75.33333333333333</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>79.72727272727273</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>3.233812434636846</v>
+      </c>
+      <c r="AM7" t="inlineStr"/>
       <c r="AN7" t="n">
-        <v>-0.2427632083429183</v>
-      </c>
-      <c r="AO7" t="inlineStr"/>
+        <v>2.320853625541119</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>2.88217070171369</v>
+      </c>
       <c r="AP7" t="n">
-        <v>0.08010261343595104</v>
-      </c>
-      <c r="AQ7" t="inlineStr"/>
+        <v>2.43612238455988</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0.481430375180375</v>
+      </c>
       <c r="AR7" t="n">
-        <v>0.7218292308871987</v>
+        <v>0.4056907440703208</v>
       </c>
       <c r="AS7" t="n">
-        <v>-7.179222783389449</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>-7.305515472182151</v>
-      </c>
+        <v>-0.6785714285714235</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
       <c r="AU7" t="n">
-        <v>-7.119085959665654</v>
+        <v>-1.366478364324372</v>
       </c>
       <c r="AV7" t="n">
-        <v>-9326396.705146704</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>-0.4939133397466731</v>
-      </c>
+        <v>1.609606506296103</v>
+      </c>
+      <c r="AW7" t="inlineStr"/>
       <c r="AX7" t="n">
-        <v>-6882742.336668966</v>
+        <v>5393170.488365799</v>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="n">
-        <v>-0.1199875741542655</v>
+        <v>0.9244385822510992</v>
       </c>
       <c r="BA7" t="n">
-        <v>2.078473659995439</v>
+        <v>3767177.153312373</v>
       </c>
       <c r="BB7" t="inlineStr"/>
       <c r="BC7" t="inlineStr"/>
@@ -1597,32 +1763,32 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>61DvZGfm</t>
+          <t>zsmd0ggn</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45535.4375</v>
+        <v>45548.64583333334</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">osmers h 
+          <t xml:space="preserve">jablonski s 
   ger </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">mhparena
-  stuttgart </t>
+          <t xml:space="preserve">signal iduna park
+  dortmund </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>nJQmYp1B</t>
+          <t>nP1i5US1</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>EuakNmc1</t>
+          <t>KWixEVWi</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1649,86 +1815,122 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>YZPE6Sx7</t>
+          <t>IkCftsQm</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>hpYJ6izc</t>
+          <t>4ljanukM</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr"/>
-      <c r="AE8" t="inlineStr"/>
-      <c r="AF8" t="inlineStr"/>
-      <c r="AG8" t="inlineStr"/>
-      <c r="AH8" t="inlineStr"/>
-      <c r="AI8" t="inlineStr"/>
-      <c r="AJ8" t="inlineStr"/>
-      <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="inlineStr"/>
-      <c r="AM8" t="n">
-        <v>-1.307164115646273</v>
-      </c>
+      <c r="T8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-0.04000000000000004</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-0.4000000000000001</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>77.375</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>70</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>8.478476535541745</v>
+      </c>
+      <c r="AM8" t="inlineStr"/>
       <c r="AN8" t="n">
-        <v>-0.250439342403628</v>
-      </c>
-      <c r="AO8" t="inlineStr"/>
+        <v>8.195779220779215</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>11.20090209997042</v>
+      </c>
       <c r="AP8" t="n">
-        <v>-1.363663419913419</v>
-      </c>
-      <c r="AQ8" t="inlineStr"/>
+        <v>7.306168831168833</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1.331818181818182</v>
+      </c>
       <c r="AR8" t="n">
-        <v>-2.002625425170066</v>
+        <v>0.9623878536922015</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.8020111832611718</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>1.69396645021645</v>
-      </c>
+        <v>-0.4368506493506459</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
       <c r="AU8" t="n">
-        <v>-0.7108134920635081</v>
+        <v>-2.093432662920236</v>
       </c>
       <c r="AV8" t="n">
-        <v>5092120.310245306</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>-0.0670364357864357</v>
-      </c>
+        <v>0.4980651680963035</v>
+      </c>
+      <c r="AW8" t="inlineStr"/>
       <c r="AX8" t="n">
-        <v>1021023.419784582</v>
+        <v>26252353.8961039</v>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="n">
-        <v>1.622375541125479</v>
+        <v>-2.072889610389609</v>
       </c>
       <c r="BA8" t="n">
-        <v>-2.424581916099783</v>
+        <v>18559583.57980874</v>
       </c>
       <c r="BB8" t="inlineStr"/>
       <c r="BC8" t="inlineStr"/>
@@ -1740,32 +1942,32 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>AgAeVYgC</t>
+          <t>2T6mXfPa</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45535.4375</v>
+        <v>45536.52083333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">stieler t 
+          <t xml:space="preserve">welz t 
   ger </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">deutsche bank park
-  frankfurt </t>
+          <t xml:space="preserve">allianz arena
+  munich </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>8vndvXTk</t>
+          <t>nVp0wiqd</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>hQAtP9Sl</t>
+          <t>fiEQZ7C7</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1792,25 +1994,25 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>IkCftsQm</t>
+          <t>f3ddUIXs</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>A15eUM4C</t>
+          <t>GzfvcwRj</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="P9" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>20</v>
+      </c>
+      <c r="R9" t="n">
         <v>2</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>4</v>
-      </c>
-      <c r="R9" t="n">
-        <v>3</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1833,49 +2035,63 @@
       <c r="AI9" t="inlineStr"/>
       <c r="AJ9" t="inlineStr"/>
       <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="inlineStr"/>
+      <c r="AL9" t="n">
+        <v>5.096331319262319</v>
+      </c>
       <c r="AM9" t="n">
-        <v>-0.1244260782463016</v>
+        <v>-1.738095238095241</v>
       </c>
       <c r="AN9" t="n">
-        <v>-0.001203575529094669</v>
-      </c>
-      <c r="AO9" t="inlineStr"/>
+        <v>7.383189033189041</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>6.727282666065534</v>
+      </c>
       <c r="AP9" t="n">
-        <v>-2.565079365079363</v>
-      </c>
-      <c r="AQ9" t="inlineStr"/>
+        <v>6.362193362193366</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1.290548340548341</v>
+      </c>
       <c r="AR9" t="n">
-        <v>-0.679241369594088</v>
+        <v>0.8184757146045434</v>
       </c>
       <c r="AS9" t="n">
-        <v>2.719895382395379</v>
+        <v>-0.1485569985569981</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.66488095238094</v>
+        <v>-2.880952380952383</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.9101673604050688</v>
+        <v>-0.226684792910298</v>
       </c>
       <c r="AV9" t="n">
-        <v>6486859.668109665</v>
+        <v>-2.127510312772245</v>
       </c>
       <c r="AW9" t="n">
-        <v>-0.1516955266955264</v>
+        <v>-43</v>
       </c>
       <c r="AX9" t="n">
-        <v>125028.5977628697</v>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+        <v>31118852.81385281</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>-70</v>
+      </c>
       <c r="AZ9" t="n">
-        <v>-2.410732323232367</v>
+        <v>1.232683982683994</v>
       </c>
       <c r="BA9" t="n">
-        <v>-1.121521367717719</v>
-      </c>
-      <c r="BB9" t="inlineStr"/>
-      <c r="BC9" t="inlineStr"/>
-      <c r="BD9" t="inlineStr"/>
+        <v>23603044.54178003</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0.3571428571428572</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>62625000</v>
+      </c>
       <c r="BE9" t="n">
         <v>0</v>
       </c>
@@ -1883,32 +2099,32 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>djSMofvg</t>
+          <t>W8b4TCOO</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45534.64583333334</v>
+        <v>45536.4375</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">jablonski s 
+          <t xml:space="preserve">stegemann s 
   ger </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadion an der alten forsterei
-  berlin </t>
+          <t xml:space="preserve">voith arena
+  heidenheim </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>pzHW4oaE</t>
+          <t>KWixEVWi</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ILyJuN3g</t>
+          <t>fTVNku3I</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1935,25 +2151,25 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>vZA6VYpf</t>
+          <t>0jdIgO6t</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>4ljanukM</t>
+          <t>4fuCGs9P</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>5</v>
+        <v>-3</v>
       </c>
       <c r="P10" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="Q10" t="n">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1977,63 +2193,1021 @@
       <c r="AJ10" t="inlineStr"/>
       <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="n">
-        <v>30</v>
+        <v>-1.921545137193633</v>
       </c>
       <c r="AM10" t="n">
-        <v>6.540874217726753</v>
+        <v>3.5</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.4538847766413965</v>
+        <v>-2.219011544011522</v>
       </c>
       <c r="AO10" t="n">
-        <v>0</v>
+        <v>-5.485823867026866</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.14502164502165</v>
+        <v>-1.440873015873009</v>
       </c>
       <c r="AQ10" t="n">
-        <v>22725000</v>
+        <v>-0.3957070707070705</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.179923686484511</v>
+        <v>-0.1784885644848053</v>
       </c>
       <c r="AS10" t="n">
-        <v>5.018095238095242</v>
+        <v>0.4819083694083659</v>
       </c>
       <c r="AT10" t="n">
-        <v>5.798614718614715</v>
+        <v>-2.75</v>
       </c>
       <c r="AU10" t="n">
-        <v>4.581510207439194</v>
+        <v>3.136031366294525</v>
       </c>
       <c r="AV10" t="n">
-        <v>6127317.46031746</v>
+        <v>-0.742615060378256</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.6170995670995669</v>
+        <v>-225</v>
       </c>
       <c r="AX10" t="n">
-        <v>3598837.638564198</v>
+        <v>-2201866.883116883</v>
       </c>
       <c r="AY10" t="n">
+        <v>-221</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>1.067370129870113</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>-2053591.164735432</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>-3</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>-11700000</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>AVR8vwXP</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45535.5625</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jollenbeck m 
+  ger </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bayarena
+  leverkusen </t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>59</v>
+      </c>
+      <c r="H11" t="n">
+        <v>591</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>WzqXh8OL</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>8f6APkLc</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>-2</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q11" t="n">
         <v>-1</v>
       </c>
-      <c r="AZ10" t="n">
-        <v>-0.3444011544011119</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>-1.113201736072</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>-11</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>25</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>0.6666666666666667</v>
-      </c>
-      <c r="BE10" t="n">
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
+      </c>
+      <c r="V11" t="n">
+        <v>-21</v>
+      </c>
+      <c r="W11" t="n">
+        <v>21</v>
+      </c>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="n">
+        <v>2.252470252314978</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>-8.75</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0.3559929653679603</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>2.854183983312581</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.064393939393938</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>-0.03062094155844131</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0.05268512492663002</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0.8429924242424249</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>-1.605650426279766</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>-3.19088316435321</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>-248</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>4426932.269119769</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>-216</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>2.156631042568534</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>17767253.22580639</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>-3</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>-26900000</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>61DvZGfm</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45535.4375</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gerach t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mhparena
+  stuttgart </t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>59</v>
+      </c>
+      <c r="H12" t="n">
+        <v>591</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>pdPRS0me</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>hpYJ6izc</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>5</v>
+      </c>
+      <c r="P12" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>7</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr"/>
+      <c r="AK12" t="inlineStr"/>
+      <c r="AL12" t="n">
+        <v>-1.088582766439927</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0.6186820586820545</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>-0.5349206349206383</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.335334295334306</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>-0.1085473785473785</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>-0.2499433106575961</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>-1.415435305435306</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>-2.399999999999999</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>-1.99900604686319</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>-2.682091836734685</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>313</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>4594295.815295811</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>276</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1.985401635401615</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>1379294.170445956</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>20625000</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>AgAeVYgC</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45535.4375</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">badstubner f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">deutsche bank park
+  frankfurt </t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>59</v>
+      </c>
+      <c r="H13" t="n">
+        <v>591</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>IkCftsQm</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>A15eUM4C</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>3</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4</v>
+      </c>
+      <c r="R13" t="n">
+        <v>3</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr"/>
+      <c r="AL13" t="n">
+        <v>-0.1244260782463016</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>-1.400000000000006</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>2.719895382395379</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0.9101673604050688</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.66488095238094</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>-0.1516955266955264</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>-0.001203575529094669</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>-2.565079365079363</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>-0.6792413695940844</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>-1.121521367717719</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>-240</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>6486859.668109665</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>-241</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>-2.410732323232367</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>125028.5977628697</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>-0.3999999999999999</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>-3</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>-24025000</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>U3QUqY85</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45535.4375</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">storks s 
+  ger </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vonovia ruhrstadion
+  bochum </t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>59</v>
+      </c>
+      <c r="H14" t="n">
+        <v>591</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>pfoInmcq</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>hAcTWKKN</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>7</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>7</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr"/>
+      <c r="AJ14" t="inlineStr"/>
+      <c r="AK14" t="inlineStr"/>
+      <c r="AL14" t="n">
+        <v>-2.471722524301995</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>7.333333333333314</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>-3.2385303932179</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>-4.939896440750744</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>-2.302356150793642</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>-0.2973755411255412</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>-0.2044975436780356</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>2.441630591630584</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>3.386011085879812</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>-1.072981169662597</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>-4968827.054022366</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>-2.057916215728739</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>-4261771.50993374</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>1925000</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>0OYDmG9t</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45535.4375</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hartmann r 
+  ger </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">weserstadion
+  bremen </t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>59</v>
+      </c>
+      <c r="H15" t="n">
+        <v>591</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2VSFgl3c</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>UgdQz0fK</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>-19</v>
+      </c>
+      <c r="P15" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>-3</v>
+      </c>
+      <c r="R15" t="n">
+        <v>-3</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr"/>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="inlineStr"/>
+      <c r="AL15" t="n">
+        <v>-8.8421384762906</v>
+      </c>
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="n">
+        <v>-7.200649350649343</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>-7.958301360208452</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>-6.798051948051963</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>-1.15</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>-0.8118956106470048</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0.7623376623376608</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AU15" t="n">
+        <v>0.03779609669954453</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0.7606889151541338</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>154</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>-25500324.67532468</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>150</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>-1.616233766233762</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>-17834328.81686237</v>
+      </c>
+      <c r="BB15" t="inlineStr"/>
+      <c r="BC15" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>13000000</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>QVJwrCwI</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45535.4375</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">exner f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">holstein stadion
+  kiel </t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>59</v>
+      </c>
+      <c r="H16" t="n">
+        <v>591</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>KUx4Q7x1</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>K6A2elS9</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>-2</v>
+      </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr"/>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr"/>
+      <c r="AJ16" t="inlineStr"/>
+      <c r="AK16" t="inlineStr"/>
+      <c r="AL16" t="n">
+        <v>-6.868331608005505</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0.8333333333333428</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>-7.179222783389449</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>-7.119085959665654</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>-7.305515472182151</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>-0.4939133397466731</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>-0.2427632083429183</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0.08010261343595104</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>1.666666666666668</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0.7218292308871987</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>2.078473659995439</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>-94</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>-9326396.705146704</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>-86</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>-0.1199875741542655</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>-6882742.336668966</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>-28200000</v>
+      </c>
+      <c r="BE16" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_preparation/df_constructed.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_constructed.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE3"/>
+  <dimension ref="A1:BE10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -525,84 +525,84 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_expected_goals_(xg)</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_goal_attempts</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts_against</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_ball_possession</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_ball_possession_against</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls_against</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals_against</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points_against</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_n_matches_last_days</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_n_matches_last_days_against</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points_against</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls_against</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals_against</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
-        </is>
-      </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
@@ -615,97 +615,97 @@
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_pot_player_sub</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_sub</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_rat_player_start</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_val_player_start</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_start</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_pot_player_start</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
         </is>
       </c>
       <c r="BE1" s="1" t="inlineStr">
@@ -717,32 +717,32 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2T6mXfPa</t>
+          <t>8OhVCWxh</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45536.52083333334</v>
+        <v>45550.52083333334</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">welz t 
+          <t xml:space="preserve">hartmann r 
   ger </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">allianz arena
-  munich </t>
+          <t xml:space="preserve">mewa arena
+  mainz </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>nVp0wiqd</t>
+          <t>EuakNmc1</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>fiEQZ7C7</t>
+          <t>Ig1f1fy3</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -769,103 +769,125 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>f3ddUIXs</t>
+          <t>GzfvcwRj</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>GzfvcwRj</t>
+          <t>IkCftsQm</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>30</v>
+        <v>-5</v>
       </c>
       <c r="P2" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="Q2" t="n">
-        <v>20</v>
+        <v>-6</v>
       </c>
       <c r="R2" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
+      <c r="T2" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="U2" t="n">
+        <v>-0.1000000000000001</v>
+      </c>
+      <c r="V2" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>73.5</v>
+      </c>
       <c r="AL2" t="n">
-        <v>6.727282666065534</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>-0.226684792910298</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>6.362193362193366</v>
-      </c>
+        <v>0.2042483660130714</v>
+      </c>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="n">
-        <v>-218</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>31118852.81385281</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>-2.944444444444446</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>51425000</v>
-      </c>
+        <v>0.401010101010101</v>
+      </c>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
       <c r="AS2" t="n">
-        <v>1.290548340548341</v>
+        <v>0.4490196078431268</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.8184757146045434</v>
+        <v>0.8842047930283172</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.232683982683994</v>
+        <v>0.360675381263615</v>
       </c>
       <c r="AV2" t="n">
-        <v>-3</v>
+        <v>86895.42483660067</v>
       </c>
       <c r="AW2" t="n">
-        <v>-0.1485569985569981</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>-197</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>5.096331319262319</v>
-      </c>
+        <v>0.981144781144792</v>
+      </c>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="n">
-        <v>23603044.54178003</v>
+        <v>-0.5929292929292842</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.2777777777777777</v>
+        <v>763468.0134680141</v>
       </c>
       <c r="BB2" t="n">
-        <v>7.383189033189041</v>
+        <v>1.111784511784514</v>
       </c>
       <c r="BC2" t="n">
-        <v>-2.127510312772245</v>
+        <v>0.1161616161616337</v>
       </c>
       <c r="BD2" t="n">
-        <v>-1.5</v>
+        <v>-0.7793028322440136</v>
       </c>
       <c r="BE2" t="n">
         <v>0</v>
@@ -874,32 +896,32 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>W8b4TCOO</t>
+          <t>CnrLfkNN</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45536.4375</v>
+        <v>45550.4375</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stegemann s 
+          <t xml:space="preserve">dankert b 
   ger </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">voith arena
-  heidenheim </t>
+          <t xml:space="preserve">wwk arena
+  augsburg </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>KWixEVWi</t>
+          <t>fTVNku3I</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>fTVNku3I</t>
+          <t>ILyJuN3g</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -926,105 +948,1372 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>4ljanukM</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
           <t>0jdIgO6t</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="n">
+        <v>3</v>
+      </c>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.6200000000000001</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="V3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>-16.5</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>73.27272727272727</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>75</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.415674603174603</v>
+      </c>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="n">
+        <v>3.210341007748141</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>3.014931118646288</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>-0.5550610595115195</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>2372027.008902976</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>3.467592592592595</v>
+      </c>
+      <c r="AX3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="n">
+        <v>-0.5879629629629903</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>2684074.074074074</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>-0.7472222222222236</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>3.215740740740742</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>-1.040997100594637</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>x4pn9lxH</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45549.5625</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dingert c 
+  ger </t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">holstein stadion
+  kiel </t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>59</v>
+      </c>
+      <c r="H4" t="n">
+        <v>591</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>A15eUM4C</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>YZPE6Sx7</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-1.79</v>
+      </c>
+      <c r="U4" t="n">
+        <v>-0.96</v>
+      </c>
+      <c r="V4" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>-16.5</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>-1.995697167755991</v>
+      </c>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="n">
+        <v>-1.801683501683501</v>
+      </c>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="n">
+        <v>-12.17039760348582</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>-14.50577342047929</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>-1.991693899782138</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>-39913401.416122</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>-13.69023569023571</v>
+      </c>
+      <c r="AX4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="n">
+        <v>2.047811447811483</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>-45693333.33333334</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>-0.120875420875425</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>-14.22727272727273</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>1.103404139433593</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>UwsvBA74</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45549.4375</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gerach t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">borussia park
+  monchengladbach </t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>59</v>
+      </c>
+      <c r="H5" t="n">
+        <v>591</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>8f6APkLc</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>vZA6VYpf</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>-10</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.295</v>
+      </c>
+      <c r="V5" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="W5" t="n">
+        <v>6.333333333333334</v>
+      </c>
+      <c r="X5" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>14.33333333333333</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>-22</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-2.666666666666666</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>-0.6666666666666665</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.06118775548123345</v>
+      </c>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="n">
+        <v>0.3421717171717167</v>
+      </c>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="n">
+        <v>-0.4701551467855722</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>1.18559550353028</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1.114078177257522</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>-855916.132478633</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1.7391414141414</v>
+      </c>
+      <c r="AX5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="n">
+        <v>-1.639898989898967</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>877575.7575757559</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>1.313131313131311</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0.445959595959593</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>0.3242811687105132</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>tI0qkTpo</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45549.4375</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">badstubner f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">volkswagen arena
+  wolfsburg </t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>59</v>
+      </c>
+      <c r="H6" t="n">
+        <v>591</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>A15eUM4C</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>KUx4Q7x1</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>15</v>
+      </c>
+      <c r="P6" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>9</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-10</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>83</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>74.7625</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.03896863370547532</v>
+      </c>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="n">
+        <v>-0.08333333333333326</v>
+      </c>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="n">
+        <v>-2.333825093035614</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>3.109908293460933</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>3.905429292929288</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>2106051.967038808</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>-1.421296296296291</v>
+      </c>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="n">
+        <v>0.3101851851852189</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>-3455555.555555554</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0.02777777777778212</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>-1.773148148148152</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0.267490696438017</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>r7j4bXNb</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45549.4375</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jollenbeck m 
+  ger </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prezero arena
+  sinsheim </t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>59</v>
+      </c>
+      <c r="H7" t="n">
+        <v>591</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>UgdQz0fK</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>pfoInmcq</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>-12</v>
+      </c>
+      <c r="P7" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-6</v>
+      </c>
+      <c r="R7" t="n">
+        <v>-3</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>-0.08000000000000007</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>2</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>68.55555555555556</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>76.45454545454545</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>-0.3357663578251817</v>
+      </c>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="n">
+        <v>-0.3490740740740739</v>
+      </c>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="n">
+        <v>-5.050016160310264</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>-6.727680815916116</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0.2841521223874182</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>-28302889.47844095</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>-7.492592592592601</v>
+      </c>
+      <c r="AX7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="n">
+        <v>2.07129629629631</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>-32011851.85185185</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>1.880555555555553</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>-7.412037037037038</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>4.244194258900166</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>WSMotj8U</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45549.4375</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dankert b 
+  ger </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">red bull arena
+  leipzig </t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>59</v>
+      </c>
+      <c r="H8" t="n">
+        <v>591</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>hAcTWKKN</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0jdIgO6t</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>2</v>
+      </c>
+      <c r="P8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>4</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.3699999999999999</v>
+      </c>
+      <c r="U8" t="n">
+        <v>-0.04000000000000004</v>
+      </c>
+      <c r="V8" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>71.375</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.5111606589867461</v>
+      </c>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="n">
+        <v>0.4383838383838381</v>
+      </c>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="n">
+        <v>5.820813646900618</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>5.914375077418541</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>-1.042242218329179</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>18320896.06448302</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>3.945791245791241</v>
+      </c>
+      <c r="AX8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="n">
+        <v>-2.86397306397302</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>18284949.49494949</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>-1.790909090909093</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>5.516835016835017</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>0.8992833253703054</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>vZqDdBhB</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45549.4375</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">storks s 
+  ger </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">europa park stadion
+  freiburg </t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>59</v>
+      </c>
+      <c r="H9" t="n">
+        <v>591</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>K6A2elS9</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>M5BRZDsC</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>5</v>
+      </c>
+      <c r="P9" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3</v>
+      </c>
+      <c r="R9" t="n">
+        <v>3</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="U9" t="n">
+        <v>-0.9299999999999999</v>
+      </c>
+      <c r="V9" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="W9" t="n">
+        <v>-3</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>-17</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>17</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>-11.5</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>75.33333333333333</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>79.72727272727273</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.6632160110420982</v>
+      </c>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="n">
+        <v>0.7259259259259261</v>
+      </c>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="n">
+        <v>0.8785800552104917</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>7.859937888198743</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>3.570031055900618</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>6485566.123188406</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>3.905092592592595</v>
+      </c>
+      <c r="AX9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="n">
+        <v>0.4930555555554861</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>7433854.166666666</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>-1.314814814814813</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>3.955092592592578</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>-1.983109040717721</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>zsmd0ggn</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45548.64583333334</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">petersen m 
+  ger </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">signal iduna park
+  dortmund </t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>59</v>
+      </c>
+      <c r="H10" t="n">
+        <v>591</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
         <is>
           <t>4fuCGs9P</t>
         </is>
       </c>
-      <c r="O3" t="n">
-        <v>-3</v>
-      </c>
-      <c r="P3" t="n">
-        <v>-3</v>
-      </c>
-      <c r="Q3" t="n">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2VSFgl3c</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-0.04000000000000004</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-0.4000000000000001</v>
+      </c>
+      <c r="V10" t="n">
         <v>-1</v>
       </c>
-      <c r="R3" t="n">
+      <c r="W10" t="n">
+        <v>1</v>
+      </c>
+      <c r="X10" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="AD10" t="n">
         <v>-1</v>
       </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="n">
-        <v>-5.485823867026866</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>3.136031366294525</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>-1.440873015873009</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>-148</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>-2201866.883116883</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>-2.666666666666668</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>-8300000</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>-0.3957070707070705</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>-0.1784885644848053</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>1.067370129870113</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0.4819083694083659</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>-150</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>-1.921545137193633</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>-2053591.164735432</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>-2.219011544011522</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>-0.7426150603781991</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>3</v>
-      </c>
-      <c r="BE3" t="n">
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>77.375</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>70</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0.6715665976535539</v>
+      </c>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="n">
+        <v>11.20235794801012</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>7.701805843110193</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>-2.336746606855304</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>20967249.82746721</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>9.050000000000011</v>
+      </c>
+      <c r="AX10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="n">
+        <v>-2.106481481481524</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>32107870.37037037</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>-1.041666666666664</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>9.709259259259255</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>-1.481449850471563</v>
+      </c>
+      <c r="BE10" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_preparation/df_constructed.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_constructed.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE10"/>
+  <dimension ref="A1:BE19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -525,84 +525,84 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_expected_goals_(xg)</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_expected_goals_(xg)_against</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
-        </is>
-      </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_n_matches_last_days</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days_against</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points_against</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_goal_attempts</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts_against</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals_against</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls_against</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_ball_possession</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_ball_possession_against</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls_against</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals_against</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points_against</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days_against</t>
-        </is>
-      </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
@@ -615,97 +615,97 @@
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_int_rep_player_sub</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_miss</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>dif_n_player_miss</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_pot_player_sub</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
         </is>
       </c>
       <c r="BE1" s="1" t="inlineStr">
@@ -717,32 +717,32 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>8OhVCWxh</t>
+          <t>dQ0zIIKl</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45550.52083333334</v>
+        <v>45557.60416666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">hartmann r 
+          <t xml:space="preserve">jollenbeck m 
   ger </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mewa arena
-  mainz </t>
+          <t xml:space="preserve">millerntor stadion
+  hamburg </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>EuakNmc1</t>
+          <t>ILyJuN3g</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ig1f1fy3</t>
+          <t>KbS1suSm</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -769,126 +769,122 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>GzfvcwRj</t>
+          <t>hpYJ6izc</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>IkCftsQm</t>
+          <t>pfoInmcq</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>-5</v>
-      </c>
-      <c r="P2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="n">
+        <v>2</v>
+      </c>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="U2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.2000000000000002</v>
+      </c>
+      <c r="W2" t="n">
+        <v>-1.48</v>
+      </c>
+      <c r="X2" t="n">
         <v>-1</v>
       </c>
-      <c r="Q2" t="n">
-        <v>-6</v>
-      </c>
-      <c r="R2" t="n">
+      <c r="Y2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB2" t="n">
         <v>-1</v>
       </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>-0.53</v>
-      </c>
-      <c r="U2" t="n">
-        <v>-0.1000000000000001</v>
-      </c>
-      <c r="V2" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>-0.5</v>
-      </c>
       <c r="AC2" t="n">
-        <v>3</v>
+        <v>-11</v>
       </c>
       <c r="AD2" t="n">
-        <v>-1.5</v>
+        <v>-3.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.5</v>
+        <v>0.5</v>
       </c>
       <c r="AF2" t="n">
-        <v>-1</v>
+        <v>1.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.5</v>
+        <v>7</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>-6.5</v>
       </c>
       <c r="AJ2" t="n">
-        <v>75.90000000000001</v>
+        <v>72.125</v>
       </c>
       <c r="AK2" t="n">
-        <v>73.5</v>
+        <v>82.7</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.2042483660130714</v>
+        <v>0.4256091617933748</v>
       </c>
       <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="n">
-        <v>0.401010101010101</v>
-      </c>
-      <c r="AP2" t="inlineStr"/>
+        <v>-19537317.86062378</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>-23458787.87878788</v>
+      </c>
       <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
+      <c r="AR2" t="n">
+        <v>-0.8947368421052635</v>
+      </c>
       <c r="AS2" t="n">
-        <v>0.4490196078431268</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>0.8842047930283172</v>
-      </c>
+        <v>3.396969696969649</v>
+      </c>
+      <c r="AT2" t="inlineStr"/>
       <c r="AU2" t="n">
-        <v>0.360675381263615</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>86895.42483660067</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0.981144781144792</v>
-      </c>
-      <c r="AX2" t="inlineStr"/>
-      <c r="AY2" t="inlineStr"/>
+        <v>-1.060606060606061</v>
+      </c>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="n">
+        <v>0.6545454545454596</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>-8.984848484848499</v>
+      </c>
       <c r="AZ2" t="n">
-        <v>-0.5929292929292842</v>
+        <v>-8.988182261208578</v>
       </c>
       <c r="BA2" t="n">
-        <v>763468.0134680141</v>
+        <v>0.1629142300194921</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.111784511784514</v>
+        <v>-8.541423001949326</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.1161616161616337</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>-0.7793028322440136</v>
-      </c>
+        <v>-9.545454545454547</v>
+      </c>
+      <c r="BD2" t="inlineStr"/>
       <c r="BE2" t="n">
         <v>0</v>
       </c>
@@ -896,32 +892,32 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>CnrLfkNN</t>
+          <t>2k0SlKj2</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45550.4375</v>
+        <v>45557.52083333334</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">dankert b 
+          <t xml:space="preserve">hartmann r 
   ger </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">wwk arena
-  augsburg </t>
+          <t xml:space="preserve">mhparena
+  stuttgart </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>fTVNku3I</t>
+          <t>nJQmYp1B</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ILyJuN3g</t>
+          <t>nP1i5US1</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -948,122 +944,126 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>4ljanukM</t>
+          <t>GzfvcwRj</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0jdIgO6t</t>
+          <t>IkCftsQm</t>
         </is>
       </c>
       <c r="O3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2</v>
+      </c>
+      <c r="R3" t="n">
         <v>1</v>
       </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="n">
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="U3" t="n">
+        <v>6</v>
+      </c>
+      <c r="V3" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AC3" t="n">
         <v>3</v>
       </c>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0.6200000000000001</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="V3" t="n">
-        <v>-2</v>
-      </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Y3" t="n">
+      <c r="AD3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE3" t="n">
         <v>2.5</v>
       </c>
-      <c r="Z3" t="n">
-        <v>-16.5</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0.5</v>
-      </c>
       <c r="AF3" t="n">
-        <v>-0.5</v>
+        <v>-4.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0.5</v>
+        <v>1.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="AI3" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AJ3" t="n">
-        <v>73.27272727272727</v>
+        <v>74.88888888888889</v>
       </c>
       <c r="AK3" t="n">
-        <v>75</v>
+        <v>74.2</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.415674603174603</v>
+        <v>0.3857425426310499</v>
       </c>
       <c r="AM3" t="inlineStr"/>
       <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="AP3" t="inlineStr"/>
+        <v>-15754576.76052877</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>-23993813.13131313</v>
+      </c>
       <c r="AQ3" t="inlineStr"/>
-      <c r="AR3" t="inlineStr"/>
+      <c r="AR3" t="n">
+        <v>-0.4657219027962065</v>
+      </c>
       <c r="AS3" t="n">
-        <v>3.210341007748141</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>3.014931118646288</v>
-      </c>
+        <v>0.2219696969697225</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
       <c r="AU3" t="n">
-        <v>-0.5550610595115195</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>2372027.008902976</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>3.467592592592595</v>
-      </c>
-      <c r="AX3" t="inlineStr"/>
-      <c r="AY3" t="inlineStr"/>
+        <v>-1.198989898989899</v>
+      </c>
+      <c r="AV3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr"/>
+      <c r="AX3" t="n">
+        <v>-1.754545454545461</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>-6.77196969696972</v>
+      </c>
       <c r="AZ3" t="n">
-        <v>-0.5879629629629903</v>
+        <v>-5.367843628679537</v>
       </c>
       <c r="BA3" t="n">
-        <v>2684074.074074074</v>
+        <v>-0.3832473340213376</v>
       </c>
       <c r="BB3" t="n">
-        <v>-0.7472222222222236</v>
+        <v>-4.601590987272118</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.215740740740742</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>-1.040997100594637</v>
-      </c>
+        <v>-5.351262626262624</v>
+      </c>
+      <c r="BD3" t="inlineStr"/>
       <c r="BE3" t="n">
         <v>0</v>
       </c>
@@ -1071,32 +1071,32 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>x4pn9lxH</t>
+          <t>Uy2KjtMk</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45549.5625</v>
+        <v>45557.4375</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">dingert c 
+          <t xml:space="preserve">exner f 
   ger </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">holstein stadion
-  kiel </t>
+          <t xml:space="preserve">bayarena
+  leverkusen </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>63WsD2ei</t>
+          <t>4jcj2zMd</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>nVp0wiqd</t>
+          <t>nwkTahLL</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1123,122 +1123,126 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>A15eUM4C</t>
+          <t>hAcTWKKN</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>YZPE6Sx7</t>
+          <t>f3ddUIXs</t>
         </is>
       </c>
       <c r="O4" t="n">
+        <v>5</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>10</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>4</v>
+      </c>
+      <c r="U4" t="n">
         <v>1</v>
       </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="n">
+      <c r="V4" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.7949999999999999</v>
+      </c>
+      <c r="X4" t="n">
         <v>1</v>
       </c>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>-1.79</v>
-      </c>
-      <c r="U4" t="n">
-        <v>-0.96</v>
-      </c>
-      <c r="V4" t="n">
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
         <v>-1.5</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="n">
-        <v>-2</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>-16.5</v>
-      </c>
       <c r="AA4" t="n">
-        <v>16.5</v>
+        <v>1.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>-3.5</v>
+        <v>1</v>
       </c>
       <c r="AE4" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="AF4" t="n">
         <v>-3</v>
       </c>
       <c r="AG4" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
       <c r="AH4" t="n">
-        <v>1</v>
+        <v>-15</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.5</v>
+        <v>15</v>
       </c>
       <c r="AJ4" t="n">
-        <v>75.5</v>
+        <v>76.82272727272726</v>
       </c>
       <c r="AK4" t="n">
-        <v>75.5</v>
+        <v>68.55555555555556</v>
       </c>
       <c r="AL4" t="n">
-        <v>-1.995697167755991</v>
+        <v>-4.731313131313101</v>
       </c>
       <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="n">
-        <v>-1.801683501683501</v>
-      </c>
-      <c r="AP4" t="inlineStr"/>
+        <v>26406530.93434344</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>22828998.31649832</v>
+      </c>
       <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="inlineStr"/>
+      <c r="AR4" t="n">
+        <v>0.5261047979797981</v>
+      </c>
       <c r="AS4" t="n">
-        <v>-12.17039760348582</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>-14.50577342047929</v>
-      </c>
+        <v>-1.258164983165017</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
       <c r="AU4" t="n">
-        <v>-1.991693899782138</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>-39913401.416122</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>-13.69023569023571</v>
-      </c>
-      <c r="AX4" t="inlineStr"/>
-      <c r="AY4" t="inlineStr"/>
+        <v>0.357323232323232</v>
+      </c>
+      <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="n">
+        <v>0.7485690235690186</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>4.688973063973066</v>
+      </c>
       <c r="AZ4" t="n">
-        <v>2.047811447811483</v>
+        <v>5.260511363636354</v>
       </c>
       <c r="BA4" t="n">
-        <v>-45693333.33333334</v>
+        <v>-0.1361111111111022</v>
       </c>
       <c r="BB4" t="n">
-        <v>-0.120875420875425</v>
+        <v>4.038131313131331</v>
       </c>
       <c r="BC4" t="n">
-        <v>-14.22727272727273</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>1.103404139433593</v>
-      </c>
+        <v>3.644528619528629</v>
+      </c>
+      <c r="BD4" t="inlineStr"/>
       <c r="BE4" t="n">
         <v>0</v>
       </c>
@@ -1246,32 +1250,32 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>UwsvBA74</t>
+          <t>IcrFCNr9</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45549.4375</v>
+        <v>45556.5625</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">gerach t 
+          <t xml:space="preserve">storks s 
   ger </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">borussia park
-  monchengladbach </t>
+          <t xml:space="preserve">deutsche bank park
+  frankfurt </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>88HSzjDr</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>nJQmYp1B</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1298,126 +1302,126 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>8f6APkLc</t>
+          <t>UgdQz0fK</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>vZA6VYpf</t>
+          <t>M5BRZDsC</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>-10</v>
+        <v>-3</v>
       </c>
       <c r="P5" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q5" t="n">
         <v>-1</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>1</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="U5" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="V5" t="n">
+        <v>-0.2399999999999998</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AI5" t="n">
         <v>2</v>
       </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.295</v>
-      </c>
-      <c r="V5" t="n">
-        <v>2.666666666666667</v>
-      </c>
-      <c r="W5" t="n">
-        <v>6.333333333333334</v>
-      </c>
-      <c r="X5" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>14.33333333333333</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>-22</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>22</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>-2.666666666666666</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>-0.6666666666666665</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>-1</v>
-      </c>
       <c r="AJ5" t="n">
-        <v>82.8</v>
+        <v>75</v>
       </c>
       <c r="AK5" t="n">
-        <v>77.5</v>
+        <v>72</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.06118775548123345</v>
+        <v>1.777220719783656</v>
       </c>
       <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="n">
-        <v>0.3421717171717167</v>
-      </c>
-      <c r="AP5" t="inlineStr"/>
+        <v>69646.46464646515</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>3727272.727272732</v>
+      </c>
       <c r="AQ5" t="inlineStr"/>
-      <c r="AR5" t="inlineStr"/>
+      <c r="AR5" t="n">
+        <v>0.02871506830316894</v>
+      </c>
       <c r="AS5" t="n">
-        <v>-0.4701551467855722</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>1.18559550353028</v>
-      </c>
+        <v>1.030303030303088</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
       <c r="AU5" t="n">
-        <v>1.114078177257522</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>-855916.132478633</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>1.7391414141414</v>
-      </c>
-      <c r="AX5" t="inlineStr"/>
-      <c r="AY5" t="inlineStr"/>
+        <v>0.1212121212121218</v>
+      </c>
+      <c r="AV5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="n">
+        <v>-0.6666666666666643</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>1.242424242424249</v>
+      </c>
       <c r="AZ5" t="n">
-        <v>-1.639898989898967</v>
+        <v>-2.731775420104924</v>
       </c>
       <c r="BA5" t="n">
-        <v>877575.7575757559</v>
+        <v>-3.788149226822</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.313131313131311</v>
+        <v>3.170579941289319</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.445959595959593</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>0.3242811687105132</v>
-      </c>
+        <v>2.818181818181813</v>
+      </c>
+      <c r="BD5" t="inlineStr"/>
       <c r="BE5" t="n">
         <v>0</v>
       </c>
@@ -1425,32 +1429,32 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>tI0qkTpo</t>
+          <t>pY1dP0SE</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45549.4375</v>
+        <v>45556.4375</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">badstubner f 
+          <t xml:space="preserve">exner f 
   ger </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">volkswagen arena
-  wolfsburg </t>
+          <t xml:space="preserve">vonovia ruhrstadion
+  bochum </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>nwkTahLL</t>
+          <t>8Y2m6ADe</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>8vndvXTk</t>
+          <t>63WsD2ei</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1477,126 +1481,122 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>A15eUM4C</t>
+          <t>8f6APkLc</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>KUx4Q7x1</t>
+          <t>f3ddUIXs</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>15</v>
-      </c>
-      <c r="P6" t="n">
-        <v>3</v>
-      </c>
+        <v>-1</v>
+      </c>
+      <c r="P6" t="inlineStr"/>
       <c r="Q6" t="n">
-        <v>9</v>
-      </c>
-      <c r="R6" t="n">
         <v>1</v>
       </c>
+      <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>1.15</v>
+        <v>-1.5</v>
       </c>
       <c r="U6" t="n">
-        <v>1.44</v>
+        <v>-1</v>
       </c>
       <c r="V6" t="n">
+        <v>-1.04</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-0.1699999999999999</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AF6" t="n">
         <v>-4.5</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>-10</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>-1.5</v>
-      </c>
       <c r="AG6" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="AI6" t="n">
-        <v>-0.5</v>
+        <v>11</v>
       </c>
       <c r="AJ6" t="n">
-        <v>83</v>
+        <v>76.18181818181819</v>
       </c>
       <c r="AK6" t="n">
-        <v>74.7625</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.03896863370547532</v>
+        <v>-1.965103173114016</v>
       </c>
       <c r="AM6" t="inlineStr"/>
       <c r="AN6" t="inlineStr"/>
       <c r="AO6" t="n">
-        <v>-0.08333333333333326</v>
-      </c>
-      <c r="AP6" t="inlineStr"/>
+        <v>718869.5357861381</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1051641.414141414</v>
+      </c>
       <c r="AQ6" t="inlineStr"/>
-      <c r="AR6" t="inlineStr"/>
+      <c r="AR6" t="n">
+        <v>-0.03812636165577366</v>
+      </c>
       <c r="AS6" t="n">
-        <v>-2.333825093035614</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>3.109908293460933</v>
-      </c>
+        <v>-0.7548821548822104</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
       <c r="AU6" t="n">
-        <v>3.905429292929288</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>2106051.967038808</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>-1.421296296296291</v>
-      </c>
-      <c r="AX6" t="inlineStr"/>
-      <c r="AY6" t="inlineStr"/>
+        <v>-0.1074074074074074</v>
+      </c>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="n">
+        <v>1.662962962962965</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>3.184175084175095</v>
+      </c>
       <c r="AZ6" t="n">
-        <v>0.3101851851852189</v>
+        <v>0.9082713095870929</v>
       </c>
       <c r="BA6" t="n">
-        <v>-3455555.555555554</v>
+        <v>-2.103823972438523</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.02777777777778212</v>
+        <v>4.679114415569501</v>
       </c>
       <c r="BC6" t="n">
-        <v>-1.773148148148152</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>0.267490696438017</v>
-      </c>
+        <v>2.109090909090909</v>
+      </c>
+      <c r="BD6" t="inlineStr"/>
       <c r="BE6" t="n">
         <v>0</v>
       </c>
@@ -1604,32 +1604,32 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>r7j4bXNb</t>
+          <t>AeNg5uyq</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45549.4375</v>
+        <v>45556.4375</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">jollenbeck m 
+          <t xml:space="preserve">dingert c 
   ger </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">prezero arena
-  sinsheim </t>
+          <t xml:space="preserve">weserstadion
+  bremen </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>hQAtP9Sl</t>
+          <t>Ig1f1fy3</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>4jcj2zMd</t>
+          <t>nVp0wiqd</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1656,126 +1656,126 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>UgdQz0fK</t>
+          <t>4fuCGs9P</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>pfoInmcq</t>
+          <t>YZPE6Sx7</t>
         </is>
       </c>
       <c r="O7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="P7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Q7" t="n">
         <v>-12</v>
       </c>
-      <c r="P7" t="n">
-        <v>-4</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>-6</v>
-      </c>
       <c r="R7" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
+      </c>
+      <c r="V7" t="n">
+        <v>-2.52</v>
+      </c>
+      <c r="W7" t="n">
+        <v>-1.58</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>-9</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AE7" t="n">
         <v>-1</v>
       </c>
-      <c r="U7" t="n">
-        <v>-0.08000000000000007</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>2</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>-10.5</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1</v>
-      </c>
       <c r="AF7" t="n">
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0.5</v>
+        <v>-20.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>20.5</v>
       </c>
       <c r="AJ7" t="n">
-        <v>68.55555555555556</v>
+        <v>80.45454545454545</v>
       </c>
       <c r="AK7" t="n">
-        <v>76.45454545454545</v>
+        <v>72.0810185185185</v>
       </c>
       <c r="AL7" t="n">
-        <v>-0.3357663578251817</v>
+        <v>0.4474140380790175</v>
       </c>
       <c r="AM7" t="inlineStr"/>
       <c r="AN7" t="inlineStr"/>
       <c r="AO7" t="n">
-        <v>-0.3490740740740739</v>
-      </c>
-      <c r="AP7" t="inlineStr"/>
+        <v>-37991709.35161503</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>-41654545.45454546</v>
+      </c>
       <c r="AQ7" t="inlineStr"/>
-      <c r="AR7" t="inlineStr"/>
+      <c r="AR7" t="n">
+        <v>-1.574699251681348</v>
+      </c>
       <c r="AS7" t="n">
-        <v>-5.050016160310264</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>-6.727680815916116</v>
-      </c>
+        <v>0.09696969696966562</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
       <c r="AU7" t="n">
-        <v>0.2841521223874182</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>-28302889.47844095</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>-7.492592592592601</v>
-      </c>
-      <c r="AX7" t="inlineStr"/>
-      <c r="AY7" t="inlineStr"/>
+        <v>-1.599999999999999</v>
+      </c>
+      <c r="AV7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr"/>
+      <c r="AX7" t="n">
+        <v>0.4393939393939377</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>-8.478787878787884</v>
+      </c>
       <c r="AZ7" t="n">
-        <v>2.07129629629631</v>
+        <v>-11.57116131476745</v>
       </c>
       <c r="BA7" t="n">
-        <v>-32011851.85185185</v>
+        <v>-1.892156862745097</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.880555555555553</v>
+        <v>-7.443163303968959</v>
       </c>
       <c r="BC7" t="n">
-        <v>-7.412037037037038</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>4.244194258900166</v>
-      </c>
+        <v>-9.378787878787904</v>
+      </c>
+      <c r="BD7" t="inlineStr"/>
       <c r="BE7" t="n">
         <v>0</v>
       </c>
@@ -1783,32 +1783,32 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>WSMotj8U</t>
+          <t>hvFA1cz8</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45549.4375</v>
+        <v>45556.4375</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">dankert b 
+          <t xml:space="preserve">badstubner f 
   ger </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">red bull arena
-  leipzig </t>
+          <t xml:space="preserve">stadion an der alten forsterei
+  berlin </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>KbS1suSm</t>
+          <t>pzHW4oaE</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>pzHW4oaE</t>
+          <t>hQAtP9Sl</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1835,126 +1835,126 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>hAcTWKKN</t>
+          <t>hpYJ6izc</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0jdIgO6t</t>
+          <t>KUx4Q7x1</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="U8" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="V8" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AD8" t="n">
         <v>-1</v>
       </c>
-      <c r="Q8" t="n">
-        <v>4</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0.3699999999999999</v>
-      </c>
-      <c r="U8" t="n">
-        <v>-0.04000000000000004</v>
-      </c>
-      <c r="V8" t="n">
+      <c r="AE8" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AF8" t="n">
         <v>-1.5</v>
       </c>
-      <c r="W8" t="n">
-        <v>1</v>
-      </c>
-      <c r="X8" t="n">
-        <v>-3</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1</v>
-      </c>
       <c r="AG8" t="n">
-        <v>-0.5</v>
+        <v>0.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>-16.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AJ8" t="n">
-        <v>71.375</v>
+        <v>70.27272727272727</v>
       </c>
       <c r="AK8" t="n">
-        <v>74.59999999999999</v>
+        <v>77.27272727272727</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.5111606589867461</v>
+        <v>-2.04280842771891</v>
       </c>
       <c r="AM8" t="inlineStr"/>
       <c r="AN8" t="inlineStr"/>
       <c r="AO8" t="n">
-        <v>0.4383838383838381</v>
-      </c>
-      <c r="AP8" t="inlineStr"/>
+        <v>-3216512.131422618</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>-677222.222222222</v>
+      </c>
       <c r="AQ8" t="inlineStr"/>
-      <c r="AR8" t="inlineStr"/>
+      <c r="AR8" t="n">
+        <v>-0.1189583079608656</v>
+      </c>
       <c r="AS8" t="n">
-        <v>5.820813646900618</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>5.914375077418541</v>
-      </c>
+        <v>-0.0148148148148266</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
       <c r="AU8" t="n">
-        <v>-1.042242218329179</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>18320896.06448302</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>3.945791245791241</v>
-      </c>
-      <c r="AX8" t="inlineStr"/>
-      <c r="AY8" t="inlineStr"/>
+        <v>-0.1444444444444442</v>
+      </c>
+      <c r="AV8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr"/>
+      <c r="AX8" t="n">
+        <v>-0.1000000000000014</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>1.014814814814827</v>
+      </c>
       <c r="AZ8" t="n">
-        <v>-2.86397306397302</v>
+        <v>-0.3451826141084382</v>
       </c>
       <c r="BA8" t="n">
-        <v>18284949.49494949</v>
+        <v>0.9716444065548941</v>
       </c>
       <c r="BB8" t="n">
-        <v>-1.790909090909093</v>
+        <v>-1.525192492455929</v>
       </c>
       <c r="BC8" t="n">
-        <v>5.516835016835017</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>0.8992833253703054</v>
-      </c>
+        <v>0.1740740740740705</v>
+      </c>
+      <c r="BD8" t="inlineStr"/>
       <c r="BE8" t="n">
         <v>0</v>
       </c>
@@ -1962,32 +1962,32 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>vZqDdBhB</t>
+          <t>QNoNA1DL</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45549.4375</v>
+        <v>45556.4375</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">storks s 
+          <t xml:space="preserve">dingert c 
   ger </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">europa park stadion
-  freiburg </t>
+          <t xml:space="preserve">voith arena
+  heidenheim </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>fiEQZ7C7</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>8Y2m6ADe</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2014,126 +2014,126 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>K6A2elS9</t>
+          <t>4ljanukM</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>M5BRZDsC</t>
+          <t>YZPE6Sx7</t>
         </is>
       </c>
       <c r="O9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W9" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AF9" t="n">
         <v>5</v>
       </c>
-      <c r="P9" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>3</v>
-      </c>
-      <c r="R9" t="n">
-        <v>3</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="U9" t="n">
-        <v>-0.9299999999999999</v>
-      </c>
-      <c r="V9" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="W9" t="n">
-        <v>-3</v>
-      </c>
-      <c r="X9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>-6.5</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>-17</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>17</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>-11.5</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>3</v>
-      </c>
       <c r="AG9" t="n">
-        <v>-3</v>
+        <v>1.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>-3.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>-0.5</v>
+        <v>3.5</v>
       </c>
       <c r="AJ9" t="n">
-        <v>75.33333333333333</v>
+        <v>73.44444444444444</v>
       </c>
       <c r="AK9" t="n">
-        <v>79.72727272727273</v>
+        <v>82.27272727272727</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.6632160110420982</v>
+        <v>2.726032321140991</v>
       </c>
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" t="inlineStr"/>
       <c r="AO9" t="n">
-        <v>0.7259259259259261</v>
-      </c>
-      <c r="AP9" t="inlineStr"/>
+        <v>-6253071.083505867</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>-6902314.814814813</v>
+      </c>
       <c r="AQ9" t="inlineStr"/>
-      <c r="AR9" t="inlineStr"/>
+      <c r="AR9" t="n">
+        <v>-0.6632160110420982</v>
+      </c>
       <c r="AS9" t="n">
-        <v>0.8785800552104917</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>7.859937888198743</v>
-      </c>
+        <v>4.495370370370438</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
       <c r="AU9" t="n">
-        <v>3.570031055900618</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>6485566.123188406</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>3.905092592592595</v>
-      </c>
-      <c r="AX9" t="inlineStr"/>
-      <c r="AY9" t="inlineStr"/>
+        <v>-0.7259259259259261</v>
+      </c>
+      <c r="AV9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr"/>
+      <c r="AX9" t="n">
+        <v>0.5787037037037024</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>-2.953703703703709</v>
+      </c>
       <c r="AZ9" t="n">
-        <v>0.4930555555554861</v>
+        <v>-4.919197147458007</v>
       </c>
       <c r="BA9" t="n">
-        <v>7433854.166666666</v>
+        <v>-0.4719490453186062</v>
       </c>
       <c r="BB9" t="n">
-        <v>-1.314814814814813</v>
+        <v>-4.837244076374503</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.955092592592578</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>-1.983109040717721</v>
-      </c>
+        <v>-3.457407407407402</v>
+      </c>
+      <c r="BD9" t="inlineStr"/>
       <c r="BE9" t="n">
         <v>0</v>
       </c>
@@ -2141,32 +2141,32 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>zsmd0ggn</t>
+          <t>dCL13J5e</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45548.64583333334</v>
+        <v>45555.64583333334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">petersen m 
+          <t xml:space="preserve">gerach t 
   ger </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">signal iduna park
-  dortmund </t>
+          <t xml:space="preserve">wwk arena
+  augsburg </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>nP1i5US1</t>
+          <t>fTVNku3I</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>KWixEVWi</t>
+          <t>EuakNmc1</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2193,58 +2193,58 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>4fuCGs9P</t>
+          <t>4ljanukM</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2VSFgl3c</t>
+          <t>vZA6VYpf</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.04000000000000004</v>
+        <v>-3.5</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4000000000000001</v>
+        <v>-2.5</v>
       </c>
       <c r="V10" t="n">
+        <v>-1.13</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-3.35</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
         <v>-1</v>
       </c>
-      <c r="W10" t="n">
-        <v>1</v>
-      </c>
-      <c r="X10" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>-0.5</v>
-      </c>
       <c r="Z10" t="n">
-        <v>12.5</v>
+        <v>-1</v>
       </c>
       <c r="AA10" t="n">
-        <v>-12.5</v>
+        <v>0.5</v>
       </c>
       <c r="AB10" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AC10" t="n">
         <v>-6</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>-5.5</v>
       </c>
       <c r="AD10" t="n">
         <v>-1</v>
@@ -2253,67 +2253,1670 @@
         <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>-2.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>-6.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AJ10" t="n">
-        <v>77.375</v>
+        <v>71.81060606060605</v>
       </c>
       <c r="AK10" t="n">
-        <v>70</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.6715665976535539</v>
+        <v>-0.9023809523809234</v>
       </c>
       <c r="AM10" t="inlineStr"/>
       <c r="AN10" t="inlineStr"/>
       <c r="AO10" t="n">
+        <v>1087956.349206349</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>-1531481.481481481</v>
+      </c>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="n">
+        <v>0.07380952380952421</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0.8333333333332575</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="n">
+        <v>-0.4777777777777783</v>
+      </c>
+      <c r="AV10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr"/>
+      <c r="AX10" t="n">
+        <v>-1.8037037037037</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>-1.192592592592604</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>1.055291005290997</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>-0.4891534391534371</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>-0.8769841269841265</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>-0.5555555555555713</v>
+      </c>
+      <c r="BD10" t="inlineStr"/>
+      <c r="BE10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>8OhVCWxh</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45550.52083333334</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hartmann r 
+  ger </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mewa arena
+  mainz </t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>59</v>
+      </c>
+      <c r="H11" t="n">
+        <v>591</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>GzfvcwRj</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>IkCftsQm</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>-5</v>
+      </c>
+      <c r="P11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>-6</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
+      </c>
+      <c r="V11" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="W11" t="n">
+        <v>-0.1000000000000001</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>73.33333333333333</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>-0.6049019607843036</v>
+      </c>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="n">
+        <v>81209.15032679681</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>763468.0134680141</v>
+      </c>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="n">
+        <v>0.2042483660130714</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>-0.2468013468013055</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AU11" t="n">
+        <v>0.401010101010101</v>
+      </c>
+      <c r="AV11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr"/>
+      <c r="AX11" t="n">
+        <v>1.111784511784514</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0.981144781144792</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0.9175381263616487</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0.360675381263615</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>0.3588235294117794</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>0.1161616161616337</v>
+      </c>
+      <c r="BD11" t="inlineStr"/>
+      <c r="BE11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>CnrLfkNN</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45550.4375</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dankert b 
+  ger </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wwk arena
+  augsburg </t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>fTVNku3I</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>59</v>
+      </c>
+      <c r="H12" t="n">
+        <v>591</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>4ljanukM</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0jdIgO6t</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>1</v>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="n">
+        <v>3</v>
+      </c>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>-3.333333333333333</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="V12" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.7350000000000001</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>-4.333333333333334</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.333333333333334</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.333333333333334</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0.3333333333333339</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>-15.33333333333334</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>15.33333333333334</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>73.27272727272727</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>70.95454545454545</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>-0.7299637983848299</v>
+      </c>
+      <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="n">
+        <v>2217871.066555277</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>2218047.138047139</v>
+      </c>
+      <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="n">
+        <v>0.4682539682539684</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>-1.592255892255935</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AU12" t="n">
+        <v>0.1111111111111109</v>
+      </c>
+      <c r="AV12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr"/>
+      <c r="AX12" t="n">
+        <v>-0.4525252525252519</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>3.021885521885537</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>3.009579504316335</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>-0.1243386243386269</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>2.752158173210816</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>2.454545454545453</v>
+      </c>
+      <c r="BD12" t="inlineStr"/>
+      <c r="BE12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>x4pn9lxH</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45549.5625</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dingert c 
+  ger </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">holstein stadion
+  kiel </t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>59</v>
+      </c>
+      <c r="H13" t="n">
+        <v>591</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>A15eUM4C</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>YZPE6Sx7</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>1</v>
+      </c>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>-0.666666666666667</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.3333333333333335</v>
+      </c>
+      <c r="V13" t="n">
+        <v>-1.16</v>
+      </c>
+      <c r="W13" t="n">
+        <v>-0.895</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>-1.333333333333334</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>6.666666666666666</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>3.666666666666666</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>-11</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>75.625</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>76.08522727272728</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1.028269157904759</v>
+      </c>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="n">
+        <v>-39605496.79714881</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>-45411818.18181819</v>
+      </c>
+      <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="n">
+        <v>-1.726768968456947</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>2.320538720538735</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AU13" t="n">
+        <v>-1.68047138047138</v>
+      </c>
+      <c r="AV13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr"/>
+      <c r="AX13" t="n">
+        <v>0.1548821548821522</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>-13.52356902356904</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>-14.49899355877616</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>-1.665713507625274</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>-12.41576678980772</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>-14.31818181818184</v>
+      </c>
+      <c r="BD13" t="inlineStr"/>
+      <c r="BE13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>vZqDdBhB</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45549.4375</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">storks s 
+  ger </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">europa park stadion
+  freiburg </t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>59</v>
+      </c>
+      <c r="H14" t="n">
+        <v>591</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>K6A2elS9</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>M5BRZDsC</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>4</v>
+      </c>
+      <c r="P14" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3</v>
+      </c>
+      <c r="R14" t="n">
+        <v>3</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-2.75</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-4.75</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.6500000000000004</v>
+      </c>
+      <c r="W14" t="n">
+        <v>-1.94</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-2.25</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>-9.75</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>-2.75</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>-18</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>18</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>75.33333333333333</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>74.6969696969697</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>-0.3017788212296182</v>
+      </c>
+      <c r="AM14" t="inlineStr"/>
+      <c r="AN14" t="inlineStr"/>
+      <c r="AO14" t="n">
+        <v>5834198.143580295</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>7022803.030303029</v>
+      </c>
+      <c r="AQ14" t="inlineStr"/>
+      <c r="AR14" t="n">
+        <v>0.6632160110420982</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>-1.363636363636374</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AU14" t="n">
+        <v>0.7259259259259261</v>
+      </c>
+      <c r="AV14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr"/>
+      <c r="AX14" t="n">
+        <v>-1.55185185185185</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>3.315824915824919</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>6.534073986019052</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>3.628060599456479</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0.3414085279073902</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>3.672390572390569</v>
+      </c>
+      <c r="BD14" t="inlineStr"/>
+      <c r="BE14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>WSMotj8U</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45549.4375</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dankert b 
+  ger </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">red bull arena
+  leipzig </t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>59</v>
+      </c>
+      <c r="H15" t="n">
+        <v>591</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>hAcTWKKN</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0jdIgO6t</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>2</v>
+      </c>
+      <c r="P15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>4</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.3699999999999999</v>
+      </c>
+      <c r="W15" t="n">
+        <v>-0.04000000000000004</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0.6076672659910969</v>
+      </c>
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="inlineStr"/>
+      <c r="AO15" t="n">
+        <v>17744168.15362682</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>18012222.22222222</v>
+      </c>
+      <c r="AQ15" t="inlineStr"/>
+      <c r="AR15" t="n">
+        <v>0.5865242817187901</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>-3.86397306397302</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AU15" t="n">
+        <v>0.4383838383838381</v>
+      </c>
+      <c r="AV15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr"/>
+      <c r="AX15" t="n">
+        <v>-1.790909090909093</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>3.885185185185179</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>5.979465420798363</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>-1.082364425556644</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>5.880672696233347</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>5.516835016835017</v>
+      </c>
+      <c r="BD15" t="inlineStr"/>
+      <c r="BE15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>r7j4bXNb</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45549.4375</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jollenbeck m 
+  ger </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prezero arena
+  sinsheim </t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>59</v>
+      </c>
+      <c r="H16" t="n">
+        <v>591</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>UgdQz0fK</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>pfoInmcq</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>-11</v>
+      </c>
+      <c r="P16" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-6</v>
+      </c>
+      <c r="R16" t="n">
+        <v>-3</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
         <v>1.5</v>
       </c>
-      <c r="AP10" t="inlineStr"/>
-      <c r="AQ10" t="inlineStr"/>
-      <c r="AR10" t="inlineStr"/>
-      <c r="AS10" t="n">
-        <v>11.20235794801012</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>7.701805843110193</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>-2.336746606855304</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>20967249.82746721</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>9.050000000000011</v>
-      </c>
-      <c r="AX10" t="inlineStr"/>
-      <c r="AY10" t="inlineStr"/>
-      <c r="AZ10" t="n">
-        <v>-2.106481481481524</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>32107870.37037037</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>-1.041666666666664</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>9.709259259259255</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>-1.481449850471563</v>
-      </c>
-      <c r="BE10" t="n">
+      <c r="U16" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.1949999999999998</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.665</v>
+      </c>
+      <c r="X16" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>4.833333333333334</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.833333333333333</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>-1.833333333333334</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>-13.5</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>74.86868686868686</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>72.18181818181819</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>4.090650199473686</v>
+      </c>
+      <c r="AM16" t="inlineStr"/>
+      <c r="AN16" t="inlineStr"/>
+      <c r="AO16" t="n">
+        <v>-28664978.25771723</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>-26614924.24242424</v>
+      </c>
+      <c r="AQ16" t="inlineStr"/>
+      <c r="AR16" t="n">
+        <v>-0.4544894851880146</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>2.711868686868712</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AU16" t="n">
+        <v>-0.2295454545454545</v>
+      </c>
+      <c r="AV16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr"/>
+      <c r="AX16" t="n">
+        <v>2.014393939393944</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>-6.042676767676781</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>-6.722937445180079</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0.1306761593526282</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>-5.203553037376565</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>-6.25378787878789</v>
+      </c>
+      <c r="BD16" t="inlineStr"/>
+      <c r="BE16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>UwsvBA74</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45549.4375</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gerach t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">borussia park
+  monchengladbach </t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>59</v>
+      </c>
+      <c r="H17" t="n">
+        <v>591</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>8f6APkLc</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>vZA6VYpf</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>-10</v>
+      </c>
+      <c r="P17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="U17" t="n">
+        <v>6.333333333333334</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.295</v>
+      </c>
+      <c r="X17" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>14.33333333333333</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>-0.6666666666666665</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>-2.666666666666666</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>-22</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>22</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>77.09090909090909</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0.3808033510887583</v>
+      </c>
+      <c r="AM17" t="inlineStr"/>
+      <c r="AN17" t="inlineStr"/>
+      <c r="AO17" t="n">
+        <v>-904589.9061378939</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>842297.979797978</v>
+      </c>
+      <c r="AQ17" t="inlineStr"/>
+      <c r="AR17" t="n">
+        <v>0.1122194873372693</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>-1.67651515151519</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AU17" t="n">
+        <v>0.35050505050505</v>
+      </c>
+      <c r="AV17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr"/>
+      <c r="AX17" t="n">
+        <v>1.390909090909094</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>1.711363636363629</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>1.082819474090172</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>1.450397092475438</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>-0.9434573219066209</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>0.320959595959593</v>
+      </c>
+      <c r="BD17" t="inlineStr"/>
+      <c r="BE17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>tI0qkTpo</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45549.4375</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">badstubner f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">volkswagen arena
+  wolfsburg </t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>59</v>
+      </c>
+      <c r="H18" t="n">
+        <v>591</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>A15eUM4C</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>KUx4Q7x1</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>15</v>
+      </c>
+      <c r="P18" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>9</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>-3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>4</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0.5449999999999999</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.8400000000000001</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>78.51363636363637</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>74.67613636363637</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0.270122275385404</v>
+      </c>
+      <c r="AM18" t="inlineStr"/>
+      <c r="AN18" t="inlineStr"/>
+      <c r="AO18" t="n">
+        <v>3205214.646464647</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>-1500589.225589229</v>
+      </c>
+      <c r="AQ18" t="inlineStr"/>
+      <c r="AR18" t="n">
+        <v>0.0442317916002124</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>-0.332491582491599</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AU18" t="n">
+        <v>-0.08838383838383823</v>
+      </c>
+      <c r="AV18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr"/>
+      <c r="AX18" t="n">
+        <v>-0.7205387205387233</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>-1.425084175084166</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>3.441799574694301</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>3.866832801701221</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>-1.989420520999488</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>-0.9604377104377022</v>
+      </c>
+      <c r="BD18" t="inlineStr"/>
+      <c r="BE18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>zsmd0ggn</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45548.64583333334</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">petersen m 
+  ger </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">signal iduna park
+  dortmund </t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>59</v>
+      </c>
+      <c r="H19" t="n">
+        <v>591</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>4fuCGs9P</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2VSFgl3c</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U19" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.6700000000000002</v>
+      </c>
+      <c r="W19" t="n">
+        <v>-0.7850000000000001</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>-7</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>-14.5</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>74.32727272727273</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>70.27272727272727</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>-2.981018518518511</v>
+      </c>
+      <c r="AM19" t="inlineStr"/>
+      <c r="AN19" t="inlineStr"/>
+      <c r="AO19" t="n">
+        <v>20917500</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>30433627.94612794</v>
+      </c>
+      <c r="AQ19" t="inlineStr"/>
+      <c r="AR19" t="n">
+        <v>0.6361111111111113</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>-2.636784511784555</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AU19" t="n">
+        <v>1.454545454545455</v>
+      </c>
+      <c r="AV19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr"/>
+      <c r="AX19" t="n">
+        <v>-0.4204545454545396</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>8.946969696969717</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>7.759259259259252</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>-2.475462962962958</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>11.23425925925926</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>9.357744107744111</v>
+      </c>
+      <c r="BD19" t="inlineStr"/>
+      <c r="BE19" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_preparation/df_constructed.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_constructed.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE3"/>
+  <dimension ref="A1:BE19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -535,74 +535,74 @@
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_goal_attempts</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts_against</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days_against</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_goals</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goals_against</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days_against</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_fouls</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_fouls_against</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession_against</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_points</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_points_against</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts_against</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession_against</t>
-        </is>
-      </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
@@ -615,97 +615,97 @@
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_int_rep_player_miss</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
         </is>
       </c>
       <c r="BE1" s="1" t="inlineStr">
@@ -717,11 +717,11 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>8OhVCWxh</t>
+          <t>bFO8E4Vg</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45550.52083333334</v>
+        <v>45564.52083333334</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -731,13 +731,13 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mewa arena
-  mainz </t>
+          <t xml:space="preserve">prezero arena
+  sinsheim </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>EuakNmc1</t>
+          <t>hQAtP9Sl</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -769,139 +769,125 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>GzfvcwRj</t>
+          <t>KUx4Q7x1</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>IkCftsQm</t>
+          <t>4fuCGs9P</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="P2" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>-6</v>
+        <v>-2</v>
       </c>
       <c r="R2" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.53</v>
+        <v>-0.04499999999999993</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1000000000000001</v>
+        <v>1.12</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.5</v>
+        <v>3.333333333333334</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.5</v>
+        <v>7.833333333333334</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-0.166666666666667</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>-1</v>
+        <v>-0.3333333333333335</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.5</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="AD2" t="n">
-        <v>-4.5</v>
+        <v>-0.1666666666666661</v>
       </c>
       <c r="AE2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>-1.166666666666664</v>
       </c>
       <c r="AG2" t="n">
-        <v>6</v>
+        <v>1.166666666666664</v>
       </c>
       <c r="AH2" t="n">
-        <v>-5</v>
+        <v>-0.8333333333333335</v>
       </c>
       <c r="AI2" t="n">
-        <v>5</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="AJ2" t="n">
-        <v>75.90000000000001</v>
+        <v>75.0959595959596</v>
       </c>
       <c r="AK2" t="n">
-        <v>73.33333333333333</v>
+        <v>74.05555555555554</v>
       </c>
       <c r="AL2" t="n">
-        <v>-0.6666666666666667</v>
+        <v>-0.2960381122145819</v>
       </c>
       <c r="AM2" t="n">
-        <v>3.666666666666657</v>
+        <v>1.061718020541562</v>
       </c>
       <c r="AN2" t="n">
-        <v>-139</v>
+        <v>3262045.454545455</v>
       </c>
       <c r="AO2" t="n">
-        <v>81209.15032679681</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>0.360675381263615</v>
-      </c>
+        <v>0.9477272727272741</v>
+      </c>
+      <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="n">
-        <v>763468.0134680141</v>
+        <v>1.145454545454555</v>
       </c>
       <c r="AR2" t="n">
-        <v>-0.2468013468013055</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>0.9175381263616487</v>
-      </c>
+        <v>1.625488074017483</v>
+      </c>
+      <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
-        <v>-5100000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>1.111784511784514</v>
-      </c>
+        <v>0.6090909090909091</v>
+      </c>
+      <c r="AU2" t="inlineStr"/>
       <c r="AV2" t="n">
-        <v>-142</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0.401010101010101</v>
-      </c>
+        <v>0.8636363636363598</v>
+      </c>
+      <c r="AW2" t="inlineStr"/>
       <c r="AX2" t="n">
-        <v>0.2042483660130714</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>0.3588235294117794</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>-0.6049019607843036</v>
-      </c>
+        <v>2.62045454545455</v>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
       <c r="BA2" t="n">
-        <v>-1</v>
+        <v>-1.065739326033452</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.981144781144792</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>0.1161616161616337</v>
-      </c>
+        <v>0.1979331126389945</v>
+      </c>
+      <c r="BC2" t="inlineStr"/>
       <c r="BD2" t="n">
-        <v>-2</v>
+        <v>3258627.55708344</v>
       </c>
       <c r="BE2" t="n">
         <v>0</v>
@@ -910,189 +896,3027 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>CnrLfkNN</t>
+          <t>pWnjRsFa</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45550.4375</v>
+        <v>45564.4375</v>
       </c>
       <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">osmers h 
+  ger </t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">holstein stadion
+  kiel </t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>59</v>
+      </c>
+      <c r="H3" t="n">
+        <v>591</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>8nuIt455</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>UgdQz0fK</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>-1.415</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V3" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="W3" t="n">
+        <v>3.833333333333334</v>
+      </c>
+      <c r="X3" t="n">
+        <v>-3.333333333333333</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>5.166666666666666</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>5.833333333333333</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>80.13068181818181</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>74.90909090909092</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>3.830006137223627</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>-8.88542731885417</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>-12220085.22727273</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0.905934343434339</v>
+      </c>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>-3.342955874534823</v>
+      </c>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="n">
+        <v>-0.6154671717171716</v>
+      </c>
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="n">
+        <v>-8.668244949494948</v>
+      </c>
+      <c r="AW3" t="inlineStr"/>
+      <c r="AX3" t="n">
+        <v>0.7489267676767497</v>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr"/>
+      <c r="BA3" t="n">
+        <v>-0.3289238163367258</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>-0.3017730517246768</v>
+      </c>
+      <c r="BC3" t="inlineStr"/>
+      <c r="BD3" t="n">
+        <v>-4818716.670380273</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>IukqGdk1</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45563.5625</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">schlager d 
+  ger </t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allianz arena
+  munich </t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>59</v>
+      </c>
+      <c r="H4" t="n">
+        <v>591</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>8nuIt455</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>hAcTWKKN</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>28</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>23</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-2.17</v>
+      </c>
+      <c r="U4" t="n">
+        <v>-0.2450000000000001</v>
+      </c>
+      <c r="V4" t="n">
+        <v>-8.666666666666668</v>
+      </c>
+      <c r="W4" t="n">
+        <v>-2.666666666666666</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>-0.333333333333333</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>-0.3333333333333335</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>-0.6666666666666665</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>3.666666666666664</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>-3.666666666666664</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>75.77727272727273</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1.715984848484844</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.425047760210816</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>13566818.18181818</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0.8124242424242389</v>
+      </c>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="n">
+        <v>2.13757575757576</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>2.167881532718482</v>
+      </c>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="n">
+        <v>0.853030303030303</v>
+      </c>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="n">
+        <v>1.996464646464645</v>
+      </c>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="n">
+        <v>-0.5289898989898916</v>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr"/>
+      <c r="BA4" t="n">
+        <v>3.029315436978436</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>0.8088735177865611</v>
+      </c>
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="n">
+        <v>5182466.375713661</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>CIlrT3pm</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45563.4375</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jablonski s 
+  ger </t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">borussia park
+  monchengladbach </t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>59</v>
+      </c>
+      <c r="H5" t="n">
+        <v>591</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>M5BRZDsC</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>6PecvuWE</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>-6</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-2</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.8333333333333339</v>
+      </c>
+      <c r="W5" t="n">
+        <v>6.166666666666666</v>
+      </c>
+      <c r="X5" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>-2.833333333333334</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>-1.666666666666667</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>78.58181818181818</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>77.09999999999999</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>-0.5788086611456151</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1.475841097308489</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>2613712.121212118</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>-0.9113636363636388</v>
+      </c>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="n">
+        <v>0.5467171717171766</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1.760688405797097</v>
+      </c>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="n">
+        <v>0.0560606060606057</v>
+      </c>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="n">
+        <v>0.8457070707070642</v>
+      </c>
+      <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="n">
+        <v>-1.943434343434348</v>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr"/>
+      <c r="BA5" t="n">
+        <v>0.591679606625263</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0.02246376811594208</v>
+      </c>
+      <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="n">
+        <v>2609795.979986197</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>6uSGCr06</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45563.4375</v>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t xml:space="preserve">zwayer f 
   ger </t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">europa park stadion
+  freiburg </t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>59</v>
+      </c>
+      <c r="H6" t="n">
+        <v>591</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>YZPE6Sx7</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0jdIgO6t</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>2</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>4</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.895</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-0.5850000000000002</v>
+      </c>
+      <c r="V6" t="n">
+        <v>9.666666666666666</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-1.333333333333334</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2.166666666666667</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-9.666666666666664</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>9.666666666666664</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>73.38888888888889</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>75</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1.34111456176673</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>3.784133216770527</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>7361742.424242423</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>-0.084595959595962</v>
+      </c>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="n">
+        <v>3.922474747474752</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>5.538447568195863</v>
+      </c>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="n">
+        <v>0.6944444444444444</v>
+      </c>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="n">
+        <v>4.768686868686871</v>
+      </c>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="n">
+        <v>-2.055303030303037</v>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr"/>
+      <c r="BA6" t="n">
+        <v>-0.3394853652576728</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0.6565029173724826</v>
+      </c>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="n">
+        <v>6238063.214277459</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>SfGPAMUI</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45563.4375</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brych f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">volkswagen arena
+  wolfsburg </t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>59</v>
+      </c>
+      <c r="H7" t="n">
+        <v>591</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>f3ddUIXs</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>GzfvcwRj</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>7</v>
+      </c>
+      <c r="R7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.1950000000000001</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.4483333333333328</v>
+      </c>
+      <c r="V7" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="W7" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>-0.3333333333333335</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>-0.3333333333333335</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>-12</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>80</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>76.7878787878788</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1.661250644994837</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0.007592234262119746</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>2442601.010101011</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0.07383838383838182</v>
+      </c>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="n">
+        <v>1.886628787878792</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.631288791832532</v>
+      </c>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="n">
+        <v>0.3582449494949496</v>
+      </c>
+      <c r="AU7" t="inlineStr"/>
+      <c r="AV7" t="n">
+        <v>1.40463383838383</v>
+      </c>
+      <c r="AW7" t="inlineStr"/>
+      <c r="AX7" t="n">
+        <v>-1.026376262626258</v>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr"/>
+      <c r="BA7" t="n">
+        <v>1.873836521450698</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0.1428553000147428</v>
+      </c>
+      <c r="BC7" t="inlineStr"/>
+      <c r="BD7" t="n">
+        <v>2074876.686200797</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>f18BYPMP</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45563.4375</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">schroder r 
+  ger </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mewa arena
+  mainz </t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>59</v>
+      </c>
+      <c r="H8" t="n">
+        <v>591</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>vZA6VYpf</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>4ljanukM</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="U8" t="n">
+        <v>-0.2000000000000002</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.333333333333334</v>
+      </c>
+      <c r="W8" t="n">
+        <v>3</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.8333333333333335</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-1.666666666666667</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>3.666666666666664</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>-3.666666666666664</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>75.05000000000001</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>75.59090909090909</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>-0.5020337301587325</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>4.638888888888886</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>3436458.333333334</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0.6687499999999993</v>
+      </c>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="n">
+        <v>2.798611111111114</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1.332936507936509</v>
+      </c>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="n">
+        <v>0.5805555555555557</v>
+      </c>
+      <c r="AU8" t="inlineStr"/>
+      <c r="AV8" t="n">
+        <v>2.554166666666674</v>
+      </c>
+      <c r="AW8" t="inlineStr"/>
+      <c r="AX8" t="n">
+        <v>-4.746527777777828</v>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr"/>
+      <c r="BA8" t="n">
+        <v>-1.779315476190476</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0.3732142857142855</v>
+      </c>
+      <c r="BC8" t="inlineStr"/>
+      <c r="BD8" t="n">
+        <v>1206914.682539683</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Q5hiEzKD</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45563.4375</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">zwayer f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">red bull arena
+  leipzig </t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>fTVNku3I</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>59</v>
+      </c>
+      <c r="H9" t="n">
+        <v>591</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>IXf9Q08n</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0jdIgO6t</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>8</v>
+      </c>
+      <c r="P9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>5</v>
+      </c>
+      <c r="R9" t="n">
+        <v>3</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="U9" t="n">
+        <v>-1.68</v>
+      </c>
+      <c r="V9" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="W9" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>73.08181818181818</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>72</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>-0.2131422305764374</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>5.881422305764403</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>21299074.07407407</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>-0.1542929292929358</v>
+      </c>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="n">
+        <v>7.00984848484849</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>5.483952067669179</v>
+      </c>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="n">
+        <v>0.9593434343434344</v>
+      </c>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="n">
+        <v>6.029629629629639</v>
+      </c>
+      <c r="AW9" t="inlineStr"/>
+      <c r="AX9" t="n">
+        <v>-1.918350168350088</v>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr"/>
+      <c r="BA9" t="n">
+        <v>0.5572133458646533</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0.4514411027568921</v>
+      </c>
+      <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="n">
+        <v>16039585.09555138</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>rsNyMnwK</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45562.64583333334</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">siebert d 
+  ger </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">signal iduna park
+  dortmund </t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>59</v>
+      </c>
+      <c r="H10" t="n">
+        <v>591</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>IkCftsQm</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>8f6APkLc</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>12</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>10</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.3099999999999998</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-1.235</v>
+      </c>
+      <c r="V10" t="n">
+        <v>2</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-10.33333333333333</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>-3.333333333333333</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>-8.166666666666668</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.8333333333333339</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>15.16666666666666</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>-15.16666666666666</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>74.72727272727272</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>77.36818181818182</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0.4576208307329637</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>7.018244660564477</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>30518112.37373738</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>-0.9239898989898983</v>
+      </c>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="n">
+        <v>9.401767676767676</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>9.140285867831622</v>
+      </c>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="n">
+        <v>1.386363636363637</v>
+      </c>
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="n">
+        <v>9.347979797979804</v>
+      </c>
+      <c r="AW10" t="inlineStr"/>
+      <c r="AX10" t="n">
+        <v>1.421717171717177</v>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr"/>
+      <c r="BA10" t="n">
+        <v>-0.6804196137576923</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0.672735507246377</v>
+      </c>
+      <c r="BC10" t="inlineStr"/>
+      <c r="BD10" t="n">
+        <v>20158975.23576728</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>dQ0zIIKl</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45557.60416666666</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jablonski s 
+  ger </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">millerntor stadion
+  hamburg </t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>59</v>
+      </c>
+      <c r="H11" t="n">
+        <v>591</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2VSFgl3c</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>6PecvuWE</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>2</v>
+      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="n">
+        <v>2</v>
+      </c>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.2000000000000002</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-1.48</v>
+      </c>
+      <c r="V11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W11" t="n">
+        <v>-11</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>72.125</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>82.7</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0.6958698830409311</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>-8.813961988304101</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>-23525909.09090909</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0.6250000000000036</v>
+      </c>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="n">
+        <v>-9.479545454545459</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>-8.445084064327489</v>
+      </c>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="n">
+        <v>-1.070454545454545</v>
+      </c>
+      <c r="AU11" t="inlineStr"/>
+      <c r="AV11" t="n">
+        <v>-9.115909090909099</v>
+      </c>
+      <c r="AW11" t="inlineStr"/>
+      <c r="AX11" t="n">
+        <v>3.547727272727229</v>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr"/>
+      <c r="BA11" t="n">
+        <v>-0.02224049707604081</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>-0.8421052631578947</v>
+      </c>
+      <c r="BC11" t="inlineStr"/>
+      <c r="BD11" t="n">
+        <v>-18286425.89546784</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>2k0SlKj2</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45557.52083333334</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">schroder r 
+  ger </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mhparena
+  stuttgart </t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>59</v>
+      </c>
+      <c r="H12" t="n">
+        <v>591</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>M5BRZDsC</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>4ljanukM</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>-5</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="V12" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="W12" t="n">
+        <v>3</v>
+      </c>
+      <c r="X12" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>74.88888888888889</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>-0.5274191232557115</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>-4.39124259658098</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>-23931111.11111111</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>-1.84151515151515</v>
+      </c>
+      <c r="AP12" t="inlineStr"/>
+      <c r="AQ12" t="n">
+        <v>-5.109797979797989</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>-4.977620313571634</v>
+      </c>
+      <c r="AS12" t="inlineStr"/>
+      <c r="AT12" t="n">
+        <v>-1.10919191919192</v>
+      </c>
+      <c r="AU12" t="inlineStr"/>
+      <c r="AV12" t="n">
+        <v>-6.720606060606059</v>
+      </c>
+      <c r="AW12" t="inlineStr"/>
+      <c r="AX12" t="n">
+        <v>0.1548484848484861</v>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr"/>
+      <c r="BA12" t="n">
+        <v>1.563346449563767</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>-0.4864241405944532</v>
+      </c>
+      <c r="BC12" t="inlineStr"/>
+      <c r="BD12" t="n">
+        <v>-15033622.15721529</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Uy2KjtMk</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45557.4375</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">osmers h 
+  ger </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bayarena
+  leverkusen </t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>59</v>
+      </c>
+      <c r="H13" t="n">
+        <v>591</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>KUx4Q7x1</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>UgdQz0fK</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>5</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>10</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.7949999999999999</v>
+      </c>
+      <c r="V13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X13" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>-15</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>76.82272727272726</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>68.55555555555556</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>-0.2586931818181739</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>4.112165404040411</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>23992146.46464647</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0.9097979797979789</v>
+      </c>
+      <c r="AP13" t="inlineStr"/>
+      <c r="AQ13" t="n">
+        <v>3.881047979797984</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>5.076849747474739</v>
+      </c>
+      <c r="AS13" t="inlineStr"/>
+      <c r="AT13" t="n">
+        <v>0.3979166666666665</v>
+      </c>
+      <c r="AU13" t="inlineStr"/>
+      <c r="AV13" t="n">
+        <v>5.024053030303037</v>
+      </c>
+      <c r="AW13" t="inlineStr"/>
+      <c r="AX13" t="n">
+        <v>-1.054027777777776</v>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr"/>
+      <c r="BA13" t="n">
+        <v>-4.701824494949477</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0.5397979797979799</v>
+      </c>
+      <c r="BC13" t="inlineStr"/>
+      <c r="BD13" t="n">
+        <v>25135565.02525252</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>IcrFCNr9</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45556.5625</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brych f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">deutsche bank park
+  frankfurt </t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>59</v>
+      </c>
+      <c r="H14" t="n">
+        <v>591</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>f3ddUIXs</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>GzfvcwRj</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>-3</v>
+      </c>
+      <c r="P14" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-0.2399999999999998</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="V14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W14" t="n">
+        <v>-2</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>72</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>-3.547361920116497</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>3.017518289300327</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>3747727.272727279</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AP14" t="inlineStr"/>
+      <c r="AQ14" t="n">
+        <v>2.909090909090907</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>-2.832164898412032</v>
+      </c>
+      <c r="AS14" t="inlineStr"/>
+      <c r="AT14" t="n">
+        <v>0.1136363636363638</v>
+      </c>
+      <c r="AU14" t="inlineStr"/>
+      <c r="AV14" t="n">
+        <v>1.204545454545453</v>
+      </c>
+      <c r="AW14" t="inlineStr"/>
+      <c r="AX14" t="n">
+        <v>0.8636363636364308</v>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr"/>
+      <c r="BA14" t="n">
+        <v>2.322498873171071</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0.05070296789404338</v>
+      </c>
+      <c r="BC14" t="inlineStr"/>
+      <c r="BD14" t="n">
+        <v>-52765.15151515137</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>hvFA1cz8</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45556.4375</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">schlager d 
+  ger </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadion an der alten forsterei
+  berlin </t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>59</v>
+      </c>
+      <c r="H15" t="n">
+        <v>591</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>IXf9Q08n</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>hAcTWKKN</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="U15" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="V15" t="n">
+        <v>-3</v>
+      </c>
+      <c r="W15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="X15" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>-16.5</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>70.27272727272727</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>77.27272727272727</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1.163076739259601</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>-1.852227702675279</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>-1216666.666666667</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>-0.4681818181818151</v>
+      </c>
+      <c r="AP15" t="inlineStr"/>
+      <c r="AQ15" t="n">
+        <v>-0.05580808080809163</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0.006264554570179826</v>
+      </c>
+      <c r="AS15" t="inlineStr"/>
+      <c r="AT15" t="n">
+        <v>-0.2424242424242424</v>
+      </c>
+      <c r="AU15" t="inlineStr"/>
+      <c r="AV15" t="n">
+        <v>0.5770202020202078</v>
+      </c>
+      <c r="AW15" t="inlineStr"/>
+      <c r="AX15" t="n">
+        <v>0.1093434343434012</v>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr"/>
+      <c r="BA15" t="n">
+        <v>-1.778318442001279</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>-0.08164297339489135</v>
+      </c>
+      <c r="BC15" t="inlineStr"/>
+      <c r="BD15" t="n">
+        <v>-2671822.229880095</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>QNoNA1DL</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45556.4375</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">siebert d 
+  ger </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">voith arena
+  heidenheim </t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>59</v>
+      </c>
+      <c r="H16" t="n">
+        <v>591</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>IkCftsQm</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>8f6APkLc</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U16" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="V16" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W16" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="X16" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>73.44444444444444</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>82.27272727272727</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>-0.4511840062111716</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>-4.951165380513203</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>-6957013.888888888</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0.65902777777778</v>
+      </c>
+      <c r="AP16" t="inlineStr"/>
+      <c r="AQ16" t="n">
+        <v>-3.612499999999997</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>-4.828286749482416</v>
+      </c>
+      <c r="AS16" t="inlineStr"/>
+      <c r="AT16" t="n">
+        <v>-0.6944444444444444</v>
+      </c>
+      <c r="AU16" t="inlineStr"/>
+      <c r="AV16" t="n">
+        <v>-2.990277777777777</v>
+      </c>
+      <c r="AW16" t="inlineStr"/>
+      <c r="AX16" t="n">
+        <v>4.482638888888971</v>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr"/>
+      <c r="BA16" t="n">
+        <v>1.784423230754754</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>-0.6148362507058158</v>
+      </c>
+      <c r="BC16" t="inlineStr"/>
+      <c r="BD16" t="n">
+        <v>-6286425.787376875</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>AeNg5uyq</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45556.4375</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reichel t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">weserstadion
+  bremen </t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>59</v>
+      </c>
+      <c r="H17" t="n">
+        <v>591</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>vZA6VYpf</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>K6A2elS9</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>-25</v>
+      </c>
+      <c r="P17" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>-12</v>
+      </c>
+      <c r="R17" t="n">
+        <v>-2</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>-3.165</v>
+      </c>
+      <c r="U17" t="n">
+        <v>-0.5999999999999999</v>
+      </c>
+      <c r="V17" t="n">
+        <v>-12</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2</v>
+      </c>
+      <c r="X17" t="n">
+        <v>-7.666666666666666</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>-4.333333333333333</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>-19</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>80.45454545454545</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>72.125</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>-1.89828431372549</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>-7.269872477976719</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>-43920454.54545455</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0.2272727272727302</v>
+      </c>
+      <c r="AP17" t="inlineStr"/>
+      <c r="AQ17" t="n">
+        <v>-9.477272727272734</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>-11.32073209718669</v>
+      </c>
+      <c r="AS17" t="inlineStr"/>
+      <c r="AT17" t="n">
+        <v>-1.695454545454545</v>
+      </c>
+      <c r="AU17" t="inlineStr"/>
+      <c r="AV17" t="n">
+        <v>-8.968181818181819</v>
+      </c>
+      <c r="AW17" t="inlineStr"/>
+      <c r="AX17" t="n">
+        <v>0.2590909090909008</v>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr"/>
+      <c r="BA17" t="n">
+        <v>1.72792163967037</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>-1.521302216538789</v>
+      </c>
+      <c r="BC17" t="inlineStr"/>
+      <c r="BD17" t="n">
+        <v>-36536403.54148906</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>pY1dP0SE</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45556.4375</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reichel t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vonovia ruhrstadion
+  bochum </t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>59</v>
+      </c>
+      <c r="H18" t="n">
+        <v>591</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>YZPE6Sx7</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>K6A2elS9</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>-1.04</v>
+      </c>
+      <c r="U18" t="n">
+        <v>-0.1699999999999999</v>
+      </c>
+      <c r="V18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>-11</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>76.18181818181819</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>-1.721333888419803</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>4.280642629858946</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1145154.671717172</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>1.018055555555559</v>
+      </c>
+      <c r="AP18" t="inlineStr"/>
+      <c r="AQ18" t="n">
+        <v>2.234595959595964</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>1.064726209463046</v>
+      </c>
+      <c r="AS18" t="inlineStr"/>
+      <c r="AT18" t="n">
+        <v>-0.1118055555555555</v>
+      </c>
+      <c r="AU18" t="inlineStr"/>
+      <c r="AV18" t="n">
+        <v>3.092992424242425</v>
+      </c>
+      <c r="AW18" t="inlineStr"/>
+      <c r="AX18" t="n">
+        <v>-1.625189393939422</v>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr"/>
+      <c r="BA18" t="n">
+        <v>-2.55337283438098</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>-0.04421977124183041</v>
+      </c>
+      <c r="BC18" t="inlineStr"/>
+      <c r="BD18" t="n">
+        <v>693022.8904759672</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>dCL13J5e</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45555.64583333334</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brand b 
+  ger </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
         <is>
           <t xml:space="preserve">wwk arena
   augsburg </t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>fTVNku3I</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>ILyJuN3g</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
         <v>59</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H19" t="n">
         <v>591</v>
       </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
         <v>20242025</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>germany</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>4ljanukM</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0jdIgO6t</t>
-        </is>
-      </c>
-      <c r="O3" t="n">
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2VSFgl3c</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>4fuCGs9P</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
         <v>1</v>
       </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="n">
-        <v>3</v>
-      </c>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>-0.21</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0.7350000000000001</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0.6666666666666667</v>
-      </c>
-      <c r="X3" t="n">
+      <c r="P19" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>6</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="U19" t="n">
+        <v>-3.965</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>-6</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
         <v>-1</v>
       </c>
-      <c r="Y3" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1.333333333333334</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0.3333333333333339</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>-3.333333333333333</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.666666666666667</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>-4.333333333333334</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.333333333333334</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>-15.33333333333334</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>15.33333333333334</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>73.27272727272727</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>70.95454545454545</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>-132</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>2217871.066555277</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>-0.1243386243386269</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>2218047.138047139</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>-1.592255892255935</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>3.009579504316335</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>2325000</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>-0.4525252525252519</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>-125</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0.1111111111111109</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0.4682539682539684</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>2.752158173210816</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>-0.7299637983848299</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>-2.133333333333333</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>3.021885521885537</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>2.454545454545453</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>-2</v>
-      </c>
-      <c r="BE3" t="n">
+      <c r="AB19" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>-7</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>71.68181818181819</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>-0.8706244778613197</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>-0.5393170426065126</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>-1614351.851851852</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>-1.713888888888885</v>
+      </c>
+      <c r="AP19" t="inlineStr"/>
+      <c r="AQ19" t="n">
+        <v>-0.6388888888888999</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0.9180346700083533</v>
+      </c>
+      <c r="AS19" t="inlineStr"/>
+      <c r="AT19" t="n">
+        <v>-0.4694444444444448</v>
+      </c>
+      <c r="AU19" t="inlineStr"/>
+      <c r="AV19" t="n">
+        <v>-1.246296296296308</v>
+      </c>
+      <c r="AW19" t="inlineStr"/>
+      <c r="AX19" t="n">
+        <v>0.6898148148147527</v>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr"/>
+      <c r="BA19" t="n">
+        <v>-0.2005952380952181</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>-0.02421679197994964</v>
+      </c>
+      <c r="BC19" t="inlineStr"/>
+      <c r="BD19" t="n">
+        <v>1088288.69047619</v>
+      </c>
+      <c r="BE19" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_preparation/df_constructed.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_constructed.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE3"/>
+  <dimension ref="A1:DP19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,215 +500,530 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>h2h_35</t>
+          <t>result</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>h2h_3</t>
+          <t>dif_mean_last_30_matches_expected_goals_(xg)</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>h2h_35_segun_loc</t>
+          <t>dif_mean_last_30_matches_expected_goals_(xg)_against</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>h2h_3_segun_loc</t>
+          <t>dif_mean_last_180_matches_expected_goals_(xg)</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>result</t>
+          <t>dif_mean_last_180_matches_expected_goals_(xg)_against</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_expected_goals_(xg)</t>
+          <t>dif_mean_last_30_matches_expected_points</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
+          <t>dif_mean_last_30_matches_expected_points_against</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_goals</t>
+          <t>dif_mean_last_180_matches_expected_points</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_goals_against</t>
+          <t>dif_mean_last_180_matches_expected_points_against</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_n_matches_last_days</t>
+          <t>dif_mean_last_30_matches_shots_on_goal</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_n_matches_last_days_against</t>
+          <t>dif_mean_last_30_matches_shots_on_goal_against</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_fouls</t>
+          <t>dif_mean_last_180_matches_shots_on_goal</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_fouls_against</t>
+          <t>dif_mean_last_180_matches_shots_on_goal_against</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_points</t>
+          <t>dif_mean_last_30_matches_goal_attempts</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_points_against</t>
+          <t>dif_mean_last_30_matches_goal_attempts_against</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
+          <t>dif_mean_last_180_matches_goal_attempts</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
+          <t>dif_mean_last_180_matches_goal_attempts_against</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_goal_attempts</t>
+          <t>dif_mean_last_30_matches_goals</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_goal_attempts_against</t>
+          <t>dif_mean_last_30_matches_goals_against</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_ball_possession</t>
+          <t>dif_mean_last_180_matches_goals</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_ball_possession_against</t>
+          <t>dif_mean_last_180_matches_goals_against</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>mean_last_match_mean_rat_player_start_home_against</t>
+          <t>dif_mean_last_30_matches_points</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>mean_last_match_mean_rat_player_start_away_against</t>
+          <t>dif_mean_last_30_matches_points_against</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_int_rep_player_miss</t>
+          <t>dif_mean_last_180_matches_points</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_180_matches_points_against</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_goal_ratio</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_goal_ratio_against</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_goal_ratio</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_goal_ratio_against</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_PPS</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_PPS_against</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_PPS</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_PPS_against</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_attacks</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_attacks_against</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_attacks</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_attacks_against</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_dangerous_attacks</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_dangerous_attacks_against</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_dangerous_attacks</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_dangerous_attacks_against</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_dead_balls</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_dead_balls_against</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_dead_balls</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_dead_balls_against</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_ball_possession</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_ball_possession_against</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_ball_possession</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_ball_possession_against</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_total_passes</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_total_passes_against</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_total_passes</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_total_passes_against</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_attacking_efficiency</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_attacking_efficiency_against</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_attacking_efficiency</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_attacking_efficiency_against</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_yellow_cards</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_yellow_cards_against</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_yellow_cards</t>
+        </is>
+      </c>
+      <c r="BW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_yellow_cards_against</t>
+        </is>
+      </c>
+      <c r="BX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_red_cards</t>
+        </is>
+      </c>
+      <c r="BY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_red_cards_against</t>
+        </is>
+      </c>
+      <c r="BZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_red_cards</t>
+        </is>
+      </c>
+      <c r="CA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_red_cards_against</t>
+        </is>
+      </c>
+      <c r="CB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_defensive_actions</t>
+        </is>
+      </c>
+      <c r="CC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_defensive_actions_against</t>
+        </is>
+      </c>
+      <c r="CD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_defensive_actions</t>
+        </is>
+      </c>
+      <c r="CE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_defensive_actions_against</t>
+        </is>
+      </c>
+      <c r="CF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_PPDA</t>
+        </is>
+      </c>
+      <c r="CG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_PPDA_against</t>
+        </is>
+      </c>
+      <c r="CH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_PPDA</t>
+        </is>
+      </c>
+      <c r="CI1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_PPDA_against</t>
+        </is>
+      </c>
+      <c r="CJ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_KGP</t>
+        </is>
+      </c>
+      <c r="CK1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_KGP_against</t>
+        </is>
+      </c>
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_KGP</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_KGP_against</t>
+        </is>
+      </c>
+      <c r="CN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_clean_sheet</t>
+        </is>
+      </c>
+      <c r="CO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_clean_sheet_against</t>
+        </is>
+      </c>
+      <c r="CP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_clean_sheet</t>
+        </is>
+      </c>
+      <c r="CQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_clean_sheet_against</t>
+        </is>
+      </c>
+      <c r="CR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_defensive_efficiency</t>
+        </is>
+      </c>
+      <c r="CS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_defensive_efficiency_against</t>
+        </is>
+      </c>
+      <c r="CT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_defensive_efficiency</t>
+        </is>
+      </c>
+      <c r="CU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_defensive_efficiency_against</t>
+        </is>
+      </c>
+      <c r="CV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_efficiency</t>
+        </is>
+      </c>
+      <c r="CW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_efficiency_against</t>
+        </is>
+      </c>
+      <c r="CX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_efficiency</t>
+        </is>
+      </c>
+      <c r="CY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_efficiency_against</t>
+        </is>
+      </c>
+      <c r="CZ1" s="1" t="inlineStr">
+        <is>
+          <t>mean_last_180_matches_mean_rat_player_start_home_against</t>
+        </is>
+      </c>
+      <c r="DA1" s="1" t="inlineStr">
+        <is>
+          <t>mean_last_180_matches_mean_rat_player_start_away_against</t>
+        </is>
+      </c>
+      <c r="DB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="DC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="DD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_miss</t>
+        </is>
+      </c>
+      <c r="DE1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_hei_player_miss</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="DF1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_sub</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="DG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_sub</t>
+        </is>
+      </c>
+      <c r="DH1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_start</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="DI1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="DJ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="DK1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="DL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="DM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_start</t>
+        </is>
+      </c>
+      <c r="DN1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_rat_player_sub</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="DO1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_rat_player_start</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="DP1" s="1" t="inlineStr">
         <is>
           <t>is_rival_match</t>
         </is>
@@ -717,32 +1032,32 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>8OhVCWxh</t>
+          <t>nc8W6DTp</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45550.52083333334</v>
+        <v>45571.60416666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">brand b 
+          <t xml:space="preserve">jollenbeck m 
   ger </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mewa arena
-  mainz </t>
+          <t xml:space="preserve">mhparena
+  stuttgart </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>EuakNmc1</t>
+          <t>nJQmYp1B</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ig1f1fy3</t>
+          <t>hQAtP9Sl</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -774,325 +1089,6523 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>IkCftsQm</t>
+          <t>KUx4Q7x1</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-1</v>
+        <v>1.965</v>
       </c>
       <c r="Q2" t="n">
-        <v>-6</v>
+        <v>-1.02</v>
       </c>
       <c r="R2" t="n">
-        <v>-1</v>
+        <v>0.4555454545454545</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>-0.4969999999999997</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.53</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1000000000000001</v>
+        <v>-1.666666666666667</v>
       </c>
       <c r="V2" t="n">
+        <v>0.6346153846153846</v>
+      </c>
+      <c r="W2" t="n">
+        <v>-0.8269230769230769</v>
+      </c>
+      <c r="X2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1.257575757575758</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>-2.159090909090909</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.310606060606061</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>-5.143939393939393</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.2954545454545454</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>-1.03030303030303</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.4294871794871795</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>-0.4935897435897436</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>-1.883928571428571</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>5.441666666666666</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>-1.826981474407945</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1.487694783666651</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>-55.00129881287495</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>67.50569573872335</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>-93.06805582497978</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>35.49568545587718</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>34</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>-29</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0.5454545454545467</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>-14.22727272727273</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>-32</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>-4.190909090909095</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>-6.872727272727275</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>-0.205128205128208</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>-1.46153846153846</v>
+      </c>
+      <c r="BH2" t="n">
         <v>-1.5</v>
       </c>
-      <c r="W2" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="AE2" t="n">
+      <c r="BI2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>6.159090909090907</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>-6.159090909090907</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>102</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>-102</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>118.8454545454545</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>-65.13636363636363</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>1.035</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>-0.9800000000000001</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>-0.310090909090909</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>-0.4484545454545455</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>0.2651515151515154</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>0.9318181818181819</v>
+      </c>
+      <c r="BX2" t="inlineStr"/>
+      <c r="BY2" t="inlineStr"/>
+      <c r="BZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>-1.666666666666667</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>-2.333333333333333</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>1.083333333333334</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>-0.4166666666666661</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>-6.791666666666671</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>27.53767507002801</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>-12.38042530568846</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>15.23111436394858</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>-0.02049062049062048</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>0.06555491661874641</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>-0.002834329941154234</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>-0.00686269089352573</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>0.2243589743589744</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>0.9800000000000001</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>-1.035</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>0.4484545454545455</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>0.310090909090909</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>2.015000000000001</v>
+      </c>
+      <c r="CW2" t="n">
+        <v>-2.015000000000001</v>
+      </c>
+      <c r="CX2" t="n">
+        <v>0.1383636363636365</v>
+      </c>
+      <c r="CY2" t="n">
+        <v>-0.1383636363636365</v>
+      </c>
+      <c r="CZ2" t="n">
+        <v>76.92425820707071</v>
+      </c>
+      <c r="DA2" t="n">
+        <v>75.49447199265381</v>
+      </c>
+      <c r="DB2" t="inlineStr"/>
+      <c r="DC2" t="n">
+        <v>-0.08178590415431586</v>
+      </c>
+      <c r="DD2" t="inlineStr"/>
+      <c r="DE2" t="inlineStr"/>
+      <c r="DF2" t="n">
+        <v>-0.7537439856325356</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>2812.686127082412</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>-0.2728282828283284</v>
+      </c>
+      <c r="DI2" t="inlineStr"/>
+      <c r="DJ2" t="inlineStr"/>
+      <c r="DK2" t="inlineStr"/>
+      <c r="DL2" t="n">
+        <v>-2.919797979797981</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>-2078.383838383841</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>0.7446387805521084</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>0.03363636363634726</v>
+      </c>
+      <c r="DP2" t="n">
         <v>1</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>6</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>75.90000000000001</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>73.33333333333333</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>-0.6666666666666667</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>3.666666666666657</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>-139</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>81209.15032679681</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>0.360675381263615</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>763468.0134680141</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>-0.2468013468013055</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>0.9175381263616487</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>-5100000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>1.111784511784514</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>-142</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0.401010101010101</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0.2042483660130714</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>0.3588235294117794</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>-0.6049019607843036</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>0.981144781144792</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>0.1161616161616337</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>CnrLfkNN</t>
+          <t>ShoJUGLi</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45550.4375</v>
+        <v>45571.52083333334</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">zwayer f 
+          <t xml:space="preserve">dankert b 
   ger </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">deutsche bank park
+  frankfurt </t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>59</v>
+      </c>
+      <c r="H3" t="n">
+        <v>591</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>UgdQz0fK</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>K6A2elS9</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>-0.9749999999999996</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.205</v>
+      </c>
+      <c r="R3" t="n">
+        <v>-0.476</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.5200000000000002</v>
+      </c>
+      <c r="T3" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="V3" t="n">
+        <v>-0.1666666666666667</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.3333333333333334</v>
+      </c>
+      <c r="X3" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>-1.545454545454546</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.8181818181818188</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>17</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>-1.636363636363637</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.909090909090908</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>-1.363636363636364</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.6363636363636365</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>-0.8333333333333335</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>11.60714285714286</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>-inf</t>
+        </is>
+      </c>
+      <c r="AP3" t="n">
+        <v>2.25988320948214</v>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>-inf</t>
+        </is>
+      </c>
+      <c r="AR3" t="n">
+        <v>650.5200534759358</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>-312.9914478479863</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>179.4093881272762</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>-77.10602141485546</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>-75</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>68</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>-13.7</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>7.299999999999997</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>-39</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>48</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>-11.4</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>8.666666666666668</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>3.666666666666668</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>0.6666666666666643</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>-27</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>27</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>-13.90909090909091</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>13.90909090909091</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>-480.5</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>216</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>-223</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>121.6</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>-2.525</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>-1.205</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>-1.024</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>0.07999999999999996</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>0.4000000000000001</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>-0.1000000000000001</v>
+      </c>
+      <c r="BX3" t="inlineStr"/>
+      <c r="BY3" t="inlineStr"/>
+      <c r="BZ3" t="inlineStr"/>
+      <c r="CA3" t="inlineStr"/>
+      <c r="CB3" t="n">
+        <v>1.333333333333334</v>
+      </c>
+      <c r="CC3" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="CE3" t="n">
+        <v>-0.3333333333333339</v>
+      </c>
+      <c r="CF3" t="n">
+        <v>16.63337218337219</v>
+      </c>
+      <c r="CG3" t="n">
+        <v>-100.5</v>
+      </c>
+      <c r="CH3" t="n">
+        <v>26.31679792429793</v>
+      </c>
+      <c r="CI3" t="n">
+        <v>-27.88731879231879</v>
+      </c>
+      <c r="CJ3" t="n">
+        <v>-0.07541241162608012</v>
+      </c>
+      <c r="CK3" t="n">
+        <v>-0.00765511684125704</v>
+      </c>
+      <c r="CL3" t="n">
+        <v>0.01240835414739212</v>
+      </c>
+      <c r="CM3" t="n">
+        <v>-0.01362827041115704</v>
+      </c>
+      <c r="CN3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP3" t="n">
+        <v>-0.3333333333333334</v>
+      </c>
+      <c r="CQ3" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="CR3" t="n">
+        <v>1.205</v>
+      </c>
+      <c r="CS3" t="n">
+        <v>2.525</v>
+      </c>
+      <c r="CT3" t="n">
+        <v>-0.07999999999999996</v>
+      </c>
+      <c r="CU3" t="n">
+        <v>1.024</v>
+      </c>
+      <c r="CV3" t="n">
+        <v>-1.32</v>
+      </c>
+      <c r="CW3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="CX3" t="n">
+        <v>-1.104</v>
+      </c>
+      <c r="CY3" t="n">
+        <v>1.104</v>
+      </c>
+      <c r="CZ3" t="n">
+        <v>75.895070496633</v>
+      </c>
+      <c r="DA3" t="n">
+        <v>75.46865625956535</v>
+      </c>
+      <c r="DB3" t="inlineStr"/>
+      <c r="DC3" t="n">
+        <v>1.908433881145584</v>
+      </c>
+      <c r="DD3" t="inlineStr"/>
+      <c r="DE3" t="inlineStr"/>
+      <c r="DF3" t="n">
+        <v>-5.165933014354067</v>
+      </c>
+      <c r="DG3" t="n">
+        <v>-58570.06102212052</v>
+      </c>
+      <c r="DH3" t="n">
+        <v>1.872727272727303</v>
+      </c>
+      <c r="DI3" t="inlineStr"/>
+      <c r="DJ3" t="inlineStr"/>
+      <c r="DK3" t="inlineStr"/>
+      <c r="DL3" t="n">
+        <v>-1.236363636363635</v>
+      </c>
+      <c r="DM3" t="n">
+        <v>-43818.18181818182</v>
+      </c>
+      <c r="DN3" t="n">
+        <v>-10.88169810230453</v>
+      </c>
+      <c r="DO3" t="n">
+        <v>-5.781818181818181</v>
+      </c>
+      <c r="DP3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0KbQSfj4</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45571.4375</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hartmann r 
+  ger </t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">voith arena
+  heidenheim </t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>59</v>
+      </c>
+      <c r="H4" t="n">
+        <v>591</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>4ljanukM</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>pfoInmcq</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.2000000000000002</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.4550000000000001</v>
+      </c>
+      <c r="R4" t="n">
+        <v>-0.07099999999999995</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.02299999999999991</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.09090909090909083</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>-0.454545454545455</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>-0.3636363636363633</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.545454545454545</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.3636363636363636</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>-0.4166666666666667</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.5833333333333333</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0.5401785714285716</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0.1589743589743593</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>-1.065360211683741</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>-1.003690833355905</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>197.9990627077636</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>-86.01370714683716</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>99.69988248621357</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>-35.40205709654364</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>-83</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>47</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>-16.8</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>16.10000000000001</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>26</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>9.200000000000003</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>8.333333333333336</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>4.666666666666668</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>-23</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>23</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>-6.363636363636367</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>6.363636363636367</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>-381</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>214.5</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>-163</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>42.79999999999995</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>0.7999999999999999</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>3.045</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>0.07099999999999997</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>0.477</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>-0.1363636363636365</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>-0.209090909090909</v>
+      </c>
+      <c r="BX4" t="inlineStr"/>
+      <c r="BY4" t="inlineStr"/>
+      <c r="BZ4" t="inlineStr"/>
+      <c r="CA4" t="inlineStr"/>
+      <c r="CB4" t="n">
+        <v>2</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>-1.666666666666667</v>
+      </c>
+      <c r="CD4" t="n">
+        <v>3</v>
+      </c>
+      <c r="CE4" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF4" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="CG4" t="n">
+        <v>-40.37232504337767</v>
+      </c>
+      <c r="CH4" t="n">
+        <v>-4.997077922077928</v>
+      </c>
+      <c r="CI4" t="n">
+        <v>-25.4460537957055</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>0.0576923076923077</v>
+      </c>
+      <c r="CK4" t="n">
+        <v>0.05541125541125541</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>-0.009637563580913326</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>-0.001219664160652847</v>
+      </c>
+      <c r="CN4" t="n">
+        <v>-0.6666666666666666</v>
+      </c>
+      <c r="CO4" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="CP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ4" t="n">
+        <v>-0.08333333333333333</v>
+      </c>
+      <c r="CR4" t="n">
+        <v>-3.045</v>
+      </c>
+      <c r="CS4" t="n">
+        <v>-0.7999999999999999</v>
+      </c>
+      <c r="CT4" t="n">
+        <v>-0.477</v>
+      </c>
+      <c r="CU4" t="n">
+        <v>-0.07099999999999997</v>
+      </c>
+      <c r="CV4" t="n">
+        <v>-2.245</v>
+      </c>
+      <c r="CW4" t="n">
+        <v>2.245</v>
+      </c>
+      <c r="CX4" t="n">
+        <v>-0.406</v>
+      </c>
+      <c r="CY4" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="CZ4" t="n">
+        <v>74.98883379247015</v>
+      </c>
+      <c r="DA4" t="n">
+        <v>75.30391796755433</v>
+      </c>
+      <c r="DB4" t="inlineStr"/>
+      <c r="DC4" t="n">
+        <v>1.232368421052655</v>
+      </c>
+      <c r="DD4" t="inlineStr"/>
+      <c r="DE4" t="inlineStr"/>
+      <c r="DF4" t="n">
+        <v>1.766008771929823</v>
+      </c>
+      <c r="DG4" t="n">
+        <v>-30199.12280701755</v>
+      </c>
+      <c r="DH4" t="n">
+        <v>5.657828282828319</v>
+      </c>
+      <c r="DI4" t="inlineStr"/>
+      <c r="DJ4" t="inlineStr"/>
+      <c r="DK4" t="inlineStr"/>
+      <c r="DL4" t="n">
+        <v>1.168434343434349</v>
+      </c>
+      <c r="DM4" t="n">
+        <v>-31833.58585858586</v>
+      </c>
+      <c r="DN4" t="n">
+        <v>-7.938991228070179</v>
+      </c>
+      <c r="DO4" t="n">
+        <v>-7.307777777777773</v>
+      </c>
+      <c r="DP4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>zwD8uYZ9</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45570.5625</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">storks s 
+  ger </t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">millerntor stadion
+  hamburg </t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>59</v>
+      </c>
+      <c r="H5" t="n">
+        <v>591</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0jdIgO6t</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>vZA6VYpf</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-0.8749999999999998</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-0.3829999999999998</v>
+      </c>
+      <c r="S5" t="n">
+        <v>-0.407</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>-0.08333333333333348</v>
+      </c>
+      <c r="W5" t="n">
+        <v>-0.08333333333333348</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>-0.09090909090909083</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.5454545454545459</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>-0.6363636363636349</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>-3.545454545454545</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>-0.8181818181818181</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.1818181818181819</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>-0.6666666666666666</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.3333333333333335</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>-4.557575757575758</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>-0.4388888888888891</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>-0.6435376754858755</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.738497939968529</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>-111.9862445042773</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>-194.4990577629698</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>-83.71210510475964</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>4.600192711880169</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>-12</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>14.80000000000001</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>-10.7</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>-28</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>26</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>-1.899999999999999</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>-11</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>-1.666666666666668</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>-7.666666666666664</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>-4.166666666666671</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>-6.083333333333332</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>9.090909090909093</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>-9.090909090909093</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>85.5</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>179</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>-48.60000000000002</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>0.3749999999999998</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>-0.5170000000000001</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>0.507</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>2</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>-0.4181818181818184</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>-0.04545454545454541</v>
+      </c>
+      <c r="BX5" t="inlineStr"/>
+      <c r="BY5" t="inlineStr"/>
+      <c r="BZ5" t="n">
+        <v>0.3333333333333334</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>-0.6666666666666666</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>2</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>10.33333333333333</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>-2.25</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>38.61340909090909</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>2.268020541549951</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>8.310033486121725</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>44.69587153386689</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>-0.02857142857142858</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>0.01645123384253819</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>0.03398433141122618</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>-0.03301314490696546</v>
+      </c>
+      <c r="CN5" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="CO5" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="CP5" t="n">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="CQ5" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="CR5" t="n">
+        <v>-0.3749999999999998</v>
+      </c>
+      <c r="CS5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="CT5" t="n">
+        <v>-0.507</v>
+      </c>
+      <c r="CU5" t="n">
+        <v>0.5170000000000001</v>
+      </c>
+      <c r="CV5" t="n">
+        <v>-1.125</v>
+      </c>
+      <c r="CW5" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="CX5" t="n">
+        <v>-1.024</v>
+      </c>
+      <c r="CY5" t="n">
+        <v>1.024</v>
+      </c>
+      <c r="CZ5" t="n">
+        <v>71.16381313131312</v>
+      </c>
+      <c r="DA5" t="n">
+        <v>74.54085858585859</v>
+      </c>
+      <c r="DB5" t="inlineStr"/>
+      <c r="DC5" t="n">
+        <v>0.1455206644061207</v>
+      </c>
+      <c r="DD5" t="inlineStr"/>
+      <c r="DE5" t="inlineStr"/>
+      <c r="DF5" t="n">
+        <v>-0.4935991940635951</v>
+      </c>
+      <c r="DG5" t="n">
+        <v>-5309.434861663964</v>
+      </c>
+      <c r="DH5" t="n">
+        <v>2.259393939393931</v>
+      </c>
+      <c r="DI5" t="inlineStr"/>
+      <c r="DJ5" t="inlineStr"/>
+      <c r="DK5" t="inlineStr"/>
+      <c r="DL5" t="n">
+        <v>-0.8874747474747444</v>
+      </c>
+      <c r="DM5" t="n">
+        <v>-11515.55555555556</v>
+      </c>
+      <c r="DN5" t="n">
+        <v>-2.215282814880325</v>
+      </c>
+      <c r="DO5" t="n">
+        <v>-4.241818181818161</v>
+      </c>
+      <c r="DP5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>tbtaPLqC</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45570.4375</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">petersen m 
+  ger </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bayarena
+  leverkusen </t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>59</v>
+      </c>
+      <c r="H6" t="n">
+        <v>591</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>hAcTWKKN</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>A15eUM4C</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.725</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-1.66</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.291666666666667</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-0.6773333333333329</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.9761904761904761</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-0.7380952380952381</v>
+      </c>
+      <c r="X6" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.489510489510489</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-2.874125874125874</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>6.923076923076923</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>-6.888111888111888</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.286713286713286</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-0.5874125874125873</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.8571428571428572</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>-0.8214285714285714</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>-2.575</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>5.964285714285714</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>-2.500703390177073</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>2.475768675768676</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>-95.99558460040447</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>297.9960200603904</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>-50.32145217203518</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>7.034852245881183</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>71</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>-71</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>32.84999999999999</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>-23.25</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>58</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>-26</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>35.86666666666667</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>-21.05</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0.3333333333333321</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>-5</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>-1.416666666666664</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>-14.65476190476191</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>13</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>-13</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>6.86013986013986</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>-6.86013986013986</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>325.5</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>-270</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>161.3818181818181</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>-29.45454545454544</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>0.7750000000000001</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>-0.3400000000000001</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>0.2916666666666666</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>0.2106666666666666</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>0.1590909090909092</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>-0.2272727272727271</v>
+      </c>
+      <c r="BX6" t="inlineStr"/>
+      <c r="BY6" t="inlineStr"/>
+      <c r="BZ6" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>-1.666666666666667</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>-2.666666666666667</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>-3.845238095238095</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>0.3690476190476204</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>-15.37777777777778</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>36.43398268398269</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>17.38691207336929</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>29.00529397503082</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>-0.0533372194695424</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>-0.04032809295967191</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>0.01072089490727599</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>-0.01915070376269848</v>
+      </c>
+      <c r="CN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP6" t="n">
+        <v>0.0357142857142857</v>
+      </c>
+      <c r="CQ6" t="n">
+        <v>-0.08333333333333333</v>
+      </c>
+      <c r="CR6" t="n">
+        <v>0.3400000000000001</v>
+      </c>
+      <c r="CS6" t="n">
+        <v>-0.7750000000000001</v>
+      </c>
+      <c r="CT6" t="n">
+        <v>-0.2106666666666666</v>
+      </c>
+      <c r="CU6" t="n">
+        <v>-0.2916666666666666</v>
+      </c>
+      <c r="CV6" t="n">
+        <v>1.115</v>
+      </c>
+      <c r="CW6" t="n">
+        <v>-1.115</v>
+      </c>
+      <c r="CX6" t="n">
+        <v>0.08100000000000007</v>
+      </c>
+      <c r="CY6" t="n">
+        <v>-0.08100000000000007</v>
+      </c>
+      <c r="CZ6" t="n">
+        <v>75.75530303030303</v>
+      </c>
+      <c r="DA6" t="n">
+        <v>72.65452249770432</v>
+      </c>
+      <c r="DB6" t="inlineStr"/>
+      <c r="DC6" t="n">
+        <v>-4.115528322440099</v>
+      </c>
+      <c r="DD6" t="inlineStr"/>
+      <c r="DE6" t="inlineStr"/>
+      <c r="DF6" t="n">
+        <v>-0.5419607843137229</v>
+      </c>
+      <c r="DG6" t="n">
+        <v>43303.67968904733</v>
+      </c>
+      <c r="DH6" t="n">
+        <v>-2.145223063973106</v>
+      </c>
+      <c r="DI6" t="inlineStr"/>
+      <c r="DJ6" t="inlineStr"/>
+      <c r="DK6" t="inlineStr"/>
+      <c r="DL6" t="n">
+        <v>-0.6776515151515135</v>
+      </c>
+      <c r="DM6" t="n">
+        <v>44874.24242424242</v>
+      </c>
+      <c r="DN6" t="n">
+        <v>11.8799031986532</v>
+      </c>
+      <c r="DO6" t="n">
+        <v>12.22800925925927</v>
+      </c>
+      <c r="DP6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>dnhZQYKG</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45570.4375</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brand b 
+  ger </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">weserstadion
+  bremen </t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>59</v>
+      </c>
+      <c r="H7" t="n">
+        <v>591</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>4fuCGs9P</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>YZPE6Sx7</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>-1.655</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R7" t="n">
+        <v>-0.1079999999999999</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.7389999999999997</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.7272727272727275</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.727272727272727</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>-15</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>-0.8181818181818183</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>2.636363636363637</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.1818181818181819</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.08333333333333348</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>-0.1666666666666666</v>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="AO7" t="n">
+        <v>-3.980519480519479</v>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="AQ7" t="n">
+        <v>-2.417680704463001</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>80.4695823784059</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>-229.9978619048387</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>6.192504325664487</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>-67.40076537924762</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0.6999999999999886</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>-13</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>38</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>4.299999999999997</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>-6.666666666666668</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0.3333333333333357</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>1.666666666666668</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>-2.000000000000004</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>-20</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>20</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>-0.8181818181818201</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0.8181818181818201</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>-123.5</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>283</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>16.19999999999999</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>0.408</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>0.06099999999999994</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>-0.2454545454545454</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>0.5090909090909093</v>
+      </c>
+      <c r="BX7" t="inlineStr"/>
+      <c r="BY7" t="inlineStr"/>
+      <c r="BZ7" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>27.33333333333333</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>26.33333333333333</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>5.583333333333334</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>7.833333333333332</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>43.17936507936507</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>-40.6309731934732</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>24.32337662337664</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>-7.349240342990342</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>-0.02852852852852852</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>0.03023255813953489</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>0.001520030284340453</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>0.005245315210897022</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="CP7" t="n">
+        <v>-0.1666666666666667</v>
+      </c>
+      <c r="CQ7" t="n">
+        <v>0.08333333333333334</v>
+      </c>
+      <c r="CR7" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="CS7" t="n">
+        <v>-0.155</v>
+      </c>
+      <c r="CT7" t="n">
+        <v>-0.06099999999999994</v>
+      </c>
+      <c r="CU7" t="n">
+        <v>-0.408</v>
+      </c>
+      <c r="CV7" t="n">
+        <v>-0.5449999999999999</v>
+      </c>
+      <c r="CW7" t="n">
+        <v>0.5449999999999999</v>
+      </c>
+      <c r="CX7" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="CY7" t="n">
+        <v>-0.347</v>
+      </c>
+      <c r="CZ7" t="n">
+        <v>76.7433608815427</v>
+      </c>
+      <c r="DA7" t="n">
+        <v>73.95325987144169</v>
+      </c>
+      <c r="DB7" t="inlineStr"/>
+      <c r="DC7" t="n">
+        <v>2.585353498448143</v>
+      </c>
+      <c r="DD7" t="inlineStr"/>
+      <c r="DE7" t="inlineStr"/>
+      <c r="DF7" t="n">
+        <v>-1.968908786730829</v>
+      </c>
+      <c r="DG7" t="n">
+        <v>-9236.809787780305</v>
+      </c>
+      <c r="DH7" t="n">
+        <v>-0.2630303030302912</v>
+      </c>
+      <c r="DI7" t="inlineStr"/>
+      <c r="DJ7" t="inlineStr"/>
+      <c r="DK7" t="inlineStr"/>
+      <c r="DL7" t="n">
+        <v>0.4640404040404</v>
+      </c>
+      <c r="DM7" t="n">
+        <v>-3937.57575757576</v>
+      </c>
+      <c r="DN7" t="n">
+        <v>-4.393449989384848</v>
+      </c>
+      <c r="DO7" t="n">
+        <v>-1.593131313131309</v>
+      </c>
+      <c r="DP7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>lpXDJjDj</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45570.4375</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">badstubner f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadion an der alten forsterei
+  berlin </t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>59</v>
+      </c>
+      <c r="H8" t="n">
+        <v>591</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>hpYJ6izc</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>IkCftsQm</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>-0.2550000000000001</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-1.73</v>
+      </c>
+      <c r="R8" t="n">
+        <v>-0.3419999999999996</v>
+      </c>
+      <c r="S8" t="n">
+        <v>-0.4710000000000001</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>-0.9090909090909092</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.09090909090909083</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.6363636363636367</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.2727272727272716</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>-0.9999999999999998</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>-0.09090909090909105</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.3333333333333335</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>-0.6666666666666666</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>-0.4166666666666667</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>-3.067307692307693</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1.84375</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>-2.65237866708455</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0.4001928626928621</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>64.50173202460533</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>-41.00603839941223</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>97.90507748577124</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>-85.40342563240921</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>-47</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>83</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>31.59999999999999</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>-26</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>-2</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>-5.600000000000001</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0.3999999999999986</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>-3.666666666666668</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>3.666666666666664</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>4.750000000000004</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>7.750000000000004</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>-13.5</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>-15.18181818181818</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>15.18181818181818</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>-113.5</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>170</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>-214.6</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>123.1</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>-1.245</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>-1.27</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>-0.4580000000000002</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>0.4709999999999999</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>0.2272727272727271</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>0.2727272727272727</v>
+      </c>
+      <c r="BX8" t="inlineStr"/>
+      <c r="BY8" t="inlineStr"/>
+      <c r="BZ8" t="inlineStr"/>
+      <c r="CA8" t="inlineStr"/>
+      <c r="CB8" t="n">
+        <v>5.666666666666667</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>-0.3333333333333339</v>
+      </c>
+      <c r="CD8" t="n">
+        <v>4.583333333333334</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>-0.5833333333333321</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>-21.88677859807891</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>-7.194444444444443</v>
+      </c>
+      <c r="CH8" t="n">
+        <v>-4.061889519149588</v>
+      </c>
+      <c r="CI8" t="n">
+        <v>-17.54110375735375</v>
+      </c>
+      <c r="CJ8" t="n">
+        <v>-0.05541125541125541</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>-0.0576923076923077</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>-0.008367796376554708</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>-0.01709972184157607</v>
+      </c>
+      <c r="CN8" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="CO8" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="CP8" t="n">
+        <v>0.08333333333333331</v>
+      </c>
+      <c r="CQ8" t="n">
+        <v>0.08333333333333334</v>
+      </c>
+      <c r="CR8" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="CS8" t="n">
+        <v>1.245</v>
+      </c>
+      <c r="CT8" t="n">
+        <v>-0.4709999999999999</v>
+      </c>
+      <c r="CU8" t="n">
+        <v>0.4580000000000002</v>
+      </c>
+      <c r="CV8" t="n">
+        <v>0.02500000000000008</v>
+      </c>
+      <c r="CW8" t="n">
+        <v>-0.02500000000000008</v>
+      </c>
+      <c r="CX8" t="n">
+        <v>-0.9290000000000002</v>
+      </c>
+      <c r="CY8" t="n">
+        <v>0.9290000000000002</v>
+      </c>
+      <c r="CZ8" t="n">
+        <v>74.90596877869605</v>
+      </c>
+      <c r="DA8" t="n">
+        <v>75.34861340679522</v>
+      </c>
+      <c r="DB8" t="inlineStr"/>
+      <c r="DC8" t="n">
+        <v>1.042163561076592</v>
+      </c>
+      <c r="DD8" t="inlineStr"/>
+      <c r="DE8" t="inlineStr"/>
+      <c r="DF8" t="n">
+        <v>1.68290200138026</v>
+      </c>
+      <c r="DG8" t="n">
+        <v>-18198.54037267081</v>
+      </c>
+      <c r="DH8" t="n">
+        <v>0.4547474747474496</v>
+      </c>
+      <c r="DI8" t="inlineStr"/>
+      <c r="DJ8" t="inlineStr"/>
+      <c r="DK8" t="inlineStr"/>
+      <c r="DL8" t="n">
+        <v>0.4654545454545485</v>
+      </c>
+      <c r="DM8" t="n">
+        <v>-25911.51515151515</v>
+      </c>
+      <c r="DN8" t="n">
+        <v>-5.627463768115931</v>
+      </c>
+      <c r="DO8" t="n">
+        <v>-6.01474747474748</v>
+      </c>
+      <c r="DP8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>ENOasf5c</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45570.4375</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stegemann s 
+  ger </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vonovia ruhrstadion
+  bochum </t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>59</v>
+      </c>
+      <c r="H9" t="n">
+        <v>591</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>8f6APkLc</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>f3ddUIXs</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.4829999999999999</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.7931666666666661</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>-0.04761904761904767</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.05952380952380953</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.118881118881119</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.944055944055944</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>4.818181818181818</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>5.181818181818182</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>-0.2237762237762237</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.4405594405594406</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>-0.4761904761904762</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0.3452380952380953</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>-3.451680672268908</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0.9305555555555554</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>-2.820130322737275</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>-1.982745470903366</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>-79.99623809043705</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>-48.48147295742231</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1.12270871477773</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>-16.12194279477575</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>22</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>19.84999999999999</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>-4.533333333333331</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>-31</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>-6.149999999999999</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0.6000000000000014</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>-3.666666666666664</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>7.333333333333332</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>0.6190476190476204</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>7.833333333333336</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>-8</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>8</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>-1.692307692307693</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>1.692307692307693</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>-127.5</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>-9.850000000000023</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>-87.94999999999999</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>-0.6496666666666666</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>-0.4265</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>-0.04895104895104918</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>-2.076923076923077</v>
+      </c>
+      <c r="BX9" t="inlineStr"/>
+      <c r="BY9" t="inlineStr"/>
+      <c r="BZ9" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>-0.1666666666666666</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>5</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>-3.333333333333333</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>3.964285714285714</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>-0.9642857142857135</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>-26.71428571428572</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>25.01666666666667</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>-14.19814459777695</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>2.255292955954729</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>-0.01846785225718195</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>0.02570480928689884</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>0.01423141901354408</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>-0.008016567271462993</v>
+      </c>
+      <c r="CN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP9" t="n">
+        <v>-0.2619047619047619</v>
+      </c>
+      <c r="CQ9" t="n">
+        <v>0.2619047619047619</v>
+      </c>
+      <c r="CR9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="CS9" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="CT9" t="n">
+        <v>0.4265</v>
+      </c>
+      <c r="CU9" t="n">
+        <v>0.6496666666666666</v>
+      </c>
+      <c r="CV9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="CW9" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="CX9" t="n">
+        <v>-0.2231666666666668</v>
+      </c>
+      <c r="CY9" t="n">
+        <v>0.2231666666666668</v>
+      </c>
+      <c r="CZ9" t="n">
+        <v>75.43897306397305</v>
+      </c>
+      <c r="DA9" t="n">
+        <v>76.21740128558309</v>
+      </c>
+      <c r="DB9" t="inlineStr"/>
+      <c r="DC9" t="n">
+        <v>-2.20541068580539</v>
+      </c>
+      <c r="DD9" t="inlineStr"/>
+      <c r="DE9" t="inlineStr"/>
+      <c r="DF9" t="n">
+        <v>-1.236495215311006</v>
+      </c>
+      <c r="DG9" t="inlineStr"/>
+      <c r="DH9" t="n">
+        <v>-0.6158459595959584</v>
+      </c>
+      <c r="DI9" t="inlineStr"/>
+      <c r="DJ9" t="inlineStr"/>
+      <c r="DK9" t="inlineStr"/>
+      <c r="DL9" t="n">
+        <v>2.547777777777782</v>
+      </c>
+      <c r="DM9" t="n">
+        <v>-19027.95454545454</v>
+      </c>
+      <c r="DN9" t="n">
+        <v>-5.945163476874001</v>
+      </c>
+      <c r="DO9" t="n">
+        <v>-3.940189393939391</v>
+      </c>
+      <c r="DP9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>UajsPCkT</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45569.64583333334</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">welz t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
         <is>
           <t xml:space="preserve">wwk arena
   augsburg </t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>fTVNku3I</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>59</v>
+      </c>
+      <c r="H10" t="n">
+        <v>591</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2VSFgl3c</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>M5BRZDsC</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.7049999999999998</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-1.345</v>
+      </c>
+      <c r="R10" t="n">
+        <v>-0.256</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.3239999999999996</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="V10" t="n">
+        <v>-0.1666666666666666</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.5833333333333333</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-2.363636363636363</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.1818181818181817</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>-0.8181818181818183</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>-2.454545454545455</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0.09090909090909105</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0.2727272727272729</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0.08333333333333326</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0.08333333333333348</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>10.59444444444444</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>-1.607142857142857</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>3.106535131535132</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0.03132029792246538</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>313.0390445467988</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>-39.02005347593581</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>93.51121087599341</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>12.29536715314978</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>-24</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>9.599999999999994</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>-20.59999999999999</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>-2.299999999999997</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>13.33333333333333</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>-6.666666666666668</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>4.833333333333336</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>-0.4166666666666643</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>1.181818181818187</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>-1.181818181818187</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>-99.5</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>-145</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>-99.39999999999998</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>-64.19999999999993</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>1.295</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>0.845</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>0.2560000000000001</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>-0.02399999999999994</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>1.154545454545455</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>0.3181818181818181</v>
+      </c>
+      <c r="BX10" t="inlineStr"/>
+      <c r="BY10" t="inlineStr"/>
+      <c r="BZ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>33.33333333333334</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>30</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>11</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>8.583333333333332</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>-19.05182072829132</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>-25.32333333333333</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>-27.03328788858202</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>-7.207053169053168</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>-0.0646298472385429</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>0.02698412698412698</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>0.01879133894114408</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>-0.01980199593298356</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>-0.08333333333333333</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>-0.845</v>
+      </c>
+      <c r="CS10" t="n">
+        <v>-1.295</v>
+      </c>
+      <c r="CT10" t="n">
+        <v>0.02399999999999994</v>
+      </c>
+      <c r="CU10" t="n">
+        <v>-0.2560000000000001</v>
+      </c>
+      <c r="CV10" t="n">
+        <v>0.4500000000000002</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>-0.4500000000000002</v>
+      </c>
+      <c r="CX10" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="CY10" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="CZ10" t="n">
+        <v>75.36484848484848</v>
+      </c>
+      <c r="DA10" t="n">
+        <v>76.1870890725436</v>
+      </c>
+      <c r="DB10" t="inlineStr"/>
+      <c r="DC10" t="n">
+        <v>0.5219772256728845</v>
+      </c>
+      <c r="DD10" t="inlineStr"/>
+      <c r="DE10" t="inlineStr"/>
+      <c r="DF10" t="n">
+        <v>-0.4004618760339582</v>
+      </c>
+      <c r="DG10" t="n">
+        <v>-387.0733652312629</v>
+      </c>
+      <c r="DH10" t="n">
+        <v>-0.06801346801350405</v>
+      </c>
+      <c r="DI10" t="inlineStr"/>
+      <c r="DJ10" t="inlineStr"/>
+      <c r="DK10" t="inlineStr"/>
+      <c r="DL10" t="n">
+        <v>-0.1979797979797979</v>
+      </c>
+      <c r="DM10" t="n">
+        <v>-3538.720538720543</v>
+      </c>
+      <c r="DN10" t="n">
+        <v>-1.243360080042009</v>
+      </c>
+      <c r="DO10" t="n">
+        <v>-2.447811447811446</v>
+      </c>
+      <c r="DP10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>bFO8E4Vg</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45564.52083333334</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dankert b 
+  ger </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prezero arena
+  sinsheim </t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>59</v>
+      </c>
+      <c r="H11" t="n">
+        <v>591</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>hpYJ6izc</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>K6A2elS9</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.02666666666666673</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.4766666666666666</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.2672727272727278</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.1190909090909089</v>
+      </c>
+      <c r="T11" t="n">
+        <v>-0.6666666666666666</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="V11" t="n">
+        <v>-0.4166666666666667</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.5833333333333333</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.3333333333333339</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.916666666666667</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>4.666666666666667</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.333333333333332</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>2.833333333333334</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0.1666666666666679</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.3333333333333334</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0.8333333333333333</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0.5833333333333333</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>-0.08333333333333348</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0.4166666666666666</v>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>-inf</t>
+        </is>
+      </c>
+      <c r="AO11" t="n">
+        <v>4.101158645276292</v>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>-inf</t>
+        </is>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1.156939170171098</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>-197.6588902832629</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>270.6790685355983</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0.4623474429393752</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>21.73411660814301</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>-18.45454545454545</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>5.727272727272727</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>-10.72727272727273</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>-0.3333333333333357</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>-5.333333333333329</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>-0.0833333333333286</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>-1.916666666666671</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>7.666666666666671</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>-7.666666666666671</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>-6.75</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>34.66666666666669</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>-105.6666666666666</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>74.90909090909093</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>-91.63636363636368</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>0.3066666666666666</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>0.5233333333333333</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>0.6418181818181817</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>0.4263636363636364</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>-2.666666666666666</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>0.5530303030303032</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>-0.8863636363636362</v>
+      </c>
+      <c r="BX11" t="inlineStr"/>
+      <c r="BY11" t="inlineStr"/>
+      <c r="BZ11" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="CB11" t="n">
+        <v>-22.66666666666666</v>
+      </c>
+      <c r="CC11" t="n">
+        <v>-26.66666666666666</v>
+      </c>
+      <c r="CD11" t="n">
+        <v>-6.083333333333332</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>-6.833333333333334</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>-40.9026936026936</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>17.50406382832853</v>
+      </c>
+      <c r="CH11" t="n">
+        <v>-11.79228322182868</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>9.874691804036729</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>0.05171263964367413</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>-0.01269776322967813</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>0.02970575040999514</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>0.0154599121459746</v>
+      </c>
+      <c r="CN11" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="CO11" t="n">
+        <v>-0.6666666666666666</v>
+      </c>
+      <c r="CP11" t="n">
+        <v>-0.08333333333333333</v>
+      </c>
+      <c r="CQ11" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="CR11" t="n">
+        <v>-0.5233333333333333</v>
+      </c>
+      <c r="CS11" t="n">
+        <v>-0.3066666666666666</v>
+      </c>
+      <c r="CT11" t="n">
+        <v>-0.4263636363636364</v>
+      </c>
+      <c r="CU11" t="n">
+        <v>-0.6418181818181817</v>
+      </c>
+      <c r="CV11" t="n">
+        <v>-0.2166666666666668</v>
+      </c>
+      <c r="CW11" t="n">
+        <v>0.2166666666666668</v>
+      </c>
+      <c r="CX11" t="n">
+        <v>0.2154545454545454</v>
+      </c>
+      <c r="CY11" t="n">
+        <v>-0.2154545454545454</v>
+      </c>
+      <c r="CZ11" t="n">
+        <v>75.555463728191</v>
+      </c>
+      <c r="DA11" t="n">
+        <v>76.89770431588613</v>
+      </c>
+      <c r="DB11" t="inlineStr"/>
+      <c r="DC11" t="n">
+        <v>-1.491552499787815</v>
+      </c>
+      <c r="DD11" t="inlineStr"/>
+      <c r="DE11" t="inlineStr"/>
+      <c r="DF11" t="n">
+        <v>-0.2762244291656017</v>
+      </c>
+      <c r="DG11" t="n">
+        <v>7120.28350734233</v>
+      </c>
+      <c r="DH11" t="n">
+        <v>2.534141414141459</v>
+      </c>
+      <c r="DI11" t="inlineStr"/>
+      <c r="DJ11" t="inlineStr"/>
+      <c r="DK11" t="inlineStr"/>
+      <c r="DL11" t="n">
+        <v>0.7692929292929307</v>
+      </c>
+      <c r="DM11" t="n">
+        <v>9290.909090909096</v>
+      </c>
+      <c r="DN11" t="n">
+        <v>1.658399117222643</v>
+      </c>
+      <c r="DO11" t="n">
+        <v>0.6731313131313215</v>
+      </c>
+      <c r="DP11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>pWnjRsFa</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45564.4375</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">welz t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">holstein stadion
+  kiel </t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>59</v>
+      </c>
+      <c r="H12" t="n">
+        <v>591</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>8f6APkLc</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>M5BRZDsC</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-1.52</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.763333333333333</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-0.2718181818181815</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.09727272727272718</v>
+      </c>
+      <c r="T12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
+      </c>
+      <c r="V12" t="n">
+        <v>-0.1666666666666667</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.08333333333333326</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-2.666666666666667</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>-5.333333333333334</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>-2.416666666666668</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>3.583333333333332</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0.1666666666666665</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>-2.666666666666667</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>-0.08333333333333326</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0.6779178338001866</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>1.365546218487395</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>-0.7398511597621509</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>-0.6999794609701731</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>-32.34361842156554</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>-27.66415872695814</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>-54.73490480994337</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>27.19353568008989</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>-27.5</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>-25.36363636363636</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>5.181818181818187</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>-12</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>-14.18181818181818</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>11.63636363636364</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>13.33333333333333</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>0.8333333333333357</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>10.16666666666667</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>5.666666666666671</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>-5.666666666666671</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>-2.25</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>13.66666666666669</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>-20</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>-19.27272727272731</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>-69.27272727272725</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>0.1866666666666666</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>1.903333333333334</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>0.5445454545454546</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>-0.1881818181818181</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>0.2727272727272727</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>1.287878787878788</v>
+      </c>
+      <c r="BX12" t="inlineStr"/>
+      <c r="BY12" t="inlineStr"/>
+      <c r="BZ12" t="n">
+        <v>-0.3333333333333334</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="CB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC12" t="n">
+        <v>5.333333333333334</v>
+      </c>
+      <c r="CD12" t="n">
+        <v>3.083333333333334</v>
+      </c>
+      <c r="CE12" t="n">
+        <v>1.416666666666666</v>
+      </c>
+      <c r="CF12" t="n">
+        <v>-4.403921568627446</v>
+      </c>
+      <c r="CG12" t="n">
+        <v>-13.83694083694084</v>
+      </c>
+      <c r="CH12" t="n">
+        <v>-39.48520634148976</v>
+      </c>
+      <c r="CI12" t="n">
+        <v>-12.56088608361335</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>0.03465153397682532</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>-0.02535703585339059</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>-0.02615971998566603</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>0.02673585686560326</v>
+      </c>
+      <c r="CN12" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="CO12" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="CP12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="CQ12" t="n">
+        <v>-0.08333333333333333</v>
+      </c>
+      <c r="CR12" t="n">
+        <v>-1.903333333333334</v>
+      </c>
+      <c r="CS12" t="n">
+        <v>-0.1866666666666666</v>
+      </c>
+      <c r="CT12" t="n">
+        <v>0.1881818181818181</v>
+      </c>
+      <c r="CU12" t="n">
+        <v>-0.5445454545454546</v>
+      </c>
+      <c r="CV12" t="n">
+        <v>-1.716666666666667</v>
+      </c>
+      <c r="CW12" t="n">
+        <v>1.716666666666667</v>
+      </c>
+      <c r="CX12" t="n">
+        <v>0.7327272727272727</v>
+      </c>
+      <c r="CY12" t="n">
+        <v>-0.7327272727272727</v>
+      </c>
+      <c r="CZ12" t="n">
+        <v>71.8065886134068</v>
+      </c>
+      <c r="DA12" t="n">
+        <v>76.35606060606061</v>
+      </c>
+      <c r="DB12" t="inlineStr"/>
+      <c r="DC12" t="n">
+        <v>-0.2731390530694</v>
+      </c>
+      <c r="DD12" t="inlineStr"/>
+      <c r="DE12" t="inlineStr"/>
+      <c r="DF12" t="n">
+        <v>3.644004909778904</v>
+      </c>
+      <c r="DG12" t="n">
+        <v>-8241.969384244931</v>
+      </c>
+      <c r="DH12" t="n">
+        <v>0.4989267676767497</v>
+      </c>
+      <c r="DI12" t="inlineStr"/>
+      <c r="DJ12" t="inlineStr"/>
+      <c r="DK12" t="inlineStr"/>
+      <c r="DL12" t="n">
+        <v>1.319570707070703</v>
+      </c>
+      <c r="DM12" t="n">
+        <v>-24029.79797979798</v>
+      </c>
+      <c r="DN12" t="n">
+        <v>-3.234364699627847</v>
+      </c>
+      <c r="DO12" t="n">
+        <v>-8.22279040404041</v>
+      </c>
+      <c r="DP12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>IukqGdk1</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45563.5625</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stegemann s 
+  ger </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allianz arena
+  munich </t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>59</v>
+      </c>
+      <c r="H13" t="n">
+        <v>591</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>4fuCGs9P</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>f3ddUIXs</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.08333333333333348</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-0.4736363636363632</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.08181818181818179</v>
+      </c>
+      <c r="T13" t="n">
+        <v>-0.6666666666666665</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="V13" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-0.3333333333333339</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>-2.666666666666666</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-0.6666666666666661</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.5499999999999998</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>-2.666666666666664</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>-6.333333333333333</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>-2.550000000000001</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0.9999999999999996</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0.1833333333333333</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>-0.2833333333333332</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>-6.696127946127946</v>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="AP13" t="n">
+        <v>-0.4637921303555972</v>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="AR13" t="n">
+        <v>-337.3509935784522</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>61.32777725202189</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>-127.1687490685956</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>62.33973207297947</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>5.480519480519476</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>5.577922077922068</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>-15</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>-11.5</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>-11.72077922077923</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>-1.655844155844157</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>-10.33333333333333</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>3.666666666666664</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>-3.650000000000002</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>4.850000000000001</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>6.333333333333329</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>-6.333333333333329</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>3.549999999999997</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>-3.549999999999997</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>116.6666666666666</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>89.18181818181813</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>-18.56060606060606</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>0.9166666666666667</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>-1.57</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>0.3827272727272728</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>0.138961038961039</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>-3</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>-0.9805194805194808</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>-0.7922077922077919</v>
+      </c>
+      <c r="BX13" t="inlineStr"/>
+      <c r="BY13" t="inlineStr"/>
+      <c r="BZ13" t="inlineStr"/>
+      <c r="CA13" t="inlineStr"/>
+      <c r="CB13" t="n">
+        <v>4.666666666666667</v>
+      </c>
+      <c r="CC13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CD13" t="n">
+        <v>1.116666666666667</v>
+      </c>
+      <c r="CE13" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="CF13" t="n">
+        <v>-14.25867465867466</v>
+      </c>
+      <c r="CG13" t="n">
+        <v>44.53769841269842</v>
+      </c>
+      <c r="CH13" t="n">
+        <v>0.5516483516483461</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>17.64148048588838</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>-0.02492207307436871</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>0.02540891823728247</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>0.01033578508381251</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>0.009418816126459707</v>
+      </c>
+      <c r="CN13" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="CO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP13" t="n">
+        <v>0.01666666666666666</v>
+      </c>
+      <c r="CQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="CS13" t="n">
+        <v>-0.9166666666666667</v>
+      </c>
+      <c r="CT13" t="n">
+        <v>-0.138961038961039</v>
+      </c>
+      <c r="CU13" t="n">
+        <v>-0.3827272727272728</v>
+      </c>
+      <c r="CV13" t="n">
+        <v>2.486666666666667</v>
+      </c>
+      <c r="CW13" t="n">
+        <v>-2.486666666666667</v>
+      </c>
+      <c r="CX13" t="n">
+        <v>0.2437662337662338</v>
+      </c>
+      <c r="CY13" t="n">
+        <v>-0.2437662337662338</v>
+      </c>
+      <c r="CZ13" t="n">
+        <v>74.76074380165291</v>
+      </c>
+      <c r="DA13" t="n">
+        <v>74.79370629370629</v>
+      </c>
+      <c r="DB13" t="inlineStr"/>
+      <c r="DC13" t="n">
+        <v>2.480233494363915</v>
+      </c>
+      <c r="DD13" t="inlineStr"/>
+      <c r="DE13" t="inlineStr"/>
+      <c r="DF13" t="n">
+        <v>2.063888888888886</v>
+      </c>
+      <c r="DG13" t="n">
+        <v>23508.35071731812</v>
+      </c>
+      <c r="DH13" t="n">
+        <v>-0.2264309764309473</v>
+      </c>
+      <c r="DI13" t="inlineStr"/>
+      <c r="DJ13" t="inlineStr"/>
+      <c r="DK13" t="inlineStr"/>
+      <c r="DL13" t="n">
+        <v>0.594444444444445</v>
+      </c>
+      <c r="DM13" t="n">
+        <v>22973.73737373738</v>
+      </c>
+      <c r="DN13" t="n">
+        <v>2.236159603279177</v>
+      </c>
+      <c r="DO13" t="n">
+        <v>1.776599326599325</v>
+      </c>
+      <c r="DP13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>CIlrT3pm</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45563.4375</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jollenbeck m 
+  ger </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">borussia park
+  monchengladbach </t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>59</v>
+      </c>
+      <c r="H14" t="n">
+        <v>591</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>UgdQz0fK</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>KUx4Q7x1</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.9533333333333336</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.103333333333333</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.3072727272727274</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.386363636363636</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>-0.1666666666666667</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.08333333333333326</v>
+      </c>
+      <c r="X14" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.916666666666667</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>6.333333333333332</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>-7.772222222222222</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1.071428571428572</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>-1.281089743589743</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>-0.3026052016248091</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>-310.0046513815577</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>188.0185590415673</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>-115.2781749822355</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>52.91172471641593</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>-43.5</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>-12.45454545454545</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>10.54545454545455</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>-6.181818181818187</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>4.454545454545453</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>1.333333333333336</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>-3.333333333333336</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>-9.083333333333332</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>-4.916666666666671</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>14.66666666666666</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>-14.66666666666666</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>2.666666666666671</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>-2.666666666666671</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>155.9999999999999</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>-167</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>118.4545454545454</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>40.90909090909088</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>-0.9533333333333335</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>-0.03454545454545446</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>-0.02272727272727271</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>-2</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>-1.181818181818182</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>-0.4545454545454546</v>
+      </c>
+      <c r="BX14" t="inlineStr"/>
+      <c r="BY14" t="inlineStr"/>
+      <c r="BZ14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>1</v>
+      </c>
+      <c r="CB14" t="n">
+        <v>-3.333333333333334</v>
+      </c>
+      <c r="CC14" t="n">
+        <v>-2.333333333333332</v>
+      </c>
+      <c r="CD14" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="CE14" t="n">
+        <v>-2.333333333333334</v>
+      </c>
+      <c r="CF14" t="n">
+        <v>-6.225175684308816</v>
+      </c>
+      <c r="CG14" t="n">
+        <v>22.58367003367004</v>
+      </c>
+      <c r="CH14" t="n">
+        <v>18.02079601489607</v>
+      </c>
+      <c r="CI14" t="n">
+        <v>13.89051895074622</v>
+      </c>
+      <c r="CJ14" t="n">
+        <v>0.03612476112476113</v>
+      </c>
+      <c r="CK14" t="n">
+        <v>0.003938422688422691</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>0.004728302830416739</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>0.01986713585744117</v>
+      </c>
+      <c r="CN14" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="CO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP14" t="n">
+        <v>-0.1666666666666667</v>
+      </c>
+      <c r="CQ14" t="n">
+        <v>-0.08333333333333331</v>
+      </c>
+      <c r="CR14" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="CS14" t="n">
+        <v>0.9533333333333335</v>
+      </c>
+      <c r="CT14" t="n">
+        <v>0.02272727272727271</v>
+      </c>
+      <c r="CU14" t="n">
+        <v>0.03454545454545446</v>
+      </c>
+      <c r="CV14" t="n">
+        <v>-1.183333333333333</v>
+      </c>
+      <c r="CW14" t="n">
+        <v>1.183333333333333</v>
+      </c>
+      <c r="CX14" t="n">
+        <v>-0.01181818181818162</v>
+      </c>
+      <c r="CY14" t="n">
+        <v>0.01181818181818162</v>
+      </c>
+      <c r="CZ14" t="n">
+        <v>76.31643709825529</v>
+      </c>
+      <c r="DA14" t="n">
+        <v>75.41010101010102</v>
+      </c>
+      <c r="DB14" t="inlineStr"/>
+      <c r="DC14" t="n">
+        <v>0.6533436853002286</v>
+      </c>
+      <c r="DD14" t="inlineStr"/>
+      <c r="DE14" t="inlineStr"/>
+      <c r="DF14" t="n">
+        <v>-0.533046928916491</v>
+      </c>
+      <c r="DG14" t="n">
+        <v>-147.0151828847447</v>
+      </c>
+      <c r="DH14" t="n">
+        <v>-2.000202020202011</v>
+      </c>
+      <c r="DI14" t="inlineStr"/>
+      <c r="DJ14" t="inlineStr"/>
+      <c r="DK14" t="inlineStr"/>
+      <c r="DL14" t="n">
+        <v>-0.956363636363637</v>
+      </c>
+      <c r="DM14" t="n">
+        <v>-2143.0303030303</v>
+      </c>
+      <c r="DN14" t="n">
+        <v>1.628550724637677</v>
+      </c>
+      <c r="DO14" t="n">
+        <v>0.7965656565656616</v>
+      </c>
+      <c r="DP14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>SfGPAMUI</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45563.4375</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">badstubner f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">volkswagen arena
+  wolfsburg </t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>59</v>
+      </c>
+      <c r="H15" t="n">
+        <v>591</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>hAcTWKKN</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>IkCftsQm</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>-2.433333333333333</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.3033333333333335</v>
+      </c>
+      <c r="R15" t="n">
+        <v>-1.076287878787879</v>
+      </c>
+      <c r="S15" t="n">
+        <v>-0.1734848484848484</v>
+      </c>
+      <c r="T15" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
+      </c>
+      <c r="V15" t="n">
+        <v>-0.5512820512820512</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.6602564102564101</v>
+      </c>
+      <c r="X15" t="n">
+        <v>-5.666666666666666</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.6666666666666661</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-3.019230769230769</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>-6.333333333333334</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>-2.903846153846153</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0.8205128205128194</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>-1.666666666666667</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>-1.198717948717949</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0.5192307692307692</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0.9038461538461539</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>-1.800070028011204</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>-0.9333333333333331</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.425164486929193</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>-1.163911782661783</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>-37.01507307532356</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>173.3372756989342</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>164.7015716135512</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>-37.42762601043205</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>19</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>-9</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>-3.492424242424235</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>9.416666666666671</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>6.462121212121211</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>3.06818181818182</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>3.666666666666671</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>8.057692307692307</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>3.865384615384617</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>-4.666666666666671</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>4.666666666666671</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>-7.564102564102569</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>7.564102564102569</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>-164.6666666666666</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>128.3333333333333</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>-176.1287878787879</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>98.71969696969694</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>0.7666666666666666</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>0.03000000000000003</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>0.1141666666666667</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>0.7492424242424243</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>0.5192307692307692</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>0.224358974358974</v>
+      </c>
+      <c r="BX15" t="inlineStr"/>
+      <c r="BY15" t="inlineStr"/>
+      <c r="BZ15" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>-0.3333333333333334</v>
+      </c>
+      <c r="CB15" t="n">
+        <v>2.333333333333332</v>
+      </c>
+      <c r="CC15" t="n">
+        <v>3</v>
+      </c>
+      <c r="CD15" t="n">
+        <v>-0.115384615384615</v>
+      </c>
+      <c r="CE15" t="n">
+        <v>2.634615384615385</v>
+      </c>
+      <c r="CF15" t="n">
+        <v>-1.242063492063487</v>
+      </c>
+      <c r="CG15" t="n">
+        <v>-27.78143479614068</v>
+      </c>
+      <c r="CH15" t="n">
+        <v>-0.8163019042803796</v>
+      </c>
+      <c r="CI15" t="n">
+        <v>-25.82781182102705</v>
+      </c>
+      <c r="CJ15" t="n">
+        <v>-0.06197554290533418</v>
+      </c>
+      <c r="CK15" t="n">
+        <v>-0.04889299068403546</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>-0.007906266955326598</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>-0.02486601723796204</v>
+      </c>
+      <c r="CN15" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="CO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP15" t="n">
+        <v>-0.05128205128205132</v>
+      </c>
+      <c r="CQ15" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="CR15" t="n">
+        <v>-0.03000000000000003</v>
+      </c>
+      <c r="CS15" t="n">
+        <v>-0.7666666666666666</v>
+      </c>
+      <c r="CT15" t="n">
+        <v>-0.7492424242424243</v>
+      </c>
+      <c r="CU15" t="n">
+        <v>-0.1141666666666667</v>
+      </c>
+      <c r="CV15" t="n">
+        <v>0.7366666666666666</v>
+      </c>
+      <c r="CW15" t="n">
+        <v>-0.7366666666666666</v>
+      </c>
+      <c r="CX15" t="n">
+        <v>-0.6350757575757576</v>
+      </c>
+      <c r="CY15" t="n">
+        <v>0.6350757575757576</v>
+      </c>
+      <c r="CZ15" t="n">
+        <v>76.37529843893481</v>
+      </c>
+      <c r="DA15" t="n">
+        <v>77.40513468013468</v>
+      </c>
+      <c r="DB15" t="inlineStr"/>
+      <c r="DC15" t="n">
+        <v>1.06719015676444</v>
+      </c>
+      <c r="DD15" t="inlineStr"/>
+      <c r="DE15" t="inlineStr"/>
+      <c r="DF15" t="n">
+        <v>1.743368593051258</v>
+      </c>
+      <c r="DG15" t="inlineStr"/>
+      <c r="DH15" t="n">
+        <v>-0.9664772727272464</v>
+      </c>
+      <c r="DI15" t="inlineStr"/>
+      <c r="DJ15" t="inlineStr"/>
+      <c r="DK15" t="inlineStr"/>
+      <c r="DL15" t="n">
+        <v>0.09646464646464636</v>
+      </c>
+      <c r="DM15" t="n">
+        <v>8156.439393939396</v>
+      </c>
+      <c r="DN15" t="n">
+        <v>1.979580937638204</v>
+      </c>
+      <c r="DO15" t="n">
+        <v>1.148169191919195</v>
+      </c>
+      <c r="DP15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Q5hiEzKD</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45563.4375</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">storks s 
+  ger </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">red bull arena
+  leipzig </t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>fTVNku3I</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>59</v>
+      </c>
+      <c r="H16" t="n">
+        <v>591</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>0jdIgO6t</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>vZA6VYpf</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>-0.9100000000000001</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.2699999999999998</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.260909090909091</v>
+      </c>
+      <c r="S16" t="n">
+        <v>-0.683636363636364</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.4166666666666666</v>
+      </c>
+      <c r="W16" t="n">
+        <v>-0.8333333333333333</v>
+      </c>
+      <c r="X16" t="n">
+        <v>-2.666666666666667</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.666666666666667</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>-9</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>6.333333333333334</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>-1.333333333333332</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>-1.666666666666667</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>-0.4199074074074076</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0.2945533769063178</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0.7360844017094017</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.531808278867103</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>-181.3651476412921</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>91.34868225311187</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>-104.0992986367035</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>26.73336861618256</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>5.27272727272728</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>-6.27272727272728</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>-33.5</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>-19.18181818181818</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>-5.727272727272727</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>-18.66666666666666</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>5.333333333333332</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>-4.333333333333332</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>-0.1666666666666714</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>2.333333333333329</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>-2.333333333333329</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>4.166666666666671</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>-4.166666666666671</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>151</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>106</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>136.0909090909091</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>-29.18181818181819</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>0.2433333333333333</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>-2.27</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>0.4663636363636363</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>-0.9527272727272726</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>-1.833333333333333</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>0.3333333333333335</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>-0.6060606060606062</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>0.446969696969697</v>
+      </c>
+      <c r="BX16" t="inlineStr"/>
+      <c r="BY16" t="inlineStr"/>
+      <c r="BZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CB16" t="n">
+        <v>-37</v>
+      </c>
+      <c r="CC16" t="n">
+        <v>-31.66666666666667</v>
+      </c>
+      <c r="CD16" t="n">
+        <v>-11.58333333333333</v>
+      </c>
+      <c r="CE16" t="n">
+        <v>-7.250000000000002</v>
+      </c>
+      <c r="CF16" t="n">
+        <v>29.82849857114563</v>
+      </c>
+      <c r="CG16" t="n">
+        <v>44.70156223893066</v>
+      </c>
+      <c r="CH16" t="n">
+        <v>9.027718552985931</v>
+      </c>
+      <c r="CI16" t="n">
+        <v>8.285518587020135</v>
+      </c>
+      <c r="CJ16" t="n">
+        <v>-0.08719450839016057</v>
+      </c>
+      <c r="CK16" t="n">
+        <v>0.04392135642135642</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>-0.03282760456658641</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>0.04777368771176825</v>
+      </c>
+      <c r="CN16" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="CO16" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="CP16" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="CQ16" t="n">
+        <v>-0.08333333333333334</v>
+      </c>
+      <c r="CR16" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="CS16" t="n">
+        <v>-0.2433333333333333</v>
+      </c>
+      <c r="CT16" t="n">
+        <v>0.9527272727272726</v>
+      </c>
+      <c r="CU16" t="n">
+        <v>-0.4663636363636363</v>
+      </c>
+      <c r="CV16" t="n">
+        <v>2.513333333333333</v>
+      </c>
+      <c r="CW16" t="n">
+        <v>-2.513333333333333</v>
+      </c>
+      <c r="CX16" t="n">
+        <v>1.419090909090909</v>
+      </c>
+      <c r="CY16" t="n">
+        <v>-1.419090909090909</v>
+      </c>
+      <c r="CZ16" t="n">
+        <v>75.42727272727274</v>
+      </c>
+      <c r="DA16" t="n">
+        <v>74.97493112947659</v>
+      </c>
+      <c r="DB16" t="inlineStr"/>
+      <c r="DC16" t="n">
+        <v>-0.2642293233082853</v>
+      </c>
+      <c r="DD16" t="inlineStr"/>
+      <c r="DE16" t="inlineStr"/>
+      <c r="DF16" t="n">
+        <v>-0.3659683299156988</v>
+      </c>
+      <c r="DG16" t="n">
+        <v>24634.74880382776</v>
+      </c>
+      <c r="DH16" t="n">
+        <v>-1.686531986531918</v>
+      </c>
+      <c r="DI16" t="inlineStr"/>
+      <c r="DJ16" t="inlineStr"/>
+      <c r="DK16" t="inlineStr"/>
+      <c r="DL16" t="n">
+        <v>-0.06565656565657108</v>
+      </c>
+      <c r="DM16" t="n">
+        <v>30165.99326599326</v>
+      </c>
+      <c r="DN16" t="n">
+        <v>5.598979835953529</v>
+      </c>
+      <c r="DO16" t="n">
+        <v>6.009629629629629</v>
+      </c>
+      <c r="DP16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>f18BYPMP</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45563.4375</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brand b 
+  ger </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mewa arena
+  mainz </t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>59</v>
+      </c>
+      <c r="H17" t="n">
+        <v>591</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2VSFgl3c</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>YZPE6Sx7</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.1733333333333331</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.793333333333334</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.5427272727272727</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.2100000000000002</v>
+      </c>
+      <c r="T17" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.08333333333333326</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0.08333333333333326</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>4.666666666666667</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.3333333333333339</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.416666666666667</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>-3.333333333333332</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>2.083333333333334</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0.3333333333333335</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0.3333333333333335</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>-0.08333333333333326</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>-0.3333333333333334</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0.581614463967405</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>5.286080586080587</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0.300648170149449</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0.7630097607071287</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>-75.01474710996432</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>249.6937535411838</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>-11.80827930757192</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>86.09256021530098</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>-53</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>12.27272727272727</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>-21.45454545454545</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>-20</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>15.45454545454545</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>-7.727272727272727</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>0.3333333333333357</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>1.916666666666671</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>-16</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>-64</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>2.090909090909122</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>-91.81818181818181</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>-1.793333333333333</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>-0.08818181818181822</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>-0.3918181818181818</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>0.6666666666666665</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="BX17" t="inlineStr"/>
+      <c r="BY17" t="inlineStr"/>
+      <c r="BZ17" t="inlineStr"/>
+      <c r="CA17" t="inlineStr"/>
+      <c r="CB17" t="n">
+        <v>24.33333333333334</v>
+      </c>
+      <c r="CC17" t="n">
+        <v>24</v>
+      </c>
+      <c r="CD17" t="n">
+        <v>7.916666666666668</v>
+      </c>
+      <c r="CE17" t="n">
+        <v>7.916666666666668</v>
+      </c>
+      <c r="CF17" t="n">
+        <v>-19.32079124579124</v>
+      </c>
+      <c r="CG17" t="n">
+        <v>-6.528097828097824</v>
+      </c>
+      <c r="CH17" t="n">
+        <v>-14.6612363127069</v>
+      </c>
+      <c r="CI17" t="n">
+        <v>-5.410273060273063</v>
+      </c>
+      <c r="CJ17" t="n">
+        <v>0.03201566951566952</v>
+      </c>
+      <c r="CK17" t="n">
+        <v>-0.03351029601029601</v>
+      </c>
+      <c r="CL17" t="n">
+        <v>0.01097856224200218</v>
+      </c>
+      <c r="CM17" t="n">
+        <v>-0.006799047046502735</v>
+      </c>
+      <c r="CN17" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="CO17" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="CP17" t="n">
+        <v>-0.1666666666666667</v>
+      </c>
+      <c r="CQ17" t="n">
+        <v>-0.08333333333333333</v>
+      </c>
+      <c r="CR17" t="n">
+        <v>1.793333333333333</v>
+      </c>
+      <c r="CS17" t="n">
+        <v>-0.1600000000000001</v>
+      </c>
+      <c r="CT17" t="n">
+        <v>0.3918181818181818</v>
+      </c>
+      <c r="CU17" t="n">
+        <v>0.08818181818181822</v>
+      </c>
+      <c r="CV17" t="n">
+        <v>1.953333333333333</v>
+      </c>
+      <c r="CW17" t="n">
+        <v>-1.953333333333333</v>
+      </c>
+      <c r="CX17" t="n">
+        <v>0.3036363636363635</v>
+      </c>
+      <c r="CY17" t="n">
+        <v>-0.3036363636363635</v>
+      </c>
+      <c r="CZ17" t="n">
+        <v>74.44363636363637</v>
+      </c>
+      <c r="DA17" t="n">
+        <v>75.80569329660239</v>
+      </c>
+      <c r="DB17" t="inlineStr"/>
+      <c r="DC17" t="n">
+        <v>-1.044505012531346</v>
+      </c>
+      <c r="DD17" t="inlineStr"/>
+      <c r="DE17" t="inlineStr"/>
+      <c r="DF17" t="n">
+        <v>-0.5068901420217209</v>
+      </c>
+      <c r="DG17" t="n">
+        <v>1414.141604010027</v>
+      </c>
+      <c r="DH17" t="n">
+        <v>-4.797222222222274</v>
+      </c>
+      <c r="DI17" t="inlineStr"/>
+      <c r="DJ17" t="inlineStr"/>
+      <c r="DK17" t="inlineStr"/>
+      <c r="DL17" t="n">
+        <v>0.3572222222222194</v>
+      </c>
+      <c r="DM17" t="n">
+        <v>4192.777777777781</v>
+      </c>
+      <c r="DN17" t="n">
+        <v>1.350559732664991</v>
+      </c>
+      <c r="DO17" t="n">
+        <v>2.487777777777765</v>
+      </c>
+      <c r="DP17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>6uSGCr06</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45563.4375</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hartmann r 
+  ger </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">europa park stadion
+  freiburg </t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>ILyJuN3g</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="G18" t="n">
         <v>59</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H18" t="n">
         <v>591</v>
       </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
         <v>20242025</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>germany</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>4ljanukM</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0jdIgO6t</t>
-        </is>
-      </c>
-      <c r="O3" t="n">
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>pfoInmcq</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>-0.04333333333333345</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.2309090909090905</v>
+      </c>
+      <c r="S18" t="n">
+        <v>-0.1336363636363636</v>
+      </c>
+      <c r="T18" t="n">
         <v>1</v>
       </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="n">
+      <c r="U18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0.3333333333333335</v>
+      </c>
+      <c r="W18" t="n">
+        <v>-0.1666666666666666</v>
+      </c>
+      <c r="X18" t="n">
         <v>3</v>
       </c>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>-0.21</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0.7350000000000001</v>
-      </c>
-      <c r="V3" t="n">
+      <c r="Y18" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-1.916666666666667</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>4.666666666666666</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>-2.333333333333332</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>-0.08333333333333215</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.833333333333332</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0.01481481481481506</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>-0.6688792688792691</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>2.346895489987595</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>-2.716589381479088</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>57.67039244908102</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>123.9836987034236</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>94.19154459006123</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>-75.73374156071677</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>-31.5</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>-20.36363636363637</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>18.63636363636364</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>-3</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>-14.27272727272727</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>12.81818181818181</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>6.333333333333336</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>-2</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>-2.083333333333336</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>0.3333333333333286</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>2.333333333333329</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>-2.333333333333329</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>-8.666666666666664</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>8.666666666666664</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>-12</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>10.33333333333337</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>-114.6363636363637</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>93.18181818181819</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>-0.1366666666666666</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>-0.2899999999999999</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>-0.04818181818181823</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>-1.666666666666667</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>-1.833333333333333</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>-0.696969696969697</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>-0.3863636363636362</v>
+      </c>
+      <c r="BX18" t="inlineStr"/>
+      <c r="BY18" t="inlineStr"/>
+      <c r="BZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB18" t="n">
+        <v>-31</v>
+      </c>
+      <c r="CC18" t="n">
+        <v>-34.33333333333334</v>
+      </c>
+      <c r="CD18" t="n">
+        <v>-7.333333333333332</v>
+      </c>
+      <c r="CE18" t="n">
+        <v>-8.833333333333332</v>
+      </c>
+      <c r="CF18" t="n">
+        <v>9.009278499278501</v>
+      </c>
+      <c r="CG18" t="n">
+        <v>13.20235342000048</v>
+      </c>
+      <c r="CH18" t="n">
+        <v>-15.22836612882067</v>
+      </c>
+      <c r="CI18" t="n">
+        <v>-33.10457160502192</v>
+      </c>
+      <c r="CJ18" t="n">
+        <v>-0.008827773533655887</v>
+      </c>
+      <c r="CK18" t="n">
+        <v>0.01440721675807621</v>
+      </c>
+      <c r="CL18" t="n">
+        <v>-0.03496390438107158</v>
+      </c>
+      <c r="CM18" t="n">
+        <v>0.01620415346666651</v>
+      </c>
+      <c r="CN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO18" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="CP18" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="CQ18" t="n">
+        <v>-0.1666666666666667</v>
+      </c>
+      <c r="CR18" t="n">
+        <v>0.2899999999999999</v>
+      </c>
+      <c r="CS18" t="n">
+        <v>0.1366666666666666</v>
+      </c>
+      <c r="CT18" t="n">
+        <v>0.04818181818181823</v>
+      </c>
+      <c r="CU18" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="CV18" t="n">
+        <v>0.1533333333333333</v>
+      </c>
+      <c r="CW18" t="n">
+        <v>-0.1533333333333333</v>
+      </c>
+      <c r="CX18" t="n">
+        <v>-0.09181818181818174</v>
+      </c>
+      <c r="CY18" t="n">
+        <v>0.09181818181818174</v>
+      </c>
+      <c r="CZ18" t="n">
+        <v>74.88301193755738</v>
+      </c>
+      <c r="DA18" t="n">
+        <v>70.49431818181817</v>
+      </c>
+      <c r="DB18" t="inlineStr"/>
+      <c r="DC18" t="n">
+        <v>-0.8127647627943873</v>
+      </c>
+      <c r="DD18" t="inlineStr"/>
+      <c r="DE18" t="inlineStr"/>
+      <c r="DF18" t="n">
+        <v>1.171962856843727</v>
+      </c>
+      <c r="DG18" t="n">
+        <v>11513.32759745601</v>
+      </c>
+      <c r="DH18" t="n">
+        <v>-1.846060606060632</v>
+      </c>
+      <c r="DI18" t="inlineStr"/>
+      <c r="DJ18" t="inlineStr"/>
+      <c r="DK18" t="inlineStr"/>
+      <c r="DL18" t="n">
+        <v>-0.06585858585858517</v>
+      </c>
+      <c r="DM18" t="n">
+        <v>11806.66666666667</v>
+      </c>
+      <c r="DN18" t="n">
+        <v>5.29577353443284</v>
+      </c>
+      <c r="DO18" t="n">
+        <v>5.10404040404039</v>
+      </c>
+      <c r="DP18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>rsNyMnwK</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45562.64583333334</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">petersen m 
+  ger </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">signal iduna park
+  dortmund </t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>59</v>
+      </c>
+      <c r="H19" t="n">
+        <v>591</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>GzfvcwRj</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>A15eUM4C</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.1599999999999999</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>-1.206666666666666</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.2377622377622377</v>
+      </c>
+      <c r="S19" t="n">
+        <v>-0.5298601398601401</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="U19" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.2976190476190476</v>
+      </c>
+      <c r="W19" t="n">
+        <v>-0.3095238095238095</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>-1.666666666666666</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.023809523809524</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-2.369047619047619</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>-7.666666666666666</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>-3.357142857142858</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>-4.75</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0.3333333333333335</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0.7857142857142858</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>-0.4880952380952384</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0.880952380952381</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>-0.9047619047619049</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>-0.2973901098901095</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>4.821296296296296</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>3.552421374532719</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0.708259619637329</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>-229.6860841973669</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>231.9940258090998</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>-44.0491983889805</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>-1.798496351500205</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>-10.82517482517483</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>-9.615384615384613</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>-2</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>4.04195804195804</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>-1.566433566433567</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>-8.666666666666671</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>-7.797619047619051</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>-14.10714285714285</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>11.66666666666667</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>-11.66666666666667</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>11.15476190476191</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>-11.15476190476191</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>157.6666666666667</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>-40.66666666666669</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>187.4825174825175</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>-11.02097902097898</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>0.5066666666666667</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>0.2727272727272729</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>0.01237762237762251</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>-0.5357142857142856</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>0.8452380952380953</v>
+      </c>
+      <c r="BX19" t="inlineStr"/>
+      <c r="BY19" t="inlineStr"/>
+      <c r="BZ19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="CA19" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="CB19" t="n">
+        <v>-3.333333333333334</v>
+      </c>
+      <c r="CC19" t="n">
+        <v>5</v>
+      </c>
+      <c r="CD19" t="n">
+        <v>-5.726190476190476</v>
+      </c>
+      <c r="CE19" t="n">
+        <v>-1.595238095238095</v>
+      </c>
+      <c r="CF19" t="n">
+        <v>7.414707977207968</v>
+      </c>
+      <c r="CG19" t="n">
+        <v>-7.756565656565648</v>
+      </c>
+      <c r="CH19" t="n">
+        <v>15.12421439511629</v>
+      </c>
+      <c r="CI19" t="n">
+        <v>31.28038852173468</v>
+      </c>
+      <c r="CJ19" t="n">
+        <v>-0.01366119345770509</v>
+      </c>
+      <c r="CK19" t="n">
+        <v>0.02642941349837902</v>
+      </c>
+      <c r="CL19" t="n">
+        <v>-0.006835023427421802</v>
+      </c>
+      <c r="CM19" t="n">
+        <v>0.01881601543880583</v>
+      </c>
+      <c r="CN19" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="W3" t="n">
-        <v>0.6666666666666667</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1.333333333333334</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0.3333333333333339</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>-3.333333333333333</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.666666666666667</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>-4.333333333333334</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.333333333333334</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>-15.33333333333334</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>15.33333333333334</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>73.27272727272727</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>70.95454545454545</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>-132</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>2217871.066555277</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>-0.1243386243386269</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>2218047.138047139</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>-1.592255892255935</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>3.009579504316335</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>2325000</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>-0.4525252525252519</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>-125</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0.1111111111111109</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0.4682539682539684</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>2.752158173210816</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>-0.7299637983848299</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>-2.133333333333333</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>3.021885521885537</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>2.454545454545453</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>-2</v>
-      </c>
-      <c r="BE3" t="n">
+      <c r="CO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP19" t="n">
+        <v>0.1785714285714286</v>
+      </c>
+      <c r="CQ19" t="n">
+        <v>-0.1785714285714285</v>
+      </c>
+      <c r="CR19" t="n">
+        <v>-1.54</v>
+      </c>
+      <c r="CS19" t="n">
+        <v>-0.5066666666666667</v>
+      </c>
+      <c r="CT19" t="n">
+        <v>-0.01237762237762251</v>
+      </c>
+      <c r="CU19" t="n">
+        <v>-0.2727272727272729</v>
+      </c>
+      <c r="CV19" t="n">
+        <v>-1.033333333333333</v>
+      </c>
+      <c r="CW19" t="n">
+        <v>1.033333333333333</v>
+      </c>
+      <c r="CX19" t="n">
+        <v>0.2603496503496505</v>
+      </c>
+      <c r="CY19" t="n">
+        <v>-0.2603496503496505</v>
+      </c>
+      <c r="CZ19" t="n">
+        <v>75.76280991735536</v>
+      </c>
+      <c r="DA19" t="n">
+        <v>74.79200336700336</v>
+      </c>
+      <c r="DB19" t="inlineStr"/>
+      <c r="DC19" t="n">
+        <v>-1.347669024339524</v>
+      </c>
+      <c r="DD19" t="inlineStr"/>
+      <c r="DE19" t="inlineStr"/>
+      <c r="DF19" t="n">
+        <v>0.1710966645863685</v>
+      </c>
+      <c r="DG19" t="n">
+        <v>26378.27485380117</v>
+      </c>
+      <c r="DH19" t="n">
+        <v>1.610101010101005</v>
+      </c>
+      <c r="DI19" t="inlineStr"/>
+      <c r="DJ19" t="inlineStr"/>
+      <c r="DK19" t="inlineStr"/>
+      <c r="DL19" t="n">
+        <v>-0.7755555555555596</v>
+      </c>
+      <c r="DM19" t="n">
+        <v>36373.53535353535</v>
+      </c>
+      <c r="DN19" t="n">
+        <v>9.107228694265302</v>
+      </c>
+      <c r="DO19" t="n">
+        <v>9.292525252525252</v>
+      </c>
+      <c r="DP19" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_preparation/df_constructed.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_constructed.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BW16"/>
+  <dimension ref="A1:BW13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -695,144 +695,144 @@
       </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
+          <t>dif_sum_wage_player_miss</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_value_player_start</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_start</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_value_player_miss</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_sub</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_value_player_sub</t>
+        </is>
+      </c>
+      <c r="BW1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_rep_player_start</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_start</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_wage_player_miss</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_value_player_miss</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="BJ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="BK1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="BL1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="BM1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="BN1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="BO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="BP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_sub</t>
-        </is>
-      </c>
-      <c r="BQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_sub</t>
-        </is>
-      </c>
-      <c r="BR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_start</t>
-        </is>
-      </c>
-      <c r="BS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="BT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="BU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="BV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="BW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>E7rNpTBk</t>
+          <t>rPiijklS</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45584.4375</v>
+        <v>45585.52083333334</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">siebert d 
+          <t xml:space="preserve">welz t 
   ger </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mewa arena
-  mainz </t>
+          <t xml:space="preserve">volkswagen arena
+  wolfsburg </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>EuakNmc1</t>
+          <t>nwkTahLL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>KbS1suSm</t>
+          <t>Ig1f1fy3</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -859,209 +859,211 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>vZA6VYpf</t>
+          <t>8f6APkLc</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2VSFgl3c</t>
+          <t>YZPE6Sx7</t>
         </is>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0.996666666666667</v>
+        <v>-1.82</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.4235000000000002</v>
+        <v>0.3580000000000003</v>
       </c>
       <c r="R2" t="n">
-        <v>0.75</v>
+        <v>-2</v>
       </c>
       <c r="S2" t="n">
-        <v>1.2</v>
+        <v>0.1298701298701297</v>
       </c>
       <c r="T2" t="n">
-        <v>-2.666666666666667</v>
+        <v>-7.5</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1369565217391298</v>
+        <v>0.5021645021645025</v>
       </c>
       <c r="V2" t="n">
-        <v>2.666666666666664</v>
+        <v>-9.333333333333334</v>
       </c>
       <c r="W2" t="n">
-        <v>4.78913043478261</v>
+        <v>3.313852813852813</v>
       </c>
       <c r="X2" t="n">
-        <v>-2.333333333333333</v>
+        <v>-1.666666666666667</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.6391304347826086</v>
+        <v>0.2251082251082253</v>
       </c>
       <c r="Z2" t="n">
-        <v>-3.5</v>
+        <v>-4.25</v>
       </c>
       <c r="AA2" t="n">
-        <v>-1.05</v>
+        <v>-0.01298701298701288</v>
       </c>
       <c r="AB2" t="n">
-        <v>18.97383357383357</v>
+        <v>23.61307932263815</v>
       </c>
       <c r="AC2" t="n">
-        <v>18.80677971548538</v>
+        <v>19.64923027900177</v>
       </c>
       <c r="AD2" t="n">
-        <v>893.7443437962941</v>
+        <v>931.066582494326</v>
       </c>
       <c r="AE2" t="n">
-        <v>901.3317456712546</v>
+        <v>873.8192551621943</v>
       </c>
       <c r="AF2" t="n">
-        <v>25</v>
+        <v>17.66666666666666</v>
       </c>
       <c r="AG2" t="n">
-        <v>10.50717703349282</v>
+        <v>18.82619047619048</v>
       </c>
       <c r="AH2" t="n">
-        <v>19.5</v>
+        <v>-4.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>16.20813397129186</v>
+        <v>13.53809523809525</v>
       </c>
       <c r="AJ2" t="n">
-        <v>13.41666666666666</v>
+        <v>1.75</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.450000000000003</v>
+        <v>3.980519480519483</v>
       </c>
       <c r="AL2" t="n">
-        <v>-3.333333333333329</v>
+        <v>-18.33333333333333</v>
       </c>
       <c r="AM2" t="n">
-        <v>-10.47826086956522</v>
+        <v>-0.4675324675324788</v>
       </c>
       <c r="AN2" t="n">
-        <v>-17.66666666666669</v>
+        <v>-248.3333333333333</v>
       </c>
       <c r="AO2" t="n">
-        <v>-129.85</v>
+        <v>-9.149999999999977</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.5</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9318181818181821</v>
-      </c>
-      <c r="AR2" t="inlineStr"/>
+        <v>0.6839826839826837</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
       <c r="AS2" t="n">
-        <v>0.03333333333333333</v>
+        <v>0.0857142857142858</v>
       </c>
       <c r="AT2" t="n">
-        <v>-3.416666666666671</v>
+        <v>5.166666666666671</v>
       </c>
       <c r="AU2" t="n">
-        <v>2.825000000000003</v>
+        <v>2.690476190476192</v>
       </c>
       <c r="AV2" t="n">
-        <v>33.97120610870611</v>
+        <v>20.66610466960601</v>
       </c>
       <c r="AW2" t="n">
-        <v>7.717998126482772</v>
+        <v>-7.980761308738423</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.06997299997299998</v>
+        <v>0.03528453596444147</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.04047277303910549</v>
+        <v>0.007173238270608076</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>-0.04166666666666666</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>-0.8138047138047144</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>0.03703703703706651</v>
-      </c>
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
       <c r="BD2" t="n">
-        <v>-31490.23569023569</v>
-      </c>
-      <c r="BE2" t="inlineStr"/>
-      <c r="BF2" t="inlineStr"/>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="n">
-        <v>0.6528829873257109</v>
-      </c>
+        <v>-1.446541507179148</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>0.106372732852936</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>4270538.119288119</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>12724.18831168831</v>
+      </c>
+      <c r="BH2" t="inlineStr"/>
       <c r="BI2" t="n">
-        <v>-7.092255892255892</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>-0.9427581784973427</v>
-      </c>
+        <v>0.8622474747474485</v>
+      </c>
+      <c r="BJ2" t="inlineStr"/>
       <c r="BK2" t="n">
-        <v>-7.158901887442909</v>
-      </c>
-      <c r="BL2" t="inlineStr"/>
-      <c r="BM2" t="n">
-        <v>-0.8497956399465687</v>
-      </c>
-      <c r="BN2" t="inlineStr"/>
+        <v>0.9278138528138697</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>-2.272186147186151</v>
+      </c>
+      <c r="BM2" t="inlineStr"/>
+      <c r="BN2" t="n">
+        <v>3.104641654641654</v>
+      </c>
       <c r="BO2" t="n">
-        <v>-5.558585858585843</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>-30882.05736042423</v>
-      </c>
+        <v>13149.49101893028</v>
+      </c>
+      <c r="BP2" t="inlineStr"/>
       <c r="BQ2" t="n">
-        <v>-21631705.41335886</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>-23879713.80471381</v>
-      </c>
+        <v>0.3637180629827685</v>
+      </c>
+      <c r="BR2" t="inlineStr"/>
       <c r="BS2" t="inlineStr"/>
-      <c r="BT2" t="inlineStr"/>
+      <c r="BT2" t="n">
+        <v>1.692275103301171</v>
+      </c>
       <c r="BU2" t="n">
-        <v>1.783164983164983</v>
-      </c>
-      <c r="BV2" t="inlineStr"/>
+        <v>2.604569662966767</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>4389194.218808111</v>
+      </c>
       <c r="BW2" t="n">
-        <v>-5.851310949685569</v>
+        <v>0.3241762866762863</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>fHjVr7t2</t>
+          <t>nBwH6AY8</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45584.4375</v>
+        <v>45585.4375</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">exner f 
+          <t xml:space="preserve">reichel t 
   ger </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">borussia park
-  monchengladbach </t>
+          <t xml:space="preserve">holstein stadion
+  kiel </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>88HSzjDr</t>
+          <t>63WsD2ei</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>KWixEVWi</t>
+          <t>pzHW4oaE</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1088,211 +1090,209 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>M5BRZDsC</t>
+          <t>hAcTWKKN</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>4ljanukM</t>
+          <t>IkCftsQm</t>
         </is>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.7533333333333332</v>
+        <v>-1.726666666666666</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.8105000000000004</v>
+        <v>0.6073182957393484</v>
       </c>
       <c r="R3" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9189723320158102</v>
+        <v>0.8074534161490682</v>
       </c>
       <c r="T3" t="n">
-        <v>-3.166666666666666</v>
+        <v>-6.083333333333334</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9387351778656123</v>
+        <v>1.614906832298136</v>
       </c>
       <c r="V3" t="n">
-        <v>-6</v>
+        <v>-9.916666666666668</v>
       </c>
       <c r="W3" t="n">
-        <v>3.962450592885377</v>
+        <v>3.596273291925467</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.166666666666667</v>
+        <v>-3</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.03952569169960474</v>
+        <v>0.4658385093167703</v>
       </c>
       <c r="Z3" t="n">
-        <v>-2.5</v>
+        <v>-3</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.2608695652173911</v>
+        <v>1.031055900621118</v>
       </c>
       <c r="AB3" t="n">
-        <v>21.47880175380175</v>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>24.08090277777778</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>21.32433484444258</v>
       </c>
       <c r="AD3" t="n">
-        <v>823.7180997505649</v>
+        <v>849.718502141244</v>
       </c>
       <c r="AE3" t="n">
-        <v>826.9128599267867</v>
+        <v>754.9657356538489</v>
       </c>
       <c r="AF3" t="n">
-        <v>-18.5</v>
+        <v>-59.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>-4.861471861471856</v>
+        <v>27.55454545454545</v>
       </c>
       <c r="AH3" t="n">
-        <v>-17.33333333333334</v>
+        <v>-58.66666666666667</v>
       </c>
       <c r="AI3" t="n">
-        <v>4.833333333333336</v>
+        <v>4.695454545454545</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-9.25</v>
+        <v>-13.33333333333333</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0.5968379446640313</v>
+        <v>0.7474120082815787</v>
       </c>
       <c r="AL3" t="n">
-        <v>6.5</v>
+        <v>1.5</v>
       </c>
       <c r="AM3" t="n">
-        <v>10.53754940711462</v>
+        <v>19.26708074534162</v>
       </c>
       <c r="AN3" t="n">
-        <v>141</v>
+        <v>100.0000000000001</v>
       </c>
       <c r="AO3" t="n">
-        <v>170.95</v>
+        <v>234.25</v>
       </c>
       <c r="AP3" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.1645021645021647</v>
+        <v>-0.9192546583850933</v>
       </c>
       <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="n">
-        <v>-1.5</v>
+        <v>-0.8</v>
       </c>
       <c r="AT3" t="n">
-        <v>-0.6666666666666714</v>
+        <v>-0.4166666666666643</v>
       </c>
       <c r="AU3" t="n">
-        <v>-4.395256916996045</v>
+        <v>-0.1304347826086953</v>
       </c>
       <c r="AV3" t="n">
-        <v>-10.46584301124083</v>
+        <v>-4.352445963999124</v>
       </c>
       <c r="AW3" t="n">
-        <v>12.43039202983235</v>
+        <v>-16.66592475434344</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.04751929126929127</v>
+        <v>-0.004982719893295046</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.001574089699500146</v>
+        <v>-0.008795038621222592</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-0.4166666666666667</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="BA3" t="n">
-        <v>-0.1304347826086956</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>0.4833333333333334</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>-2.466666666666669</v>
-      </c>
+        <v>0.4472049689440994</v>
+      </c>
+      <c r="BB3" t="inlineStr"/>
+      <c r="BC3" t="inlineStr"/>
       <c r="BD3" t="n">
-        <v>2416.666666666668</v>
-      </c>
-      <c r="BE3" t="inlineStr"/>
-      <c r="BF3" t="inlineStr"/>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="n">
-        <v>-0.1201854273364518</v>
-      </c>
+        <v>2.086570982321206</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>-0.7698775925320547</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>-4655847.763347763</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>-11036.97691197692</v>
+      </c>
+      <c r="BH3" t="inlineStr"/>
       <c r="BI3" t="n">
-        <v>3.76666666666668</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>-1.518367476662632</v>
-      </c>
+        <v>-4.945165945165954</v>
+      </c>
+      <c r="BJ3" t="inlineStr"/>
       <c r="BK3" t="n">
-        <v>3.981357378954641</v>
-      </c>
-      <c r="BL3" t="inlineStr"/>
-      <c r="BM3" t="n">
-        <v>0.1688324071047183</v>
-      </c>
-      <c r="BN3" t="inlineStr"/>
+        <v>-0.7374458874458867</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>-0.315981240981241</v>
+      </c>
+      <c r="BM3" t="inlineStr"/>
+      <c r="BN3" t="n">
+        <v>-5.185209235209228</v>
+      </c>
       <c r="BO3" t="n">
-        <v>3.083333333333343</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>2562.419636046638</v>
-      </c>
+        <v>-9312.095456031384</v>
+      </c>
+      <c r="BP3" t="inlineStr"/>
       <c r="BQ3" t="n">
-        <v>4017780.456576223</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>5308333.333333334</v>
-      </c>
+        <v>-0.1591245193729667</v>
+      </c>
+      <c r="BR3" t="inlineStr"/>
       <c r="BS3" t="inlineStr"/>
-      <c r="BT3" t="inlineStr"/>
+      <c r="BT3" t="n">
+        <v>-3.383567355241112</v>
+      </c>
       <c r="BU3" t="n">
-        <v>-0.6833333333333265</v>
-      </c>
-      <c r="BV3" t="inlineStr"/>
+        <v>-4.851261175713603</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>-2342168.257081627</v>
+      </c>
       <c r="BW3" t="n">
-        <v>4.918597217681878</v>
+        <v>-0.4131313131313132</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>r3GGwC4M</t>
+          <t>2mcmYkSq</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45584.4375</v>
+        <v>45584.5625</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stieler t 
+          <t xml:space="preserve">jablonski s 
   ger </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">bayarena
-  leverkusen </t>
+          <t xml:space="preserve">allianz arena
+  munich </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>4jcj2zMd</t>
+          <t>nVp0wiqd</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>8vndvXTk</t>
+          <t>nJQmYp1B</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1324,179 +1324,179 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>UgdQz0fK</t>
+          <t>GzfvcwRj</t>
         </is>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0.05666666666666709</v>
+        <v>0.8475000000000001</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.198577075098814</v>
+        <v>1.734681818181818</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S4" t="n">
-        <v>2.625</v>
+        <v>1.55</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5</v>
+        <v>-1.6</v>
       </c>
       <c r="U4" t="n">
-        <v>5.46195652173913</v>
+        <v>3.408333333333333</v>
       </c>
       <c r="V4" t="n">
-        <v>9.250000000000002</v>
+        <v>7</v>
       </c>
       <c r="W4" t="n">
-        <v>15.23913043478261</v>
+        <v>8.766666666666669</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.6666666666666665</v>
+        <v>0.2</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.746376811594203</v>
+        <v>1.541666666666667</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.75</v>
+        <v>1.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.25</v>
+        <v>1.3</v>
       </c>
       <c r="AB4" t="n">
-        <v>16.45143946467476</v>
+        <v>13.29858585858586</v>
       </c>
       <c r="AC4" t="n">
-        <v>12.91271647821613</v>
+        <v>17.67838404606516</v>
       </c>
       <c r="AD4" t="n">
-        <v>724.7344050626748</v>
+        <v>932.8115439748174</v>
       </c>
       <c r="AE4" t="n">
-        <v>819.6632622117054</v>
+        <v>960.9502943890363</v>
       </c>
       <c r="AF4" t="n">
-        <v>14.33333333333334</v>
+        <v>3</v>
       </c>
       <c r="AG4" t="n">
-        <v>71.14624505928855</v>
+        <v>36.3821510297483</v>
       </c>
       <c r="AH4" t="n">
-        <v>43.00000000000001</v>
+        <v>8</v>
       </c>
       <c r="AI4" t="n">
-        <v>62.23913043478261</v>
+        <v>30.98398169336385</v>
       </c>
       <c r="AJ4" t="n">
-        <v>13</v>
+        <v>-0.2999999999999972</v>
       </c>
       <c r="AK4" t="n">
-        <v>11.5</v>
+        <v>3.599999999999998</v>
       </c>
       <c r="AL4" t="n">
-        <v>18.5</v>
+        <v>3.799999999999997</v>
       </c>
       <c r="AM4" t="n">
-        <v>20.04347826086956</v>
+        <v>4.099999999999994</v>
       </c>
       <c r="AN4" t="n">
-        <v>361.3333333333334</v>
+        <v>96.25</v>
       </c>
       <c r="AO4" t="n">
-        <v>348.7000000000001</v>
+        <v>35.37857142857143</v>
       </c>
       <c r="AP4" t="n">
-        <v>-0.5</v>
+        <v>0.2999999999999998</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-1.08695652173913</v>
+        <v>-0.6521739130434779</v>
       </c>
       <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="n">
-        <v>-1.75</v>
+        <v>-1</v>
       </c>
       <c r="AT4" t="n">
-        <v>-1.75</v>
+        <v>-2.900000000000002</v>
       </c>
       <c r="AU4" t="n">
-        <v>-2.583333333333332</v>
+        <v>0.3249999999999993</v>
       </c>
       <c r="AV4" t="n">
-        <v>-61.02357543586358</v>
+        <v>2.573983898066601</v>
       </c>
       <c r="AW4" t="n">
-        <v>-28.594677981208</v>
+        <v>-5.284891306475792</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.07006874156183304</v>
+        <v>-0.02107726866719523</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.03113164034668271</v>
+        <v>-0.000970203983232866</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.4166666666666666</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>1.330555555555555</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>-0.6388888888889426</v>
-      </c>
+        <v>0.1333333333333334</v>
+      </c>
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="inlineStr"/>
       <c r="BD4" t="n">
-        <v>63424.99999999999</v>
-      </c>
-      <c r="BE4" t="inlineStr"/>
-      <c r="BF4" t="inlineStr"/>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="n">
-        <v>2.157206487060535</v>
-      </c>
+        <v>-1.088242185088177</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>2.664955001139212</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>33596553.03030303</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>49385.06493506493</v>
+      </c>
+      <c r="BH4" t="inlineStr"/>
       <c r="BI4" t="n">
-        <v>4.12777777777778</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>-4.512668655979212</v>
-      </c>
+        <v>6.618831168831179</v>
+      </c>
+      <c r="BJ4" t="inlineStr"/>
       <c r="BK4" t="n">
-        <v>8.182057607732077</v>
-      </c>
-      <c r="BL4" t="inlineStr"/>
-      <c r="BM4" t="n">
-        <v>0.9550993603182891</v>
-      </c>
-      <c r="BN4" t="inlineStr"/>
+        <v>-2.013636363636351</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1.826190476190476</v>
+      </c>
+      <c r="BM4" t="inlineStr"/>
+      <c r="BN4" t="n">
+        <v>6.258658008657989</v>
+      </c>
       <c r="BO4" t="n">
-        <v>6.646759259259255</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>57083.96674459259</v>
-      </c>
+        <v>51135.93170532025</v>
+      </c>
+      <c r="BP4" t="inlineStr"/>
       <c r="BQ4" t="n">
-        <v>31403242.11040078</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>34240694.44444444</v>
-      </c>
+        <v>1.201072004477577</v>
+      </c>
+      <c r="BR4" t="inlineStr"/>
       <c r="BS4" t="inlineStr"/>
-      <c r="BT4" t="inlineStr"/>
+      <c r="BT4" t="n">
+        <v>5.703150786548605</v>
+      </c>
       <c r="BU4" t="n">
-        <v>1.613425925925931</v>
-      </c>
-      <c r="BV4" t="inlineStr"/>
+        <v>8.297274268559107</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>27952495.23654951</v>
+      </c>
       <c r="BW4" t="n">
-        <v>3.618142201059072</v>
+        <v>1.623593073593074</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>M93rhBJF</t>
+          <t>Eq0zfXl3</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -1504,24 +1504,24 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">siebert d 
+          <t xml:space="preserve">burda m 
   ger </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">europa park stadion
-  freiburg </t>
+          <t xml:space="preserve">prezero arena
+  sinsheim </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>fiEQZ7C7</t>
+          <t>hQAtP9Sl</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>fTVNku3I</t>
+          <t>8Y2m6ADe</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1548,184 +1548,186 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>YZPE6Sx7</t>
+          <t>KUx4Q7x1</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2VSFgl3c</t>
+          <t>f3ddUIXs</t>
         </is>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>3.176666666666666</v>
+        <v>0.7066666666666668</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.418026315789474</v>
+        <v>1.416</v>
       </c>
       <c r="R5" t="n">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="S5" t="n">
-        <v>1.857142857142857</v>
+        <v>1.284782608695652</v>
       </c>
       <c r="T5" t="n">
-        <v>5.333333333333334</v>
+        <v>-0.25</v>
       </c>
       <c r="U5" t="n">
-        <v>2.714285714285714</v>
+        <v>2.006521739130435</v>
       </c>
       <c r="V5" t="n">
-        <v>5.333333333333334</v>
+        <v>4.749999999999998</v>
       </c>
       <c r="W5" t="n">
-        <v>4.19047619047619</v>
+        <v>4.928260869565216</v>
       </c>
       <c r="X5" t="n">
-        <v>1.666666666666667</v>
+        <v>0.25</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.6190476190476191</v>
+        <v>1.197826086956522</v>
       </c>
       <c r="Z5" t="n">
         <v>2</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.142857142857143</v>
+        <v>1.545652173913044</v>
       </c>
       <c r="AB5" t="n">
-        <v>18.19856831621538</v>
+        <v>24.23353079668869</v>
       </c>
       <c r="AC5" t="n">
-        <v>20.34932274411848</v>
+        <v>22.2240920177255</v>
       </c>
       <c r="AD5" t="n">
-        <v>885.9139431699239</v>
+        <v>814.7492937217449</v>
       </c>
       <c r="AE5" t="n">
-        <v>832.898978363493</v>
+        <v>790.4586707757715</v>
       </c>
       <c r="AF5" t="n">
-        <v>-69</v>
+        <v>-55.33333333333333</v>
       </c>
       <c r="AG5" t="n">
-        <v>22.7</v>
+        <v>3.866028708133967</v>
       </c>
       <c r="AH5" t="n">
-        <v>-54</v>
+        <v>1.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.6000000000000014</v>
+        <v>15.50478468899522</v>
       </c>
       <c r="AJ5" t="n">
-        <v>8.333333333333336</v>
+        <v>9.166666666666664</v>
       </c>
       <c r="AK5" t="n">
-        <v>6.666666666666664</v>
+        <v>5.945652173913039</v>
       </c>
       <c r="AL5" t="n">
-        <v>-7.333333333333343</v>
+        <v>9.666666666666671</v>
       </c>
       <c r="AM5" t="n">
-        <v>4.19047619047619</v>
+        <v>8.139130434782615</v>
       </c>
       <c r="AN5" t="n">
-        <v>9.833333333333314</v>
+        <v>47</v>
       </c>
       <c r="AO5" t="n">
-        <v>93.87368421052633</v>
+        <v>90.76428571428573</v>
       </c>
       <c r="AP5" t="n">
-        <v>-2</v>
+        <v>-2.583333333333333</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-1.05</v>
-      </c>
-      <c r="AR5" t="inlineStr"/>
+        <v>-0.5195652173913046</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1</v>
+      </c>
       <c r="AS5" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="AT5" t="n">
-        <v>-1.333333333333329</v>
+        <v>-7.25</v>
       </c>
       <c r="AU5" t="n">
-        <v>-3.095238095238095</v>
+        <v>-4.406521739130438</v>
       </c>
       <c r="AV5" t="n">
-        <v>23.31936090605409</v>
+        <v>5.367079885119217</v>
       </c>
       <c r="AW5" t="n">
-        <v>13.2825256993473</v>
+        <v>6.689962906345777</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.1390896457243926</v>
+        <v>-0.001841130721083641</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.01001544946429198</v>
+        <v>-0.008605130413885283</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.4285714285714285</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>0.4810185185185187</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>-1.331481481481489</v>
-      </c>
+        <v>0.1608695652173913</v>
+      </c>
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="inlineStr"/>
       <c r="BD5" t="n">
-        <v>3868.055555555555</v>
-      </c>
-      <c r="BE5" t="inlineStr"/>
-      <c r="BF5" t="inlineStr"/>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="n">
-        <v>2.151863109619875</v>
-      </c>
+        <v>0.6691832648488969</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>-1.051913846960282</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>5194976.851851852</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>13209.25925925926</v>
+      </c>
+      <c r="BH5" t="inlineStr"/>
       <c r="BI5" t="n">
-        <v>1.714351851851845</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>-0.7950880124372475</v>
-      </c>
+        <v>3.187037037037044</v>
+      </c>
+      <c r="BJ5" t="inlineStr"/>
       <c r="BK5" t="n">
-        <v>1.958802008136544</v>
-      </c>
-      <c r="BL5" t="inlineStr"/>
-      <c r="BM5" t="n">
-        <v>0.2388881341894871</v>
-      </c>
-      <c r="BN5" t="inlineStr"/>
+        <v>0.7874999999999943</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>-0.6518518518518484</v>
+      </c>
+      <c r="BM5" t="inlineStr"/>
+      <c r="BN5" t="n">
+        <v>4.441666666666663</v>
+      </c>
       <c r="BO5" t="n">
-        <v>2.31805555555556</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>3121.224297973349</v>
-      </c>
+        <v>9460.688044898567</v>
+      </c>
+      <c r="BP5" t="inlineStr"/>
       <c r="BQ5" t="n">
-        <v>2237248.604206725</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>5193888.88888889</v>
-      </c>
+        <v>0.2392787524366471</v>
+      </c>
+      <c r="BR5" t="inlineStr"/>
       <c r="BS5" t="inlineStr"/>
-      <c r="BT5" t="inlineStr"/>
+      <c r="BT5" t="n">
+        <v>3.234419507794115</v>
+      </c>
       <c r="BU5" t="n">
-        <v>0.9435185185185198</v>
-      </c>
-      <c r="BV5" t="inlineStr"/>
+        <v>2.931299843374148</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>4087964.059217929</v>
+      </c>
       <c r="BW5" t="n">
-        <v>0.2355958274487051</v>
+        <v>0.6555555555555557</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Eq0zfXl3</t>
+          <t>r3GGwC4M</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -1733,24 +1735,24 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">brych f 
+          <t xml:space="preserve">stieler t 
   ger </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">prezero arena
-  sinsheim </t>
+          <t xml:space="preserve">bayarena
+  leverkusen </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>hQAtP9Sl</t>
+          <t>4jcj2zMd</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>8Y2m6ADe</t>
+          <t>8vndvXTk</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1777,211 +1779,209 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>KUx4Q7x1</t>
+          <t>hAcTWKKN</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>8f6APkLc</t>
+          <t>UgdQz0fK</t>
         </is>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7066666666666668</v>
+        <v>-0.1449999999999998</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.416</v>
+        <v>2.139772727272727</v>
       </c>
       <c r="R6" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.284782608695652</v>
+        <v>2.625</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="U6" t="n">
-        <v>2.006521739130435</v>
+        <v>5.375</v>
       </c>
       <c r="V6" t="n">
-        <v>4.749999999999998</v>
+        <v>10.75</v>
       </c>
       <c r="W6" t="n">
-        <v>4.928260869565216</v>
+        <v>15.41666666666667</v>
       </c>
       <c r="X6" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>16.17481909430439</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>12.89947811977611</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>694.5660202504989</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>814.1965799913603</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>14.33333333333334</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>71.14624505928855</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>43.00000000000001</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>62.23913043478261</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>12.45833333333333</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>25</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>20.66666666666667</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>449.5833333333333</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>360.5666666666667</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>-1.079710144927536</v>
+      </c>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>-2.75</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>-2.749999999999998</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>-69.52248416602228</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>-28.67192593758189</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0.07006874156183304</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0.03113164034668271</v>
+      </c>
+      <c r="AZ6" t="n">
         <v>0.25</v>
       </c>
-      <c r="Y6" t="n">
-        <v>1.197826086956522</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.545652173913044</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>24.23353079668869</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>22.2240920177255</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>814.7492937217449</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>790.4586707757715</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>-55.33333333333333</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>3.866028708133967</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>15.50478468899522</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>9.166666666666664</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>5.945652173913039</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>9.666666666666671</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>8.139130434782615</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>47</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>90.76428571428573</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>-2.583333333333333</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>-0.5195652173913046</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>-7.25</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>-4.406521739130438</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>5.367079885119217</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>6.689962906345777</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>-0.001841130721083641</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>-0.008605130413885283</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0.5</v>
-      </c>
       <c r="BA6" t="n">
-        <v>0.1608695652173913</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>0.6555555555555557</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>0.9290740740740659</v>
-      </c>
+        <v>0.4166666666666666</v>
+      </c>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="inlineStr"/>
       <c r="BD6" t="n">
-        <v>13299.62962962963</v>
-      </c>
-      <c r="BE6" t="inlineStr"/>
-      <c r="BF6" t="inlineStr"/>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="n">
-        <v>-0.8886988083582459</v>
-      </c>
+        <v>-4.307227181143645</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>2.190585979208272</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>35045158.73015872</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>64430.95238095237</v>
+      </c>
+      <c r="BH6" t="inlineStr"/>
       <c r="BI6" t="n">
-        <v>4.352407407407398</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>0.7465432686794884</v>
-      </c>
+        <v>6.785317460317458</v>
+      </c>
+      <c r="BJ6" t="inlineStr"/>
       <c r="BK6" t="n">
-        <v>3.129009111516851</v>
-      </c>
-      <c r="BL6" t="inlineStr"/>
-      <c r="BM6" t="n">
-        <v>0.2392787524366471</v>
-      </c>
-      <c r="BN6" t="inlineStr"/>
+        <v>-0.7150793650793901</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1.662301587301588</v>
+      </c>
+      <c r="BM6" t="inlineStr"/>
+      <c r="BN6" t="n">
+        <v>4.207936507936523</v>
+      </c>
       <c r="BO6" t="n">
-        <v>3.297777777777796</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>9652.669065826956</v>
-      </c>
+        <v>56876.13641948007</v>
+      </c>
+      <c r="BP6" t="inlineStr"/>
       <c r="BQ6" t="n">
-        <v>4122088.735854216</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>5168578.703703703</v>
-      </c>
+        <v>0.9404624529237529</v>
+      </c>
+      <c r="BR6" t="inlineStr"/>
       <c r="BS6" t="inlineStr"/>
-      <c r="BT6" t="inlineStr"/>
+      <c r="BT6" t="n">
+        <v>3.56187460630187</v>
+      </c>
       <c r="BU6" t="n">
-        <v>-0.3696296296296246</v>
-      </c>
-      <c r="BV6" t="inlineStr"/>
+        <v>8.166407663543879</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>30588600.80431694</v>
+      </c>
       <c r="BW6" t="n">
-        <v>3.221392659627952</v>
+        <v>1.36984126984127</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>z1eeWTdd</t>
+          <t>fHjVr7t2</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45583.64583333334</v>
+        <v>45584.4375</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">gerach t 
+          <t xml:space="preserve">exner f 
   ger </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">signal iduna park
-  dortmund </t>
+          <t xml:space="preserve">borussia park
+  monchengladbach </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>nP1i5US1</t>
+          <t>88HSzjDr</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ILyJuN3g</t>
+          <t>KWixEVWi</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2008,209 +2008,211 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>IkCftsQm</t>
+          <t>2VSFgl3c</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0jdIgO6t</t>
+          <t>4ljanukM</t>
         </is>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.300000000000001</v>
+        <v>-0.7533333333333332</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.9391979949874689</v>
+        <v>0.8105000000000004</v>
       </c>
       <c r="R7" t="n">
-        <v>1.75</v>
+        <v>-1</v>
       </c>
       <c r="S7" t="n">
-        <v>1.15527950310559</v>
+        <v>0.9189723320158102</v>
       </c>
       <c r="T7" t="n">
-        <v>3.083333333333333</v>
+        <v>-3.166666666666666</v>
       </c>
       <c r="U7" t="n">
-        <v>1.594202898550725</v>
+        <v>0.9387351778656123</v>
       </c>
       <c r="V7" t="n">
-        <v>7.749999999999998</v>
+        <v>-6</v>
       </c>
       <c r="W7" t="n">
-        <v>2.811594202898549</v>
+        <v>3.962450592885377</v>
       </c>
       <c r="X7" t="n">
-        <v>1.75</v>
+        <v>-2.166666666666667</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.3954451345755692</v>
+        <v>-0.03952569169960474</v>
       </c>
       <c r="Z7" t="n">
-        <v>3</v>
+        <v>-2.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.5155279503105588</v>
+        <v>0.2608695652173911</v>
       </c>
       <c r="AB7" t="n">
-        <v>15.74334178893002</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>19.72753654159919</v>
+        <v>21.47880175380175</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
       <c r="AD7" t="n">
-        <v>733.0633150288402</v>
+        <v>823.7180997505649</v>
       </c>
       <c r="AE7" t="n">
-        <v>839.6607987970957</v>
+        <v>826.9128599267867</v>
       </c>
       <c r="AF7" t="n">
-        <v>12.33333333333333</v>
+        <v>-18.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>15.75</v>
+        <v>-4.861471861471856</v>
       </c>
       <c r="AH7" t="n">
-        <v>22</v>
+        <v>-17.33333333333334</v>
       </c>
       <c r="AI7" t="n">
-        <v>-1.309090909090905</v>
+        <v>4.833333333333336</v>
       </c>
       <c r="AJ7" t="n">
-        <v>13.25</v>
+        <v>-9.25</v>
       </c>
       <c r="AK7" t="n">
-        <v>5.734989648033132</v>
+        <v>-0.5968379446640313</v>
       </c>
       <c r="AL7" t="n">
-        <v>20</v>
+        <v>6.5</v>
       </c>
       <c r="AM7" t="n">
-        <v>11.21325051759834</v>
+        <v>10.53754940711462</v>
       </c>
       <c r="AN7" t="n">
-        <v>306</v>
+        <v>141</v>
       </c>
       <c r="AO7" t="n">
-        <v>155.5500000000001</v>
+        <v>170.95</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.583333333333333</v>
+        <v>1</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-0.6397515527950315</v>
+        <v>-0.1645021645021647</v>
       </c>
       <c r="AR7" t="inlineStr"/>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>-1.5</v>
       </c>
       <c r="AT7" t="n">
-        <v>5.166666666666664</v>
+        <v>-0.6666666666666714</v>
       </c>
       <c r="AU7" t="n">
-        <v>-1.509316770186336</v>
+        <v>-4.395256916996045</v>
       </c>
       <c r="AV7" t="n">
-        <v>-64.66277828460009</v>
+        <v>-10.46584301124083</v>
       </c>
       <c r="AW7" t="n">
-        <v>-21.72839919578044</v>
+        <v>12.43039202983235</v>
       </c>
       <c r="AX7" t="n">
-        <v>-0.03266710043305789</v>
+        <v>0.04751929126929127</v>
       </c>
       <c r="AY7" t="n">
-        <v>-0.01711462257735812</v>
+        <v>0.001574089699500146</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.3333333333333333</v>
+        <v>-0.4166666666666667</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.1946169772256729</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>1.63030303030303</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>0.6063973063972981</v>
-      </c>
+        <v>-0.1304347826086956</v>
+      </c>
+      <c r="BB7" t="inlineStr"/>
+      <c r="BC7" t="inlineStr"/>
       <c r="BD7" t="n">
-        <v>41070.03367003366</v>
-      </c>
-      <c r="BE7" t="inlineStr"/>
-      <c r="BF7" t="inlineStr"/>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="n">
-        <v>-0.873741721453392</v>
-      </c>
+        <v>-1.707927816435472</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>-0.04267150796244934</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>5131190.476190476</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>2314.285714285714</v>
+      </c>
+      <c r="BH7" t="inlineStr"/>
       <c r="BI7" t="n">
-        <v>10.59511784511784</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>-0.5995571383443234</v>
-      </c>
+        <v>3.019047619047626</v>
+      </c>
+      <c r="BJ7" t="inlineStr"/>
       <c r="BK7" t="n">
-        <v>9.12811090087979</v>
-      </c>
-      <c r="BL7" t="inlineStr"/>
-      <c r="BM7" t="n">
-        <v>0.8543211619298576</v>
-      </c>
-      <c r="BN7" t="inlineStr"/>
+        <v>-2.230952380952374</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>-0.7023809523809454</v>
+      </c>
+      <c r="BM7" t="inlineStr"/>
+      <c r="BN7" t="n">
+        <v>3.697619047619071</v>
+      </c>
       <c r="BO7" t="n">
-        <v>11.46127946127945</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>26457.34576890183</v>
-      </c>
+        <v>2415.688289045596</v>
+      </c>
+      <c r="BP7" t="inlineStr"/>
       <c r="BQ7" t="n">
-        <v>20508180.70648734</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>35206414.14141414</v>
-      </c>
+        <v>0.1589104749451267</v>
+      </c>
+      <c r="BR7" t="inlineStr"/>
       <c r="BS7" t="inlineStr"/>
-      <c r="BT7" t="inlineStr"/>
+      <c r="BT7" t="n">
+        <v>4.792678123881132</v>
+      </c>
       <c r="BU7" t="n">
-        <v>-0.0747474747474719</v>
-      </c>
-      <c r="BV7" t="inlineStr"/>
+        <v>3.890520166876826</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>3852930.793598905</v>
+      </c>
       <c r="BW7" t="n">
-        <v>10.93873374697174</v>
+        <v>0.4690476190476192</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>nc8W6DTp</t>
+          <t>M93rhBJF</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45571.60416666666</v>
+        <v>45584.4375</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">reichel t 
+          <t xml:space="preserve">badstubner f 
   ger </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">mhparena
-  stuttgart </t>
+          <t xml:space="preserve">europa park stadion
+  freiburg </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>nJQmYp1B</t>
+          <t>fiEQZ7C7</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>hQAtP9Sl</t>
+          <t>fTVNku3I</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2237,225 +2239,209 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>f3ddUIXs</t>
+          <t>4fuCGs9P</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>4fuCGs9P</t>
+          <t>M5BRZDsC</t>
         </is>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>3.84</v>
+        <v>3.176666666666666</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.382105263157895</v>
+        <v>1.418026315789474</v>
       </c>
       <c r="R8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S8" t="n">
-        <v>2.662337662337662</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="T8" t="n">
-        <v>5.666666666666666</v>
+        <v>5.333333333333334</v>
       </c>
       <c r="U8" t="n">
-        <v>6.519480519480519</v>
+        <v>2.714285714285714</v>
       </c>
       <c r="V8" t="n">
-        <v>16.5</v>
+        <v>5.333333333333334</v>
       </c>
       <c r="W8" t="n">
-        <v>14.83549783549784</v>
+        <v>4.19047619047619</v>
       </c>
       <c r="X8" t="n">
-        <v>2.666666666666667</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="Y8" t="n">
+        <v>0.6190476190476191</v>
+      </c>
+      <c r="Z8" t="n">
         <v>2</v>
       </c>
-      <c r="Z8" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AA8" t="n">
-        <v>2.415584415584416</v>
+        <v>1.142857142857143</v>
       </c>
       <c r="AB8" t="n">
-        <v>13.03180438842204</v>
+        <v>18.19856831621538</v>
       </c>
       <c r="AC8" t="n">
-        <v>16.52550724023109</v>
+        <v>20.34932274411848</v>
       </c>
       <c r="AD8" t="n">
-        <v>873.5725148807396</v>
+        <v>885.9139431699239</v>
       </c>
       <c r="AE8" t="n">
-        <v>815.1798281098756</v>
+        <v>832.898978363493</v>
       </c>
       <c r="AF8" t="n">
-        <v>19.5</v>
+        <v>-69</v>
       </c>
       <c r="AG8" t="n">
-        <v>57.90476190476191</v>
+        <v>22.7</v>
       </c>
       <c r="AH8" t="n">
-        <v>12.5</v>
+        <v>-54</v>
       </c>
       <c r="AI8" t="n">
-        <v>36.29047619047619</v>
+        <v>0.6000000000000014</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.3333333333333286</v>
+        <v>8.333333333333336</v>
       </c>
       <c r="AK8" t="n">
-        <v>9.309523809523807</v>
+        <v>6.666666666666664</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>-7.333333333333343</v>
       </c>
       <c r="AM8" t="n">
-        <v>17.19913419913419</v>
+        <v>4.19047619047619</v>
       </c>
       <c r="AN8" t="n">
-        <v>150.5</v>
+        <v>9.833333333333314</v>
       </c>
       <c r="AO8" t="n">
-        <v>283.4210526315789</v>
+        <v>93.87368421052633</v>
       </c>
       <c r="AP8" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AQ8" t="n">
-        <v>-1.396103896103896</v>
+        <v>-1.05</v>
       </c>
       <c r="AR8" t="inlineStr"/>
       <c r="AS8" t="n">
-        <v>-1.4</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="AT8" t="n">
-        <v>-2.666666666666666</v>
+        <v>-1.333333333333329</v>
       </c>
       <c r="AU8" t="n">
-        <v>-1.54978354978355</v>
+        <v>-3.095238095238095</v>
       </c>
       <c r="AV8" t="n">
-        <v>-12.32696078431372</v>
+        <v>23.31936090605409</v>
       </c>
       <c r="AW8" t="n">
-        <v>-20.05562583271563</v>
+        <v>13.2825256993473</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.09531272573868924</v>
+        <v>-0.1390896457243926</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.02059955942118073</v>
+        <v>-0.01001544946429198</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="BA8" t="n">
         <v>0.4285714285714285</v>
       </c>
-      <c r="BB8" t="n">
-        <v>-0.1958152958152959</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>-0.3159932659932565</v>
-      </c>
+      <c r="BB8" t="inlineStr"/>
+      <c r="BC8" t="inlineStr"/>
       <c r="BD8" t="n">
-        <v>-2692.472342472342</v>
+        <v>-0.8271844172104466</v>
       </c>
       <c r="BE8" t="n">
-        <v>-26000</v>
+        <v>1.972065612875756</v>
       </c>
       <c r="BF8" t="n">
-        <v>2400000</v>
+        <v>5381904.761904763</v>
       </c>
       <c r="BG8" t="n">
-        <v>-3.066666666666666</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>-0.1641996405154309</v>
-      </c>
+        <v>4045.238095238095</v>
+      </c>
+      <c r="BH8" t="inlineStr"/>
       <c r="BI8" t="n">
-        <v>1.411712361712375</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>-1.93927875243665</v>
-      </c>
+        <v>2.44285714285715</v>
+      </c>
+      <c r="BJ8" t="inlineStr"/>
       <c r="BK8" t="n">
-        <v>2.04899622794359</v>
+        <v>-1.275793650793673</v>
       </c>
       <c r="BL8" t="n">
-        <v>60</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>0.2443735601630339</v>
-      </c>
+        <v>0.9956349206349202</v>
+      </c>
+      <c r="BM8" t="inlineStr"/>
       <c r="BN8" t="n">
-        <v>1</v>
+        <v>1.767063492063471</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.34783549783549</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>-512.6174020910839</v>
-      </c>
+        <v>2784.877743830348</v>
+      </c>
+      <c r="BP8" t="inlineStr"/>
       <c r="BQ8" t="n">
-        <v>4416343.162198429</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>6268771.043771042</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>85</v>
-      </c>
+        <v>0.2290413256350314</v>
+      </c>
+      <c r="BR8" t="inlineStr"/>
+      <c r="BS8" t="inlineStr"/>
       <c r="BT8" t="n">
-        <v>0</v>
+        <v>0.2612278182197372</v>
       </c>
       <c r="BU8" t="n">
-        <v>-2.729894179894185</v>
+        <v>1.671632664229946</v>
       </c>
       <c r="BV8" t="n">
-        <v>2.800000000000011</v>
+        <v>1924586.889432981</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.6386699070909856</v>
+        <v>0.4944444444444447</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>ShoJUGLi</t>
+          <t>E7rNpTBk</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45571.52083333334</v>
+        <v>45584.4375</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">zwayer f 
+          <t xml:space="preserve">siebert d 
   ger </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">deutsche bank park
-  frankfurt </t>
+          <t xml:space="preserve">mewa arena
+  mainz </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>8vndvXTk</t>
+          <t>EuakNmc1</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>nVp0wiqd</t>
+          <t>KbS1suSm</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2482,229 +2468,209 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>A15eUM4C</t>
+          <t>0jdIgO6t</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>hAcTWKKN</t>
+          <t>2VSFgl3c</t>
         </is>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.401666666666667</v>
+        <v>0.996666666666667</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.5553132832080201</v>
+        <v>0.4235000000000002</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.09610983981693355</v>
+        <v>1.2</v>
       </c>
       <c r="T9" t="n">
-        <v>-7</v>
+        <v>-2.666666666666667</v>
       </c>
       <c r="U9" t="n">
-        <v>-2.041189931350115</v>
+        <v>0.1369565217391298</v>
       </c>
       <c r="V9" t="n">
-        <v>-14.25</v>
+        <v>2.666666666666664</v>
       </c>
       <c r="W9" t="n">
-        <v>-3.734553775743708</v>
+        <v>4.78913043478261</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.75</v>
+        <v>-2.333333333333333</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.4988558352402745</v>
+        <v>-0.6391304347826086</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>-3.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.1922196796338671</v>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>-1.05</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>18.97383357383357</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>18.80677971548538</v>
       </c>
       <c r="AD9" t="n">
-        <v>1298.060004493361</v>
+        <v>893.7443437962941</v>
       </c>
       <c r="AE9" t="n">
-        <v>1046.664945470352</v>
+        <v>901.3317456712546</v>
       </c>
       <c r="AF9" t="n">
-        <v>-65.66666666666667</v>
+        <v>25</v>
       </c>
       <c r="AG9" t="n">
-        <v>-29.57070707070707</v>
+        <v>10.50717703349282</v>
       </c>
       <c r="AH9" t="n">
-        <v>-44</v>
+        <v>19.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>-11.75757575757576</v>
+        <v>16.20813397129186</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-8</v>
+        <v>13.41666666666666</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.279176201372998</v>
+        <v>2.450000000000003</v>
       </c>
       <c r="AL9" t="n">
-        <v>-42</v>
+        <v>-3.333333333333329</v>
       </c>
       <c r="AM9" t="n">
-        <v>-17.10297482837528</v>
+        <v>-10.47826086956522</v>
       </c>
       <c r="AN9" t="n">
-        <v>-568.8333333333333</v>
+        <v>-17.66666666666669</v>
       </c>
       <c r="AO9" t="n">
-        <v>-179.5842105263157</v>
+        <v>-129.85</v>
       </c>
       <c r="AP9" t="n">
-        <v>-2.5</v>
+        <v>1.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-0.6161616161616161</v>
+        <v>0.9318181818181821</v>
       </c>
       <c r="AR9" t="inlineStr"/>
       <c r="AS9" t="n">
-        <v>-2</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="AT9" t="n">
-        <v>-2</v>
+        <v>-3.416666666666671</v>
       </c>
       <c r="AU9" t="n">
-        <v>-0.5125858123569795</v>
+        <v>2.825000000000003</v>
       </c>
       <c r="AV9" t="n">
-        <v>86.42643358438505</v>
+        <v>33.97120610870611</v>
       </c>
       <c r="AW9" t="n">
-        <v>24.09542703326451</v>
+        <v>7.717998126482772</v>
       </c>
       <c r="AX9" t="n">
-        <v>-0.05814469423076903</v>
+        <v>0.06997299997299998</v>
       </c>
       <c r="AY9" t="n">
-        <v>-0.01328353982935117</v>
+        <v>0.04047277303910549</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="BA9" t="n">
-        <v>-0.006864988558352408</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>-1.388888888888889</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>1.322222222222251</v>
-      </c>
+        <v>-0.04166666666666666</v>
+      </c>
+      <c r="BB9" t="inlineStr"/>
+      <c r="BC9" t="inlineStr"/>
       <c r="BD9" t="n">
-        <v>-41816.66666666666</v>
+        <v>-1.128159994726218</v>
       </c>
       <c r="BE9" t="n">
-        <v>-273000</v>
+        <v>0.3493346142284643</v>
       </c>
       <c r="BF9" t="n">
-        <v>-188575000</v>
+        <v>-23900375.18037518</v>
       </c>
       <c r="BG9" t="n">
-        <v>-2.666666666666668</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>-4.478409090909093</v>
-      </c>
+        <v>-31400.2886002886</v>
+      </c>
+      <c r="BH9" t="inlineStr"/>
       <c r="BI9" t="n">
-        <v>-3.972222222222214</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>1.737788399108098</v>
-      </c>
+        <v>-5.612554112554108</v>
+      </c>
+      <c r="BJ9" t="inlineStr"/>
       <c r="BK9" t="n">
-        <v>-9.030224067298363</v>
+        <v>-0.02037037037035816</v>
       </c>
       <c r="BL9" t="n">
-        <v>-385</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>-1.322728418239254</v>
-      </c>
+        <v>1.674434824434826</v>
+      </c>
+      <c r="BM9" t="inlineStr"/>
       <c r="BN9" t="n">
-        <v>-5</v>
+        <v>-7.036435786435774</v>
       </c>
       <c r="BO9" t="n">
-        <v>-5.866666666666674</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>-49850.87626368586</v>
-      </c>
+        <v>-31066.50115389059</v>
+      </c>
+      <c r="BP9" t="inlineStr"/>
       <c r="BQ9" t="n">
-        <v>-29414448.11116028</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>-32054861.1111111</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>-422</v>
-      </c>
+        <v>-0.8493754878346873</v>
+      </c>
+      <c r="BR9" t="inlineStr"/>
+      <c r="BS9" t="inlineStr"/>
       <c r="BT9" t="n">
-        <v>-9</v>
+        <v>-5.502291214199644</v>
       </c>
       <c r="BU9" t="n">
-        <v>-2.038888888888888</v>
+        <v>-7.269611019580609</v>
       </c>
       <c r="BV9" t="n">
-        <v>-11.5</v>
+        <v>-21476216.41353245</v>
       </c>
       <c r="BW9" t="n">
-        <v>-2.930095041124474</v>
+        <v>-0.8153920153920158</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>0KbQSfj4</t>
+          <t>z1eeWTdd</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45571.4375</v>
+        <v>45583.64583333334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">siebert d 
+          <t xml:space="preserve">dingert c 
   ger </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">voith arena
-  heidenheim </t>
+          <t xml:space="preserve">signal iduna park
+  dortmund </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>KWixEVWi</t>
+          <t>nP1i5US1</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>KbS1suSm</t>
+          <t>ILyJuN3g</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2731,223 +2697,209 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
+          <t>hpYJ6izc</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
           <t>vZA6VYpf</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2VSFgl3c</t>
         </is>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.61</v>
+        <v>1.300000000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.4816052631578946</v>
+        <v>0.9391979949874689</v>
       </c>
       <c r="R10" t="n">
-        <v>2.5</v>
+        <v>1.75</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3157894736842106</v>
+        <v>1.15527950310559</v>
       </c>
       <c r="T10" t="n">
-        <v>1.833333333333333</v>
+        <v>3.083333333333333</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.176201372997712</v>
+        <v>1.594202898550725</v>
       </c>
       <c r="V10" t="n">
-        <v>2.499999999999998</v>
+        <v>7.749999999999998</v>
       </c>
       <c r="W10" t="n">
-        <v>0.8443935926773456</v>
+        <v>2.811594202898549</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.8333333333333335</v>
+        <v>1.75</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0.4759725400457666</v>
+        <v>0.3954451345755692</v>
       </c>
       <c r="Z10" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0.4668192219679632</v>
+        <v>0.5155279503105588</v>
       </c>
       <c r="AB10" t="n">
-        <v>20.37298474945534</v>
+        <v>15.74334178893002</v>
       </c>
       <c r="AC10" t="n">
-        <v>20.7540593529089</v>
+        <v>19.72753654159919</v>
       </c>
       <c r="AD10" t="n">
-        <v>1108.081876817196</v>
+        <v>733.0633150288402</v>
       </c>
       <c r="AE10" t="n">
-        <v>975.096884151051</v>
+        <v>839.6607987970957</v>
       </c>
       <c r="AF10" t="n">
-        <v>-55.5</v>
+        <v>12.33333333333333</v>
       </c>
       <c r="AG10" t="n">
-        <v>-17.65656565656566</v>
+        <v>15.75</v>
       </c>
       <c r="AH10" t="n">
-        <v>-38.5</v>
+        <v>22</v>
       </c>
       <c r="AI10" t="n">
-        <v>2.348484848484851</v>
+        <v>-1.309090909090905</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-1.666666666666664</v>
+        <v>13.25</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.7963386727688757</v>
+        <v>5.734989648033132</v>
       </c>
       <c r="AL10" t="n">
-        <v>-25</v>
+        <v>20</v>
       </c>
       <c r="AM10" t="n">
-        <v>-14.74141876430205</v>
+        <v>11.21325051759834</v>
       </c>
       <c r="AN10" t="n">
-        <v>-270.5</v>
+        <v>306</v>
       </c>
       <c r="AO10" t="n">
-        <v>-200.771052631579</v>
+        <v>155.5500000000001</v>
       </c>
       <c r="AP10" t="n">
+        <v>1.583333333333333</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>-0.6397515527950315</v>
+      </c>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="n">
         <v>0</v>
       </c>
-      <c r="AQ10" t="n">
-        <v>-0.002392344497607279</v>
-      </c>
-      <c r="AR10" t="inlineStr"/>
-      <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
-        <v>0.5000000000000009</v>
+        <v>5.166666666666664</v>
       </c>
       <c r="AU10" t="n">
-        <v>4.11441647597254</v>
+        <v>-1.509316770186336</v>
       </c>
       <c r="AV10" t="n">
-        <v>50.88180014430015</v>
+        <v>-64.66277828460009</v>
       </c>
       <c r="AW10" t="n">
-        <v>11.84274039492498</v>
+        <v>-21.72839919578044</v>
       </c>
       <c r="AX10" t="n">
-        <v>-0.1424963924963925</v>
+        <v>-0.03266710043305789</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.02223712429452592</v>
+        <v>-0.01711462257735812</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.06178489702517162</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>-1.208249158249159</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>3.751851851851853</v>
-      </c>
+        <v>0.1946169772256729</v>
+      </c>
+      <c r="BB10" t="inlineStr"/>
+      <c r="BC10" t="inlineStr"/>
       <c r="BD10" t="n">
-        <v>-34560.60606060606</v>
+        <v>-0.5740564945207041</v>
       </c>
       <c r="BE10" t="n">
-        <v>-84000</v>
+        <v>-0.6286207236517818</v>
       </c>
       <c r="BF10" t="n">
-        <v>-55900000</v>
+        <v>35161341.99134199</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.6499999999999986</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>0.3342037959348438</v>
-      </c>
+        <v>40811.97691197691</v>
+      </c>
+      <c r="BH10" t="inlineStr"/>
       <c r="BI10" t="n">
-        <v>-9.784848484848496</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>0.404718962972936</v>
-      </c>
+        <v>11.34083694083692</v>
+      </c>
+      <c r="BJ10" t="inlineStr"/>
       <c r="BK10" t="n">
-        <v>-8.926981754435815</v>
+        <v>0.741847041847052</v>
       </c>
       <c r="BL10" t="n">
-        <v>41</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>-0.9367096476271666</v>
-      </c>
+        <v>-0.1264069264069256</v>
+      </c>
+      <c r="BM10" t="inlineStr"/>
       <c r="BN10" t="n">
-        <v>1</v>
+        <v>10.55295815295815</v>
       </c>
       <c r="BO10" t="n">
-        <v>-7.969696969696969</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>-32594.17840744231</v>
-      </c>
+        <v>27557.4241928933</v>
+      </c>
+      <c r="BP10" t="inlineStr"/>
       <c r="BQ10" t="n">
-        <v>-22624496.18268996</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>-27282676.76767677</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>38</v>
-      </c>
+        <v>0.8976888154887503</v>
+      </c>
+      <c r="BR10" t="inlineStr"/>
+      <c r="BS10" t="inlineStr"/>
       <c r="BT10" t="n">
-        <v>-3</v>
+        <v>10.91741088086299</v>
       </c>
       <c r="BU10" t="n">
-        <v>0.9387205387205348</v>
+        <v>9.515824381205221</v>
       </c>
       <c r="BV10" t="n">
-        <v>6.050000000000011</v>
+        <v>20720545.86871847</v>
       </c>
       <c r="BW10" t="n">
-        <v>-9.692955409979916</v>
+        <v>1.611688311688312</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>zwD8uYZ9</t>
+          <t>nc8W6DTp</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45570.5625</v>
+        <v>45571.60416666666</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">dingert c 
+          <t xml:space="preserve">osmers h 
   ger </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">millerntor stadion
-  hamburg </t>
+          <t xml:space="preserve">mhparena
+  stuttgart </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ILyJuN3g</t>
+          <t>nJQmYp1B</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>EuakNmc1</t>
+          <t>hQAtP9Sl</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2974,225 +2926,225 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>YZPE6Sx7</t>
+          <t>f3ddUIXs</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>4ljanukM</t>
+          <t>4fuCGs9P</t>
         </is>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.640000000000001</v>
+        <v>3.84</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.654500000000001</v>
+        <v>2.382105263157895</v>
       </c>
       <c r="R11" t="n">
+        <v>5</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.662337662337662</v>
+      </c>
+      <c r="T11" t="n">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="U11" t="n">
+        <v>6.519480519480519</v>
+      </c>
+      <c r="V11" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="W11" t="n">
+        <v>14.83549783549784</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="Y11" t="n">
         <v>2</v>
       </c>
-      <c r="S11" t="n">
-        <v>1.948051948051948</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.833333333333333</v>
-      </c>
-      <c r="U11" t="n">
-        <v>5.047619047619047</v>
-      </c>
-      <c r="V11" t="n">
-        <v>16</v>
-      </c>
-      <c r="W11" t="n">
-        <v>11.4978354978355</v>
-      </c>
-      <c r="X11" t="n">
-        <v>-2</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.584415584415584</v>
-      </c>
       <c r="Z11" t="n">
-        <v>-3.5</v>
+        <v>2.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.831168831168831</v>
+        <v>2.415584415584416</v>
       </c>
       <c r="AB11" t="n">
-        <v>13.24307359307359</v>
+        <v>13.03180438842204</v>
       </c>
       <c r="AC11" t="n">
-        <v>15.85195102580032</v>
+        <v>16.52550724023109</v>
       </c>
       <c r="AD11" t="n">
-        <v>805.0903711923211</v>
+        <v>873.5725148807396</v>
       </c>
       <c r="AE11" t="n">
-        <v>755.0678608600734</v>
+        <v>815.1798281098756</v>
       </c>
       <c r="AF11" t="n">
-        <v>72.5</v>
+        <v>19.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>53.46190476190476</v>
+        <v>57.90476190476191</v>
       </c>
       <c r="AH11" t="n">
-        <v>-2</v>
+        <v>12.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>22.68571428571429</v>
+        <v>36.29047619047619</v>
       </c>
       <c r="AJ11" t="n">
-        <v>19.5</v>
+        <v>0.3333333333333286</v>
       </c>
       <c r="AK11" t="n">
-        <v>9.686147186147181</v>
+        <v>9.309523809523807</v>
       </c>
       <c r="AL11" t="n">
-        <v>4.666666666666671</v>
+        <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>22.72294372294371</v>
+        <v>17.19913419913419</v>
       </c>
       <c r="AN11" t="n">
-        <v>171</v>
+        <v>150.5</v>
       </c>
       <c r="AO11" t="n">
-        <v>258.6842105263157</v>
+        <v>283.4210526315789</v>
       </c>
       <c r="AP11" t="n">
-        <v>-1.666666666666667</v>
+        <v>-1</v>
       </c>
       <c r="AQ11" t="n">
-        <v>-0.8727272727272726</v>
+        <v>-1.396103896103896</v>
       </c>
       <c r="AR11" t="inlineStr"/>
       <c r="AS11" t="n">
-        <v>0.5833333333333333</v>
+        <v>-1.4</v>
       </c>
       <c r="AT11" t="n">
-        <v>-9.666666666666668</v>
+        <v>-2.666666666666666</v>
       </c>
       <c r="AU11" t="n">
-        <v>-4.482683982683982</v>
+        <v>-1.54978354978355</v>
       </c>
       <c r="AV11" t="n">
-        <v>40.9329365079365</v>
+        <v>-12.32696078431372</v>
       </c>
       <c r="AW11" t="n">
-        <v>-11.6407922672262</v>
+        <v>-20.05562583271563</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.1498982498982499</v>
+        <v>0.09531272573868924</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.02578587062112861</v>
+        <v>0.02059955942118073</v>
       </c>
       <c r="AZ11" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.2337662337662337</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="BB11" t="n">
-        <v>-0.4111111111111108</v>
+        <v>-35000</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.046296296296248</v>
+        <v>87</v>
       </c>
       <c r="BD11" t="n">
-        <v>-8096.464646464643</v>
+        <v>-1.93927875243665</v>
       </c>
       <c r="BE11" t="n">
-        <v>45000</v>
+        <v>-0.1641996405154309</v>
       </c>
       <c r="BF11" t="n">
-        <v>-4690000</v>
+        <v>6268771.043771042</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.600000000000001</v>
+        <v>-2692.472342472342</v>
       </c>
       <c r="BH11" t="n">
-        <v>-0.468746993746997</v>
+        <v>1</v>
       </c>
       <c r="BI11" t="n">
-        <v>-3.407407407407405</v>
+        <v>1.34783549783549</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.7547213994582194</v>
+        <v>700000</v>
       </c>
       <c r="BK11" t="n">
-        <v>-2.879398622819679</v>
+        <v>-0.3159932659932565</v>
       </c>
       <c r="BL11" t="n">
-        <v>250</v>
+        <v>-2.729894179894185</v>
       </c>
       <c r="BM11" t="n">
-        <v>-0.1303922685501633</v>
+        <v>56</v>
       </c>
       <c r="BN11" t="n">
-        <v>4</v>
+        <v>1.411712361712375</v>
       </c>
       <c r="BO11" t="n">
-        <v>-4.325420875420875</v>
+        <v>-512.6174020910839</v>
       </c>
       <c r="BP11" t="n">
-        <v>-5393.445735551</v>
+        <v>-4.466666666666669</v>
       </c>
       <c r="BQ11" t="n">
-        <v>-1412195.909597225</v>
+        <v>0.2443735601630339</v>
       </c>
       <c r="BR11" t="n">
-        <v>-4245134.68013468</v>
+        <v>-1</v>
       </c>
       <c r="BS11" t="n">
-        <v>257</v>
+        <v>3.199999999999989</v>
       </c>
       <c r="BT11" t="n">
-        <v>4</v>
+        <v>0.6386699070909856</v>
       </c>
       <c r="BU11" t="n">
-        <v>-0.869696969696971</v>
+        <v>2.04899622794359</v>
       </c>
       <c r="BV11" t="n">
-        <v>2</v>
+        <v>4416343.162198429</v>
       </c>
       <c r="BW11" t="n">
-        <v>-4.339561656666916</v>
+        <v>-0.1958152958152959</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>tbtaPLqC</t>
+          <t>ShoJUGLi</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45570.4375</v>
+        <v>45571.52083333334</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">stieler t 
+          <t xml:space="preserve">brand b 
   ger </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">bayarena
-  leverkusen </t>
+          <t xml:space="preserve">deutsche bank park
+  frankfurt </t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>4jcj2zMd</t>
+          <t>8vndvXTk</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>63WsD2ei</t>
+          <t>nVp0wiqd</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3219,223 +3171,229 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>K6A2elS9</t>
+          <t>A15eUM4C</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>UgdQz0fK</t>
+          <t>hAcTWKKN</t>
         </is>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.051666666666667</v>
+        <v>-1.401666666666667</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.622883295194508</v>
+        <v>-0.5553132832080201</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.062111801242236</v>
+        <v>-0.09610983981693355</v>
       </c>
       <c r="T12" t="n">
-        <v>3.666666666666667</v>
+        <v>-7</v>
       </c>
       <c r="U12" t="n">
-        <v>5.08695652173913</v>
+        <v>-2.041189931350115</v>
       </c>
       <c r="V12" t="n">
-        <v>12.33333333333334</v>
+        <v>-14.25</v>
       </c>
       <c r="W12" t="n">
-        <v>14.12008281573499</v>
+        <v>-3.734553775743708</v>
       </c>
       <c r="X12" t="n">
-        <v>0.3333333333333335</v>
+        <v>-1.75</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.9130434782608694</v>
+        <v>-0.4988558352402745</v>
       </c>
       <c r="Z12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.7763975155279503</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>15.1473544973545</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>15.38765589213857</v>
+        <v>0.1922196796338671</v>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
       <c r="AD12" t="n">
-        <v>770.7488086680588</v>
+        <v>1298.060004493361</v>
       </c>
       <c r="AE12" t="n">
-        <v>811.398066276884</v>
+        <v>1046.664945470352</v>
       </c>
       <c r="AF12" t="n">
-        <v>-10</v>
+        <v>-65.66666666666667</v>
       </c>
       <c r="AG12" t="n">
-        <v>64.51363636363637</v>
+        <v>-29.57070707070707</v>
       </c>
       <c r="AH12" t="n">
-        <v>37</v>
+        <v>-44</v>
       </c>
       <c r="AI12" t="n">
-        <v>61.75</v>
+        <v>-11.75757575757576</v>
       </c>
       <c r="AJ12" t="n">
-        <v>10.33333333333333</v>
+        <v>-8</v>
       </c>
       <c r="AK12" t="n">
-        <v>11.4368530020704</v>
+        <v>2.279176201372998</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>-42</v>
       </c>
       <c r="AM12" t="n">
-        <v>16.09109730848861</v>
+        <v>-17.10297482837528</v>
       </c>
       <c r="AN12" t="n">
-        <v>192.0000000000001</v>
+        <v>-568.8333333333333</v>
       </c>
       <c r="AO12" t="n">
-        <v>251.1684210526317</v>
+        <v>-179.5842105263157</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.666666666666667</v>
+        <v>-2.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-0.173913043478261</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>-1</v>
-      </c>
+        <v>-0.6161616161616161</v>
+      </c>
+      <c r="AR12" t="inlineStr"/>
       <c r="AS12" t="n">
-        <v>-0.3571428571428572</v>
+        <v>-2</v>
       </c>
       <c r="AT12" t="n">
-        <v>-4.999999999999999</v>
+        <v>-2</v>
       </c>
       <c r="AU12" t="n">
-        <v>-2.815734989648032</v>
+        <v>-0.5125858123569795</v>
       </c>
       <c r="AV12" t="n">
-        <v>-2.314682539682551</v>
+        <v>86.42643358438505</v>
       </c>
       <c r="AW12" t="n">
-        <v>-22.6759583817998</v>
+        <v>24.09542703326451</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.06273673252611867</v>
+        <v>-0.05814469423076903</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.05374594610484556</v>
+        <v>-0.01328353982935117</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>-0.1759834368530021</v>
+        <v>-0.006864988558352408</v>
       </c>
       <c r="BB12" t="n">
-        <v>2.025</v>
+        <v>-273000</v>
       </c>
       <c r="BC12" t="n">
-        <v>-1.342003367003372</v>
+        <v>-422</v>
       </c>
       <c r="BD12" t="n">
-        <v>81911.40572390571</v>
+        <v>1.737788399108098</v>
       </c>
       <c r="BE12" t="n">
-        <v>-29000</v>
+        <v>-4.478409090909093</v>
       </c>
       <c r="BF12" t="n">
-        <v>-3800000</v>
-      </c>
-      <c r="BG12" t="inlineStr"/>
+        <v>-32054861.1111111</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>-41816.66666666666</v>
+      </c>
       <c r="BH12" t="n">
-        <v>-0.9392790449513164</v>
+        <v>-5</v>
       </c>
       <c r="BI12" t="n">
-        <v>13.60867003367002</v>
+        <v>-5.866666666666674</v>
       </c>
       <c r="BJ12" t="n">
-        <v>-4.45476822307873</v>
+        <v>-188575000</v>
       </c>
       <c r="BK12" t="n">
-        <v>12.6900422157167</v>
+        <v>1.322222222222251</v>
       </c>
       <c r="BL12" t="n">
-        <v>-138</v>
+        <v>-2.038888888888888</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.317095259156293</v>
+        <v>-385</v>
       </c>
       <c r="BN12" t="n">
-        <v>-2</v>
+        <v>-3.972222222222214</v>
       </c>
       <c r="BO12" t="n">
-        <v>13.70416666666667</v>
+        <v>-49850.87626368586</v>
       </c>
       <c r="BP12" t="n">
-        <v>66906.34908934335</v>
+        <v>-2.666666666666668</v>
       </c>
       <c r="BQ12" t="n">
-        <v>38404837.215588</v>
+        <v>-1.322728418239254</v>
       </c>
       <c r="BR12" t="n">
-        <v>47556127.94612794</v>
+        <v>-9</v>
       </c>
       <c r="BS12" t="n">
-        <v>-147</v>
+        <v>-11.5</v>
       </c>
       <c r="BT12" t="n">
-        <v>-2</v>
+        <v>-2.930095041124474</v>
       </c>
       <c r="BU12" t="n">
-        <v>-0.310521885521883</v>
-      </c>
-      <c r="BV12" t="inlineStr"/>
+        <v>-9.030224067298363</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>-29414448.11116028</v>
+      </c>
       <c r="BW12" t="n">
-        <v>11.94463393544552</v>
+        <v>-1.388888888888889</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>ENOasf5c</t>
+          <t>0KbQSfj4</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45570.4375</v>
+        <v>45571.4375</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">burda m 
+          <t xml:space="preserve">stegemann s 
   ger </t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">vonovia ruhrstadion
-  bochum </t>
+          <t xml:space="preserve">voith arena
+  heidenheim </t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>8Y2m6ADe</t>
+          <t>KWixEVWi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>nwkTahLL</t>
+          <t>KbS1suSm</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3462,931 +3420,192 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>IkCftsQm</t>
+          <t>vZA6VYpf</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>GzfvcwRj</t>
+          <t>2VSFgl3c</t>
         </is>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.8249999999999997</v>
+        <v>1.61</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.1836052631578947</v>
+        <v>-0.4816052631578946</v>
       </c>
       <c r="R13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-0.3157894736842106</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.833333333333333</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-1.176201372997712</v>
+      </c>
+      <c r="V13" t="n">
+        <v>2.499999999999998</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.8443935926773456</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-0.8333333333333335</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>-0.4759725400457666</v>
+      </c>
+      <c r="Z13" t="n">
         <v>-2</v>
       </c>
-      <c r="S13" t="n">
-        <v>0.6818181818181818</v>
-      </c>
-      <c r="T13" t="n">
-        <v>-0.5000000000000004</v>
-      </c>
-      <c r="U13" t="n">
-        <v>-0.172727272727272</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1</v>
-      </c>
-      <c r="W13" t="n">
-        <v>3.272727272727272</v>
-      </c>
-      <c r="X13" t="n">
-        <v>-1.666666666666667</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>-0.03636363636363638</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>-2.5</v>
-      </c>
       <c r="AA13" t="n">
-        <v>0.5318181818181817</v>
+        <v>-0.4668192219679632</v>
       </c>
       <c r="AB13" t="n">
-        <v>20.97172619047619</v>
+        <v>20.37298474945534</v>
       </c>
       <c r="AC13" t="n">
-        <v>21.29237880439267</v>
+        <v>20.7540593529089</v>
       </c>
       <c r="AD13" t="n">
-        <v>827.5675123304995</v>
+        <v>1108.081876817196</v>
       </c>
       <c r="AE13" t="n">
-        <v>799.57140873158</v>
+        <v>975.096884151051</v>
       </c>
       <c r="AF13" t="n">
-        <v>-48.5</v>
+        <v>-55.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>27.41102756892231</v>
+        <v>-17.65656565656566</v>
       </c>
       <c r="AH13" t="n">
-        <v>-78</v>
+        <v>-38.5</v>
       </c>
       <c r="AI13" t="n">
-        <v>9.937343358395992</v>
+        <v>2.348484848484851</v>
       </c>
       <c r="AJ13" t="n">
-        <v>-15.33333333333333</v>
+        <v>-1.666666666666664</v>
       </c>
       <c r="AK13" t="n">
-        <v>-0.6999999999999957</v>
+        <v>0.7963386727688757</v>
       </c>
       <c r="AL13" t="n">
-        <v>-15</v>
+        <v>-25</v>
       </c>
       <c r="AM13" t="n">
-        <v>-0.6454545454545411</v>
+        <v>-14.74141876430205</v>
       </c>
       <c r="AN13" t="n">
-        <v>189</v>
+        <v>-270.5</v>
       </c>
       <c r="AO13" t="n">
-        <v>45.6447368421052</v>
+        <v>-200.771052631579</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.666666666666666</v>
+        <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.4454545454545453</v>
+        <v>-0.002392344497607279</v>
       </c>
       <c r="AR13" t="inlineStr"/>
-      <c r="AS13" t="n">
-        <v>0.3333333333333333</v>
-      </c>
+      <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
-        <v>6</v>
+        <v>0.5000000000000009</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.6272727272727288</v>
+        <v>4.11441647597254</v>
       </c>
       <c r="AV13" t="n">
-        <v>-11.35112044817927</v>
+        <v>50.88180014430015</v>
       </c>
       <c r="AW13" t="n">
-        <v>-3.141745981407553</v>
+        <v>11.84274039492498</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.04466156603253377</v>
+        <v>-0.1424963924963925</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.022284548214788</v>
+        <v>0.02223712429452592</v>
       </c>
       <c r="AZ13" t="n">
-        <v>-1.166666666666667</v>
+        <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.04090909090909092</v>
+        <v>0.06178489702517162</v>
       </c>
       <c r="BB13" t="n">
-        <v>-0.4189814814814812</v>
+        <v>-111000</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.442222222222199</v>
+        <v>-41</v>
       </c>
       <c r="BD13" t="n">
-        <v>-19354.72222222222</v>
+        <v>0.404718962972936</v>
       </c>
       <c r="BE13" t="n">
-        <v>-212000</v>
+        <v>0.3342037959348438</v>
       </c>
       <c r="BF13" t="n">
-        <v>-70525000</v>
+        <v>-27282676.76767677</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.428571428571427</v>
+        <v>-34560.60606060606</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.5741362581919844</v>
+        <v>0</v>
       </c>
       <c r="BI13" t="n">
-        <v>-6.237592592592577</v>
+        <v>-7.969696969696969</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.5546055387967215</v>
+        <v>-62900000</v>
       </c>
       <c r="BK13" t="n">
-        <v>-4.6881608716361</v>
+        <v>3.751851851851853</v>
       </c>
       <c r="BL13" t="n">
-        <v>-384</v>
+        <v>0.9387205387205348</v>
       </c>
       <c r="BM13" t="n">
-        <v>-0.3334286492374725</v>
+        <v>-34</v>
       </c>
       <c r="BN13" t="n">
+        <v>-9.784848484848496</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>-32594.17840744231</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>-0.9367096476271666</v>
+      </c>
+      <c r="BR13" t="n">
         <v>-5</v>
       </c>
-      <c r="BO13" t="n">
-        <v>-3.713055555555556</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>-17281.67090047894</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>-6019114.377982412</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>-8035939.814814814</v>
-      </c>
       <c r="BS13" t="n">
-        <v>-411</v>
+        <v>9</v>
       </c>
       <c r="BT13" t="n">
-        <v>-9</v>
+        <v>-9.692955409979916</v>
       </c>
       <c r="BU13" t="n">
-        <v>3.348333333333333</v>
+        <v>-8.926981754435815</v>
       </c>
       <c r="BV13" t="n">
-        <v>2.928571428571416</v>
+        <v>-22624496.18268996</v>
       </c>
       <c r="BW13" t="n">
-        <v>-3.810392630961516</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>lpXDJjDj</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45570.4375</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">reichel t 
-  ger </t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadion an der alten forsterei
-  berlin </t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>pzHW4oaE</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>nP1i5US1</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
-        <v>59</v>
-      </c>
-      <c r="H14" t="n">
-        <v>591</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>M5BRZDsC</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>8f6APkLc</t>
-        </is>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0.4376578947368417</v>
-      </c>
-      <c r="R14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1.155502392344498</v>
-      </c>
-      <c r="T14" t="n">
-        <v>-0.6666666666666665</v>
-      </c>
-      <c r="U14" t="n">
-        <v>-0.4234449760765546</v>
-      </c>
-      <c r="V14" t="n">
-        <v>4.333333333333334</v>
-      </c>
-      <c r="W14" t="n">
-        <v>2.557416267942584</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>-0.861244019138756</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>-0.5239234449760766</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>12.34523809523809</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>18.63375377601513</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1062.549784092493</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1006.179961163952</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>-118.5</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>-24.90476190476191</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>-17.5</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>7.174603174603178</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>-12.5</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>-0.9736842105263221</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>-27.33333333333333</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>-18.96172248803828</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>-118</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>-212.3157894736842</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>-0.9999999999999998</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>-0.4397759103641459</v>
-      </c>
-      <c r="AR14" t="inlineStr"/>
-      <c r="AS14" t="n">
-        <v>0.3999999999999999</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>-0.3333333333333321</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>3.358851674641148</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>6.379668003565072</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>7.587228681191519</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>-0.0545555219641684</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>0.02860942326286475</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>-0.1961722488038277</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>-1.208922558922558</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>0.3016835016835273</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>-29987.54208754209</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>-75000</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>-83900000</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>5.333333333333332</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>1.638486312399358</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>-6.635521885521882</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>-0.9919348767174654</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>-4.535316414664237</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>-91</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>-0.6779351485873224</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BO14" t="n">
-        <v>-6.981649831649818</v>
-      </c>
-      <c r="BP14" t="n">
-        <v>-17943.45839345839</v>
-      </c>
-      <c r="BQ14" t="n">
-        <v>-18145903.1829684</v>
-      </c>
-      <c r="BR14" t="n">
-        <v>-30789309.76430977</v>
-      </c>
-      <c r="BS14" t="n">
-        <v>-107</v>
-      </c>
-      <c r="BT14" t="n">
-        <v>-5</v>
-      </c>
-      <c r="BU14" t="n">
-        <v>0.3860269360269335</v>
-      </c>
-      <c r="BV14" t="n">
-        <v>0.6666666666666572</v>
-      </c>
-      <c r="BW14" t="n">
-        <v>-6.902709810318498</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>dnhZQYKG</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45570.4375</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">welz t 
-  ger </t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">weserstadion
-  bremen </t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Ig1f1fy3</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>fiEQZ7C7</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
-        <v>59</v>
-      </c>
-      <c r="H15" t="n">
-        <v>591</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>KUx4Q7x1</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>0jdIgO6t</t>
-        </is>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>-2.19</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0.5068421052631575</v>
-      </c>
-      <c r="R15" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1.127819548872181</v>
-      </c>
-      <c r="T15" t="n">
-        <v>-7.666666666666666</v>
-      </c>
-      <c r="U15" t="n">
-        <v>-0.5388471177944854</v>
-      </c>
-      <c r="V15" t="n">
-        <v>-16.16666666666667</v>
-      </c>
-      <c r="W15" t="n">
-        <v>2.523809523809524</v>
-      </c>
-      <c r="X15" t="n">
-        <v>-4.166666666666667</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0.08521303258145374</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0.1428571428571428</v>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="AD15" t="n">
-        <v>1156.025135167185</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>895.5362312054083</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>-3.338888888888889</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>39.5</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>11.08333333333333</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>-3.552713678800501e-15</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>-2.471177944862159</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>-13.66666666666667</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>4.035087719298247</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>-161.5</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>49.89473684210532</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>-0.1190476190476191</v>
-      </c>
-      <c r="AR15" t="inlineStr"/>
-      <c r="AS15" t="inlineStr"/>
-      <c r="AT15" t="n">
-        <v>-6.666666666666666</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>2.393483709273182</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>100.7480956543457</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>-4.241067412120046</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>0.05174361953480134</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>-0.001156447674129764</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>-0.8333333333333333</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>-0.1954887218045113</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>-0.5105639730639733</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>-0.05715488215486175</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>-2564.267676767678</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>-55000</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>-19500000</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>3.833333333333332</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>-2.416210596759793</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>-1.8567760942761</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>3.355647848210822</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>-3.902178921172066</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>-276</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>-0.4086384439359267</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>-4</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>-1.486994949494942</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>-5080.549474256564</v>
-      </c>
-      <c r="BQ15" t="n">
-        <v>-3612687.046723089</v>
-      </c>
-      <c r="BR15" t="n">
-        <v>-4496767.676767678</v>
-      </c>
-      <c r="BS15" t="n">
-        <v>-306</v>
-      </c>
-      <c r="BT15" t="n">
-        <v>-4</v>
-      </c>
-      <c r="BU15" t="n">
-        <v>0.332996632996629</v>
-      </c>
-      <c r="BV15" t="n">
-        <v>3.166666666666657</v>
-      </c>
-      <c r="BW15" t="n">
-        <v>-0.029352448974862</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>UajsPCkT</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45569.64583333334</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">badstubner f 
-  ger </t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">wwk arena
-  augsburg </t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>fTVNku3I</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>88HSzjDr</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
-        <v>59</v>
-      </c>
-      <c r="H16" t="n">
-        <v>591</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>pfoInmcq</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>hpYJ6izc</t>
-        </is>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0.395</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0.6125789473684218</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1.118181818181818</v>
-      </c>
-      <c r="T16" t="n">
-        <v>-1.000000000000001</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0.8454545454545457</v>
-      </c>
-      <c r="V16" t="n">
-        <v>3</v>
-      </c>
-      <c r="W16" t="n">
-        <v>4.013636363636364</v>
-      </c>
-      <c r="X16" t="n">
-        <v>-0.3333333333333333</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0.2318181818181815</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0.8318181818181818</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>23.71633597883598</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>21.92870333583249</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>971.0885425629924</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>884.4179609480398</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>33.4812030075188</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>13</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>21.5187969924812</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>22.66666666666666</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>4.963636363636368</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>-5.333333333333343</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>-3.563636363636363</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>-186.5</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>-31.29999999999995</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>1.666666666666667</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>-0.2785714285714282</v>
-      </c>
-      <c r="AR16" t="inlineStr"/>
-      <c r="AS16" t="n">
-        <v>0.6666666666666667</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>1.666666666666667</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>1.822727272727274</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>26.2780502504032</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>-2.251820717809871</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>0.03854816960284435</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>0.0261264320588924</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>-0.004545454545454519</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>-0.375</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>0.3916666666666515</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>-2225</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>-13000</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>-26400000</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>2.100000000000001</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>-0.8436632621751805</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>-1.066666666666663</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>0.4866580112154395</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>-1.148797005511412</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>-76</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>-0.04256035822784399</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BO16" t="n">
-        <v>-1.841666666666669</v>
-      </c>
-      <c r="BP16" t="n">
-        <v>-1262.155595254764</v>
-      </c>
-      <c r="BQ16" t="n">
-        <v>-1317073.565985347</v>
-      </c>
-      <c r="BR16" t="n">
-        <v>-3110000</v>
-      </c>
-      <c r="BS16" t="n">
-        <v>-105</v>
-      </c>
-      <c r="BT16" t="n">
-        <v>-3</v>
-      </c>
-      <c r="BU16" t="n">
-        <v>-0.3416666666666686</v>
-      </c>
-      <c r="BV16" t="n">
-        <v>-2.233333333333348</v>
-      </c>
-      <c r="BW16" t="n">
-        <v>-0.9255606109489491</v>
+        <v>-1.208249158249159</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/data_preparation/df_constructed.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_constructed.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BW13"/>
+  <dimension ref="A1:BW19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,334 +505,334 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_expected_goals_(xg)</t>
+          <t>dif_mean_last_60_matches_expected_goals_(xg)</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_expected_goals_(xg)</t>
+          <t>dif_mean_last_240_matches_expected_goals_(xg)</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_expected_points</t>
+          <t>dif_mean_last_60_matches_expected_points</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_expected_points</t>
+          <t>dif_mean_last_240_matches_expected_points</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_shots_on_goal</t>
+          <t>dif_mean_last_60_matches_shots_on_goal</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_shots_on_goal</t>
+          <t>dif_mean_last_240_matches_shots_on_goal</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_goal_attempts</t>
+          <t>dif_mean_last_60_matches_goal_attempts</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_goal_attempts</t>
+          <t>dif_mean_last_240_matches_goal_attempts</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_goals</t>
+          <t>dif_mean_last_60_matches_goals</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_goals</t>
+          <t>dif_mean_last_240_matches_goals</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_points</t>
+          <t>dif_mean_last_60_matches_points</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_points</t>
+          <t>dif_mean_last_240_matches_points</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_goal_ratio</t>
+          <t>dif_mean_last_60_matches_goal_ratio</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_goal_ratio</t>
+          <t>dif_mean_last_240_matches_goal_ratio</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_PPS</t>
+          <t>dif_mean_last_60_matches_PPS</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_PPS</t>
+          <t>dif_mean_last_240_matches_PPS</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_attacks</t>
+          <t>dif_mean_last_60_matches_attacks</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_attacks</t>
+          <t>dif_mean_last_240_matches_attacks</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_dangerous_attacks</t>
+          <t>dif_mean_last_60_matches_dangerous_attacks</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_dangerous_attacks</t>
+          <t>dif_mean_last_240_matches_dangerous_attacks</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_dead_balls</t>
+          <t>dif_mean_last_60_matches_dead_balls</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_dead_balls</t>
+          <t>dif_mean_last_240_matches_dead_balls</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_ball_possession</t>
+          <t>dif_mean_last_60_matches_ball_possession</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_ball_possession</t>
+          <t>dif_mean_last_240_matches_ball_possession</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_total_passes</t>
+          <t>dif_mean_last_60_matches_total_passes</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_total_passes</t>
+          <t>dif_mean_last_240_matches_total_passes</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_yellow_cards</t>
+          <t>dif_mean_last_60_matches_yellow_cards</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_yellow_cards</t>
+          <t>dif_mean_last_240_matches_yellow_cards</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_red_cards</t>
+          <t>dif_mean_last_60_matches_red_cards</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_red_cards</t>
+          <t>dif_mean_last_240_matches_red_cards</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_defensive_actions</t>
+          <t>dif_mean_last_60_matches_defensive_actions</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_defensive_actions</t>
+          <t>dif_mean_last_240_matches_defensive_actions</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_PPDA</t>
+          <t>dif_mean_last_60_matches_PPDA</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_PPDA</t>
+          <t>dif_mean_last_240_matches_PPDA</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_KGP</t>
+          <t>dif_mean_last_60_matches_KGP</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_KGP</t>
+          <t>dif_mean_last_240_matches_KGP</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_clean_sheet</t>
+          <t>dif_mean_last_60_matches_clean_sheet</t>
         </is>
       </c>
       <c r="BA1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_clean_sheet</t>
+          <t>dif_mean_last_240_matches_clean_sheet</t>
         </is>
       </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_value_player_miss</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_start</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_value_player_sub</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
           <t>dif_sum_wage_player_miss</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>dif_sum_pot_player_miss</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_start</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_sub</t>
+        </is>
+      </c>
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_value_player_start</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_start</t>
-        </is>
-      </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="BJ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_value_player_miss</t>
-        </is>
-      </c>
-      <c r="BK1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="BL1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="BM1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="BN1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="BO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_sub</t>
-        </is>
-      </c>
-      <c r="BP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="BQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="BR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="BS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="BT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="BU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="BV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_sub</t>
-        </is>
-      </c>
-      <c r="BW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_start</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>rPiijklS</t>
+          <t>zyC4c6ee</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45585.52083333334</v>
+        <v>45592.64583333334</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">welz t 
+          <t xml:space="preserve">osmers h 
   ger </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">volkswagen arena
-  wolfsburg </t>
+          <t xml:space="preserve">voith arena
+  heidenheim </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>nwkTahLL</t>
+          <t>KWixEVWi</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ig1f1fy3</t>
+          <t>hQAtP9Sl</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -859,211 +859,211 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>8f6APkLc</t>
+          <t>4ljanukM</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>YZPE6Sx7</t>
+          <t>KUx4Q7x1</t>
         </is>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.82</v>
+        <v>1.92</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.3580000000000003</v>
+        <v>0.7764705882352942</v>
       </c>
       <c r="R2" t="n">
-        <v>-2</v>
+        <v>2.5</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1298701298701297</v>
+        <v>1.263157894736842</v>
       </c>
       <c r="T2" t="n">
-        <v>-7.5</v>
+        <v>4.4</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5021645021645025</v>
+        <v>2.388888888888888</v>
       </c>
       <c r="V2" t="n">
-        <v>-9.333333333333334</v>
+        <v>8.200000000000001</v>
       </c>
       <c r="W2" t="n">
-        <v>3.313852813852813</v>
+        <v>4.333333333333332</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.666666666666667</v>
+        <v>1.4</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.2251082251082253</v>
+        <v>0.6111111111111112</v>
       </c>
       <c r="Z2" t="n">
-        <v>-4.25</v>
+        <v>1.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0.01298701298701288</v>
+        <v>0.4736842105263159</v>
       </c>
       <c r="AB2" t="n">
-        <v>23.61307932263815</v>
+        <v>0.8059434030022263</v>
       </c>
       <c r="AC2" t="n">
-        <v>19.64923027900177</v>
+        <v>-2.321875076504083</v>
       </c>
       <c r="AD2" t="n">
-        <v>931.066582494326</v>
+        <v>181.4165864949856</v>
       </c>
       <c r="AE2" t="n">
-        <v>873.8192551621943</v>
+        <v>55.83106843603397</v>
       </c>
       <c r="AF2" t="n">
-        <v>17.66666666666666</v>
+        <v>-13.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>18.82619047619048</v>
+        <v>-24.66666666666667</v>
       </c>
       <c r="AH2" t="n">
-        <v>-4.5</v>
+        <v>-17</v>
       </c>
       <c r="AI2" t="n">
-        <v>13.53809523809525</v>
+        <v>-6.400000000000006</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.75</v>
+        <v>-7.666666666666664</v>
       </c>
       <c r="AK2" t="n">
-        <v>3.980519480519483</v>
+        <v>-2.631578947368418</v>
       </c>
       <c r="AL2" t="n">
-        <v>-18.33333333333333</v>
+        <v>-4</v>
       </c>
       <c r="AM2" t="n">
-        <v>-0.4675324675324788</v>
+        <v>-7.888888888888886</v>
       </c>
       <c r="AN2" t="n">
-        <v>-248.3333333333333</v>
+        <v>47.39999999999992</v>
       </c>
       <c r="AO2" t="n">
-        <v>-9.149999999999977</v>
+        <v>-86.00000000000006</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.333333333333333</v>
+        <v>-1.8</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.6839826839826837</v>
+        <v>-1.166666666666667</v>
       </c>
       <c r="AR2" t="n">
-        <v>-0.6666666666666667</v>
+        <v>-1</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.0857142857142858</v>
+        <v>0.09999999999999998</v>
       </c>
       <c r="AT2" t="n">
-        <v>5.166666666666671</v>
+        <v>2.333333333333332</v>
       </c>
       <c r="AU2" t="n">
-        <v>2.690476190476192</v>
+        <v>3.684210526315788</v>
       </c>
       <c r="AV2" t="n">
-        <v>20.66610466960601</v>
+        <v>-11.1872897384161</v>
       </c>
       <c r="AW2" t="n">
-        <v>-7.980761308738423</v>
+        <v>-13.11228520673414</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.03528453596444147</v>
+        <v>-0.127552353084268</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.007173238270608076</v>
+        <v>-0.01821903569119519</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.1904761904761905</v>
-      </c>
-      <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="inlineStr"/>
+        <v>0.1052631578947368</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>-0.7111111111111157</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>1.525780548680189</v>
+      </c>
       <c r="BD2" t="n">
-        <v>-1.446541507179148</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>0.106372732852936</v>
-      </c>
+        <v>-1.073159866540124</v>
+      </c>
+      <c r="BE2" t="inlineStr"/>
       <c r="BF2" t="n">
-        <v>4270538.119288119</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>12724.18831168831</v>
-      </c>
+        <v>-0.6269841269841272</v>
+      </c>
+      <c r="BG2" t="inlineStr"/>
       <c r="BH2" t="inlineStr"/>
       <c r="BI2" t="n">
-        <v>0.8622474747474485</v>
-      </c>
-      <c r="BJ2" t="inlineStr"/>
-      <c r="BK2" t="n">
-        <v>0.9278138528138697</v>
-      </c>
+        <v>-2.292063492063491</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>-3473661.002921382</v>
+      </c>
+      <c r="BK2" t="inlineStr"/>
       <c r="BL2" t="n">
-        <v>-2.272186147186151</v>
+        <v>-5.339618715525873</v>
       </c>
       <c r="BM2" t="inlineStr"/>
       <c r="BN2" t="n">
-        <v>3.104641654641654</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>13149.49101893028</v>
-      </c>
+        <v>-1.680500682347684</v>
+      </c>
+      <c r="BO2" t="inlineStr"/>
       <c r="BP2" t="inlineStr"/>
       <c r="BQ2" t="n">
-        <v>0.3637180629827685</v>
+        <v>1.173015873015856</v>
       </c>
       <c r="BR2" t="inlineStr"/>
-      <c r="BS2" t="inlineStr"/>
+      <c r="BS2" t="n">
+        <v>-7933.333333333336</v>
+      </c>
       <c r="BT2" t="n">
-        <v>1.692275103301171</v>
+        <v>-3.839682539682542</v>
       </c>
       <c r="BU2" t="n">
-        <v>2.604569662966767</v>
+        <v>-0.1814344349486554</v>
       </c>
       <c r="BV2" t="n">
-        <v>4389194.218808111</v>
+        <v>-4129.83649600191</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.3241762866762863</v>
+        <v>-4257777.777777778</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>nBwH6AY8</t>
+          <t>ABBmcc1C</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45585.4375</v>
+        <v>45592.5625</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">reichel t 
+          <t xml:space="preserve">brand b 
   ger </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">holstein stadion
-  kiel </t>
+          <t xml:space="preserve">stadion an der alten forsterei
+  berlin </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>63WsD2ei</t>
+          <t>pzHW4oaE</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>pzHW4oaE</t>
+          <t>8vndvXTk</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1090,209 +1090,209 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>hAcTWKKN</t>
+          <t>hpYJ6izc</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>IkCftsQm</t>
+          <t>K6A2elS9</t>
         </is>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.726666666666666</v>
+        <v>-0.5920000000000005</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.6073182957393484</v>
+        <v>-0.4252941176470586</v>
       </c>
       <c r="R3" t="n">
-        <v>-2</v>
+        <v>-0.5</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8074534161490682</v>
+        <v>-0.4736842105263159</v>
       </c>
       <c r="T3" t="n">
-        <v>-6.083333333333334</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>1.614906832298136</v>
+        <v>-0.666666666666667</v>
       </c>
       <c r="V3" t="n">
-        <v>-9.916666666666668</v>
+        <v>3.999999999999998</v>
       </c>
       <c r="W3" t="n">
-        <v>3.596273291925467</v>
+        <v>-1.722222222222221</v>
       </c>
       <c r="X3" t="n">
-        <v>-3</v>
+        <v>-0.9999999999999999</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.4658385093167703</v>
+        <v>-0.6111111111111109</v>
       </c>
       <c r="Z3" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.031055900621118</v>
+        <v>-0.7894736842105263</v>
       </c>
       <c r="AB3" t="n">
-        <v>24.08090277777778</v>
+        <v>-4.492732708468003</v>
       </c>
       <c r="AC3" t="n">
-        <v>21.32433484444258</v>
+        <v>-0.7592517163015096</v>
       </c>
       <c r="AD3" t="n">
-        <v>849.718502141244</v>
+        <v>-44.39218791193198</v>
       </c>
       <c r="AE3" t="n">
-        <v>754.9657356538489</v>
+        <v>59.47227649177609</v>
       </c>
       <c r="AF3" t="n">
-        <v>-59.5</v>
+        <v>-49</v>
       </c>
       <c r="AG3" t="n">
-        <v>27.55454545454545</v>
+        <v>-35.40000000000001</v>
       </c>
       <c r="AH3" t="n">
-        <v>-58.66666666666667</v>
+        <v>11</v>
       </c>
       <c r="AI3" t="n">
-        <v>4.695454545454545</v>
+        <v>-8.866666666666667</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-13.33333333333333</v>
+        <v>6.666666666666664</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.7474120082815787</v>
+        <v>-4.210526315789476</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.5</v>
+        <v>-4.800000000000011</v>
       </c>
       <c r="AM3" t="n">
-        <v>19.26708074534162</v>
+        <v>-10.22222222222221</v>
       </c>
       <c r="AN3" t="n">
-        <v>100.0000000000001</v>
+        <v>-55.19999999999999</v>
       </c>
       <c r="AO3" t="n">
-        <v>234.25</v>
+        <v>-141.0588235294118</v>
       </c>
       <c r="AP3" t="n">
-        <v>-2</v>
+        <v>0.1999999999999997</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.9192546583850933</v>
+        <v>-0.4117647058823528</v>
       </c>
       <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="n">
-        <v>-0.8</v>
+        <v>2</v>
       </c>
       <c r="AT3" t="n">
-        <v>-0.4166666666666643</v>
+        <v>-0.3333333333333357</v>
       </c>
       <c r="AU3" t="n">
-        <v>-0.1304347826086953</v>
+        <v>2.684210526315786</v>
       </c>
       <c r="AV3" t="n">
-        <v>-4.352445963999124</v>
+        <v>1.748225169908022</v>
       </c>
       <c r="AW3" t="n">
-        <v>-16.66592475434344</v>
+        <v>-9.124113531706818</v>
       </c>
       <c r="AX3" t="n">
-        <v>-0.004982719893295046</v>
+        <v>0.03305785279007403</v>
       </c>
       <c r="AY3" t="n">
-        <v>-0.008795038621222592</v>
+        <v>-0.0009351352108242575</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.4472049689440994</v>
-      </c>
-      <c r="BB3" t="inlineStr"/>
-      <c r="BC3" t="inlineStr"/>
+        <v>-0.1052631578947368</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>2.456349206349209</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>3.765622955374511</v>
+      </c>
       <c r="BD3" t="n">
-        <v>2.086570982321206</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>-0.7698775925320547</v>
-      </c>
+        <v>-1.867936097537267</v>
+      </c>
+      <c r="BE3" t="inlineStr"/>
       <c r="BF3" t="n">
-        <v>-4655847.763347763</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>-11036.97691197692</v>
-      </c>
+        <v>-0.2581649831649833</v>
+      </c>
+      <c r="BG3" t="inlineStr"/>
       <c r="BH3" t="inlineStr"/>
       <c r="BI3" t="n">
-        <v>-4.945165945165954</v>
-      </c>
-      <c r="BJ3" t="inlineStr"/>
-      <c r="BK3" t="n">
-        <v>-0.7374458874458867</v>
-      </c>
+        <v>-1.829304954304945</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>-4668033.640236486</v>
+      </c>
+      <c r="BK3" t="inlineStr"/>
       <c r="BL3" t="n">
-        <v>-0.315981240981241</v>
+        <v>-4.969929552848782</v>
       </c>
       <c r="BM3" t="inlineStr"/>
       <c r="BN3" t="n">
-        <v>-5.185209235209228</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>-9312.095456031384</v>
-      </c>
+        <v>0.3235654070240486</v>
+      </c>
+      <c r="BO3" t="inlineStr"/>
       <c r="BP3" t="inlineStr"/>
       <c r="BQ3" t="n">
-        <v>-0.1591245193729667</v>
+        <v>1.032311207311153</v>
       </c>
       <c r="BR3" t="inlineStr"/>
-      <c r="BS3" t="inlineStr"/>
+      <c r="BS3" t="n">
+        <v>-6800.048100048098</v>
+      </c>
       <c r="BT3" t="n">
-        <v>-3.383567355241112</v>
+        <v>-4.159788359788351</v>
       </c>
       <c r="BU3" t="n">
-        <v>-4.851261175713603</v>
+        <v>-0.2327903326922616</v>
       </c>
       <c r="BV3" t="n">
-        <v>-2342168.257081627</v>
+        <v>-745.0663408002438</v>
       </c>
       <c r="BW3" t="n">
-        <v>-0.4131313131313132</v>
+        <v>-8518617.724867728</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>2mcmYkSq</t>
+          <t>WQadeyWO</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45584.5625</v>
+        <v>45592.47916666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">jablonski s 
+          <t xml:space="preserve">brand b 
   ger </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">allianz arena
-  munich </t>
+          <t xml:space="preserve">vonovia ruhrstadion
+  bochum </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>nVp0wiqd</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>nJQmYp1B</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1319,209 +1319,211 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>8f6APkLc</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>K6A2elS9</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>GzfvcwRj</t>
         </is>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0.8475000000000001</v>
+        <v>-3.7</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.734681818181818</v>
+        <v>-2.259504643962848</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5</v>
+        <v>-4.5</v>
       </c>
       <c r="S4" t="n">
-        <v>1.55</v>
+        <v>-2.421052631578947</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.6</v>
+        <v>-7.8</v>
       </c>
       <c r="U4" t="n">
-        <v>3.408333333333333</v>
+        <v>-4.116666666666667</v>
       </c>
       <c r="V4" t="n">
-        <v>7</v>
+        <v>-20</v>
       </c>
       <c r="W4" t="n">
-        <v>8.766666666666669</v>
+        <v>-7.5</v>
       </c>
       <c r="X4" t="n">
-        <v>0.2</v>
+        <v>-3.8</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.541666666666667</v>
+        <v>-2.711111111111111</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.5</v>
+        <v>-3.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>13.29858585858586</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>17.67838404606516</v>
+        <v>-2.676691729323308</v>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
       <c r="AD4" t="n">
-        <v>932.8115439748174</v>
+        <v>479.0040713277384</v>
       </c>
       <c r="AE4" t="n">
-        <v>960.9502943890363</v>
+        <v>257.9394826779711</v>
       </c>
       <c r="AF4" t="n">
-        <v>3</v>
+        <v>-27</v>
       </c>
       <c r="AG4" t="n">
-        <v>36.3821510297483</v>
+        <v>-5.35294117647058</v>
       </c>
       <c r="AH4" t="n">
-        <v>8</v>
+        <v>-41</v>
       </c>
       <c r="AI4" t="n">
-        <v>30.98398169336385</v>
+        <v>-16.3921568627451</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-0.2999999999999972</v>
+        <v>-10.16666666666667</v>
       </c>
       <c r="AK4" t="n">
-        <v>3.599999999999998</v>
+        <v>-5.150375939849631</v>
       </c>
       <c r="AL4" t="n">
-        <v>3.799999999999997</v>
+        <v>-44.00000000000001</v>
       </c>
       <c r="AM4" t="n">
-        <v>4.099999999999994</v>
+        <v>-25.45555555555556</v>
       </c>
       <c r="AN4" t="n">
-        <v>96.25</v>
+        <v>-551.5999999999999</v>
       </c>
       <c r="AO4" t="n">
-        <v>35.37857142857143</v>
+        <v>-308.7708978328173</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.2999999999999998</v>
+        <v>0.2000000000000002</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-0.6521739130434779</v>
+        <v>1.35</v>
       </c>
       <c r="AR4" t="inlineStr"/>
-      <c r="AS4" t="n">
-        <v>-1</v>
-      </c>
+      <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
-        <v>-2.900000000000002</v>
+        <v>1.333333333333332</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.3249999999999993</v>
+        <v>1.3859649122807</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.573983898066601</v>
+        <v>62.71676996952495</v>
       </c>
       <c r="AW4" t="n">
-        <v>-5.284891306475792</v>
+        <v>32.63870987429621</v>
       </c>
       <c r="AX4" t="n">
-        <v>-0.02107726866719523</v>
+        <v>0.03681870812779452</v>
       </c>
       <c r="AY4" t="n">
-        <v>-0.000970203983232866</v>
+        <v>0.04269159330149178</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.3</v>
+        <v>-0.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.1333333333333334</v>
-      </c>
-      <c r="BB4" t="inlineStr"/>
-      <c r="BC4" t="inlineStr"/>
+        <v>-0.4962406015037594</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>1.413492063492065</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>-1.269674846996836</v>
+      </c>
       <c r="BD4" t="n">
-        <v>-1.088242185088177</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>2.664955001139212</v>
-      </c>
+        <v>2.26281602384546</v>
+      </c>
+      <c r="BE4" t="inlineStr"/>
       <c r="BF4" t="n">
-        <v>33596553.03030303</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>49385.06493506493</v>
-      </c>
+        <v>-2.103174603174603</v>
+      </c>
+      <c r="BG4" t="inlineStr"/>
       <c r="BH4" t="inlineStr"/>
       <c r="BI4" t="n">
-        <v>6.618831168831179</v>
-      </c>
-      <c r="BJ4" t="inlineStr"/>
-      <c r="BK4" t="n">
-        <v>-2.013636363636351</v>
-      </c>
+        <v>-11.15925925925927</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>-35608706.77471393</v>
+      </c>
+      <c r="BK4" t="inlineStr"/>
       <c r="BL4" t="n">
-        <v>1.826190476190476</v>
+        <v>-9.58879825884469</v>
       </c>
       <c r="BM4" t="inlineStr"/>
       <c r="BN4" t="n">
-        <v>6.258658008657989</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>51135.93170532025</v>
-      </c>
+        <v>-13.03375614753324</v>
+      </c>
+      <c r="BO4" t="inlineStr"/>
       <c r="BP4" t="inlineStr"/>
       <c r="BQ4" t="n">
-        <v>1.201072004477577</v>
+        <v>1.554034391534373</v>
       </c>
       <c r="BR4" t="inlineStr"/>
-      <c r="BS4" t="inlineStr"/>
+      <c r="BS4" t="n">
+        <v>-60115.34391534392</v>
+      </c>
       <c r="BT4" t="n">
-        <v>5.703150786548605</v>
+        <v>-12.04616402116402</v>
       </c>
       <c r="BU4" t="n">
-        <v>8.297274268559107</v>
+        <v>-1.64404941463765</v>
       </c>
       <c r="BV4" t="n">
-        <v>27952495.23654951</v>
+        <v>-60084.00234812773</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.623593073593074</v>
+        <v>-44083376.32275132</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Eq0zfXl3</t>
+          <t>MiACepQ7</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45584.4375</v>
+        <v>45591.5625</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">burda m 
+          <t xml:space="preserve">hartmann r 
   ger </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">prezero arena
-  sinsheim </t>
+          <t xml:space="preserve">weserstadion
+  bremen </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>hQAtP9Sl</t>
+          <t>Ig1f1fy3</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>8Y2m6ADe</t>
+          <t>4jcj2zMd</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1548,211 +1550,215 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>KUx4Q7x1</t>
+          <t>4fuCGs9P</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>f3ddUIXs</t>
+          <t>A15eUM4C</t>
         </is>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7066666666666668</v>
+        <v>-1.726</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.416</v>
+        <v>-1.964264705882353</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5</v>
+        <v>-1.357142857142857</v>
       </c>
       <c r="S5" t="n">
-        <v>1.284782608695652</v>
+        <v>-1.930622009569378</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.25</v>
+        <v>-4.5</v>
       </c>
       <c r="U5" t="n">
-        <v>2.006521739130435</v>
+        <v>-4.666666666666667</v>
       </c>
       <c r="V5" t="n">
-        <v>4.749999999999998</v>
+        <v>-12.26666666666667</v>
       </c>
       <c r="W5" t="n">
-        <v>4.928260869565216</v>
+        <v>-11.91269841269841</v>
       </c>
       <c r="X5" t="n">
-        <v>0.25</v>
+        <v>-1.466666666666667</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.197826086956522</v>
+        <v>-1.849206349206349</v>
       </c>
       <c r="Z5" t="n">
-        <v>2</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.545652173913044</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>24.23353079668869</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>22.2240920177255</v>
+        <v>-2.203349282296651</v>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
       <c r="AD5" t="n">
-        <v>814.7492937217449</v>
+        <v>183.387776649553</v>
       </c>
       <c r="AE5" t="n">
-        <v>790.4586707757715</v>
+        <v>127.6065256442947</v>
       </c>
       <c r="AF5" t="n">
-        <v>-55.33333333333333</v>
+        <v>-70.33333333333334</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.866028708133967</v>
+        <v>-64.12222222222222</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.5</v>
+        <v>-47.16666666666666</v>
       </c>
       <c r="AI5" t="n">
-        <v>15.50478468899522</v>
+        <v>-51.91111111111111</v>
       </c>
       <c r="AJ5" t="n">
-        <v>9.166666666666664</v>
+        <v>-12.90476190476191</v>
       </c>
       <c r="AK5" t="n">
-        <v>5.945652173913039</v>
+        <v>-9.52392344497607</v>
       </c>
       <c r="AL5" t="n">
-        <v>9.666666666666671</v>
+        <v>-17.93333333333332</v>
       </c>
       <c r="AM5" t="n">
-        <v>8.139130434782615</v>
+        <v>-18.98412698412699</v>
       </c>
       <c r="AN5" t="n">
-        <v>47</v>
+        <v>-275.8000000000001</v>
       </c>
       <c r="AO5" t="n">
-        <v>90.76428571428573</v>
+        <v>-274.2908496732027</v>
       </c>
       <c r="AP5" t="n">
-        <v>-2.583333333333333</v>
+        <v>-2.533333333333334</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.5195652173913046</v>
+        <v>-0.7588235294117651</v>
       </c>
       <c r="AR5" t="n">
-        <v>1</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.8333333333333334</v>
+        <v>-0.0714285714285714</v>
       </c>
       <c r="AT5" t="n">
-        <v>-7.25</v>
+        <v>1.119047619047617</v>
       </c>
       <c r="AU5" t="n">
-        <v>-4.406521739130438</v>
+        <v>0.4449760765550241</v>
       </c>
       <c r="AV5" t="n">
-        <v>5.367079885119217</v>
+        <v>45.51971758796024</v>
       </c>
       <c r="AW5" t="n">
-        <v>6.689962906345777</v>
+        <v>43.92033965009961</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.001841130721083641</v>
+        <v>-0.05427421204837672</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.008605130413885283</v>
+        <v>-0.01933830273660526</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.5</v>
+        <v>-0.4761904761904762</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.1608695652173913</v>
-      </c>
-      <c r="BB5" t="inlineStr"/>
-      <c r="BC5" t="inlineStr"/>
+        <v>-0.5215311004784688</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0.5737734487734514</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0.036196368152698</v>
+      </c>
       <c r="BD5" t="n">
-        <v>0.6691832648488969</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>-1.051913846960282</v>
-      </c>
+        <v>5.558781945619302</v>
+      </c>
+      <c r="BE5" t="inlineStr"/>
       <c r="BF5" t="n">
-        <v>5194976.851851852</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>13209.25925925926</v>
-      </c>
+        <v>-1.96948051948052</v>
+      </c>
+      <c r="BG5" t="inlineStr"/>
       <c r="BH5" t="inlineStr"/>
       <c r="BI5" t="n">
-        <v>3.187037037037044</v>
-      </c>
-      <c r="BJ5" t="inlineStr"/>
-      <c r="BK5" t="n">
-        <v>0.7874999999999943</v>
-      </c>
+        <v>-9.332287157287141</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>-35965204.17881285</v>
+      </c>
+      <c r="BK5" t="inlineStr"/>
       <c r="BL5" t="n">
-        <v>-0.6518518518518484</v>
+        <v>-8.074303983433765</v>
       </c>
       <c r="BM5" t="inlineStr"/>
       <c r="BN5" t="n">
-        <v>4.441666666666663</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>9460.688044898567</v>
-      </c>
+        <v>-10.36053935546897</v>
+      </c>
+      <c r="BO5" t="inlineStr"/>
       <c r="BP5" t="inlineStr"/>
       <c r="BQ5" t="n">
-        <v>0.2392787524366471</v>
+        <v>-0.5766233766233881</v>
       </c>
       <c r="BR5" t="inlineStr"/>
-      <c r="BS5" t="inlineStr"/>
+      <c r="BS5" t="n">
+        <v>-75975.97402597402</v>
+      </c>
       <c r="BT5" t="n">
-        <v>3.234419507794115</v>
+        <v>-9.125541125541147</v>
       </c>
       <c r="BU5" t="n">
-        <v>2.931299843374148</v>
+        <v>-1.302458351761757</v>
       </c>
       <c r="BV5" t="n">
-        <v>4087964.059217929</v>
+        <v>-62985.35329047366</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.6555555555555557</v>
+        <v>-44258798.7012987</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>r3GGwC4M</t>
+          <t>rwXP4l3L</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45584.4375</v>
+        <v>45591.4375</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">stieler t 
+          <t xml:space="preserve">hartmann r 
   ger </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">bayarena
-  leverkusen </t>
+          <t xml:space="preserve">mhparena
+  stuttgart </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>4jcj2zMd</t>
+          <t>nJQmYp1B</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>8vndvXTk</t>
+          <t>63WsD2ei</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1779,209 +1785,209 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>hAcTWKKN</t>
+          <t>GzfvcwRj</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>UgdQz0fK</t>
+          <t>A15eUM4C</t>
         </is>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.1449999999999998</v>
+        <v>2.878</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.139772727272727</v>
+        <v>1.054869281045752</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.214285714285714</v>
       </c>
       <c r="S6" t="n">
-        <v>2.625</v>
+        <v>1.057894736842105</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5</v>
+        <v>7.600000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>5.375</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="V6" t="n">
-        <v>10.75</v>
+        <v>18.1</v>
       </c>
       <c r="W6" t="n">
-        <v>15.41666666666667</v>
+        <v>9.070175438596491</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.75</v>
+        <v>3.633333333333334</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.666666666666667</v>
+        <v>0.9853801169590644</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.75</v>
+        <v>2.785714285714286</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.25</v>
+        <v>0.5684210526315789</v>
       </c>
       <c r="AB6" t="n">
-        <v>16.17481909430439</v>
+        <v>-7.239537037037037</v>
       </c>
       <c r="AC6" t="n">
-        <v>12.89947811977611</v>
+        <v>-3.276322889261486</v>
       </c>
       <c r="AD6" t="n">
-        <v>694.5660202504989</v>
+        <v>-188.9897361068924</v>
       </c>
       <c r="AE6" t="n">
-        <v>814.1965799913603</v>
+        <v>-122.3848955345136</v>
       </c>
       <c r="AF6" t="n">
-        <v>14.33333333333334</v>
+        <v>96.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>71.14624505928855</v>
+        <v>32.39583333333333</v>
       </c>
       <c r="AH6" t="n">
-        <v>43.00000000000001</v>
+        <v>61.33333333333334</v>
       </c>
       <c r="AI6" t="n">
-        <v>62.23913043478261</v>
+        <v>20.35833333333333</v>
       </c>
       <c r="AJ6" t="n">
-        <v>18.75</v>
+        <v>12.04761904761904</v>
       </c>
       <c r="AK6" t="n">
-        <v>12.45833333333333</v>
+        <v>5.860526315789471</v>
       </c>
       <c r="AL6" t="n">
-        <v>25</v>
+        <v>33.2</v>
       </c>
       <c r="AM6" t="n">
-        <v>20.66666666666667</v>
+        <v>19.41520467836257</v>
       </c>
       <c r="AN6" t="n">
-        <v>449.5833333333333</v>
+        <v>405.0000000000001</v>
       </c>
       <c r="AO6" t="n">
-        <v>360.5666666666667</v>
+        <v>261.9738562091503</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.5</v>
+        <v>0.6333333333333331</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-1.079710144927536</v>
+        <v>-0.125730994152047</v>
       </c>
       <c r="AR6" t="inlineStr"/>
       <c r="AS6" t="n">
-        <v>-1.75</v>
+        <v>-0.8333333333333333</v>
       </c>
       <c r="AT6" t="n">
-        <v>-2.75</v>
+        <v>-1.214285714285715</v>
       </c>
       <c r="AU6" t="n">
-        <v>-2.749999999999998</v>
+        <v>-2.055263157894736</v>
       </c>
       <c r="AV6" t="n">
-        <v>-69.52248416602228</v>
+        <v>-30.02026009547362</v>
       </c>
       <c r="AW6" t="n">
-        <v>-28.67192593758189</v>
+        <v>-9.944133298712437</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.07006874156183304</v>
+        <v>-0.002783979467607195</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.03113164034668271</v>
+        <v>0.01730762691596557</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.25</v>
+        <v>0.3095238095238095</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.4166666666666666</v>
-      </c>
-      <c r="BB6" t="inlineStr"/>
-      <c r="BC6" t="inlineStr"/>
+        <v>0.03421052631578947</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>-1.780645743145744</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>-1.372187889613933</v>
+      </c>
       <c r="BD6" t="n">
-        <v>-4.307227181143645</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>2.190585979208272</v>
-      </c>
+        <v>-0.2101177179491174</v>
+      </c>
+      <c r="BE6" t="inlineStr"/>
       <c r="BF6" t="n">
-        <v>35045158.73015872</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>64430.95238095237</v>
-      </c>
+        <v>0.4522727272727276</v>
+      </c>
+      <c r="BG6" t="inlineStr"/>
       <c r="BH6" t="inlineStr"/>
       <c r="BI6" t="n">
-        <v>6.785317460317458</v>
-      </c>
-      <c r="BJ6" t="inlineStr"/>
-      <c r="BK6" t="n">
-        <v>-0.7150793650793901</v>
-      </c>
+        <v>6.224891774891788</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>8521587.598109595</v>
+      </c>
+      <c r="BK6" t="inlineStr"/>
       <c r="BL6" t="n">
-        <v>1.662301587301588</v>
+        <v>5.660592976182215</v>
       </c>
       <c r="BM6" t="inlineStr"/>
       <c r="BN6" t="n">
-        <v>4.207936507936523</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>56876.13641948007</v>
-      </c>
+        <v>5.319130388789588</v>
+      </c>
+      <c r="BO6" t="inlineStr"/>
       <c r="BP6" t="inlineStr"/>
       <c r="BQ6" t="n">
-        <v>0.9404624529237529</v>
+        <v>0.08535353535347667</v>
       </c>
       <c r="BR6" t="inlineStr"/>
-      <c r="BS6" t="inlineStr"/>
+      <c r="BS6" t="n">
+        <v>10737.82467532467</v>
+      </c>
       <c r="BT6" t="n">
-        <v>3.56187460630187</v>
+        <v>7.13140331890331</v>
       </c>
       <c r="BU6" t="n">
-        <v>8.166407663543879</v>
+        <v>0.4824062998405105</v>
       </c>
       <c r="BV6" t="n">
-        <v>30588600.80431694</v>
+        <v>8477.515033820197</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.36984126984127</v>
+        <v>11752938.76262626</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>fHjVr7t2</t>
+          <t>ELNeaSQr</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45584.4375</v>
+        <v>45591.4375</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">exner f 
+          <t xml:space="preserve">welz t 
   ger </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">borussia park
-  monchengladbach </t>
+          <t xml:space="preserve">red bull arena
+  leipzig </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>88HSzjDr</t>
+          <t>KbS1suSm</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>KWixEVWi</t>
+          <t>fiEQZ7C7</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2008,211 +2014,209 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2VSFgl3c</t>
+          <t>4ljanukM</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>4ljanukM</t>
+          <t>YZPE6Sx7</t>
         </is>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.7533333333333332</v>
+        <v>-0.6840000000000002</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.8105000000000004</v>
+        <v>0.6176470588235299</v>
       </c>
       <c r="R7" t="n">
-        <v>-1</v>
+        <v>-0.4999999999999999</v>
       </c>
       <c r="S7" t="n">
-        <v>0.9189723320158102</v>
+        <v>0.631578947368421</v>
       </c>
       <c r="T7" t="n">
-        <v>-3.166666666666666</v>
+        <v>-1.8</v>
       </c>
       <c r="U7" t="n">
-        <v>0.9387351778656123</v>
+        <v>1.666666666666666</v>
       </c>
       <c r="V7" t="n">
-        <v>-6</v>
+        <v>-5.799999999999999</v>
       </c>
       <c r="W7" t="n">
-        <v>3.962450592885377</v>
+        <v>3.611111111111111</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.166666666666667</v>
+        <v>1.2</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.03952569169960474</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="Z7" t="n">
-        <v>-2.5</v>
+        <v>1</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.2608695652173911</v>
+        <v>1.578947368421052</v>
       </c>
       <c r="AB7" t="n">
-        <v>21.47880175380175</v>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>0.4807828282828281</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-2.871852791350144</v>
       </c>
       <c r="AD7" t="n">
-        <v>823.7180997505649</v>
+        <v>-38.22061122552046</v>
       </c>
       <c r="AE7" t="n">
-        <v>826.9128599267867</v>
+        <v>-145.5976548141379</v>
       </c>
       <c r="AF7" t="n">
-        <v>-18.5</v>
+        <v>48.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>-4.861471861471856</v>
+        <v>26.80000000000001</v>
       </c>
       <c r="AH7" t="n">
-        <v>-17.33333333333334</v>
+        <v>-15.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>4.833333333333336</v>
+        <v>17.93333333333334</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-9.25</v>
+        <v>-3.333333333333339</v>
       </c>
       <c r="AK7" t="n">
-        <v>-0.5968379446640313</v>
+        <v>5.210526315789465</v>
       </c>
       <c r="AL7" t="n">
-        <v>6.5</v>
+        <v>6.800000000000011</v>
       </c>
       <c r="AM7" t="n">
-        <v>10.53754940711462</v>
+        <v>14.11111111111111</v>
       </c>
       <c r="AN7" t="n">
-        <v>141</v>
+        <v>161.6</v>
       </c>
       <c r="AO7" t="n">
-        <v>170.95</v>
+        <v>197.7647058823529</v>
       </c>
       <c r="AP7" t="n">
-        <v>1</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-0.1645021645021647</v>
+        <v>-0.715686274509804</v>
       </c>
       <c r="AR7" t="inlineStr"/>
       <c r="AS7" t="n">
-        <v>-1.5</v>
+        <v>-0.6666666666666667</v>
       </c>
       <c r="AT7" t="n">
-        <v>-0.6666666666666714</v>
+        <v>1.833333333333332</v>
       </c>
       <c r="AU7" t="n">
-        <v>-4.395256916996045</v>
+        <v>-0.1578947368421044</v>
       </c>
       <c r="AV7" t="n">
-        <v>-10.46584301124083</v>
+        <v>-17.56203644193162</v>
       </c>
       <c r="AW7" t="n">
-        <v>12.43039202983235</v>
+        <v>-16.66572767330928</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.04751929126929127</v>
+        <v>-0.05502310427071028</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.001574089699500146</v>
+        <v>-0.0154848222235259</v>
       </c>
       <c r="AZ7" t="n">
-        <v>-0.4166666666666667</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="BA7" t="n">
-        <v>-0.1304347826086956</v>
-      </c>
-      <c r="BB7" t="inlineStr"/>
-      <c r="BC7" t="inlineStr"/>
+        <v>0.1052631578947368</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>-0.9236652236652212</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>-1.482267460760042</v>
+      </c>
       <c r="BD7" t="n">
-        <v>-1.707927816435472</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>-0.04267150796244934</v>
-      </c>
+        <v>1.299669782967612</v>
+      </c>
+      <c r="BE7" t="inlineStr"/>
       <c r="BF7" t="n">
-        <v>5131190.476190476</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>2314.285714285714</v>
-      </c>
+        <v>0.6209595959595957</v>
+      </c>
+      <c r="BG7" t="inlineStr"/>
       <c r="BH7" t="inlineStr"/>
       <c r="BI7" t="n">
-        <v>3.019047619047626</v>
-      </c>
-      <c r="BJ7" t="inlineStr"/>
-      <c r="BK7" t="n">
-        <v>-2.230952380952374</v>
-      </c>
+        <v>4.397438672438668</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>17961559.22970048</v>
+      </c>
+      <c r="BK7" t="inlineStr"/>
       <c r="BL7" t="n">
-        <v>-0.7023809523809454</v>
+        <v>5.514369023387729</v>
       </c>
       <c r="BM7" t="inlineStr"/>
       <c r="BN7" t="n">
-        <v>3.697619047619071</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>2415.688289045596</v>
-      </c>
+        <v>4.338213140120487</v>
+      </c>
+      <c r="BO7" t="inlineStr"/>
       <c r="BP7" t="inlineStr"/>
       <c r="BQ7" t="n">
-        <v>0.1589104749451267</v>
+        <v>-0.3420634920634598</v>
       </c>
       <c r="BR7" t="inlineStr"/>
-      <c r="BS7" t="inlineStr"/>
+      <c r="BS7" t="n">
+        <v>30769.01154401154</v>
+      </c>
       <c r="BT7" t="n">
-        <v>4.792678123881132</v>
+        <v>5.396933621933655</v>
       </c>
       <c r="BU7" t="n">
-        <v>3.890520166876826</v>
+        <v>0.5729332121864767</v>
       </c>
       <c r="BV7" t="n">
-        <v>3852930.793598905</v>
+        <v>28413.4005773333</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.4690476190476192</v>
+        <v>20203881.67388167</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>M93rhBJF</t>
+          <t>x0haJmIE</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45584.4375</v>
+        <v>45591.4375</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">badstubner f 
+          <t xml:space="preserve">reichel t 
   ger </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">europa park stadion
-  freiburg </t>
+          <t xml:space="preserve">wwk arena
+  augsburg </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>fiEQZ7C7</t>
+          <t>fTVNku3I</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>fTVNku3I</t>
+          <t>nP1i5US1</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2239,209 +2243,211 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>4fuCGs9P</t>
+          <t>2VSFgl3c</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>M5BRZDsC</t>
+          <t>IkCftsQm</t>
         </is>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>3.176666666666666</v>
+        <v>0.1640000000000001</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.418026315789474</v>
+        <v>-0.5070588235294113</v>
       </c>
       <c r="R8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.857142857142857</v>
+        <v>-0.4736842105263159</v>
       </c>
       <c r="T8" t="n">
-        <v>5.333333333333334</v>
+        <v>-0.4000000000000004</v>
       </c>
       <c r="U8" t="n">
-        <v>2.714285714285714</v>
+        <v>-2.611111111111112</v>
       </c>
       <c r="V8" t="n">
-        <v>5.333333333333334</v>
+        <v>4.199999999999999</v>
       </c>
       <c r="W8" t="n">
-        <v>4.19047619047619</v>
+        <v>0.05555555555555536</v>
       </c>
       <c r="X8" t="n">
-        <v>1.666666666666667</v>
+        <v>-1</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.6190476190476191</v>
+        <v>-1</v>
       </c>
       <c r="Z8" t="n">
-        <v>2</v>
+        <v>-0.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.142857142857143</v>
+        <v>-1.263157894736842</v>
       </c>
       <c r="AB8" t="n">
-        <v>18.19856831621538</v>
+        <v>0.8158257102374749</v>
       </c>
       <c r="AC8" t="n">
-        <v>20.34932274411848</v>
+        <v>0.3590433930152712</v>
       </c>
       <c r="AD8" t="n">
-        <v>885.9139431699239</v>
+        <v>280.8218851525485</v>
       </c>
       <c r="AE8" t="n">
-        <v>832.898978363493</v>
+        <v>153.6030541643073</v>
       </c>
       <c r="AF8" t="n">
-        <v>-69</v>
+        <v>-11</v>
       </c>
       <c r="AG8" t="n">
-        <v>22.7</v>
+        <v>-18.46666666666667</v>
       </c>
       <c r="AH8" t="n">
-        <v>-54</v>
+        <v>32</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.6000000000000014</v>
+        <v>5.466666666666669</v>
       </c>
       <c r="AJ8" t="n">
-        <v>8.333333333333336</v>
+        <v>-0.1666666666666679</v>
       </c>
       <c r="AK8" t="n">
-        <v>6.666666666666664</v>
+        <v>-3.89473684210526</v>
       </c>
       <c r="AL8" t="n">
-        <v>-7.333333333333343</v>
+        <v>-14.8</v>
       </c>
       <c r="AM8" t="n">
-        <v>4.19047619047619</v>
+        <v>-19.55555555555556</v>
       </c>
       <c r="AN8" t="n">
-        <v>9.833333333333314</v>
+        <v>-176</v>
       </c>
       <c r="AO8" t="n">
-        <v>93.87368421052633</v>
+        <v>-255.9411764705881</v>
       </c>
       <c r="AP8" t="n">
-        <v>-2</v>
+        <v>-1.6</v>
       </c>
       <c r="AQ8" t="n">
-        <v>-1.05</v>
-      </c>
-      <c r="AR8" t="inlineStr"/>
+        <v>-0.3496732026143787</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>-1</v>
+      </c>
       <c r="AS8" t="n">
-        <v>0.6000000000000001</v>
+        <v>-1.5</v>
       </c>
       <c r="AT8" t="n">
-        <v>-1.333333333333329</v>
+        <v>0.6666666666666679</v>
       </c>
       <c r="AU8" t="n">
-        <v>-3.095238095238095</v>
+        <v>4.000000000000002</v>
       </c>
       <c r="AV8" t="n">
-        <v>23.31936090605409</v>
+        <v>11.11571241224668</v>
       </c>
       <c r="AW8" t="n">
-        <v>13.2825256993473</v>
+        <v>1.163363931075239</v>
       </c>
       <c r="AX8" t="n">
-        <v>-0.1390896457243926</v>
+        <v>0.09609284185745956</v>
       </c>
       <c r="AY8" t="n">
-        <v>-0.01001544946429198</v>
+        <v>0.02609042386851434</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.3333333333333333</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.4285714285714285</v>
-      </c>
-      <c r="BB8" t="inlineStr"/>
-      <c r="BC8" t="inlineStr"/>
+        <v>-0.1578947368421053</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>-0.8511904761904745</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>-0.1317902349900528</v>
+      </c>
       <c r="BD8" t="n">
-        <v>-0.8271844172104466</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>1.972065612875756</v>
-      </c>
+        <v>0.1123695709474362</v>
+      </c>
+      <c r="BE8" t="inlineStr"/>
       <c r="BF8" t="n">
-        <v>5381904.761904763</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>4045.238095238095</v>
-      </c>
+        <v>-1.486688311688312</v>
+      </c>
+      <c r="BG8" t="inlineStr"/>
       <c r="BH8" t="inlineStr"/>
       <c r="BI8" t="n">
-        <v>2.44285714285715</v>
-      </c>
-      <c r="BJ8" t="inlineStr"/>
-      <c r="BK8" t="n">
-        <v>-1.275793650793673</v>
-      </c>
+        <v>-8.274783549783535</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>-17554024.68847604</v>
+      </c>
+      <c r="BK8" t="inlineStr"/>
       <c r="BL8" t="n">
-        <v>0.9956349206349202</v>
+        <v>-6.333913909506691</v>
       </c>
       <c r="BM8" t="inlineStr"/>
       <c r="BN8" t="n">
-        <v>1.767063492063471</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>2784.877743830348</v>
-      </c>
+        <v>-5.304871251947134</v>
+      </c>
+      <c r="BO8" t="inlineStr"/>
       <c r="BP8" t="inlineStr"/>
       <c r="BQ8" t="n">
-        <v>0.2290413256350314</v>
+        <v>-1.019372294372317</v>
       </c>
       <c r="BR8" t="inlineStr"/>
-      <c r="BS8" t="inlineStr"/>
+      <c r="BS8" t="n">
+        <v>-35674.5670995671</v>
+      </c>
       <c r="BT8" t="n">
-        <v>0.2612278182197372</v>
+        <v>-7.20930735930736</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.671632664229946</v>
+        <v>-0.7392015370047886</v>
       </c>
       <c r="BV8" t="n">
-        <v>1924586.889432981</v>
+        <v>-22438.55046317812</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.4944444444444447</v>
+        <v>-32149350.64935065</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>E7rNpTBk</t>
+          <t>Mku6FvHt</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45584.4375</v>
+        <v>45591.4375</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">siebert d 
+          <t xml:space="preserve">burda m 
   ger </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">mewa arena
-  mainz </t>
+          <t xml:space="preserve">millerntor stadion
+  hamburg </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>EuakNmc1</t>
+          <t>ILyJuN3g</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>KbS1suSm</t>
+          <t>nwkTahLL</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2473,204 +2479,204 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2VSFgl3c</t>
+          <t>f3ddUIXs</t>
         </is>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0.996666666666667</v>
+        <v>0.5980000000000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.4235000000000002</v>
+        <v>0.3170588235294118</v>
       </c>
       <c r="R9" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="S9" t="n">
-        <v>1.2</v>
+        <v>0.4736842105263157</v>
       </c>
       <c r="T9" t="n">
-        <v>-2.666666666666667</v>
+        <v>0.1999999999999997</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1369565217391298</v>
+        <v>0.7222222222222223</v>
       </c>
       <c r="V9" t="n">
-        <v>2.666666666666664</v>
+        <v>6.799999999999999</v>
       </c>
       <c r="W9" t="n">
-        <v>4.78913043478261</v>
+        <v>3.722222222222223</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.333333333333333</v>
+        <v>-1</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.6391304347826086</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="Z9" t="n">
-        <v>-3.5</v>
+        <v>-0.9999999999999999</v>
       </c>
       <c r="AA9" t="n">
-        <v>-1.05</v>
+        <v>0.631578947368421</v>
       </c>
       <c r="AB9" t="n">
-        <v>18.97383357383357</v>
+        <v>-2.546013071895426</v>
       </c>
       <c r="AC9" t="n">
-        <v>18.80677971548538</v>
+        <v>-2.790456946352199</v>
       </c>
       <c r="AD9" t="n">
-        <v>893.7443437962941</v>
+        <v>-32.39420678272023</v>
       </c>
       <c r="AE9" t="n">
-        <v>901.3317456712546</v>
+        <v>-143.6553356724521</v>
       </c>
       <c r="AF9" t="n">
-        <v>25</v>
+        <v>-10</v>
       </c>
       <c r="AG9" t="n">
-        <v>10.50717703349282</v>
+        <v>30.46666666666667</v>
       </c>
       <c r="AH9" t="n">
-        <v>19.5</v>
+        <v>-32</v>
       </c>
       <c r="AI9" t="n">
-        <v>16.20813397129186</v>
+        <v>13.93333333333333</v>
       </c>
       <c r="AJ9" t="n">
-        <v>13.41666666666666</v>
+        <v>2</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.450000000000003</v>
+        <v>0.4210526315789522</v>
       </c>
       <c r="AL9" t="n">
-        <v>-3.333333333333329</v>
+        <v>6.400000000000006</v>
       </c>
       <c r="AM9" t="n">
-        <v>-10.47826086956522</v>
+        <v>15.22222222222223</v>
       </c>
       <c r="AN9" t="n">
-        <v>-17.66666666666669</v>
+        <v>109.6</v>
       </c>
       <c r="AO9" t="n">
-        <v>-129.85</v>
+        <v>236.6470588235294</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.5</v>
+        <v>-2.9</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.9318181818181821</v>
+        <v>-0.5784313725490198</v>
       </c>
       <c r="AR9" t="inlineStr"/>
       <c r="AS9" t="n">
-        <v>0.03333333333333333</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AT9" t="n">
-        <v>-3.416666666666671</v>
+        <v>-6.333333333333332</v>
       </c>
       <c r="AU9" t="n">
-        <v>2.825000000000003</v>
+        <v>-2.210526315789474</v>
       </c>
       <c r="AV9" t="n">
-        <v>33.97120610870611</v>
+        <v>4.016275856413451</v>
       </c>
       <c r="AW9" t="n">
-        <v>7.717998126482772</v>
+        <v>-18.49457309611932</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.06997299997299998</v>
+        <v>0.0123407177838121</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.04047277303910549</v>
+        <v>0.0225101626541523</v>
       </c>
       <c r="AZ9" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.3333333333333334</v>
       </c>
       <c r="BA9" t="n">
-        <v>-0.04166666666666666</v>
-      </c>
-      <c r="BB9" t="inlineStr"/>
-      <c r="BC9" t="inlineStr"/>
+        <v>-0.1052631578947368</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>2.060930735930739</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0.8669854225581766</v>
+      </c>
       <c r="BD9" t="n">
-        <v>-1.128159994726218</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>0.3493346142284643</v>
-      </c>
+        <v>-0.2216020778327277</v>
+      </c>
+      <c r="BE9" t="inlineStr"/>
       <c r="BF9" t="n">
-        <v>-23900375.18037518</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>-31400.2886002886</v>
-      </c>
+        <v>-0.4189814814814812</v>
+      </c>
+      <c r="BG9" t="inlineStr"/>
       <c r="BH9" t="inlineStr"/>
       <c r="BI9" t="n">
-        <v>-5.612554112554108</v>
-      </c>
-      <c r="BJ9" t="inlineStr"/>
-      <c r="BK9" t="n">
-        <v>-0.02037037037035816</v>
-      </c>
+        <v>-4.656331168831159</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>-6073651.279491061</v>
+      </c>
+      <c r="BK9" t="inlineStr"/>
       <c r="BL9" t="n">
-        <v>1.674434824434826</v>
+        <v>-6.237617048414265</v>
       </c>
       <c r="BM9" t="inlineStr"/>
       <c r="BN9" t="n">
-        <v>-7.036435786435774</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>-31066.50115389059</v>
-      </c>
+        <v>-4.752368555077524</v>
+      </c>
+      <c r="BO9" t="inlineStr"/>
       <c r="BP9" t="inlineStr"/>
       <c r="BQ9" t="n">
-        <v>-0.8493754878346873</v>
+        <v>0.6108585858585798</v>
       </c>
       <c r="BR9" t="inlineStr"/>
-      <c r="BS9" t="inlineStr"/>
+      <c r="BS9" t="n">
+        <v>-19158.24314574314</v>
+      </c>
       <c r="BT9" t="n">
-        <v>-5.502291214199644</v>
+        <v>-6.325132275132262</v>
       </c>
       <c r="BU9" t="n">
-        <v>-7.269611019580609</v>
+        <v>-0.3637180629827685</v>
       </c>
       <c r="BV9" t="n">
-        <v>-21476216.41353245</v>
+        <v>-16294.13797416893</v>
       </c>
       <c r="BW9" t="n">
-        <v>-0.8153920153920158</v>
+        <v>-7946945.045695045</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>z1eeWTdd</t>
+          <t>4E8uaJWa</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45583.64583333334</v>
+        <v>45590.64583333334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">dingert c 
+          <t xml:space="preserve">badstubner f 
   ger </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">signal iduna park
-  dortmund </t>
+          <t xml:space="preserve">mewa arena
+  mainz </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>nP1i5US1</t>
+          <t>EuakNmc1</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ILyJuN3g</t>
+          <t>88HSzjDr</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2697,209 +2703,209 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>hpYJ6izc</t>
+          <t>0jdIgO6t</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>vZA6VYpf</t>
+          <t>M5BRZDsC</t>
         </is>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.300000000000001</v>
+        <v>-1.19</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.9391979949874689</v>
+        <v>-0.1964052287581703</v>
       </c>
       <c r="R10" t="n">
-        <v>1.75</v>
+        <v>-1.5</v>
       </c>
       <c r="S10" t="n">
-        <v>1.15527950310559</v>
+        <v>0.1499999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>3.083333333333333</v>
+        <v>-4.399999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>1.594202898550725</v>
+        <v>-0.8362573099415203</v>
       </c>
       <c r="V10" t="n">
-        <v>7.749999999999998</v>
+        <v>-13.2</v>
       </c>
       <c r="W10" t="n">
-        <v>2.811594202898549</v>
+        <v>-0.5818713450292385</v>
       </c>
       <c r="X10" t="n">
-        <v>1.75</v>
+        <v>0.5999999999999999</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.3954451345755692</v>
+        <v>1.029239766081871</v>
       </c>
       <c r="Z10" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.5155279503105588</v>
+        <v>1.539473684210526</v>
       </c>
       <c r="AB10" t="n">
-        <v>15.74334178893002</v>
+        <v>7.026146549528903</v>
       </c>
       <c r="AC10" t="n">
-        <v>19.72753654159919</v>
+        <v>3.09463857316877</v>
       </c>
       <c r="AD10" t="n">
-        <v>733.0633150288402</v>
+        <v>182.9922436247838</v>
       </c>
       <c r="AE10" t="n">
-        <v>839.6607987970957</v>
+        <v>78.71963000145115</v>
       </c>
       <c r="AF10" t="n">
-        <v>12.33333333333333</v>
+        <v>36</v>
       </c>
       <c r="AG10" t="n">
-        <v>15.75</v>
+        <v>30.37083333333334</v>
       </c>
       <c r="AH10" t="n">
-        <v>22</v>
+        <v>-0.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>-1.309090909090905</v>
+        <v>9.495833333333337</v>
       </c>
       <c r="AJ10" t="n">
-        <v>13.25</v>
+        <v>-10.5</v>
       </c>
       <c r="AK10" t="n">
-        <v>5.734989648033132</v>
+        <v>0.04473684210526585</v>
       </c>
       <c r="AL10" t="n">
-        <v>20</v>
+        <v>-26.8</v>
       </c>
       <c r="AM10" t="n">
-        <v>11.21325051759834</v>
+        <v>-8.491228070175438</v>
       </c>
       <c r="AN10" t="n">
-        <v>306</v>
+        <v>-286.6</v>
       </c>
       <c r="AO10" t="n">
-        <v>155.5500000000001</v>
+        <v>-84.41176470588238</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.583333333333333</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-0.6397515527950315</v>
+        <v>0.8333333333333328</v>
       </c>
       <c r="AR10" t="inlineStr"/>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AT10" t="n">
-        <v>5.166666666666664</v>
+        <v>1.833333333333332</v>
       </c>
       <c r="AU10" t="n">
-        <v>-1.509316770186336</v>
+        <v>0.1684210526315777</v>
       </c>
       <c r="AV10" t="n">
-        <v>-64.66277828460009</v>
+        <v>20.63507473080857</v>
       </c>
       <c r="AW10" t="n">
-        <v>-21.72839919578044</v>
+        <v>5.485366489042526</v>
       </c>
       <c r="AX10" t="n">
-        <v>-0.03266710043305789</v>
+        <v>-0.03816941941941943</v>
       </c>
       <c r="AY10" t="n">
-        <v>-0.01711462257735812</v>
+        <v>-0.01899048350800872</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.3333333333333333</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.1946169772256729</v>
-      </c>
-      <c r="BB10" t="inlineStr"/>
-      <c r="BC10" t="inlineStr"/>
+        <v>0.2078947368421053</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>1.438095238095237</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0.05780232625606985</v>
+      </c>
       <c r="BD10" t="n">
-        <v>-0.5740564945207041</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>-0.6286207236517818</v>
-      </c>
+        <v>0.1750488587363179</v>
+      </c>
+      <c r="BE10" t="inlineStr"/>
       <c r="BF10" t="n">
-        <v>35161341.99134199</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>40811.97691197691</v>
-      </c>
+        <v>-0.07619047619047636</v>
+      </c>
+      <c r="BG10" t="inlineStr"/>
       <c r="BH10" t="inlineStr"/>
       <c r="BI10" t="n">
-        <v>11.34083694083692</v>
-      </c>
-      <c r="BJ10" t="inlineStr"/>
-      <c r="BK10" t="n">
-        <v>0.741847041847052</v>
-      </c>
+        <v>-0.6619047619047649</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>-2704651.024441398</v>
+      </c>
+      <c r="BK10" t="inlineStr"/>
       <c r="BL10" t="n">
-        <v>-0.1264069264069256</v>
+        <v>-0.6020139281008596</v>
       </c>
       <c r="BM10" t="inlineStr"/>
       <c r="BN10" t="n">
-        <v>10.55295815295815</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>27557.4241928933</v>
-      </c>
+        <v>-2.233149432021619</v>
+      </c>
+      <c r="BO10" t="inlineStr"/>
       <c r="BP10" t="inlineStr"/>
       <c r="BQ10" t="n">
-        <v>0.8976888154887503</v>
+        <v>-1.541269841269838</v>
       </c>
       <c r="BR10" t="inlineStr"/>
-      <c r="BS10" t="inlineStr"/>
+      <c r="BS10" t="n">
+        <v>846.0317460317456</v>
+      </c>
       <c r="BT10" t="n">
-        <v>10.91741088086299</v>
+        <v>-0.9492063492063494</v>
       </c>
       <c r="BU10" t="n">
-        <v>9.515824381205221</v>
+        <v>-0.0715763151526474</v>
       </c>
       <c r="BV10" t="n">
-        <v>20720545.86871847</v>
+        <v>-888.0110354938734</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.611688311688312</v>
+        <v>-1748888.888888889</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>nc8W6DTp</t>
+          <t>rPiijklS</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45571.60416666666</v>
+        <v>45585.52083333334</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">osmers h 
+          <t xml:space="preserve">welz t 
   ger </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">mhparena
-  stuttgart </t>
+          <t xml:space="preserve">volkswagen arena
+  wolfsburg </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>nJQmYp1B</t>
+          <t>nwkTahLL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>hQAtP9Sl</t>
+          <t>Ig1f1fy3</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2926,225 +2932,215 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>f3ddUIXs</t>
+          <t>8f6APkLc</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>4fuCGs9P</t>
+          <t>YZPE6Sx7</t>
         </is>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>3.84</v>
+        <v>-0.2350000000000001</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.382105263157895</v>
+        <v>-0.002777777777777768</v>
       </c>
       <c r="R11" t="n">
-        <v>5</v>
+        <v>-0.5</v>
       </c>
       <c r="S11" t="n">
-        <v>2.662337662337662</v>
+        <v>-0.3157894736842104</v>
       </c>
       <c r="T11" t="n">
-        <v>5.666666666666666</v>
+        <v>-2.333333333333334</v>
       </c>
       <c r="U11" t="n">
-        <v>6.519480519480519</v>
+        <v>-0.4210526315789473</v>
       </c>
       <c r="V11" t="n">
-        <v>16.5</v>
+        <v>-1</v>
       </c>
       <c r="W11" t="n">
-        <v>14.83549783549784</v>
+        <v>1.789473684210527</v>
       </c>
       <c r="X11" t="n">
-        <v>2.666666666666667</v>
+        <v>0.8333333333333333</v>
       </c>
       <c r="Y11" t="n">
-        <v>2</v>
+        <v>2.220446049250313e-16</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.5</v>
+        <v>-0.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.415584415584416</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>13.03180438842204</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>16.52550724023109</v>
+        <v>-0.3157894736842104</v>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>-inf</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>-inf</t>
+        </is>
       </c>
       <c r="AD11" t="n">
-        <v>873.5725148807396</v>
+        <v>14.511414132429</v>
       </c>
       <c r="AE11" t="n">
-        <v>815.1798281098756</v>
+        <v>-17.43854022422514</v>
       </c>
       <c r="AF11" t="n">
-        <v>19.5</v>
+        <v>44.33333333333334</v>
       </c>
       <c r="AG11" t="n">
-        <v>57.90476190476191</v>
+        <v>14.9375</v>
       </c>
       <c r="AH11" t="n">
-        <v>12.5</v>
+        <v>18</v>
       </c>
       <c r="AI11" t="n">
-        <v>36.29047619047619</v>
+        <v>9.25</v>
       </c>
       <c r="AJ11" t="n">
         <v>0.3333333333333286</v>
       </c>
       <c r="AK11" t="n">
-        <v>9.309523809523807</v>
+        <v>4.05263157894737</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="AM11" t="n">
-        <v>17.19913419913419</v>
+        <v>-2</v>
       </c>
       <c r="AN11" t="n">
-        <v>150.5</v>
+        <v>-193.1666666666667</v>
       </c>
       <c r="AO11" t="n">
-        <v>283.4210526315789</v>
+        <v>-72.66666666666669</v>
       </c>
       <c r="AP11" t="n">
-        <v>-1</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="AQ11" t="n">
-        <v>-1.396103896103896</v>
-      </c>
-      <c r="AR11" t="inlineStr"/>
+        <v>1.160818713450292</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0.3333333333333333</v>
+      </c>
       <c r="AS11" t="n">
-        <v>-1.4</v>
+        <v>0.5</v>
       </c>
       <c r="AT11" t="n">
-        <v>-2.666666666666666</v>
+        <v>5.666666666666664</v>
       </c>
       <c r="AU11" t="n">
-        <v>-1.54978354978355</v>
+        <v>1.842105263157896</v>
       </c>
       <c r="AV11" t="n">
-        <v>-12.32696078431372</v>
+        <v>-15.43269764234403</v>
       </c>
       <c r="AW11" t="n">
-        <v>-20.05562583271563</v>
+        <v>-8.39706589019363</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.09531272573868924</v>
+        <v>0.02093541544517427</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.02059955942118073</v>
+        <v>0.01809180936344106</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.2631578947368421</v>
       </c>
       <c r="BB11" t="n">
-        <v>-35000</v>
+        <v>-2.272186147186151</v>
       </c>
       <c r="BC11" t="n">
-        <v>87</v>
+        <v>0.106372732852936</v>
       </c>
       <c r="BD11" t="n">
-        <v>-1.93927875243665</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>-0.1641996405154309</v>
-      </c>
+        <v>-1.446541507179148</v>
+      </c>
+      <c r="BE11" t="inlineStr"/>
       <c r="BF11" t="n">
-        <v>6268771.043771042</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>-2692.472342472342</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>1</v>
-      </c>
+        <v>0.3241762866762863</v>
+      </c>
+      <c r="BG11" t="inlineStr"/>
+      <c r="BH11" t="inlineStr"/>
       <c r="BI11" t="n">
-        <v>1.34783549783549</v>
+        <v>0.8622474747474485</v>
       </c>
       <c r="BJ11" t="n">
-        <v>700000</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>-0.3159932659932565</v>
-      </c>
+        <v>4389194.218808111</v>
+      </c>
+      <c r="BK11" t="inlineStr"/>
       <c r="BL11" t="n">
-        <v>-2.729894179894185</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>56</v>
-      </c>
+        <v>1.692275103301171</v>
+      </c>
+      <c r="BM11" t="inlineStr"/>
       <c r="BN11" t="n">
-        <v>1.411712361712375</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>-512.6174020910839</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>-4.466666666666669</v>
-      </c>
+        <v>2.604569662966767</v>
+      </c>
+      <c r="BO11" t="inlineStr"/>
+      <c r="BP11" t="inlineStr"/>
       <c r="BQ11" t="n">
-        <v>0.2443735601630339</v>
-      </c>
-      <c r="BR11" t="n">
-        <v>-1</v>
-      </c>
+        <v>0.9278138528138697</v>
+      </c>
+      <c r="BR11" t="inlineStr"/>
       <c r="BS11" t="n">
-        <v>3.199999999999989</v>
+        <v>12724.18831168831</v>
       </c>
       <c r="BT11" t="n">
-        <v>0.6386699070909856</v>
+        <v>3.104641654641654</v>
       </c>
       <c r="BU11" t="n">
-        <v>2.04899622794359</v>
+        <v>0.3637180629827685</v>
       </c>
       <c r="BV11" t="n">
-        <v>4416343.162198429</v>
+        <v>13149.49101893028</v>
       </c>
       <c r="BW11" t="n">
-        <v>-0.1958152958152959</v>
+        <v>4270538.119288119</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>ShoJUGLi</t>
+          <t>nBwH6AY8</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45571.52083333334</v>
+        <v>45585.4375</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">brand b 
+          <t xml:space="preserve">reichel t 
   ger </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">deutsche bank park
-  frankfurt </t>
+          <t xml:space="preserve">holstein stadion
+  kiel </t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>8vndvXTk</t>
+          <t>63WsD2ei</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>nVp0wiqd</t>
+          <t>pzHW4oaE</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3171,229 +3167,209 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>A15eUM4C</t>
+          <t>hAcTWKKN</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>hAcTWKKN</t>
+          <t>IkCftsQm</t>
         </is>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.401666666666667</v>
+        <v>-1.243333333333333</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.5553132832080201</v>
+        <v>-0.1272222222222223</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>-0.9999999999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.09610983981693355</v>
+        <v>-0.1578947368421051</v>
       </c>
       <c r="T12" t="n">
-        <v>-7</v>
+        <v>-3.833333333333333</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.041189931350115</v>
+        <v>-0.3684210526315788</v>
       </c>
       <c r="V12" t="n">
-        <v>-14.25</v>
+        <v>-9.333333333333332</v>
       </c>
       <c r="W12" t="n">
-        <v>-3.734553775743708</v>
+        <v>-2.894736842105262</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.75</v>
+        <v>-2</v>
       </c>
       <c r="Y12" t="n">
-        <v>-0.4988558352402745</v>
+        <v>0.631578947368421</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.1922196796338671</v>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>0.7894736842105263</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>4.001518620268621</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.002671378329273</v>
       </c>
       <c r="AD12" t="n">
-        <v>1298.060004493361</v>
+        <v>-26.51163913248672</v>
       </c>
       <c r="AE12" t="n">
-        <v>1046.664945470352</v>
+        <v>-138.0127378590239</v>
       </c>
       <c r="AF12" t="n">
-        <v>-65.66666666666667</v>
+        <v>-6.000000000000014</v>
       </c>
       <c r="AG12" t="n">
-        <v>-29.57070707070707</v>
+        <v>20.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>-44</v>
+        <v>-43.00000000000001</v>
       </c>
       <c r="AI12" t="n">
-        <v>-11.75757575757576</v>
+        <v>-7.6875</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-8</v>
+        <v>-2.333333333333336</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.279176201372998</v>
+        <v>-2.210526315789473</v>
       </c>
       <c r="AL12" t="n">
-        <v>-42</v>
+        <v>7.666666666666671</v>
       </c>
       <c r="AM12" t="n">
-        <v>-17.10297482837528</v>
+        <v>14.42105263157895</v>
       </c>
       <c r="AN12" t="n">
-        <v>-568.8333333333333</v>
+        <v>47.99999999999994</v>
       </c>
       <c r="AO12" t="n">
-        <v>-179.5842105263157</v>
+        <v>184.8888888888889</v>
       </c>
       <c r="AP12" t="n">
-        <v>-2.5</v>
+        <v>-1.833333333333333</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-0.6161616161616161</v>
+        <v>-0.7456140350877192</v>
       </c>
       <c r="AR12" t="inlineStr"/>
       <c r="AS12" t="n">
-        <v>-2</v>
+        <v>-0.6666666666666667</v>
       </c>
       <c r="AT12" t="n">
-        <v>-2</v>
+        <v>1.666666666666668</v>
       </c>
       <c r="AU12" t="n">
-        <v>-0.5125858123569795</v>
+        <v>-0.6315789473684212</v>
       </c>
       <c r="AV12" t="n">
-        <v>86.42643358438505</v>
+        <v>-4.619139542563182</v>
       </c>
       <c r="AW12" t="n">
-        <v>24.09542703326451</v>
+        <v>-10.65697253732944</v>
       </c>
       <c r="AX12" t="n">
-        <v>-0.05814469423076903</v>
+        <v>-0.006266876116679844</v>
       </c>
       <c r="AY12" t="n">
-        <v>-0.01328353982935117</v>
+        <v>-0.03151796441786024</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="BA12" t="n">
-        <v>-0.006864988558352408</v>
+        <v>0.4736842105263158</v>
       </c>
       <c r="BB12" t="n">
-        <v>-273000</v>
+        <v>-0.315981240981241</v>
       </c>
       <c r="BC12" t="n">
-        <v>-422</v>
+        <v>-0.7698775925320547</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.737788399108098</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>-4.478409090909093</v>
-      </c>
+        <v>2.086570982321206</v>
+      </c>
+      <c r="BE12" t="inlineStr"/>
       <c r="BF12" t="n">
-        <v>-32054861.1111111</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>-41816.66666666666</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>-5</v>
-      </c>
+        <v>-0.4131313131313132</v>
+      </c>
+      <c r="BG12" t="inlineStr"/>
+      <c r="BH12" t="inlineStr"/>
       <c r="BI12" t="n">
-        <v>-5.866666666666674</v>
+        <v>-4.945165945165954</v>
       </c>
       <c r="BJ12" t="n">
-        <v>-188575000</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>1.322222222222251</v>
-      </c>
+        <v>-2342168.257081627</v>
+      </c>
+      <c r="BK12" t="inlineStr"/>
       <c r="BL12" t="n">
-        <v>-2.038888888888888</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>-385</v>
-      </c>
+        <v>-3.383567355241112</v>
+      </c>
+      <c r="BM12" t="inlineStr"/>
       <c r="BN12" t="n">
-        <v>-3.972222222222214</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>-49850.87626368586</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>-2.666666666666668</v>
-      </c>
+        <v>-4.851261175713603</v>
+      </c>
+      <c r="BO12" t="inlineStr"/>
+      <c r="BP12" t="inlineStr"/>
       <c r="BQ12" t="n">
-        <v>-1.322728418239254</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>-9</v>
-      </c>
+        <v>-0.7374458874458583</v>
+      </c>
+      <c r="BR12" t="inlineStr"/>
       <c r="BS12" t="n">
-        <v>-11.5</v>
+        <v>-11036.97691197692</v>
       </c>
       <c r="BT12" t="n">
-        <v>-2.930095041124474</v>
+        <v>-5.185209235209228</v>
       </c>
       <c r="BU12" t="n">
-        <v>-9.030224067298363</v>
+        <v>-0.1591245193729667</v>
       </c>
       <c r="BV12" t="n">
-        <v>-29414448.11116028</v>
+        <v>-9312.095456031384</v>
       </c>
       <c r="BW12" t="n">
-        <v>-1.388888888888889</v>
+        <v>-4655847.763347763</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>0KbQSfj4</t>
+          <t>2mcmYkSq</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45571.4375</v>
+        <v>45584.5625</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">stegemann s 
+          <t xml:space="preserve">osmers h 
   ger </t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">voith arena
-  heidenheim </t>
+          <t xml:space="preserve">allianz arena
+  munich </t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>KWixEVWi</t>
+          <t>nVp0wiqd</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>KbS1suSm</t>
+          <t>nJQmYp1B</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3420,192 +3396,1558 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>vZA6VYpf</t>
+          <t>UgdQz0fK</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2VSFgl3c</t>
+          <t>KUx4Q7x1</t>
         </is>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.61</v>
+        <v>0.5416666666666667</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.4816052631578946</v>
+        <v>0.6380994152046779</v>
       </c>
       <c r="R13" t="n">
-        <v>2.5</v>
+        <v>0.7142857142857144</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3157894736842106</v>
+        <v>0.5210526315789474</v>
       </c>
       <c r="T13" t="n">
-        <v>1.833333333333333</v>
+        <v>2.523809523809523</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.176201372997712</v>
+        <v>0.1473684210526316</v>
       </c>
       <c r="V13" t="n">
-        <v>2.499999999999998</v>
+        <v>6.214285714285715</v>
       </c>
       <c r="W13" t="n">
-        <v>0.8443935926773456</v>
+        <v>1.815789473684211</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.8333333333333335</v>
+        <v>0.8809523809523812</v>
       </c>
       <c r="Y13" t="n">
-        <v>-0.4759725400457666</v>
+        <v>0.3789473684210525</v>
       </c>
       <c r="Z13" t="n">
-        <v>-2</v>
+        <v>1.142857142857143</v>
       </c>
       <c r="AA13" t="n">
-        <v>-0.4668192219679632</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>20.37298474945534</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>20.7540593529089</v>
+        <v>0.0631578947368423</v>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>-inf</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>-inf</t>
+        </is>
       </c>
       <c r="AD13" t="n">
-        <v>1108.081876817196</v>
+        <v>-284.5064901742963</v>
       </c>
       <c r="AE13" t="n">
-        <v>975.096884151051</v>
+        <v>-58.64128252890066</v>
       </c>
       <c r="AF13" t="n">
-        <v>-55.5</v>
+        <v>19.16666666666667</v>
       </c>
       <c r="AG13" t="n">
-        <v>-17.65656565656566</v>
+        <v>5.790441176470594</v>
       </c>
       <c r="AH13" t="n">
-        <v>-38.5</v>
+        <v>17.25</v>
       </c>
       <c r="AI13" t="n">
-        <v>2.348484848484851</v>
+        <v>14.57352941176471</v>
       </c>
       <c r="AJ13" t="n">
-        <v>-1.666666666666664</v>
+        <v>2.166666666666668</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.7963386727688757</v>
+        <v>2.628947368421059</v>
       </c>
       <c r="AL13" t="n">
-        <v>-25</v>
+        <v>7.476190476190474</v>
       </c>
       <c r="AM13" t="n">
-        <v>-14.74141876430205</v>
+        <v>1.747368421052627</v>
       </c>
       <c r="AN13" t="n">
-        <v>-270.5</v>
+        <v>190.3333333333334</v>
       </c>
       <c r="AO13" t="n">
-        <v>-200.771052631579</v>
+        <v>13.62280701754389</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>1.80952380952381</v>
       </c>
       <c r="AQ13" t="n">
-        <v>-0.002392344497607279</v>
+        <v>0.1794117647058824</v>
       </c>
       <c r="AR13" t="inlineStr"/>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
-        <v>0.5000000000000009</v>
+        <v>-1.047619047619047</v>
       </c>
       <c r="AU13" t="n">
-        <v>4.11441647597254</v>
+        <v>0.05000000000000071</v>
       </c>
       <c r="AV13" t="n">
-        <v>50.88180014430015</v>
+        <v>-22.45417058375786</v>
       </c>
       <c r="AW13" t="n">
-        <v>11.84274039492498</v>
+        <v>-10.74876279635689</v>
       </c>
       <c r="AX13" t="n">
-        <v>-0.1424963924963925</v>
+        <v>-0.009688431300656303</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.02223712429452592</v>
+        <v>0.00423653178595397</v>
       </c>
       <c r="AZ13" t="n">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>-0.1394736842105263</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>2.037896825396825</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>2.443650318979273</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>-1.341587495322017</v>
+      </c>
+      <c r="BE13" t="inlineStr"/>
+      <c r="BF13" t="n">
+        <v>1.650901875901876</v>
+      </c>
+      <c r="BG13" t="inlineStr"/>
+      <c r="BH13" t="inlineStr"/>
+      <c r="BI13" t="n">
+        <v>6.678282828282832</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>27052256.89789012</v>
+      </c>
+      <c r="BK13" t="inlineStr"/>
+      <c r="BL13" t="n">
+        <v>5.721760905932726</v>
+      </c>
+      <c r="BM13" t="inlineStr"/>
+      <c r="BN13" t="n">
+        <v>7.887532947788358</v>
+      </c>
+      <c r="BO13" t="inlineStr"/>
+      <c r="BP13" t="inlineStr"/>
+      <c r="BQ13" t="n">
+        <v>-1.980086580086549</v>
+      </c>
+      <c r="BR13" t="inlineStr"/>
+      <c r="BS13" t="n">
+        <v>49744.17388167389</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>6.145869408369407</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>1.161643114797139</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>51066.93250276842</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>32626361.38167388</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>E7rNpTBk</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45584.4375</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stegemann s 
+  ger </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mewa arena
+  mainz </t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>59</v>
+      </c>
+      <c r="H14" t="n">
+        <v>591</v>
+      </c>
+      <c r="I14" t="n">
         <v>0</v>
       </c>
-      <c r="BA13" t="n">
-        <v>0.06178489702517162</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>-111000</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>-41</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>0.404718962972936</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>0.3342037959348438</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>-27282676.76767677</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>-34560.60606060606</v>
-      </c>
-      <c r="BH13" t="n">
+      <c r="J14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>0jdIgO6t</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>pfoInmcq</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
         <v>0</v>
       </c>
-      <c r="BI13" t="n">
-        <v>-7.969696969696969</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>-62900000</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>3.751851851851853</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>0.9387205387205348</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>-34</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>-9.784848484848496</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>-32594.17840744231</v>
-      </c>
-      <c r="BP13" t="n">
+      <c r="P14" t="n">
+        <v>-0.8383333333333329</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-0.8277777777777775</v>
+      </c>
+      <c r="R14" t="n">
         <v>-1</v>
       </c>
-      <c r="BQ13" t="n">
-        <v>-0.9367096476271666</v>
-      </c>
-      <c r="BR13" t="n">
+      <c r="S14" t="n">
+        <v>-0.7894736842105263</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-2.666666666666667</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-2.526315789473684</v>
+      </c>
+      <c r="V14" t="n">
+        <v>-8.16666666666667</v>
+      </c>
+      <c r="W14" t="n">
+        <v>-3.999999999999998</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-1.105263157894737</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>3.635743817729112</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.910812094129622</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>109.5009253312115</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>118.1778491122031</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>-0.3333333333333286</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>-11.9375</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>3.333333333333336</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>-15.49999999999999</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>-4.94736842105263</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>-23</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>-15.15789473684211</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>-245.1666666666667</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>-203.4444444444444</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.62280701754386</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>5.551115123125783e-17</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>1.500000000000004</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>1.789473684210529</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>13.21372697936165</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>12.45869618523126</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0.004124397922847522</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0.02197106918644985</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>-0.1052631578947368</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>1.688744588744587</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0.3826716332465985</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>-1.017602248235818</v>
+      </c>
+      <c r="BE14" t="inlineStr"/>
+      <c r="BF14" t="n">
+        <v>-0.830880230880231</v>
+      </c>
+      <c r="BG14" t="inlineStr"/>
+      <c r="BH14" t="inlineStr"/>
+      <c r="BI14" t="n">
+        <v>-5.724819624819631</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>-21443429.20142539</v>
+      </c>
+      <c r="BK14" t="inlineStr"/>
+      <c r="BL14" t="n">
+        <v>-5.560772793966038</v>
+      </c>
+      <c r="BM14" t="inlineStr"/>
+      <c r="BN14" t="n">
+        <v>-7.291088835853316</v>
+      </c>
+      <c r="BO14" t="inlineStr"/>
+      <c r="BP14" t="inlineStr"/>
+      <c r="BQ14" t="n">
+        <v>-0.07936507936506132</v>
+      </c>
+      <c r="BR14" t="inlineStr"/>
+      <c r="BS14" t="n">
+        <v>-31845.59884559884</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>-7.115584415584422</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>-0.829649395643425</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>-31001.96798682258</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>-24401818.18181818</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Eq0zfXl3</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45584.4375</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">burda m 
+  ger </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prezero arena
+  sinsheim </t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>59</v>
+      </c>
+      <c r="H15" t="n">
+        <v>591</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>GzfvcwRj</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>f3ddUIXs</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.2800000000000005</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>-0.1148333333333327</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S15" t="n">
+        <v>-0.2781954887218046</v>
+      </c>
+      <c r="T15" t="n">
+        <v>-0.166666666666667</v>
+      </c>
+      <c r="U15" t="n">
+        <v>-0.9949874686716793</v>
+      </c>
+      <c r="V15" t="n">
+        <v>-1.500000000000004</v>
+      </c>
+      <c r="W15" t="n">
+        <v>-5.245614035087721</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.3333333333333337</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.085213032581454</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.556390977443609</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.876178274340039</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>4.165848157331986</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>-14.82838183003545</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>17.7741159357241</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>-40.66666666666667</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>-40.59722222222221</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>11.33333333333333</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>-18.5625</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>10.33333333333334</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>-0.9598997493734416</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>9</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0.02005012531328987</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>-21</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>-59.58888888888885</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>-0.1666666666666665</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>-0.2731829573934836</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0.06666666666666671</v>
+      </c>
+      <c r="AT15" t="n">
         <v>-5</v>
       </c>
-      <c r="BS13" t="n">
-        <v>9</v>
-      </c>
-      <c r="BT13" t="n">
-        <v>-9.692955409979916</v>
-      </c>
-      <c r="BU13" t="n">
-        <v>-8.926981754435815</v>
-      </c>
-      <c r="BV13" t="n">
-        <v>-22624496.18268996</v>
-      </c>
-      <c r="BW13" t="n">
-        <v>-1.208249158249159</v>
+      <c r="AU15" t="n">
+        <v>-2.43859649122807</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>13.88935226748957</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>17.18296486154859</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0.01529250522707809</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>-0.06235933831556632</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>-0.8134920634920597</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>-1.143217502925591</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>0.4682563443731169</v>
+      </c>
+      <c r="BE15" t="inlineStr"/>
+      <c r="BF15" t="n">
+        <v>0.6412698412698414</v>
+      </c>
+      <c r="BG15" t="inlineStr"/>
+      <c r="BH15" t="inlineStr"/>
+      <c r="BI15" t="n">
+        <v>3.12433862433862</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>3848001.752657878</v>
+      </c>
+      <c r="BK15" t="inlineStr"/>
+      <c r="BL15" t="n">
+        <v>3.315877120078795</v>
+      </c>
+      <c r="BM15" t="inlineStr"/>
+      <c r="BN15" t="n">
+        <v>2.777769191347247</v>
+      </c>
+      <c r="BO15" t="inlineStr"/>
+      <c r="BP15" t="inlineStr"/>
+      <c r="BQ15" t="n">
+        <v>0.7919973544973686</v>
+      </c>
+      <c r="BR15" t="inlineStr"/>
+      <c r="BS15" t="n">
+        <v>13013.75661375661</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>4.582671957671963</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>0.2187015156939971</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>8893.810533660157</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>5205162.037037037</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>M93rhBJF</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45584.4375</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">badstubner f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">europa park stadion
+  freiburg </t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>fTVNku3I</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>59</v>
+      </c>
+      <c r="H16" t="n">
+        <v>591</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>4fuCGs9P</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>M5BRZDsC</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.9449999999999996</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.2933333333333328</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.3157894736842104</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.1052631578947372</v>
+      </c>
+      <c r="V16" t="n">
+        <v>-0.1666666666666643</v>
+      </c>
+      <c r="W16" t="n">
+        <v>-4.052631578947366</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.4210526315789473</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.3157894736842104</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>-2.191216082392553</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.630913069920322</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>-148.8396680275191</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>-2.063000938208006</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>-19</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>-21.6875</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>-29.66666666666667</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>-29.0625</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>-0.5000000000000071</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>-6.210526315789473</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>-5.15789473684211</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>-27</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>-26.50000000000006</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>-0.8333333333333335</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>-0.3157894736842106</v>
+      </c>
+      <c r="AR16" t="inlineStr"/>
+      <c r="AS16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>-3.500000000000004</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>-3.789473684210527</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>9.727761184931317</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>23.38738849153292</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>-0.08069004119041931</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>-0.04403289786355624</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0.2105263157894737</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0.9956349206349202</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>1.97206561287576</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>-0.8271844172104466</v>
+      </c>
+      <c r="BE16" t="inlineStr"/>
+      <c r="BF16" t="n">
+        <v>0.4944444444444447</v>
+      </c>
+      <c r="BG16" t="inlineStr"/>
+      <c r="BH16" t="inlineStr"/>
+      <c r="BI16" t="n">
+        <v>2.44285714285715</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>1924586.889432981</v>
+      </c>
+      <c r="BK16" t="inlineStr"/>
+      <c r="BL16" t="n">
+        <v>0.2612278182197372</v>
+      </c>
+      <c r="BM16" t="inlineStr"/>
+      <c r="BN16" t="n">
+        <v>1.671632664229946</v>
+      </c>
+      <c r="BO16" t="inlineStr"/>
+      <c r="BP16" t="inlineStr"/>
+      <c r="BQ16" t="n">
+        <v>-1.275793650793673</v>
+      </c>
+      <c r="BR16" t="inlineStr"/>
+      <c r="BS16" t="n">
+        <v>4045.238095238095</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>1.767063492063471</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>0.2290413256350314</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>2784.877743830351</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>5381904.761904763</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>r3GGwC4M</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45584.4375</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brand b 
+  ger </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bayarena
+  leverkusen </t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>59</v>
+      </c>
+      <c r="H17" t="n">
+        <v>591</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>hAcTWKKN</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>K6A2elS9</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.4366666666666668</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.188968253968254</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.299043062200957</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.785714285714286</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3.956937799043063</v>
+      </c>
+      <c r="V17" t="n">
+        <v>11.80952380952381</v>
+      </c>
+      <c r="W17" t="n">
+        <v>8.160287081339712</v>
+      </c>
+      <c r="X17" t="n">
+        <v>-0.1190476190476193</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.38755980861244</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-0.2142857142857144</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.708133971291866</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>-7.666216486594638</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>-3.986461721429946</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>-264.0001542944669</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>-157.977081593141</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>36.21052631578948</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>61.49999999999999</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>39.46052631578947</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>21.54761904761904</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>7.53827751196172</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>32.0952380952381</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>19.64593301435407</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>449.3333333333333</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>276.53216374269</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>-0.02380952380952372</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>-0.9365079365079365</v>
+      </c>
+      <c r="AR17" t="inlineStr"/>
+      <c r="AS17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>-1.523809523809526</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>-1.588516746411484</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>-50.80406350622118</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>-30.63001675824129</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0.06190292413778099</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>-0.001211069017661874</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0.4162679425837321</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>1.878968253968257</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>1.958551347173639</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>-3.998030759353213</v>
+      </c>
+      <c r="BE17" t="inlineStr"/>
+      <c r="BF17" t="n">
+        <v>1.392989417989418</v>
+      </c>
+      <c r="BG17" t="inlineStr"/>
+      <c r="BH17" t="inlineStr"/>
+      <c r="BI17" t="n">
+        <v>7.041798941798945</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>30585890.97509019</v>
+      </c>
+      <c r="BK17" t="inlineStr"/>
+      <c r="BL17" t="n">
+        <v>3.648078481791458</v>
+      </c>
+      <c r="BM17" t="inlineStr"/>
+      <c r="BN17" t="n">
+        <v>8.058965356477515</v>
+      </c>
+      <c r="BO17" t="inlineStr"/>
+      <c r="BP17" t="inlineStr"/>
+      <c r="BQ17" t="n">
+        <v>-0.9808201058201576</v>
+      </c>
+      <c r="BR17" t="inlineStr"/>
+      <c r="BS17" t="n">
+        <v>65045.76719576719</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>4.233862433862456</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>0.9105434996965289</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>56512.5458955512</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>35172056.87830687</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>fHjVr7t2</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45584.4375</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stegemann s 
+  ger </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">borussia park
+  monchengladbach </t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>59</v>
+      </c>
+      <c r="H18" t="n">
+        <v>591</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2VSFgl3c</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>pfoInmcq</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>-0.4566666666666668</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.1290350877192981</v>
+      </c>
+      <c r="R18" t="n">
+        <v>-0.4999999999999999</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>-0.9999999999999996</v>
+      </c>
+      <c r="U18" t="n">
+        <v>-0.4736842105263159</v>
+      </c>
+      <c r="V18" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="W18" t="n">
+        <v>-0.05000000000000071</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-0.8333333333333335</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>-0.7210526315789474</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-0.7578947368421052</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>-2.796452036525567</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>-1.90323717795355</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>-178.0116696292387</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>-106.2278350326475</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>12.33333333333334</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>-5.408088235294116</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>17.33333333333334</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>7.091911764705884</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>-1.518421052631581</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>24</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>11.42105263157895</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>278.8333333333333</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>143.8888888888889</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0.3684210526315788</v>
+      </c>
+      <c r="AR18" t="inlineStr"/>
+      <c r="AS18" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0.1666666666666679</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>-0.378947368421052</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>-28.00732395502287</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>-9.558032948932585</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0.08273933273933273</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0.02872016971395197</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>-2.775557561562891e-17</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>-0.1552631578947369</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>-0.6999999999999957</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>-0.1577336197636967</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>-1.614087236725283</v>
+      </c>
+      <c r="BE18" t="inlineStr"/>
+      <c r="BF18" t="n">
+        <v>0.4714285714285715</v>
+      </c>
+      <c r="BG18" t="inlineStr"/>
+      <c r="BH18" t="inlineStr"/>
+      <c r="BI18" t="n">
+        <v>2.957142857142856</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>3920842.284282134</v>
+      </c>
+      <c r="BK18" t="inlineStr"/>
+      <c r="BL18" t="n">
+        <v>5.012450380609906</v>
+      </c>
+      <c r="BM18" t="inlineStr"/>
+      <c r="BN18" t="n">
+        <v>3.971006709319894</v>
+      </c>
+      <c r="BO18" t="inlineStr"/>
+      <c r="BP18" t="inlineStr"/>
+      <c r="BQ18" t="n">
+        <v>-2.371428571428538</v>
+      </c>
+      <c r="BR18" t="inlineStr"/>
+      <c r="BS18" t="n">
+        <v>2285.714285714286</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>3.600000000000009</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>0.1651216550693504</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>2418.483320101499</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>5112857.142857143</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>z1eeWTdd</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45583.64583333334</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dingert c 
+  ger </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">signal iduna park
+  dortmund </t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>59</v>
+      </c>
+      <c r="H19" t="n">
+        <v>591</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>hpYJ6izc</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>vZA6VYpf</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.04666666666666663</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.1844444444444437</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.1578947368421053</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.166666666666667</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.736842105263158</v>
+      </c>
+      <c r="V19" t="n">
+        <v>-0.1666666666666679</v>
+      </c>
+      <c r="W19" t="n">
+        <v>-1.473684210526315</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.5263157894736841</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0.4736842105263159</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.559179845209258</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.546297636469952</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>-148.3364585842155</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>7.665501711267865</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>-9.333333333333343</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>-3.875</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>10.66666666666666</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>-9.25</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0.6666666666666643</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>2.105263157894733</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>19</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>8.736842105263165</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>236.5</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>90.1111111111112</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>2.733333333333333</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="AR19" t="inlineStr"/>
+      <c r="AS19" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>4.999999999999996</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>1.157894736842106</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>-48.76823430965993</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>-13.02257196510858</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>-0.06133232209183596</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>-0.02913702606569234</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0.1052631578947368</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>-0.1264069264069292</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>-0.6286207236517818</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>-0.5740564945207041</v>
+      </c>
+      <c r="BE19" t="inlineStr"/>
+      <c r="BF19" t="n">
+        <v>1.611688311688312</v>
+      </c>
+      <c r="BG19" t="inlineStr"/>
+      <c r="BH19" t="inlineStr"/>
+      <c r="BI19" t="n">
+        <v>11.34083694083692</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>20720545.86871847</v>
+      </c>
+      <c r="BK19" t="inlineStr"/>
+      <c r="BL19" t="n">
+        <v>10.91741088086299</v>
+      </c>
+      <c r="BM19" t="inlineStr"/>
+      <c r="BN19" t="n">
+        <v>9.515824381205221</v>
+      </c>
+      <c r="BO19" t="inlineStr"/>
+      <c r="BP19" t="inlineStr"/>
+      <c r="BQ19" t="n">
+        <v>0.741847041847052</v>
+      </c>
+      <c r="BR19" t="inlineStr"/>
+      <c r="BS19" t="n">
+        <v>40811.97691197691</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>10.55295815295815</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>0.8976888154887501</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>27557.42419289329</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>35161341.99134199</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/data_preparation/df_constructed.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_constructed.xlsx
@@ -695,112 +695,112 @@
       </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
+          <t>dif_sum_value_player_miss</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_value_player_sub</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_age_player_start</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_sub</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_start</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_wage_player_miss</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_value_player_start</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_sub</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_start</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_sub</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_value_player_miss</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_start</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="BJ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_sub</t>
-        </is>
-      </c>
-      <c r="BK1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_wage_player_miss</t>
-        </is>
-      </c>
-      <c r="BL1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="BM1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="BN1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>dif_n_player_miss</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="BQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="BR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="BS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_start</t>
-        </is>
-      </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="BU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="BV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_sub</t>
-        </is>
-      </c>
-      <c r="BW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_start</t>
         </is>
       </c>
     </row>
@@ -984,55 +984,55 @@
       <c r="BA2" t="n">
         <v>0.1052631578947368</v>
       </c>
-      <c r="BB2" t="n">
-        <v>-0.7111111111111157</v>
-      </c>
+      <c r="BB2" t="inlineStr"/>
       <c r="BC2" t="n">
-        <v>1.525780548680189</v>
+        <v>-3473661.002921382</v>
       </c>
       <c r="BD2" t="n">
-        <v>-1.073159866540124</v>
+        <v>-1.680500682347684</v>
       </c>
       <c r="BE2" t="inlineStr"/>
       <c r="BF2" t="n">
+        <v>-5.339618715525873</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>-0.7111111111111157</v>
+      </c>
+      <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="inlineStr"/>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="n">
+        <v>-4129.83649600191</v>
+      </c>
+      <c r="BL2" t="n">
         <v>-0.6269841269841272</v>
       </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
-      <c r="BI2" t="n">
+      <c r="BM2" t="n">
         <v>-2.292063492063491</v>
       </c>
-      <c r="BJ2" t="n">
-        <v>-3473661.002921382</v>
-      </c>
-      <c r="BK2" t="inlineStr"/>
-      <c r="BL2" t="n">
-        <v>-5.339618715525873</v>
-      </c>
-      <c r="BM2" t="inlineStr"/>
-      <c r="BN2" t="n">
-        <v>-1.680500682347684</v>
-      </c>
-      <c r="BO2" t="inlineStr"/>
-      <c r="BP2" t="inlineStr"/>
+      <c r="BN2" t="inlineStr"/>
+      <c r="BO2" t="n">
+        <v>-4257777.777777778</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>1.525780548680189</v>
+      </c>
       <c r="BQ2" t="n">
-        <v>1.173015873015856</v>
+        <v>-7933.333333333336</v>
       </c>
       <c r="BR2" t="inlineStr"/>
       <c r="BS2" t="n">
-        <v>-7933.333333333336</v>
+        <v>-0.1814344349486554</v>
       </c>
       <c r="BT2" t="n">
+        <v>1.173015873015856</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>-1.073159866540124</v>
+      </c>
+      <c r="BV2" t="inlineStr"/>
+      <c r="BW2" t="n">
         <v>-3.839682539682542</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>-0.1814344349486554</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>-4129.83649600191</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>-4257777.777777778</v>
       </c>
     </row>
     <row r="3">
@@ -1213,55 +1213,55 @@
       <c r="BA3" t="n">
         <v>-0.1052631578947368</v>
       </c>
-      <c r="BB3" t="n">
-        <v>2.456349206349209</v>
-      </c>
+      <c r="BB3" t="inlineStr"/>
       <c r="BC3" t="n">
-        <v>3.765622955374511</v>
+        <v>-4668033.640236486</v>
       </c>
       <c r="BD3" t="n">
-        <v>-1.867936097537267</v>
+        <v>0.3235654070240486</v>
       </c>
       <c r="BE3" t="inlineStr"/>
       <c r="BF3" t="n">
+        <v>-4.969929552848782</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>2.456349206349209</v>
+      </c>
+      <c r="BH3" t="inlineStr"/>
+      <c r="BI3" t="inlineStr"/>
+      <c r="BJ3" t="inlineStr"/>
+      <c r="BK3" t="n">
+        <v>-745.0663408002438</v>
+      </c>
+      <c r="BL3" t="n">
         <v>-0.2581649831649833</v>
       </c>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
-      <c r="BI3" t="n">
+      <c r="BM3" t="n">
         <v>-1.829304954304945</v>
       </c>
-      <c r="BJ3" t="n">
-        <v>-4668033.640236486</v>
-      </c>
-      <c r="BK3" t="inlineStr"/>
-      <c r="BL3" t="n">
-        <v>-4.969929552848782</v>
-      </c>
-      <c r="BM3" t="inlineStr"/>
-      <c r="BN3" t="n">
-        <v>0.3235654070240486</v>
-      </c>
-      <c r="BO3" t="inlineStr"/>
-      <c r="BP3" t="inlineStr"/>
+      <c r="BN3" t="inlineStr"/>
+      <c r="BO3" t="n">
+        <v>-8518617.724867728</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>3.765622955374511</v>
+      </c>
       <c r="BQ3" t="n">
-        <v>1.032311207311153</v>
+        <v>-6800.048100048098</v>
       </c>
       <c r="BR3" t="inlineStr"/>
       <c r="BS3" t="n">
-        <v>-6800.048100048098</v>
+        <v>-0.2327903326922616</v>
       </c>
       <c r="BT3" t="n">
+        <v>1.032311207311153</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>-1.867936097537267</v>
+      </c>
+      <c r="BV3" t="inlineStr"/>
+      <c r="BW3" t="n">
         <v>-4.159788359788351</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>-0.2327903326922616</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>-745.0663408002438</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>-8518617.724867728</v>
       </c>
     </row>
     <row r="4">
@@ -1444,55 +1444,55 @@
       <c r="BA4" t="n">
         <v>-0.4962406015037594</v>
       </c>
-      <c r="BB4" t="n">
-        <v>1.413492063492065</v>
-      </c>
+      <c r="BB4" t="inlineStr"/>
       <c r="BC4" t="n">
-        <v>-1.269674846996836</v>
+        <v>-35608706.77471393</v>
       </c>
       <c r="BD4" t="n">
-        <v>2.26281602384546</v>
+        <v>-13.03375614753324</v>
       </c>
       <c r="BE4" t="inlineStr"/>
       <c r="BF4" t="n">
+        <v>-9.58879825884469</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>1.413492063492065</v>
+      </c>
+      <c r="BH4" t="inlineStr"/>
+      <c r="BI4" t="inlineStr"/>
+      <c r="BJ4" t="inlineStr"/>
+      <c r="BK4" t="n">
+        <v>-60084.00234812773</v>
+      </c>
+      <c r="BL4" t="n">
         <v>-2.103174603174603</v>
       </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
-      <c r="BI4" t="n">
+      <c r="BM4" t="n">
         <v>-11.15925925925927</v>
       </c>
-      <c r="BJ4" t="n">
-        <v>-35608706.77471393</v>
-      </c>
-      <c r="BK4" t="inlineStr"/>
-      <c r="BL4" t="n">
-        <v>-9.58879825884469</v>
-      </c>
-      <c r="BM4" t="inlineStr"/>
-      <c r="BN4" t="n">
-        <v>-13.03375614753324</v>
-      </c>
-      <c r="BO4" t="inlineStr"/>
-      <c r="BP4" t="inlineStr"/>
+      <c r="BN4" t="inlineStr"/>
+      <c r="BO4" t="n">
+        <v>-44083376.32275132</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>-1.269674846996836</v>
+      </c>
       <c r="BQ4" t="n">
-        <v>1.554034391534373</v>
+        <v>-60115.34391534392</v>
       </c>
       <c r="BR4" t="inlineStr"/>
       <c r="BS4" t="n">
-        <v>-60115.34391534392</v>
+        <v>-1.64404941463765</v>
       </c>
       <c r="BT4" t="n">
+        <v>1.554034391534373</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>2.26281602384546</v>
+      </c>
+      <c r="BV4" t="inlineStr"/>
+      <c r="BW4" t="n">
         <v>-12.04616402116402</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>-1.64404941463765</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>-60084.00234812773</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>-44083376.32275132</v>
       </c>
     </row>
     <row r="5">
@@ -1679,55 +1679,55 @@
       <c r="BA5" t="n">
         <v>-0.5215311004784688</v>
       </c>
-      <c r="BB5" t="n">
-        <v>0.5737734487734514</v>
-      </c>
+      <c r="BB5" t="inlineStr"/>
       <c r="BC5" t="n">
-        <v>0.036196368152698</v>
+        <v>-35965204.17881285</v>
       </c>
       <c r="BD5" t="n">
-        <v>5.558781945619302</v>
+        <v>-10.36053935546897</v>
       </c>
       <c r="BE5" t="inlineStr"/>
       <c r="BF5" t="n">
+        <v>-8.074303983433765</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>0.5737734487734514</v>
+      </c>
+      <c r="BH5" t="inlineStr"/>
+      <c r="BI5" t="inlineStr"/>
+      <c r="BJ5" t="inlineStr"/>
+      <c r="BK5" t="n">
+        <v>-62985.35329047366</v>
+      </c>
+      <c r="BL5" t="n">
         <v>-1.96948051948052</v>
       </c>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
-      <c r="BI5" t="n">
+      <c r="BM5" t="n">
         <v>-9.332287157287141</v>
       </c>
-      <c r="BJ5" t="n">
-        <v>-35965204.17881285</v>
-      </c>
-      <c r="BK5" t="inlineStr"/>
-      <c r="BL5" t="n">
-        <v>-8.074303983433765</v>
-      </c>
-      <c r="BM5" t="inlineStr"/>
-      <c r="BN5" t="n">
-        <v>-10.36053935546897</v>
-      </c>
-      <c r="BO5" t="inlineStr"/>
-      <c r="BP5" t="inlineStr"/>
+      <c r="BN5" t="inlineStr"/>
+      <c r="BO5" t="n">
+        <v>-44258798.7012987</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>0.036196368152698</v>
+      </c>
       <c r="BQ5" t="n">
-        <v>-0.5766233766233881</v>
+        <v>-75975.97402597402</v>
       </c>
       <c r="BR5" t="inlineStr"/>
       <c r="BS5" t="n">
-        <v>-75975.97402597402</v>
+        <v>-1.302458351761757</v>
       </c>
       <c r="BT5" t="n">
+        <v>-0.5766233766233881</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>5.558781945619302</v>
+      </c>
+      <c r="BV5" t="inlineStr"/>
+      <c r="BW5" t="n">
         <v>-9.125541125541147</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>-1.302458351761757</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>-62985.35329047366</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>-44258798.7012987</v>
       </c>
     </row>
     <row r="6">
@@ -1908,55 +1908,55 @@
       <c r="BA6" t="n">
         <v>0.03421052631578947</v>
       </c>
-      <c r="BB6" t="n">
-        <v>-1.780645743145744</v>
-      </c>
+      <c r="BB6" t="inlineStr"/>
       <c r="BC6" t="n">
-        <v>-1.372187889613933</v>
+        <v>8521587.598109595</v>
       </c>
       <c r="BD6" t="n">
-        <v>-0.2101177179491174</v>
+        <v>5.319130388789588</v>
       </c>
       <c r="BE6" t="inlineStr"/>
       <c r="BF6" t="n">
+        <v>5.660592976182215</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>-1.780645743145744</v>
+      </c>
+      <c r="BH6" t="inlineStr"/>
+      <c r="BI6" t="inlineStr"/>
+      <c r="BJ6" t="inlineStr"/>
+      <c r="BK6" t="n">
+        <v>8477.515033820197</v>
+      </c>
+      <c r="BL6" t="n">
         <v>0.4522727272727276</v>
       </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
-      <c r="BI6" t="n">
+      <c r="BM6" t="n">
         <v>6.224891774891788</v>
       </c>
-      <c r="BJ6" t="n">
-        <v>8521587.598109595</v>
-      </c>
-      <c r="BK6" t="inlineStr"/>
-      <c r="BL6" t="n">
-        <v>5.660592976182215</v>
-      </c>
-      <c r="BM6" t="inlineStr"/>
-      <c r="BN6" t="n">
-        <v>5.319130388789588</v>
-      </c>
-      <c r="BO6" t="inlineStr"/>
-      <c r="BP6" t="inlineStr"/>
+      <c r="BN6" t="inlineStr"/>
+      <c r="BO6" t="n">
+        <v>11752938.76262626</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>-1.372187889613933</v>
+      </c>
       <c r="BQ6" t="n">
-        <v>0.08535353535347667</v>
+        <v>10737.82467532467</v>
       </c>
       <c r="BR6" t="inlineStr"/>
       <c r="BS6" t="n">
-        <v>10737.82467532467</v>
+        <v>0.4824062998405105</v>
       </c>
       <c r="BT6" t="n">
+        <v>0.08535353535347667</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>-0.2101177179491174</v>
+      </c>
+      <c r="BV6" t="inlineStr"/>
+      <c r="BW6" t="n">
         <v>7.13140331890331</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>0.4824062998405105</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>8477.515033820197</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>11752938.76262626</v>
       </c>
     </row>
     <row r="7">
@@ -2137,55 +2137,55 @@
       <c r="BA7" t="n">
         <v>0.1052631578947368</v>
       </c>
-      <c r="BB7" t="n">
-        <v>-0.9236652236652212</v>
-      </c>
+      <c r="BB7" t="inlineStr"/>
       <c r="BC7" t="n">
-        <v>-1.482267460760042</v>
+        <v>17961559.22970048</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.299669782967612</v>
+        <v>4.338213140120487</v>
       </c>
       <c r="BE7" t="inlineStr"/>
       <c r="BF7" t="n">
+        <v>5.514369023387729</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>-0.9236652236652212</v>
+      </c>
+      <c r="BH7" t="inlineStr"/>
+      <c r="BI7" t="inlineStr"/>
+      <c r="BJ7" t="inlineStr"/>
+      <c r="BK7" t="n">
+        <v>28413.4005773333</v>
+      </c>
+      <c r="BL7" t="n">
         <v>0.6209595959595957</v>
       </c>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
-      <c r="BI7" t="n">
+      <c r="BM7" t="n">
         <v>4.397438672438668</v>
       </c>
-      <c r="BJ7" t="n">
-        <v>17961559.22970048</v>
-      </c>
-      <c r="BK7" t="inlineStr"/>
-      <c r="BL7" t="n">
-        <v>5.514369023387729</v>
-      </c>
-      <c r="BM7" t="inlineStr"/>
-      <c r="BN7" t="n">
-        <v>4.338213140120487</v>
-      </c>
-      <c r="BO7" t="inlineStr"/>
-      <c r="BP7" t="inlineStr"/>
+      <c r="BN7" t="inlineStr"/>
+      <c r="BO7" t="n">
+        <v>20203881.67388167</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>-1.482267460760042</v>
+      </c>
       <c r="BQ7" t="n">
-        <v>-0.3420634920634598</v>
+        <v>30769.01154401154</v>
       </c>
       <c r="BR7" t="inlineStr"/>
       <c r="BS7" t="n">
-        <v>30769.01154401154</v>
+        <v>0.5729332121864767</v>
       </c>
       <c r="BT7" t="n">
+        <v>-0.3420634920634598</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>1.299669782967612</v>
+      </c>
+      <c r="BV7" t="inlineStr"/>
+      <c r="BW7" t="n">
         <v>5.396933621933655</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>0.5729332121864767</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>28413.4005773333</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>20203881.67388167</v>
       </c>
     </row>
     <row r="8">
@@ -2368,55 +2368,55 @@
       <c r="BA8" t="n">
         <v>-0.1578947368421053</v>
       </c>
-      <c r="BB8" t="n">
-        <v>-0.8511904761904745</v>
-      </c>
+      <c r="BB8" t="inlineStr"/>
       <c r="BC8" t="n">
-        <v>-0.1317902349900528</v>
+        <v>-17554024.68847604</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.1123695709474362</v>
+        <v>-5.304871251947134</v>
       </c>
       <c r="BE8" t="inlineStr"/>
       <c r="BF8" t="n">
+        <v>-6.333913909506691</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>-0.8511904761904745</v>
+      </c>
+      <c r="BH8" t="inlineStr"/>
+      <c r="BI8" t="inlineStr"/>
+      <c r="BJ8" t="inlineStr"/>
+      <c r="BK8" t="n">
+        <v>-22438.55046317812</v>
+      </c>
+      <c r="BL8" t="n">
         <v>-1.486688311688312</v>
       </c>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
-      <c r="BI8" t="n">
+      <c r="BM8" t="n">
         <v>-8.274783549783535</v>
       </c>
-      <c r="BJ8" t="n">
-        <v>-17554024.68847604</v>
-      </c>
-      <c r="BK8" t="inlineStr"/>
-      <c r="BL8" t="n">
-        <v>-6.333913909506691</v>
-      </c>
-      <c r="BM8" t="inlineStr"/>
-      <c r="BN8" t="n">
-        <v>-5.304871251947134</v>
-      </c>
-      <c r="BO8" t="inlineStr"/>
-      <c r="BP8" t="inlineStr"/>
+      <c r="BN8" t="inlineStr"/>
+      <c r="BO8" t="n">
+        <v>-32149350.64935065</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>-0.1317902349900528</v>
+      </c>
       <c r="BQ8" t="n">
-        <v>-1.019372294372317</v>
+        <v>-35674.5670995671</v>
       </c>
       <c r="BR8" t="inlineStr"/>
       <c r="BS8" t="n">
-        <v>-35674.5670995671</v>
+        <v>-0.7392015370047886</v>
       </c>
       <c r="BT8" t="n">
+        <v>-1.019372294372317</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>0.1123695709474362</v>
+      </c>
+      <c r="BV8" t="inlineStr"/>
+      <c r="BW8" t="n">
         <v>-7.20930735930736</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>-0.7392015370047886</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>-22438.55046317812</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>-32149350.64935065</v>
       </c>
     </row>
     <row r="9">
@@ -2597,55 +2597,55 @@
       <c r="BA9" t="n">
         <v>-0.1052631578947368</v>
       </c>
-      <c r="BB9" t="n">
-        <v>2.060930735930739</v>
-      </c>
+      <c r="BB9" t="inlineStr"/>
       <c r="BC9" t="n">
-        <v>0.8669854225581766</v>
+        <v>-6073651.279491061</v>
       </c>
       <c r="BD9" t="n">
-        <v>-0.2216020778327277</v>
+        <v>-4.752368555077524</v>
       </c>
       <c r="BE9" t="inlineStr"/>
       <c r="BF9" t="n">
+        <v>-6.237617048414265</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>2.060930735930739</v>
+      </c>
+      <c r="BH9" t="inlineStr"/>
+      <c r="BI9" t="inlineStr"/>
+      <c r="BJ9" t="inlineStr"/>
+      <c r="BK9" t="n">
+        <v>-16294.13797416893</v>
+      </c>
+      <c r="BL9" t="n">
         <v>-0.4189814814814812</v>
       </c>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
-      <c r="BI9" t="n">
+      <c r="BM9" t="n">
         <v>-4.656331168831159</v>
       </c>
-      <c r="BJ9" t="n">
-        <v>-6073651.279491061</v>
-      </c>
-      <c r="BK9" t="inlineStr"/>
-      <c r="BL9" t="n">
-        <v>-6.237617048414265</v>
-      </c>
-      <c r="BM9" t="inlineStr"/>
-      <c r="BN9" t="n">
-        <v>-4.752368555077524</v>
-      </c>
-      <c r="BO9" t="inlineStr"/>
-      <c r="BP9" t="inlineStr"/>
+      <c r="BN9" t="inlineStr"/>
+      <c r="BO9" t="n">
+        <v>-7946945.045695045</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>0.8669854225581766</v>
+      </c>
       <c r="BQ9" t="n">
-        <v>0.6108585858585798</v>
+        <v>-19158.24314574314</v>
       </c>
       <c r="BR9" t="inlineStr"/>
       <c r="BS9" t="n">
-        <v>-19158.24314574314</v>
+        <v>-0.3637180629827685</v>
       </c>
       <c r="BT9" t="n">
+        <v>0.6108585858585798</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>-0.2216020778327277</v>
+      </c>
+      <c r="BV9" t="inlineStr"/>
+      <c r="BW9" t="n">
         <v>-6.325132275132262</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>-0.3637180629827685</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>-16294.13797416893</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>-7946945.045695045</v>
       </c>
     </row>
     <row r="10">
@@ -2826,55 +2826,55 @@
       <c r="BA10" t="n">
         <v>0.2078947368421053</v>
       </c>
-      <c r="BB10" t="n">
-        <v>1.438095238095237</v>
-      </c>
+      <c r="BB10" t="inlineStr"/>
       <c r="BC10" t="n">
-        <v>0.05780232625606985</v>
+        <v>-2704651.024441398</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.1750488587363179</v>
+        <v>-2.233149432021619</v>
       </c>
       <c r="BE10" t="inlineStr"/>
       <c r="BF10" t="n">
+        <v>-0.6020139281008596</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>1.438095238095237</v>
+      </c>
+      <c r="BH10" t="inlineStr"/>
+      <c r="BI10" t="inlineStr"/>
+      <c r="BJ10" t="inlineStr"/>
+      <c r="BK10" t="n">
+        <v>-888.0110354938734</v>
+      </c>
+      <c r="BL10" t="n">
         <v>-0.07619047619047636</v>
       </c>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
-      <c r="BI10" t="n">
+      <c r="BM10" t="n">
         <v>-0.6619047619047649</v>
       </c>
-      <c r="BJ10" t="n">
-        <v>-2704651.024441398</v>
-      </c>
-      <c r="BK10" t="inlineStr"/>
-      <c r="BL10" t="n">
-        <v>-0.6020139281008596</v>
-      </c>
-      <c r="BM10" t="inlineStr"/>
-      <c r="BN10" t="n">
-        <v>-2.233149432021619</v>
-      </c>
-      <c r="BO10" t="inlineStr"/>
-      <c r="BP10" t="inlineStr"/>
+      <c r="BN10" t="inlineStr"/>
+      <c r="BO10" t="n">
+        <v>-1748888.888888889</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>0.05780232625606985</v>
+      </c>
       <c r="BQ10" t="n">
-        <v>-1.541269841269838</v>
+        <v>846.0317460317456</v>
       </c>
       <c r="BR10" t="inlineStr"/>
       <c r="BS10" t="n">
-        <v>846.0317460317456</v>
+        <v>-0.0715763151526474</v>
       </c>
       <c r="BT10" t="n">
+        <v>-1.541269841269838</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>0.1750488587363179</v>
+      </c>
+      <c r="BV10" t="inlineStr"/>
+      <c r="BW10" t="n">
         <v>-0.9492063492063494</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>-0.0715763151526474</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>-888.0110354938734</v>
-      </c>
-      <c r="BW10" t="n">
-        <v>-1748888.888888889</v>
       </c>
     </row>
     <row r="11">
@@ -3061,55 +3061,55 @@
       <c r="BA11" t="n">
         <v>0.2631578947368421</v>
       </c>
-      <c r="BB11" t="n">
-        <v>-2.272186147186151</v>
-      </c>
+      <c r="BB11" t="inlineStr"/>
       <c r="BC11" t="n">
-        <v>0.106372732852936</v>
+        <v>4389194.218808111</v>
       </c>
       <c r="BD11" t="n">
-        <v>-1.446541507179148</v>
+        <v>2.604569662966767</v>
       </c>
       <c r="BE11" t="inlineStr"/>
       <c r="BF11" t="n">
+        <v>1.692275103301171</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>-2.272186147186151</v>
+      </c>
+      <c r="BH11" t="inlineStr"/>
+      <c r="BI11" t="inlineStr"/>
+      <c r="BJ11" t="inlineStr"/>
+      <c r="BK11" t="n">
+        <v>13149.49101893028</v>
+      </c>
+      <c r="BL11" t="n">
         <v>0.3241762866762863</v>
       </c>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
-      <c r="BI11" t="n">
+      <c r="BM11" t="n">
         <v>0.8622474747474485</v>
       </c>
-      <c r="BJ11" t="n">
-        <v>4389194.218808111</v>
-      </c>
-      <c r="BK11" t="inlineStr"/>
-      <c r="BL11" t="n">
-        <v>1.692275103301171</v>
-      </c>
-      <c r="BM11" t="inlineStr"/>
-      <c r="BN11" t="n">
-        <v>2.604569662966767</v>
-      </c>
-      <c r="BO11" t="inlineStr"/>
-      <c r="BP11" t="inlineStr"/>
+      <c r="BN11" t="inlineStr"/>
+      <c r="BO11" t="n">
+        <v>4270538.119288119</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>0.106372732852936</v>
+      </c>
       <c r="BQ11" t="n">
-        <v>0.9278138528138697</v>
+        <v>12724.18831168831</v>
       </c>
       <c r="BR11" t="inlineStr"/>
       <c r="BS11" t="n">
-        <v>12724.18831168831</v>
+        <v>0.3637180629827685</v>
       </c>
       <c r="BT11" t="n">
+        <v>0.9278138528138697</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>-1.446541507179148</v>
+      </c>
+      <c r="BV11" t="inlineStr"/>
+      <c r="BW11" t="n">
         <v>3.104641654641654</v>
-      </c>
-      <c r="BU11" t="n">
-        <v>0.3637180629827685</v>
-      </c>
-      <c r="BV11" t="n">
-        <v>13149.49101893028</v>
-      </c>
-      <c r="BW11" t="n">
-        <v>4270538.119288119</v>
       </c>
     </row>
     <row r="12">
@@ -3290,55 +3290,55 @@
       <c r="BA12" t="n">
         <v>0.4736842105263158</v>
       </c>
-      <c r="BB12" t="n">
-        <v>-0.315981240981241</v>
-      </c>
+      <c r="BB12" t="inlineStr"/>
       <c r="BC12" t="n">
-        <v>-0.7698775925320547</v>
+        <v>-2342168.257081627</v>
       </c>
       <c r="BD12" t="n">
-        <v>2.086570982321206</v>
+        <v>-4.851261175713603</v>
       </c>
       <c r="BE12" t="inlineStr"/>
       <c r="BF12" t="n">
+        <v>-3.383567355241112</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>-0.315981240981241</v>
+      </c>
+      <c r="BH12" t="inlineStr"/>
+      <c r="BI12" t="inlineStr"/>
+      <c r="BJ12" t="inlineStr"/>
+      <c r="BK12" t="n">
+        <v>-9312.095456031384</v>
+      </c>
+      <c r="BL12" t="n">
         <v>-0.4131313131313132</v>
       </c>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
-      <c r="BI12" t="n">
+      <c r="BM12" t="n">
         <v>-4.945165945165954</v>
       </c>
-      <c r="BJ12" t="n">
-        <v>-2342168.257081627</v>
-      </c>
-      <c r="BK12" t="inlineStr"/>
-      <c r="BL12" t="n">
-        <v>-3.383567355241112</v>
-      </c>
-      <c r="BM12" t="inlineStr"/>
-      <c r="BN12" t="n">
-        <v>-4.851261175713603</v>
-      </c>
-      <c r="BO12" t="inlineStr"/>
-      <c r="BP12" t="inlineStr"/>
+      <c r="BN12" t="inlineStr"/>
+      <c r="BO12" t="n">
+        <v>-4655847.763347763</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>-0.7698775925320547</v>
+      </c>
       <c r="BQ12" t="n">
-        <v>-0.7374458874458583</v>
+        <v>-11036.97691197692</v>
       </c>
       <c r="BR12" t="inlineStr"/>
       <c r="BS12" t="n">
-        <v>-11036.97691197692</v>
+        <v>-0.1591245193729667</v>
       </c>
       <c r="BT12" t="n">
+        <v>-0.7374458874458583</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>2.086570982321206</v>
+      </c>
+      <c r="BV12" t="inlineStr"/>
+      <c r="BW12" t="n">
         <v>-5.185209235209228</v>
-      </c>
-      <c r="BU12" t="n">
-        <v>-0.1591245193729667</v>
-      </c>
-      <c r="BV12" t="n">
-        <v>-9312.095456031384</v>
-      </c>
-      <c r="BW12" t="n">
-        <v>-4655847.763347763</v>
       </c>
     </row>
     <row r="13">
@@ -3521,55 +3521,55 @@
       <c r="BA13" t="n">
         <v>-0.1394736842105263</v>
       </c>
-      <c r="BB13" t="n">
-        <v>2.037896825396825</v>
-      </c>
+      <c r="BB13" t="inlineStr"/>
       <c r="BC13" t="n">
-        <v>2.443650318979273</v>
+        <v>27052256.89789012</v>
       </c>
       <c r="BD13" t="n">
-        <v>-1.341587495322017</v>
+        <v>7.887532947788358</v>
       </c>
       <c r="BE13" t="inlineStr"/>
       <c r="BF13" t="n">
+        <v>5.721760905932726</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>2.037896825396825</v>
+      </c>
+      <c r="BH13" t="inlineStr"/>
+      <c r="BI13" t="inlineStr"/>
+      <c r="BJ13" t="inlineStr"/>
+      <c r="BK13" t="n">
+        <v>51066.93250276842</v>
+      </c>
+      <c r="BL13" t="n">
         <v>1.650901875901876</v>
       </c>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
-      <c r="BI13" t="n">
+      <c r="BM13" t="n">
         <v>6.678282828282832</v>
       </c>
-      <c r="BJ13" t="n">
-        <v>27052256.89789012</v>
-      </c>
-      <c r="BK13" t="inlineStr"/>
-      <c r="BL13" t="n">
-        <v>5.721760905932726</v>
-      </c>
-      <c r="BM13" t="inlineStr"/>
-      <c r="BN13" t="n">
-        <v>7.887532947788358</v>
-      </c>
-      <c r="BO13" t="inlineStr"/>
-      <c r="BP13" t="inlineStr"/>
+      <c r="BN13" t="inlineStr"/>
+      <c r="BO13" t="n">
+        <v>32626361.38167388</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>2.443650318979273</v>
+      </c>
       <c r="BQ13" t="n">
-        <v>-1.980086580086549</v>
+        <v>49744.17388167389</v>
       </c>
       <c r="BR13" t="inlineStr"/>
       <c r="BS13" t="n">
-        <v>49744.17388167389</v>
+        <v>1.161643114797139</v>
       </c>
       <c r="BT13" t="n">
+        <v>-1.980086580086549</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>-1.341587495322017</v>
+      </c>
+      <c r="BV13" t="inlineStr"/>
+      <c r="BW13" t="n">
         <v>6.145869408369407</v>
-      </c>
-      <c r="BU13" t="n">
-        <v>1.161643114797139</v>
-      </c>
-      <c r="BV13" t="n">
-        <v>51066.93250276842</v>
-      </c>
-      <c r="BW13" t="n">
-        <v>32626361.38167388</v>
       </c>
     </row>
     <row r="14">
@@ -3752,55 +3752,55 @@
       <c r="BA14" t="n">
         <v>-0.1052631578947368</v>
       </c>
-      <c r="BB14" t="n">
-        <v>1.688744588744587</v>
-      </c>
+      <c r="BB14" t="inlineStr"/>
       <c r="BC14" t="n">
-        <v>0.3826716332465985</v>
+        <v>-21443429.20142539</v>
       </c>
       <c r="BD14" t="n">
-        <v>-1.017602248235818</v>
+        <v>-7.291088835853316</v>
       </c>
       <c r="BE14" t="inlineStr"/>
       <c r="BF14" t="n">
+        <v>-5.560772793966038</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>1.688744588744587</v>
+      </c>
+      <c r="BH14" t="inlineStr"/>
+      <c r="BI14" t="inlineStr"/>
+      <c r="BJ14" t="inlineStr"/>
+      <c r="BK14" t="n">
+        <v>-31001.96798682258</v>
+      </c>
+      <c r="BL14" t="n">
         <v>-0.830880230880231</v>
       </c>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
-      <c r="BI14" t="n">
+      <c r="BM14" t="n">
         <v>-5.724819624819631</v>
       </c>
-      <c r="BJ14" t="n">
-        <v>-21443429.20142539</v>
-      </c>
-      <c r="BK14" t="inlineStr"/>
-      <c r="BL14" t="n">
-        <v>-5.560772793966038</v>
-      </c>
-      <c r="BM14" t="inlineStr"/>
-      <c r="BN14" t="n">
-        <v>-7.291088835853316</v>
-      </c>
-      <c r="BO14" t="inlineStr"/>
-      <c r="BP14" t="inlineStr"/>
+      <c r="BN14" t="inlineStr"/>
+      <c r="BO14" t="n">
+        <v>-24401818.18181818</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>0.3826716332465985</v>
+      </c>
       <c r="BQ14" t="n">
-        <v>-0.07936507936506132</v>
+        <v>-31845.59884559884</v>
       </c>
       <c r="BR14" t="inlineStr"/>
       <c r="BS14" t="n">
-        <v>-31845.59884559884</v>
+        <v>-0.829649395643425</v>
       </c>
       <c r="BT14" t="n">
+        <v>-0.07936507936506132</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>-1.017602248235818</v>
+      </c>
+      <c r="BV14" t="inlineStr"/>
+      <c r="BW14" t="n">
         <v>-7.115584415584422</v>
-      </c>
-      <c r="BU14" t="n">
-        <v>-0.829649395643425</v>
-      </c>
-      <c r="BV14" t="n">
-        <v>-31001.96798682258</v>
-      </c>
-      <c r="BW14" t="n">
-        <v>-24401818.18181818</v>
       </c>
     </row>
     <row r="15">
@@ -3983,55 +3983,55 @@
       <c r="BA15" t="n">
         <v>0.2857142857142857</v>
       </c>
-      <c r="BB15" t="n">
-        <v>-0.8134920634920597</v>
-      </c>
+      <c r="BB15" t="inlineStr"/>
       <c r="BC15" t="n">
-        <v>-1.143217502925591</v>
+        <v>3848001.752657878</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.4682563443731169</v>
+        <v>2.777769191347247</v>
       </c>
       <c r="BE15" t="inlineStr"/>
       <c r="BF15" t="n">
+        <v>3.315877120078795</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>-0.8134920634920597</v>
+      </c>
+      <c r="BH15" t="inlineStr"/>
+      <c r="BI15" t="inlineStr"/>
+      <c r="BJ15" t="inlineStr"/>
+      <c r="BK15" t="n">
+        <v>8893.810533660157</v>
+      </c>
+      <c r="BL15" t="n">
         <v>0.6412698412698414</v>
       </c>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
-      <c r="BI15" t="n">
+      <c r="BM15" t="n">
         <v>3.12433862433862</v>
       </c>
-      <c r="BJ15" t="n">
-        <v>3848001.752657878</v>
-      </c>
-      <c r="BK15" t="inlineStr"/>
-      <c r="BL15" t="n">
-        <v>3.315877120078795</v>
-      </c>
-      <c r="BM15" t="inlineStr"/>
-      <c r="BN15" t="n">
-        <v>2.777769191347247</v>
-      </c>
-      <c r="BO15" t="inlineStr"/>
-      <c r="BP15" t="inlineStr"/>
+      <c r="BN15" t="inlineStr"/>
+      <c r="BO15" t="n">
+        <v>5205162.037037037</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>-1.143217502925591</v>
+      </c>
       <c r="BQ15" t="n">
-        <v>0.7919973544973686</v>
+        <v>13013.75661375661</v>
       </c>
       <c r="BR15" t="inlineStr"/>
       <c r="BS15" t="n">
-        <v>13013.75661375661</v>
+        <v>0.2187015156939971</v>
       </c>
       <c r="BT15" t="n">
+        <v>0.7919973544973686</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>0.4682563443731169</v>
+      </c>
+      <c r="BV15" t="inlineStr"/>
+      <c r="BW15" t="n">
         <v>4.582671957671963</v>
-      </c>
-      <c r="BU15" t="n">
-        <v>0.2187015156939971</v>
-      </c>
-      <c r="BV15" t="n">
-        <v>8893.810533660157</v>
-      </c>
-      <c r="BW15" t="n">
-        <v>5205162.037037037</v>
       </c>
     </row>
     <row r="16">
@@ -4212,55 +4212,55 @@
       <c r="BA16" t="n">
         <v>0.2105263157894737</v>
       </c>
-      <c r="BB16" t="n">
-        <v>0.9956349206349202</v>
-      </c>
+      <c r="BB16" t="inlineStr"/>
       <c r="BC16" t="n">
-        <v>1.97206561287576</v>
+        <v>1924586.889432981</v>
       </c>
       <c r="BD16" t="n">
-        <v>-0.8271844172104466</v>
+        <v>1.671632664229946</v>
       </c>
       <c r="BE16" t="inlineStr"/>
       <c r="BF16" t="n">
+        <v>0.2612278182197372</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>0.9956349206349202</v>
+      </c>
+      <c r="BH16" t="inlineStr"/>
+      <c r="BI16" t="inlineStr"/>
+      <c r="BJ16" t="inlineStr"/>
+      <c r="BK16" t="n">
+        <v>2784.877743830351</v>
+      </c>
+      <c r="BL16" t="n">
         <v>0.4944444444444447</v>
       </c>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
-      <c r="BI16" t="n">
+      <c r="BM16" t="n">
         <v>2.44285714285715</v>
       </c>
-      <c r="BJ16" t="n">
-        <v>1924586.889432981</v>
-      </c>
-      <c r="BK16" t="inlineStr"/>
-      <c r="BL16" t="n">
-        <v>0.2612278182197372</v>
-      </c>
-      <c r="BM16" t="inlineStr"/>
-      <c r="BN16" t="n">
-        <v>1.671632664229946</v>
-      </c>
-      <c r="BO16" t="inlineStr"/>
-      <c r="BP16" t="inlineStr"/>
+      <c r="BN16" t="inlineStr"/>
+      <c r="BO16" t="n">
+        <v>5381904.761904763</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>1.97206561287576</v>
+      </c>
       <c r="BQ16" t="n">
-        <v>-1.275793650793673</v>
+        <v>4045.238095238095</v>
       </c>
       <c r="BR16" t="inlineStr"/>
       <c r="BS16" t="n">
-        <v>4045.238095238095</v>
+        <v>0.2290413256350314</v>
       </c>
       <c r="BT16" t="n">
+        <v>-1.275793650793673</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>-0.8271844172104466</v>
+      </c>
+      <c r="BV16" t="inlineStr"/>
+      <c r="BW16" t="n">
         <v>1.767063492063471</v>
-      </c>
-      <c r="BU16" t="n">
-        <v>0.2290413256350314</v>
-      </c>
-      <c r="BV16" t="n">
-        <v>2784.877743830351</v>
-      </c>
-      <c r="BW16" t="n">
-        <v>5381904.761904763</v>
       </c>
     </row>
     <row r="17">
@@ -4441,55 +4441,55 @@
       <c r="BA17" t="n">
         <v>0.4162679425837321</v>
       </c>
-      <c r="BB17" t="n">
-        <v>1.878968253968257</v>
-      </c>
+      <c r="BB17" t="inlineStr"/>
       <c r="BC17" t="n">
-        <v>1.958551347173639</v>
+        <v>30585890.97509019</v>
       </c>
       <c r="BD17" t="n">
-        <v>-3.998030759353213</v>
+        <v>8.058965356477515</v>
       </c>
       <c r="BE17" t="inlineStr"/>
       <c r="BF17" t="n">
+        <v>3.648078481791458</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>1.878968253968257</v>
+      </c>
+      <c r="BH17" t="inlineStr"/>
+      <c r="BI17" t="inlineStr"/>
+      <c r="BJ17" t="inlineStr"/>
+      <c r="BK17" t="n">
+        <v>56512.5458955512</v>
+      </c>
+      <c r="BL17" t="n">
         <v>1.392989417989418</v>
       </c>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
-      <c r="BI17" t="n">
+      <c r="BM17" t="n">
         <v>7.041798941798945</v>
       </c>
-      <c r="BJ17" t="n">
-        <v>30585890.97509019</v>
-      </c>
-      <c r="BK17" t="inlineStr"/>
-      <c r="BL17" t="n">
-        <v>3.648078481791458</v>
-      </c>
-      <c r="BM17" t="inlineStr"/>
-      <c r="BN17" t="n">
-        <v>8.058965356477515</v>
-      </c>
-      <c r="BO17" t="inlineStr"/>
-      <c r="BP17" t="inlineStr"/>
+      <c r="BN17" t="inlineStr"/>
+      <c r="BO17" t="n">
+        <v>35172056.87830687</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>1.958551347173639</v>
+      </c>
       <c r="BQ17" t="n">
-        <v>-0.9808201058201576</v>
+        <v>65045.76719576719</v>
       </c>
       <c r="BR17" t="inlineStr"/>
       <c r="BS17" t="n">
-        <v>65045.76719576719</v>
+        <v>0.9105434996965289</v>
       </c>
       <c r="BT17" t="n">
+        <v>-0.9808201058201576</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>-3.998030759353213</v>
+      </c>
+      <c r="BV17" t="inlineStr"/>
+      <c r="BW17" t="n">
         <v>4.233862433862456</v>
-      </c>
-      <c r="BU17" t="n">
-        <v>0.9105434996965289</v>
-      </c>
-      <c r="BV17" t="n">
-        <v>56512.5458955512</v>
-      </c>
-      <c r="BW17" t="n">
-        <v>35172056.87830687</v>
       </c>
     </row>
     <row r="18">
@@ -4670,55 +4670,55 @@
       <c r="BA18" t="n">
         <v>-0.1552631578947369</v>
       </c>
-      <c r="BB18" t="n">
-        <v>-0.6999999999999957</v>
-      </c>
+      <c r="BB18" t="inlineStr"/>
       <c r="BC18" t="n">
-        <v>-0.1577336197636967</v>
+        <v>3920842.284282134</v>
       </c>
       <c r="BD18" t="n">
-        <v>-1.614087236725283</v>
+        <v>3.971006709319894</v>
       </c>
       <c r="BE18" t="inlineStr"/>
       <c r="BF18" t="n">
+        <v>5.012450380609906</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>-0.6999999999999957</v>
+      </c>
+      <c r="BH18" t="inlineStr"/>
+      <c r="BI18" t="inlineStr"/>
+      <c r="BJ18" t="inlineStr"/>
+      <c r="BK18" t="n">
+        <v>2418.483320101499</v>
+      </c>
+      <c r="BL18" t="n">
         <v>0.4714285714285715</v>
       </c>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
-      <c r="BI18" t="n">
+      <c r="BM18" t="n">
         <v>2.957142857142856</v>
       </c>
-      <c r="BJ18" t="n">
-        <v>3920842.284282134</v>
-      </c>
-      <c r="BK18" t="inlineStr"/>
-      <c r="BL18" t="n">
-        <v>5.012450380609906</v>
-      </c>
-      <c r="BM18" t="inlineStr"/>
-      <c r="BN18" t="n">
-        <v>3.971006709319894</v>
-      </c>
-      <c r="BO18" t="inlineStr"/>
-      <c r="BP18" t="inlineStr"/>
+      <c r="BN18" t="inlineStr"/>
+      <c r="BO18" t="n">
+        <v>5112857.142857143</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>-0.1577336197636967</v>
+      </c>
       <c r="BQ18" t="n">
-        <v>-2.371428571428538</v>
+        <v>2285.714285714286</v>
       </c>
       <c r="BR18" t="inlineStr"/>
       <c r="BS18" t="n">
-        <v>2285.714285714286</v>
+        <v>0.1651216550693504</v>
       </c>
       <c r="BT18" t="n">
+        <v>-2.371428571428538</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>-1.614087236725283</v>
+      </c>
+      <c r="BV18" t="inlineStr"/>
+      <c r="BW18" t="n">
         <v>3.600000000000009</v>
-      </c>
-      <c r="BU18" t="n">
-        <v>0.1651216550693504</v>
-      </c>
-      <c r="BV18" t="n">
-        <v>2418.483320101499</v>
-      </c>
-      <c r="BW18" t="n">
-        <v>5112857.142857143</v>
       </c>
     </row>
     <row r="19">
@@ -4899,55 +4899,55 @@
       <c r="BA19" t="n">
         <v>0.1052631578947368</v>
       </c>
-      <c r="BB19" t="n">
-        <v>-0.1264069264069292</v>
-      </c>
+      <c r="BB19" t="inlineStr"/>
       <c r="BC19" t="n">
-        <v>-0.6286207236517818</v>
+        <v>20720545.86871847</v>
       </c>
       <c r="BD19" t="n">
-        <v>-0.5740564945207041</v>
+        <v>9.515824381205221</v>
       </c>
       <c r="BE19" t="inlineStr"/>
       <c r="BF19" t="n">
+        <v>10.91741088086299</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>-0.1264069264069292</v>
+      </c>
+      <c r="BH19" t="inlineStr"/>
+      <c r="BI19" t="inlineStr"/>
+      <c r="BJ19" t="inlineStr"/>
+      <c r="BK19" t="n">
+        <v>27557.42419289329</v>
+      </c>
+      <c r="BL19" t="n">
         <v>1.611688311688312</v>
       </c>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
-      <c r="BI19" t="n">
+      <c r="BM19" t="n">
         <v>11.34083694083692</v>
       </c>
-      <c r="BJ19" t="n">
-        <v>20720545.86871847</v>
-      </c>
-      <c r="BK19" t="inlineStr"/>
-      <c r="BL19" t="n">
-        <v>10.91741088086299</v>
-      </c>
-      <c r="BM19" t="inlineStr"/>
-      <c r="BN19" t="n">
-        <v>9.515824381205221</v>
-      </c>
-      <c r="BO19" t="inlineStr"/>
-      <c r="BP19" t="inlineStr"/>
+      <c r="BN19" t="inlineStr"/>
+      <c r="BO19" t="n">
+        <v>35161341.99134199</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>-0.6286207236517818</v>
+      </c>
       <c r="BQ19" t="n">
-        <v>0.741847041847052</v>
+        <v>40811.97691197691</v>
       </c>
       <c r="BR19" t="inlineStr"/>
       <c r="BS19" t="n">
-        <v>40811.97691197691</v>
+        <v>0.8976888154887501</v>
       </c>
       <c r="BT19" t="n">
+        <v>0.741847041847052</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>-0.5740564945207041</v>
+      </c>
+      <c r="BV19" t="inlineStr"/>
+      <c r="BW19" t="n">
         <v>10.55295815295815</v>
-      </c>
-      <c r="BU19" t="n">
-        <v>0.8976888154887501</v>
-      </c>
-      <c r="BV19" t="n">
-        <v>27557.42419289329</v>
-      </c>
-      <c r="BW19" t="n">
-        <v>35161341.99134199</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/data_preparation/df_constructed.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_constructed.xlsx
@@ -695,112 +695,112 @@
       </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_start</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_wage_player_miss</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
           <t>dif_sum_value_player_miss</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_value_player_sub</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_start</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_start</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="BJ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_wage_player_sub</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_start</t>
-        </is>
-      </c>
-      <c r="BM1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="BN1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_wage_player_miss</t>
-        </is>
-      </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_value_player_start</t>
-        </is>
-      </c>
-      <c r="BP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="BQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_start</t>
-        </is>
-      </c>
-      <c r="BR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="BS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="BT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="BU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="BV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="BW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
         </is>
       </c>
     </row>
@@ -984,55 +984,71 @@
       <c r="BA2" t="n">
         <v>0.1052631578947368</v>
       </c>
-      <c r="BB2" t="inlineStr"/>
+      <c r="BB2" t="n">
+        <v>5.238095238095241</v>
+      </c>
       <c r="BC2" t="n">
-        <v>-3473661.002921382</v>
+        <v>-8088.888888888891</v>
       </c>
       <c r="BD2" t="n">
-        <v>-1.680500682347684</v>
-      </c>
-      <c r="BE2" t="inlineStr"/>
+        <v>-112666.6666666667</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>-276.6666666666667</v>
+      </c>
       <c r="BF2" t="n">
-        <v>-5.339618715525873</v>
+        <v>-6.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>-0.7111111111111157</v>
-      </c>
-      <c r="BH2" t="inlineStr"/>
-      <c r="BI2" t="inlineStr"/>
-      <c r="BJ2" t="inlineStr"/>
+        <v>-0.9603174603174693</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>-5.485110723669081</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>-33687500</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>-290.6666666666667</v>
+      </c>
       <c r="BK2" t="n">
-        <v>-4129.83649600191</v>
+        <v>1.268518518518476</v>
       </c>
       <c r="BL2" t="n">
-        <v>-0.6269841269841272</v>
+        <v>-1.195498105166337</v>
       </c>
       <c r="BM2" t="n">
-        <v>-2.292063492063491</v>
-      </c>
-      <c r="BN2" t="inlineStr"/>
+        <v>-1.62483533713511</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>-0.1450068407734311</v>
+      </c>
       <c r="BO2" t="n">
-        <v>-4257777.777777778</v>
+        <v>-4.079629629629636</v>
       </c>
       <c r="BP2" t="n">
-        <v>1.525780548680189</v>
+        <v>-3372858.126596685</v>
       </c>
       <c r="BQ2" t="n">
-        <v>-7933.333333333336</v>
-      </c>
-      <c r="BR2" t="inlineStr"/>
+        <v>-0.6481481481481486</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>-2.440740740740736</v>
+      </c>
       <c r="BS2" t="n">
-        <v>-0.1814344349486554</v>
+        <v>-3.5</v>
       </c>
       <c r="BT2" t="n">
-        <v>1.173015873015856</v>
+        <v>1.597951702928821</v>
       </c>
       <c r="BU2" t="n">
-        <v>-1.073159866540124</v>
-      </c>
-      <c r="BV2" t="inlineStr"/>
+        <v>-0.6962962962963033</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>-4112.345477219616</v>
+      </c>
       <c r="BW2" t="n">
-        <v>-3.839682539682542</v>
+        <v>-4439074.074074075</v>
       </c>
     </row>
     <row r="3">
@@ -1213,55 +1229,71 @@
       <c r="BA3" t="n">
         <v>-0.1052631578947368</v>
       </c>
-      <c r="BB3" t="inlineStr"/>
+      <c r="BB3" t="n">
+        <v>0.9999999999999716</v>
+      </c>
       <c r="BC3" t="n">
-        <v>-4668033.640236486</v>
+        <v>-7198.821548821546</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.3235654070240486</v>
-      </c>
-      <c r="BE3" t="inlineStr"/>
+        <v>72000</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>85.66666666666667</v>
+      </c>
       <c r="BF3" t="n">
-        <v>-4.969929552848782</v>
+        <v>1.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.456349206349209</v>
-      </c>
-      <c r="BH3" t="inlineStr"/>
-      <c r="BI3" t="inlineStr"/>
-      <c r="BJ3" t="inlineStr"/>
+        <v>9.611111111111111</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>-5.002937538651807</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>10825000</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>56</v>
+      </c>
       <c r="BK3" t="n">
-        <v>-745.0663408002438</v>
+        <v>1.168097643097582</v>
       </c>
       <c r="BL3" t="n">
-        <v>-0.2581649831649833</v>
+        <v>-2.103326678890596</v>
       </c>
       <c r="BM3" t="n">
-        <v>-1.829304954304945</v>
-      </c>
-      <c r="BN3" t="inlineStr"/>
+        <v>0.3414792392235881</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>-0.2569942171445931</v>
+      </c>
       <c r="BO3" t="n">
-        <v>-8518617.724867728</v>
+        <v>-4.035185185185185</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.765622955374511</v>
+        <v>-4663079.648978146</v>
       </c>
       <c r="BQ3" t="n">
-        <v>-6800.048100048098</v>
-      </c>
-      <c r="BR3" t="inlineStr"/>
+        <v>-0.2819023569023569</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>-1.938973063973052</v>
+      </c>
       <c r="BS3" t="n">
-        <v>-0.2327903326922616</v>
+        <v>0.8333333333333333</v>
       </c>
       <c r="BT3" t="n">
-        <v>1.032311207311153</v>
+        <v>3.711916786916785</v>
       </c>
       <c r="BU3" t="n">
-        <v>-1.867936097537267</v>
-      </c>
-      <c r="BV3" t="inlineStr"/>
+        <v>2.305555555555557</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>-713.1658511357746</v>
+      </c>
       <c r="BW3" t="n">
-        <v>-4.159788359788351</v>
+        <v>-8667824.074074075</v>
       </c>
     </row>
     <row r="4">
@@ -1444,55 +1476,71 @@
       <c r="BA4" t="n">
         <v>-0.4962406015037594</v>
       </c>
-      <c r="BB4" t="inlineStr"/>
+      <c r="BB4" t="n">
+        <v>2.197222222222251</v>
+      </c>
       <c r="BC4" t="n">
-        <v>-35608706.77471393</v>
+        <v>-62225.92592592593</v>
       </c>
       <c r="BD4" t="n">
-        <v>-13.03375614753324</v>
-      </c>
-      <c r="BE4" t="inlineStr"/>
+        <v>-157333.3333333333</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>-124.8333333333333</v>
+      </c>
       <c r="BF4" t="n">
-        <v>-9.58879825884469</v>
+        <v>-3.499999999999999</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.413492063492065</v>
-      </c>
-      <c r="BH4" t="inlineStr"/>
-      <c r="BI4" t="inlineStr"/>
-      <c r="BJ4" t="inlineStr"/>
+        <v>5.011111111111113</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>-9.329671573982722</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>-82225000</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>-165.5</v>
+      </c>
       <c r="BK4" t="n">
-        <v>-60084.00234812773</v>
+        <v>1.497685185185162</v>
       </c>
       <c r="BL4" t="n">
-        <v>-2.103174603174603</v>
+        <v>2.495592574636703</v>
       </c>
       <c r="BM4" t="n">
-        <v>-11.15925925925927</v>
-      </c>
-      <c r="BN4" t="inlineStr"/>
+        <v>-12.82658994771998</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>-1.584724317077258</v>
+      </c>
       <c r="BO4" t="n">
-        <v>-44083376.32275132</v>
+        <v>-12.11574074074075</v>
       </c>
       <c r="BP4" t="n">
-        <v>-1.269674846996836</v>
+        <v>-33133763.2422796</v>
       </c>
       <c r="BQ4" t="n">
-        <v>-60115.34391534392</v>
-      </c>
-      <c r="BR4" t="inlineStr"/>
+        <v>-2.170370370370371</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>-11.38518518518519</v>
+      </c>
       <c r="BS4" t="n">
-        <v>-1.64404941463765</v>
+        <v>-1.666666666666667</v>
       </c>
       <c r="BT4" t="n">
-        <v>1.554034391534373</v>
+        <v>-1.323351317585068</v>
       </c>
       <c r="BU4" t="n">
-        <v>2.26281602384546</v>
-      </c>
-      <c r="BV4" t="inlineStr"/>
+        <v>1.275925925925922</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>-58140.10885055776</v>
+      </c>
       <c r="BW4" t="n">
-        <v>-12.04616402116402</v>
+        <v>-45659375</v>
       </c>
     </row>
     <row r="5">
@@ -1679,55 +1727,71 @@
       <c r="BA5" t="n">
         <v>-0.5215311004784688</v>
       </c>
-      <c r="BB5" t="inlineStr"/>
+      <c r="BB5" t="n">
+        <v>3.694444444444457</v>
+      </c>
       <c r="BC5" t="n">
-        <v>-35965204.17881285</v>
+        <v>-78820.02164502164</v>
       </c>
       <c r="BD5" t="n">
-        <v>-10.36053935546897</v>
-      </c>
-      <c r="BE5" t="inlineStr"/>
+        <v>-83666.66666666666</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>66.33333333333334</v>
+      </c>
       <c r="BF5" t="n">
-        <v>-8.074303983433765</v>
+        <v>-1.833333333333333</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.5737734487734514</v>
-      </c>
-      <c r="BH5" t="inlineStr"/>
-      <c r="BI5" t="inlineStr"/>
-      <c r="BJ5" t="inlineStr"/>
+        <v>-0.12222222222222</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>-7.859823278871232</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>-49666666.66666666</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>70.16666666666666</v>
+      </c>
       <c r="BK5" t="n">
-        <v>-62985.35329047366</v>
+        <v>-0.5319805194805269</v>
       </c>
       <c r="BL5" t="n">
-        <v>-1.96948051948052</v>
+        <v>5.667624780999063</v>
       </c>
       <c r="BM5" t="n">
-        <v>-9.332287157287141</v>
-      </c>
-      <c r="BN5" t="inlineStr"/>
+        <v>-9.977549843874868</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>-1.21641498704745</v>
+      </c>
       <c r="BO5" t="n">
-        <v>-44258798.7012987</v>
+        <v>-9.362049062049081</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.036196368152698</v>
+        <v>-33255355.68897831</v>
       </c>
       <c r="BQ5" t="n">
-        <v>-75975.97402597402</v>
-      </c>
-      <c r="BR5" t="inlineStr"/>
+        <v>-2.063528138528139</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>-9.689562289562275</v>
+      </c>
       <c r="BS5" t="n">
-        <v>-1.302458351761757</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="BT5" t="n">
-        <v>-0.5766233766233881</v>
+        <v>0.09814728887186419</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.558781945619302</v>
-      </c>
-      <c r="BV5" t="inlineStr"/>
+        <v>0.5893157768157771</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>-60386.38089449772</v>
+      </c>
       <c r="BW5" t="n">
-        <v>-9.125541125541147</v>
+        <v>-47450167.74891775</v>
       </c>
     </row>
     <row r="6">
@@ -1908,61 +1972,77 @@
       <c r="BA6" t="n">
         <v>0.03421052631578947</v>
       </c>
-      <c r="BB6" t="inlineStr"/>
+      <c r="BB6" t="n">
+        <v>-5.269841269841237</v>
+      </c>
       <c r="BC6" t="n">
-        <v>8521587.598109595</v>
+        <v>10697.13203463203</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.319130388789588</v>
-      </c>
-      <c r="BE6" t="inlineStr"/>
+        <v>48166.66666666666</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>165.5</v>
+      </c>
       <c r="BF6" t="n">
-        <v>5.660592976182215</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="BG6" t="n">
-        <v>-1.780645743145744</v>
-      </c>
-      <c r="BH6" t="inlineStr"/>
-      <c r="BI6" t="inlineStr"/>
-      <c r="BJ6" t="inlineStr"/>
+        <v>-2.491269841269833</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>5.530303112854611</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>16583333.33333333</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>192.5</v>
+      </c>
       <c r="BK6" t="n">
-        <v>8477.515033820197</v>
+        <v>0.2513107263106917</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.4522727272727276</v>
+        <v>0.3397406559877822</v>
       </c>
       <c r="BM6" t="n">
-        <v>6.224891774891788</v>
-      </c>
-      <c r="BN6" t="inlineStr"/>
+        <v>5.375454941702088</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>0.4993734335839599</v>
+      </c>
       <c r="BO6" t="n">
-        <v>11752938.76262626</v>
+        <v>7.202681577681574</v>
       </c>
       <c r="BP6" t="n">
-        <v>-1.372187889613933</v>
+        <v>8734800.633830953</v>
       </c>
       <c r="BQ6" t="n">
-        <v>10737.82467532467</v>
-      </c>
-      <c r="BR6" t="inlineStr"/>
+        <v>0.4649350649350652</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>6.154256854256857</v>
+      </c>
       <c r="BS6" t="n">
-        <v>0.4824062998405105</v>
+        <v>2.333333333333333</v>
       </c>
       <c r="BT6" t="n">
-        <v>0.08535353535347667</v>
+        <v>-1.351704442265085</v>
       </c>
       <c r="BU6" t="n">
-        <v>-0.2101177179491174</v>
-      </c>
-      <c r="BV6" t="inlineStr"/>
+        <v>-1.918897306397305</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>8523.671497584541</v>
+      </c>
       <c r="BW6" t="n">
-        <v>7.13140331890331</v>
+        <v>11756835.61808562</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>ELNeaSQr</t>
+          <t>Mku6FvHt</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -1970,24 +2050,24 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">welz t 
+          <t xml:space="preserve">burda m 
   ger </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">red bull arena
-  leipzig </t>
+          <t xml:space="preserve">millerntor stadion
+  hamburg </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>KbS1suSm</t>
+          <t>ILyJuN3g</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>fiEQZ7C7</t>
+          <t>nwkTahLL</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2014,184 +2094,200 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>4ljanukM</t>
+          <t>0jdIgO6t</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>YZPE6Sx7</t>
+          <t>f3ddUIXs</t>
         </is>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.6840000000000002</v>
+        <v>0.5980000000000001</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.6176470588235299</v>
+        <v>0.3170588235294118</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.4999999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="S7" t="n">
+        <v>0.4736842105263157</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.1999999999999997</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.7222222222222223</v>
+      </c>
+      <c r="V7" t="n">
+        <v>6.799999999999999</v>
+      </c>
+      <c r="W7" t="n">
+        <v>3.722222222222223</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>-0.9999999999999999</v>
+      </c>
+      <c r="AA7" t="n">
         <v>0.631578947368421</v>
       </c>
-      <c r="T7" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.666666666666666</v>
-      </c>
-      <c r="V7" t="n">
-        <v>-5.799999999999999</v>
-      </c>
-      <c r="W7" t="n">
-        <v>3.611111111111111</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.578947368421052</v>
-      </c>
       <c r="AB7" t="n">
-        <v>0.4807828282828281</v>
+        <v>-2.546013071895426</v>
       </c>
       <c r="AC7" t="n">
-        <v>-2.871852791350144</v>
+        <v>-2.790456946352199</v>
       </c>
       <c r="AD7" t="n">
-        <v>-38.22061122552046</v>
+        <v>-32.39420678272023</v>
       </c>
       <c r="AE7" t="n">
-        <v>-145.5976548141379</v>
+        <v>-143.6553356724521</v>
       </c>
       <c r="AF7" t="n">
-        <v>48.5</v>
+        <v>-10</v>
       </c>
       <c r="AG7" t="n">
-        <v>26.80000000000001</v>
+        <v>30.46666666666667</v>
       </c>
       <c r="AH7" t="n">
-        <v>-15.5</v>
+        <v>-32</v>
       </c>
       <c r="AI7" t="n">
-        <v>17.93333333333334</v>
+        <v>13.93333333333333</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-3.333333333333339</v>
+        <v>2</v>
       </c>
       <c r="AK7" t="n">
-        <v>5.210526315789465</v>
+        <v>0.4210526315789522</v>
       </c>
       <c r="AL7" t="n">
-        <v>6.800000000000011</v>
+        <v>6.400000000000006</v>
       </c>
       <c r="AM7" t="n">
-        <v>14.11111111111111</v>
+        <v>15.22222222222223</v>
       </c>
       <c r="AN7" t="n">
-        <v>161.6</v>
+        <v>109.6</v>
       </c>
       <c r="AO7" t="n">
-        <v>197.7647058823529</v>
+        <v>236.6470588235294</v>
       </c>
       <c r="AP7" t="n">
-        <v>-0.3999999999999999</v>
+        <v>-2.9</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-0.715686274509804</v>
+        <v>-0.5784313725490198</v>
       </c>
       <c r="AR7" t="inlineStr"/>
       <c r="AS7" t="n">
-        <v>-0.6666666666666667</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.833333333333332</v>
+        <v>-6.333333333333332</v>
       </c>
       <c r="AU7" t="n">
-        <v>-0.1578947368421044</v>
+        <v>-2.210526315789474</v>
       </c>
       <c r="AV7" t="n">
-        <v>-17.56203644193162</v>
+        <v>4.016275856413451</v>
       </c>
       <c r="AW7" t="n">
-        <v>-16.66572767330928</v>
+        <v>-18.49457309611932</v>
       </c>
       <c r="AX7" t="n">
-        <v>-0.05502310427071028</v>
+        <v>0.0123407177838121</v>
       </c>
       <c r="AY7" t="n">
-        <v>-0.0154848222235259</v>
+        <v>0.0225101626541523</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.3333333333333333</v>
+        <v>-0.3333333333333334</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.1052631578947368</v>
-      </c>
-      <c r="BB7" t="inlineStr"/>
+        <v>-0.1052631578947368</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>2.872222222222263</v>
+      </c>
       <c r="BC7" t="n">
-        <v>17961559.22970048</v>
+        <v>-19114.01515151515</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.338213140120487</v>
-      </c>
-      <c r="BE7" t="inlineStr"/>
+        <v>-128166.6666666667</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>-119.8333333333334</v>
+      </c>
       <c r="BF7" t="n">
-        <v>5.514369023387729</v>
+        <v>-3.833333333333333</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.9236652236652212</v>
-      </c>
-      <c r="BH7" t="inlineStr"/>
-      <c r="BI7" t="inlineStr"/>
-      <c r="BJ7" t="inlineStr"/>
+        <v>5.886111111111109</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>-6.347175667183421</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>-50573333.33333334</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>-140.3333333333334</v>
+      </c>
       <c r="BK7" t="n">
-        <v>28413.4005773333</v>
+        <v>0.5159090909090764</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.6209595959595957</v>
+        <v>-0.2005633699519365</v>
       </c>
       <c r="BM7" t="n">
-        <v>4.397438672438668</v>
-      </c>
-      <c r="BN7" t="inlineStr"/>
+        <v>-4.793102333969202</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>-0.3637180629827685</v>
+      </c>
       <c r="BO7" t="n">
-        <v>20203881.67388167</v>
+        <v>-6.414814814814804</v>
       </c>
       <c r="BP7" t="n">
-        <v>-1.482267460760042</v>
+        <v>-6098764.757630856</v>
       </c>
       <c r="BQ7" t="n">
-        <v>30769.01154401154</v>
-      </c>
-      <c r="BR7" t="inlineStr"/>
+        <v>-0.4189814814814812</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>-4.678914141414126</v>
+      </c>
       <c r="BS7" t="n">
-        <v>0.5729332121864767</v>
+        <v>-1.166666666666666</v>
       </c>
       <c r="BT7" t="n">
-        <v>-0.3420634920634598</v>
+        <v>0.9892842251201337</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.299669782967612</v>
-      </c>
-      <c r="BV7" t="inlineStr"/>
+        <v>2.07803030303031</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>-16293.21901009207</v>
+      </c>
       <c r="BW7" t="n">
-        <v>5.396933621933655</v>
+        <v>-7962832.491582491</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>x0haJmIE</t>
+          <t>ELNeaSQr</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -2199,24 +2295,24 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">reichel t 
+          <t xml:space="preserve">welz t 
   ger </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">wwk arena
-  augsburg </t>
+          <t xml:space="preserve">red bull arena
+  leipzig </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>fTVNku3I</t>
+          <t>KbS1suSm</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>nP1i5US1</t>
+          <t>fiEQZ7C7</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2243,186 +2339,200 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2VSFgl3c</t>
+          <t>4ljanukM</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>IkCftsQm</t>
+          <t>YZPE6Sx7</t>
         </is>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1640000000000001</v>
+        <v>-0.6840000000000002</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.5070588235294113</v>
+        <v>0.6176470588235299</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>-0.4999999999999999</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4736842105263159</v>
+        <v>0.631578947368421</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4000000000000004</v>
+        <v>-1.8</v>
       </c>
       <c r="U8" t="n">
-        <v>-2.611111111111112</v>
+        <v>1.666666666666666</v>
       </c>
       <c r="V8" t="n">
-        <v>4.199999999999999</v>
+        <v>-5.799999999999999</v>
       </c>
       <c r="W8" t="n">
-        <v>0.05555555555555536</v>
+        <v>3.611111111111111</v>
       </c>
       <c r="X8" t="n">
-        <v>-1</v>
+        <v>1.2</v>
       </c>
       <c r="Y8" t="n">
-        <v>-1</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="Z8" t="n">
-        <v>-0.5</v>
+        <v>1</v>
       </c>
       <c r="AA8" t="n">
-        <v>-1.263157894736842</v>
+        <v>1.578947368421052</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8158257102374749</v>
+        <v>0.4807828282828281</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.3590433930152712</v>
+        <v>-2.871852791350144</v>
       </c>
       <c r="AD8" t="n">
-        <v>280.8218851525485</v>
+        <v>-38.22061122552046</v>
       </c>
       <c r="AE8" t="n">
-        <v>153.6030541643073</v>
+        <v>-145.5976548141379</v>
       </c>
       <c r="AF8" t="n">
-        <v>-11</v>
+        <v>48.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>-18.46666666666667</v>
+        <v>26.80000000000001</v>
       </c>
       <c r="AH8" t="n">
-        <v>32</v>
+        <v>-15.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>5.466666666666669</v>
+        <v>17.93333333333334</v>
       </c>
       <c r="AJ8" t="n">
-        <v>-0.1666666666666679</v>
+        <v>-3.333333333333339</v>
       </c>
       <c r="AK8" t="n">
-        <v>-3.89473684210526</v>
+        <v>5.210526315789465</v>
       </c>
       <c r="AL8" t="n">
-        <v>-14.8</v>
+        <v>6.800000000000011</v>
       </c>
       <c r="AM8" t="n">
-        <v>-19.55555555555556</v>
+        <v>14.11111111111111</v>
       </c>
       <c r="AN8" t="n">
-        <v>-176</v>
+        <v>161.6</v>
       </c>
       <c r="AO8" t="n">
-        <v>-255.9411764705881</v>
+        <v>197.7647058823529</v>
       </c>
       <c r="AP8" t="n">
-        <v>-1.6</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="AQ8" t="n">
-        <v>-0.3496732026143787</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>-1</v>
-      </c>
+        <v>-0.715686274509804</v>
+      </c>
+      <c r="AR8" t="inlineStr"/>
       <c r="AS8" t="n">
-        <v>-1.5</v>
+        <v>-0.6666666666666667</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.6666666666666679</v>
+        <v>1.833333333333332</v>
       </c>
       <c r="AU8" t="n">
-        <v>4.000000000000002</v>
+        <v>-0.1578947368421044</v>
       </c>
       <c r="AV8" t="n">
-        <v>11.11571241224668</v>
+        <v>-17.56203644193162</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.163363931075239</v>
+        <v>-16.66572767330928</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.09609284185745956</v>
+        <v>-0.05502310427071028</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.02609042386851434</v>
+        <v>-0.0154848222235259</v>
       </c>
       <c r="AZ8" t="n">
-        <v>-0.3333333333333333</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="BA8" t="n">
-        <v>-0.1578947368421053</v>
-      </c>
-      <c r="BB8" t="inlineStr"/>
+        <v>0.1052631578947368</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>-2.614682539682548</v>
+      </c>
       <c r="BC8" t="n">
-        <v>-17554024.68847604</v>
+        <v>30683.16498316498</v>
       </c>
       <c r="BD8" t="n">
-        <v>-5.304871251947134</v>
-      </c>
-      <c r="BE8" t="inlineStr"/>
+        <v>37166.66666666667</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>-151</v>
+      </c>
       <c r="BF8" t="n">
-        <v>-6.333913909506691</v>
+        <v>1</v>
       </c>
       <c r="BG8" t="n">
-        <v>-0.8511904761904745</v>
-      </c>
-      <c r="BH8" t="inlineStr"/>
-      <c r="BI8" t="inlineStr"/>
-      <c r="BJ8" t="inlineStr"/>
+        <v>-1.657936507936505</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>5.354626179459601</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>23500000</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>-146</v>
+      </c>
       <c r="BK8" t="n">
-        <v>-22438.55046317812</v>
+        <v>-0.455892255892195</v>
       </c>
       <c r="BL8" t="n">
-        <v>-1.486688311688312</v>
+        <v>1.163020543896977</v>
       </c>
       <c r="BM8" t="n">
-        <v>-8.274783549783535</v>
-      </c>
-      <c r="BN8" t="inlineStr"/>
+        <v>4.33117619970578</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>0.5565561388552371</v>
+      </c>
       <c r="BO8" t="n">
-        <v>-32149350.64935065</v>
+        <v>5.30589225589226</v>
       </c>
       <c r="BP8" t="n">
-        <v>-0.1317902349900528</v>
+        <v>17543626.16653462</v>
       </c>
       <c r="BQ8" t="n">
-        <v>-35674.5670995671</v>
-      </c>
-      <c r="BR8" t="inlineStr"/>
+        <v>0.6164983164983164</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>4.295117845117829</v>
+      </c>
       <c r="BS8" t="n">
-        <v>-0.7392015370047886</v>
+        <v>-2.333333333333333</v>
       </c>
       <c r="BT8" t="n">
-        <v>-1.019372294372317</v>
+        <v>-1.205308414364978</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.1123695709474362</v>
-      </c>
-      <c r="BV8" t="inlineStr"/>
+        <v>-0.9715488215488222</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>28441.49023494242</v>
+      </c>
       <c r="BW8" t="n">
-        <v>-7.20930735930736</v>
+        <v>20196195.28619529</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Mku6FvHt</t>
+          <t>x0haJmIE</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -2430,24 +2540,24 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">burda m 
+          <t xml:space="preserve">reichel t 
   ger </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">millerntor stadion
-  hamburg </t>
+          <t xml:space="preserve">wwk arena
+  augsburg </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ILyJuN3g</t>
+          <t>fTVNku3I</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>nwkTahLL</t>
+          <t>nP1i5US1</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2474,178 +2584,196 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0jdIgO6t</t>
+          <t>2VSFgl3c</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>f3ddUIXs</t>
+          <t>IkCftsQm</t>
         </is>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5980000000000001</v>
+        <v>0.1640000000000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.3170588235294118</v>
+        <v>-0.5070588235294113</v>
       </c>
       <c r="R9" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4736842105263157</v>
+        <v>-0.4736842105263159</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1999999999999997</v>
+        <v>-0.4000000000000004</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7222222222222223</v>
+        <v>-2.611111111111112</v>
       </c>
       <c r="V9" t="n">
-        <v>6.799999999999999</v>
+        <v>4.199999999999999</v>
       </c>
       <c r="W9" t="n">
-        <v>3.722222222222223</v>
+        <v>0.05555555555555536</v>
       </c>
       <c r="X9" t="n">
         <v>-1</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.3333333333333333</v>
+        <v>-1</v>
       </c>
       <c r="Z9" t="n">
-        <v>-0.9999999999999999</v>
+        <v>-0.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.631578947368421</v>
+        <v>-1.263157894736842</v>
       </c>
       <c r="AB9" t="n">
-        <v>-2.546013071895426</v>
+        <v>0.8158257102374749</v>
       </c>
       <c r="AC9" t="n">
-        <v>-2.790456946352199</v>
+        <v>0.3590433930152712</v>
       </c>
       <c r="AD9" t="n">
-        <v>-32.39420678272023</v>
+        <v>280.8218851525485</v>
       </c>
       <c r="AE9" t="n">
-        <v>-143.6553356724521</v>
+        <v>153.6030541643073</v>
       </c>
       <c r="AF9" t="n">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="AG9" t="n">
-        <v>30.46666666666667</v>
+        <v>-18.46666666666667</v>
       </c>
       <c r="AH9" t="n">
-        <v>-32</v>
+        <v>32</v>
       </c>
       <c r="AI9" t="n">
-        <v>13.93333333333333</v>
+        <v>5.466666666666669</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2</v>
+        <v>-0.1666666666666679</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.4210526315789522</v>
+        <v>-3.89473684210526</v>
       </c>
       <c r="AL9" t="n">
-        <v>6.400000000000006</v>
+        <v>-14.8</v>
       </c>
       <c r="AM9" t="n">
-        <v>15.22222222222223</v>
+        <v>-19.55555555555556</v>
       </c>
       <c r="AN9" t="n">
-        <v>109.6</v>
+        <v>-176</v>
       </c>
       <c r="AO9" t="n">
-        <v>236.6470588235294</v>
+        <v>-255.9411764705881</v>
       </c>
       <c r="AP9" t="n">
-        <v>-2.9</v>
+        <v>-1.6</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-0.5784313725490198</v>
-      </c>
-      <c r="AR9" t="inlineStr"/>
+        <v>-0.3496732026143787</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>-1</v>
+      </c>
       <c r="AS9" t="n">
-        <v>0.3333333333333333</v>
+        <v>-1.5</v>
       </c>
       <c r="AT9" t="n">
-        <v>-6.333333333333332</v>
+        <v>0.6666666666666679</v>
       </c>
       <c r="AU9" t="n">
-        <v>-2.210526315789474</v>
+        <v>4.000000000000002</v>
       </c>
       <c r="AV9" t="n">
-        <v>4.016275856413451</v>
+        <v>11.11571241224668</v>
       </c>
       <c r="AW9" t="n">
-        <v>-18.49457309611932</v>
+        <v>1.163363931075239</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.0123407177838121</v>
+        <v>0.09609284185745956</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.0225101626541523</v>
+        <v>0.02609042386851434</v>
       </c>
       <c r="AZ9" t="n">
-        <v>-0.3333333333333334</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="BA9" t="n">
-        <v>-0.1052631578947368</v>
-      </c>
-      <c r="BB9" t="inlineStr"/>
+        <v>-0.1578947368421053</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>-0.458333333333286</v>
+      </c>
       <c r="BC9" t="n">
-        <v>-6073651.279491061</v>
+        <v>-35805.30303030302</v>
       </c>
       <c r="BD9" t="n">
-        <v>-4.752368555077524</v>
-      </c>
-      <c r="BE9" t="inlineStr"/>
+        <v>9000</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>199.8333333333333</v>
+      </c>
       <c r="BF9" t="n">
-        <v>-6.237617048414265</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.060930735930739</v>
-      </c>
-      <c r="BH9" t="inlineStr"/>
-      <c r="BI9" t="inlineStr"/>
-      <c r="BJ9" t="inlineStr"/>
+        <v>3.280555555555562</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>-6.307917087506269</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>-28604166.66666666</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>198.5</v>
+      </c>
       <c r="BK9" t="n">
-        <v>-16294.13797416893</v>
+        <v>-1.090151515151518</v>
       </c>
       <c r="BL9" t="n">
-        <v>-0.4189814814814812</v>
+        <v>0.0516685996220474</v>
       </c>
       <c r="BM9" t="n">
-        <v>-4.656331168831159</v>
-      </c>
-      <c r="BN9" t="inlineStr"/>
+        <v>-5.422789907516986</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>-0.7538957046656118</v>
+      </c>
       <c r="BO9" t="n">
-        <v>-7946945.045695045</v>
+        <v>-7.184848484848487</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.8669854225581766</v>
+        <v>-17487682.22187287</v>
       </c>
       <c r="BQ9" t="n">
-        <v>-19158.24314574314</v>
-      </c>
-      <c r="BR9" t="inlineStr"/>
+        <v>-1.482575757575757</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>-8.287121212121207</v>
+      </c>
       <c r="BS9" t="n">
-        <v>-0.3637180629827685</v>
+        <v>3</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.6108585858585798</v>
+        <v>-0.1944316988982706</v>
       </c>
       <c r="BU9" t="n">
-        <v>-0.2216020778327277</v>
-      </c>
-      <c r="BV9" t="inlineStr"/>
+        <v>-0.8522727272727266</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>-23136.38348446653</v>
+      </c>
       <c r="BW9" t="n">
-        <v>-6.325132275132262</v>
+        <v>-32232575.75757576</v>
       </c>
     </row>
     <row r="10">
@@ -2826,55 +2954,71 @@
       <c r="BA10" t="n">
         <v>0.2078947368421053</v>
       </c>
-      <c r="BB10" t="inlineStr"/>
+      <c r="BB10" t="n">
+        <v>2.927777777777806</v>
+      </c>
       <c r="BC10" t="n">
-        <v>-2704651.024441398</v>
+        <v>820.3703703703686</v>
       </c>
       <c r="BD10" t="n">
-        <v>-2.233149432021619</v>
-      </c>
-      <c r="BE10" t="inlineStr"/>
+        <v>-24250</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>-209</v>
+      </c>
       <c r="BF10" t="n">
-        <v>-0.6020139281008596</v>
+        <v>-3.916666666666667</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.438095238095237</v>
-      </c>
-      <c r="BH10" t="inlineStr"/>
-      <c r="BI10" t="inlineStr"/>
-      <c r="BJ10" t="inlineStr"/>
+        <v>4.783333333333331</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>-0.4576980990024282</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>-11516666.66666667</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>-243.25</v>
+      </c>
       <c r="BK10" t="n">
-        <v>-888.0110354938734</v>
+        <v>-1.581481481481489</v>
       </c>
       <c r="BL10" t="n">
-        <v>-0.07619047619047636</v>
+        <v>0.3840028265657622</v>
       </c>
       <c r="BM10" t="n">
-        <v>-0.6619047619047649</v>
-      </c>
-      <c r="BN10" t="inlineStr"/>
+        <v>-2.165382411892722</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>-0.04071757126677067</v>
+      </c>
       <c r="BO10" t="n">
-        <v>-1748888.888888889</v>
+        <v>-0.8240740740740762</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.05780232625606985</v>
+        <v>-2467115.291109856</v>
       </c>
       <c r="BQ10" t="n">
-        <v>846.0317460317456</v>
-      </c>
-      <c r="BR10" t="inlineStr"/>
+        <v>-0.07222222222222263</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>-0.7055555555555486</v>
+      </c>
       <c r="BS10" t="n">
-        <v>-0.0715763151526474</v>
+        <v>-3.166666666666667</v>
       </c>
       <c r="BT10" t="n">
-        <v>-1.541269841269838</v>
+        <v>-0.06437899755977838</v>
       </c>
       <c r="BU10" t="n">
-        <v>0.1750488587363179</v>
-      </c>
-      <c r="BV10" t="inlineStr"/>
+        <v>1.427777777777777</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>-700.264082472313</v>
+      </c>
       <c r="BW10" t="n">
-        <v>-0.9492063492063494</v>
+        <v>-1652037.037037037</v>
       </c>
     </row>
     <row r="11">
@@ -3061,55 +3205,71 @@
       <c r="BA11" t="n">
         <v>0.2631578947368421</v>
       </c>
-      <c r="BB11" t="inlineStr"/>
+      <c r="BB11" t="n">
+        <v>-1.719444444444463</v>
+      </c>
       <c r="BC11" t="n">
+        <v>12724.18831168831</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>129000</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>200.8333333333333</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>5.333333333333334</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>-3.338888888888889</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>1.692275103301171</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>44716666.66666666</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>224</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>0.9278138528138697</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>-1.446541507179148</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>2.604569662966767</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>0.3637180629827685</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>3.104641654641654</v>
+      </c>
+      <c r="BP11" t="n">
         <v>4389194.218808111</v>
       </c>
-      <c r="BD11" t="n">
-        <v>2.604569662966767</v>
-      </c>
-      <c r="BE11" t="inlineStr"/>
-      <c r="BF11" t="n">
-        <v>1.692275103301171</v>
-      </c>
-      <c r="BG11" t="n">
+      <c r="BQ11" t="n">
+        <v>0.3241762866762863</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>0.8622474747474485</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>0.106372732852936</v>
+      </c>
+      <c r="BU11" t="n">
         <v>-2.272186147186151</v>
       </c>
-      <c r="BH11" t="inlineStr"/>
-      <c r="BI11" t="inlineStr"/>
-      <c r="BJ11" t="inlineStr"/>
-      <c r="BK11" t="n">
+      <c r="BV11" t="n">
         <v>13149.49101893028</v>
       </c>
-      <c r="BL11" t="n">
-        <v>0.3241762866762863</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>0.8622474747474485</v>
-      </c>
-      <c r="BN11" t="inlineStr"/>
-      <c r="BO11" t="n">
+      <c r="BW11" t="n">
         <v>4270538.119288119</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>0.106372732852936</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>12724.18831168831</v>
-      </c>
-      <c r="BR11" t="inlineStr"/>
-      <c r="BS11" t="n">
-        <v>0.3637180629827685</v>
-      </c>
-      <c r="BT11" t="n">
-        <v>0.9278138528138697</v>
-      </c>
-      <c r="BU11" t="n">
-        <v>-1.446541507179148</v>
-      </c>
-      <c r="BV11" t="inlineStr"/>
-      <c r="BW11" t="n">
-        <v>3.104641654641654</v>
       </c>
     </row>
     <row r="12">
@@ -3290,55 +3450,71 @@
       <c r="BA12" t="n">
         <v>0.4736842105263158</v>
       </c>
-      <c r="BB12" t="inlineStr"/>
+      <c r="BB12" t="n">
+        <v>11.08333333333337</v>
+      </c>
       <c r="BC12" t="n">
-        <v>-2342168.257081627</v>
+        <v>-10615.5303030303</v>
       </c>
       <c r="BD12" t="n">
-        <v>-4.851261175713603</v>
-      </c>
-      <c r="BE12" t="inlineStr"/>
+        <v>-56000</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>-61.33333333333334</v>
+      </c>
       <c r="BF12" t="n">
-        <v>-3.383567355241112</v>
+        <v>-1.666666666666667</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.315981240981241</v>
-      </c>
-      <c r="BH12" t="inlineStr"/>
-      <c r="BI12" t="inlineStr"/>
-      <c r="BJ12" t="inlineStr"/>
+        <v>-4.361111111111114</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>-3.242583814608992</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>-10883333.33333333</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>-52.33333333333334</v>
+      </c>
       <c r="BK12" t="n">
-        <v>-9312.095456031384</v>
+        <v>-0.9495791245791168</v>
       </c>
       <c r="BL12" t="n">
-        <v>-0.4131313131313132</v>
+        <v>2.096168561500377</v>
       </c>
       <c r="BM12" t="n">
-        <v>-4.945165945165954</v>
-      </c>
-      <c r="BN12" t="inlineStr"/>
+        <v>-4.752397297591799</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>-0.1349206349206351</v>
+      </c>
       <c r="BO12" t="n">
-        <v>-4655847.763347763</v>
+        <v>-5.404629629629625</v>
       </c>
       <c r="BP12" t="n">
-        <v>-0.7698775925320547</v>
+        <v>-2321056.203310208</v>
       </c>
       <c r="BQ12" t="n">
-        <v>-11036.97691197692</v>
-      </c>
-      <c r="BR12" t="inlineStr"/>
+        <v>-0.3893939393939396</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>-4.843434343434353</v>
+      </c>
       <c r="BS12" t="n">
-        <v>-0.1591245193729667</v>
+        <v>-0.6666666666666665</v>
       </c>
       <c r="BT12" t="n">
-        <v>-0.7374458874458583</v>
+        <v>-0.6711373845241084</v>
       </c>
       <c r="BU12" t="n">
-        <v>2.086570982321206</v>
-      </c>
-      <c r="BV12" t="inlineStr"/>
+        <v>-0.06898148148147953</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>-9194.626663276553</v>
+      </c>
       <c r="BW12" t="n">
-        <v>-5.185209235209228</v>
+        <v>-4526435.185185185</v>
       </c>
     </row>
     <row r="13">
@@ -3521,55 +3697,71 @@
       <c r="BA13" t="n">
         <v>-0.1394736842105263</v>
       </c>
-      <c r="BB13" t="inlineStr"/>
+      <c r="BB13" t="n">
+        <v>0.1428571428571388</v>
+      </c>
       <c r="BC13" t="n">
-        <v>27052256.89789012</v>
+        <v>51872.77537277537</v>
       </c>
       <c r="BD13" t="n">
-        <v>7.887532947788358</v>
-      </c>
-      <c r="BE13" t="inlineStr"/>
+        <v>117000</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>-115</v>
+      </c>
       <c r="BF13" t="n">
-        <v>5.721760905932726</v>
+        <v>-1</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.037896825396825</v>
-      </c>
-      <c r="BH13" t="inlineStr"/>
-      <c r="BI13" t="inlineStr"/>
-      <c r="BJ13" t="inlineStr"/>
+        <v>-0.1714285714285744</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>5.484948529569266</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>139600000</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>-132</v>
+      </c>
       <c r="BK13" t="n">
-        <v>51066.93250276842</v>
+        <v>-2.013347763347724</v>
       </c>
       <c r="BL13" t="n">
-        <v>1.650901875901876</v>
+        <v>-1.898429417876002</v>
       </c>
       <c r="BM13" t="n">
-        <v>6.678282828282832</v>
-      </c>
-      <c r="BN13" t="inlineStr"/>
+        <v>7.507264484741256</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>1.085350883493298</v>
+      </c>
       <c r="BO13" t="n">
-        <v>32626361.38167388</v>
+        <v>6.238985088985103</v>
       </c>
       <c r="BP13" t="n">
-        <v>2.443650318979273</v>
+        <v>24338034.28470467</v>
       </c>
       <c r="BQ13" t="n">
-        <v>49744.17388167389</v>
-      </c>
-      <c r="BR13" t="inlineStr"/>
+        <v>1.705435305435305</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>6.982780182780189</v>
+      </c>
       <c r="BS13" t="n">
-        <v>1.161643114797139</v>
+        <v>-2</v>
       </c>
       <c r="BT13" t="n">
-        <v>-1.980086580086549</v>
+        <v>2.431809302668437</v>
       </c>
       <c r="BU13" t="n">
-        <v>-1.341587495322017</v>
-      </c>
-      <c r="BV13" t="inlineStr"/>
+        <v>2.217508417508419</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>48927.51325901481</v>
+      </c>
       <c r="BW13" t="n">
-        <v>6.145869408369407</v>
+        <v>34218256.97450697</v>
       </c>
     </row>
     <row r="14">
@@ -3752,55 +3944,71 @@
       <c r="BA14" t="n">
         <v>-0.1052631578947368</v>
       </c>
-      <c r="BB14" t="inlineStr"/>
+      <c r="BB14" t="n">
+        <v>2.25</v>
+      </c>
       <c r="BC14" t="n">
-        <v>-21443429.20142539</v>
+        <v>-31701.6835016835</v>
       </c>
       <c r="BD14" t="n">
-        <v>-7.291088835853316</v>
-      </c>
-      <c r="BE14" t="inlineStr"/>
+        <v>-166000</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>-234</v>
+      </c>
       <c r="BF14" t="n">
-        <v>-5.560772793966038</v>
+        <v>-7</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.688744588744587</v>
-      </c>
-      <c r="BH14" t="inlineStr"/>
-      <c r="BI14" t="inlineStr"/>
-      <c r="BJ14" t="inlineStr"/>
+        <v>4.25</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>-5.569909529468347</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>-66900000</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>-257</v>
+      </c>
       <c r="BK14" t="n">
-        <v>-31001.96798682258</v>
+        <v>0.005892255892263165</v>
       </c>
       <c r="BL14" t="n">
-        <v>-0.830880230880231</v>
+        <v>-1.161408972148138</v>
       </c>
       <c r="BM14" t="n">
-        <v>-5.724819624819631</v>
-      </c>
-      <c r="BN14" t="inlineStr"/>
+        <v>-7.321746498971734</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>-0.7987774695205039</v>
+      </c>
       <c r="BO14" t="n">
-        <v>-24401818.18181818</v>
+        <v>-7.215151515151518</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.3826716332465985</v>
+        <v>-21173112.83817089</v>
       </c>
       <c r="BQ14" t="n">
-        <v>-31845.59884559884</v>
-      </c>
-      <c r="BR14" t="inlineStr"/>
+        <v>-0.8239057239057244</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>-5.689562289562275</v>
+      </c>
       <c r="BS14" t="n">
-        <v>-0.829649395643425</v>
+        <v>-3</v>
       </c>
       <c r="BT14" t="n">
-        <v>-0.07936507936506132</v>
+        <v>0.232660556248014</v>
       </c>
       <c r="BU14" t="n">
-        <v>-1.017602248235818</v>
-      </c>
-      <c r="BV14" t="inlineStr"/>
+        <v>1.847474747474749</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>-30828.63530446734</v>
+      </c>
       <c r="BW14" t="n">
-        <v>-7.115584415584422</v>
+        <v>-24578787.87878788</v>
       </c>
     </row>
     <row r="15">
@@ -3983,55 +4191,71 @@
       <c r="BA15" t="n">
         <v>0.2857142857142857</v>
       </c>
-      <c r="BB15" t="inlineStr"/>
+      <c r="BB15" t="n">
+        <v>-0.1999999999999886</v>
+      </c>
       <c r="BC15" t="n">
-        <v>3848001.752657878</v>
+        <v>13240.74074074074</v>
       </c>
       <c r="BD15" t="n">
-        <v>2.777769191347247</v>
-      </c>
-      <c r="BE15" t="inlineStr"/>
+        <v>122000</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>242</v>
+      </c>
       <c r="BF15" t="n">
-        <v>3.315877120078795</v>
+        <v>7</v>
       </c>
       <c r="BG15" t="n">
-        <v>-0.8134920634920597</v>
-      </c>
-      <c r="BH15" t="inlineStr"/>
-      <c r="BI15" t="inlineStr"/>
-      <c r="BJ15" t="inlineStr"/>
+        <v>4.300000000000001</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>3.355054428429042</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>28925000</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>240</v>
+      </c>
       <c r="BK15" t="n">
-        <v>8893.810533660157</v>
+        <v>0.7226851851852132</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.6412698412698414</v>
+        <v>0.3945800902457108</v>
       </c>
       <c r="BM15" t="n">
-        <v>3.12433862433862</v>
-      </c>
-      <c r="BN15" t="inlineStr"/>
+        <v>2.701141113215414</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>0.1884851016429965</v>
+      </c>
       <c r="BO15" t="n">
-        <v>5205162.037037037</v>
+        <v>4.908333333333331</v>
       </c>
       <c r="BP15" t="n">
-        <v>-1.143217502925591</v>
+        <v>3742646.598900469</v>
       </c>
       <c r="BQ15" t="n">
-        <v>13013.75661375661</v>
-      </c>
-      <c r="BR15" t="inlineStr"/>
+        <v>0.6648148148148152</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>3.361111111111114</v>
+      </c>
       <c r="BS15" t="n">
-        <v>0.2187015156939971</v>
+        <v>3</v>
       </c>
       <c r="BT15" t="n">
-        <v>0.7919973544973686</v>
+        <v>-1.221755116801553</v>
       </c>
       <c r="BU15" t="n">
-        <v>0.4682563443731169</v>
-      </c>
-      <c r="BV15" t="inlineStr"/>
+        <v>-0.7925925925925874</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>8922.59280680333</v>
+      </c>
       <c r="BW15" t="n">
-        <v>4.582671957671963</v>
+        <v>5421458.333333334</v>
       </c>
     </row>
     <row r="16">
@@ -4212,55 +4436,71 @@
       <c r="BA16" t="n">
         <v>0.2105263157894737</v>
       </c>
-      <c r="BB16" t="inlineStr"/>
+      <c r="BB16" t="n">
+        <v>3.5</v>
+      </c>
       <c r="BC16" t="n">
-        <v>1924586.889432981</v>
+        <v>3997.222222222223</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.671632664229946</v>
-      </c>
-      <c r="BE16" t="inlineStr"/>
+        <v>-39000</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>-140</v>
+      </c>
       <c r="BF16" t="n">
-        <v>0.2612278182197372</v>
+        <v>-2</v>
       </c>
       <c r="BG16" t="n">
-        <v>0.9956349206349202</v>
-      </c>
-      <c r="BH16" t="inlineStr"/>
-      <c r="BI16" t="inlineStr"/>
-      <c r="BJ16" t="inlineStr"/>
+        <v>0.1666666666666679</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>0.4556908367674311</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>-1925000</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>-141</v>
+      </c>
       <c r="BK16" t="n">
-        <v>2784.877743830351</v>
+        <v>-1.106481481481524</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.4944444444444447</v>
+        <v>-0.621644098316068</v>
       </c>
       <c r="BM16" t="n">
-        <v>2.44285714285715</v>
-      </c>
-      <c r="BN16" t="inlineStr"/>
+        <v>1.729560209424577</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>0.2284120350171825</v>
+      </c>
       <c r="BO16" t="n">
-        <v>5381904.761904763</v>
+        <v>1.901851851851845</v>
       </c>
       <c r="BP16" t="n">
-        <v>1.97206561287576</v>
+        <v>2130762.208565557</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4045.238095238095</v>
-      </c>
-      <c r="BR16" t="inlineStr"/>
+        <v>0.4935185185185187</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>2.530555555555566</v>
+      </c>
       <c r="BS16" t="n">
-        <v>0.2290413256350314</v>
+        <v>-2</v>
       </c>
       <c r="BT16" t="n">
-        <v>-1.275793650793673</v>
+        <v>1.777237445147954</v>
       </c>
       <c r="BU16" t="n">
-        <v>-0.8271844172104466</v>
-      </c>
-      <c r="BV16" t="inlineStr"/>
+        <v>0.9601851851851855</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>2756.788086221241</v>
+      </c>
       <c r="BW16" t="n">
-        <v>1.767063492063471</v>
+        <v>5545555.555555558</v>
       </c>
     </row>
     <row r="17">
@@ -4441,55 +4681,71 @@
       <c r="BA17" t="n">
         <v>0.4162679425837321</v>
       </c>
-      <c r="BB17" t="inlineStr"/>
+      <c r="BB17" t="n">
+        <v>5</v>
+      </c>
       <c r="BC17" t="n">
-        <v>30585890.97509019</v>
+        <v>67889.8148148148</v>
       </c>
       <c r="BD17" t="n">
-        <v>8.058965356477515</v>
-      </c>
-      <c r="BE17" t="inlineStr"/>
+        <v>112000</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>29</v>
+      </c>
       <c r="BF17" t="n">
-        <v>3.648078481791458</v>
+        <v>3</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.878968253968257</v>
-      </c>
-      <c r="BH17" t="inlineStr"/>
-      <c r="BI17" t="inlineStr"/>
-      <c r="BJ17" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>3.433597777228925</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>132925000</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>16</v>
+      </c>
       <c r="BK17" t="n">
-        <v>56512.5458955512</v>
+        <v>-1.025462962963019</v>
       </c>
       <c r="BL17" t="n">
-        <v>1.392989417989418</v>
+        <v>-4.106873594732974</v>
       </c>
       <c r="BM17" t="n">
-        <v>7.041798941798945</v>
-      </c>
-      <c r="BN17" t="inlineStr"/>
+        <v>7.675975844883411</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>0.8245001349822221</v>
+      </c>
       <c r="BO17" t="n">
-        <v>35172056.87830687</v>
+        <v>4.470370370370389</v>
       </c>
       <c r="BP17" t="n">
-        <v>1.958551347173639</v>
+        <v>27876042.48525566</v>
       </c>
       <c r="BQ17" t="n">
-        <v>65045.76719576719</v>
-      </c>
-      <c r="BR17" t="inlineStr"/>
+        <v>1.487037037037037</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>7.399074074074079</v>
+      </c>
       <c r="BS17" t="n">
-        <v>0.9105434996965289</v>
+        <v>0</v>
       </c>
       <c r="BT17" t="n">
-        <v>-0.9808201058201576</v>
+        <v>1.896600426454473</v>
       </c>
       <c r="BU17" t="n">
-        <v>-3.998030759353213</v>
-      </c>
-      <c r="BV17" t="inlineStr"/>
+        <v>1.863425925925931</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>53913.57349957526</v>
+      </c>
       <c r="BW17" t="n">
-        <v>4.233862433862456</v>
+        <v>38363425.92592593</v>
       </c>
     </row>
     <row r="18">
@@ -4670,55 +4926,71 @@
       <c r="BA18" t="n">
         <v>-0.1552631578947369</v>
       </c>
-      <c r="BB18" t="inlineStr"/>
+      <c r="BB18" t="n">
+        <v>-6.833333333333314</v>
+      </c>
       <c r="BC18" t="n">
-        <v>3920842.284282134</v>
+        <v>2250</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.971006709319894</v>
-      </c>
-      <c r="BE18" t="inlineStr"/>
+        <v>43000</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>220</v>
+      </c>
       <c r="BF18" t="n">
-        <v>5.012450380609906</v>
+        <v>5</v>
       </c>
       <c r="BG18" t="n">
-        <v>-0.6999999999999957</v>
-      </c>
-      <c r="BH18" t="inlineStr"/>
-      <c r="BI18" t="inlineStr"/>
-      <c r="BJ18" t="inlineStr"/>
+        <v>-1.166666666666668</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>5.000032690421691</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>34625000</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>251</v>
+      </c>
       <c r="BK18" t="n">
-        <v>2418.483320101499</v>
+        <v>-2.216666666666612</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.4714285714285715</v>
+        <v>-1.701942355889685</v>
       </c>
       <c r="BM18" t="n">
-        <v>2.957142857142856</v>
-      </c>
-      <c r="BN18" t="inlineStr"/>
+        <v>3.94443536377176</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>0.1419172932330826</v>
+      </c>
       <c r="BO18" t="n">
-        <v>5112857.142857143</v>
+        <v>3.333333333333343</v>
       </c>
       <c r="BP18" t="n">
-        <v>-0.1577336197636967</v>
+        <v>3746417.447604518</v>
       </c>
       <c r="BQ18" t="n">
-        <v>2285.714285714286</v>
-      </c>
-      <c r="BR18" t="inlineStr"/>
+        <v>0.4666666666666668</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>2.933333333333323</v>
+      </c>
       <c r="BS18" t="n">
-        <v>0.1651216550693504</v>
+        <v>3</v>
       </c>
       <c r="BT18" t="n">
-        <v>-2.371428571428538</v>
+        <v>-0.09706603465184571</v>
       </c>
       <c r="BU18" t="n">
-        <v>-1.614087236725283</v>
-      </c>
-      <c r="BV18" t="inlineStr"/>
+        <v>-0.649999999999995</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>2357.795757509713</v>
+      </c>
       <c r="BW18" t="n">
-        <v>3.600000000000009</v>
+        <v>4960000</v>
       </c>
     </row>
     <row r="19">
@@ -4899,55 +5171,71 @@
       <c r="BA19" t="n">
         <v>0.1052631578947368</v>
       </c>
-      <c r="BB19" t="inlineStr"/>
+      <c r="BB19" t="n">
+        <v>-8.833333333333314</v>
+      </c>
       <c r="BC19" t="n">
-        <v>20720545.86871847</v>
+        <v>40898.48484848485</v>
       </c>
       <c r="BD19" t="n">
-        <v>9.515824381205221</v>
-      </c>
-      <c r="BE19" t="inlineStr"/>
+        <v>6000</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>-181</v>
+      </c>
       <c r="BF19" t="n">
-        <v>10.91741088086299</v>
+        <v>-1</v>
       </c>
       <c r="BG19" t="n">
-        <v>-0.1264069264069292</v>
-      </c>
-      <c r="BH19" t="inlineStr"/>
-      <c r="BI19" t="inlineStr"/>
-      <c r="BJ19" t="inlineStr"/>
+        <v>-7</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>11.00097267763172</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>42490000</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>-165</v>
+      </c>
       <c r="BK19" t="n">
-        <v>27557.42419289329</v>
+        <v>0.9075757575757564</v>
       </c>
       <c r="BL19" t="n">
-        <v>1.611688311688312</v>
+        <v>-0.5343942310761065</v>
       </c>
       <c r="BM19" t="n">
-        <v>11.34083694083692</v>
-      </c>
-      <c r="BN19" t="inlineStr"/>
+        <v>9.67447681566675</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>0.9123829831495733</v>
+      </c>
       <c r="BO19" t="n">
-        <v>35161341.99134199</v>
+        <v>10.61818181818182</v>
       </c>
       <c r="BP19" t="n">
-        <v>-0.6286207236517818</v>
+        <v>20679316.8802551</v>
       </c>
       <c r="BQ19" t="n">
-        <v>40811.97691197691</v>
-      </c>
-      <c r="BR19" t="inlineStr"/>
+        <v>1.607575757575757</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>11.37575757575756</v>
+      </c>
       <c r="BS19" t="n">
-        <v>0.8976888154887501</v>
+        <v>-3</v>
       </c>
       <c r="BT19" t="n">
-        <v>0.741847041847052</v>
+        <v>-0.6882780623055211</v>
       </c>
       <c r="BU19" t="n">
-        <v>-0.5740564945207041</v>
-      </c>
-      <c r="BV19" t="inlineStr"/>
+        <v>-0.1424242424242479</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>28254.33825010484</v>
+      </c>
       <c r="BW19" t="n">
-        <v>10.55295815295815</v>
+        <v>35260454.54545455</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/data_preparation/df_constructed.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_constructed.xlsx
@@ -695,112 +695,112 @@
       </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_wage_player_start</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_wage_player_miss</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_sub</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_value_player_miss</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_value_player_start</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_start</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_value_player_sub</t>
+        </is>
+      </c>
+      <c r="BW1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_start</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_wage_player_miss</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_value_player_miss</t>
-        </is>
-      </c>
-      <c r="BJ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="BK1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="BL1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="BM1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="BN1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="BO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="BP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_sub</t>
-        </is>
-      </c>
-      <c r="BQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_start</t>
-        </is>
-      </c>
-      <c r="BR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="BS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="BT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="BU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="BV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_sub</t>
-        </is>
-      </c>
-      <c r="BW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_start</t>
         </is>
       </c>
     </row>
@@ -985,70 +985,70 @@
         <v>0.1052631578947368</v>
       </c>
       <c r="BB2" t="n">
-        <v>5.238095238095241</v>
+        <v>-8088.888888888891</v>
       </c>
       <c r="BC2" t="n">
-        <v>-8088.888888888891</v>
+        <v>-112666.6666666667</v>
       </c>
       <c r="BD2" t="n">
-        <v>-112666.6666666667</v>
+        <v>-1.195498105166337</v>
       </c>
       <c r="BE2" t="n">
-        <v>-276.6666666666667</v>
+        <v>-0.1450068407734311</v>
       </c>
       <c r="BF2" t="n">
-        <v>-6.5</v>
+        <v>-4112.345477219616</v>
       </c>
       <c r="BG2" t="n">
-        <v>-0.9603174603174693</v>
+        <v>-4.079629629629636</v>
       </c>
       <c r="BH2" t="n">
-        <v>-5.485110723669081</v>
+        <v>-290.6666666666667</v>
       </c>
       <c r="BI2" t="n">
         <v>-33687500</v>
       </c>
       <c r="BJ2" t="n">
-        <v>-290.6666666666667</v>
+        <v>-0.9603174603174693</v>
       </c>
       <c r="BK2" t="n">
+        <v>-276.6666666666667</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>-4439074.074074075</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>-0.6481481481481486</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>-0.6962962962963033</v>
+      </c>
+      <c r="BO2" t="n">
         <v>1.268518518518476</v>
       </c>
-      <c r="BL2" t="n">
-        <v>-1.195498105166337</v>
-      </c>
-      <c r="BM2" t="n">
+      <c r="BP2" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="BQ2" t="n">
         <v>-1.62483533713511</v>
       </c>
-      <c r="BN2" t="n">
-        <v>-0.1450068407734311</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>-4.079629629629636</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>-3372858.126596685</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>-0.6481481481481486</v>
-      </c>
       <c r="BR2" t="n">
-        <v>-2.440740740740736</v>
+        <v>1.597951702928821</v>
       </c>
       <c r="BS2" t="n">
         <v>-3.5</v>
       </c>
       <c r="BT2" t="n">
-        <v>1.597951702928821</v>
+        <v>-2.440740740740736</v>
       </c>
       <c r="BU2" t="n">
-        <v>-0.6962962962963033</v>
+        <v>-5.485110723669081</v>
       </c>
       <c r="BV2" t="n">
-        <v>-4112.345477219616</v>
+        <v>-3372858.126596685</v>
       </c>
       <c r="BW2" t="n">
-        <v>-4439074.074074075</v>
+        <v>5.238095238095241</v>
       </c>
     </row>
     <row r="3">
@@ -1230,70 +1230,70 @@
         <v>-0.1052631578947368</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.9999999999999716</v>
+        <v>-7198.821548821546</v>
       </c>
       <c r="BC3" t="n">
-        <v>-7198.821548821546</v>
+        <v>72000</v>
       </c>
       <c r="BD3" t="n">
-        <v>72000</v>
+        <v>-2.103326678890596</v>
       </c>
       <c r="BE3" t="n">
-        <v>85.66666666666667</v>
+        <v>-0.2569942171445931</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.5</v>
+        <v>-713.1658511357746</v>
       </c>
       <c r="BG3" t="n">
-        <v>9.611111111111111</v>
+        <v>-4.035185185185185</v>
       </c>
       <c r="BH3" t="n">
-        <v>-5.002937538651807</v>
+        <v>56</v>
       </c>
       <c r="BI3" t="n">
         <v>10825000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>56</v>
+        <v>9.611111111111111</v>
       </c>
       <c r="BK3" t="n">
+        <v>85.66666666666667</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>-8667824.074074075</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>-0.2819023569023569</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>2.305555555555557</v>
+      </c>
+      <c r="BO3" t="n">
         <v>1.168097643097582</v>
       </c>
-      <c r="BL3" t="n">
-        <v>-2.103326678890596</v>
-      </c>
-      <c r="BM3" t="n">
+      <c r="BP3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BQ3" t="n">
         <v>0.3414792392235881</v>
       </c>
-      <c r="BN3" t="n">
-        <v>-0.2569942171445931</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>-4.035185185185185</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>-4663079.648978146</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>-0.2819023569023569</v>
-      </c>
       <c r="BR3" t="n">
-        <v>-1.938973063973052</v>
+        <v>3.711916786916785</v>
       </c>
       <c r="BS3" t="n">
         <v>0.8333333333333333</v>
       </c>
       <c r="BT3" t="n">
-        <v>3.711916786916785</v>
+        <v>-1.938973063973052</v>
       </c>
       <c r="BU3" t="n">
-        <v>2.305555555555557</v>
+        <v>-5.002937538651807</v>
       </c>
       <c r="BV3" t="n">
-        <v>-713.1658511357746</v>
+        <v>-4663079.648978146</v>
       </c>
       <c r="BW3" t="n">
-        <v>-8667824.074074075</v>
+        <v>0.9999999999999716</v>
       </c>
     </row>
     <row r="4">
@@ -1477,70 +1477,70 @@
         <v>-0.4962406015037594</v>
       </c>
       <c r="BB4" t="n">
-        <v>2.197222222222251</v>
+        <v>-62296.29629629629</v>
       </c>
       <c r="BC4" t="n">
-        <v>-62225.92592592593</v>
+        <v>-157333.3333333333</v>
       </c>
       <c r="BD4" t="n">
-        <v>-157333.3333333333</v>
+        <v>2.71838340036868</v>
       </c>
       <c r="BE4" t="n">
-        <v>-124.8333333333333</v>
+        <v>-1.584724317077258</v>
       </c>
       <c r="BF4" t="n">
-        <v>-3.499999999999999</v>
+        <v>-57921.07931341678</v>
       </c>
       <c r="BG4" t="n">
-        <v>5.011111111111113</v>
+        <v>-12.10148148148149</v>
       </c>
       <c r="BH4" t="n">
-        <v>-9.329671573982722</v>
+        <v>-165.5</v>
       </c>
       <c r="BI4" t="n">
         <v>-82225000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>-165.5</v>
+        <v>5.011111111111113</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.497685185185162</v>
+        <v>-124.8333333333333</v>
       </c>
       <c r="BL4" t="n">
-        <v>2.495592574636703</v>
+        <v>-45655351.85185185</v>
       </c>
       <c r="BM4" t="n">
-        <v>-12.82658994771998</v>
+        <v>-2.170370370370371</v>
       </c>
       <c r="BN4" t="n">
-        <v>-1.584724317077258</v>
+        <v>1.303703703703697</v>
       </c>
       <c r="BO4" t="n">
-        <v>-12.11574074074075</v>
+        <v>1.61611111111111</v>
       </c>
       <c r="BP4" t="n">
-        <v>-33133763.2422796</v>
+        <v>-3.499999999999999</v>
       </c>
       <c r="BQ4" t="n">
-        <v>-2.170370370370371</v>
+        <v>-12.70604883878877</v>
       </c>
       <c r="BR4" t="n">
-        <v>-11.38518518518519</v>
+        <v>-1.138150066594346</v>
       </c>
       <c r="BS4" t="n">
         <v>-1.666666666666667</v>
       </c>
       <c r="BT4" t="n">
-        <v>-1.323351317585068</v>
+        <v>-11.30592592592595</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.275925925925922</v>
+        <v>-9.451637184338423</v>
       </c>
       <c r="BV4" t="n">
-        <v>-58140.10885055776</v>
+        <v>-33137118.68814665</v>
       </c>
       <c r="BW4" t="n">
-        <v>-45659375</v>
+        <v>2.197222222222251</v>
       </c>
     </row>
     <row r="5">
@@ -1728,70 +1728,70 @@
         <v>-0.5215311004784688</v>
       </c>
       <c r="BB5" t="n">
-        <v>3.694444444444457</v>
+        <v>-78820.02164502164</v>
       </c>
       <c r="BC5" t="n">
-        <v>-78820.02164502164</v>
+        <v>-83666.66666666666</v>
       </c>
       <c r="BD5" t="n">
-        <v>-83666.66666666666</v>
+        <v>5.667624780999063</v>
       </c>
       <c r="BE5" t="n">
-        <v>66.33333333333334</v>
+        <v>-1.21641498704745</v>
       </c>
       <c r="BF5" t="n">
-        <v>-1.833333333333333</v>
+        <v>-60386.38089449772</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.12222222222222</v>
+        <v>-9.362049062049081</v>
       </c>
       <c r="BH5" t="n">
-        <v>-7.859823278871232</v>
+        <v>70.16666666666666</v>
       </c>
       <c r="BI5" t="n">
         <v>-49666666.66666666</v>
       </c>
       <c r="BJ5" t="n">
-        <v>70.16666666666666</v>
+        <v>-0.12222222222222</v>
       </c>
       <c r="BK5" t="n">
+        <v>66.33333333333334</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>-47450167.74891775</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>-2.063528138528139</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>0.5893157768157771</v>
+      </c>
+      <c r="BO5" t="n">
         <v>-0.5319805194805269</v>
       </c>
-      <c r="BL5" t="n">
-        <v>5.667624780999063</v>
-      </c>
-      <c r="BM5" t="n">
+      <c r="BP5" t="n">
+        <v>-1.833333333333333</v>
+      </c>
+      <c r="BQ5" t="n">
         <v>-9.977549843874868</v>
       </c>
-      <c r="BN5" t="n">
-        <v>-1.21641498704745</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>-9.362049062049081</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>-33255355.68897831</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>-2.063528138528139</v>
-      </c>
       <c r="BR5" t="n">
-        <v>-9.689562289562275</v>
+        <v>0.09814728887186419</v>
       </c>
       <c r="BS5" t="n">
         <v>1.166666666666667</v>
       </c>
       <c r="BT5" t="n">
-        <v>0.09814728887186419</v>
+        <v>-9.689562289562275</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.5893157768157771</v>
+        <v>-7.859823278871232</v>
       </c>
       <c r="BV5" t="n">
-        <v>-60386.38089449772</v>
+        <v>-33255355.68897831</v>
       </c>
       <c r="BW5" t="n">
-        <v>-47450167.74891775</v>
+        <v>3.694444444444457</v>
       </c>
     </row>
     <row r="6">
@@ -1973,70 +1973,70 @@
         <v>0.03421052631578947</v>
       </c>
       <c r="BB6" t="n">
-        <v>-5.269841269841237</v>
+        <v>10697.13203463203</v>
       </c>
       <c r="BC6" t="n">
-        <v>10697.13203463203</v>
+        <v>48166.66666666666</v>
       </c>
       <c r="BD6" t="n">
-        <v>48166.66666666666</v>
+        <v>0.3397406559877822</v>
       </c>
       <c r="BE6" t="n">
-        <v>165.5</v>
+        <v>0.4993734335839599</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.166666666666667</v>
+        <v>8523.671497584541</v>
       </c>
       <c r="BG6" t="n">
-        <v>-2.491269841269833</v>
+        <v>7.202681577681574</v>
       </c>
       <c r="BH6" t="n">
-        <v>5.530303112854611</v>
+        <v>192.5</v>
       </c>
       <c r="BI6" t="n">
         <v>16583333.33333333</v>
       </c>
       <c r="BJ6" t="n">
-        <v>192.5</v>
+        <v>-2.491269841269833</v>
       </c>
       <c r="BK6" t="n">
+        <v>165.5</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>11756835.61808562</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>0.4649350649350652</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>-1.918897306397305</v>
+      </c>
+      <c r="BO6" t="n">
         <v>0.2513107263106917</v>
       </c>
-      <c r="BL6" t="n">
-        <v>0.3397406559877822</v>
-      </c>
-      <c r="BM6" t="n">
+      <c r="BP6" t="n">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="BQ6" t="n">
         <v>5.375454941702088</v>
       </c>
-      <c r="BN6" t="n">
-        <v>0.4993734335839599</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>7.202681577681574</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>8734800.633830953</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>0.4649350649350652</v>
-      </c>
       <c r="BR6" t="n">
-        <v>6.154256854256857</v>
+        <v>-1.351704442265085</v>
       </c>
       <c r="BS6" t="n">
         <v>2.333333333333333</v>
       </c>
       <c r="BT6" t="n">
-        <v>-1.351704442265085</v>
+        <v>6.154256854256857</v>
       </c>
       <c r="BU6" t="n">
-        <v>-1.918897306397305</v>
+        <v>5.530303112854611</v>
       </c>
       <c r="BV6" t="n">
-        <v>8523.671497584541</v>
+        <v>8734800.633830953</v>
       </c>
       <c r="BW6" t="n">
-        <v>11756835.61808562</v>
+        <v>-5.269841269841237</v>
       </c>
     </row>
     <row r="7">
@@ -2218,70 +2218,70 @@
         <v>-0.1052631578947368</v>
       </c>
       <c r="BB7" t="n">
-        <v>2.872222222222263</v>
+        <v>-19114.01515151515</v>
       </c>
       <c r="BC7" t="n">
-        <v>-19114.01515151515</v>
+        <v>-128166.6666666667</v>
       </c>
       <c r="BD7" t="n">
-        <v>-128166.6666666667</v>
+        <v>-0.2005633699519365</v>
       </c>
       <c r="BE7" t="n">
-        <v>-119.8333333333334</v>
+        <v>-0.3637180629827685</v>
       </c>
       <c r="BF7" t="n">
-        <v>-3.833333333333333</v>
+        <v>-16293.21901009207</v>
       </c>
       <c r="BG7" t="n">
-        <v>5.886111111111109</v>
+        <v>-6.414814814814804</v>
       </c>
       <c r="BH7" t="n">
-        <v>-6.347175667183421</v>
+        <v>-140.3333333333334</v>
       </c>
       <c r="BI7" t="n">
         <v>-50573333.33333334</v>
       </c>
       <c r="BJ7" t="n">
-        <v>-140.3333333333334</v>
+        <v>5.886111111111109</v>
       </c>
       <c r="BK7" t="n">
+        <v>-119.8333333333334</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>-7962832.491582491</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>-0.4189814814814812</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>2.07803030303031</v>
+      </c>
+      <c r="BO7" t="n">
         <v>0.5159090909090764</v>
       </c>
-      <c r="BL7" t="n">
-        <v>-0.2005633699519365</v>
-      </c>
-      <c r="BM7" t="n">
+      <c r="BP7" t="n">
+        <v>-3.833333333333333</v>
+      </c>
+      <c r="BQ7" t="n">
         <v>-4.793102333969202</v>
       </c>
-      <c r="BN7" t="n">
-        <v>-0.3637180629827685</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>-6.414814814814804</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>-6098764.757630856</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>-0.4189814814814812</v>
-      </c>
       <c r="BR7" t="n">
-        <v>-4.678914141414126</v>
+        <v>0.9892842251201337</v>
       </c>
       <c r="BS7" t="n">
         <v>-1.166666666666666</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.9892842251201337</v>
+        <v>-4.678914141414126</v>
       </c>
       <c r="BU7" t="n">
-        <v>2.07803030303031</v>
+        <v>-6.347175667183421</v>
       </c>
       <c r="BV7" t="n">
-        <v>-16293.21901009207</v>
+        <v>-6098764.757630856</v>
       </c>
       <c r="BW7" t="n">
-        <v>-7962832.491582491</v>
+        <v>2.872222222222263</v>
       </c>
     </row>
     <row r="8">
@@ -2463,70 +2463,70 @@
         <v>0.1052631578947368</v>
       </c>
       <c r="BB8" t="n">
-        <v>-2.614682539682548</v>
+        <v>30683.16498316498</v>
       </c>
       <c r="BC8" t="n">
-        <v>30683.16498316498</v>
+        <v>37166.66666666667</v>
       </c>
       <c r="BD8" t="n">
-        <v>37166.66666666667</v>
+        <v>1.163020543896977</v>
       </c>
       <c r="BE8" t="n">
-        <v>-151</v>
+        <v>0.5565561388552371</v>
       </c>
       <c r="BF8" t="n">
-        <v>1</v>
+        <v>28441.49023494242</v>
       </c>
       <c r="BG8" t="n">
-        <v>-1.657936507936505</v>
+        <v>5.30589225589226</v>
       </c>
       <c r="BH8" t="n">
-        <v>5.354626179459601</v>
+        <v>-146</v>
       </c>
       <c r="BI8" t="n">
         <v>23500000</v>
       </c>
       <c r="BJ8" t="n">
-        <v>-146</v>
+        <v>-1.657936507936505</v>
       </c>
       <c r="BK8" t="n">
+        <v>-151</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>20196195.28619529</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>0.6164983164983164</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>-0.9715488215488222</v>
+      </c>
+      <c r="BO8" t="n">
         <v>-0.455892255892195</v>
       </c>
-      <c r="BL8" t="n">
-        <v>1.163020543896977</v>
-      </c>
-      <c r="BM8" t="n">
+      <c r="BP8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ8" t="n">
         <v>4.33117619970578</v>
       </c>
-      <c r="BN8" t="n">
-        <v>0.5565561388552371</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>5.30589225589226</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>17543626.16653462</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>0.6164983164983164</v>
-      </c>
       <c r="BR8" t="n">
-        <v>4.295117845117829</v>
+        <v>-1.205308414364978</v>
       </c>
       <c r="BS8" t="n">
         <v>-2.333333333333333</v>
       </c>
       <c r="BT8" t="n">
-        <v>-1.205308414364978</v>
+        <v>4.295117845117829</v>
       </c>
       <c r="BU8" t="n">
-        <v>-0.9715488215488222</v>
+        <v>5.354626179459601</v>
       </c>
       <c r="BV8" t="n">
-        <v>28441.49023494242</v>
+        <v>17543626.16653462</v>
       </c>
       <c r="BW8" t="n">
-        <v>20196195.28619529</v>
+        <v>-2.614682539682548</v>
       </c>
     </row>
     <row r="9">
@@ -2710,70 +2710,70 @@
         <v>-0.1578947368421053</v>
       </c>
       <c r="BB9" t="n">
-        <v>-0.458333333333286</v>
+        <v>-35534.4696969697</v>
       </c>
       <c r="BC9" t="n">
-        <v>-35805.30303030302</v>
+        <v>9000</v>
       </c>
       <c r="BD9" t="n">
-        <v>9000</v>
+        <v>0.3183272700014186</v>
       </c>
       <c r="BE9" t="n">
-        <v>199.8333333333333</v>
+        <v>-0.7805114612819215</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.166666666666667</v>
+        <v>-23159.91060530955</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.280555555555562</v>
+        <v>-7.351515151515159</v>
       </c>
       <c r="BH9" t="n">
-        <v>-6.307917087506269</v>
+        <v>198.5</v>
       </c>
       <c r="BI9" t="n">
         <v>-28604166.66666666</v>
       </c>
       <c r="BJ9" t="n">
-        <v>198.5</v>
+        <v>3.280555555555562</v>
       </c>
       <c r="BK9" t="n">
-        <v>-1.090151515151518</v>
+        <v>199.8333333333333</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.0516685996220474</v>
+        <v>-32232575.75757576</v>
       </c>
       <c r="BM9" t="n">
-        <v>-5.422789907516986</v>
+        <v>-1.482575757575757</v>
       </c>
       <c r="BN9" t="n">
-        <v>-0.7538957046656118</v>
+        <v>-0.7064393939393945</v>
       </c>
       <c r="BO9" t="n">
-        <v>-7.184848484848487</v>
+        <v>-1.131818181818176</v>
       </c>
       <c r="BP9" t="n">
-        <v>-17487682.22187287</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="BQ9" t="n">
-        <v>-1.482575757575757</v>
+        <v>-5.400055421643955</v>
       </c>
       <c r="BR9" t="n">
-        <v>-8.287121212121207</v>
+        <v>-0.2024565728563559</v>
       </c>
       <c r="BS9" t="n">
         <v>3</v>
       </c>
       <c r="BT9" t="n">
-        <v>-0.1944316988982706</v>
+        <v>-8.245454545454535</v>
       </c>
       <c r="BU9" t="n">
-        <v>-0.8522727272727266</v>
+        <v>-6.321023659215214</v>
       </c>
       <c r="BV9" t="n">
-        <v>-23136.38348446653</v>
+        <v>-17492727.57667083</v>
       </c>
       <c r="BW9" t="n">
-        <v>-32232575.75757576</v>
+        <v>-0.458333333333286</v>
       </c>
     </row>
     <row r="10">
@@ -2955,70 +2955,70 @@
         <v>0.2078947368421053</v>
       </c>
       <c r="BB10" t="n">
-        <v>2.927777777777806</v>
+        <v>820.3703703703686</v>
       </c>
       <c r="BC10" t="n">
-        <v>820.3703703703686</v>
+        <v>-24250</v>
       </c>
       <c r="BD10" t="n">
-        <v>-24250</v>
+        <v>0.3840028265657622</v>
       </c>
       <c r="BE10" t="n">
-        <v>-209</v>
+        <v>-0.04071757126677067</v>
       </c>
       <c r="BF10" t="n">
-        <v>-3.916666666666667</v>
+        <v>-700.264082472313</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.783333333333331</v>
+        <v>-0.8240740740740762</v>
       </c>
       <c r="BH10" t="n">
-        <v>-0.4576980990024282</v>
+        <v>-243.25</v>
       </c>
       <c r="BI10" t="n">
         <v>-11516666.66666667</v>
       </c>
       <c r="BJ10" t="n">
-        <v>-243.25</v>
+        <v>4.783333333333331</v>
       </c>
       <c r="BK10" t="n">
+        <v>-209</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>-1652037.037037037</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>-0.07222222222222263</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>1.427777777777777</v>
+      </c>
+      <c r="BO10" t="n">
         <v>-1.581481481481489</v>
       </c>
-      <c r="BL10" t="n">
-        <v>0.3840028265657622</v>
-      </c>
-      <c r="BM10" t="n">
+      <c r="BP10" t="n">
+        <v>-3.916666666666667</v>
+      </c>
+      <c r="BQ10" t="n">
         <v>-2.165382411892722</v>
       </c>
-      <c r="BN10" t="n">
-        <v>-0.04071757126677067</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>-0.8240740740740762</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>-2467115.291109856</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>-0.07222222222222263</v>
-      </c>
       <c r="BR10" t="n">
-        <v>-0.7055555555555486</v>
+        <v>-0.06437899755977838</v>
       </c>
       <c r="BS10" t="n">
         <v>-3.166666666666667</v>
       </c>
       <c r="BT10" t="n">
-        <v>-0.06437899755977838</v>
+        <v>-0.7055555555555486</v>
       </c>
       <c r="BU10" t="n">
-        <v>1.427777777777777</v>
+        <v>-0.4576980990024282</v>
       </c>
       <c r="BV10" t="n">
-        <v>-700.264082472313</v>
+        <v>-2467115.291109856</v>
       </c>
       <c r="BW10" t="n">
-        <v>-1652037.037037037</v>
+        <v>2.927777777777806</v>
       </c>
     </row>
     <row r="11">
@@ -3206,70 +3206,70 @@
         <v>0.2631578947368421</v>
       </c>
       <c r="BB11" t="n">
-        <v>-1.719444444444463</v>
+        <v>12724.18831168831</v>
       </c>
       <c r="BC11" t="n">
-        <v>12724.18831168831</v>
+        <v>129000</v>
       </c>
       <c r="BD11" t="n">
-        <v>129000</v>
+        <v>-1.446541507179148</v>
       </c>
       <c r="BE11" t="n">
-        <v>200.8333333333333</v>
+        <v>0.3637180629827685</v>
       </c>
       <c r="BF11" t="n">
-        <v>5.333333333333334</v>
+        <v>13149.49101893028</v>
       </c>
       <c r="BG11" t="n">
-        <v>-3.338888888888889</v>
+        <v>3.104641654641654</v>
       </c>
       <c r="BH11" t="n">
-        <v>1.692275103301171</v>
+        <v>224</v>
       </c>
       <c r="BI11" t="n">
         <v>44716666.66666666</v>
       </c>
       <c r="BJ11" t="n">
-        <v>224</v>
+        <v>-3.338888888888889</v>
       </c>
       <c r="BK11" t="n">
+        <v>200.8333333333333</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>4270538.119288119</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>0.3241762866762863</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>-2.272186147186151</v>
+      </c>
+      <c r="BO11" t="n">
         <v>0.9278138528138697</v>
       </c>
-      <c r="BL11" t="n">
-        <v>-1.446541507179148</v>
-      </c>
-      <c r="BM11" t="n">
+      <c r="BP11" t="n">
+        <v>5.333333333333334</v>
+      </c>
+      <c r="BQ11" t="n">
         <v>2.604569662966767</v>
       </c>
-      <c r="BN11" t="n">
-        <v>0.3637180629827685</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>3.104641654641654</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>4389194.218808111</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>0.3241762866762863</v>
-      </c>
       <c r="BR11" t="n">
-        <v>0.8622474747474485</v>
+        <v>0.106372732852936</v>
       </c>
       <c r="BS11" t="n">
         <v>2.666666666666667</v>
       </c>
       <c r="BT11" t="n">
-        <v>0.106372732852936</v>
+        <v>0.8622474747474485</v>
       </c>
       <c r="BU11" t="n">
-        <v>-2.272186147186151</v>
+        <v>1.692275103301171</v>
       </c>
       <c r="BV11" t="n">
-        <v>13149.49101893028</v>
+        <v>4389194.218808111</v>
       </c>
       <c r="BW11" t="n">
-        <v>4270538.119288119</v>
+        <v>-1.719444444444463</v>
       </c>
     </row>
     <row r="12">
@@ -3451,70 +3451,70 @@
         <v>0.4736842105263158</v>
       </c>
       <c r="BB12" t="n">
-        <v>11.08333333333337</v>
+        <v>-10615.5303030303</v>
       </c>
       <c r="BC12" t="n">
-        <v>-10615.5303030303</v>
+        <v>-67000</v>
       </c>
       <c r="BD12" t="n">
-        <v>-56000</v>
+        <v>2.096168561500377</v>
       </c>
       <c r="BE12" t="n">
-        <v>-61.33333333333334</v>
+        <v>-0.1349206349206351</v>
       </c>
       <c r="BF12" t="n">
-        <v>-1.666666666666667</v>
+        <v>-9194.626663276553</v>
       </c>
       <c r="BG12" t="n">
-        <v>-4.361111111111114</v>
+        <v>-5.404629629629625</v>
       </c>
       <c r="BH12" t="n">
+        <v>-77</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>-11600000</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>-86</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>-4526435.185185185</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>-0.3893939393939396</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>-0.06898148148147953</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>-0.9495791245791168</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>-2</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>-4.752397297591799</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>-0.6711373845241084</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>-4.843434343434353</v>
+      </c>
+      <c r="BU12" t="n">
         <v>-3.242583814608992</v>
       </c>
-      <c r="BI12" t="n">
-        <v>-10883333.33333333</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>-52.33333333333334</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>-0.9495791245791168</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>2.096168561500377</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>-4.752397297591799</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>-0.1349206349206351</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>-5.404629629629625</v>
-      </c>
-      <c r="BP12" t="n">
+      <c r="BV12" t="n">
         <v>-2321056.203310208</v>
       </c>
-      <c r="BQ12" t="n">
-        <v>-0.3893939393939396</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>-4.843434343434353</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>-0.6666666666666665</v>
-      </c>
-      <c r="BT12" t="n">
-        <v>-0.6711373845241084</v>
-      </c>
-      <c r="BU12" t="n">
-        <v>-0.06898148148147953</v>
-      </c>
-      <c r="BV12" t="n">
-        <v>-9194.626663276553</v>
-      </c>
       <c r="BW12" t="n">
-        <v>-4526435.185185185</v>
+        <v>9.666666666666657</v>
       </c>
     </row>
     <row r="13">
@@ -3698,70 +3698,70 @@
         <v>-0.1394736842105263</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.1428571428571388</v>
+        <v>51872.77537277537</v>
       </c>
       <c r="BC13" t="n">
-        <v>51872.77537277537</v>
+        <v>207000</v>
       </c>
       <c r="BD13" t="n">
-        <v>117000</v>
+        <v>-1.898429417876002</v>
       </c>
       <c r="BE13" t="n">
-        <v>-115</v>
+        <v>1.085350883493298</v>
       </c>
       <c r="BF13" t="n">
-        <v>-1</v>
+        <v>48927.51325901481</v>
       </c>
       <c r="BG13" t="n">
-        <v>-0.1714285714285744</v>
+        <v>6.238985088985103</v>
       </c>
       <c r="BH13" t="n">
+        <v>32</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>183100000</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>0.3333333333333321</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>42</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>34218256.97450697</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>1.705435305435305</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>2.217508417508419</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>-2.013347763347724</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>4</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>7.507264484741256</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>2.431809302668437</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>6.982780182780189</v>
+      </c>
+      <c r="BU13" t="n">
         <v>5.484948529569266</v>
       </c>
-      <c r="BI13" t="n">
-        <v>139600000</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>-132</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>-2.013347763347724</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>-1.898429417876002</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>7.507264484741256</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>1.085350883493298</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>6.238985088985103</v>
-      </c>
-      <c r="BP13" t="n">
+      <c r="BV13" t="n">
         <v>24338034.28470467</v>
       </c>
-      <c r="BQ13" t="n">
-        <v>1.705435305435305</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>6.982780182780189</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>-2</v>
-      </c>
-      <c r="BT13" t="n">
-        <v>2.431809302668437</v>
-      </c>
-      <c r="BU13" t="n">
-        <v>2.217508417508419</v>
-      </c>
-      <c r="BV13" t="n">
-        <v>48927.51325901481</v>
-      </c>
       <c r="BW13" t="n">
-        <v>34218256.97450697</v>
+        <v>1.166666666666657</v>
       </c>
     </row>
     <row r="14">
@@ -3945,70 +3945,70 @@
         <v>-0.1052631578947368</v>
       </c>
       <c r="BB14" t="n">
-        <v>2.25</v>
+        <v>-31701.6835016835</v>
       </c>
       <c r="BC14" t="n">
-        <v>-31701.6835016835</v>
+        <v>-149000</v>
       </c>
       <c r="BD14" t="n">
-        <v>-166000</v>
+        <v>-1.161408972148138</v>
       </c>
       <c r="BE14" t="n">
-        <v>-234</v>
+        <v>-0.7987774695205039</v>
       </c>
       <c r="BF14" t="n">
-        <v>-7</v>
+        <v>-30828.63530446734</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.25</v>
+        <v>-7.215151515151518</v>
       </c>
       <c r="BH14" t="n">
+        <v>-188</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>-82900000</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>-164</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>-24578787.87878788</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>-0.8239057239057244</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>1.847474747474749</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>0.005892255892263165</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>-5</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>-7.321746498971734</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>0.232660556248014</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>-2</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>-5.689562289562275</v>
+      </c>
+      <c r="BU14" t="n">
         <v>-5.569909529468347</v>
       </c>
-      <c r="BI14" t="n">
-        <v>-66900000</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>-257</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>0.005892255892263165</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>-1.161408972148138</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>-7.321746498971734</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>-0.7987774695205039</v>
-      </c>
-      <c r="BO14" t="n">
-        <v>-7.215151515151518</v>
-      </c>
-      <c r="BP14" t="n">
+      <c r="BV14" t="n">
         <v>-21173112.83817089</v>
       </c>
-      <c r="BQ14" t="n">
-        <v>-0.8239057239057244</v>
-      </c>
-      <c r="BR14" t="n">
-        <v>-5.689562289562275</v>
-      </c>
-      <c r="BS14" t="n">
-        <v>-3</v>
-      </c>
-      <c r="BT14" t="n">
-        <v>0.232660556248014</v>
-      </c>
-      <c r="BU14" t="n">
-        <v>1.847474747474749</v>
-      </c>
-      <c r="BV14" t="n">
-        <v>-30828.63530446734</v>
-      </c>
       <c r="BW14" t="n">
-        <v>-24578787.87878788</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="15">
@@ -4192,70 +4192,70 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="BB15" t="n">
-        <v>-0.1999999999999886</v>
+        <v>13311.11111111111</v>
       </c>
       <c r="BC15" t="n">
-        <v>13240.74074074074</v>
+        <v>122000</v>
       </c>
       <c r="BD15" t="n">
-        <v>122000</v>
+        <v>0.171789264513734</v>
       </c>
       <c r="BE15" t="n">
-        <v>242</v>
+        <v>0.1884851016429965</v>
       </c>
       <c r="BF15" t="n">
+        <v>8703.563269662338</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>4.894074074074069</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>243</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>27325000</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>239</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>5417435.185185186</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>0.6648148148148152</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>-0.8203703703703624</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>0.6042592592592655</v>
+      </c>
+      <c r="BP15" t="n">
         <v>7</v>
       </c>
-      <c r="BG15" t="n">
-        <v>4.300000000000001</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>3.355054428429042</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>28925000</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>240</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>0.7226851851852132</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>0.3945800902457108</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>2.701141113215414</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>0.1884851016429965</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>4.908333333333331</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>3742646.598900469</v>
-      </c>
       <c r="BQ15" t="n">
-        <v>0.6648148148148152</v>
+        <v>2.580600004284207</v>
       </c>
       <c r="BR15" t="n">
-        <v>3.361111111111114</v>
+        <v>-1.406956367792276</v>
       </c>
       <c r="BS15" t="n">
         <v>3</v>
       </c>
       <c r="BT15" t="n">
-        <v>-1.221755116801553</v>
+        <v>3.281851851851869</v>
       </c>
       <c r="BU15" t="n">
-        <v>-0.7925925925925874</v>
+        <v>3.477020038784744</v>
       </c>
       <c r="BV15" t="n">
-        <v>8922.59280680333</v>
+        <v>3746002.044767525</v>
       </c>
       <c r="BW15" t="n">
-        <v>5421458.333333334</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="16">
@@ -4437,70 +4437,70 @@
         <v>0.2105263157894737</v>
       </c>
       <c r="BB16" t="n">
-        <v>3.5</v>
+        <v>3726.388888888891</v>
       </c>
       <c r="BC16" t="n">
-        <v>3997.222222222223</v>
+        <v>-61000</v>
       </c>
       <c r="BD16" t="n">
-        <v>-39000</v>
+        <v>-0.8883027686954392</v>
       </c>
       <c r="BE16" t="n">
-        <v>-140</v>
+        <v>0.2550277916334922</v>
       </c>
       <c r="BF16" t="n">
-        <v>-2</v>
+        <v>2780.315207064265</v>
       </c>
       <c r="BG16" t="n">
-        <v>0.1666666666666679</v>
+        <v>2.068518518518516</v>
       </c>
       <c r="BH16" t="n">
-        <v>0.4556908367674311</v>
+        <v>-214</v>
       </c>
       <c r="BI16" t="n">
-        <v>-1925000</v>
+        <v>-3425000</v>
       </c>
       <c r="BJ16" t="n">
-        <v>-141</v>
+        <v>-2.166666666666664</v>
       </c>
       <c r="BK16" t="n">
-        <v>-1.106481481481524</v>
+        <v>-213</v>
       </c>
       <c r="BL16" t="n">
-        <v>-0.621644098316068</v>
+        <v>5545555.555555558</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.729560209424577</v>
+        <v>0.4935185185185187</v>
       </c>
       <c r="BN16" t="n">
-        <v>0.2284120350171825</v>
+        <v>0.8143518518518533</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.901851851851845</v>
+        <v>-1.064814814814866</v>
       </c>
       <c r="BP16" t="n">
-        <v>2130762.208565557</v>
+        <v>-3</v>
       </c>
       <c r="BQ16" t="n">
-        <v>0.4935185185185187</v>
+        <v>1.706825723551546</v>
       </c>
       <c r="BR16" t="n">
-        <v>2.530555555555566</v>
+        <v>1.785262319106039</v>
       </c>
       <c r="BS16" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="BT16" t="n">
-        <v>1.777237445147954</v>
+        <v>2.488888888888894</v>
       </c>
       <c r="BU16" t="n">
-        <v>0.9601851851851855</v>
+        <v>0.4687974084763766</v>
       </c>
       <c r="BV16" t="n">
-        <v>2756.788086221241</v>
+        <v>2135807.563363511</v>
       </c>
       <c r="BW16" t="n">
-        <v>5545555.555555558</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -4682,70 +4682,70 @@
         <v>0.4162679425837321</v>
       </c>
       <c r="BB17" t="n">
-        <v>5</v>
+        <v>67889.8148148148</v>
       </c>
       <c r="BC17" t="n">
-        <v>67889.8148148148</v>
+        <v>112000</v>
       </c>
       <c r="BD17" t="n">
-        <v>112000</v>
+        <v>-4.106873594732974</v>
       </c>
       <c r="BE17" t="n">
-        <v>29</v>
+        <v>0.8245001349822221</v>
       </c>
       <c r="BF17" t="n">
-        <v>3</v>
+        <v>53913.57349957526</v>
       </c>
       <c r="BG17" t="n">
-        <v>2</v>
+        <v>4.470370370370389</v>
       </c>
       <c r="BH17" t="n">
-        <v>3.433597777228925</v>
+        <v>16</v>
       </c>
       <c r="BI17" t="n">
         <v>132925000</v>
       </c>
       <c r="BJ17" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="BK17" t="n">
+        <v>29</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>38363425.92592593</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>1.487037037037037</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>1.863425925925931</v>
+      </c>
+      <c r="BO17" t="n">
         <v>-1.025462962963019</v>
       </c>
-      <c r="BL17" t="n">
-        <v>-4.106873594732974</v>
-      </c>
-      <c r="BM17" t="n">
+      <c r="BP17" t="n">
+        <v>3</v>
+      </c>
+      <c r="BQ17" t="n">
         <v>7.675975844883411</v>
       </c>
-      <c r="BN17" t="n">
-        <v>0.8245001349822221</v>
-      </c>
-      <c r="BO17" t="n">
-        <v>4.470370370370389</v>
-      </c>
-      <c r="BP17" t="n">
-        <v>27876042.48525566</v>
-      </c>
-      <c r="BQ17" t="n">
-        <v>1.487037037037037</v>
-      </c>
       <c r="BR17" t="n">
-        <v>7.399074074074079</v>
+        <v>1.896600426454473</v>
       </c>
       <c r="BS17" t="n">
         <v>0</v>
       </c>
       <c r="BT17" t="n">
-        <v>1.896600426454473</v>
+        <v>7.399074074074079</v>
       </c>
       <c r="BU17" t="n">
-        <v>1.863425925925931</v>
+        <v>3.433597777228925</v>
       </c>
       <c r="BV17" t="n">
-        <v>53913.57349957526</v>
+        <v>27876042.48525566</v>
       </c>
       <c r="BW17" t="n">
-        <v>38363425.92592593</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
@@ -4927,70 +4927,70 @@
         <v>-0.1552631578947369</v>
       </c>
       <c r="BB18" t="n">
-        <v>-6.833333333333314</v>
+        <v>2250</v>
       </c>
       <c r="BC18" t="n">
-        <v>2250</v>
+        <v>-18000</v>
       </c>
       <c r="BD18" t="n">
-        <v>43000</v>
+        <v>-1.701942355889685</v>
       </c>
       <c r="BE18" t="n">
-        <v>220</v>
+        <v>0.1419172932330826</v>
       </c>
       <c r="BF18" t="n">
-        <v>5</v>
+        <v>2357.795757509713</v>
       </c>
       <c r="BG18" t="n">
-        <v>-1.166666666666668</v>
+        <v>3.333333333333343</v>
       </c>
       <c r="BH18" t="n">
+        <v>93</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>9125000</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>-2.199999999999999</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>66</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>4960000</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>0.4666666666666668</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>-0.649999999999995</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>-2.216666666666612</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>3.94443536377176</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>-0.09706603465184571</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>2.933333333333323</v>
+      </c>
+      <c r="BU18" t="n">
         <v>5.000032690421691</v>
       </c>
-      <c r="BI18" t="n">
-        <v>34625000</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>251</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>-2.216666666666612</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>-1.701942355889685</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>3.94443536377176</v>
-      </c>
-      <c r="BN18" t="n">
-        <v>0.1419172932330826</v>
-      </c>
-      <c r="BO18" t="n">
-        <v>3.333333333333343</v>
-      </c>
-      <c r="BP18" t="n">
+      <c r="BV18" t="n">
         <v>3746417.447604518</v>
       </c>
-      <c r="BQ18" t="n">
-        <v>0.4666666666666668</v>
-      </c>
-      <c r="BR18" t="n">
-        <v>2.933333333333323</v>
-      </c>
-      <c r="BS18" t="n">
-        <v>3</v>
-      </c>
-      <c r="BT18" t="n">
-        <v>-0.09706603465184571</v>
-      </c>
-      <c r="BU18" t="n">
-        <v>-0.649999999999995</v>
-      </c>
-      <c r="BV18" t="n">
-        <v>2357.795757509713</v>
-      </c>
       <c r="BW18" t="n">
-        <v>4960000</v>
+        <v>-2.599999999999994</v>
       </c>
     </row>
     <row r="19">
@@ -5004,7 +5004,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">dingert c 
+          <t xml:space="preserve">jollenbeck m 
   ger </t>
         </is>
       </c>
@@ -5172,70 +5172,70 @@
         <v>0.1052631578947368</v>
       </c>
       <c r="BB19" t="n">
-        <v>-8.833333333333314</v>
+        <v>40898.48484848485</v>
       </c>
       <c r="BC19" t="n">
-        <v>40898.48484848485</v>
+        <v>-25000</v>
       </c>
       <c r="BD19" t="n">
-        <v>6000</v>
+        <v>-0.5343942310761065</v>
       </c>
       <c r="BE19" t="n">
-        <v>-181</v>
+        <v>0.9123829831495733</v>
       </c>
       <c r="BF19" t="n">
-        <v>-1</v>
+        <v>28254.33825010484</v>
       </c>
       <c r="BG19" t="n">
-        <v>-7</v>
+        <v>10.61818181818182</v>
       </c>
       <c r="BH19" t="n">
+        <v>-304</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>39890000</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>-6.666666666666668</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>-315</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>35260454.54545455</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>1.607575757575757</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>-0.1424242424242479</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>0.9075757575757564</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>-3</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>9.67447681566675</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>-0.6882780623055211</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>-5</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>11.37575757575756</v>
+      </c>
+      <c r="BU19" t="n">
         <v>11.00097267763172</v>
       </c>
-      <c r="BI19" t="n">
-        <v>42490000</v>
-      </c>
-      <c r="BJ19" t="n">
-        <v>-165</v>
-      </c>
-      <c r="BK19" t="n">
-        <v>0.9075757575757564</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>-0.5343942310761065</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>9.67447681566675</v>
-      </c>
-      <c r="BN19" t="n">
-        <v>0.9123829831495733</v>
-      </c>
-      <c r="BO19" t="n">
-        <v>10.61818181818182</v>
-      </c>
-      <c r="BP19" t="n">
+      <c r="BV19" t="n">
         <v>20679316.8802551</v>
       </c>
-      <c r="BQ19" t="n">
-        <v>1.607575757575757</v>
-      </c>
-      <c r="BR19" t="n">
-        <v>11.37575757575756</v>
-      </c>
-      <c r="BS19" t="n">
-        <v>-3</v>
-      </c>
-      <c r="BT19" t="n">
-        <v>-0.6882780623055211</v>
-      </c>
-      <c r="BU19" t="n">
-        <v>-0.1424242424242479</v>
-      </c>
-      <c r="BV19" t="n">
-        <v>28254.33825010484</v>
-      </c>
       <c r="BW19" t="n">
-        <v>35260454.54545455</v>
+        <v>-8.416666666666657</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/data_preparation/df_constructed.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_constructed.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BW3"/>
+  <dimension ref="A1:BW19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -695,139 +695,139 @@
       </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_start</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_sub</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_start</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_value_player_miss</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_rat_player_start</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_sub</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_wage_player_miss</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_value_player_start</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>dif_sum_pot_player_miss</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_start</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="BJ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_start</t>
-        </is>
-      </c>
-      <c r="BK1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="BL1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_sub</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_value_player_sub</t>
-        </is>
-      </c>
-      <c r="BP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_value_player_miss</t>
-        </is>
-      </c>
-      <c r="BQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_start</t>
-        </is>
-      </c>
-      <c r="BR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="BS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="BT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="BU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="BV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="BW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_wage_player_miss</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>rPiijklS</t>
+          <t>raQ4MDUN</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45585.52083333334</v>
+        <v>45599.5625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">welz t 
+          <t xml:space="preserve">schlager d 
   ger </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">volkswagen arena
-  wolfsburg </t>
+          <t xml:space="preserve">borussia park
+  monchengladbach </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>nwkTahLL</t>
+          <t>88HSzjDr</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -859,445 +859,4381 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>8f6APkLc</t>
+          <t>M5BRZDsC</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>YZPE6Sx7</t>
+          <t>4fuCGs9P</t>
         </is>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.2350000000000001</v>
+        <v>0.6459999999999997</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.002777777777777768</v>
+        <v>0.3799019607843139</v>
       </c>
       <c r="R2" t="n">
+        <v>0.9999999999999998</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.1578947368421053</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.600000000000001</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.4912280701754383</v>
+      </c>
+      <c r="V2" t="n">
+        <v>5.199999999999999</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.502923976608187</v>
+      </c>
+      <c r="X2" t="n">
+        <v>-0.2000000000000002</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>-0.3099415204678364</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>-0.7578947368421052</v>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>-inf</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>-inf</t>
+        </is>
+      </c>
+      <c r="AD2" t="n">
+        <v>-11.78158905181789</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>-35.05414997535476</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>45</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>-11.20952380952382</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>52</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>3.428571428571431</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>-1.999999999999996</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>-1.478947368421053</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>19.59999999999999</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>5.771929824561411</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>204</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>55.17647058823536</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0.934640522875817</v>
+      </c>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="n">
         <v>-0.5</v>
       </c>
-      <c r="S2" t="n">
-        <v>-0.3157894736842104</v>
-      </c>
-      <c r="T2" t="n">
-        <v>-2.333333333333334</v>
-      </c>
-      <c r="U2" t="n">
-        <v>-0.4210526315789473</v>
-      </c>
-      <c r="V2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.789473684210527</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0.8333333333333333</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>2.220446049250313e-16</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>-0.3157894736842104</v>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>-inf</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>-inf</t>
-        </is>
-      </c>
-      <c r="AD2" t="n">
-        <v>14.511414132429</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>-17.43854022422514</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>44.33333333333334</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>14.9375</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0.3333333333333286</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>4.05263157894737</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>-12</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>-193.1666666666667</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>-72.66666666666669</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>3.166666666666667</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>1.160818713450292</v>
-      </c>
-      <c r="AR2" t="n">
+      <c r="AT2" t="n">
+        <v>0.4999999999999964</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>2.734210526315788</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>-45.65923845419426</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>-25.29505279798098</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0.1366366366366366</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>0.02076741054254223</v>
+      </c>
+      <c r="AZ2" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="AS2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>5.666666666666664</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>1.842105263157896</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>-15.43269764234403</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>-8.39706589019363</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0.02093541544517427</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>0.01809180936344106</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0.5</v>
-      </c>
       <c r="BA2" t="n">
-        <v>0.2631578947368421</v>
+        <v>0.1078947368421052</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.7017676767676733</v>
+        <v>-0.8298701298701303</v>
       </c>
       <c r="BC2" t="n">
-        <v>14063.29507764088</v>
+        <v>0.361038961038961</v>
       </c>
       <c r="BD2" t="n">
-        <v>-57</v>
+        <v>1.268564527260178</v>
       </c>
       <c r="BE2" t="n">
-        <v>3.040516458646422</v>
+        <v>2817.91196889268</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.2962121212121205</v>
+        <v>0.2085999159389156</v>
       </c>
       <c r="BG2" t="n">
-        <v>2</v>
+        <v>-3.247619047619082</v>
       </c>
       <c r="BH2" t="n">
-        <v>-1</v>
+        <v>0.9636363636363683</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.4021155179243412</v>
+        <v>925.9740259740283</v>
       </c>
       <c r="BJ2" t="n">
-        <v>3914520.202020202</v>
+        <v>10067857.14285714</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.383580213110605</v>
+        <v>1.50129870129868</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.7737373737374185</v>
+        <v>1.285714285714286</v>
       </c>
       <c r="BM2" t="n">
-        <v>-1.898742869486711</v>
+        <v>1.075324675324666</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.8166941142543465</v>
+        <v>2.960163843638824</v>
       </c>
       <c r="BO2" t="n">
-        <v>4590911.773794647</v>
+        <v>-10000</v>
       </c>
       <c r="BP2" t="n">
-        <v>29700000</v>
+        <v>2.285714285714286</v>
       </c>
       <c r="BQ2" t="n">
-        <v>12355.30303030304</v>
+        <v>-5.238095238095237</v>
       </c>
       <c r="BR2" t="n">
-        <v>3.052020202020188</v>
+        <v>0.7780433815575805</v>
       </c>
       <c r="BS2" t="n">
-        <v>-2.418181818181814</v>
+        <v>76.57142857142856</v>
       </c>
       <c r="BT2" t="n">
-        <v>-69</v>
+        <v>2120779.220779221</v>
       </c>
       <c r="BU2" t="n">
-        <v>-2.866666666666667</v>
+        <v>106.2857142857142</v>
       </c>
       <c r="BV2" t="n">
-        <v>-4.199999999999989</v>
+        <v>-3.505181644115964</v>
       </c>
       <c r="BW2" t="n">
-        <v>46000</v>
+        <v>2466642.363484469</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>nBwH6AY8</t>
+          <t>GnZmQeVb</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45585.4375</v>
+        <v>45599.47916666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">reichel t 
+          <t xml:space="preserve">zwayer f 
   ger </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">europa park stadion
+  freiburg </t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>59</v>
+      </c>
+      <c r="H3" t="n">
+        <v>591</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>YZPE6Sx7</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>pfoInmcq</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.4405882352941175</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.3157894736842106</v>
+      </c>
+      <c r="T3" t="n">
+        <v>5</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.277777777777778</v>
+      </c>
+      <c r="V3" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.222222222222221</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>-0.05555555555555558</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>-0.1578947368421053</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>-3.783534716917069</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.3635659979356975</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>-95.1838579952515</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>17.35143213153631</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>-81</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>-11.42857142857142</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>-37</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>-19.28571428571429</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0.3684210526315752</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1.8888888888889</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>148.8</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>17.41176470588232</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>-2.666666666666664</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>-2.105263157894735</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>-8.353636536620623</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>3.796314140505672</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>-0.08718485927788254</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>-0.00702993639745042</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0.05263157894736842</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>-0.7222222222222179</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>0.234920634920635</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>1.149829401284123</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>2449.405274903802</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>0.2359846538990051</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>0.5530612244898236</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>1.907936507936483</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>1158.730158730163</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>16180000</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>0.4857142857142378</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>4.228571428571429</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>1.566666666666677</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>3.05070072131204</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>68514.28571428571</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>4.257142857142856</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>-1.295578231292517</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>0.03996262536634276</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>295.7428571428571</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>4563650.793650795</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>313.0857142857143</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>0.1336152351517228</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>3597642.711026579</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>dr2N9zoI</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45598.60416666666</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">zwayer f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">signal iduna park
+  dortmund </t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>59</v>
+      </c>
+      <c r="H4" t="n">
+        <v>591</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>IkCftsQm</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>pfoInmcq</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>-0.1460000000000001</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-0.4658823529411764</v>
+      </c>
+      <c r="R4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="S4" t="n">
+        <v>-0.7894736842105262</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-1.200000000000001</v>
+      </c>
+      <c r="U4" t="n">
+        <v>-0.1111111111111112</v>
+      </c>
+      <c r="V4" t="n">
+        <v>2.200000000000001</v>
+      </c>
+      <c r="W4" t="n">
+        <v>-0.5555555555555554</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>-0.8888888888888886</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>-0.9473684210526315</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>4.586461871461871</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.561866461078725</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>148.2168248915458</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>13.70595135408004</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>-60</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>2.857142857142861</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1.714285714285715</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.166666666666671</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>3.368421052631575</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>8.800000000000011</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>11.1111111111111</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>49.19999999999993</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>86.11764705882342</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.117647058823529</v>
+      </c>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0.8333333333333357</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>-0.2105263157894708</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>8.843118424786955</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>-7.313078974828727</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>-0.0185980685980686</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0.02437173100414217</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>-0.2631578947368421</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>1.035714285714285</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>0.3826479076479075</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>-0.8847936314113802</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>-9309.288544833369</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>-0.1196040665763567</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>1.749999999999943</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>-0.1738455988455883</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>1363.564213564212</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>-9000000</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>2.419696969696957</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>-1.285714285714286</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>1.463708513708525</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>-1.021867976439594</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>-67857.14285714286</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>-2.857142857142857</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>-1.821428571428573</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>0.6838839613232324</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>-98.57142857142858</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>6265674.603174608</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>-106.7142857142857</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>-0.3019751181104766</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>-2535884.185759455</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>485V7EFU</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45598.47916666666</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">storks s 
+  ger </t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">deutsche bank park
+  frankfurt </t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>59</v>
+      </c>
+      <c r="H5" t="n">
+        <v>591</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>hAcTWKKN</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>8f6APkLc</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.686</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.9164086687306499</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.157894736842105</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.2000000000000011</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.044444444444445</v>
+      </c>
+      <c r="V5" t="n">
+        <v>-3.000000000000002</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.8111111111111118</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.105555555555555</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.729323308270677</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>3.1650623885918</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.379479171714079</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>126.5981368959931</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>66.19440864857134</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>-76</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>-17.65178571428571</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>-26</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.0714285714285694</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>-4.500000000000004</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>2.82706766917293</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>-6.799999999999997</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>-2.366666666666674</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>-145.6</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>-49.37461300309599</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>-0.5058823529411767</v>
+      </c>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>-1.166666666666664</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>-1.152882205513786</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>10.68352643182828</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>9.839235060494769</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>-0.07259643415389991</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>-0.01363569478676256</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0.2330827067669173</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>-3.827777777777776</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0.6722222222222225</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>-2.884360977859426</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>10970.82701808487</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>0.4322429450248999</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>-8.911904761904736</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>7.912037037037038</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>17396.2962962963</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>-5771428.571428573</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>-0.2513888888888403</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>-2</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>4.453236571281693</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>-51285.71428571429</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>-2.285714285714286</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>-7.285714285714285</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>6.92090385166459</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>-158</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>12779745.37037037</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>-139</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>-0.8875278512828402</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>7517295.8916851</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>2q7yHiho</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45598.47916666666</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">siebert d 
+  ger </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t xml:space="preserve">holstein stadion
   kiel </t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>63WsD2ei</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>59</v>
+      </c>
+      <c r="H6" t="n">
+        <v>591</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>A15eUM4C</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>4ljanukM</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-0.5899999999999996</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.002352941176470669</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-1.110223024625157e-16</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-0.7777777777777777</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-9.000000000000002</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-2.444444444444443</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-0.2777777777777777</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.3157894736842104</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>8.192399267399267</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.812801303061883</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>200.2045653613823</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>-35.53242421276735</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-56</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>19.42857142857142</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-37</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>2.357142857142854</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>3.000000000000004</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.3157894736842124</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.7999999999999972</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>9.444444444444457</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>-61.19999999999999</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>129.1176470588235</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>-0.1666666666666672</v>
+      </c>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="n">
+        <v>-0.1666666666666667</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>-0.6666666666666679</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>-0.8947368421052637</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>3.14818866775904</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>-10.99063569737971</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>-0.01981230737539318</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0.009886114482322225</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0.1578947368421053</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>-0.2623015873015859</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>-0.01428571428571423</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>-0.1651255467862214</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>-4035.372592973117</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>-0.03726708074534169</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>1.333333333333343</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>-2.116666666666674</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>-5582.142857142859</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>-1996428.571428572</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>-1.286507936507888</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>-0.8571428571428572</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>-2.74126984126984</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>-1.052587213375048</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>-20714.28571428572</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>-1.142857142857143</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>0.8095238095238066</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>0.4708938495306683</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>-55.57142857142858</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>-1280119.047619048</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>-59.85714285714286</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>-0.2437405625865665</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>-279511.0057753078</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>AoSdOZaB</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45598.47916666666</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dankert b 
+  ger </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">volkswagen arena
+  wolfsburg </t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>fTVNku3I</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>59</v>
+      </c>
+      <c r="H7" t="n">
+        <v>591</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>f3ddUIXs</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2VSFgl3c</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>-1.154</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.2117647058823524</v>
+      </c>
+      <c r="R7" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.1578947368421054</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.4444444444444446</v>
+      </c>
+      <c r="V7" t="n">
+        <v>-9.199999999999999</v>
+      </c>
+      <c r="W7" t="n">
+        <v>-0.8888888888888875</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.3999999999999999</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.3888888888888891</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>-0.4999999999999999</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.1578947368421053</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.930317460317461</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.2782205176813015</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>76.98538806932686</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>18.35069742676191</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>87</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>-4.214285714285708</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>-6.642857142857153</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>-4.333333333333329</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.8947368421052602</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>-6.400000000000006</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>-0.4444444444444429</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>-116.4</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>-20.11764705882354</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0.0555555555555558</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>2.666666666666668</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>-2.842105263157894</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>1.265375459590807</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>21.68206967711981</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0.08633485840799655</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>-0.0240767085096267</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0.2105263157894737</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>-1.287499999999998</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0.2666666666666662</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0.5730678236206757</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>12570.96941647473</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0.294920918925784</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>-0.9190476190476318</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>3.061111111111103</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>13479.16666666667</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>42046428.57142857</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>-0.5277777777777715</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>0.5714285714285712</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>1.430555555555557</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>1.06426801182991</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>104428.5714285714</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>3.285714285714286</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>-2.140476190476189</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>1.386131924859285</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>58</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>4591944.444444444</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>76.42857142857139</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>0.3743461898316127</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>3284005.811255922</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>8MVuSH0n</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45598.47916666666</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jollenbeck m 
+  ger </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prezero arena
+  sinsheim </t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>59</v>
+      </c>
+      <c r="H8" t="n">
+        <v>591</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>KUx4Q7x1</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0jdIgO6t</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>-0.7060000000000002</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-0.9199999999999997</v>
+      </c>
+      <c r="R8" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="S8" t="n">
+        <v>-1.263157894736842</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.7999999999999994</v>
+      </c>
+      <c r="U8" t="n">
+        <v>-1.444444444444445</v>
+      </c>
+      <c r="V8" t="n">
+        <v>-6.799999999999999</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-8.111111111111109</v>
+      </c>
+      <c r="X8" t="n">
+        <v>2.220446049250313e-16</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>-0.2222222222222223</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>-0.4736842105263159</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>8.385695611577965</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>5.958093753576733</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>123.8112196506603</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>123.4108442943761</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>-86</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>-39.14285714285714</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>-20</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>-27.21428571428572</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>-1.000000000000004</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>-1.631578947368425</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>9.599999999999994</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>-8.666666666666671</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>46</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>-138.4117647058823</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0.6830065359477127</v>
+      </c>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="n">
+        <v>-0.08333333333333331</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0.1666666666666643</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>-0.2631578947368407</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>-2.287065602697826</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>24.49024343169835</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>-0.005568437113302981</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>-0.04451646003810688</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0.7370851370851383</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0.6591269841269844</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>-1.623421649361497</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>7836.352786728719</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>0.1751641007280107</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>-4.186224489795933</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>5.078968253968242</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>13116.77489177489</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>38085714.28571428</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0.9097763347763532</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>4.471608946608953</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>2.953699725504237</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>117000</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>5.999999999999999</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>-3.15425170068027</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>5.983715240482169</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>224.4285714285714</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>5391316.73881674</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>240.1428571428571</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>0.9778613199665926</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>3650474.40028643</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>jVWMBdG5</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45598.47916666666</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gerach t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allianz arena
+  munich </t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>pzHW4oaE</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="G9" t="n">
         <v>59</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H9" t="n">
         <v>591</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I9" t="n">
         <v>0</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J9" t="n">
         <v>20242025</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>germany</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>K6A2elS9</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>hpYJ6izc</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.246</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.708235294117647</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.578947368421053</v>
+      </c>
+      <c r="T9" t="n">
+        <v>7.799999999999999</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3.611111111111111</v>
+      </c>
+      <c r="V9" t="n">
+        <v>17</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8.611111111111111</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.055555555555555</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.263157894736842</v>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>-inf</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>-inf</t>
+        </is>
+      </c>
+      <c r="AD9" t="n">
+        <v>-334.3986093946495</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>-231.3581709345638</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>186</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>63.42857142857142</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>61</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>29.71428571428572</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>10.66666666666667</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>6.263157894736842</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>48.80000000000001</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>37.11111111111111</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>636</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>481.1176470588236</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0.3999999999999999</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>-0.6875</v>
+      </c>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="n">
+        <v>-3.333333333333336</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>-3.578947368421053</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>-55.41139974622637</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>-31.08841723027799</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0.01753125509434089</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>-0.0116297834819149</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0.3728715728715741</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>1.792063492063492</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0.373099941731077</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>48018.108795475</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>1.478027216284625</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>5.980952380952374</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>7.97258297258297</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>52037.37373737372</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>90507142.85714285</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>-2.748484848484821</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>8.352669552669539</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>8.022982877361486</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>141714.2857142857</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>4.571428571428572</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>-6.904761904761912</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>7.817549867450353</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>202</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>40489613.997114</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>251.8571428571428</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>0.5885165199683513</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>30359804.68823833</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>IHYEDIog</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45597.6875</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stieler t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bayarena
+  leverkusen </t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>59</v>
+      </c>
+      <c r="H10" t="n">
+        <v>591</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
         <is>
           <t>hAcTWKKN</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>GzfvcwRj</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.4559999999999993</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.9693888888888891</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.022727272727272</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.907268170426065</v>
+      </c>
+      <c r="V10" t="n">
+        <v>5</v>
+      </c>
+      <c r="W10" t="n">
+        <v>4.804511278195488</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.5999999999999999</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.5238095238095239</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.145454545454546</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>3.341327561327561</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-0.09265497799332367</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>140.4162225069409</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>110.7923283894642</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>39</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>10.45882352941176</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>38</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>32.70196078431373</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.166666666666668</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>6.327272727272724</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>3.200000000000003</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>-2.952380952380949</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>89.20000000000005</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>-30.11111111111109</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0.3289473684210529</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>-1.666666666666664</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>-2.045454545454545</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>12.43671058476038</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>-1.594759265257117</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0.04128179021796043</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0.01365380138206914</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0.01818181818181819</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>1.570544733044731</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>1.645165945165945</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0.2567727529608348</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>56548.54661162711</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0.7777872991301784</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>-2.435374149659907</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>6.531367243867237</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>74075.84776334776</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>35550000</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>-1.715945165945158</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>-3.071428571428571</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>7.782683982683977</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>6.9970391665438</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>56571.42857142857</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>-1.071428571428571</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>4.766326530612243</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>6.265552361295391</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>-194.4285714285714</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>38165264.7005772</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>-229.5714285714286</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>-4.493546673055192</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>28149954.55089931</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>zyC4c6ee</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45592.64583333334</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">storks s 
+  ger </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">voith arena
+  heidenheim </t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>59</v>
+      </c>
+      <c r="H11" t="n">
+        <v>591</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>M5BRZDsC</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>8f6APkLc</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.346666666666666</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.6488888888888884</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.105263157894737</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.499999999999999</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.894736842105263</v>
+      </c>
+      <c r="V11" t="n">
+        <v>6.833333333333332</v>
+      </c>
+      <c r="W11" t="n">
+        <v>4.105263157894736</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.4210526315789476</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.1578947368421053</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>-3.917269386387033</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>-3.648793932126676</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>44.33520432812224</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>17.11424760591012</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>-13.5</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>-24.66666666666667</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>-17</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>-6.400000000000006</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>-8.666666666666671</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>-2.947368421052637</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>-8.666666666666671</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>-9.157894736842096</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>-3.833333333333258</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>-95.66666666666663</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>-1.105263157894737</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>1.833333333333332</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>3.526315789473687</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>-6.991944347230795</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>-11.60689255032138</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>-0.127552353084268</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>-0.01821903569119519</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0.1052631578947368</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>-0.6539682539682588</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>-0.6448412698412702</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>1.686147304078002</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>-3994.846847968776</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>-0.137897019982669</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>4.733843537414941</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>-4.264682539682539</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>-8186.904761904763</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>-35703571.42857143</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>1.098015873015839</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>-3.714285714285714</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>-2.55992063492063</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>-1.589699144341182</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>-120000</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>-6.857142857142857</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>-1.150510204081638</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>-5.437696207392207</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>-292.7142857142857</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>-4553134.920634922</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>-306</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>-0.89072863317719</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>-3216553.638236377</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>ABBmcc1C</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45592.5625</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brych f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadion an der alten forsterei
+  berlin </t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>59</v>
+      </c>
+      <c r="H12" t="n">
+        <v>591</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>A15eUM4C</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>UgdQz0fK</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>-0.3072222222222218</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-1.110223024625157e-16</v>
+      </c>
+      <c r="S12" t="n">
+        <v>-0.3157894736842104</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-0.3157894736842097</v>
+      </c>
+      <c r="V12" t="n">
+        <v>6.666666666666666</v>
+      </c>
+      <c r="W12" t="n">
+        <v>-0.5789473684210531</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>-0.4210526315789476</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-0.4736842105263157</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>-4.405980960760374</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>-0.928355427139441</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>-37.82321702295715</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>55.89168543233939</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>-49</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>-35.40000000000001</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>-8.866666666666667</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>4.666666666666675</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>-4.84210526315789</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>-1.666666666666671</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>-8.947368421052644</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>-26.16666666666663</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>-126.6111111111111</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>-0.3888888888888886</v>
+      </c>
+      <c r="AR12" t="inlineStr"/>
+      <c r="AS12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>1.333333333333339</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>3.210526315789473</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>-1.16800971660734</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>-9.492173010455559</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0.03305785279007403</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>-0.0009351352108242575</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>2.775557561562891e-17</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>-0.05263157894736842</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>2.314430014430016</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>-0.2865079365079366</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>3.539449815013725</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>-1153.117100109579</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>-0.3090778895290174</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>1.190476190476147</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>-3.974170274170277</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>-7259.595959595961</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>11496428.57142857</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>1.008008658008606</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>0.8571428571428572</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>-1.926479076479069</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>0.1304690297171334</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>73428.57142857143</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>1.571428571428572</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>9.476190476190482</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>-5.068253425772227</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>87.85714285714288</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>-8669296.536796536</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>57.71428571428572</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>-1.895693237422591</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>-5055049.59910599</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>WQadeyWO</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45592.47916666666</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stieler t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vonovia ruhrstadion
+  bochum </t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>59</v>
+      </c>
+      <c r="H13" t="n">
+        <v>591</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>KUx4Q7x1</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>GzfvcwRj</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-3.575</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>-2.301722222222222</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-5</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-2.578947368421053</v>
+      </c>
+      <c r="T13" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-4.521303258145363</v>
+      </c>
+      <c r="V13" t="n">
+        <v>-19.5</v>
+      </c>
+      <c r="W13" t="n">
+        <v>-8.005012531328322</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-4.166666666666666</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>-2.879699248120301</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-2.977443609022556</v>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="AD13" t="n">
+        <v>272.3259625298296</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>203.7566976091855</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>-27</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>-5.35294117647058</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>-41</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>-16.3921568627451</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>-4.959899749373442</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>-42</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>-25.80952380952381</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>-514.5</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>-310.0055555555556</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.397759103641457</v>
+      </c>
+      <c r="AR13" t="inlineStr"/>
+      <c r="AS13" t="inlineStr"/>
+      <c r="AT13" t="n">
+        <v>2.666666666666671</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>1.822055137844611</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>53.00379899116727</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>31.08316123593318</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0.03681870812779452</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0.04269159330149178</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>-0.6666666666666666</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>-0.5488721804511278</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.140476190476186</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>-2.177777777777778</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>-1.028188778885376</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>-57835.8187134503</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>-1.601192271780507</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>1.740476190476215</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>-11.91044973544973</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>-62174.07407407407</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>-96232142.85714285</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>1.991865079365056</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>-1.714285714285714</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>-11.42619047619047</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>-12.60668847836031</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>-163857.1428571429</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>-3.857142857142858</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>4.714285714285715</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>-9.670200293342717</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>-131.8571428571428</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>-44600062.83068783</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>-170.5714285714286</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>2.19470456873708</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>-32822050.98081744</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>MiACepQ7</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45591.5625</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brych f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">weserstadion
+  bremen </t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>59</v>
+      </c>
+      <c r="H14" t="n">
+        <v>591</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>f3ddUIXs</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>UgdQz0fK</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-1.786666666666666</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-1.968253968253968</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-1.785714285714286</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-2.066985645933014</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-4.666666666666667</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-4.717703349282298</v>
+      </c>
+      <c r="V14" t="n">
+        <v>-12.80952380952381</v>
+      </c>
+      <c r="W14" t="n">
+        <v>-12.11961722488038</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-1.047619047619047</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>-1.703349282296651</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-0.7857142857142856</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-2.181818181818182</v>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="AD14" t="n">
+        <v>-10.02520646788361</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>67.86783391528121</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>-70.33333333333334</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>-64.12222222222222</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>-47.16666666666666</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>-51.91111111111111</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>-11.97619047619048</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>-9.232057416267949</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>-14.0952380952381</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>-17.73205741626793</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>-217.9999999999999</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>-255.5584795321637</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>-2.261904761904762</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>-0.7619047619047619</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>-0.126984126984127</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0.8333333333333321</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0.3540669856459342</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>38.03796811983701</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>41.55728787315739</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>-0.05427421204837672</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>-0.01933830273660526</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>-0.4761904761904762</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>-0.5215311004784688</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0.65169552669553</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>-2.025324675324675</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>-0.1465236895673598</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>-61203.69744631783</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>-1.260791685095091</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>4.009523809523813</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>-9.368398268398266</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>-78090.25974025973</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>-48128571.42857143</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>-0.854870129870136</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>-9.583261183261172</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>-10.29334960077921</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>-75714.28571428571</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>-0.1404761904761891</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>-7.862002396132155</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>91</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>-45940422.07792208</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>95.57142857142858</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>6.020903157740491</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>-35145227.6275863</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>rwXP4l3L</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45591.4375</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gerach t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mhparena
+  stuttgart </t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>59</v>
+      </c>
+      <c r="H15" t="n">
+        <v>591</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>K6A2elS9</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>hpYJ6izc</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.8326023391812862</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.785714285714286</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.9078947368421052</v>
+      </c>
+      <c r="T15" t="n">
+        <v>4.976190476190476</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.978947368421052</v>
+      </c>
+      <c r="V15" t="n">
+        <v>13.07142857142857</v>
+      </c>
+      <c r="W15" t="n">
+        <v>7.813157894736841</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2.833333333333333</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.8421052631578947</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.5763157894736841</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>-8.401940321583178</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>-3.856856885804254</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>-294.5019424864247</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>-160.6489352456286</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>32.39583333333333</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>61.33333333333334</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>20.35833333333333</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>9.380952380952387</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>5.018421052631581</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>24.61904761904762</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>17.16315789473684</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>289.3333333333333</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>233.0935672514619</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0.6190476190476188</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>-0.07368421052631557</v>
+      </c>
+      <c r="AR15" t="inlineStr"/>
+      <c r="AS15" t="n">
+        <v>-0.8333333333333333</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>1.69047619047619</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>-1.084210526315792</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>-26.34187730788858</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>-9.884795596496737</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>-0.002783979467607195</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0.01730762691596557</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0.0368421052631579</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>-1.758639971139967</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0.4762626262626264</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>-1.532912346860943</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>8135.815275767056</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>0.4830043859649122</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>-4.707482993197232</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>7.318632756132772</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>10942.00937950938</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>19207142.85714286</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>0.170310245310219</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>2.428571428571428</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>6.352236652236655</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>5.179616289689022</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>51000.00000000001</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>3.428571428571428</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>-2.921088435374145</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>5.521453867588235</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>172.1428571428572</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>11851640.06132756</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>201.2857142857143</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>0.4894660629316547</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>8653238.661645053</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Mku6FvHt</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45591.4375</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">schlager d 
+  ger </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">millerntor stadion
+  hamburg </t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>59</v>
+      </c>
+      <c r="H16" t="n">
+        <v>591</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
         <is>
           <t>IkCftsQm</t>
         </is>
       </c>
-      <c r="O3" t="n">
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>4fuCGs9P</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
         <v>0</v>
       </c>
-      <c r="P3" t="n">
-        <v>-1.243333333333333</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>-0.1272222222222223</v>
-      </c>
-      <c r="R3" t="n">
-        <v>-0.9999999999999999</v>
-      </c>
-      <c r="S3" t="n">
-        <v>-0.1578947368421051</v>
-      </c>
-      <c r="T3" t="n">
-        <v>-3.833333333333333</v>
-      </c>
-      <c r="U3" t="n">
-        <v>-0.3684210526315788</v>
-      </c>
-      <c r="V3" t="n">
-        <v>-9.333333333333332</v>
-      </c>
-      <c r="W3" t="n">
-        <v>-2.894736842105262</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-2</v>
-      </c>
-      <c r="Y3" t="n">
+      <c r="P16" t="n">
+        <v>-0.001666666666666816</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.1327777777777781</v>
+      </c>
+      <c r="R16" t="n">
+        <v>-1.110223024625157e-16</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.3157894736842104</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-0.3333333333333335</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.5263157894736841</v>
+      </c>
+      <c r="V16" t="n">
+        <v>4.166666666666666</v>
+      </c>
+      <c r="W16" t="n">
+        <v>3.052631578947366</v>
+      </c>
+      <c r="X16" t="n">
+        <v>-0.6666666666666666</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.3684210526315788</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AA16" t="n">
         <v>0.631578947368421</v>
       </c>
-      <c r="Z3" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0.7894736842105263</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>4.001518620268621</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.002671378329273</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>-26.51163913248672</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>-138.0127378590239</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>-6.000000000000014</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>-43.00000000000001</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>-7.6875</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>-2.333333333333336</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>-2.210526315789473</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>7.666666666666671</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>14.42105263157895</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>47.99999999999994</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>184.8888888888889</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>-1.833333333333333</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>-0.7456140350877192</v>
-      </c>
-      <c r="AR3" t="inlineStr"/>
-      <c r="AS3" t="n">
+      <c r="AB16" t="n">
+        <v>-5.182391845627139</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>-3.61013214466449</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>-153.0061458087206</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>-177.6781415205782</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>-10</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>30.46666666666667</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>-32</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>13.93333333333333</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>2.666666666666657</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0.6315789473684248</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>-0.6666666666666714</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>12.52631578947368</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>29.00000000000006</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>202.7222222222222</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>-2.566666666666666</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>-0.6023391812865497</v>
+      </c>
+      <c r="AR16" t="inlineStr"/>
+      <c r="AS16" t="n">
+        <v>0.2083333333333333</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>-5.833333333333339</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>-2.052631578947366</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>6.436392345330528</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>-16.43726488022848</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0.0123407177838121</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0.0225101626541523</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>-0.3333333333333334</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>-0.1052631578947368</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>2.152597402597401</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>-0.3916666666666662</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>0.6975618636609333</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>-17335.24073106116</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>-0.4198584138599617</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>3.383333333333354</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>-6.282539682539664</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>-18785.82251082251</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>-50514285.71428572</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>0.6485569985569839</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>-1.142857142857142</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>-4.477958152958166</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>-5.29472444480183</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>-128571.4285714286</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>-3.857142857142857</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>5.109523809523807</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>-6.473707273978192</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>-117.8571428571428</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>-7597269.119769119</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>-136.5714285714286</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>-0.153431651767562</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>-6540368.071471012</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>ELNeaSQr</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45591.4375</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dankert b 
+  ger </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">red bull arena
+  leipzig </t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>59</v>
+      </c>
+      <c r="H17" t="n">
+        <v>591</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>vZA6VYpf</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2VSFgl3c</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>-0.3466666666666669</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.6577777777777778</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.110223024625157e-16</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.7894736842105262</v>
+      </c>
+      <c r="T17" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.578947368421053</v>
+      </c>
+      <c r="V17" t="n">
+        <v>-6.666666666666668</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.842105263157896</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.263157894736842</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.578947368421052</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>-2.154208754208755</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>-3.527500890051013</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>-175.8606676483772</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>-185.512282311278</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>26.80000000000001</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>-15.5</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>17.93333333333334</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>-4.166666666666671</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>4.94736842105263</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>2.333333333333329</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>12.31578947368421</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>100.8333333333333</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>175.4999999999999</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0.09999999999999987</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>-0.564327485380117</v>
+      </c>
+      <c r="AR17" t="inlineStr"/>
+      <c r="AS17" t="n">
         <v>-0.6666666666666667</v>
       </c>
-      <c r="AT3" t="n">
-        <v>1.666666666666668</v>
-      </c>
-      <c r="AU3" t="n">
+      <c r="AT17" t="n">
+        <v>-0.6666666666666643</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>-0.9473684210526319</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>-10.62790786115386</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>-14.40414641130682</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>-0.05502310427071028</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>-0.0154848222235259</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0.1578947368421053</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>-1.025613275613281</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>0.6248556998556998</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>-0.9697325060667055</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>28442.73683712442</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>0.5750691456112296</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>-2.926870748299308</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>5.351479076479094</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>30921.28427128426</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>29142857.14285714</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>-0.3693362193361907</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>-2.142857142857143</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>4.302958152958141</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>4.377248121702053</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>45571.42857142858</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>1.142857142857143</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>-1.699659863945577</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>5.123074758646268</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>-135.4285714285714</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>20518524.53102453</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>-130.2857142857143</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>1.042329297366251</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>17293006.10192763</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>x0haJmIE</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45591.4375</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jollenbeck m 
+  ger </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wwk arena
+  augsburg </t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>fTVNku3I</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>59</v>
+      </c>
+      <c r="H18" t="n">
+        <v>591</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>YZPE6Sx7</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0jdIgO6t</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>-0.3716666666666668</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>-0.648333333333333</v>
+      </c>
+      <c r="R18" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="S18" t="n">
         <v>-0.6315789473684212</v>
       </c>
-      <c r="AV3" t="n">
-        <v>-4.619139542563182</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>-10.65697253732944</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>-0.006266876116679844</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>-0.03151796441786024</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>-0.1666666666666667</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>0.4736842105263158</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>-4.843434343434353</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>-9194.626663276553</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>-156</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>-4.752397297591799</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>-0.3893939393939396</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>-4</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>-2</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>-0.1349206349206351</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>-4526435.185185185</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>-3.242583814608992</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>-0.9495791245791168</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>2.096168561500377</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>-0.6711373845241084</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>-2321056.203310208</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>-20100000</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>-10615.5303030303</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>-5.404629629629625</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>-0.06898148148147953</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>-162</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>-3</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>-98000</v>
+      <c r="T18" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="U18" t="n">
+        <v>-2.842105263157896</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0.8333333333333339</v>
+      </c>
+      <c r="W18" t="n">
+        <v>-0.7894736842105257</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>-1.105263157894737</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-1.578947368421052</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>-1.889589685913216</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>-0.4712571364416727</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>124.3423941169303</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>108.5109366517813</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>-11</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>-18.46666666666667</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>5.466666666666669</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>-4.315789473684209</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>-23</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>-21.89473684210526</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>-257.6666666666666</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>-278.7222222222222</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>-0.3859649122807016</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0.3333333333333357</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>3.894736842105262</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>16.05100217360426</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>3.361368767148406</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0.09609284185745956</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0.02609042386851434</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>-0.1578947368421053</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>-0.8741883116883109</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>-1.512662337662337</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>-0.1140103957816372</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>-22164.84401090025</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>-0.7205971255432344</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>-0.178571428571388</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>-7.272077922077941</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>-36169.96753246753</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>-32917857.14285714</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>-1.009090909090901</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>2.714285714285714</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>-8.350000000000009</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>-5.184174488393225</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>857.1428571428551</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>0.5714285714285712</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>3.347619047619052</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>-6.171988533295576</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>179.8571428571429</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>-32467532.46753247</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>174.8571428571429</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>0.2212646441281834</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>-16808052.20857499</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>4E8uaJWa</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45590.64583333334</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">siebert d 
+  ger </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mewa arena
+  mainz </t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>59</v>
+      </c>
+      <c r="H19" t="n">
+        <v>591</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>vZA6VYpf</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>4ljanukM</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>-1.483333333333333</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>-0.344970760233918</v>
+      </c>
+      <c r="R19" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="S19" t="n">
+        <v>-0.1578947368421053</v>
+      </c>
+      <c r="T19" t="n">
+        <v>-4.833333333333334</v>
+      </c>
+      <c r="U19" t="n">
+        <v>-1.15</v>
+      </c>
+      <c r="V19" t="n">
+        <v>-10.33333333333333</v>
+      </c>
+      <c r="W19" t="n">
+        <v>-0.3342105263157897</v>
+      </c>
+      <c r="X19" t="n">
+        <v>2.220446049250313e-16</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.8210526315789475</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.231578947368421</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>4.498872124607418</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.551447966225779</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>187.1590683149671</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>85.90149454391954</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>36</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>30.37083333333334</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>9.495833333333337</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>-11.83333333333333</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>-0.3500000000000014</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>-26.66666666666667</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>-9.336842105263159</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>-274.3333333333334</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>-91.5555555555556</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>2.220446049250313e-16</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0.6842105263157894</v>
+      </c>
+      <c r="AR19" t="inlineStr"/>
+      <c r="AS19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0.6947368421052644</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>17.97077793280251</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>5.438918014249737</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>-0.03816941941941943</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>-0.01899048350800872</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0.1552631578947369</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>1.266666666666666</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>-0.06190476190476213</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>-0.1954239070290029</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>-758.4479974640126</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>-0.05451502839538147</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>2.838095238095264</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>-0.734920634920627</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>831.7460317460282</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>-12019285.71428571</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>-1.469841269841226</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>-3.085714285714285</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>-0.7333333333333343</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>-2.146333012089798</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>-21085.71428571428</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>-3.685714285714285</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>5.528571428571425</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>-0.3073175598510431</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>-203.1714285714285</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>-1630317.460317461</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>-238.6571428571428</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>0.3288183756964429</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>-2569367.86312195</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/data_preparation/df_constructed.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_constructed.xlsx
@@ -695,112 +695,112 @@
       </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_start</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_age_player_start</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_value_player_sub</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_value_player_start</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_sub</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_value_player_miss</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_wage_player_miss</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_rep_player_start</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_sub</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_miss</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_start</t>
-        </is>
-      </c>
-      <c r="BJ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_value_player_miss</t>
-        </is>
-      </c>
-      <c r="BK1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="BL1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="BM1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="BN1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="BO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_wage_player_miss</t>
-        </is>
-      </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>dif_sum_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="BQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="BR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="BS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="BT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_start</t>
-        </is>
-      </c>
-      <c r="BU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="BV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="BW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_sub</t>
         </is>
       </c>
     </row>
@@ -987,70 +987,70 @@
         <v>0.1078947368421052</v>
       </c>
       <c r="BB2" t="n">
-        <v>-0.8298701298701303</v>
+        <v>1.285714285714286</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.361038961038961</v>
+        <v>925.9740259740283</v>
       </c>
       <c r="BD2" t="n">
         <v>1.268564527260178</v>
       </c>
       <c r="BE2" t="n">
+        <v>-0.8298701298701303</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>2466642.363484469</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>106.2857142857142</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>2120779.220779221</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>0.2085999159389156</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>1.50129870129868</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>2.960163843638824</v>
+      </c>
+      <c r="BL2" t="n">
         <v>2817.91196889268</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>0.2085999159389156</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>-3.247619047619082</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>0.9636363636363683</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>925.9740259740283</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>10067857.14285714</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>1.50129870129868</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>1.285714285714286</v>
       </c>
       <c r="BM2" t="n">
         <v>1.075324675324666</v>
       </c>
       <c r="BN2" t="n">
-        <v>2.960163843638824</v>
+        <v>0.9636363636363683</v>
       </c>
       <c r="BO2" t="n">
+        <v>76.57142857142856</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>10067857.14285714</v>
+      </c>
+      <c r="BQ2" t="n">
         <v>-10000</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>2.285714285714286</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>-5.238095238095237</v>
       </c>
       <c r="BR2" t="n">
         <v>0.7780433815575805</v>
       </c>
       <c r="BS2" t="n">
-        <v>76.57142857142856</v>
+        <v>-5.238095238095237</v>
       </c>
       <c r="BT2" t="n">
-        <v>2120779.220779221</v>
+        <v>0.361038961038961</v>
       </c>
       <c r="BU2" t="n">
-        <v>106.2857142857142</v>
+        <v>-3.247619047619082</v>
       </c>
       <c r="BV2" t="n">
         <v>-3.505181644115964</v>
       </c>
       <c r="BW2" t="n">
-        <v>2466642.363484469</v>
+        <v>2.285714285714286</v>
       </c>
     </row>
     <row r="3">
@@ -1232,70 +1232,70 @@
         <v>0.05263157894736842</v>
       </c>
       <c r="BB3" t="n">
-        <v>-0.7222222222222179</v>
+        <v>4.228571428571429</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.234920634920635</v>
+        <v>1158.730158730163</v>
       </c>
       <c r="BD3" t="n">
         <v>1.149829401284123</v>
       </c>
       <c r="BE3" t="n">
+        <v>-0.7222222222222179</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>3597642.711026579</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>313.0857142857143</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>4563650.793650795</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>0.2359846538990051</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>0.4857142857142378</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>3.05070072131204</v>
+      </c>
+      <c r="BL3" t="n">
         <v>2449.405274903802</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>0.2359846538990051</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>0.5530612244898236</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>1.907936507936483</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>1158.730158730163</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>16180000</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>0.4857142857142378</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>4.228571428571429</v>
       </c>
       <c r="BM3" t="n">
         <v>1.566666666666677</v>
       </c>
       <c r="BN3" t="n">
-        <v>3.05070072131204</v>
+        <v>1.907936507936483</v>
       </c>
       <c r="BO3" t="n">
+        <v>295.7428571428571</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>16180000</v>
+      </c>
+      <c r="BQ3" t="n">
         <v>68514.28571428571</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>4.257142857142856</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>-1.295578231292517</v>
       </c>
       <c r="BR3" t="n">
         <v>0.03996262536634276</v>
       </c>
       <c r="BS3" t="n">
-        <v>295.7428571428571</v>
+        <v>-1.295578231292517</v>
       </c>
       <c r="BT3" t="n">
-        <v>4563650.793650795</v>
+        <v>0.234920634920635</v>
       </c>
       <c r="BU3" t="n">
-        <v>313.0857142857143</v>
+        <v>0.5530612244898236</v>
       </c>
       <c r="BV3" t="n">
         <v>0.1336152351517228</v>
       </c>
       <c r="BW3" t="n">
-        <v>3597642.711026579</v>
+        <v>4.257142857142856</v>
       </c>
     </row>
     <row r="4">
@@ -1477,70 +1477,70 @@
         <v>-0.2631578947368421</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.035714285714285</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.3826479076479075</v>
+        <v>1363.564213564212</v>
       </c>
       <c r="BD4" t="n">
         <v>-0.8847936314113802</v>
       </c>
       <c r="BE4" t="n">
+        <v>1.035714285714285</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>-2535884.185759455</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>-106.7142857142857</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>6265674.603174608</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>-0.1196040665763567</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>2.419696969696957</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>-1.021867976439594</v>
+      </c>
+      <c r="BL4" t="n">
         <v>-9309.288544833369</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>-0.1196040665763567</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>1.749999999999943</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>-0.1738455988455883</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>1363.564213564212</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>-9000000</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>2.419696969696957</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>-1.285714285714286</v>
       </c>
       <c r="BM4" t="n">
         <v>1.463708513708525</v>
       </c>
       <c r="BN4" t="n">
-        <v>-1.021867976439594</v>
+        <v>-0.1738455988455883</v>
       </c>
       <c r="BO4" t="n">
+        <v>-98.57142857142858</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>-9000000</v>
+      </c>
+      <c r="BQ4" t="n">
         <v>-67857.14285714286</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>-2.857142857142857</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>-1.821428571428573</v>
       </c>
       <c r="BR4" t="n">
         <v>0.6838839613232324</v>
       </c>
       <c r="BS4" t="n">
-        <v>-98.57142857142858</v>
+        <v>-1.821428571428573</v>
       </c>
       <c r="BT4" t="n">
-        <v>6265674.603174608</v>
+        <v>0.3826479076479075</v>
       </c>
       <c r="BU4" t="n">
-        <v>-106.7142857142857</v>
+        <v>1.749999999999943</v>
       </c>
       <c r="BV4" t="n">
         <v>-0.3019751181104766</v>
       </c>
       <c r="BW4" t="n">
-        <v>-2535884.185759455</v>
+        <v>-2.857142857142857</v>
       </c>
     </row>
     <row r="5">
@@ -1722,70 +1722,70 @@
         <v>0.2330827067669173</v>
       </c>
       <c r="BB5" t="n">
-        <v>-3.827777777777776</v>
+        <v>-2</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.6722222222222225</v>
+        <v>17396.2962962963</v>
       </c>
       <c r="BD5" t="n">
         <v>-2.884360977859426</v>
       </c>
       <c r="BE5" t="n">
+        <v>-3.827777777777776</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>7517295.8916851</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>-139</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>12779745.37037037</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>0.4322429450248999</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>-0.2513888888888403</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>4.453236571281693</v>
+      </c>
+      <c r="BL5" t="n">
         <v>10970.82701808487</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>0.4322429450248999</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>-8.911904761904736</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>7.912037037037038</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>17396.2962962963</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>-5771428.571428573</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>-0.2513888888888403</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>-2</v>
       </c>
       <c r="BM5" t="n">
         <v>5</v>
       </c>
       <c r="BN5" t="n">
-        <v>4.453236571281693</v>
+        <v>7.912037037037038</v>
       </c>
       <c r="BO5" t="n">
+        <v>-158</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>-5771428.571428573</v>
+      </c>
+      <c r="BQ5" t="n">
         <v>-51285.71428571429</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>-2.285714285714286</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>-7.285714285714285</v>
       </c>
       <c r="BR5" t="n">
         <v>6.92090385166459</v>
       </c>
       <c r="BS5" t="n">
-        <v>-158</v>
+        <v>-7.285714285714285</v>
       </c>
       <c r="BT5" t="n">
-        <v>12779745.37037037</v>
+        <v>0.6722222222222225</v>
       </c>
       <c r="BU5" t="n">
-        <v>-139</v>
+        <v>-8.911904761904736</v>
       </c>
       <c r="BV5" t="n">
         <v>-0.8875278512828402</v>
       </c>
       <c r="BW5" t="n">
-        <v>7517295.8916851</v>
+        <v>-2.285714285714286</v>
       </c>
     </row>
     <row r="6">
@@ -1967,70 +1967,70 @@
         <v>0.1578947368421053</v>
       </c>
       <c r="BB6" t="n">
-        <v>-0.2623015873015859</v>
+        <v>-0.8571428571428572</v>
       </c>
       <c r="BC6" t="n">
-        <v>-0.01428571428571423</v>
+        <v>-5582.142857142859</v>
       </c>
       <c r="BD6" t="n">
         <v>-0.1651255467862214</v>
       </c>
       <c r="BE6" t="n">
+        <v>-0.2623015873015859</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>-279511.0057753078</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>-59.85714285714286</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>-1280119.047619048</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>-0.03726708074534169</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>-1.286507936507888</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>-1.052587213375048</v>
+      </c>
+      <c r="BL6" t="n">
         <v>-4035.372592973117</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>-0.03726708074534169</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>1.333333333333343</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>-2.116666666666674</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>-5582.142857142859</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>-1996428.571428572</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>-1.286507936507888</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>-0.8571428571428572</v>
       </c>
       <c r="BM6" t="n">
         <v>-2.74126984126984</v>
       </c>
       <c r="BN6" t="n">
-        <v>-1.052587213375048</v>
+        <v>-2.116666666666674</v>
       </c>
       <c r="BO6" t="n">
+        <v>-55.57142857142858</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>-1996428.571428572</v>
+      </c>
+      <c r="BQ6" t="n">
         <v>-20714.28571428572</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>-1.142857142857143</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>0.8095238095238066</v>
       </c>
       <c r="BR6" t="n">
         <v>0.4708938495306683</v>
       </c>
       <c r="BS6" t="n">
-        <v>-55.57142857142858</v>
+        <v>0.8095238095238066</v>
       </c>
       <c r="BT6" t="n">
-        <v>-1280119.047619048</v>
+        <v>-0.01428571428571423</v>
       </c>
       <c r="BU6" t="n">
-        <v>-59.85714285714286</v>
+        <v>1.333333333333343</v>
       </c>
       <c r="BV6" t="n">
         <v>-0.2437405625865665</v>
       </c>
       <c r="BW6" t="n">
-        <v>-279511.0057753078</v>
+        <v>-1.142857142857143</v>
       </c>
     </row>
     <row r="7">
@@ -2214,70 +2214,70 @@
         <v>0.2105263157894737</v>
       </c>
       <c r="BB7" t="n">
-        <v>-1.287499999999998</v>
+        <v>0.5714285714285712</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.2666666666666662</v>
+        <v>13479.16666666667</v>
       </c>
       <c r="BD7" t="n">
         <v>0.5730678236206757</v>
       </c>
       <c r="BE7" t="n">
+        <v>-1.287499999999998</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>3284005.811255922</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>76.42857142857139</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>4591944.444444444</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>0.294920918925784</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>-0.5277777777777715</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>1.06426801182991</v>
+      </c>
+      <c r="BL7" t="n">
         <v>12570.96941647473</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>0.294920918925784</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>-0.9190476190476318</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>3.061111111111103</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>13479.16666666667</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>42046428.57142857</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>-0.5277777777777715</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>0.5714285714285712</v>
       </c>
       <c r="BM7" t="n">
         <v>1.430555555555557</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.06426801182991</v>
+        <v>3.061111111111103</v>
       </c>
       <c r="BO7" t="n">
+        <v>58</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>42046428.57142857</v>
+      </c>
+      <c r="BQ7" t="n">
         <v>104428.5714285714</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>3.285714285714286</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>-2.140476190476189</v>
       </c>
       <c r="BR7" t="n">
         <v>1.386131924859285</v>
       </c>
       <c r="BS7" t="n">
-        <v>58</v>
+        <v>-2.140476190476189</v>
       </c>
       <c r="BT7" t="n">
-        <v>4591944.444444444</v>
+        <v>0.2666666666666662</v>
       </c>
       <c r="BU7" t="n">
-        <v>76.42857142857139</v>
+        <v>-0.9190476190476318</v>
       </c>
       <c r="BV7" t="n">
         <v>0.3743461898316127</v>
       </c>
       <c r="BW7" t="n">
-        <v>3284005.811255922</v>
+        <v>3.285714285714286</v>
       </c>
     </row>
     <row r="8">
@@ -2459,70 +2459,70 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.7370851370851383</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.6591269841269844</v>
+        <v>13116.77489177489</v>
       </c>
       <c r="BD8" t="n">
         <v>-1.623421649361497</v>
       </c>
       <c r="BE8" t="n">
+        <v>0.7370851370851383</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>3650474.40028643</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>240.1428571428571</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>5391316.73881674</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>0.1751641007280107</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>0.9097763347763532</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>2.953699725504237</v>
+      </c>
+      <c r="BL8" t="n">
         <v>7836.352786728719</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>0.1751641007280107</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>-4.186224489795933</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>5.078968253968242</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>13116.77489177489</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>38085714.28571428</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>0.9097763347763532</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>2.571428571428571</v>
       </c>
       <c r="BM8" t="n">
         <v>4.471608946608953</v>
       </c>
       <c r="BN8" t="n">
-        <v>2.953699725504237</v>
+        <v>5.078968253968242</v>
       </c>
       <c r="BO8" t="n">
+        <v>224.4285714285714</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>38085714.28571428</v>
+      </c>
+      <c r="BQ8" t="n">
         <v>117000</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>5.999999999999999</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>-3.15425170068027</v>
       </c>
       <c r="BR8" t="n">
         <v>5.983715240482169</v>
       </c>
       <c r="BS8" t="n">
-        <v>224.4285714285714</v>
+        <v>-3.15425170068027</v>
       </c>
       <c r="BT8" t="n">
-        <v>5391316.73881674</v>
+        <v>0.6591269841269844</v>
       </c>
       <c r="BU8" t="n">
-        <v>240.1428571428571</v>
+        <v>-4.186224489795933</v>
       </c>
       <c r="BV8" t="n">
         <v>0.9778613199665926</v>
       </c>
       <c r="BW8" t="n">
-        <v>3650474.40028643</v>
+        <v>5.999999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -2706,70 +2706,70 @@
         <v>0.3157894736842105</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.3728715728715741</v>
+        <v>2.857142857142857</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.792063492063492</v>
+        <v>52037.37373737372</v>
       </c>
       <c r="BD9" t="n">
         <v>0.373099941731077</v>
       </c>
       <c r="BE9" t="n">
+        <v>0.3728715728715741</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>30359804.68823833</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>251.8571428571428</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>40489613.997114</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>1.478027216284625</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>-2.748484848484821</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>8.022982877361486</v>
+      </c>
+      <c r="BL9" t="n">
         <v>48018.108795475</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>1.478027216284625</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>5.980952380952374</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>7.97258297258297</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>52037.37373737372</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>90507142.85714285</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>-2.748484848484821</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>2.857142857142857</v>
       </c>
       <c r="BM9" t="n">
         <v>8.352669552669539</v>
       </c>
       <c r="BN9" t="n">
-        <v>8.022982877361486</v>
+        <v>7.97258297258297</v>
       </c>
       <c r="BO9" t="n">
+        <v>202</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>90507142.85714285</v>
+      </c>
+      <c r="BQ9" t="n">
         <v>141714.2857142857</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>4.571428571428572</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>-6.904761904761912</v>
       </c>
       <c r="BR9" t="n">
         <v>7.817549867450353</v>
       </c>
       <c r="BS9" t="n">
-        <v>202</v>
+        <v>-6.904761904761912</v>
       </c>
       <c r="BT9" t="n">
-        <v>40489613.997114</v>
+        <v>1.792063492063492</v>
       </c>
       <c r="BU9" t="n">
-        <v>251.8571428571428</v>
+        <v>5.980952380952374</v>
       </c>
       <c r="BV9" t="n">
         <v>0.5885165199683513</v>
       </c>
       <c r="BW9" t="n">
-        <v>30359804.68823833</v>
+        <v>4.571428571428572</v>
       </c>
     </row>
     <row r="10">
@@ -2953,70 +2953,70 @@
         <v>0.01818181818181819</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.570544733044731</v>
+        <v>-3.071428571428571</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.645165945165945</v>
+        <v>74075.84776334776</v>
       </c>
       <c r="BD10" t="n">
         <v>0.2567727529608348</v>
       </c>
       <c r="BE10" t="n">
+        <v>1.570544733044731</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>28149954.55089931</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>-229.5714285714286</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>38165264.7005772</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>0.7777872991301784</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>-1.715945165945158</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>6.9970391665438</v>
+      </c>
+      <c r="BL10" t="n">
         <v>56548.54661162711</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>0.7777872991301784</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>-2.435374149659907</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>6.531367243867237</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>74075.84776334776</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>35550000</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>-1.715945165945158</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>-3.071428571428571</v>
       </c>
       <c r="BM10" t="n">
         <v>7.782683982683977</v>
       </c>
       <c r="BN10" t="n">
-        <v>6.9970391665438</v>
+        <v>6.531367243867237</v>
       </c>
       <c r="BO10" t="n">
+        <v>-194.4285714285714</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>35550000</v>
+      </c>
+      <c r="BQ10" t="n">
         <v>56571.42857142857</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>-1.071428571428571</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>4.766326530612243</v>
       </c>
       <c r="BR10" t="n">
         <v>6.265552361295391</v>
       </c>
       <c r="BS10" t="n">
-        <v>-194.4285714285714</v>
+        <v>4.766326530612243</v>
       </c>
       <c r="BT10" t="n">
-        <v>38165264.7005772</v>
+        <v>1.645165945165945</v>
       </c>
       <c r="BU10" t="n">
-        <v>-229.5714285714286</v>
+        <v>-2.435374149659907</v>
       </c>
       <c r="BV10" t="n">
         <v>-4.493546673055192</v>
       </c>
       <c r="BW10" t="n">
-        <v>28149954.55089931</v>
+        <v>-1.071428571428571</v>
       </c>
     </row>
     <row r="11">
@@ -3200,70 +3200,70 @@
         <v>0.1052631578947368</v>
       </c>
       <c r="BB11" t="n">
-        <v>-0.6539682539682588</v>
+        <v>-3.714285714285714</v>
       </c>
       <c r="BC11" t="n">
-        <v>-0.6448412698412702</v>
+        <v>-8186.904761904763</v>
       </c>
       <c r="BD11" t="n">
         <v>1.686147304078002</v>
       </c>
       <c r="BE11" t="n">
+        <v>-0.6539682539682588</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>-3216553.638236377</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>-306</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>-4553134.920634922</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>-0.137897019982669</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>1.098015873015839</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>-1.589699144341182</v>
+      </c>
+      <c r="BL11" t="n">
         <v>-3994.846847968776</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>-0.137897019982669</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>4.733843537414941</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>-4.264682539682539</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>-8186.904761904763</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>-35703571.42857143</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>1.098015873015839</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>-3.714285714285714</v>
       </c>
       <c r="BM11" t="n">
         <v>-2.55992063492063</v>
       </c>
       <c r="BN11" t="n">
-        <v>-1.589699144341182</v>
+        <v>-4.264682539682539</v>
       </c>
       <c r="BO11" t="n">
+        <v>-292.7142857142857</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>-35703571.42857143</v>
+      </c>
+      <c r="BQ11" t="n">
         <v>-120000</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>-6.857142857142857</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>-1.150510204081638</v>
       </c>
       <c r="BR11" t="n">
         <v>-5.437696207392207</v>
       </c>
       <c r="BS11" t="n">
-        <v>-292.7142857142857</v>
+        <v>-1.150510204081638</v>
       </c>
       <c r="BT11" t="n">
-        <v>-4553134.920634922</v>
+        <v>-0.6448412698412702</v>
       </c>
       <c r="BU11" t="n">
-        <v>-306</v>
+        <v>4.733843537414941</v>
       </c>
       <c r="BV11" t="n">
         <v>-0.89072863317719</v>
       </c>
       <c r="BW11" t="n">
-        <v>-3216553.638236377</v>
+        <v>-6.857142857142857</v>
       </c>
     </row>
     <row r="12">
@@ -3445,70 +3445,70 @@
         <v>-0.05263157894736842</v>
       </c>
       <c r="BB12" t="n">
-        <v>2.314430014430016</v>
+        <v>0.8571428571428572</v>
       </c>
       <c r="BC12" t="n">
-        <v>-0.2865079365079366</v>
+        <v>-7259.595959595961</v>
       </c>
       <c r="BD12" t="n">
         <v>3.539449815013725</v>
       </c>
       <c r="BE12" t="n">
+        <v>2.314430014430016</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>-5055049.59910599</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>57.71428571428572</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>-8669296.536796536</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>-0.3090778895290174</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>1.008008658008606</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>0.1304690297171334</v>
+      </c>
+      <c r="BL12" t="n">
         <v>-1153.117100109579</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>-0.3090778895290174</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>1.190476190476147</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>-3.974170274170277</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>-7259.595959595961</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>11496428.57142857</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>1.008008658008606</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>0.8571428571428572</v>
       </c>
       <c r="BM12" t="n">
         <v>-1.926479076479069</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.1304690297171334</v>
+        <v>-3.974170274170277</v>
       </c>
       <c r="BO12" t="n">
+        <v>87.85714285714288</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>11496428.57142857</v>
+      </c>
+      <c r="BQ12" t="n">
         <v>73428.57142857143</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>1.571428571428572</v>
-      </c>
-      <c r="BQ12" t="n">
-        <v>9.476190476190482</v>
       </c>
       <c r="BR12" t="n">
         <v>-5.068253425772227</v>
       </c>
       <c r="BS12" t="n">
-        <v>87.85714285714288</v>
+        <v>9.476190476190482</v>
       </c>
       <c r="BT12" t="n">
-        <v>-8669296.536796536</v>
+        <v>-0.2865079365079366</v>
       </c>
       <c r="BU12" t="n">
-        <v>57.71428571428572</v>
+        <v>1.190476190476147</v>
       </c>
       <c r="BV12" t="n">
         <v>-1.895693237422591</v>
       </c>
       <c r="BW12" t="n">
-        <v>-5055049.59910599</v>
+        <v>1.571428571428572</v>
       </c>
     </row>
     <row r="13">
@@ -3692,70 +3692,70 @@
         <v>-0.5488721804511278</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.140476190476186</v>
+        <v>-1.714285714285714</v>
       </c>
       <c r="BC13" t="n">
-        <v>-2.177777777777778</v>
+        <v>-62174.07407407407</v>
       </c>
       <c r="BD13" t="n">
         <v>-1.028188778885376</v>
       </c>
       <c r="BE13" t="n">
+        <v>1.140476190476186</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>-32822050.98081744</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>-170.5714285714286</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>-44600062.83068783</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>-1.601192271780507</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>1.991865079365056</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>-12.60668847836031</v>
+      </c>
+      <c r="BL13" t="n">
         <v>-57835.8187134503</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>-1.601192271780507</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>1.740476190476215</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>-11.91044973544973</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>-62174.07407407407</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>-96232142.85714285</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>1.991865079365056</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>-1.714285714285714</v>
       </c>
       <c r="BM13" t="n">
         <v>-11.42619047619047</v>
       </c>
       <c r="BN13" t="n">
-        <v>-12.60668847836031</v>
+        <v>-11.91044973544973</v>
       </c>
       <c r="BO13" t="n">
+        <v>-131.8571428571428</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>-96232142.85714285</v>
+      </c>
+      <c r="BQ13" t="n">
         <v>-163857.1428571429</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>-3.857142857142858</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>4.714285714285715</v>
       </c>
       <c r="BR13" t="n">
         <v>-9.670200293342717</v>
       </c>
       <c r="BS13" t="n">
-        <v>-131.8571428571428</v>
+        <v>4.714285714285715</v>
       </c>
       <c r="BT13" t="n">
-        <v>-44600062.83068783</v>
+        <v>-2.177777777777778</v>
       </c>
       <c r="BU13" t="n">
-        <v>-170.5714285714286</v>
+        <v>1.740476190476215</v>
       </c>
       <c r="BV13" t="n">
         <v>2.19470456873708</v>
       </c>
       <c r="BW13" t="n">
-        <v>-32822050.98081744</v>
+        <v>-3.857142857142858</v>
       </c>
     </row>
     <row r="14">
@@ -3943,70 +3943,70 @@
         <v>-0.5215311004784688</v>
       </c>
       <c r="BB14" t="n">
-        <v>0.65169552669553</v>
+        <v>1.5</v>
       </c>
       <c r="BC14" t="n">
-        <v>-2.025324675324675</v>
+        <v>-78090.25974025973</v>
       </c>
       <c r="BD14" t="n">
         <v>-0.1465236895673598</v>
       </c>
       <c r="BE14" t="n">
+        <v>0.65169552669553</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>-35145227.6275863</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>95.57142857142858</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>-45940422.07792208</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>-1.260791685095091</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>-0.854870129870136</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>-10.29334960077921</v>
+      </c>
+      <c r="BL14" t="n">
         <v>-61203.69744631783</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>-1.260791685095091</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>4.009523809523813</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>-9.368398268398266</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>-78090.25974025973</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>-48128571.42857143</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>-0.854870129870136</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>1.5</v>
       </c>
       <c r="BM14" t="n">
         <v>-9.583261183261172</v>
       </c>
       <c r="BN14" t="n">
-        <v>-10.29334960077921</v>
+        <v>-9.368398268398266</v>
       </c>
       <c r="BO14" t="n">
+        <v>91</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>-48128571.42857143</v>
+      </c>
+      <c r="BQ14" t="n">
         <v>-75714.28571428571</v>
-      </c>
-      <c r="BP14" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="BQ14" t="n">
-        <v>-0.1404761904761891</v>
       </c>
       <c r="BR14" t="n">
         <v>-7.862002396132155</v>
       </c>
       <c r="BS14" t="n">
-        <v>91</v>
+        <v>-0.1404761904761891</v>
       </c>
       <c r="BT14" t="n">
-        <v>-45940422.07792208</v>
+        <v>-2.025324675324675</v>
       </c>
       <c r="BU14" t="n">
-        <v>95.57142857142858</v>
+        <v>4.009523809523813</v>
       </c>
       <c r="BV14" t="n">
         <v>6.020903157740491</v>
       </c>
       <c r="BW14" t="n">
-        <v>-35145227.6275863</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="15">
@@ -4188,70 +4188,70 @@
         <v>0.0368421052631579</v>
       </c>
       <c r="BB15" t="n">
-        <v>-1.758639971139967</v>
+        <v>2.428571428571428</v>
       </c>
       <c r="BC15" t="n">
-        <v>0.4762626262626264</v>
+        <v>10942.00937950938</v>
       </c>
       <c r="BD15" t="n">
         <v>-1.532912346860943</v>
       </c>
       <c r="BE15" t="n">
+        <v>-1.758639971139967</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>8653238.661645053</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>201.2857142857143</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>11851640.06132756</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>0.4830043859649122</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>0.170310245310219</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>5.179616289689022</v>
+      </c>
+      <c r="BL15" t="n">
         <v>8135.815275767056</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>0.4830043859649122</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>-4.707482993197232</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>7.318632756132772</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>10942.00937950938</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>19207142.85714286</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>0.170310245310219</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>2.428571428571428</v>
       </c>
       <c r="BM15" t="n">
         <v>6.352236652236655</v>
       </c>
       <c r="BN15" t="n">
-        <v>5.179616289689022</v>
+        <v>7.318632756132772</v>
       </c>
       <c r="BO15" t="n">
+        <v>172.1428571428572</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>19207142.85714286</v>
+      </c>
+      <c r="BQ15" t="n">
         <v>51000.00000000001</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>3.428571428571428</v>
-      </c>
-      <c r="BQ15" t="n">
-        <v>-2.921088435374145</v>
       </c>
       <c r="BR15" t="n">
         <v>5.521453867588235</v>
       </c>
       <c r="BS15" t="n">
-        <v>172.1428571428572</v>
+        <v>-2.921088435374145</v>
       </c>
       <c r="BT15" t="n">
-        <v>11851640.06132756</v>
+        <v>0.4762626262626264</v>
       </c>
       <c r="BU15" t="n">
-        <v>201.2857142857143</v>
+        <v>-4.707482993197232</v>
       </c>
       <c r="BV15" t="n">
         <v>0.4894660629316547</v>
       </c>
       <c r="BW15" t="n">
-        <v>8653238.661645053</v>
+        <v>3.428571428571428</v>
       </c>
     </row>
     <row r="16">
@@ -4433,70 +4433,70 @@
         <v>-0.1052631578947368</v>
       </c>
       <c r="BB16" t="n">
-        <v>2.152597402597401</v>
+        <v>-1.142857142857142</v>
       </c>
       <c r="BC16" t="n">
-        <v>-0.3916666666666662</v>
+        <v>-18785.82251082251</v>
       </c>
       <c r="BD16" t="n">
         <v>0.6975618636609333</v>
       </c>
       <c r="BE16" t="n">
+        <v>2.152597402597401</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>-6540368.071471012</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>-136.5714285714286</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>-7597269.119769119</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>-0.4198584138599617</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>0.6485569985569839</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>-5.29472444480183</v>
+      </c>
+      <c r="BL16" t="n">
         <v>-17335.24073106116</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>-0.4198584138599617</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>3.383333333333354</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>-6.282539682539664</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>-18785.82251082251</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>-50514285.71428572</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>0.6485569985569839</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>-1.142857142857142</v>
       </c>
       <c r="BM16" t="n">
         <v>-4.477958152958166</v>
       </c>
       <c r="BN16" t="n">
-        <v>-5.29472444480183</v>
+        <v>-6.282539682539664</v>
       </c>
       <c r="BO16" t="n">
+        <v>-117.8571428571428</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>-50514285.71428572</v>
+      </c>
+      <c r="BQ16" t="n">
         <v>-128571.4285714286</v>
-      </c>
-      <c r="BP16" t="n">
-        <v>-3.857142857142857</v>
-      </c>
-      <c r="BQ16" t="n">
-        <v>5.109523809523807</v>
       </c>
       <c r="BR16" t="n">
         <v>-6.473707273978192</v>
       </c>
       <c r="BS16" t="n">
-        <v>-117.8571428571428</v>
+        <v>5.109523809523807</v>
       </c>
       <c r="BT16" t="n">
-        <v>-7597269.119769119</v>
+        <v>-0.3916666666666662</v>
       </c>
       <c r="BU16" t="n">
-        <v>-136.5714285714286</v>
+        <v>3.383333333333354</v>
       </c>
       <c r="BV16" t="n">
         <v>-0.153431651767562</v>
       </c>
       <c r="BW16" t="n">
-        <v>-6540368.071471012</v>
+        <v>-3.857142857142857</v>
       </c>
     </row>
     <row r="17">
@@ -4678,70 +4678,70 @@
         <v>0.1578947368421053</v>
       </c>
       <c r="BB17" t="n">
-        <v>-1.025613275613281</v>
+        <v>-2.142857142857143</v>
       </c>
       <c r="BC17" t="n">
-        <v>0.6248556998556998</v>
+        <v>30921.28427128426</v>
       </c>
       <c r="BD17" t="n">
         <v>-0.9697325060667055</v>
       </c>
       <c r="BE17" t="n">
+        <v>-1.025613275613281</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>17293006.10192763</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>-130.2857142857143</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>20518524.53102453</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>0.5750691456112296</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>-0.3693362193361907</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>4.377248121702053</v>
+      </c>
+      <c r="BL17" t="n">
         <v>28442.73683712442</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>0.5750691456112296</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>-2.926870748299308</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>5.351479076479094</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>30921.28427128426</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>29142857.14285714</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>-0.3693362193361907</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>-2.142857142857143</v>
       </c>
       <c r="BM17" t="n">
         <v>4.302958152958141</v>
       </c>
       <c r="BN17" t="n">
-        <v>4.377248121702053</v>
+        <v>5.351479076479094</v>
       </c>
       <c r="BO17" t="n">
+        <v>-135.4285714285714</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>29142857.14285714</v>
+      </c>
+      <c r="BQ17" t="n">
         <v>45571.42857142858</v>
-      </c>
-      <c r="BP17" t="n">
-        <v>1.142857142857143</v>
-      </c>
-      <c r="BQ17" t="n">
-        <v>-1.699659863945577</v>
       </c>
       <c r="BR17" t="n">
         <v>5.123074758646268</v>
       </c>
       <c r="BS17" t="n">
-        <v>-135.4285714285714</v>
+        <v>-1.699659863945577</v>
       </c>
       <c r="BT17" t="n">
-        <v>20518524.53102453</v>
+        <v>0.6248556998556998</v>
       </c>
       <c r="BU17" t="n">
-        <v>-130.2857142857143</v>
+        <v>-2.926870748299308</v>
       </c>
       <c r="BV17" t="n">
         <v>1.042329297366251</v>
       </c>
       <c r="BW17" t="n">
-        <v>17293006.10192763</v>
+        <v>1.142857142857143</v>
       </c>
     </row>
     <row r="18">
@@ -4925,70 +4925,70 @@
         <v>-0.1578947368421053</v>
       </c>
       <c r="BB18" t="n">
-        <v>-0.8741883116883109</v>
+        <v>2.714285714285714</v>
       </c>
       <c r="BC18" t="n">
-        <v>-1.512662337662337</v>
+        <v>-36169.96753246753</v>
       </c>
       <c r="BD18" t="n">
         <v>-0.1140103957816372</v>
       </c>
       <c r="BE18" t="n">
+        <v>-0.8741883116883109</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>-16808052.20857499</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>174.8571428571429</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>-32467532.46753247</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>-0.7205971255432344</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>-1.009090909090901</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>-5.184174488393225</v>
+      </c>
+      <c r="BL18" t="n">
         <v>-22164.84401090025</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>-0.7205971255432344</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>-0.178571428571388</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>-7.272077922077941</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>-36169.96753246753</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>-32917857.14285714</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>-1.009090909090901</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>2.714285714285714</v>
       </c>
       <c r="BM18" t="n">
         <v>-8.350000000000009</v>
       </c>
       <c r="BN18" t="n">
-        <v>-5.184174488393225</v>
+        <v>-7.272077922077941</v>
       </c>
       <c r="BO18" t="n">
+        <v>179.8571428571429</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>-32917857.14285714</v>
+      </c>
+      <c r="BQ18" t="n">
         <v>857.1428571428551</v>
-      </c>
-      <c r="BP18" t="n">
-        <v>0.5714285714285712</v>
-      </c>
-      <c r="BQ18" t="n">
-        <v>3.347619047619052</v>
       </c>
       <c r="BR18" t="n">
         <v>-6.171988533295576</v>
       </c>
       <c r="BS18" t="n">
-        <v>179.8571428571429</v>
+        <v>3.347619047619052</v>
       </c>
       <c r="BT18" t="n">
-        <v>-32467532.46753247</v>
+        <v>-1.512662337662337</v>
       </c>
       <c r="BU18" t="n">
-        <v>174.8571428571429</v>
+        <v>-0.178571428571388</v>
       </c>
       <c r="BV18" t="n">
         <v>0.2212646441281834</v>
       </c>
       <c r="BW18" t="n">
-        <v>-16808052.20857499</v>
+        <v>0.5714285714285712</v>
       </c>
     </row>
     <row r="19">
@@ -5170,70 +5170,70 @@
         <v>0.1552631578947369</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.266666666666666</v>
+        <v>-3.085714285714285</v>
       </c>
       <c r="BC19" t="n">
-        <v>-0.06190476190476213</v>
+        <v>831.7460317460282</v>
       </c>
       <c r="BD19" t="n">
         <v>-0.1954239070290029</v>
       </c>
       <c r="BE19" t="n">
+        <v>1.266666666666666</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>-2569367.86312195</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>-238.6571428571428</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>-1630317.460317461</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>-0.05451502839538147</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>-1.469841269841226</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>-2.146333012089798</v>
+      </c>
+      <c r="BL19" t="n">
         <v>-758.4479974640126</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>-0.05451502839538147</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>2.838095238095264</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>-0.734920634920627</v>
-      </c>
-      <c r="BI19" t="n">
-        <v>831.7460317460282</v>
-      </c>
-      <c r="BJ19" t="n">
-        <v>-12019285.71428571</v>
-      </c>
-      <c r="BK19" t="n">
-        <v>-1.469841269841226</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>-3.085714285714285</v>
       </c>
       <c r="BM19" t="n">
         <v>-0.7333333333333343</v>
       </c>
       <c r="BN19" t="n">
-        <v>-2.146333012089798</v>
+        <v>-0.734920634920627</v>
       </c>
       <c r="BO19" t="n">
+        <v>-203.1714285714285</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>-12019285.71428571</v>
+      </c>
+      <c r="BQ19" t="n">
         <v>-21085.71428571428</v>
-      </c>
-      <c r="BP19" t="n">
-        <v>-3.685714285714285</v>
-      </c>
-      <c r="BQ19" t="n">
-        <v>5.528571428571425</v>
       </c>
       <c r="BR19" t="n">
         <v>-0.3073175598510431</v>
       </c>
       <c r="BS19" t="n">
-        <v>-203.1714285714285</v>
+        <v>5.528571428571425</v>
       </c>
       <c r="BT19" t="n">
-        <v>-1630317.460317461</v>
+        <v>-0.06190476190476213</v>
       </c>
       <c r="BU19" t="n">
-        <v>-238.6571428571428</v>
+        <v>2.838095238095264</v>
       </c>
       <c r="BV19" t="n">
         <v>0.3288183756964429</v>
       </c>
       <c r="BW19" t="n">
-        <v>-2569367.86312195</v>
+        <v>-3.685714285714285</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/data_preparation/df_constructed.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_constructed.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BW10"/>
+  <dimension ref="A1:BW19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -695,127 +695,127 @@
       </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_rep_player_start</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_start</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_wage_player_miss</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_sub</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_value_player_start</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_rep_player_sub</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_start</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_start</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_start</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_miss</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_value_player_sub</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="BL1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="BM1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>dif_sum_value_player_miss</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_sub</t>
-        </is>
-      </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_sub</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="BR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>dif_sum_rat_player_miss</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="BU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="BV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_wage_player_miss</t>
-        </is>
-      </c>
-      <c r="BW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rep_player_miss</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>zyC4c6ee</t>
+          <t>xMovyDqH</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45592.64583333334</v>
+        <v>45606.64583333334</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">storks s 
+          <t xml:space="preserve">reichel t 
   ger </t>
         </is>
       </c>
@@ -832,7 +832,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>hQAtP9Sl</t>
+          <t>nwkTahLL</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -859,222 +859,222 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>M5BRZDsC</t>
+          <t>4ljanukM</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>8f6APkLc</t>
+          <t>f3ddUIXs</t>
         </is>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.346666666666666</v>
+        <v>0.4300000000000002</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.6488888888888884</v>
+        <v>0.0929411764705883</v>
       </c>
       <c r="R2" t="n">
-        <v>2</v>
+        <v>0.4285714285714284</v>
       </c>
       <c r="S2" t="n">
-        <v>1.105263157894737</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="T2" t="n">
-        <v>2.499999999999999</v>
+        <v>1.166666666666666</v>
       </c>
       <c r="U2" t="n">
-        <v>1.894736842105263</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="V2" t="n">
-        <v>6.833333333333332</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="W2" t="n">
-        <v>4.105263157894736</v>
+        <v>-0.7222222222222214</v>
       </c>
       <c r="X2" t="n">
-        <v>0.6666666666666667</v>
+        <v>-0.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.4210526315789476</v>
+        <v>0.7222222222222223</v>
       </c>
       <c r="Z2" t="n">
+        <v>-0.4285714285714285</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.631578947368421</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>-2.825330388565683</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.5651916371859613</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>-8.162306327613749</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>70.64607720756359</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>-87</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>-38.07692307692308</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>-50</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>-26.23076923076923</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>-7.105427357601002e-15</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>-4.315789473684212</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>-8.222222222222229</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>-78.41176470588238</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>-1.333333333333334</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>-0.7222222222222225</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="AS2" t="n">
         <v>0.5</v>
       </c>
-      <c r="AA2" t="n">
-        <v>0.1578947368421053</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>-3.917269386387033</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>-3.648793932126676</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>44.33520432812224</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>17.11424760591012</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>-13.5</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>-24.66666666666667</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>-17</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>-6.400000000000006</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>-8.666666666666671</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>-2.947368421052637</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>-8.666666666666671</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>-9.157894736842096</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>-3.833333333333258</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>-95.66666666666663</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>-1.105263157894737</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>0.09999999999999998</v>
-      </c>
       <c r="AT2" t="n">
-        <v>1.833333333333332</v>
+        <v>-5.714285714285712</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.526315789473687</v>
+        <v>1.263157894736842</v>
       </c>
       <c r="AV2" t="n">
-        <v>-6.991944347230795</v>
+        <v>4.014944927042723</v>
       </c>
       <c r="AW2" t="n">
-        <v>-11.60689255032138</v>
+        <v>-0.8164295320536397</v>
       </c>
       <c r="AX2" t="n">
-        <v>-0.127552353084268</v>
+        <v>-0.0479449874094299</v>
       </c>
       <c r="AY2" t="n">
-        <v>-0.01821903569119519</v>
+        <v>-0.05492320041236257</v>
       </c>
       <c r="AZ2" t="n">
+        <v>-0.1428571428571428</v>
+      </c>
+      <c r="BA2" t="n">
         <v>0</v>
       </c>
-      <c r="BA2" t="n">
-        <v>0.1052631578947368</v>
-      </c>
       <c r="BB2" t="n">
-        <v>-0.1145835603501506</v>
+        <v>-0.3499007936507934</v>
       </c>
       <c r="BC2" t="n">
-        <v>-4.325462962962959</v>
+        <v>2.324801587301579</v>
       </c>
       <c r="BD2" t="n">
-        <v>-0.5296296296296319</v>
+        <v>-13612.4007936508</v>
       </c>
       <c r="BE2" t="n">
-        <v>-0.6356481481481484</v>
+        <v>-2.428571428571429</v>
       </c>
       <c r="BF2" t="n">
-        <v>-7984.722222222223</v>
+        <v>-140000</v>
       </c>
       <c r="BG2" t="n">
-        <v>-2.436574074074059</v>
+        <v>-6.044976025567294</v>
       </c>
       <c r="BH2" t="n">
-        <v>-4531990.740740741</v>
+        <v>-13005.82984771469</v>
       </c>
       <c r="BI2" t="n">
-        <v>-3</v>
+        <v>-215.4285714285714</v>
       </c>
       <c r="BJ2" t="n">
-        <v>-2934761.45072827</v>
+        <v>-5.249603174603166</v>
       </c>
       <c r="BK2" t="n">
-        <v>2</v>
+        <v>3.254081632652998</v>
       </c>
       <c r="BL2" t="n">
-        <v>-549</v>
+        <v>-6523700.396825397</v>
       </c>
       <c r="BM2" t="n">
-        <v>-1.467370418800627</v>
+        <v>2.239880952380947</v>
       </c>
       <c r="BN2" t="n">
-        <v>-57800000</v>
+        <v>-2.370932539682542</v>
       </c>
       <c r="BO2" t="n">
-        <v>-3502.039519087572</v>
+        <v>-0.3491879717700823</v>
       </c>
       <c r="BP2" t="n">
-        <v>-0.6305682684973704</v>
+        <v>0.539455782312924</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.197685185185151</v>
+        <v>-3.885033631024029</v>
       </c>
       <c r="BR2" t="n">
-        <v>-7</v>
+        <v>-5922832.874516563</v>
       </c>
       <c r="BS2" t="n">
-        <v>-534</v>
+        <v>-52321428.57142857</v>
       </c>
       <c r="BT2" t="n">
-        <v>1.788427893405007</v>
+        <v>0.1980415538380953</v>
       </c>
       <c r="BU2" t="n">
-        <v>-5.413222064823898</v>
+        <v>-5.142857142857143</v>
       </c>
       <c r="BV2" t="n">
-        <v>-212000</v>
+        <v>-199.1428571428571</v>
       </c>
       <c r="BW2" t="n">
-        <v>-12</v>
+        <v>0.9268963358174531</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>ABBmcc1C</t>
+          <t>UkaNveph</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45592.5625</v>
+        <v>45606.5625</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">brych f 
+          <t xml:space="preserve">osmers h 
   ger </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadion an der alten forsterei
-  berlin </t>
+          <t xml:space="preserve">mhparena
+  stuttgart </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>pzHW4oaE</t>
+          <t>nJQmYp1B</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>A15eUM4C</t>
+          <t>GzfvcwRj</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1118,213 +1118,215 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.21</v>
+        <v>0.4116666666666664</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.3072222222222218</v>
+        <v>0.7063071895424833</v>
       </c>
       <c r="R3" t="n">
-        <v>-1.110223024625157e-16</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3157894736842104</v>
+        <v>0.7500000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>1.333333333333333</v>
+        <v>2.5</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3157894736842097</v>
+        <v>2.85672514619883</v>
       </c>
       <c r="V3" t="n">
-        <v>6.666666666666666</v>
+        <v>8.666666666666668</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.5789473684210531</v>
+        <v>4.988304093567253</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.4210526315789476</v>
+        <v>1.002923976608187</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.4736842105263157</v>
+        <v>0.9</v>
       </c>
       <c r="AB3" t="n">
-        <v>-4.405980960760374</v>
+        <v>-0.2697793899999774</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.928355427139441</v>
+        <v>-2.066458352449065</v>
       </c>
       <c r="AD3" t="n">
-        <v>-37.82321702295715</v>
+        <v>-22.15264273029575</v>
       </c>
       <c r="AE3" t="n">
-        <v>55.89168543233939</v>
+        <v>-145.0320106625602</v>
       </c>
       <c r="AF3" t="n">
-        <v>-49</v>
+        <v>64</v>
       </c>
       <c r="AG3" t="n">
-        <v>-35.40000000000001</v>
+        <v>17.02197802197801</v>
       </c>
       <c r="AH3" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="AI3" t="n">
-        <v>-8.866666666666667</v>
+        <v>4.489010989010993</v>
       </c>
       <c r="AJ3" t="n">
-        <v>4.666666666666675</v>
+        <v>10.71428571428572</v>
       </c>
       <c r="AK3" t="n">
-        <v>-4.84210526315789</v>
+        <v>-1.02105263157895</v>
       </c>
       <c r="AL3" t="n">
-        <v>-1.666666666666671</v>
+        <v>20</v>
       </c>
       <c r="AM3" t="n">
-        <v>-8.947368421052644</v>
+        <v>22.04093567251461</v>
       </c>
       <c r="AN3" t="n">
-        <v>-26.16666666666663</v>
+        <v>284.8333333333334</v>
       </c>
       <c r="AO3" t="n">
-        <v>-126.6111111111111</v>
+        <v>278.1797385620915</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.1666666666666667</v>
+        <v>-1.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.3888888888888886</v>
-      </c>
-      <c r="AR3" t="inlineStr"/>
+        <v>-0.9195046439628483</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>-0.5</v>
+      </c>
       <c r="AS3" t="n">
-        <v>2</v>
+        <v>-0.75</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.333333333333339</v>
+        <v>0.4285714285714306</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.210526315789473</v>
+        <v>0.8710526315789462</v>
       </c>
       <c r="AV3" t="n">
-        <v>-1.16800971660734</v>
+        <v>-26.78846777300568</v>
       </c>
       <c r="AW3" t="n">
-        <v>-9.492173010455559</v>
+        <v>-30.06792176930404</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.03305785279007403</v>
+        <v>-0.005279115814673316</v>
       </c>
       <c r="AY3" t="n">
-        <v>-0.0009351352108242575</v>
+        <v>-0.02466191651860965</v>
       </c>
       <c r="AZ3" t="n">
-        <v>2.775557561562891e-17</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="BA3" t="n">
-        <v>-0.05263157894736842</v>
+        <v>0.3026315789473684</v>
       </c>
       <c r="BB3" t="n">
-        <v>-0.3405407458039036</v>
+        <v>-0.1956349206349208</v>
       </c>
       <c r="BC3" t="n">
-        <v>-3.809217171717165</v>
+        <v>0.4782467532467365</v>
       </c>
       <c r="BD3" t="n">
-        <v>2.177020202020206</v>
+        <v>-7029.797979797986</v>
       </c>
       <c r="BE3" t="n">
-        <v>-0.3194444444444444</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="BF3" t="n">
-        <v>-7063.510101010103</v>
+        <v>64142.85714285714</v>
       </c>
       <c r="BG3" t="n">
-        <v>-1.829040404040413</v>
+        <v>-2.733246265013165</v>
       </c>
       <c r="BH3" t="n">
-        <v>-8420984.848484851</v>
+        <v>-1701.713292972687</v>
       </c>
       <c r="BI3" t="n">
-        <v>8.5</v>
+        <v>203.8571428571428</v>
       </c>
       <c r="BJ3" t="n">
-        <v>-5201651.432875116</v>
+        <v>-1.615800865800864</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.5</v>
+        <v>6.966666666666669</v>
       </c>
       <c r="BL3" t="n">
-        <v>63</v>
+        <v>-668668.8311688323</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.03441938178781356</v>
+        <v>0.1871212121212125</v>
       </c>
       <c r="BN3" t="n">
-        <v>10525000</v>
+        <v>-0.2170634920635024</v>
       </c>
       <c r="BO3" t="n">
-        <v>-1539.121161489573</v>
+        <v>0.07464928555154127</v>
       </c>
       <c r="BP3" t="n">
-        <v>-1.923421558947894</v>
+        <v>2.652380952380952</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.8829545454544814</v>
+        <v>1.320594641365304</v>
       </c>
       <c r="BR3" t="n">
-        <v>1</v>
+        <v>1735406.750100359</v>
       </c>
       <c r="BS3" t="n">
-        <v>101</v>
+        <v>17417857.14285714</v>
       </c>
       <c r="BT3" t="n">
-        <v>3.32275828460039</v>
+        <v>1.390690877626923</v>
       </c>
       <c r="BU3" t="n">
-        <v>-4.994415964152793</v>
+        <v>3.142857142857143</v>
       </c>
       <c r="BV3" t="n">
-        <v>88000</v>
+        <v>192.5714285714286</v>
       </c>
       <c r="BW3" t="n">
-        <v>2</v>
+        <v>1.594705513784458</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>WQadeyWO</t>
+          <t>UJQITUyi</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45592.47916666666</v>
+        <v>45606.47916666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stieler t 
+          <t xml:space="preserve">dingert c 
   ger </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">vonovia ruhrstadion
-  bochum </t>
+          <t xml:space="preserve">wwk arena
+  augsburg </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>8Y2m6ADe</t>
+          <t>fTVNku3I</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>nVp0wiqd</t>
+          <t>hQAtP9Sl</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1351,227 +1353,227 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>2VSFgl3c</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>KUx4Q7x1</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>GzfvcwRj</t>
         </is>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-3.575</v>
+        <v>1.508333333333334</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.301722222222222</v>
+        <v>0.2152941176470586</v>
       </c>
       <c r="R4" t="n">
-        <v>-5</v>
+        <v>1.714285714285714</v>
       </c>
       <c r="S4" t="n">
-        <v>-2.578947368421053</v>
+        <v>0.4736842105263156</v>
       </c>
       <c r="T4" t="n">
-        <v>-8.5</v>
+        <v>1.5</v>
       </c>
       <c r="U4" t="n">
-        <v>-4.521303258145363</v>
+        <v>-0.1111111111111107</v>
       </c>
       <c r="V4" t="n">
-        <v>-19.5</v>
+        <v>9.833333333333332</v>
       </c>
       <c r="W4" t="n">
-        <v>-8.005012531328322</v>
+        <v>4.722222222222221</v>
       </c>
       <c r="X4" t="n">
-        <v>-4.166666666666666</v>
+        <v>2.220446049250313e-16</v>
       </c>
       <c r="Y4" t="n">
-        <v>-2.879699248120301</v>
+        <v>-0.7222222222222221</v>
       </c>
       <c r="Z4" t="n">
-        <v>-4.5</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AA4" t="n">
-        <v>-2.977443609022556</v>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>-0.4736842105263159</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>-0.5489262371615315</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>-2.298518389331606</v>
       </c>
       <c r="AD4" t="n">
-        <v>272.3259625298296</v>
+        <v>137.1934149720423</v>
       </c>
       <c r="AE4" t="n">
-        <v>203.7566976091855</v>
+        <v>19.42572491147652</v>
       </c>
       <c r="AF4" t="n">
-        <v>-27</v>
+        <v>16</v>
       </c>
       <c r="AG4" t="n">
-        <v>-5.35294117647058</v>
+        <v>-1.07692307692308</v>
       </c>
       <c r="AH4" t="n">
-        <v>-41</v>
+        <v>40</v>
       </c>
       <c r="AI4" t="n">
-        <v>-16.3921568627451</v>
+        <v>11.07692307692308</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-9.5</v>
+        <v>3.571428571428569</v>
       </c>
       <c r="AK4" t="n">
-        <v>-4.959899749373442</v>
+        <v>0.05263157894736281</v>
       </c>
       <c r="AL4" t="n">
-        <v>-42</v>
+        <v>-9</v>
       </c>
       <c r="AM4" t="n">
-        <v>-25.80952380952381</v>
+        <v>-8.333333333333343</v>
       </c>
       <c r="AN4" t="n">
-        <v>-514.5</v>
+        <v>-13.16666666666657</v>
       </c>
       <c r="AO4" t="n">
-        <v>-310.0055555555556</v>
+        <v>-97</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.5</v>
+        <v>-1</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.397759103641457</v>
-      </c>
-      <c r="AR4" t="inlineStr"/>
-      <c r="AS4" t="inlineStr"/>
+        <v>-0.2222222222222223</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>-0.3333333333333334</v>
+      </c>
       <c r="AT4" t="n">
-        <v>2.666666666666671</v>
+        <v>3</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.822055137844611</v>
+        <v>4.842105263157894</v>
       </c>
       <c r="AV4" t="n">
-        <v>53.00379899116727</v>
+        <v>-8.087609656737346</v>
       </c>
       <c r="AW4" t="n">
-        <v>31.08316123593318</v>
+        <v>-25.46793936037142</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.03681870812779452</v>
+        <v>-0.05033218400470944</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.04269159330149178</v>
+        <v>0.0445031025923889</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-0.6666666666666666</v>
+        <v>-0.1428571428571428</v>
       </c>
       <c r="BA4" t="n">
-        <v>-0.5488721804511278</v>
+        <v>-0.1578947368421053</v>
       </c>
       <c r="BB4" t="n">
-        <v>-1.650108932461874</v>
+        <v>-0.5134920634920637</v>
       </c>
       <c r="BC4" t="n">
-        <v>-11.86851851851851</v>
+        <v>-1.068253968253941</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.074074074074069</v>
+        <v>-6840.476190476191</v>
       </c>
       <c r="BE4" t="n">
-        <v>-2.190740740740741</v>
+        <v>-1.571428571428572</v>
       </c>
       <c r="BF4" t="n">
-        <v>-62553.70370370369</v>
+        <v>-85857.14285714287</v>
       </c>
       <c r="BG4" t="n">
-        <v>-11.42962962962963</v>
+        <v>-0.7413864748451289</v>
       </c>
       <c r="BH4" t="n">
-        <v>-44265925.92592593</v>
+        <v>-3335.340108930333</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.300000000000001</v>
+        <v>-144.8571428571429</v>
       </c>
       <c r="BJ4" t="n">
-        <v>-33921897.79670866</v>
+        <v>-2.560714285714283</v>
       </c>
       <c r="BK4" t="n">
-        <v>-4.050000000000011</v>
+        <v>1.063435374149719</v>
       </c>
       <c r="BL4" t="n">
-        <v>-124</v>
+        <v>-2393611.111111111</v>
       </c>
       <c r="BM4" t="n">
-        <v>-12.40224766919813</v>
+        <v>-1.039285714285718</v>
       </c>
       <c r="BN4" t="n">
-        <v>-57775000</v>
+        <v>-1.305555555555557</v>
       </c>
       <c r="BO4" t="n">
-        <v>-58404.33982297373</v>
+        <v>-0.09083436404864997</v>
       </c>
       <c r="BP4" t="n">
-        <v>2.174448777486731</v>
+        <v>-0.3005102040816396</v>
       </c>
       <c r="BQ4" t="n">
-        <v>2.186111111111074</v>
+        <v>0.998125861189763</v>
       </c>
       <c r="BR4" t="n">
-        <v>-1</v>
+        <v>-227973.6543740304</v>
       </c>
       <c r="BS4" t="n">
-        <v>-91</v>
+        <v>-28075000</v>
       </c>
       <c r="BT4" t="n">
-        <v>-0.5514054272181248</v>
+        <v>-0.08460897915784926</v>
       </c>
       <c r="BU4" t="n">
-        <v>-10.10098866132147</v>
+        <v>-5.142857142857143</v>
       </c>
       <c r="BV4" t="n">
-        <v>-125000</v>
+        <v>-134.7142857142857</v>
       </c>
       <c r="BW4" t="n">
-        <v>-2</v>
+        <v>-0.01510974405711707</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>MiACepQ7</t>
+          <t>j5mWxZE4</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45591.5625</v>
+        <v>45605.60416666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">badstubner f 
+          <t xml:space="preserve">petersen m 
   ger </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">weserstadion
-  bremen </t>
+          <t xml:space="preserve">red bull arena
+  leipzig </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ig1f1fy3</t>
+          <t>KbS1suSm</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>4jcj2zMd</t>
+          <t>88HSzjDr</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1598,231 +1600,225 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>f3ddUIXs</t>
+          <t>pfoInmcq</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>UgdQz0fK</t>
+          <t>M5BRZDsC</t>
         </is>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.786666666666666</v>
+        <v>0.6533333333333333</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.968253968253968</v>
+        <v>0.8005882352941176</v>
       </c>
       <c r="R5" t="n">
-        <v>-1.785714285714286</v>
+        <v>0.4285714285714284</v>
       </c>
       <c r="S5" t="n">
-        <v>-2.066985645933014</v>
+        <v>0.9473684210526316</v>
       </c>
       <c r="T5" t="n">
-        <v>-4.666666666666667</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>-4.717703349282298</v>
+        <v>1.611111111111112</v>
       </c>
       <c r="V5" t="n">
-        <v>-12.80952380952381</v>
+        <v>0.3333333333333339</v>
       </c>
       <c r="W5" t="n">
-        <v>-12.11961722488038</v>
+        <v>3.222222222222225</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.047619047619047</v>
+        <v>2</v>
       </c>
       <c r="Y5" t="n">
-        <v>-1.703349282296651</v>
+        <v>1.944444444444445</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.7857142857142856</v>
+        <v>2.142857142857143</v>
       </c>
       <c r="AA5" t="n">
-        <v>-2.181818181818182</v>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>2.368421052631579</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.248222912353347</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-0.1944177265015465</v>
       </c>
       <c r="AD5" t="n">
-        <v>-10.02520646788361</v>
+        <v>48.83161188627028</v>
       </c>
       <c r="AE5" t="n">
-        <v>67.86783391528121</v>
+        <v>-18.23484151119089</v>
       </c>
       <c r="AF5" t="n">
-        <v>-70.33333333333334</v>
+        <v>107</v>
       </c>
       <c r="AG5" t="n">
-        <v>-64.12222222222222</v>
+        <v>51</v>
       </c>
       <c r="AH5" t="n">
-        <v>-47.16666666666666</v>
+        <v>-1</v>
       </c>
       <c r="AI5" t="n">
-        <v>-51.91111111111111</v>
+        <v>9.384615384615387</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-11.97619047619048</v>
+        <v>5.428571428571431</v>
       </c>
       <c r="AK5" t="n">
-        <v>-9.232057416267949</v>
+        <v>0.8421052631578974</v>
       </c>
       <c r="AL5" t="n">
-        <v>-14.0952380952381</v>
+        <v>-5.333333333333343</v>
       </c>
       <c r="AM5" t="n">
-        <v>-17.73205741626793</v>
+        <v>6.444444444444443</v>
       </c>
       <c r="AN5" t="n">
-        <v>-217.9999999999999</v>
+        <v>-12.49999999999994</v>
       </c>
       <c r="AO5" t="n">
-        <v>-255.5584795321637</v>
+        <v>84</v>
       </c>
       <c r="AP5" t="n">
-        <v>-2.261904761904762</v>
+        <v>-0.2999999999999998</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.7619047619047619</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0.5</v>
-      </c>
+        <v>-0.7058823529411766</v>
+      </c>
+      <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="n">
-        <v>-0.126984126984127</v>
+        <v>2</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.8333333333333321</v>
+        <v>0.4285714285714306</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.3540669856459342</v>
+        <v>-0.3157894736842088</v>
       </c>
       <c r="AV5" t="n">
-        <v>38.03796811983701</v>
+        <v>-0.6489097071766743</v>
       </c>
       <c r="AW5" t="n">
-        <v>41.55728787315739</v>
+        <v>-11.35946014204917</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.05427421204837672</v>
+        <v>-0.0555051555051555</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.01933830273660526</v>
+        <v>-0.03692391287234778</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.4761904761904762</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0.5215311004784688</v>
+        <v>0.3157894736842105</v>
       </c>
       <c r="BB5" t="n">
-        <v>-1.345666687727722</v>
+        <v>0.8493867243867246</v>
       </c>
       <c r="BC5" t="n">
-        <v>-9.379797979797985</v>
+        <v>-1.310028860028837</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.7512205387205384</v>
+        <v>33094.73304473305</v>
       </c>
       <c r="BE5" t="n">
-        <v>-2.011363636363636</v>
+        <v>-1.285714285714285</v>
       </c>
       <c r="BF5" t="n">
-        <v>-77938.63636363635</v>
+        <v>103857.1428571429</v>
       </c>
       <c r="BG5" t="n">
-        <v>-9.494107744107737</v>
+        <v>4.683320074788128</v>
       </c>
       <c r="BH5" t="n">
-        <v>-45728219.6969697</v>
+        <v>28728.39962834868</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.899999999999999</v>
+        <v>-75.71428571428572</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-36561580.54435977</v>
+        <v>6.551911976911967</v>
       </c>
       <c r="BK5" t="n">
-        <v>4.800000000000011</v>
+        <v>-0.8717687074829712</v>
       </c>
       <c r="BL5" t="n">
-        <v>209</v>
+        <v>23421064.21356422</v>
       </c>
       <c r="BM5" t="n">
-        <v>-10.60776874233501</v>
+        <v>-0.3596681096681102</v>
       </c>
       <c r="BN5" t="n">
-        <v>-53000000</v>
+        <v>5.313636363636348</v>
       </c>
       <c r="BO5" t="n">
-        <v>-63000.76468004855</v>
+        <v>0.7226101996862819</v>
       </c>
       <c r="BP5" t="n">
-        <v>6.356303234142956</v>
+        <v>2.341496598639456</v>
       </c>
       <c r="BQ5" t="n">
-        <v>-0.959469696969677</v>
+        <v>4.994523099094707</v>
       </c>
       <c r="BR5" t="n">
-        <v>3</v>
+        <v>16932104.41474454</v>
       </c>
       <c r="BS5" t="n">
-        <v>207</v>
+        <v>44317857.14285714</v>
       </c>
       <c r="BT5" t="n">
-        <v>-0.4585275834208602</v>
+        <v>2.255013534780829</v>
       </c>
       <c r="BU5" t="n">
-        <v>-7.795904152521572</v>
+        <v>1.571428571428571</v>
       </c>
       <c r="BV5" t="n">
-        <v>-37000</v>
+        <v>-61.14285714285711</v>
       </c>
       <c r="BW5" t="n">
-        <v>1</v>
+        <v>-0.06548365341560114</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>x0haJmIE</t>
+          <t>YmumZjET</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45591.4375</v>
+        <v>45605.47916666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">welz t 
+          <t xml:space="preserve">hartmann r 
   ger </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">wwk arena
-  augsburg </t>
+          <t xml:space="preserve">weserstadion
+  bremen </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>fTVNku3I</t>
+          <t>Ig1f1fy3</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>nP1i5US1</t>
+          <t>63WsD2ei</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1849,227 +1845,231 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>YZPE6Sx7</t>
+          <t>4fuCGs9P</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0jdIgO6t</t>
+          <t>A15eUM4C</t>
         </is>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.3716666666666668</v>
+        <v>0.4016666666666668</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.648333333333333</v>
+        <v>-0.1423529411764706</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.5</v>
+        <v>-1.110223024625157e-16</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6315789473684212</v>
+        <v>-0.1578947368421053</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.5</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="U6" t="n">
-        <v>-2.842105263157896</v>
+        <v>0.6666666666666661</v>
       </c>
       <c r="V6" t="n">
-        <v>0.8333333333333339</v>
+        <v>5.333333333333336</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.7894736842105257</v>
+        <v>1.5</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.333333333333333</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="Y6" t="n">
-        <v>-1.105263157894737</v>
+        <v>-0.1111111111111109</v>
       </c>
       <c r="Z6" t="n">
-        <v>-1.5</v>
+        <v>2.142857142857143</v>
       </c>
       <c r="AA6" t="n">
-        <v>-1.578947368421052</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>-1.889589685913216</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>-0.4712571364416727</v>
+        <v>0.1578947368421053</v>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
       <c r="AD6" t="n">
-        <v>124.3423941169303</v>
+        <v>-46.83529265916053</v>
       </c>
       <c r="AE6" t="n">
-        <v>108.5109366517813</v>
+        <v>29.59098514204942</v>
       </c>
       <c r="AF6" t="n">
-        <v>-11</v>
+        <v>34</v>
       </c>
       <c r="AG6" t="n">
-        <v>-18.46666666666667</v>
+        <v>-6</v>
       </c>
       <c r="AH6" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="AI6" t="n">
-        <v>5.466666666666669</v>
+        <v>4.53846153846154</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-1.5</v>
+        <v>3.285714285714288</v>
       </c>
       <c r="AK6" t="n">
-        <v>-4.315789473684209</v>
+        <v>3</v>
       </c>
       <c r="AL6" t="n">
-        <v>-23</v>
+        <v>11.66666666666667</v>
       </c>
       <c r="AM6" t="n">
-        <v>-21.89473684210526</v>
+        <v>0.5555555555555571</v>
       </c>
       <c r="AN6" t="n">
-        <v>-257.6666666666666</v>
+        <v>172.6666666666667</v>
       </c>
       <c r="AO6" t="n">
-        <v>-278.7222222222222</v>
+        <v>1.882352941176407</v>
       </c>
       <c r="AP6" t="n">
-        <v>-1.5</v>
+        <v>-0.6666666666666663</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.3859649122807016</v>
+        <v>-0.4313725490196081</v>
       </c>
       <c r="AR6" t="n">
-        <v>-1</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="AS6" t="n">
-        <v>-1.5</v>
+        <v>-0.6785714285714286</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.3333333333333357</v>
+        <v>-1.571428571428573</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.894736842105262</v>
+        <v>-3.157894736842106</v>
       </c>
       <c r="AV6" t="n">
-        <v>16.05100217360426</v>
+        <v>15.41580378924033</v>
       </c>
       <c r="AW6" t="n">
-        <v>3.361368767148406</v>
+        <v>25.30707867637981</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.09609284185745956</v>
+        <v>-0.06360022603714025</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.02609042386851434</v>
+        <v>0.01255912972227</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.1428571428571428</v>
       </c>
       <c r="BA6" t="n">
-        <v>-0.1578947368421053</v>
+        <v>-0.3684210526315789</v>
       </c>
       <c r="BB6" t="n">
-        <v>-0.7763317700817698</v>
+        <v>0.0974025974025976</v>
       </c>
       <c r="BC6" t="n">
-        <v>-7.74545454545455</v>
+        <v>-2.833116883116872</v>
       </c>
       <c r="BD6" t="n">
-        <v>-0.375</v>
+        <v>6986.327561327562</v>
       </c>
       <c r="BE6" t="n">
-        <v>-1.482575757575757</v>
+        <v>1</v>
       </c>
       <c r="BF6" t="n">
-        <v>-35055.30303030303</v>
+        <v>35571.42857142857</v>
       </c>
       <c r="BG6" t="n">
-        <v>-8.135606060606065</v>
+        <v>3.682177068872079</v>
       </c>
       <c r="BH6" t="n">
-        <v>-32096212.12121212</v>
+        <v>3668.801450265981</v>
       </c>
       <c r="BI6" t="n">
-        <v>3</v>
+        <v>78.85714285714286</v>
       </c>
       <c r="BJ6" t="n">
-        <v>-16990756.13592061</v>
+        <v>4.50382395382394</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.400000000000006</v>
+        <v>-2.46666666666664</v>
       </c>
       <c r="BL6" t="n">
-        <v>-47</v>
+        <v>4098906.926406926</v>
       </c>
       <c r="BM6" t="n">
-        <v>-5.179490867319799</v>
+        <v>0.5748556998557</v>
       </c>
       <c r="BN6" t="n">
-        <v>-77800000</v>
+        <v>4.681240981240975</v>
       </c>
       <c r="BO6" t="n">
-        <v>-22647.56097946888</v>
+        <v>0</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.4448428520796597</v>
+        <v>1.609523809523807</v>
       </c>
       <c r="BQ6" t="n">
-        <v>-1.241666666666646</v>
+        <v>1.80950392638853</v>
       </c>
       <c r="BR6" t="n">
-        <v>0</v>
+        <v>1588547.342381929</v>
       </c>
       <c r="BS6" t="n">
-        <v>-19</v>
+        <v>7542857.142857143</v>
       </c>
       <c r="BT6" t="n">
-        <v>-0.2459703551808836</v>
+        <v>2.030208284686864</v>
       </c>
       <c r="BU6" t="n">
-        <v>-6.175930356193504</v>
+        <v>1</v>
       </c>
       <c r="BV6" t="n">
-        <v>-95000</v>
+        <v>79.28571428571431</v>
       </c>
       <c r="BW6" t="n">
-        <v>-5</v>
+        <v>-1.412805305188442</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>ELNeaSQr</t>
+          <t>biQrHC9r</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45591.4375</v>
+        <v>45605.47916666666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">jablonski s 
+          <t xml:space="preserve">badstubner f 
   ger </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">red bull arena
-  leipzig </t>
+          <t xml:space="preserve">vonovia ruhrstadion
+  bochum </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>KbS1suSm</t>
+          <t>8Y2m6ADe</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>fiEQZ7C7</t>
+          <t>4jcj2zMd</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2096,208 +2096,208 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>vZA6VYpf</t>
+          <t>8f6APkLc</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2VSFgl3c</t>
+          <t>hAcTWKKN</t>
         </is>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.3466666666666669</v>
+        <v>-2.391666666666667</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.6577777777777778</v>
+        <v>-2.361868421052631</v>
       </c>
       <c r="R7" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>-3</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7894736842105262</v>
+        <v>-2.779220779220779</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.5</v>
+        <v>-5.5</v>
       </c>
       <c r="U7" t="n">
-        <v>1.578947368421053</v>
+        <v>-5.5</v>
       </c>
       <c r="V7" t="n">
-        <v>-6.666666666666668</v>
+        <v>-12</v>
       </c>
       <c r="W7" t="n">
-        <v>2.842105263157896</v>
+        <v>-10.34285714285714</v>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>-2.833333333333333</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.263157894736842</v>
+        <v>-2.678571428571429</v>
       </c>
       <c r="Z7" t="n">
-        <v>1</v>
+        <v>-3.428571428571429</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.578947368421052</v>
+        <v>-3.480519480519481</v>
       </c>
       <c r="AB7" t="n">
-        <v>-2.154208754208755</v>
+        <v>2.470918106947519</v>
       </c>
       <c r="AC7" t="n">
-        <v>-3.527500890051013</v>
+        <v>2.640468890731771</v>
       </c>
       <c r="AD7" t="n">
-        <v>-175.8606676483772</v>
+        <v>143.1609613063715</v>
       </c>
       <c r="AE7" t="n">
-        <v>-185.512282311278</v>
+        <v>84.08859229330037</v>
       </c>
       <c r="AF7" t="n">
-        <v>48.5</v>
+        <v>-27</v>
       </c>
       <c r="AG7" t="n">
-        <v>26.80000000000001</v>
+        <v>-8.762499999999989</v>
       </c>
       <c r="AH7" t="n">
-        <v>-15.5</v>
+        <v>-37</v>
       </c>
       <c r="AI7" t="n">
-        <v>17.93333333333334</v>
+        <v>-33.01666666666667</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-4.166666666666671</v>
+        <v>-10.42857142857143</v>
       </c>
       <c r="AK7" t="n">
-        <v>4.94736842105263</v>
+        <v>-9.906926406926406</v>
       </c>
       <c r="AL7" t="n">
-        <v>2.333333333333329</v>
+        <v>-24.66666666666666</v>
       </c>
       <c r="AM7" t="n">
-        <v>12.31578947368421</v>
+        <v>-17.9095238095238</v>
       </c>
       <c r="AN7" t="n">
-        <v>100.8333333333333</v>
+        <v>-309.8333333333333</v>
       </c>
       <c r="AO7" t="n">
-        <v>175.4999999999999</v>
+        <v>-205.1432748538011</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.09999999999999987</v>
+        <v>0.1666666666666665</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-0.564327485380117</v>
+        <v>1.15</v>
       </c>
       <c r="AR7" t="inlineStr"/>
       <c r="AS7" t="n">
-        <v>-0.6666666666666667</v>
+        <v>0.2</v>
       </c>
       <c r="AT7" t="n">
-        <v>-0.6666666666666643</v>
+        <v>1.714285714285712</v>
       </c>
       <c r="AU7" t="n">
-        <v>-0.9473684210526319</v>
+        <v>2.569264069264069</v>
       </c>
       <c r="AV7" t="n">
-        <v>-10.62790786115386</v>
+        <v>13.10786799674785</v>
       </c>
       <c r="AW7" t="n">
-        <v>-14.40414641130682</v>
+        <v>18.49169622478498</v>
       </c>
       <c r="AX7" t="n">
-        <v>-0.05502310427071028</v>
+        <v>0.03659375975061279</v>
       </c>
       <c r="AY7" t="n">
-        <v>-0.0154848222235259</v>
+        <v>0.02552748184216082</v>
       </c>
       <c r="AZ7" t="n">
+        <v>-0.1428571428571428</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>-0.606060606060606</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>-2.121428571428571</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>1.64570105820107</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>-84806.61375661375</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>2.071428571428572</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>-59785.71428571428</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>-10.18924541476511</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>-63854.76473990406</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>135.2857142857143</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>-12.27526455026455</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>6.735714285714295</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>-49685730.82010582</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>1.777645502645502</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>-12.38756613756614</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>-1.249593170601574</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>-0.2261904761904781</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>-11.61686553163774</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>-34384701.66069127</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>-36500000</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>3.723160573271173</v>
+      </c>
+      <c r="BU7" t="n">
         <v>0.5</v>
       </c>
-      <c r="BA7" t="n">
-        <v>0.1578947368421053</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>0.6074219397210379</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>5.275378787878793</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>-1.058501683501689</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>0.6094696969696971</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>30958.67003367003</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>4.191835016835</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>20366056.3973064</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>-1.533333333333331</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>17449139.95099577</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>-4.133333333333354</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>133</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>4.415895573898851</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>138000000</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>28394.97242526671</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>0.8250734033182994</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>-0.3079966329966339</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>120</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>-0.9028667040285328</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>5.103069256850048</v>
-      </c>
       <c r="BV7" t="n">
-        <v>230000</v>
+        <v>128.7142857142857</v>
       </c>
       <c r="BW7" t="n">
-        <v>7</v>
+        <v>1.489778583498179</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Mku6FvHt</t>
+          <t>6HTjFjve</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45591.4375</v>
+        <v>45605.47916666666</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">reichel t 
+          <t xml:space="preserve">exner f 
   ger </t>
         </is>
       </c>
@@ -2314,7 +2314,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>nwkTahLL</t>
+          <t>nVp0wiqd</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2341,225 +2341,227 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>IkCftsQm</t>
+          <t>0jdIgO6t</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>4fuCGs9P</t>
+          <t>K6A2elS9</t>
         </is>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.001666666666666816</v>
+        <v>-2.913333333333333</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.1327777777777781</v>
+        <v>-1.464705882352942</v>
       </c>
       <c r="R8" t="n">
-        <v>-1.110223024625157e-16</v>
+        <v>-3.428571428571429</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3157894736842104</v>
+        <v>-1.578947368421053</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3333333333333335</v>
+        <v>-8.833333333333332</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5263157894736841</v>
+        <v>-3.777777777777778</v>
       </c>
       <c r="V8" t="n">
-        <v>4.166666666666666</v>
+        <v>-16.33333333333334</v>
       </c>
       <c r="W8" t="n">
-        <v>3.052631578947366</v>
+        <v>-5.555555555555557</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.6666666666666666</v>
+        <v>-3.666666666666667</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.3684210526315788</v>
+        <v>-1.722222222222222</v>
       </c>
       <c r="Z8" t="n">
-        <v>-1</v>
+        <v>-2.571428571428571</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.631578947368421</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>-5.182391845627139</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>-3.61013214466449</v>
+        <v>-1.263157894736842</v>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
       <c r="AD8" t="n">
-        <v>-153.0061458087206</v>
+        <v>511.338360550177</v>
       </c>
       <c r="AE8" t="n">
-        <v>-177.6781415205782</v>
+        <v>153.5351290403999</v>
       </c>
       <c r="AF8" t="n">
-        <v>-10</v>
+        <v>-56</v>
       </c>
       <c r="AG8" t="n">
-        <v>30.46666666666667</v>
+        <v>-6.615384615384613</v>
       </c>
       <c r="AH8" t="n">
-        <v>-32</v>
+        <v>-64</v>
       </c>
       <c r="AI8" t="n">
-        <v>13.93333333333333</v>
+        <v>-7.53846153846154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.666666666666657</v>
+        <v>-4.857142857142858</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.6315789473684248</v>
+        <v>-2.210526315789469</v>
       </c>
       <c r="AL8" t="n">
-        <v>-0.6666666666666714</v>
+        <v>-47.33333333333334</v>
       </c>
       <c r="AM8" t="n">
-        <v>12.52631578947368</v>
+        <v>-18.11111111111111</v>
       </c>
       <c r="AN8" t="n">
-        <v>29.00000000000006</v>
+        <v>-623.3333333333333</v>
       </c>
       <c r="AO8" t="n">
-        <v>202.7222222222222</v>
+        <v>-231.8823529411765</v>
       </c>
       <c r="AP8" t="n">
-        <v>-2.566666666666666</v>
+        <v>-1.6</v>
       </c>
       <c r="AQ8" t="n">
-        <v>-0.6023391812865497</v>
+        <v>0.2169117647058822</v>
       </c>
       <c r="AR8" t="inlineStr"/>
-      <c r="AS8" t="n">
-        <v>0.2083333333333333</v>
-      </c>
+      <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
-        <v>-5.833333333333339</v>
+        <v>2.714285714285715</v>
       </c>
       <c r="AU8" t="n">
-        <v>-2.052631578947366</v>
+        <v>0.5789473684210531</v>
       </c>
       <c r="AV8" t="n">
-        <v>6.436392345330528</v>
+        <v>60.0688079004307</v>
       </c>
       <c r="AW8" t="n">
-        <v>-16.43726488022848</v>
+        <v>21.60593422839553</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.0123407177838121</v>
+        <v>0.01857756362317348</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.0225101626541523</v>
+        <v>0.02761399769246548</v>
       </c>
       <c r="AZ8" t="n">
-        <v>-0.3333333333333334</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="BA8" t="n">
-        <v>-0.1052631578947368</v>
+        <v>-0.3684210526315789</v>
       </c>
       <c r="BB8" t="n">
-        <v>-0.4273348161699555</v>
+        <v>-2.242857142857142</v>
       </c>
       <c r="BC8" t="n">
-        <v>-6.263888888888886</v>
+        <v>1.289033189033148</v>
       </c>
       <c r="BD8" t="n">
-        <v>2.190530303030297</v>
+        <v>-63318.75901875902</v>
       </c>
       <c r="BE8" t="n">
-        <v>-0.3784722222222219</v>
+        <v>-1.142857142857143</v>
       </c>
       <c r="BF8" t="n">
-        <v>-18592.48737373737</v>
+        <v>-161428.5714285714</v>
       </c>
       <c r="BG8" t="n">
-        <v>-4.389330808080814</v>
+        <v>-12.22423829180796</v>
       </c>
       <c r="BH8" t="n">
-        <v>-7457531.565656567</v>
+        <v>-58121.64817681459</v>
       </c>
       <c r="BI8" t="n">
-        <v>0</v>
+        <v>-149</v>
       </c>
       <c r="BJ8" t="n">
-        <v>-6515788.213012477</v>
+        <v>-12.35714285714286</v>
       </c>
       <c r="BK8" t="n">
-        <v>3.857142857142861</v>
+        <v>2.36904761904762</v>
       </c>
       <c r="BL8" t="n">
-        <v>-54</v>
+        <v>-45574650.07215007</v>
       </c>
       <c r="BM8" t="n">
-        <v>-5.532502593009553</v>
+        <v>-0.3989898989899032</v>
       </c>
       <c r="BN8" t="n">
-        <v>-76660000</v>
+        <v>-12.60533910533911</v>
       </c>
       <c r="BO8" t="n">
-        <v>-17068.19751957135</v>
+        <v>-1.647461791734237</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.2284038136785682</v>
+        <v>5.835714285714289</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.4395202020201907</v>
+        <v>-13.2218192540174</v>
       </c>
       <c r="BR8" t="n">
-        <v>0</v>
+        <v>-34425618.90326306</v>
       </c>
       <c r="BS8" t="n">
-        <v>-55</v>
+        <v>-96888571.42857143</v>
       </c>
       <c r="BT8" t="n">
-        <v>1.010581433530348</v>
+        <v>1.598315027765494</v>
       </c>
       <c r="BU8" t="n">
-        <v>-6.742473301122686</v>
+        <v>-3.428571428571429</v>
       </c>
       <c r="BV8" t="n">
-        <v>-173000</v>
+        <v>-112.8571428571428</v>
       </c>
       <c r="BW8" t="n">
-        <v>-5</v>
+        <v>-0.80365251363704</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>rwXP4l3L</t>
+          <t>nee3ysec</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45591.4375</v>
+        <v>45605.47916666666</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">hartmann r 
+          <t xml:space="preserve">welz t 
   ger </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">mhparena
-  stuttgart </t>
+          <t xml:space="preserve">mewa arena
+  mainz </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>nJQmYp1B</t>
+          <t>EuakNmc1</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>63WsD2ei</t>
+          <t>nP1i5US1</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2586,439 +2588,2658 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>K6A2elS9</t>
+          <t>vZA6VYpf</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>hpYJ6izc</t>
+          <t>IkCftsQm</t>
         </is>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.875</v>
+        <v>-0.9133333333333331</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.8326023391812862</v>
+        <v>-0.2717647058823525</v>
       </c>
       <c r="R9" t="n">
-        <v>1.785714285714286</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="S9" t="n">
-        <v>0.9078947368421052</v>
+        <v>-0.1578947368421053</v>
       </c>
       <c r="T9" t="n">
-        <v>4.976190476190476</v>
+        <v>-2.5</v>
       </c>
       <c r="U9" t="n">
-        <v>2.978947368421052</v>
+        <v>-2.055555555555556</v>
       </c>
       <c r="V9" t="n">
-        <v>13.07142857142857</v>
+        <v>-5.166666666666668</v>
       </c>
       <c r="W9" t="n">
-        <v>7.813157894736841</v>
+        <v>-2.333333333333334</v>
       </c>
       <c r="X9" t="n">
-        <v>2.833333333333333</v>
+        <v>2.220446049250313e-16</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.8421052631578947</v>
+        <v>0.2777777777777779</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.857142857142857</v>
+        <v>-0.4285714285714286</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.5763157894736841</v>
+        <v>0.1578947368421052</v>
       </c>
       <c r="AB9" t="n">
-        <v>-8.401940321583178</v>
+        <v>4.401531572647301</v>
       </c>
       <c r="AC9" t="n">
-        <v>-3.856856885804254</v>
+        <v>1.4788084397526</v>
       </c>
       <c r="AD9" t="n">
-        <v>-294.5019424864247</v>
+        <v>323.0138301900229</v>
       </c>
       <c r="AE9" t="n">
-        <v>-160.6489352456286</v>
+        <v>159.6628481621305</v>
       </c>
       <c r="AF9" t="n">
-        <v>96.5</v>
+        <v>22</v>
       </c>
       <c r="AG9" t="n">
-        <v>32.39583333333333</v>
+        <v>-25.69230769230771</v>
       </c>
       <c r="AH9" t="n">
-        <v>61.33333333333334</v>
+        <v>27</v>
       </c>
       <c r="AI9" t="n">
-        <v>20.35833333333333</v>
+        <v>-4.153846153846153</v>
       </c>
       <c r="AJ9" t="n">
-        <v>9.380952380952387</v>
+        <v>-15.57142857142857</v>
       </c>
       <c r="AK9" t="n">
-        <v>5.018421052631581</v>
+        <v>-8.578947368421051</v>
       </c>
       <c r="AL9" t="n">
-        <v>24.61904761904762</v>
+        <v>-32.66666666666666</v>
       </c>
       <c r="AM9" t="n">
-        <v>17.16315789473684</v>
+        <v>-25.88888888888889</v>
       </c>
       <c r="AN9" t="n">
-        <v>289.3333333333333</v>
+        <v>-328.8333333333334</v>
       </c>
       <c r="AO9" t="n">
-        <v>233.0935672514619</v>
+        <v>-276.7647058823529</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.6190476190476188</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-0.07368421052631557</v>
-      </c>
-      <c r="AR9" t="inlineStr"/>
+        <v>0.09150326797385655</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>-1.333333333333333</v>
+      </c>
       <c r="AS9" t="n">
-        <v>-0.8333333333333333</v>
+        <v>-1</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.69047619047619</v>
+        <v>4.999999999999996</v>
       </c>
       <c r="AU9" t="n">
-        <v>-1.084210526315792</v>
+        <v>4</v>
       </c>
       <c r="AV9" t="n">
-        <v>-26.34187730788858</v>
+        <v>10.33153287837516</v>
       </c>
       <c r="AW9" t="n">
-        <v>-9.884795596496737</v>
+        <v>14.58870889473109</v>
       </c>
       <c r="AX9" t="n">
-        <v>-0.002783979467607195</v>
+        <v>0.08341253341253342</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.01730762691596557</v>
+        <v>-0.02959240036862009</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.3333333333333333</v>
+        <v>-0.1428571428571428</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.0368421052631579</v>
+        <v>0.05263157894736842</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.5091478696741856</v>
+        <v>-1.190476190476191</v>
       </c>
       <c r="BC9" t="n">
-        <v>7.423484848484833</v>
+        <v>-2.801010101010064</v>
       </c>
       <c r="BD9" t="n">
-        <v>-1.83186026936027</v>
+        <v>-33083.83838383839</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.4793650793650794</v>
+        <v>-1.095238095238095</v>
       </c>
       <c r="BF9" t="n">
-        <v>10798.57503607504</v>
+        <v>-52547.61904761905</v>
       </c>
       <c r="BG9" t="n">
-        <v>6.392592592592607</v>
+        <v>-5.626260998817415</v>
       </c>
       <c r="BH9" t="n">
-        <v>11844644.66089466</v>
+        <v>-21908.04634453462</v>
       </c>
       <c r="BI9" t="n">
-        <v>-5.5</v>
+        <v>-102.5714285714286</v>
       </c>
       <c r="BJ9" t="n">
-        <v>9150217.300497619</v>
+        <v>-6.97258297258297</v>
       </c>
       <c r="BK9" t="n">
-        <v>-1.333333333333343</v>
+        <v>1.500000000000028</v>
       </c>
       <c r="BL9" t="n">
-        <v>254</v>
+        <v>-31112525.25252525</v>
       </c>
       <c r="BM9" t="n">
-        <v>5.618019686898407</v>
+        <v>0.7082251082251041</v>
       </c>
       <c r="BN9" t="n">
-        <v>34950000</v>
+        <v>-7.260606060606051</v>
       </c>
       <c r="BO9" t="n">
-        <v>8647.773419054882</v>
+        <v>-0.7035067296456061</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.5358141731139199</v>
+        <v>5.988095238095241</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.4914742664742562</v>
+        <v>-6.384601336547377</v>
       </c>
       <c r="BR9" t="n">
-        <v>3</v>
+        <v>-18268609.98227042</v>
       </c>
       <c r="BS9" t="n">
-        <v>212</v>
+        <v>-41159523.80952381</v>
       </c>
       <c r="BT9" t="n">
-        <v>-1.362564926809782</v>
+        <v>-0.8143382392829039</v>
       </c>
       <c r="BU9" t="n">
-        <v>5.562675711016695</v>
+        <v>-3.19047619047619</v>
       </c>
       <c r="BV9" t="n">
-        <v>68000</v>
+        <v>-83.11904761904761</v>
       </c>
       <c r="BW9" t="n">
-        <v>5</v>
+        <v>0.3915994148855759</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>4E8uaJWa</t>
+          <t>v3DAZKP9</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45590.64583333334</v>
+        <v>45604.6875</v>
       </c>
       <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jablonski s 
+  ger </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadion an der alten forsterei
+  berlin </t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>59</v>
+      </c>
+      <c r="H10" t="n">
+        <v>591</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>hpYJ6izc</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>YZPE6Sx7</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-0.4366666666666668</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-0.1523529411764708</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>-0.1578947368421053</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-1.666666666666667</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-0.1666666666666661</v>
+      </c>
+      <c r="V10" t="n">
+        <v>-4</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-0.05555555555555536</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.1666666666666666</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>-0.3333333333333335</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-1.110223024625157e-16</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.220446049250313e-16</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.210239528989529</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-1.490768125636547</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>134.3354007702477</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>79.05873290422457</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>-71</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>-10.46153846153845</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>-14</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>8.692307692307693</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>-9</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>-0.6842105263157876</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>-29.66666666666666</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>-10.11111111111111</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>-275.9999999999999</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>-117.8235294117648</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0.4477124183006533</v>
+      </c>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1.142857142857146</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>2.210526315789476</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>12.89388481721653</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>-2.769098793952303</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0.006053378146401403</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0.02433786762267351</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>-0.1428571428571428</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>-0.1578947368421053</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>-0.2845598845598847</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>2.524531024531058</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>164.5021645021625</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>-2.428571428571428</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>-8857.142857142855</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>-1.348672712271934</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>1201.528336180185</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>-179.5714285714286</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>-1.158585858585852</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>-6.124489795918407</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>-4842770.562770562</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>-0.3624819624819686</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>-1.852380952380955</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>-0.2805099281235275</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>2.724149659863947</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>-1.074407716071661</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>-2813225.241486928</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>-7614285.714285715</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>-1.504392286003963</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>-1.714285714285714</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>-161.8571428571429</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>-0.2615480919501856</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>raQ4MDUN</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45599.5625</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">badstubner f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">borussia park
+  monchengladbach </t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>59</v>
+      </c>
+      <c r="H11" t="n">
+        <v>591</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>vZA6VYpf</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>hAcTWKKN</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.3583333333333332</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.301783625730994</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.9999999999999998</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.1578947368421053</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.833333333333333</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.3105263157894749</v>
+      </c>
+      <c r="V11" t="n">
+        <v>2.333333333333332</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.8263157894736839</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-0.1666666666666665</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>-0.2947368421052632</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>-0.7578947368421052</v>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>-inf</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>-inf</t>
+        </is>
+      </c>
+      <c r="AD11" t="n">
+        <v>-180.8314726058619</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>-90.11119110872852</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>45</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>-11.20952380952382</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>52</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>3.428571428571431</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0.3333333333333357</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>-0.757894736842097</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>18</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>6.015789473684208</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>189</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>58.44444444444446</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0.830409356725146</v>
+      </c>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>-0.8333333333333357</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>2.331578947368421</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>-38.31179132353209</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>-23.97724740199433</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0.1366366366366366</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0.02076741054254223</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0.1078947368421052</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>0.3168831168831168</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>1.754545454545422</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>797.4025974025972</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1.571428571428571</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>-4142.857142857145</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>0.9629640164782245</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>2631.404032384744</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>129.2857142857143</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>0.8350649350649633</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>-3.575850340136071</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1850259.740259741</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>-0.8220779220779235</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>0.9155844155844193</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>0.2335999159389155</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>-4.681972789115644</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>2.955798764273752</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>2633265.379357484</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>13110714.28571429</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>-3.744467358401636</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>2.857142857142858</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>98.99999999999997</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>1.343167701863358</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>GnZmQeVb</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45599.47916666666</v>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t xml:space="preserve">petersen m 
   ger </t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mewa arena
-  mainz </t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">europa park stadion
+  freiburg </t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>EuakNmc1</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>88HSzjDr</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
+      <c r="G12" t="n">
         <v>59</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H12" t="n">
         <v>591</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I12" t="n">
         <v>0</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J12" t="n">
         <v>20242025</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>germany</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>vZA6VYpf</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>pfoInmcq</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>M5BRZDsC</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.066666666666666</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.3466666666666665</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.3157894736842106</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.947368421052631</v>
+      </c>
+      <c r="V12" t="n">
+        <v>8.333333333333334</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.5789473684210531</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.5000000000000002</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>-0.1578947368421053</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-0.3157894736842104</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>-6.556327239942969</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>-0.7303211522226261</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>-241.1668854156394</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>-37.56153757119236</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>-81</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>-11.42857142857142</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>-37</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>-19.28571428571429</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>14.83333333333334</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0.473684210526315</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>18.66666666666666</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>2.421052631578945</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>142</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>22.44444444444446</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>-0.5789473684210529</v>
+      </c>
+      <c r="AR12" t="inlineStr"/>
+      <c r="AS12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>-4.166666666666664</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>-2.578947368421055</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>-7.041901180662425</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>3.558561999318052</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>-0.08718485927788254</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>-0.00702993639745042</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0.05263157894736842</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>0.2269841269841273</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0.7206349206348364</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>1077.777777777781</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>3.952380952380953</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>62976.19047619048</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>0.08539132316127507</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>2290.752340045645</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>291.2857142857143</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>1.814285714285717</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>0.3387755102040728</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>4451269.841269841</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>-0.4873015873015838</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>1.600000000000009</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>0.1955684874324186</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>-1.593197278911564</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>3.01312779740563</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>3582265.507513594</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>14573809.52380952</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>0.3432569865890969</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>4.047619047619047</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>274.547619047619</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>1.117605985602058</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>dr2N9zoI</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45598.60416666666</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jablonski s 
+  ger </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">signal iduna park
+  dortmund </t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>59</v>
+      </c>
+      <c r="H13" t="n">
+        <v>591</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2VSFgl3c</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>YZPE6Sx7</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-0.1016666666666666</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>-0.4333333333333327</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-0.7894736842105262</v>
+      </c>
+      <c r="T13" t="n">
+        <v>-1.666666666666667</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-0.3157894736842111</v>
+      </c>
+      <c r="V13" t="n">
+        <v>2.166666666666666</v>
+      </c>
+      <c r="W13" t="n">
+        <v>-0.4210526315789469</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-1.666666666666667</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-1.263157894736842</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.05816267066267056</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0.2910664718991436</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>-85.66773522213614</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>-56.78274237617694</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>-60</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>2.857142857142861</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>1.714285714285715</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>3.315789473684216</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>19.00000000000001</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>14.21052631578948</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>148.8333333333333</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>117.2777777777778</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0.6333333333333331</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR13" t="inlineStr"/>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>-1.333333333333332</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>-0.8947368421052655</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>4.359741544465315</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>-7.909971412735068</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>-0.0185980685980686</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0.02437173100414217</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>-0.2631578947368421</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0.3220418470418469</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>2.426911976911981</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>949.4227994228058</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>-1.142857142857143</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>-81285.71428571429</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>0.6612831017574621</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>-7253.141543698825</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>-95.28571428571425</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>-0.07139249639250522</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>2.021428571428544</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>6312572.150072142</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>0.7038239538239601</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>1.313636363636377</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>-0.06500505305790605</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>-2.900000000000002</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>-0.536879129642287</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>-1218881.350586489</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>-19157142.85714286</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>-0.7845939093341201</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>-2.857142857142858</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>-92.14285714285717</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>-0.4593842800278019</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>AoSdOZaB</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45598.47916666666</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">welz t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">volkswagen arena
+  wolfsburg </t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>fTVNku3I</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>59</v>
+      </c>
+      <c r="H14" t="n">
+        <v>591</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>0jdIgO6t</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>IkCftsQm</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-0.8549999999999998</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.2355555555555553</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.1578947368421054</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-2.499999999999999</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.3684210526315783</v>
+      </c>
+      <c r="V14" t="n">
+        <v>-8.499999999999998</v>
+      </c>
+      <c r="W14" t="n">
+        <v>-1.105263157894738</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.1666666666666665</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.3157894736842106</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-0.9999999999999999</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>-0.6116402116402111</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>-0.7007083817455335</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>-125.0271002450798</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>-45.72931586456443</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>87</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>-4.214285714285708</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>-6.642857142857153</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>-5.166666666666664</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0.6315789473684248</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>2.333333333333329</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>-23.33333333333337</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>5.555555555555543</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0.2105263157894739</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0.8333333333333333</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0.7916666666666667</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0.3333333333333321</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>-3.578947368421051</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>-0.177429880779826</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>20.06687377380022</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0.08633485840799655</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>-0.0240767085096267</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0.2105263157894737</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0.2534722222222219</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>-0.2569444444444571</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>12565.97222222223</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0.5714285714285721</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>107571.4285714286</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>1.296457873420522</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>12385.22011675483</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>78</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>3.513888888888886</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>-0.7469387755101877</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>4457986.111111112</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>-1.729166666666664</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>1.267361111111114</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>0.3073540740059979</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>-2.032312925170068</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>1.037144889853877</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>3070674.865241152</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>44832142.85714286</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>-0.2715667207871775</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>3.571428571428572</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>58.71428571428572</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>0.6064457202338716</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>2q7yHiho</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45598.47916666666</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dingert c 
+  ger </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">holstein stadion
+  kiel </t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>59</v>
+      </c>
+      <c r="H15" t="n">
+        <v>591</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>GzfvcwRj</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>KUx4Q7x1</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>-0.7516666666666669</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>-0.08444444444444454</v>
+      </c>
+      <c r="R15" t="n">
+        <v>-1.110223024625157e-16</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>-2.833333333333333</v>
+      </c>
+      <c r="U15" t="n">
+        <v>-0.8421052631578938</v>
+      </c>
+      <c r="V15" t="n">
+        <v>-9.500000000000002</v>
+      </c>
+      <c r="W15" t="n">
+        <v>-2.947368421052632</v>
+      </c>
+      <c r="X15" t="n">
+        <v>-0.8333333333333335</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>-0.3157894736842106</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.1578947368421053</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>3.785945467930762</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0.7570578908264274</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>35.99054298858655</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>-77.17393224957985</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>-56</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>19.42857142857142</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>-37</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>2.357142857142854</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>-2.333333333333329</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>-1.368421052631582</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>-1.333333333333329</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>8.315789473684205</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>-67.83333333333337</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>116.3333333333333</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>-0.1666666666666665</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0.05263157894736836</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>4.333333333333336</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0.6842105263157876</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>-2.693001090812416</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>-12.15220870772914</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>-0.01981230737539318</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0.009886114482322225</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>2.775557561562891e-17</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0.1578947368421053</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>-0.02857142857142847</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>-0.9071428571428442</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>-5826.5873015873</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>-0.7142857142857144</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>-17857.14285714286</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>0.6032306203113507</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>-3969.549467384206</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>-49</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>-2.324603174603183</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>2.273809523809518</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>-1396309.523809524</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>-0.3527777777777743</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>-3.025396825396825</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>-0.04567044208987947</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>1.011904761904763</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>-0.9790390089882237</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>-274490.9282622973</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>-1450000</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>-0.3190858660918252</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>-44.28571428571431</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>-0.2459574218703438</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>8MVuSH0n</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45598.47916666666</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reichel t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prezero arena
+  sinsheim </t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>59</v>
+      </c>
+      <c r="H16" t="n">
+        <v>591</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
         <is>
           <t>4ljanukM</t>
         </is>
       </c>
-      <c r="O10" t="n">
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>f3ddUIXs</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
         <v>0</v>
       </c>
-      <c r="P10" t="n">
-        <v>-1.483333333333333</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>-0.344970760233918</v>
-      </c>
-      <c r="R10" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="S10" t="n">
-        <v>-0.1578947368421053</v>
-      </c>
-      <c r="T10" t="n">
-        <v>-4.833333333333334</v>
-      </c>
-      <c r="U10" t="n">
-        <v>-1.15</v>
-      </c>
-      <c r="V10" t="n">
-        <v>-10.33333333333333</v>
-      </c>
-      <c r="W10" t="n">
-        <v>-0.3342105263157897</v>
-      </c>
-      <c r="X10" t="n">
-        <v>2.220446049250313e-16</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0.8210526315789475</v>
-      </c>
-      <c r="Z10" t="n">
+      <c r="P16" t="n">
+        <v>-0.6650000000000005</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-0.8944444444444446</v>
+      </c>
+      <c r="R16" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AA10" t="n">
-        <v>1.231578947368421</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>4.498872124607418</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.551447966225779</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>187.1590683149671</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>85.90149454391954</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>36</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>30.37083333333334</v>
-      </c>
-      <c r="AH10" t="n">
+      <c r="S16" t="n">
+        <v>-1.263157894736842</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.6666666666666656</v>
+      </c>
+      <c r="U16" t="n">
+        <v>-1.368421052631578</v>
+      </c>
+      <c r="V16" t="n">
+        <v>-7.166666666666666</v>
+      </c>
+      <c r="W16" t="n">
+        <v>-8.157894736842106</v>
+      </c>
+      <c r="X16" t="n">
+        <v>-1.110223024625157e-16</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>-0.2105263157894737</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-0.4736842105263159</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>3.633037659508247</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>4.58502291913373</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>-39.33692937281862</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>69.05037102856565</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>-86</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>-39.14285714285714</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>-20</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>-27.21428571428572</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>-4.333333333333336</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>-2.684210526315795</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>7.666666666666671</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>-8.31578947368422</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>38.83333333333326</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>-130.5555555555555</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>2.266666666666667</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0.8654970760233918</v>
+      </c>
+      <c r="AR16" t="inlineStr"/>
+      <c r="AS16" t="n">
+        <v>-0.08333333333333331</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>1.666666666666668</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0.2105263157894726</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>-2.841206810020299</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>22.81790141623551</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>-0.005568437113302981</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>-0.04451646003810688</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0.6384920634920637</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0.8224747474747289</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>12888.20346320346</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>2.142857142857143</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>113142.8571428572</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>5.928953335720252</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>7818.098818474758</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>203.5714285714286</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>5.482142857142861</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>-4.249149659863974</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>5428935.786435787</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>0.4831168831168888</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>4.477958152958166</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>0.1783387039026139</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>-1.761394557823124</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>3.297350519155046</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>3515117.257429288</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>36995714.28571428</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>0.236591478696738</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>195.5714285714286</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>-1.381358157298003</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>485V7EFU</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45598.47916666666</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">exner f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">deutsche bank park
+  frankfurt </t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>59</v>
+      </c>
+      <c r="H17" t="n">
+        <v>591</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>hpYJ6izc</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>K6A2elS9</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.751666666666667</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.9757777777777779</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.300751879699248</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.38095238095238</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.77635683940025e-15</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.503759398496239</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.666666666666666</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.290726817042607</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.87218045112782</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>-1.74920014625897</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>-0.01499400194638767</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>-79.51148426683434</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>4.440992080579775</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>-76</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>-17.65178571428571</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>-26</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0.0714285714285694</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0.4999999999999964</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>4.345864661654126</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>2.666666666666657</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0.1654135338345952</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>-46.16666666666663</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>-23.80555555555554</v>
+      </c>
+      <c r="AP17" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AI10" t="n">
-        <v>9.495833333333337</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>-11.83333333333333</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>-0.3500000000000014</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>-26.66666666666667</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>-9.336842105263159</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>-274.3333333333334</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>-91.5555555555556</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>2.220446049250313e-16</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>0.6842105263157894</v>
-      </c>
-      <c r="AR10" t="inlineStr"/>
-      <c r="AS10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>0.6947368421052644</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>17.97077793280251</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>5.438918014249737</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>-0.03816941941941943</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>-0.01899048350800872</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>-0.3333333333333333</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>0.1552631578947369</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>-0.04276753312794512</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>-0.5740740740740762</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>1.177777777777777</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>-0.03888888888888942</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>1153.703703703704</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>-0.62222222222222</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>-1392037.037037037</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>6.357142857142858</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>-2577566.600542859</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>2.214285714285722</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>-391</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>-2.117724771414714</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>-23725000</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>-724.0372835910566</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>0.4972910289557717</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>-1.664814814814775</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>-5</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>-346</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>-0.1388132716507933</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>-0.3227184397092913</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>-54000</v>
-      </c>
-      <c r="BW10" t="n">
-        <v>-7</v>
+      <c r="AQ17" t="n">
+        <v>-0.5952380952380953</v>
+      </c>
+      <c r="AR17" t="inlineStr"/>
+      <c r="AS17" t="n">
+        <v>-0.3333333333333334</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>-3.666666666666668</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>-1.892230576441106</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>7.796238941329186</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>8.943996362043933</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>-0.07259643415389991</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>-0.01363569478676256</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0.2807017543859649</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>0.6972222222222224</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>-0.5004629629629562</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>17612.96296296297</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>-1.857142857142857</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>-47571.42857142857</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>7.216747627771511</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>10709.18332552012</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>-129.5714285714286</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>7.671296296296291</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>-9.854761904761915</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>12465254.62962963</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>-3.710185185185185</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>4.982407407407422</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>0.4303632457767796</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>-6.904761904761905</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>4.338418275542338</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>7815724.254258199</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>-5496428.571428571</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>-0.7627889206228531</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>-2</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>-145.8571428571429</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>-3.177228563490171</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>jVWMBdG5</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45598.47916666666</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">osmers h 
+  ger </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allianz arena
+  munich </t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>59</v>
+      </c>
+      <c r="H18" t="n">
+        <v>591</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>8f6APkLc</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>UgdQz0fK</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.218333333333334</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.728888888888889</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.736842105263158</v>
+      </c>
+      <c r="T18" t="n">
+        <v>7.833333333333333</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3.842105263157895</v>
+      </c>
+      <c r="V18" t="n">
+        <v>16.66666666666667</v>
+      </c>
+      <c r="W18" t="n">
+        <v>8.94736842105263</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>2.210526315789473</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.421052631578947</v>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>-inf</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>-inf</t>
+        </is>
+      </c>
+      <c r="AD18" t="n">
+        <v>-463.6754395090367</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>-280.1749164426976</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>186</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>63.42857142857142</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>61</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>29.71428571428572</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>15.66666666666667</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>7.842105263157897</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>48.99999999999999</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>37.78947368421053</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>605.1666666666666</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>479.4444444444445</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>-0.7581699346405228</v>
+      </c>
+      <c r="AR18" t="inlineStr"/>
+      <c r="AS18" t="inlineStr"/>
+      <c r="AT18" t="n">
+        <v>-5.833333333333339</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>-4.368421052631581</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>-47.28286620704968</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>-29.73018285699402</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0.01753125509434089</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>-0.0116297834819149</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0.3684210526315789</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>1.905194805194805</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>-2.686435786435737</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>54157.72005772006</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>2.571428571428572</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>128857.1428571428</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>8.081757088800444</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>48869.35076662243</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>230.4285714285714</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>7.993506493506487</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>5.214285714285751</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>41822572.15007215</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>0.8418470418470463</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>8.850793650793634</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>1.544704899503661</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>-6.780952380952385</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>7.976205218929678</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>31829658.1680918</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>85292857.14285713</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>0.8616264927023565</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>3.714285714285714</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>182.1428571428571</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>0.2595840090422179</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>IHYEDIog</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45597.6875</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hartmann r 
+  ger </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bayarena
+  leverkusen </t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>59</v>
+      </c>
+      <c r="H19" t="n">
+        <v>591</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>4fuCGs9P</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>A15eUM4C</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.2283333333333337</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.8790726817042607</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1.022727272727272</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.500000000000001</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.590909090909092</v>
+      </c>
+      <c r="V19" t="n">
+        <v>3.333333333333334</v>
+      </c>
+      <c r="W19" t="n">
+        <v>4.349999999999998</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.3333333333333335</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.4545454545454544</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0.9954545454545456</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>-0.4519385706885708</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>-1.018050315912158</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>-41.49683430924145</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>54.90525224316849</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>39</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>10.45882352941176</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>38</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>32.70196078431373</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>-0.8333333333333357</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>5.690909090909091</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>71.16666666666657</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>-29.52631578947376</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>1.833333333333334</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0.461904761904762</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0.06666666666666671</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>1.166666666666664</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>-1.190909090909091</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>5.884360834928646</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>-2.925423930992515</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0.04128179021796043</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0.01365380138206914</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0.01818181818181819</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>1.61984126984127</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>-1.62348484848485</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>74223.44877344876</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>-2.785714285714286</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>43214.28571428571</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>5.705744052006764</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>54847.29470735663</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>-209.5714285714286</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>6.219769119769126</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>-3.847619047619048</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>37889145.02164502</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>1.745418470418471</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>7.62222222222222</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>0.7445806392732532</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>4.478571428571431</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>5.957852614730101</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>24833570.65633271</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>24578571.42857143</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>-4.351062530275243</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>-1.642857142857143</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>-175.4285714285714</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>0.09274446620753451</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/data_preparation/df_constructed.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_constructed.xlsx
@@ -695,144 +695,144 @@
       </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_start</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_value_player_start</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_value_player_sub</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_wage_player_miss</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
           <t>dif_sum_pot_player_miss</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_start</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_start</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_start</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_value_player_miss</t>
+        </is>
+      </c>
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_wage_player_sub</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_start</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="BJ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="BK1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_value_player_miss</t>
-        </is>
-      </c>
-      <c r="BL1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="BM1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_wage_player_miss</t>
-        </is>
-      </c>
-      <c r="BN1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="BO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="BP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="BQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="BR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="BS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="BT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="BU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_sub</t>
-        </is>
-      </c>
-      <c r="BV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="BW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>raQ4MDUN</t>
+          <t>xMovyDqH</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45599.5625</v>
+        <v>45606.64583333334</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">burda m 
+          <t xml:space="preserve">brych f 
   ger </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">borussia park
-  monchengladbach </t>
+          <t xml:space="preserve">voith arena
+  heidenheim </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>88HSzjDr</t>
+          <t>KWixEVWi</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ig1f1fy3</t>
+          <t>nwkTahLL</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -859,231 +859,227 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>UgdQz0fK</t>
+          <t>A15eUM4C</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>4fuCGs9P</t>
+          <t>2VSFgl3c</t>
         </is>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3583333333333332</v>
+        <v>0.1257142857142854</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.301783625730994</v>
+        <v>-0.006666666666666821</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8571428571428574</v>
+        <v>0.375</v>
       </c>
       <c r="S2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="T2" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.4500000000000002</v>
+      </c>
+      <c r="V2" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="W2" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="X2" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AA2" t="n">
         <v>0.1499999999999999</v>
       </c>
-      <c r="T2" t="n">
-        <v>1.285714285714285</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0.4952380952380953</v>
-      </c>
-      <c r="V2" t="n">
-        <v>3.857142857142856</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.416666666666668</v>
-      </c>
-      <c r="X2" t="n">
-        <v>-0.4285714285714286</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>-0.3785714285714286</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>-1.714285714285714</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>-1.014285714285714</v>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>-inf</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>-inf</t>
-        </is>
+      <c r="AB2" t="n">
+        <v>-5.96651138893786</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>-1.030332965538073</v>
       </c>
       <c r="AD2" t="n">
-        <v>-180.8314726058619</v>
+        <v>-97.7201017328309</v>
       </c>
       <c r="AE2" t="n">
-        <v>-90.11119110872852</v>
+        <v>31.43980213135816</v>
       </c>
       <c r="AF2" t="n">
-        <v>45</v>
+        <v>-87</v>
       </c>
       <c r="AG2" t="n">
-        <v>-11.20952380952382</v>
+        <v>-38.07692307692308</v>
       </c>
       <c r="AH2" t="n">
-        <v>52</v>
+        <v>-50</v>
       </c>
       <c r="AI2" t="n">
-        <v>3.428571428571431</v>
+        <v>-26.23076923076923</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-7.105427357601002e-15</v>
+        <v>3.625</v>
       </c>
       <c r="AK2" t="n">
-        <v>-0.8285714285714363</v>
+        <v>-2.649999999999999</v>
       </c>
       <c r="AL2" t="n">
-        <v>18.28571428571429</v>
+        <v>-2.25</v>
       </c>
       <c r="AM2" t="n">
-        <v>6.676190476190484</v>
+        <v>-8</v>
       </c>
       <c r="AN2" t="n">
-        <v>189</v>
+        <v>-0.8571428571428896</v>
       </c>
       <c r="AO2" t="n">
-        <v>58.44444444444446</v>
+        <v>-90.55555555555554</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.285714285714286</v>
+        <v>-0.875</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.7815789473684209</v>
+        <v>-0.6000000000000003</v>
       </c>
       <c r="AR2" t="n">
-        <v>-0.6666666666666667</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="AS2" t="n">
-        <v>-0.5</v>
+        <v>0.5</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.428571428571431</v>
+        <v>-5.375</v>
       </c>
       <c r="AU2" t="n">
-        <v>2.94761904761905</v>
+        <v>1.049999999999997</v>
       </c>
       <c r="AV2" t="n">
-        <v>-38.31179132353209</v>
+        <v>4.48678236854289</v>
       </c>
       <c r="AW2" t="n">
-        <v>-23.97724740199433</v>
+        <v>-0.364527501520449</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.1366366366366366</v>
+        <v>-0.0479449874094299</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.02076741054254223</v>
+        <v>-0.05492320041236257</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.1428571428571428</v>
+        <v>-0.375</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.05238095238095239</v>
+        <v>-0.1</v>
       </c>
       <c r="BB2" t="n">
-        <v>238</v>
+        <v>0.3775510204081627</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.2883116883116883</v>
+        <v>-0.3076178451178448</v>
       </c>
       <c r="BD2" t="n">
-        <v>1600259.740259741</v>
+        <v>-6356085.858585859</v>
       </c>
       <c r="BE2" t="n">
-        <v>2314.833827227587</v>
+        <v>2.203156565656567</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.2467986737028909</v>
+        <v>0.7908282380197704</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.19652268021833</v>
+        <v>1.622979797979809</v>
       </c>
       <c r="BH2" t="n">
-        <v>325.9740259740247</v>
+        <v>-6041529.678057254</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.8064935064934957</v>
+        <v>-143571.4285714286</v>
       </c>
       <c r="BJ2" t="n">
-        <v>203</v>
+        <v>-3.909595624837209</v>
       </c>
       <c r="BK2" t="n">
-        <v>16725000</v>
+        <v>-227.5714285714286</v>
       </c>
       <c r="BL2" t="n">
-        <v>3</v>
+        <v>-5.193139730639714</v>
       </c>
       <c r="BM2" t="n">
-        <v>15000</v>
+        <v>-2.571428571428571</v>
       </c>
       <c r="BN2" t="n">
-        <v>-3.607142857142858</v>
+        <v>-210.8571428571429</v>
       </c>
       <c r="BO2" t="n">
-        <v>-3.425426797513268</v>
+        <v>-2.616203703703704</v>
       </c>
       <c r="BP2" t="n">
-        <v>5</v>
+        <v>-0.3497862912847685</v>
       </c>
       <c r="BQ2" t="n">
-        <v>-2.964285714285722</v>
+        <v>-5.285714285714286</v>
       </c>
       <c r="BR2" t="n">
-        <v>2.654968254204107</v>
+        <v>2.296938775510171</v>
       </c>
       <c r="BS2" t="n">
-        <v>-0.9077922077922089</v>
+        <v>-13729.96632996634</v>
       </c>
       <c r="BT2" t="n">
-        <v>2.040259740259785</v>
+        <v>0.9093779791404835</v>
       </c>
       <c r="BU2" t="n">
-        <v>2646835.161025092</v>
+        <v>-6.070304050604008</v>
       </c>
       <c r="BV2" t="n">
-        <v>1.225939265866529</v>
+        <v>-53367857.14285714</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.6727272727272862</v>
+        <v>-13235.1108413253</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>GnZmQeVb</t>
+          <t>UkaNveph</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45599.47916666666</v>
+        <v>45606.5625</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stegemann s 
+          <t xml:space="preserve">schlager d 
   ger </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">europa park stadion
-  freiburg </t>
+          <t xml:space="preserve">mhparena
+  stuttgart </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>fiEQZ7C7</t>
+          <t>nJQmYp1B</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>EuakNmc1</t>
+          <t>8vndvXTk</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1110,225 +1106,227 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>YZPE6Sx7</t>
+          <t>hAcTWKKN</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>K6A2elS9</t>
+          <t>UkPWzhq8</t>
         </is>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.066666666666666</v>
+        <v>0.03571428571428559</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3466666666666665</v>
+        <v>0.5514035087719293</v>
       </c>
       <c r="R3" t="n">
-        <v>1.285714285714286</v>
+        <v>0.375</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="T3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>1.649999999999999</v>
+        <v>2.628571428571429</v>
       </c>
       <c r="V3" t="n">
-        <v>9.142857142857141</v>
+        <v>5.5</v>
       </c>
       <c r="W3" t="n">
-        <v>1.25</v>
+        <v>4.130952380952381</v>
       </c>
       <c r="X3" t="n">
-        <v>1.142857142857143</v>
+        <v>-0.75</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.1000000000000001</v>
+        <v>0.6547619047619049</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.142857142857143</v>
+        <v>-0.375</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="AB3" t="n">
-        <v>-6.738756681855879</v>
+        <v>-2.656135712090627</v>
       </c>
       <c r="AC3" t="n">
-        <v>-1.085471761278161</v>
+        <v>-2.8619219800749</v>
       </c>
       <c r="AD3" t="n">
-        <v>-241.1668854156394</v>
+        <v>-122.8561460456103</v>
       </c>
       <c r="AE3" t="n">
-        <v>-37.56153757119236</v>
+        <v>-176.5155618910406</v>
       </c>
       <c r="AF3" t="n">
-        <v>-81</v>
+        <v>64</v>
       </c>
       <c r="AG3" t="n">
-        <v>-11.42857142857142</v>
+        <v>17.02197802197801</v>
       </c>
       <c r="AH3" t="n">
-        <v>-37</v>
+        <v>25</v>
       </c>
       <c r="AI3" t="n">
-        <v>-19.28571428571429</v>
+        <v>4.489010989010993</v>
       </c>
       <c r="AJ3" t="n">
-        <v>16.14285714285715</v>
+        <v>8</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.649999999999999</v>
+        <v>-1.490476190476194</v>
       </c>
       <c r="AL3" t="n">
-        <v>23.14285714285714</v>
+        <v>18.5</v>
       </c>
       <c r="AM3" t="n">
-        <v>4.799999999999997</v>
+        <v>21.22857142857143</v>
       </c>
       <c r="AN3" t="n">
-        <v>142</v>
+        <v>202.8571428571428</v>
       </c>
       <c r="AO3" t="n">
-        <v>22.44444444444446</v>
+        <v>247.3187134502924</v>
       </c>
       <c r="AP3" t="n">
-        <v>-1.714285714285714</v>
+        <v>-0.875</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="AR3" t="inlineStr"/>
+        <v>-0.7192982456140349</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>-0.5</v>
+      </c>
       <c r="AS3" t="n">
-        <v>1</v>
+        <v>-0.9166666666666667</v>
       </c>
       <c r="AT3" t="n">
-        <v>-3.571428571428569</v>
+        <v>0.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>-2.449999999999998</v>
+        <v>0.8857142857142861</v>
       </c>
       <c r="AV3" t="n">
-        <v>-7.041901180662425</v>
+        <v>-20.53162502855815</v>
       </c>
       <c r="AW3" t="n">
-        <v>3.558561999318052</v>
+        <v>-27.49674209802243</v>
       </c>
       <c r="AX3" t="n">
-        <v>-0.08718485927788254</v>
+        <v>-0.005279115814673316</v>
       </c>
       <c r="AY3" t="n">
-        <v>-0.00702993639745042</v>
+        <v>-0.02466191651860965</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.4285714285714285</v>
+        <v>-0.25</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.1</v>
+        <v>0.2880952380952381</v>
       </c>
       <c r="BB3" t="n">
-        <v>136</v>
+        <v>2.738095238095241</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.2682539682539684</v>
+        <v>-0.208670033670034</v>
       </c>
       <c r="BD3" t="n">
-        <v>4831111.111111111</v>
+        <v>-476979.1666666698</v>
       </c>
       <c r="BE3" t="n">
-        <v>1934.469827040448</v>
+        <v>0.3305134680134643</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.1747601641030867</v>
+        <v>0.7802279736731919</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.153080175277928</v>
+        <v>0.5404040404040131</v>
       </c>
       <c r="BH3" t="n">
-        <v>1563.492063492064</v>
+        <v>2439717.465186602</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.555555555555543</v>
+        <v>65428.57142857143</v>
       </c>
       <c r="BJ3" t="n">
-        <v>124</v>
+        <v>1.59123839857682</v>
       </c>
       <c r="BK3" t="n">
-        <v>-5500000</v>
+        <v>214.5714285714286</v>
       </c>
       <c r="BL3" t="n">
-        <v>2</v>
+        <v>-1.725589225589218</v>
       </c>
       <c r="BM3" t="n">
-        <v>-1000</v>
+        <v>2.714285714285714</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.1999999999999993</v>
+        <v>201.2857142857143</v>
       </c>
       <c r="BO3" t="n">
-        <v>-0.2143660626305746</v>
+        <v>-0.1446127946127973</v>
       </c>
       <c r="BP3" t="n">
-        <v>2</v>
+        <v>0.07122063308208793</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.4666666666666686</v>
+        <v>3.285714285714286</v>
       </c>
       <c r="BR3" t="n">
-        <v>2.791519153948258</v>
+        <v>6.080952380952397</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.1682539682539641</v>
+        <v>-6611.279461279468</v>
       </c>
       <c r="BT3" t="n">
-        <v>1.27936507936505</v>
+        <v>1.513768479649865</v>
       </c>
       <c r="BU3" t="n">
-        <v>3007429.573139845</v>
+        <v>-2.447670366913783</v>
       </c>
       <c r="BV3" t="n">
-        <v>-0.2236122782793331</v>
+        <v>17857142.85714286</v>
       </c>
       <c r="BW3" t="n">
-        <v>2.020634920634919</v>
+        <v>-1537.794621206966</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>dr2N9zoI</t>
+          <t>UJQITUyi</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45598.60416666666</v>
+        <v>45606.47916666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">zwayer f 
+          <t xml:space="preserve">stegemann s 
   ger </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">signal iduna park
-  dortmund </t>
+          <t xml:space="preserve">wwk arena
+  augsburg </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>nP1i5US1</t>
+          <t>fTVNku3I</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>KbS1suSm</t>
+          <t>hQAtP9Sl</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1367,213 +1365,201 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.1016666666666666</v>
+        <v>1.11</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.4333333333333327</v>
+        <v>0.1322222222222222</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.4285714285714285</v>
+        <v>1.5</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7499999999999998</v>
+        <v>0.45</v>
       </c>
       <c r="T4" t="n">
-        <v>-2.428571428571429</v>
+        <v>-0.5</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6500000000000004</v>
+        <v>-0.7500000000000004</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8571428571428577</v>
+        <v>4.625</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.7499999999999982</v>
+        <v>3.149999999999999</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.857142857142857</v>
+        <v>0.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>-1.1</v>
+        <v>-0.4500000000000002</v>
       </c>
       <c r="Z4" t="n">
-        <v>-2.571428571428571</v>
+        <v>1.125</v>
       </c>
       <c r="AA4" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>-1.516357376283847</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>-2.510531629763525</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>37.15846521413158</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>-12.93410610212396</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>-1.07692307692308</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>40</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>11.07692307692308</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>-1.700000000000003</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>-15</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>-10.8</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>-107.5714285714286</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>-129.0555555555555</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>-0.1999999999999997</v>
+      </c>
+      <c r="AR4" t="n">
         <v>-1.5</v>
       </c>
-      <c r="AB4" t="n">
-        <v>-2.868949701092559</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>-0.7450680482770089</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>-85.66773522213614</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>-56.78274237617694</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>-60</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>2.857142857142861</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>1.714285714285715</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>2.714285714285708</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>3.799999999999997</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>19.71428571428572</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>148.8333333333333</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>117.2777777777778</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1.105263157894737</v>
-      </c>
-      <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>-0.3333333333333334</v>
       </c>
       <c r="AT4" t="n">
-        <v>-1.285714285714288</v>
+        <v>2</v>
       </c>
       <c r="AU4" t="n">
-        <v>-0.9000000000000021</v>
+        <v>4.349999999999998</v>
       </c>
       <c r="AV4" t="n">
-        <v>4.359741544465315</v>
+        <v>-4.133230403948861</v>
       </c>
       <c r="AW4" t="n">
-        <v>-7.909971412735068</v>
+        <v>-22.96455133408513</v>
       </c>
       <c r="AX4" t="n">
-        <v>-0.0185980685980686</v>
+        <v>-0.05033218400470944</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.02437173100414217</v>
+        <v>0.0445031025923889</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-0.5714285714285714</v>
+        <v>0.125</v>
       </c>
       <c r="BA4" t="n">
-        <v>-0.3</v>
+        <v>-0.05000000000000002</v>
       </c>
       <c r="BB4" t="n">
-        <v>159</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>0.2993145743145744</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>7960137.08513708</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>-6025.760591317878</v>
-      </c>
+        <v>-0.7981292517006828</v>
+      </c>
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="inlineStr"/>
       <c r="BF4" t="n">
-        <v>-0.06837806893092169</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>-0.2665271371706623</v>
-      </c>
+        <v>0.6380313947747709</v>
+      </c>
+      <c r="BG4" t="inlineStr"/>
       <c r="BH4" t="n">
-        <v>837.4098124098018</v>
+        <v>-517740.6465975549</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.3490620490620699</v>
+        <v>-79857.14285714287</v>
       </c>
       <c r="BJ4" t="n">
-        <v>139</v>
+        <v>0.5826973921546283</v>
       </c>
       <c r="BK4" t="n">
-        <v>-1000000</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>2</v>
-      </c>
+        <v>-110.4285714285714</v>
+      </c>
+      <c r="BL4" t="inlineStr"/>
       <c r="BM4" t="n">
-        <v>-18000</v>
+        <v>-1.142857142857143</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>-1.201458988699159</v>
-      </c>
+        <v>-104.4285714285714</v>
+      </c>
+      <c r="BO4" t="inlineStr"/>
       <c r="BP4" t="n">
-        <v>4</v>
+        <v>-0.1423175599984809</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.125</v>
+        <v>-4.857142857142858</v>
       </c>
       <c r="BR4" t="n">
-        <v>-0.5983870661502095</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>0.333694083694084</v>
-      </c>
+        <v>0.5443877551020364</v>
+      </c>
+      <c r="BS4" t="inlineStr"/>
       <c r="BT4" t="n">
-        <v>2.159054834054842</v>
+        <v>-0.3412669932406835</v>
       </c>
       <c r="BU4" t="n">
-        <v>-899322.8188404515</v>
+        <v>-0.7226451545530495</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.5358862763606282</v>
+        <v>-26432142.85714286</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.446753246753261</v>
+        <v>-3782.336641793878</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2q7yHiho</t>
+          <t>j5mWxZE4</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45598.47916666666</v>
+        <v>45605.60416666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">kampka r 
+          <t xml:space="preserve">dankert b 
   ger </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">holstein stadion
-  kiel </t>
+          <t xml:space="preserve">red bull arena
+  leipzig </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>63WsD2ei</t>
+          <t>KbS1suSm</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>KWixEVWi</t>
+          <t>88HSzjDr</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1600,227 +1586,225 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>4fX0k7gg</t>
+          <t>IkCftsQm</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>4ljanukM</t>
+          <t>4fuCGs9P</t>
         </is>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.7516666666666669</v>
+        <v>0.09857142857142875</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.08444444444444454</v>
+        <v>0.5766666666666667</v>
       </c>
       <c r="R5" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>0.7499999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.999999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6499999999999995</v>
+        <v>1.45</v>
       </c>
       <c r="V5" t="n">
-        <v>-7.428571428571429</v>
+        <v>-1.625</v>
       </c>
       <c r="W5" t="n">
-        <v>-2.549999999999999</v>
+        <v>2.149999999999999</v>
       </c>
       <c r="X5" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.703756731048636</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.1320598648620592</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>-88.44062437232091</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>-67.89257486745072</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>107</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>51</v>
+      </c>
+      <c r="AH5" t="n">
         <v>-1</v>
       </c>
-      <c r="Y5" t="n">
-        <v>-0.3999999999999997</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>-0.4285714285714286</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0.1499999999999999</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2.639653938498477</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0.5073002343803426</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>35.99054298858655</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>-77.17393224957985</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>-56</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>19.42857142857142</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>-37</v>
-      </c>
       <c r="AI5" t="n">
-        <v>2.357142857142854</v>
+        <v>9.384615384615387</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.8571428571428541</v>
+        <v>-0.125</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.8999999999999986</v>
+        <v>-1.149999999999999</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.8571428571428612</v>
+        <v>-8.25</v>
       </c>
       <c r="AM5" t="n">
-        <v>8.599999999999994</v>
+        <v>4.100000000000009</v>
       </c>
       <c r="AN5" t="n">
-        <v>-67.83333333333337</v>
+        <v>-19.57142857142861</v>
       </c>
       <c r="AO5" t="n">
-        <v>116.3333333333333</v>
+        <v>75.8888888888888</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.7142857142857144</v>
+        <v>-0.1071428571428572</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.3500000000000001</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0</v>
-      </c>
+        <v>-0.5789473684210527</v>
+      </c>
+      <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="n">
-        <v>-0.25</v>
+        <v>2</v>
       </c>
       <c r="AT5" t="n">
-        <v>4.428571428571431</v>
+        <v>-1.25</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.8999999999999986</v>
+        <v>-0.9499999999999993</v>
       </c>
       <c r="AV5" t="n">
-        <v>-2.693001090812416</v>
+        <v>0.03468513393456973</v>
       </c>
       <c r="AW5" t="n">
-        <v>-12.15220870772914</v>
+        <v>-10.49858712412411</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.01981230737539318</v>
+        <v>-0.0555051555051555</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.009886114482322225</v>
+        <v>-0.03692391287234778</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.1428571428571428</v>
+        <v>0.375</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="BB5" t="n">
-        <v>223</v>
+        <v>1.817687074829934</v>
       </c>
       <c r="BC5" t="n">
-        <v>-0.04155844155844157</v>
+        <v>0.895486111111111</v>
       </c>
       <c r="BD5" t="n">
-        <v>-1291893.93939394</v>
+        <v>22125902.77777778</v>
       </c>
       <c r="BE5" t="n">
-        <v>-4004.391230176281</v>
+        <v>0.2128472222222229</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.04567044208987947</v>
+        <v>2.591271312630198</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.1462384038283489</v>
+        <v>-1.06701388888888</v>
       </c>
       <c r="BH5" t="n">
-        <v>-5604.509379509376</v>
+        <v>15584271.31802334</v>
       </c>
       <c r="BI5" t="n">
-        <v>-2.058369408369416</v>
+        <v>101000</v>
       </c>
       <c r="BJ5" t="n">
-        <v>221</v>
+        <v>4.71436943766308</v>
       </c>
       <c r="BK5" t="n">
-        <v>8325000</v>
+        <v>-108.8571428571429</v>
       </c>
       <c r="BL5" t="n">
-        <v>3</v>
+        <v>6.126388888888883</v>
       </c>
       <c r="BM5" t="n">
-        <v>53000</v>
+        <v>-1.714285714285714</v>
       </c>
       <c r="BN5" t="n">
-        <v>4.600000000000001</v>
+        <v>-92.14285714285711</v>
       </c>
       <c r="BO5" t="n">
-        <v>-0.2860187261923954</v>
+        <v>5.640624999999986</v>
       </c>
       <c r="BP5" t="n">
-        <v>3</v>
+        <v>0.6816601599033623</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.9000000000000057</v>
+        <v>1</v>
       </c>
       <c r="BR5" t="n">
-        <v>-1.029186894229284</v>
+        <v>-2.181292517006796</v>
       </c>
       <c r="BS5" t="n">
-        <v>-0.5436868686868728</v>
+        <v>33696.52777777778</v>
       </c>
       <c r="BT5" t="n">
-        <v>-0.474675324675303</v>
+        <v>-0.3265257988466885</v>
       </c>
       <c r="BU5" t="n">
-        <v>-355838.1628082895</v>
+        <v>4.678356317086511</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.395999032023866</v>
+        <v>49317857.14285715</v>
       </c>
       <c r="BW5" t="n">
-        <v>-2.811111111111103</v>
+        <v>26736.88442447571</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>485V7EFU</t>
+          <t>biQrHC9r</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45598.47916666666</v>
+        <v>45605.47916666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">exner f 
+          <t xml:space="preserve">siebert d 
   ger </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">deutsche bank park
-  frankfurt </t>
+          <t xml:space="preserve">vonovia ruhrstadion
+  bochum </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>8vndvXTk</t>
+          <t>8Y2m6ADe</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>8Y2m6ADe</t>
+          <t>4jcj2zMd</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1852,220 +1836,220 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>K6A2elS9</t>
+          <t>GzfvcwRj</t>
         </is>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.751666666666667</v>
+        <v>-2.367142857142857</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.9757777777777779</v>
+        <v>-2.353857142857143</v>
       </c>
       <c r="R6" t="n">
-        <v>2.5</v>
+        <v>-3.267857142857143</v>
       </c>
       <c r="S6" t="n">
-        <v>1.292857142857143</v>
+        <v>-2.838509316770186</v>
       </c>
       <c r="T6" t="n">
-        <v>1.738095238095238</v>
+        <v>-5.482142857142858</v>
       </c>
       <c r="U6" t="n">
-        <v>1.38095238095238</v>
+        <v>-5.432712215320912</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.0714285714285694</v>
+        <v>-12.46428571428572</v>
       </c>
       <c r="W6" t="n">
-        <v>1.164285714285713</v>
+        <v>-10.47619047619048</v>
       </c>
       <c r="X6" t="n">
-        <v>2.714285714285714</v>
+        <v>-3.428571428571429</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.338095238095238</v>
+        <v>-2.863354037267081</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.785714285714286</v>
+        <v>-4.071428571428571</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.014285714285714</v>
+        <v>-3.670807453416149</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.3381407730147226</v>
+        <v>-0.7398150885614951</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.6965898778232926</v>
+        <v>1.46036763737978</v>
       </c>
       <c r="AD6" t="n">
-        <v>-79.51148426683434</v>
+        <v>18.84122884296164</v>
       </c>
       <c r="AE6" t="n">
-        <v>4.440992080579775</v>
+        <v>42.20169125287771</v>
       </c>
       <c r="AF6" t="n">
-        <v>-76</v>
+        <v>-27</v>
       </c>
       <c r="AG6" t="n">
-        <v>-17.65178571428571</v>
+        <v>-8.762499999999989</v>
       </c>
       <c r="AH6" t="n">
-        <v>-26</v>
+        <v>-37</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.0714285714285694</v>
+        <v>-33.01666666666667</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.9047619047619051</v>
+        <v>-10.875</v>
       </c>
       <c r="AK6" t="n">
-        <v>4.06428571428571</v>
+        <v>-9.964803312629403</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.761904761904759</v>
+        <v>-28.28571428571429</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0.6714285714285637</v>
+        <v>-19.2463768115942</v>
       </c>
       <c r="AN6" t="n">
-        <v>-46.16666666666663</v>
+        <v>-306.8571428571429</v>
       </c>
       <c r="AO6" t="n">
-        <v>-23.80555555555554</v>
+        <v>-208.9210526315789</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.7857142857142856</v>
+        <v>0.4464285714285714</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.7092731829573935</v>
+        <v>1.181818181818182</v>
       </c>
       <c r="AR6" t="inlineStr"/>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AT6" t="n">
-        <v>-4.523809523809526</v>
+        <v>0.625</v>
       </c>
       <c r="AU6" t="n">
-        <v>-2.223809523809527</v>
+        <v>2.120082815734989</v>
       </c>
       <c r="AV6" t="n">
-        <v>7.796238941329186</v>
+        <v>13.66523420265916</v>
       </c>
       <c r="AW6" t="n">
-        <v>8.943996362043933</v>
+        <v>18.38634811831883</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.07259643415389991</v>
+        <v>0.03659375975061279</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.01363569478676256</v>
+        <v>0.02552748184216082</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.3095238095238095</v>
+        <v>-0.2678571428571428</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.2833333333333333</v>
+        <v>-0.6376811594202898</v>
       </c>
       <c r="BB6" t="n">
-        <v>-62</v>
+        <v>1.952380952380953</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.6972222222222224</v>
+        <v>-2.023863636363636</v>
       </c>
       <c r="BD6" t="n">
-        <v>11939861.11111111</v>
+        <v>-46171269.99158249</v>
       </c>
       <c r="BE6" t="n">
-        <v>10849.18453518078</v>
+        <v>1.840425084175084</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.4365149887706277</v>
+        <v>2.963943170071417</v>
       </c>
       <c r="BG6" t="n">
-        <v>-3.212718787060886</v>
+        <v>1.498674242424244</v>
       </c>
       <c r="BH6" t="n">
-        <v>16877.77777777778</v>
+        <v>-36276816.4581707</v>
       </c>
       <c r="BI6" t="n">
-        <v>7.641666666666666</v>
+        <v>-11428.57142857143</v>
       </c>
       <c r="BJ6" t="n">
-        <v>-87</v>
+        <v>-11.32112164037241</v>
       </c>
       <c r="BK6" t="n">
-        <v>-6300000</v>
+        <v>147</v>
       </c>
       <c r="BL6" t="n">
-        <v>-1</v>
+        <v>-11.86222643097642</v>
       </c>
       <c r="BM6" t="n">
-        <v>-45000</v>
+        <v>2.142857142857143</v>
       </c>
       <c r="BN6" t="n">
-        <v>-6.333333333333332</v>
+        <v>142.4285714285714</v>
       </c>
       <c r="BO6" t="n">
-        <v>-0.6267921058334593</v>
+        <v>-11.9101430976431</v>
       </c>
       <c r="BP6" t="n">
-        <v>-1</v>
+        <v>-1.364937584882438</v>
       </c>
       <c r="BQ6" t="n">
-        <v>-4</v>
+        <v>2.428571428571428</v>
       </c>
       <c r="BR6" t="n">
-        <v>4.250191687315748</v>
+        <v>12.25</v>
       </c>
       <c r="BS6" t="n">
-        <v>-3.836111111111112</v>
+        <v>-82257.76515151515</v>
       </c>
       <c r="BT6" t="n">
-        <v>-0.2583333333332973</v>
+        <v>1.776625471462843</v>
       </c>
       <c r="BU6" t="n">
-        <v>7773194.38560604</v>
+        <v>-10.66006282357974</v>
       </c>
       <c r="BV6" t="n">
-        <v>7.201763615109471</v>
+        <v>-20246428.57142857</v>
       </c>
       <c r="BW6" t="n">
-        <v>4.713888888888889</v>
+        <v>-65353.74310595404</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>jVWMBdG5</t>
+          <t>nee3ysec</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45598.47916666666</v>
+        <v>45605.47916666666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">haslberger w 
+          <t xml:space="preserve">stieler t 
   ger </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">allianz arena
-  munich </t>
+          <t xml:space="preserve">mewa arena
+  mainz </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>nVp0wiqd</t>
+          <t>EuakNmc1</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>pzHW4oaE</t>
+          <t>nP1i5US1</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2092,227 +2076,227 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>vZA6VYpf</t>
+          <t>YZPE6Sx7</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>hpYJ6izc</t>
+          <t>pfoInmcq</t>
         </is>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.218333333333334</v>
+        <v>-1.145714285714286</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.728888888888889</v>
+        <v>-0.3977777777777778</v>
       </c>
       <c r="R7" t="n">
-        <v>2.142857142857143</v>
+        <v>-1.5</v>
       </c>
       <c r="S7" t="n">
-        <v>1.65</v>
+        <v>-0.2999999999999998</v>
       </c>
       <c r="T7" t="n">
-        <v>8</v>
+        <v>-3.875</v>
       </c>
       <c r="U7" t="n">
-        <v>4.1</v>
+        <v>-2.65</v>
       </c>
       <c r="V7" t="n">
-        <v>15.57142857142857</v>
+        <v>-6.625</v>
       </c>
       <c r="W7" t="n">
-        <v>8.950000000000001</v>
+        <v>-3.199999999999999</v>
       </c>
       <c r="X7" t="n">
-        <v>3.142857142857143</v>
+        <v>-0.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.399999999999999</v>
+        <v>0.05000000000000004</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.714285714285714</v>
+        <v>-0.75</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>-inf</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>-inf</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>4.433975939944315</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.784058499960877</v>
       </c>
       <c r="AD7" t="n">
-        <v>-463.6754395090367</v>
+        <v>156.0030070881812</v>
       </c>
       <c r="AE7" t="n">
-        <v>-280.1749164426976</v>
+        <v>103.7892492907417</v>
       </c>
       <c r="AF7" t="n">
-        <v>186</v>
+        <v>22</v>
       </c>
       <c r="AG7" t="n">
-        <v>63.42857142857142</v>
+        <v>-25.69230769230771</v>
       </c>
       <c r="AH7" t="n">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="AI7" t="n">
-        <v>29.71428571428572</v>
+        <v>-4.153846153846153</v>
       </c>
       <c r="AJ7" t="n">
-        <v>15</v>
+        <v>-21.5</v>
       </c>
       <c r="AK7" t="n">
-        <v>8</v>
+        <v>-11.3</v>
       </c>
       <c r="AL7" t="n">
-        <v>44.57142857142857</v>
+        <v>-35.5</v>
       </c>
       <c r="AM7" t="n">
-        <v>36.8</v>
+        <v>-27.7</v>
       </c>
       <c r="AN7" t="n">
-        <v>605.1666666666666</v>
+        <v>-300.2857142857143</v>
       </c>
       <c r="AO7" t="n">
-        <v>479.4444444444445</v>
+        <v>-268.5555555555555</v>
       </c>
       <c r="AP7" t="n">
-        <v>-2.220446049250313e-16</v>
+        <v>0.375</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-0.7222222222222223</v>
-      </c>
-      <c r="AR7" t="inlineStr"/>
-      <c r="AS7" t="inlineStr"/>
+        <v>0.1815789473684211</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>-1</v>
+      </c>
       <c r="AT7" t="n">
-        <v>-6</v>
+        <v>5.375</v>
       </c>
       <c r="AU7" t="n">
-        <v>-4.5</v>
+        <v>4.199999999999998</v>
       </c>
       <c r="AV7" t="n">
-        <v>-47.28286620704968</v>
+        <v>9.199387755922942</v>
       </c>
       <c r="AW7" t="n">
-        <v>-29.73018285699402</v>
+        <v>13.91192045731323</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.01753125509434089</v>
+        <v>0.08341253341253342</v>
       </c>
       <c r="AY7" t="n">
-        <v>-0.0116297834819149</v>
+        <v>-0.02959240036862009</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.7142857142857142</v>
+        <v>-0.125</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.4500000000000001</v>
+        <v>0.04999999999999999</v>
       </c>
       <c r="BB7" t="n">
-        <v>272</v>
+        <v>6.119047619047624</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.976623376623376</v>
+        <v>-1.146085858585859</v>
       </c>
       <c r="BD7" t="n">
-        <v>42658286.43578643</v>
+        <v>-30257335.85858586</v>
       </c>
       <c r="BE7" t="n">
-        <v>50096.24752774234</v>
+        <v>0.3959595959595994</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.49516160392456</v>
+        <v>-0.03119675302340852</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.08121353041597601</v>
+        <v>-3.133080808080763</v>
       </c>
       <c r="BH7" t="n">
-        <v>55243.43434343435</v>
+        <v>-18492191.47258186</v>
       </c>
       <c r="BI7" t="n">
-        <v>8.093506493506482</v>
+        <v>-80642.85714285714</v>
       </c>
       <c r="BJ7" t="n">
-        <v>228</v>
+        <v>-5.808847598050377</v>
       </c>
       <c r="BK7" t="n">
-        <v>86050000</v>
+        <v>-161.8571428571428</v>
       </c>
       <c r="BL7" t="n">
-        <v>3</v>
+        <v>-6.720202020202024</v>
       </c>
       <c r="BM7" t="n">
-        <v>175000</v>
+        <v>-1.785714285714286</v>
       </c>
       <c r="BN7" t="n">
-        <v>-5</v>
+        <v>-137.0238095238095</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.205250898986634</v>
+        <v>-7.30441919191918</v>
       </c>
       <c r="BP7" t="n">
-        <v>5</v>
+        <v>-0.6958263249478418</v>
       </c>
       <c r="BQ7" t="n">
-        <v>3.5</v>
+        <v>-4.880952380952381</v>
       </c>
       <c r="BR7" t="n">
-        <v>7.463654981443383</v>
+        <v>1.136904761904759</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.8989898989898961</v>
+        <v>-32590.78282828283</v>
       </c>
       <c r="BT7" t="n">
-        <v>-2.315007215007199</v>
+        <v>0.6627883769137703</v>
       </c>
       <c r="BU7" t="n">
-        <v>31187561.89479988</v>
+        <v>-5.331014088250924</v>
       </c>
       <c r="BV7" t="n">
-        <v>7.866229138489871</v>
+        <v>-63640476.19047619</v>
       </c>
       <c r="BW7" t="n">
-        <v>9.022222222222226</v>
+        <v>-21240.47309115034</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>8MVuSH0n</t>
+          <t>6HTjFjve</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45598.47916666666</v>
+        <v>45605.47916666666</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">zwayer f 
+          <t xml:space="preserve">jollenbeck m 
   ger </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">prezero arena
-  sinsheim </t>
+          <t xml:space="preserve">millerntor stadion
+  hamburg </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>hQAtP9Sl</t>
+          <t>ILyJuN3g</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ILyJuN3g</t>
+          <t>nVp0wiqd</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2344,199 +2328,201 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0jdIgO6t</t>
+          <t>hpYJ6izc</t>
         </is>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.6650000000000005</v>
+        <v>-2.828571428571428</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.8944444444444446</v>
+        <v>-1.512222222222223</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.4285714285714287</v>
+        <v>-3.375</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.2</v>
+        <v>-1.65</v>
       </c>
       <c r="T8" t="n">
-        <v>2.571428571428571</v>
+        <v>-10.125</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5999999999999996</v>
+        <v>-4.800000000000001</v>
       </c>
       <c r="V8" t="n">
-        <v>-4.714285714285714</v>
+        <v>-15.875</v>
       </c>
       <c r="W8" t="n">
-        <v>-7.25</v>
+        <v>-6.449999999999999</v>
       </c>
       <c r="X8" t="n">
-        <v>0.4285714285714284</v>
+        <v>-3.625</v>
       </c>
       <c r="Y8" t="n">
-        <v>-0.05000000000000027</v>
+        <v>-1.9</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.857142857142857</v>
+        <v>-3</v>
       </c>
       <c r="AA8" t="n">
-        <v>-0.1499999999999999</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>5.612898492730427</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>5.230374947780217</v>
+        <v>-1.5</v>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
       <c r="AD8" t="n">
-        <v>-39.33692937281862</v>
+        <v>361.8556616060502</v>
       </c>
       <c r="AE8" t="n">
-        <v>69.05037102856565</v>
+        <v>115.280925646005</v>
       </c>
       <c r="AF8" t="n">
-        <v>-86</v>
+        <v>-56</v>
       </c>
       <c r="AG8" t="n">
-        <v>-39.14285714285714</v>
+        <v>-6.615384615384613</v>
       </c>
       <c r="AH8" t="n">
-        <v>-20</v>
+        <v>-64</v>
       </c>
       <c r="AI8" t="n">
-        <v>-27.21428571428572</v>
+        <v>-7.53846153846154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>-7.142857142857139</v>
+        <v>-9.25</v>
       </c>
       <c r="AK8" t="n">
-        <v>-3.750000000000007</v>
+        <v>-4.100000000000001</v>
       </c>
       <c r="AL8" t="n">
-        <v>4.857142857142847</v>
+        <v>-53</v>
       </c>
       <c r="AM8" t="n">
-        <v>-8.5</v>
+        <v>-23.3</v>
       </c>
       <c r="AN8" t="n">
-        <v>38.83333333333326</v>
+        <v>-667.8571428571429</v>
       </c>
       <c r="AO8" t="n">
-        <v>-130.5555555555555</v>
+        <v>-270.9444444444444</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.738095238095238</v>
+        <v>-0.2142857142857142</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.7684210526315789</v>
+        <v>0.5701754385964912</v>
       </c>
       <c r="AR8" t="inlineStr"/>
-      <c r="AS8" t="n">
-        <v>-0.08333333333333331</v>
-      </c>
+      <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
-        <v>1.857142857142858</v>
+        <v>5</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.3500000000000014</v>
+        <v>1.600000000000003</v>
       </c>
       <c r="AV8" t="n">
-        <v>-2.841206810020299</v>
+        <v>55.01901221397462</v>
       </c>
       <c r="AW8" t="n">
-        <v>22.81790141623551</v>
+        <v>21.77895110988679</v>
       </c>
       <c r="AX8" t="n">
-        <v>-0.005568437113302981</v>
+        <v>0.01857756362317348</v>
       </c>
       <c r="AY8" t="n">
-        <v>-0.04451646003810688</v>
+        <v>0.02761399769246548</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="BB8" t="n">
-        <v>24</v>
+        <v>4.897619047619052</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.5845238095238099</v>
+        <v>-2.331944444444444</v>
       </c>
       <c r="BD8" t="n">
-        <v>5149094.516594516</v>
+        <v>-47224346.59090909</v>
       </c>
       <c r="BE8" t="n">
-        <v>7956.194056569995</v>
+        <v>-0.5477272727272791</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.2116720372359471</v>
+        <v>1.474570540935645</v>
       </c>
       <c r="BG8" t="n">
-        <v>-1.643262919202762</v>
+        <v>1.005681818181785</v>
       </c>
       <c r="BH8" t="n">
-        <v>12067.56854256854</v>
+        <v>-33479546.4745657</v>
       </c>
       <c r="BI8" t="n">
-        <v>5.466269841269835</v>
+        <v>-149285.7142857143</v>
       </c>
       <c r="BJ8" t="n">
-        <v>34</v>
+        <v>-12.54221007481941</v>
       </c>
       <c r="BK8" t="n">
-        <v>20760000</v>
+        <v>-115.8571428571429</v>
       </c>
       <c r="BL8" t="n">
-        <v>0</v>
+        <v>-12.45416666666667</v>
       </c>
       <c r="BM8" t="n">
-        <v>69000</v>
+        <v>-0.7142857142857144</v>
       </c>
       <c r="BN8" t="n">
-        <v>2.5</v>
+        <v>-84.28571428571428</v>
       </c>
       <c r="BO8" t="n">
-        <v>-0.09674185463657636</v>
+        <v>-12.86300505050505</v>
       </c>
       <c r="BP8" t="n">
-        <v>3</v>
+        <v>-1.603642070863433</v>
       </c>
       <c r="BQ8" t="n">
-        <v>-6.25</v>
+        <v>-2.571428571428572</v>
       </c>
       <c r="BR8" t="n">
-        <v>3.435445757250278</v>
+        <v>2.492857142857162</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.3101010101010075</v>
+        <v>-65116.41414141414</v>
       </c>
       <c r="BT8" t="n">
-        <v>1.044696969696957</v>
+        <v>-0.5115454076367385</v>
       </c>
       <c r="BU8" t="n">
-        <v>3847498.209810241</v>
+        <v>-12.08477758427934</v>
       </c>
       <c r="BV8" t="n">
-        <v>6.581334288101218</v>
+        <v>-91827142.85714285</v>
       </c>
       <c r="BW8" t="n">
-        <v>4.284307359307348</v>
+        <v>-59535.90327944043</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>AoSdOZaB</t>
+          <t>YmumZjET</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45598.47916666666</v>
+        <v>45605.47916666666</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -2546,18 +2532,18 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">volkswagen arena
-  wolfsburg </t>
+          <t xml:space="preserve">weserstadion
+  bremen </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>nwkTahLL</t>
+          <t>Ig1f1fy3</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>fTVNku3I</t>
+          <t>63WsD2ei</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2584,213 +2570,231 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>f3ddUIXs</t>
+          <t>M5BRZDsC</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>SMaB5LKo</t>
+          <t>4ljanukM</t>
         </is>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.8549999999999998</v>
+        <v>0.1028571428571425</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.2355555555555553</v>
+        <v>-0.2283333333333333</v>
       </c>
       <c r="R9" t="n">
-        <v>-1.285714285714286</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
+        <v>-0.1499999999999999</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.2000000000000002</v>
+      </c>
+      <c r="V9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.150000000000002</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>-0.1000000000000003</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="AA9" t="n">
         <v>0.1500000000000001</v>
       </c>
-      <c r="T9" t="n">
-        <v>-2.428571428571428</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="V9" t="n">
-        <v>-7.428571428571431</v>
-      </c>
-      <c r="W9" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="X9" t="n">
-        <v>-0.142857142857143</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>-0.857142857142857</v>
-      </c>
-      <c r="AA9" t="n">
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="AD9" t="n">
+        <v>-166.4404585061379</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>-21.16803923184236</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>34</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>4.53846153846154</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>2.800000000000004</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0.2999999999999972</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>162.7142857142858</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AP9" t="n">
         <v>0</v>
       </c>
-      <c r="AB9" t="n">
-        <v>0.4160823303680448</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>-0.3365520835373772</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>-125.0271002450798</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>-45.72931586456443</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>87</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>-4.214285714285708</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>-6.642857142857153</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>-3.142857142857146</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1.050000000000004</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>-1.142857142857153</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>0.7999999999999972</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>-23.33333333333337</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>5.555555555555543</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>1.571428571428572</v>
-      </c>
       <c r="AQ9" t="n">
-        <v>0.3000000000000003</v>
+        <v>-0.1710526315789471</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.8333333333333333</v>
+        <v>0</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.7916666666666667</v>
+        <v>-0.5</v>
       </c>
       <c r="AT9" t="n">
-        <v>2.428571428571423</v>
+        <v>-1</v>
       </c>
       <c r="AU9" t="n">
-        <v>-2.649999999999999</v>
+        <v>-2.849999999999998</v>
       </c>
       <c r="AV9" t="n">
-        <v>-0.177429880779826</v>
+        <v>12.20482815634518</v>
       </c>
       <c r="AW9" t="n">
-        <v>20.06687377380022</v>
+        <v>23.50885065874618</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.08633485840799655</v>
+        <v>-0.06360022603714025</v>
       </c>
       <c r="AY9" t="n">
-        <v>-0.0240767085096267</v>
+        <v>0.01255912972227</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.1428571428571428</v>
+        <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="BB9" t="n">
-        <v>118</v>
-      </c>
-      <c r="BC9" t="inlineStr"/>
-      <c r="BD9" t="inlineStr"/>
+        <v>1.214285714285715</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0.09772727272727288</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>4073626.893939395</v>
+      </c>
       <c r="BE9" t="n">
-        <v>12560.8106081348</v>
+        <v>0.8377209595959627</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.3053794404524168</v>
+        <v>1.374202753053567</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.8374778460028409</v>
-      </c>
-      <c r="BH9" t="inlineStr"/>
-      <c r="BI9" t="inlineStr"/>
+        <v>-3.2525883838384</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>1537195.451264029</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>24428.57142857143</v>
+      </c>
       <c r="BJ9" t="n">
-        <v>85</v>
+        <v>1.940461439542531</v>
       </c>
       <c r="BK9" t="n">
-        <v>48000000</v>
+        <v>38</v>
       </c>
       <c r="BL9" t="n">
-        <v>1</v>
+        <v>4.183901515151504</v>
       </c>
       <c r="BM9" t="n">
-        <v>113000</v>
+        <v>0.4285714285714284</v>
       </c>
       <c r="BN9" t="n">
-        <v>-2.857142857142858</v>
+        <v>38.71428571428569</v>
       </c>
       <c r="BO9" t="n">
-        <v>-0.8076797305843968</v>
+        <v>4.861363636363649</v>
       </c>
       <c r="BP9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BQ9" t="n">
-        <v>3.238095238095241</v>
+        <v>0.4285714285714284</v>
       </c>
       <c r="BR9" t="n">
-        <v>1.273835100228297</v>
-      </c>
-      <c r="BS9" t="inlineStr"/>
-      <c r="BT9" t="inlineStr"/>
+        <v>-2.452380952380963</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>7243.592171717173</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>-1.212872132158459</v>
+      </c>
       <c r="BU9" t="n">
-        <v>3025715.876861111</v>
+        <v>3.51653808743697</v>
       </c>
       <c r="BV9" t="n">
-        <v>1.098576807118377</v>
-      </c>
-      <c r="BW9" t="inlineStr"/>
+        <v>6114285.714285715</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>3934.688670168503</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>IHYEDIog</t>
+          <t>v3DAZKP9</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45597.6875</v>
+        <v>45604.6875</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">schlager d 
+          <t xml:space="preserve">brand b 
   ger </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">bayarena
-  leverkusen </t>
+          <t xml:space="preserve">stadion an der alten forsterei
+  berlin </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4jcj2zMd</t>
+          <t>pzHW4oaE</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>nJQmYp1B</t>
+          <t>fiEQZ7C7</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2817,196 +2821,194 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>hAcTWKKN</t>
+          <t>K6A2elS9</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>4bJLk19p</t>
+          <t>vZA6VYpf</t>
         </is>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2283333333333337</v>
+        <v>-0.6914285714285713</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.8790726817042607</v>
+        <v>-0.2672222222222222</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>-0.375</v>
       </c>
       <c r="S10" t="n">
-        <v>0.9813664596273292</v>
+        <v>-0.2999999999999998</v>
       </c>
       <c r="T10" t="n">
-        <v>0.8571428571428559</v>
+        <v>-2</v>
       </c>
       <c r="U10" t="n">
-        <v>1.376811594202898</v>
+        <v>-0.4500000000000002</v>
       </c>
       <c r="V10" t="n">
-        <v>1.714285714285714</v>
+        <v>-4</v>
       </c>
       <c r="W10" t="n">
-        <v>3.801242236024844</v>
+        <v>-0.4499999999999975</v>
       </c>
       <c r="X10" t="n">
-        <v>0.5714285714285716</v>
+        <v>-0.625</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.5217391304347825</v>
+        <v>-0.6000000000000001</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.4285714285714286</v>
+        <v>-1.125</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.944099378881988</v>
+        <v>-0.45</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.07611614575900338</v>
+        <v>-3.215237019924519</v>
       </c>
       <c r="AC10" t="n">
-        <v>-0.865133526015351</v>
+        <v>-2.990857979739559</v>
       </c>
       <c r="AD10" t="n">
-        <v>-41.49683430924145</v>
+        <v>16.99569098189153</v>
       </c>
       <c r="AE10" t="n">
-        <v>54.90525224316849</v>
+        <v>36.49754953464293</v>
       </c>
       <c r="AF10" t="n">
-        <v>39</v>
+        <v>-71</v>
       </c>
       <c r="AG10" t="n">
-        <v>10.45882352941176</v>
+        <v>-10.46153846153845</v>
       </c>
       <c r="AH10" t="n">
-        <v>38</v>
+        <v>-14</v>
       </c>
       <c r="AI10" t="n">
-        <v>32.70196078431373</v>
+        <v>8.692307692307693</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-3.571428571428577</v>
+        <v>-9.125</v>
       </c>
       <c r="AK10" t="n">
-        <v>4.552795031055904</v>
+        <v>-1.149999999999999</v>
       </c>
       <c r="AL10" t="n">
-        <v>-0.5714285714285694</v>
+        <v>-23.25</v>
       </c>
       <c r="AM10" t="n">
-        <v>-3.66459627329192</v>
+        <v>-9.5</v>
       </c>
       <c r="AN10" t="n">
-        <v>71.16666666666657</v>
+        <v>-327.7142857142857</v>
       </c>
       <c r="AO10" t="n">
-        <v>-29.52631578947376</v>
+        <v>-146.7222222222222</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.857142857142857</v>
+        <v>0.625</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.5346320346320348</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>-1.5</v>
-      </c>
+        <v>0.5026315789473685</v>
+      </c>
+      <c r="AR10" t="inlineStr"/>
       <c r="AS10" t="n">
-        <v>0.06666666666666671</v>
+        <v>-1</v>
       </c>
       <c r="AT10" t="n">
-        <v>2.000000000000004</v>
+        <v>4.125</v>
       </c>
       <c r="AU10" t="n">
-        <v>-0.8260869565217401</v>
+        <v>3.349999999999998</v>
       </c>
       <c r="AV10" t="n">
-        <v>5.884360834928646</v>
+        <v>12.86345896707828</v>
       </c>
       <c r="AW10" t="n">
-        <v>-2.925423930992515</v>
+        <v>-1.910765312830016</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.04128179021796043</v>
+        <v>0.006053378146401403</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.01365380138206914</v>
+        <v>0.02433786762267351</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.2857142857142857</v>
+        <v>-0.375</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.06211180124223603</v>
+        <v>-0.25</v>
       </c>
       <c r="BB10" t="n">
-        <v>-389</v>
+        <v>2.826190476190476</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.545887445887447</v>
+        <v>-0.3114898989898991</v>
       </c>
       <c r="BD10" t="n">
-        <v>35003412.69841269</v>
+        <v>-5143674.242424242</v>
       </c>
       <c r="BE10" t="n">
-        <v>57515.87850451186</v>
+        <v>-0.3671717171717184</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.898878722142765</v>
+        <v>-1.158462607877937</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.1660901681246685</v>
+        <v>2.153409090909093</v>
       </c>
       <c r="BH10" t="n">
-        <v>72474.53102453102</v>
+        <v>-2229956.750443399</v>
       </c>
       <c r="BI10" t="n">
-        <v>6.18189033189033</v>
+        <v>-3714.285714285725</v>
       </c>
       <c r="BJ10" t="n">
-        <v>-342</v>
+        <v>-0.7742130225295796</v>
       </c>
       <c r="BK10" t="n">
-        <v>-5050000</v>
+        <v>-169.2857142857143</v>
       </c>
       <c r="BL10" t="n">
-        <v>-5</v>
+        <v>-1.304040404040407</v>
       </c>
       <c r="BM10" t="n">
-        <v>-46000</v>
+        <v>-2.285714285714286</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.5</v>
+        <v>-150.8571428571429</v>
       </c>
       <c r="BO10" t="n">
-        <v>-4.010122517906694</v>
+        <v>-2.020833333333357</v>
       </c>
       <c r="BP10" t="n">
-        <v>-6</v>
+        <v>-0.263948390360929</v>
       </c>
       <c r="BQ10" t="n">
-        <v>-12.33333333333334</v>
+        <v>-1.428571428571429</v>
       </c>
       <c r="BR10" t="n">
-        <v>5.952163066183402</v>
+        <v>-5.971428571428589</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.882323232323234</v>
+        <v>-263.0050505050494</v>
       </c>
       <c r="BT10" t="n">
-        <v>-1.616810966810959</v>
+        <v>-0.3341039825888039</v>
       </c>
       <c r="BU10" t="n">
-        <v>27697001.39226345</v>
+        <v>-1.098939720989293</v>
       </c>
       <c r="BV10" t="n">
-        <v>5.926214058191036</v>
+        <v>-6442857.142857142</v>
       </c>
       <c r="BW10" t="n">
-        <v>7.741991341991337</v>
+        <v>1801.547931772395</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/data_preparation/df_constructed.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_constructed.xlsx
@@ -695,112 +695,112 @@
       </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_sub</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_start</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_start</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_age_player_miss</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_start</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_value_player_start</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_value_player_miss</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_sub</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_value_player_sub</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>dif_sum_wage_player_miss</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="BK1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_pot_player_start</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="BO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="BP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="BQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="BR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="BS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_start</t>
-        </is>
-      </c>
-      <c r="BT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="BU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="BV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_value_player_miss</t>
-        </is>
-      </c>
-      <c r="BW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_sub</t>
         </is>
       </c>
     </row>
@@ -985,70 +985,70 @@
         <v>-0.1</v>
       </c>
       <c r="BB2" t="n">
+        <v>1.622979797979809</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>-13235.1108413253</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>-2.571428571428571</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>-5.285714285714286</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>-6.070304050604008</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>-0.3076178451178448</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>-13729.96632996634</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>0.9093779791404835</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>2.203156565656567</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>-0.3497862912847685</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>-3.909595624837209</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>-2.616203703703704</v>
+      </c>
+      <c r="BN2" t="n">
         <v>0.3775510204081627</v>
       </c>
-      <c r="BC2" t="n">
-        <v>-0.3076178451178448</v>
-      </c>
-      <c r="BD2" t="n">
+      <c r="BO2" t="n">
         <v>-6356085.858585859</v>
       </c>
-      <c r="BE2" t="n">
-        <v>2.203156565656567</v>
-      </c>
-      <c r="BF2" t="n">
+      <c r="BP2" t="n">
+        <v>-53367857.14285714</v>
+      </c>
+      <c r="BQ2" t="n">
         <v>0.7908282380197704</v>
       </c>
-      <c r="BG2" t="n">
-        <v>1.622979797979809</v>
-      </c>
-      <c r="BH2" t="n">
+      <c r="BR2" t="n">
         <v>-6041529.678057254</v>
       </c>
-      <c r="BI2" t="n">
+      <c r="BS2" t="n">
+        <v>-227.5714285714286</v>
+      </c>
+      <c r="BT2" t="n">
         <v>-143571.4285714286</v>
       </c>
-      <c r="BJ2" t="n">
-        <v>-3.909595624837209</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>-227.5714285714286</v>
-      </c>
-      <c r="BL2" t="n">
+      <c r="BU2" t="n">
         <v>-5.193139730639714</v>
       </c>
-      <c r="BM2" t="n">
-        <v>-2.571428571428571</v>
-      </c>
-      <c r="BN2" t="n">
+      <c r="BV2" t="n">
+        <v>2.296938775510171</v>
+      </c>
+      <c r="BW2" t="n">
         <v>-210.8571428571429</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>-2.616203703703704</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>-0.3497862912847685</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>-5.285714285714286</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>2.296938775510171</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>-13729.96632996634</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>0.9093779791404835</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>-6.070304050604008</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>-53367857.14285714</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>-13235.1108413253</v>
       </c>
     </row>
     <row r="3">
@@ -1232,70 +1232,70 @@
         <v>0.2880952380952381</v>
       </c>
       <c r="BB3" t="n">
+        <v>0.5404040404040131</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>-1537.794621206966</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>2.714285714285714</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>3.285714285714286</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>-2.447670366913783</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>-0.208670033670034</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>-6611.279461279468</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>1.513768479649865</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>0.3305134680134643</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>0.07122063308208793</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1.59123839857682</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>-0.1446127946127973</v>
+      </c>
+      <c r="BN3" t="n">
         <v>2.738095238095241</v>
       </c>
-      <c r="BC3" t="n">
-        <v>-0.208670033670034</v>
-      </c>
-      <c r="BD3" t="n">
+      <c r="BO3" t="n">
         <v>-476979.1666666698</v>
       </c>
-      <c r="BE3" t="n">
-        <v>0.3305134680134643</v>
-      </c>
-      <c r="BF3" t="n">
+      <c r="BP3" t="n">
+        <v>17857142.85714286</v>
+      </c>
+      <c r="BQ3" t="n">
         <v>0.7802279736731919</v>
       </c>
-      <c r="BG3" t="n">
-        <v>0.5404040404040131</v>
-      </c>
-      <c r="BH3" t="n">
+      <c r="BR3" t="n">
         <v>2439717.465186602</v>
       </c>
-      <c r="BI3" t="n">
+      <c r="BS3" t="n">
+        <v>214.5714285714286</v>
+      </c>
+      <c r="BT3" t="n">
         <v>65428.57142857143</v>
       </c>
-      <c r="BJ3" t="n">
-        <v>1.59123839857682</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>214.5714285714286</v>
-      </c>
-      <c r="BL3" t="n">
+      <c r="BU3" t="n">
         <v>-1.725589225589218</v>
       </c>
-      <c r="BM3" t="n">
-        <v>2.714285714285714</v>
-      </c>
-      <c r="BN3" t="n">
+      <c r="BV3" t="n">
+        <v>6.080952380952397</v>
+      </c>
+      <c r="BW3" t="n">
         <v>201.2857142857143</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>-0.1446127946127973</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>0.07122063308208793</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>3.285714285714286</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>6.080952380952397</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>-6611.279461279468</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>1.513768479649865</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>-2.447670366913783</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>17857142.85714286</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>-1537.794621206966</v>
       </c>
     </row>
     <row r="4">
@@ -1478,57 +1478,57 @@
       <c r="BA4" t="n">
         <v>-0.05000000000000002</v>
       </c>
-      <c r="BB4" t="n">
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="n">
+        <v>-3782.336641793878</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>-1.142857142857143</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>-4.857142857142858</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>-0.7226451545530495</v>
+      </c>
+      <c r="BG4" t="inlineStr"/>
+      <c r="BH4" t="inlineStr"/>
+      <c r="BI4" t="n">
+        <v>-0.3412669932406835</v>
+      </c>
+      <c r="BJ4" t="inlineStr"/>
+      <c r="BK4" t="n">
+        <v>-0.1423175599984809</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>0.5826973921546283</v>
+      </c>
+      <c r="BM4" t="inlineStr"/>
+      <c r="BN4" t="n">
         <v>-0.7981292517006828</v>
-      </c>
-      <c r="BC4" t="inlineStr"/>
-      <c r="BD4" t="inlineStr"/>
-      <c r="BE4" t="inlineStr"/>
-      <c r="BF4" t="n">
-        <v>0.6380313947747709</v>
-      </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="n">
-        <v>-517740.6465975549</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>-79857.14285714287</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>0.5826973921546283</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>-110.4285714285714</v>
-      </c>
-      <c r="BL4" t="inlineStr"/>
-      <c r="BM4" t="n">
-        <v>-1.142857142857143</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>-104.4285714285714</v>
       </c>
       <c r="BO4" t="inlineStr"/>
       <c r="BP4" t="n">
-        <v>-0.1423175599984809</v>
+        <v>-26432142.85714286</v>
       </c>
       <c r="BQ4" t="n">
-        <v>-4.857142857142858</v>
+        <v>0.6380313947747709</v>
       </c>
       <c r="BR4" t="n">
+        <v>-517740.6465975549</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>-110.4285714285714</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>-79857.14285714287</v>
+      </c>
+      <c r="BU4" t="inlineStr"/>
+      <c r="BV4" t="n">
         <v>0.5443877551020364</v>
       </c>
-      <c r="BS4" t="inlineStr"/>
-      <c r="BT4" t="n">
-        <v>-0.3412669932406835</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>-0.7226451545530495</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>-26432142.85714286</v>
-      </c>
       <c r="BW4" t="n">
-        <v>-3782.336641793878</v>
+        <v>-104.4285714285714</v>
       </c>
     </row>
     <row r="5">
@@ -1710,70 +1710,70 @@
         <v>0.3</v>
       </c>
       <c r="BB5" t="n">
+        <v>-1.06701388888888</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>26736.88442447571</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>-1.714285714285714</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>4.678356317086511</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>0.895486111111111</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>33696.52777777778</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>-0.3265257988466885</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>0.2128472222222229</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>0.6816601599033623</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>4.71436943766308</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>5.640624999999986</v>
+      </c>
+      <c r="BN5" t="n">
         <v>1.817687074829934</v>
       </c>
-      <c r="BC5" t="n">
-        <v>0.895486111111111</v>
-      </c>
-      <c r="BD5" t="n">
+      <c r="BO5" t="n">
         <v>22125902.77777778</v>
       </c>
-      <c r="BE5" t="n">
-        <v>0.2128472222222229</v>
-      </c>
-      <c r="BF5" t="n">
+      <c r="BP5" t="n">
+        <v>49317857.14285715</v>
+      </c>
+      <c r="BQ5" t="n">
         <v>2.591271312630198</v>
       </c>
-      <c r="BG5" t="n">
-        <v>-1.06701388888888</v>
-      </c>
-      <c r="BH5" t="n">
+      <c r="BR5" t="n">
         <v>15584271.31802334</v>
       </c>
-      <c r="BI5" t="n">
+      <c r="BS5" t="n">
+        <v>-108.8571428571429</v>
+      </c>
+      <c r="BT5" t="n">
         <v>101000</v>
       </c>
-      <c r="BJ5" t="n">
-        <v>4.71436943766308</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>-108.8571428571429</v>
-      </c>
-      <c r="BL5" t="n">
+      <c r="BU5" t="n">
         <v>6.126388888888883</v>
       </c>
-      <c r="BM5" t="n">
-        <v>-1.714285714285714</v>
-      </c>
-      <c r="BN5" t="n">
+      <c r="BV5" t="n">
+        <v>-2.181292517006796</v>
+      </c>
+      <c r="BW5" t="n">
         <v>-92.14285714285711</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>5.640624999999986</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>0.6816601599033623</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>-2.181292517006796</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>33696.52777777778</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>-0.3265257988466885</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>4.678356317086511</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>49317857.14285715</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>26736.88442447571</v>
       </c>
     </row>
     <row r="6">
@@ -1955,70 +1955,70 @@
         <v>-0.6376811594202898</v>
       </c>
       <c r="BB6" t="n">
+        <v>1.498674242424244</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>-65353.74310595404</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>2.142857142857143</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>2.428571428571428</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>-10.66006282357974</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>-2.023863636363636</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>-82257.76515151515</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>1.776625471462843</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>1.840425084175084</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>-1.364937584882438</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>-11.32112164037241</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>-11.9101430976431</v>
+      </c>
+      <c r="BN6" t="n">
         <v>1.952380952380953</v>
       </c>
-      <c r="BC6" t="n">
-        <v>-2.023863636363636</v>
-      </c>
-      <c r="BD6" t="n">
+      <c r="BO6" t="n">
         <v>-46171269.99158249</v>
       </c>
-      <c r="BE6" t="n">
-        <v>1.840425084175084</v>
-      </c>
-      <c r="BF6" t="n">
+      <c r="BP6" t="n">
+        <v>-20246428.57142857</v>
+      </c>
+      <c r="BQ6" t="n">
         <v>2.963943170071417</v>
       </c>
-      <c r="BG6" t="n">
-        <v>1.498674242424244</v>
-      </c>
-      <c r="BH6" t="n">
+      <c r="BR6" t="n">
         <v>-36276816.4581707</v>
       </c>
-      <c r="BI6" t="n">
+      <c r="BS6" t="n">
+        <v>147</v>
+      </c>
+      <c r="BT6" t="n">
         <v>-11428.57142857143</v>
       </c>
-      <c r="BJ6" t="n">
-        <v>-11.32112164037241</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>147</v>
-      </c>
-      <c r="BL6" t="n">
+      <c r="BU6" t="n">
         <v>-11.86222643097642</v>
       </c>
-      <c r="BM6" t="n">
-        <v>2.142857142857143</v>
-      </c>
-      <c r="BN6" t="n">
+      <c r="BV6" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="BW6" t="n">
         <v>142.4285714285714</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>-11.9101430976431</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>-1.364937584882438</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>2.428571428571428</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>12.25</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>-82257.76515151515</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>1.776625471462843</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>-10.66006282357974</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>-20246428.57142857</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>-65353.74310595404</v>
       </c>
     </row>
     <row r="7">
@@ -2202,70 +2202,70 @@
         <v>0.04999999999999999</v>
       </c>
       <c r="BB7" t="n">
+        <v>-3.133080808080763</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>-21240.47309115034</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>-1.785714285714286</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>-4.880952380952381</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>-5.331014088250924</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>-1.146085858585859</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>-32590.78282828283</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>0.6627883769137703</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>0.3959595959595994</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>-0.6958263249478418</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>-5.808847598050377</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>-7.30441919191918</v>
+      </c>
+      <c r="BN7" t="n">
         <v>6.119047619047624</v>
       </c>
-      <c r="BC7" t="n">
-        <v>-1.146085858585859</v>
-      </c>
-      <c r="BD7" t="n">
+      <c r="BO7" t="n">
         <v>-30257335.85858586</v>
       </c>
-      <c r="BE7" t="n">
-        <v>0.3959595959595994</v>
-      </c>
-      <c r="BF7" t="n">
+      <c r="BP7" t="n">
+        <v>-63640476.19047619</v>
+      </c>
+      <c r="BQ7" t="n">
         <v>-0.03119675302340852</v>
       </c>
-      <c r="BG7" t="n">
-        <v>-3.133080808080763</v>
-      </c>
-      <c r="BH7" t="n">
+      <c r="BR7" t="n">
         <v>-18492191.47258186</v>
       </c>
-      <c r="BI7" t="n">
+      <c r="BS7" t="n">
+        <v>-161.8571428571428</v>
+      </c>
+      <c r="BT7" t="n">
         <v>-80642.85714285714</v>
       </c>
-      <c r="BJ7" t="n">
-        <v>-5.808847598050377</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>-161.8571428571428</v>
-      </c>
-      <c r="BL7" t="n">
+      <c r="BU7" t="n">
         <v>-6.720202020202024</v>
       </c>
-      <c r="BM7" t="n">
-        <v>-1.785714285714286</v>
-      </c>
-      <c r="BN7" t="n">
+      <c r="BV7" t="n">
+        <v>1.136904761904759</v>
+      </c>
+      <c r="BW7" t="n">
         <v>-137.0238095238095</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>-7.30441919191918</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>-0.6958263249478418</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>-4.880952380952381</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>1.136904761904759</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>-32590.78282828283</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>0.6627883769137703</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>-5.331014088250924</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>-63640476.19047619</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>-21240.47309115034</v>
       </c>
     </row>
     <row r="8">
@@ -2449,70 +2449,70 @@
         <v>-0.4</v>
       </c>
       <c r="BB8" t="n">
+        <v>1.005681818181785</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>-59535.90327944043</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>-0.7142857142857144</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>-2.571428571428572</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>-12.08477758427934</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>-2.331944444444444</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>-65116.41414141414</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>-0.5115454076367385</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>-0.5477272727272791</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>-1.603642070863433</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>-12.54221007481941</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>-12.86300505050505</v>
+      </c>
+      <c r="BN8" t="n">
         <v>4.897619047619052</v>
       </c>
-      <c r="BC8" t="n">
-        <v>-2.331944444444444</v>
-      </c>
-      <c r="BD8" t="n">
+      <c r="BO8" t="n">
         <v>-47224346.59090909</v>
       </c>
-      <c r="BE8" t="n">
-        <v>-0.5477272727272791</v>
-      </c>
-      <c r="BF8" t="n">
+      <c r="BP8" t="n">
+        <v>-91827142.85714285</v>
+      </c>
+      <c r="BQ8" t="n">
         <v>1.474570540935645</v>
       </c>
-      <c r="BG8" t="n">
-        <v>1.005681818181785</v>
-      </c>
-      <c r="BH8" t="n">
+      <c r="BR8" t="n">
         <v>-33479546.4745657</v>
       </c>
-      <c r="BI8" t="n">
+      <c r="BS8" t="n">
+        <v>-115.8571428571429</v>
+      </c>
+      <c r="BT8" t="n">
         <v>-149285.7142857143</v>
       </c>
-      <c r="BJ8" t="n">
-        <v>-12.54221007481941</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>-115.8571428571429</v>
-      </c>
-      <c r="BL8" t="n">
+      <c r="BU8" t="n">
         <v>-12.45416666666667</v>
       </c>
-      <c r="BM8" t="n">
-        <v>-0.7142857142857144</v>
-      </c>
-      <c r="BN8" t="n">
+      <c r="BV8" t="n">
+        <v>2.492857142857162</v>
+      </c>
+      <c r="BW8" t="n">
         <v>-84.28571428571428</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>-12.86300505050505</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>-1.603642070863433</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>-2.571428571428572</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>2.492857142857162</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>-65116.41414141414</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>-0.5115454076367385</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>-12.08477758427934</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>-91827142.85714285</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>-59535.90327944043</v>
       </c>
     </row>
     <row r="9">
@@ -2700,70 +2700,70 @@
         <v>-0.3</v>
       </c>
       <c r="BB9" t="n">
+        <v>-3.2525883838384</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>3934.688670168503</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0.4285714285714284</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0.4285714285714284</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>3.51653808743697</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>0.09772727272727288</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>7243.592171717173</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>-1.212872132158459</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0.8377209595959627</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1.940461439542531</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>4.861363636363649</v>
+      </c>
+      <c r="BN9" t="n">
         <v>1.214285714285715</v>
       </c>
-      <c r="BC9" t="n">
-        <v>0.09772727272727288</v>
-      </c>
-      <c r="BD9" t="n">
+      <c r="BO9" t="n">
         <v>4073626.893939395</v>
       </c>
-      <c r="BE9" t="n">
-        <v>0.8377209595959627</v>
-      </c>
-      <c r="BF9" t="n">
+      <c r="BP9" t="n">
+        <v>6114285.714285715</v>
+      </c>
+      <c r="BQ9" t="n">
         <v>1.374202753053567</v>
       </c>
-      <c r="BG9" t="n">
-        <v>-3.2525883838384</v>
-      </c>
-      <c r="BH9" t="n">
+      <c r="BR9" t="n">
         <v>1537195.451264029</v>
       </c>
-      <c r="BI9" t="n">
+      <c r="BS9" t="n">
+        <v>38</v>
+      </c>
+      <c r="BT9" t="n">
         <v>24428.57142857143</v>
       </c>
-      <c r="BJ9" t="n">
-        <v>1.940461439542531</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>38</v>
-      </c>
-      <c r="BL9" t="n">
+      <c r="BU9" t="n">
         <v>4.183901515151504</v>
       </c>
-      <c r="BM9" t="n">
-        <v>0.4285714285714284</v>
-      </c>
-      <c r="BN9" t="n">
+      <c r="BV9" t="n">
+        <v>-2.452380952380963</v>
+      </c>
+      <c r="BW9" t="n">
         <v>38.71428571428569</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>4.861363636363649</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>0.4285714285714284</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>-2.452380952380963</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>7243.592171717173</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>-1.212872132158459</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>3.51653808743697</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>6114285.714285715</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>3934.688670168503</v>
       </c>
     </row>
     <row r="10">
@@ -2945,70 +2945,70 @@
         <v>-0.25</v>
       </c>
       <c r="BB10" t="n">
+        <v>2.153409090909093</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>1801.547931772395</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>-2.285714285714286</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>-1.428571428571429</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>-1.098939720989293</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>-0.3114898989898991</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>-263.0050505050494</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>-0.3341039825888039</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>-0.3671717171717184</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>-0.263948390360929</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>-0.7742130225295796</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>-2.020833333333357</v>
+      </c>
+      <c r="BN10" t="n">
         <v>2.826190476190476</v>
       </c>
-      <c r="BC10" t="n">
-        <v>-0.3114898989898991</v>
-      </c>
-      <c r="BD10" t="n">
+      <c r="BO10" t="n">
         <v>-5143674.242424242</v>
       </c>
-      <c r="BE10" t="n">
-        <v>-0.3671717171717184</v>
-      </c>
-      <c r="BF10" t="n">
+      <c r="BP10" t="n">
+        <v>-6442857.142857142</v>
+      </c>
+      <c r="BQ10" t="n">
         <v>-1.158462607877937</v>
       </c>
-      <c r="BG10" t="n">
-        <v>2.153409090909093</v>
-      </c>
-      <c r="BH10" t="n">
+      <c r="BR10" t="n">
         <v>-2229956.750443399</v>
       </c>
-      <c r="BI10" t="n">
+      <c r="BS10" t="n">
+        <v>-169.2857142857143</v>
+      </c>
+      <c r="BT10" t="n">
         <v>-3714.285714285725</v>
       </c>
-      <c r="BJ10" t="n">
-        <v>-0.7742130225295796</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>-169.2857142857143</v>
-      </c>
-      <c r="BL10" t="n">
+      <c r="BU10" t="n">
         <v>-1.304040404040407</v>
       </c>
-      <c r="BM10" t="n">
-        <v>-2.285714285714286</v>
-      </c>
-      <c r="BN10" t="n">
+      <c r="BV10" t="n">
+        <v>-5.971428571428589</v>
+      </c>
+      <c r="BW10" t="n">
         <v>-150.8571428571429</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>-2.020833333333357</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>-0.263948390360929</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>-1.428571428571429</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>-5.971428571428589</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>-263.0050505050494</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>-0.3341039825888039</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>-1.098939720989293</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>-6442857.142857142</v>
-      </c>
-      <c r="BW10" t="n">
-        <v>1801.547931772395</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/data_preparation/df_constructed.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_constructed.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BW10"/>
+  <dimension ref="A1:BW17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,44 +460,44 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>id_country</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>id_competition</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>is_cup</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>season</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>country</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>competition</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
           <t>result</t>
@@ -510,7 +510,7 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_240_matches_expected_goals_(xg)</t>
+          <t>dif_mean_last_360_matches_expected_goals_(xg)</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
@@ -520,7 +520,7 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_240_matches_expected_points</t>
+          <t>dif_mean_last_360_matches_expected_points</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
@@ -530,7 +530,7 @@
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_240_matches_shots_on_goal</t>
+          <t>dif_mean_last_360_matches_shots_on_goal</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
@@ -540,7 +540,7 @@
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_240_matches_goal_attempts</t>
+          <t>dif_mean_last_360_matches_goal_attempts</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
@@ -550,7 +550,7 @@
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_240_matches_goals</t>
+          <t>dif_mean_last_360_matches_goals</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
@@ -560,7 +560,7 @@
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_240_matches_points</t>
+          <t>dif_mean_last_360_matches_points</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
@@ -570,7 +570,7 @@
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_240_matches_goal_ratio</t>
+          <t>dif_mean_last_360_matches_goal_ratio</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
@@ -580,7 +580,7 @@
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_240_matches_PPS</t>
+          <t>dif_mean_last_360_matches_PPS</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_240_matches_attacks</t>
+          <t>dif_mean_last_360_matches_attacks</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_240_matches_dangerous_attacks</t>
+          <t>dif_mean_last_360_matches_dangerous_attacks</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_240_matches_dead_balls</t>
+          <t>dif_mean_last_360_matches_dead_balls</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_240_matches_ball_possession</t>
+          <t>dif_mean_last_360_matches_ball_possession</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_240_matches_total_passes</t>
+          <t>dif_mean_last_360_matches_total_passes</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_240_matches_yellow_cards</t>
+          <t>dif_mean_last_360_matches_yellow_cards</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_240_matches_red_cards</t>
+          <t>dif_mean_last_360_matches_red_cards</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_240_matches_defensive_actions</t>
+          <t>dif_mean_last_360_matches_defensive_actions</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
@@ -670,7 +670,7 @@
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_240_matches_PPDA</t>
+          <t>dif_mean_last_360_matches_PPDA</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_240_matches_KGP</t>
+          <t>dif_mean_last_360_matches_KGP</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
@@ -690,375 +690,369 @@
       </c>
       <c r="BA1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_240_matches_clean_sheet</t>
+          <t>dif_mean_last_360_matches_clean_sheet</t>
         </is>
       </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_value_player_sub</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_wage_player_miss</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_start</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_start</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_sub</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_value_player_start</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_value_player_miss</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_hei_player_start</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_sub</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_start</t>
-        </is>
-      </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_start</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="BJ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="BK1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="BL1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="BM1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_miss</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_start</t>
-        </is>
-      </c>
-      <c r="BP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_value_player_miss</t>
-        </is>
-      </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="BR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_sub</t>
-        </is>
-      </c>
-      <c r="BS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="BT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_wage_player_miss</t>
-        </is>
-      </c>
-      <c r="BU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="BV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="BW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>xMovyDqH</t>
+          <t>6w5RRTN0</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45606.64583333334</v>
+        <v>45619.60416666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">brych f 
+          <t xml:space="preserve">dankert b 
   ger </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">voith arena
-  heidenheim </t>
+          <t xml:space="preserve">deutsche bank park
+  frankfurt </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>KWixEVWi</t>
+          <t>8vndvXTk</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>nwkTahLL</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>UgdQz0fK</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>4fuCGs9P</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>59</v>
       </c>
-      <c r="H2" t="n">
+      <c r="J2" t="n">
         <v>591</v>
       </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
         <v>20242025</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>germany</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>A15eUM4C</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2VSFgl3c</t>
-        </is>
-      </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1257142857142854</v>
+        <v>-0.3983333333333334</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.006666666666666821</v>
+        <v>0.9315294117647057</v>
       </c>
       <c r="R2" t="n">
-        <v>0.375</v>
+        <v>-1</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3</v>
+        <v>0.75</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5</v>
+        <v>-2.416666666666666</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4500000000000002</v>
+        <v>0.6480263157894743</v>
       </c>
       <c r="V2" t="n">
-        <v>2.375</v>
+        <v>-5.583333333333334</v>
       </c>
       <c r="W2" t="n">
-        <v>-1.4</v>
+        <v>4.30263157894737</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.75</v>
+        <v>1.75</v>
       </c>
       <c r="Y2" t="n">
+        <v>0.9473684210526316</v>
+      </c>
+      <c r="Z2" t="n">
         <v>0.5</v>
       </c>
-      <c r="Z2" t="n">
-        <v>-1.5</v>
-      </c>
       <c r="AA2" t="n">
-        <v>0.1499999999999999</v>
+        <v>0.868421052631579</v>
       </c>
       <c r="AB2" t="n">
-        <v>-5.96651138893786</v>
+        <v>24.27428902116402</v>
       </c>
       <c r="AC2" t="n">
-        <v>-1.030332965538073</v>
+        <v>19.53784523985533</v>
       </c>
       <c r="AD2" t="n">
-        <v>-97.7201017328309</v>
+        <v>1107.061810041728</v>
       </c>
       <c r="AE2" t="n">
-        <v>31.43980213135816</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>-87</v>
-      </c>
+        <v>859.130694973652</v>
+      </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="n">
-        <v>-38.07692307692308</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>-50</v>
-      </c>
+        <v>42.40000000000001</v>
+      </c>
+      <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="n">
-        <v>-26.23076923076923</v>
+        <v>33.75</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3.625</v>
+        <v>-7.166666666666664</v>
       </c>
       <c r="AK2" t="n">
-        <v>-2.649999999999999</v>
+        <v>10.01315789473684</v>
       </c>
       <c r="AL2" t="n">
+        <v>-16.5</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>6.440789473684205</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>-295.6666666666667</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>95.75294117647059</v>
+      </c>
+      <c r="AP2" t="n">
         <v>-2.25</v>
       </c>
-      <c r="AM2" t="n">
-        <v>-8</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>-0.8571428571428896</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>-90.55555555555554</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>-0.875</v>
-      </c>
       <c r="AQ2" t="n">
-        <v>-0.6000000000000003</v>
+        <v>-0.05964912280701729</v>
       </c>
       <c r="AR2" t="n">
-        <v>-0.3333333333333333</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.5</v>
+        <v>-0.2142857142857142</v>
       </c>
       <c r="AT2" t="n">
-        <v>-5.375</v>
+        <v>-0.5833333333333321</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.049999999999997</v>
+        <v>-0.3684210526315788</v>
       </c>
       <c r="AV2" t="n">
-        <v>4.48678236854289</v>
+        <v>23.36676554820719</v>
       </c>
       <c r="AW2" t="n">
-        <v>-0.364527501520449</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>-0.0479449874094299</v>
-      </c>
+        <v>-8.363342855351874</v>
+      </c>
+      <c r="AX2" t="inlineStr"/>
       <c r="AY2" t="n">
-        <v>-0.05492320041236257</v>
+        <v>0.02505216016690719</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-0.375</v>
+        <v>-0.25</v>
       </c>
       <c r="BA2" t="n">
-        <v>-0.1</v>
+        <v>-0.03289473684210525</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.622979797979809</v>
+        <v>-1.667201428756442</v>
       </c>
       <c r="BC2" t="n">
-        <v>-13235.1108413253</v>
+        <v>2.72768269233012</v>
       </c>
       <c r="BD2" t="n">
-        <v>-2.571428571428571</v>
+        <v>-2.775336700336702</v>
       </c>
       <c r="BE2" t="n">
-        <v>-5.285714285714286</v>
+        <v>4.940470262241561</v>
       </c>
       <c r="BF2" t="n">
-        <v>-6.070304050604008</v>
+        <v>4.545033670033675</v>
       </c>
       <c r="BG2" t="n">
-        <v>-0.3076178451178448</v>
+        <v>6159357.659290052</v>
       </c>
       <c r="BH2" t="n">
-        <v>-13729.96632996634</v>
+        <v>-1.571428571428571</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.9093779791404835</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="BJ2" t="n">
-        <v>2.203156565656567</v>
+        <v>-54285.71428571429</v>
       </c>
       <c r="BK2" t="n">
-        <v>-0.3497862912847685</v>
+        <v>0.5832912457912458</v>
       </c>
       <c r="BL2" t="n">
-        <v>-3.909595624837209</v>
+        <v>1.615951178451169</v>
       </c>
       <c r="BM2" t="n">
-        <v>-2.616203703703704</v>
+        <v>0.4260682622331231</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.3775510204081627</v>
+        <v>9712.54208754209</v>
       </c>
       <c r="BO2" t="n">
-        <v>-6356085.858585859</v>
+        <v>-113.1428571428571</v>
       </c>
       <c r="BP2" t="n">
-        <v>-53367857.14285714</v>
+        <v>-9.164285714285683</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.7908282380197704</v>
+        <v>6792.720169771674</v>
       </c>
       <c r="BR2" t="n">
-        <v>-6041529.678057254</v>
+        <v>7673282.82828283</v>
       </c>
       <c r="BS2" t="n">
-        <v>-227.5714285714286</v>
+        <v>-7992857.142857144</v>
       </c>
       <c r="BT2" t="n">
-        <v>-143571.4285714286</v>
+        <v>-129</v>
       </c>
       <c r="BU2" t="n">
-        <v>-5.193139730639714</v>
+        <v>2.515782828282852</v>
       </c>
       <c r="BV2" t="n">
-        <v>2.296938775510171</v>
+        <v>-7.073809523809526</v>
       </c>
       <c r="BW2" t="n">
-        <v>-210.8571428571429</v>
+        <v>-1.623419788135777</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>UkaNveph</t>
+          <t>fwAoyY0E</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45606.5625</v>
+        <v>45619.47916666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1079,1936 +1073,3539 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>8vndvXTk</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>hAcTWKKN</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>UkPWzhq8</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
         <v>59</v>
       </c>
-      <c r="H3" t="n">
+      <c r="J3" t="n">
         <v>591</v>
       </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
         <v>20242025</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>germany</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>hAcTWKKN</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>UkPWzhq8</t>
-        </is>
-      </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0.03571428571428559</v>
+        <v>2.258333333333333</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.5514035087719293</v>
+        <v>2.321875</v>
       </c>
       <c r="R3" t="n">
-        <v>0.375</v>
+        <v>1.75</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5714285714285714</v>
+        <v>2.578431372549019</v>
       </c>
       <c r="T3" t="n">
-        <v>2</v>
+        <v>5.333333333333334</v>
       </c>
       <c r="U3" t="n">
-        <v>2.628571428571429</v>
+        <v>5.705882352941177</v>
       </c>
       <c r="V3" t="n">
-        <v>5.5</v>
+        <v>14.66666666666666</v>
       </c>
       <c r="W3" t="n">
-        <v>4.130952380952381</v>
+        <v>10.41176470588235</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.75</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.6547619047619049</v>
+        <v>3.176470588235294</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.375</v>
+        <v>4.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.7</v>
+        <v>4.117647058823529</v>
       </c>
       <c r="AB3" t="n">
-        <v>-2.656135712090627</v>
+        <v>14.83455387205387</v>
       </c>
       <c r="AC3" t="n">
-        <v>-2.8619219800749</v>
+        <v>19.86932443580823</v>
       </c>
       <c r="AD3" t="n">
-        <v>-122.8561460456103</v>
+        <v>653.0649818684367</v>
       </c>
       <c r="AE3" t="n">
-        <v>-176.5155618910406</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>64</v>
-      </c>
+        <v>742.5641036385017</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="n">
-        <v>17.02197802197801</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>25</v>
-      </c>
+        <v>15.70879120879118</v>
+      </c>
+      <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="n">
-        <v>4.489010989010993</v>
+        <v>13.82417582417582</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8</v>
+        <v>11.66666666666666</v>
       </c>
       <c r="AK3" t="n">
-        <v>-1.490476190476194</v>
+        <v>6.398692810457522</v>
       </c>
       <c r="AL3" t="n">
-        <v>18.5</v>
+        <v>47.33333333333333</v>
       </c>
       <c r="AM3" t="n">
-        <v>21.22857142857143</v>
+        <v>25.52941176470588</v>
       </c>
       <c r="AN3" t="n">
-        <v>202.8571428571428</v>
+        <v>458.3333333333334</v>
       </c>
       <c r="AO3" t="n">
-        <v>247.3187134502924</v>
+        <v>314.7333333333333</v>
       </c>
       <c r="AP3" t="n">
-        <v>-0.875</v>
+        <v>-2.333333333333334</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.7192982456140349</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>-0.5</v>
-      </c>
+        <v>-1.941176470588235</v>
+      </c>
+      <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="n">
-        <v>-0.9166666666666667</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.5</v>
+        <v>-1.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.8857142857142861</v>
+        <v>-3.676470588235293</v>
       </c>
       <c r="AV3" t="n">
-        <v>-20.53162502855815</v>
+        <v>-42.99160340464688</v>
       </c>
       <c r="AW3" t="n">
-        <v>-27.49674209802243</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>-0.005279115814673316</v>
-      </c>
+        <v>-7.991251519697116</v>
+      </c>
+      <c r="AX3" t="inlineStr"/>
       <c r="AY3" t="n">
-        <v>-0.02466191651860965</v>
+        <v>-0.04394440910916127</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-0.25</v>
+        <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.2880952380952381</v>
+        <v>0.5686274509803921</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.5404040404040131</v>
+        <v>-1.887098599341158</v>
       </c>
       <c r="BC3" t="n">
-        <v>-1537.794621206966</v>
+        <v>5.74098376515424</v>
       </c>
       <c r="BD3" t="n">
-        <v>2.714285714285714</v>
+        <v>-3.77041245791246</v>
       </c>
       <c r="BE3" t="n">
-        <v>3.285714285714286</v>
+        <v>5.012486099585644</v>
       </c>
       <c r="BF3" t="n">
-        <v>-2.447670366913783</v>
+        <v>5.675799663299671</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0.208670033670034</v>
+        <v>10155717.28320942</v>
       </c>
       <c r="BH3" t="n">
-        <v>-6611.279461279468</v>
+        <v>1.142857142857143</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.513768479649865</v>
+        <v>1.714285714285715</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.3305134680134643</v>
+        <v>24571.42857142857</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.07122063308208793</v>
+        <v>0.4723484848484847</v>
       </c>
       <c r="BL3" t="n">
-        <v>1.59123839857682</v>
+        <v>4.108627946127939</v>
       </c>
       <c r="BM3" t="n">
-        <v>-0.1446127946127973</v>
+        <v>0.497288895315211</v>
       </c>
       <c r="BN3" t="n">
-        <v>2.738095238095241</v>
+        <v>9624.368686868682</v>
       </c>
       <c r="BO3" t="n">
-        <v>-476979.1666666698</v>
+        <v>105.4285714285714</v>
       </c>
       <c r="BP3" t="n">
-        <v>17857142.85714286</v>
+        <v>-2.645238095238057</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.7802279736731919</v>
+        <v>9133.118645275395</v>
       </c>
       <c r="BR3" t="n">
-        <v>2439717.465186602</v>
+        <v>10911550.92592593</v>
       </c>
       <c r="BS3" t="n">
-        <v>214.5714285714286</v>
+        <v>13025000</v>
       </c>
       <c r="BT3" t="n">
-        <v>65428.57142857143</v>
+        <v>78.28571428571431</v>
       </c>
       <c r="BU3" t="n">
-        <v>-1.725589225589218</v>
+        <v>-0.06237373737374696</v>
       </c>
       <c r="BV3" t="n">
-        <v>6.080952380952397</v>
+        <v>-3.595238095238095</v>
       </c>
       <c r="BW3" t="n">
-        <v>201.2857142857143</v>
+        <v>0.7197938407892366</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>UJQITUyi</t>
+          <t>pOGITkgl</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45606.47916666666</v>
+        <v>45619.47916666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stegemann s 
+          <t xml:space="preserve">brand b 
   ger </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">wwk arena
-  augsburg </t>
+          <t xml:space="preserve">signal iduna park
+  dortmund </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>fTVNku3I</t>
+          <t>nP1i5US1</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>hQAtP9Sl</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>IkCftsQm</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vZA6VYpf</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
         <v>59</v>
       </c>
-      <c r="H4" t="n">
+      <c r="J4" t="n">
         <v>591</v>
       </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
         <v>20242025</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>germany</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>f3ddUIXs</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0jdIgO6t</t>
-        </is>
-      </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.11</v>
+        <v>2.295</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1322222222222222</v>
+        <v>1.830666666666666</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="S4" t="n">
-        <v>0.45</v>
+        <v>2.682352941176471</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5</v>
+        <v>5</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7500000000000004</v>
+        <v>3.733333333333333</v>
       </c>
       <c r="V4" t="n">
-        <v>4.625</v>
+        <v>8.833333333333332</v>
       </c>
       <c r="W4" t="n">
-        <v>3.149999999999999</v>
+        <v>11.73333333333333</v>
       </c>
       <c r="X4" t="n">
-        <v>0.5</v>
+        <v>1.833333333333333</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.4500000000000002</v>
+        <v>1.145833333333333</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.125</v>
+        <v>3</v>
       </c>
       <c r="AA4" t="n">
-        <v>-0.3</v>
+        <v>1.223529411764706</v>
       </c>
       <c r="AB4" t="n">
-        <v>-1.516357376283847</v>
+        <v>19.05717703349282</v>
       </c>
       <c r="AC4" t="n">
-        <v>-2.510531629763525</v>
+        <v>15.8990622669778</v>
       </c>
       <c r="AD4" t="n">
-        <v>37.15846521413158</v>
+        <v>773.0617890614209</v>
       </c>
       <c r="AE4" t="n">
-        <v>-12.93410610212396</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>16</v>
-      </c>
+        <v>738.9973974970897</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="n">
-        <v>-1.07692307692308</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>40</v>
-      </c>
+        <v>38.42307692307692</v>
+      </c>
+      <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="n">
-        <v>11.07692307692308</v>
+        <v>36.17948717948718</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-1.25</v>
+        <v>19.66666666666666</v>
       </c>
       <c r="AK4" t="n">
-        <v>-1.700000000000003</v>
+        <v>15.78039215686274</v>
       </c>
       <c r="AL4" t="n">
-        <v>-15</v>
+        <v>28</v>
       </c>
       <c r="AM4" t="n">
-        <v>-10.8</v>
+        <v>30.125</v>
       </c>
       <c r="AN4" t="n">
-        <v>-107.5714285714286</v>
+        <v>322.1666666666666</v>
       </c>
       <c r="AO4" t="n">
-        <v>-129.0555555555555</v>
+        <v>342.1333333333334</v>
       </c>
       <c r="AP4" t="n">
-        <v>-0.75</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-0.1999999999999997</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>-0.3333333333333334</v>
-      </c>
+        <v>-0.6125</v>
+      </c>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU4" t="n">
-        <v>4.349999999999998</v>
+        <v>0.5137254901960784</v>
       </c>
       <c r="AV4" t="n">
-        <v>-4.133230403948861</v>
+        <v>-24.00997718299508</v>
       </c>
       <c r="AW4" t="n">
-        <v>-22.96455133408513</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>-0.05033218400470944</v>
-      </c>
+        <v>-33.42069928193193</v>
+      </c>
+      <c r="AX4" t="inlineStr"/>
       <c r="AY4" t="n">
-        <v>0.0445031025923889</v>
+        <v>0.01716042146862258</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.125</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="BA4" t="n">
-        <v>-0.05000000000000002</v>
-      </c>
-      <c r="BB4" t="inlineStr"/>
+        <v>-0.1607843137254901</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>-1.791051712100138</v>
+      </c>
       <c r="BC4" t="n">
-        <v>-3782.336641793878</v>
+        <v>3.130878727956059</v>
       </c>
       <c r="BD4" t="n">
-        <v>-1.142857142857143</v>
+        <v>-0.4806818181818144</v>
       </c>
       <c r="BE4" t="n">
-        <v>-4.857142857142858</v>
+        <v>5.522616390186883</v>
       </c>
       <c r="BF4" t="n">
-        <v>-0.7226451545530495</v>
-      </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+        <v>5.071590909090915</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>15608154.07011046</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>-1.857142857142858</v>
+      </c>
       <c r="BI4" t="n">
-        <v>-0.3412669932406835</v>
-      </c>
-      <c r="BJ4" t="inlineStr"/>
+        <v>1.285714285714286</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>27857.14285714286</v>
+      </c>
       <c r="BK4" t="n">
-        <v>-0.1423175599984809</v>
+        <v>0.8738636363636363</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.5826973921546283</v>
-      </c>
-      <c r="BM4" t="inlineStr"/>
+        <v>5.211363636363615</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>0.521807285253745</v>
+      </c>
       <c r="BN4" t="n">
-        <v>-0.7981292517006828</v>
-      </c>
-      <c r="BO4" t="inlineStr"/>
+        <v>30697.72727272727</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>-106.5714285714286</v>
+      </c>
       <c r="BP4" t="n">
-        <v>-26432142.85714286</v>
+        <v>-2.024999999999977</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.6380313947747709</v>
+        <v>19522.6496548276</v>
       </c>
       <c r="BR4" t="n">
-        <v>-517740.6465975549</v>
+        <v>25298863.63636364</v>
       </c>
       <c r="BS4" t="n">
-        <v>-110.4285714285714</v>
+        <v>51285714.28571428</v>
       </c>
       <c r="BT4" t="n">
-        <v>-79857.14285714287</v>
-      </c>
-      <c r="BU4" t="inlineStr"/>
+        <v>-113.8571428571429</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>1.826136363636351</v>
+      </c>
       <c r="BV4" t="n">
-        <v>0.5443877551020364</v>
+        <v>-4.066666666666674</v>
       </c>
       <c r="BW4" t="n">
-        <v>-104.4285714285714</v>
+        <v>-0.006070604512501632</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>j5mWxZE4</t>
+          <t>2qNaDU87</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45605.60416666666</v>
+        <v>45619.47916666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">dankert b 
+          <t xml:space="preserve">willenborg f 
   ger </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">red bull arena
-  leipzig </t>
+          <t xml:space="preserve">bayarena
+  leverkusen </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>KbS1suSm</t>
+          <t>4jcj2zMd</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>88HSzjDr</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>hAcTWKKN</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>4ljanukM</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
         <v>59</v>
       </c>
-      <c r="H5" t="n">
+      <c r="J5" t="n">
         <v>591</v>
       </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
         <v>20242025</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>germany</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>IkCftsQm</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>4fuCGs9P</t>
-        </is>
-      </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0.09857142857142875</v>
+        <v>1.833333333333333</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5766666666666667</v>
+        <v>2.2465</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7499999999999999</v>
+        <v>2.809523809523809</v>
       </c>
       <c r="T5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="U5" t="n">
+        <v>5.896825396825397</v>
+      </c>
+      <c r="V5" t="n">
+        <v>10</v>
+      </c>
+      <c r="W5" t="n">
+        <v>14.96031746031746</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.301587301587302</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>17.8977989481279</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>14.34980911725967</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>718.0740473424044</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>699.6211797406373</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="n">
+        <v>88.84821428571428</v>
+      </c>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="n">
+        <v>71.26785714285714</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>10.93650793650793</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>24</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>29.7936507936508</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>286</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>446.5257352941176</v>
+      </c>
+      <c r="AP5" t="n">
         <v>0.75</v>
       </c>
-      <c r="U5" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V5" t="n">
-        <v>-1.625</v>
-      </c>
-      <c r="W5" t="n">
-        <v>2.149999999999999</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.375</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.875</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.703756731048636</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0.1320598648620592</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>-88.44062437232091</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>-67.89257486745072</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>107</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>51</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>9.384615384615387</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>-0.125</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>-1.149999999999999</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>-8.25</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>4.100000000000009</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>-19.57142857142861</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>75.8888888888888</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>-0.1071428571428572</v>
-      </c>
       <c r="AQ5" t="n">
-        <v>-0.5789473684210527</v>
+        <v>0.4206349206349209</v>
       </c>
       <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="AT5" t="n">
-        <v>-1.25</v>
+        <v>1.75</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0.9499999999999993</v>
+        <v>-3.84920634920635</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.03468513393456973</v>
+        <v>-17.25462090244699</v>
       </c>
       <c r="AW5" t="n">
-        <v>-10.49858712412411</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>-0.0555051555051555</v>
-      </c>
+        <v>-32.02661773487407</v>
+      </c>
+      <c r="AX5" t="inlineStr"/>
       <c r="AY5" t="n">
-        <v>-0.03692391287234778</v>
+        <v>0.04344650649590027</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.375</v>
+        <v>0.25</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.3</v>
+        <v>0.1666666666666666</v>
       </c>
       <c r="BB5" t="n">
-        <v>-1.06701388888888</v>
+        <v>-1.3538992523887</v>
       </c>
       <c r="BC5" t="n">
-        <v>26736.88442447571</v>
+        <v>10.80434748586522</v>
       </c>
       <c r="BD5" t="n">
-        <v>-1.714285714285714</v>
+        <v>-0.3375631313131322</v>
       </c>
       <c r="BE5" t="n">
-        <v>1</v>
+        <v>11.87124982815918</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.678356317086511</v>
+        <v>11.20814393939392</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.895486111111111</v>
+        <v>35886549.89579412</v>
       </c>
       <c r="BH5" t="n">
-        <v>33696.52777777778</v>
+        <v>-2</v>
       </c>
       <c r="BI5" t="n">
-        <v>-0.3265257988466885</v>
+        <v>-2.285714285714286</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.2128472222222229</v>
+        <v>12000</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.6816601599033623</v>
+        <v>1.975</v>
       </c>
       <c r="BL5" t="n">
-        <v>4.71436943766308</v>
+        <v>11.14671717171717</v>
       </c>
       <c r="BM5" t="n">
-        <v>5.640624999999986</v>
+        <v>1.319541165445098</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.817687074829934</v>
+        <v>77193.75</v>
       </c>
       <c r="BO5" t="n">
-        <v>22125902.77777778</v>
+        <v>-130.7142857142857</v>
       </c>
       <c r="BP5" t="n">
-        <v>49317857.14285715</v>
+        <v>-11.59523809523807</v>
       </c>
       <c r="BQ5" t="n">
-        <v>2.591271312630198</v>
+        <v>61401.20860597204</v>
       </c>
       <c r="BR5" t="n">
-        <v>15584271.31802334</v>
+        <v>45194659.09090909</v>
       </c>
       <c r="BS5" t="n">
-        <v>-108.8571428571429</v>
+        <v>22782142.85714286</v>
       </c>
       <c r="BT5" t="n">
-        <v>101000</v>
+        <v>-123.2857142857143</v>
       </c>
       <c r="BU5" t="n">
-        <v>6.126388888888883</v>
+        <v>-1.899431818181796</v>
       </c>
       <c r="BV5" t="n">
-        <v>-2.181292517006796</v>
+        <v>-0.1666666666666643</v>
       </c>
       <c r="BW5" t="n">
-        <v>-92.14285714285711</v>
+        <v>-3.508229611838146</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>biQrHC9r</t>
+          <t>E38ZP7hD</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45605.47916666666</v>
+        <v>45619.47916666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">siebert d 
+          <t xml:space="preserve">stieler t 
   ger </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">vonovia ruhrstadion
-  bochum </t>
+          <t xml:space="preserve">prezero arena
+  sinsheim </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>8Y2m6ADe</t>
+          <t>hQAtP9Sl</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>4jcj2zMd</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>KUx4Q7x1</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>pfoInmcq</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>59</v>
       </c>
-      <c r="H6" t="n">
+      <c r="J6" t="n">
         <v>591</v>
       </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
         <v>20242025</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>germany</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>UgdQz0fK</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>GzfvcwRj</t>
-        </is>
-      </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.367142857142857</v>
+        <v>0.1266666666666665</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.353857142857143</v>
+        <v>0.2012500000000002</v>
       </c>
       <c r="R6" t="n">
-        <v>-3.267857142857143</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-2.838509316770186</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>-5.482142857142858</v>
+        <v>3</v>
       </c>
       <c r="U6" t="n">
-        <v>-5.432712215320912</v>
+        <v>0.7647058823529411</v>
       </c>
       <c r="V6" t="n">
-        <v>-12.46428571428572</v>
+        <v>7.166666666666668</v>
       </c>
       <c r="W6" t="n">
-        <v>-10.47619047619048</v>
+        <v>4.411764705882353</v>
       </c>
       <c r="X6" t="n">
-        <v>-3.428571428571429</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="Y6" t="n">
-        <v>-2.863354037267081</v>
+        <v>-0.7058823529411764</v>
       </c>
       <c r="Z6" t="n">
-        <v>-4.071428571428571</v>
+        <v>-1</v>
       </c>
       <c r="AA6" t="n">
-        <v>-3.670807453416149</v>
+        <v>-0.5294117647058825</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.7398150885614951</v>
+        <v>16.52009189640768</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.46036763737978</v>
+        <v>20.31169940293962</v>
       </c>
       <c r="AD6" t="n">
-        <v>18.84122884296164</v>
+        <v>867.7326186485105</v>
       </c>
       <c r="AE6" t="n">
-        <v>42.20169125287771</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>-27</v>
-      </c>
+        <v>913.7597505786052</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="n">
-        <v>-8.762499999999989</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>-37</v>
-      </c>
+        <v>27.23076923076921</v>
+      </c>
+      <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="n">
-        <v>-33.01666666666667</v>
+        <v>22.46153846153847</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-10.875</v>
+        <v>14.58333333333333</v>
       </c>
       <c r="AK6" t="n">
-        <v>-9.964803312629403</v>
+        <v>6.294117647058819</v>
       </c>
       <c r="AL6" t="n">
-        <v>-28.28571428571429</v>
+        <v>8.5</v>
       </c>
       <c r="AM6" t="n">
-        <v>-19.2463768115942</v>
+        <v>1.17647058823529</v>
       </c>
       <c r="AN6" t="n">
-        <v>-306.8571428571429</v>
+        <v>38</v>
       </c>
       <c r="AO6" t="n">
-        <v>-208.9210526315789</v>
+        <v>-11.25</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.4464285714285714</v>
+        <v>-1.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.181818181818182</v>
+        <v>0.2389705882352939</v>
       </c>
       <c r="AR6" t="inlineStr"/>
       <c r="AS6" t="n">
-        <v>0.2</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.625</v>
+        <v>2.75</v>
       </c>
       <c r="AU6" t="n">
-        <v>2.120082815734989</v>
+        <v>-1.058823529411764</v>
       </c>
       <c r="AV6" t="n">
-        <v>13.66523420265916</v>
+        <v>6.24292718045578</v>
       </c>
       <c r="AW6" t="n">
-        <v>18.38634811831883</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0.03659375975061279</v>
-      </c>
+        <v>12.89385280251953</v>
+      </c>
+      <c r="AX6" t="inlineStr"/>
       <c r="AY6" t="n">
-        <v>0.02552748184216082</v>
+        <v>0.04727321206037509</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-0.2678571428571428</v>
+        <v>-0.9166666666666666</v>
       </c>
       <c r="BA6" t="n">
-        <v>-0.6376811594202898</v>
+        <v>-0.2941176470588235</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.498674242424244</v>
+        <v>-0.9685483902492393</v>
       </c>
       <c r="BC6" t="n">
-        <v>-65353.74310595404</v>
+        <v>-6.244502514921436</v>
       </c>
       <c r="BD6" t="n">
-        <v>2.142857142857143</v>
+        <v>0.9482638888888921</v>
       </c>
       <c r="BE6" t="n">
-        <v>2.428571428571428</v>
+        <v>-4.094978261440147</v>
       </c>
       <c r="BF6" t="n">
-        <v>-10.66006282357974</v>
+        <v>-4.709027777777777</v>
       </c>
       <c r="BG6" t="n">
-        <v>-2.023863636363636</v>
+        <v>-16068608.74787515</v>
       </c>
       <c r="BH6" t="n">
-        <v>-82257.76515151515</v>
+        <v>2.571428571428572</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.776625471462843</v>
+        <v>2.000000000000001</v>
       </c>
       <c r="BJ6" t="n">
-        <v>1.840425084175084</v>
+        <v>-6857.142857142841</v>
       </c>
       <c r="BK6" t="n">
-        <v>-1.364937584882438</v>
+        <v>-0.6809027777777774</v>
       </c>
       <c r="BL6" t="n">
-        <v>-11.32112164037241</v>
+        <v>-5.386458333333337</v>
       </c>
       <c r="BM6" t="n">
-        <v>-11.9101430976431</v>
+        <v>-0.7201599419672176</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.952380952380953</v>
+        <v>-27957.29166666667</v>
       </c>
       <c r="BO6" t="n">
-        <v>-46171269.99158249</v>
+        <v>174.7142857142857</v>
       </c>
       <c r="BP6" t="n">
-        <v>-20246428.57142857</v>
+        <v>2.09370748299321</v>
       </c>
       <c r="BQ6" t="n">
-        <v>2.963943170071417</v>
+        <v>-24864.63586830267</v>
       </c>
       <c r="BR6" t="n">
-        <v>-36276816.4581707</v>
+        <v>-22108541.66666667</v>
       </c>
       <c r="BS6" t="n">
-        <v>147</v>
+        <v>-37171428.57142857</v>
       </c>
       <c r="BT6" t="n">
-        <v>-11428.57142857143</v>
+        <v>181.2857142857143</v>
       </c>
       <c r="BU6" t="n">
-        <v>-11.86222643097642</v>
+        <v>1.964930555555554</v>
       </c>
       <c r="BV6" t="n">
-        <v>12.25</v>
+        <v>2.048129251700683</v>
       </c>
       <c r="BW6" t="n">
-        <v>142.4285714285714</v>
+        <v>-0.5866735410272668</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>nee3ysec</t>
+          <t>SrjMmBpK</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45605.47916666666</v>
+        <v>45619.47916666666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">stieler t 
+          <t xml:space="preserve">jollenbeck m 
   ger </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">mewa arena
-  mainz </t>
+          <t xml:space="preserve">volkswagen arena
+  wolfsburg </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>EuakNmc1</t>
+          <t>nwkTahLL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>nP1i5US1</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>f3ddUIXs</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>hpYJ6izc</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
         <v>59</v>
       </c>
-      <c r="H7" t="n">
+      <c r="J7" t="n">
         <v>591</v>
       </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
         <v>20242025</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>germany</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>YZPE6Sx7</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>pfoInmcq</t>
-        </is>
-      </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.145714285714286</v>
+        <v>0.5700000000000002</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.3977777777777778</v>
+        <v>0.6887500000000002</v>
       </c>
       <c r="R7" t="n">
-        <v>-1.5</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2999999999999998</v>
+        <v>0.8235294117647058</v>
       </c>
       <c r="T7" t="n">
-        <v>-3.875</v>
+        <v>1.25</v>
       </c>
       <c r="U7" t="n">
-        <v>-2.65</v>
+        <v>0.9869281045751639</v>
       </c>
       <c r="V7" t="n">
-        <v>-6.625</v>
+        <v>1.75</v>
       </c>
       <c r="W7" t="n">
-        <v>-3.199999999999999</v>
+        <v>4.163398692810455</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5</v>
+        <v>0.75</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.05000000000000004</v>
+        <v>0.2516339869281048</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.75</v>
+        <v>1.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>-0.05882352941176483</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.433975939944315</v>
+        <v>18.49064407814408</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.784058499960877</v>
+        <v>18.89844925221944</v>
       </c>
       <c r="AD7" t="n">
-        <v>156.0030070881812</v>
+        <v>788.7193336356406</v>
       </c>
       <c r="AE7" t="n">
-        <v>103.7892492907417</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>22</v>
-      </c>
+        <v>787.6267782232951</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="n">
-        <v>-25.69230769230771</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>27</v>
-      </c>
+        <v>40.29120879120879</v>
+      </c>
+      <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="n">
-        <v>-4.153846153846153</v>
+        <v>15.82967032967033</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-21.5</v>
+        <v>-4.25</v>
       </c>
       <c r="AK7" t="n">
-        <v>-11.3</v>
+        <v>4.718954248366011</v>
       </c>
       <c r="AL7" t="n">
-        <v>-35.5</v>
+        <v>2</v>
       </c>
       <c r="AM7" t="n">
-        <v>-27.7</v>
+        <v>11.24183006535948</v>
       </c>
       <c r="AN7" t="n">
-        <v>-300.2857142857143</v>
+        <v>238.3333333333334</v>
       </c>
       <c r="AO7" t="n">
-        <v>-268.5555555555555</v>
+        <v>186.625</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.375</v>
+        <v>0.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.1815789473684211</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>-1.333333333333333</v>
-      </c>
+        <v>-0.5718954248366017</v>
+      </c>
+      <c r="AR7" t="inlineStr"/>
       <c r="AS7" t="n">
-        <v>-1</v>
+        <v>-0.3333333333333334</v>
       </c>
       <c r="AT7" t="n">
-        <v>5.375</v>
+        <v>-4.75</v>
       </c>
       <c r="AU7" t="n">
-        <v>4.199999999999998</v>
+        <v>-2.604575163398692</v>
       </c>
       <c r="AV7" t="n">
-        <v>9.199387755922942</v>
+        <v>-8.767614549193492</v>
       </c>
       <c r="AW7" t="n">
-        <v>13.91192045731323</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>0.08341253341253342</v>
-      </c>
+        <v>-1.372683819127253</v>
+      </c>
+      <c r="AX7" t="inlineStr"/>
       <c r="AY7" t="n">
-        <v>-0.02959240036862009</v>
+        <v>0.01354379830270865</v>
       </c>
       <c r="AZ7" t="n">
-        <v>-0.125</v>
+        <v>0.75</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.04999999999999999</v>
+        <v>0.3954248366013072</v>
       </c>
       <c r="BB7" t="n">
-        <v>-3.133080808080763</v>
+        <v>-1.240427176088524</v>
       </c>
       <c r="BC7" t="n">
-        <v>-21240.47309115034</v>
+        <v>0.295691058433988</v>
       </c>
       <c r="BD7" t="n">
-        <v>-1.785714285714286</v>
+        <v>-2.09393939393939</v>
       </c>
       <c r="BE7" t="n">
-        <v>-4.880952380952381</v>
+        <v>2.359226083948244</v>
       </c>
       <c r="BF7" t="n">
-        <v>-5.331014088250924</v>
+        <v>2.189225589225586</v>
       </c>
       <c r="BG7" t="n">
-        <v>-1.146085858585859</v>
+        <v>3931773.737828379</v>
       </c>
       <c r="BH7" t="n">
-        <v>-32590.78282828283</v>
+        <v>2.714285714285714</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.6627883769137703</v>
+        <v>4.571428571428571</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.3959595959595994</v>
+        <v>106000</v>
       </c>
       <c r="BK7" t="n">
-        <v>-0.6958263249478418</v>
+        <v>0.01797138047138014</v>
       </c>
       <c r="BL7" t="n">
-        <v>-5.808847598050377</v>
+        <v>0.5870370370370495</v>
       </c>
       <c r="BM7" t="n">
-        <v>-7.30441919191918</v>
+        <v>0.2851617343681803</v>
       </c>
       <c r="BN7" t="n">
-        <v>6.119047619047624</v>
+        <v>9161.153198653203</v>
       </c>
       <c r="BO7" t="n">
-        <v>-30257335.85858586</v>
+        <v>229.1428571428571</v>
       </c>
       <c r="BP7" t="n">
-        <v>-63640476.19047619</v>
+        <v>3.464965986394617</v>
       </c>
       <c r="BQ7" t="n">
-        <v>-0.03119675302340852</v>
+        <v>7881.282723503027</v>
       </c>
       <c r="BR7" t="n">
-        <v>-18492191.47258186</v>
+        <v>3547146.464646464</v>
       </c>
       <c r="BS7" t="n">
-        <v>-161.8571428571428</v>
+        <v>42657142.85714285</v>
       </c>
       <c r="BT7" t="n">
-        <v>-80642.85714285714</v>
+        <v>199.2857142857143</v>
       </c>
       <c r="BU7" t="n">
-        <v>-6.720202020202024</v>
+        <v>-1.542297979798008</v>
       </c>
       <c r="BV7" t="n">
-        <v>1.136904761904759</v>
+        <v>-4.901360544217692</v>
       </c>
       <c r="BW7" t="n">
-        <v>-137.0238095238095</v>
+        <v>1.837750054471911</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>6HTjFjve</t>
+          <t>EuQnZBVQ</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45605.47916666666</v>
+        <v>45618.6875</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">jollenbeck m 
+          <t xml:space="preserve">brych f 
   ger </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">millerntor stadion
-  hamburg </t>
+          <t xml:space="preserve">allianz arena
+  munich </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ILyJuN3g</t>
+          <t>nVp0wiqd</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>nVp0wiqd</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
+          <t>fTVNku3I</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>K6A2elS9</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2VSFgl3c</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
         <v>59</v>
       </c>
-      <c r="H8" t="n">
+      <c r="J8" t="n">
         <v>591</v>
       </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
         <v>20242025</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>germany</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>KUx4Q7x1</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>hpYJ6izc</t>
-        </is>
-      </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.828571428571428</v>
+        <v>2.883333333333333</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.512222222222223</v>
+        <v>2.761333333333333</v>
       </c>
       <c r="R8" t="n">
-        <v>-3.375</v>
+        <v>4</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.65</v>
+        <v>3.125</v>
       </c>
       <c r="T8" t="n">
-        <v>-10.125</v>
+        <v>9.666666666666666</v>
       </c>
       <c r="U8" t="n">
-        <v>-4.800000000000001</v>
+        <v>5.929166666666667</v>
       </c>
       <c r="V8" t="n">
-        <v>-15.875</v>
+        <v>23</v>
       </c>
       <c r="W8" t="n">
-        <v>-6.449999999999999</v>
+        <v>13.25</v>
       </c>
       <c r="X8" t="n">
-        <v>-3.625</v>
+        <v>4.333333333333333</v>
       </c>
       <c r="Y8" t="n">
-        <v>-1.9</v>
+        <v>2.679166666666667</v>
       </c>
       <c r="Z8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>3.125</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>8.774434824434824</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>16.35429481724464</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>652.3882259438739</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>771.4646214240738</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="n">
+        <v>48.62820512820514</v>
+      </c>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="n">
+        <v>28.98076923076923</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>19</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>8.616666666666667</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>64.00000000000001</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>27.43333333333334</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>676.3333333333333</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>373.8666666666666</v>
+      </c>
+      <c r="AP8" t="n">
         <v>-3</v>
       </c>
-      <c r="AA8" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="AD8" t="n">
-        <v>361.8556616060502</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>115.280925646005</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>-56</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>-6.615384615384613</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>-64</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>-7.53846153846154</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>-9.25</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>-4.100000000000001</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>-53</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>-23.3</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>-667.8571428571429</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>-270.9444444444444</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>-0.2142857142857142</v>
-      </c>
       <c r="AQ8" t="n">
-        <v>0.5701754385964912</v>
+        <v>-1.991071428571429</v>
       </c>
       <c r="AR8" t="inlineStr"/>
-      <c r="AS8" t="inlineStr"/>
+      <c r="AS8" t="n">
+        <v>-1</v>
+      </c>
       <c r="AT8" t="n">
-        <v>5</v>
+        <v>-9.999999999999998</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.600000000000003</v>
+        <v>-5.429166666666667</v>
       </c>
       <c r="AV8" t="n">
-        <v>55.01901221397462</v>
+        <v>-22.48925143083038</v>
       </c>
       <c r="AW8" t="n">
-        <v>21.77895110988679</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>0.01857756362317348</v>
-      </c>
+        <v>-3.598696478730545</v>
+      </c>
+      <c r="AX8" t="inlineStr"/>
       <c r="AY8" t="n">
-        <v>0.02761399769246548</v>
+        <v>-0.03264975619882272</v>
       </c>
       <c r="AZ8" t="n">
-        <v>-0.5</v>
+        <v>1</v>
       </c>
       <c r="BA8" t="n">
-        <v>-0.4</v>
+        <v>0.65</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.005681818181785</v>
+        <v>2.251232931370318</v>
       </c>
       <c r="BC8" t="n">
-        <v>-59535.90327944043</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>-0.7142857142857144</v>
-      </c>
+        <v>8.329613716499352</v>
+      </c>
+      <c r="BD8" t="inlineStr"/>
       <c r="BE8" t="n">
-        <v>-2.571428571428572</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>-12.08477758427934</v>
-      </c>
+        <v>6.531270117696209</v>
+      </c>
+      <c r="BF8" t="inlineStr"/>
       <c r="BG8" t="n">
-        <v>-2.331944444444444</v>
+        <v>30075703.86615073</v>
       </c>
       <c r="BH8" t="n">
-        <v>-65116.41414141414</v>
+        <v>0.2857142857142856</v>
       </c>
       <c r="BI8" t="n">
-        <v>-0.5115454076367385</v>
+        <v>2.142857142857143</v>
       </c>
       <c r="BJ8" t="n">
-        <v>-0.5477272727272791</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>-1.603642070863433</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>-12.54221007481941</v>
-      </c>
+        <v>120714.2857142857</v>
+      </c>
+      <c r="BK8" t="inlineStr"/>
+      <c r="BL8" t="inlineStr"/>
       <c r="BM8" t="n">
-        <v>-12.86300505050505</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>4.897619047619052</v>
-      </c>
+        <v>1.525032312566175</v>
+      </c>
+      <c r="BN8" t="inlineStr"/>
       <c r="BO8" t="n">
-        <v>-47224346.59090909</v>
+        <v>68.85714285714289</v>
       </c>
       <c r="BP8" t="n">
-        <v>-91827142.85714285</v>
+        <v>1.235714285714266</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.474570540935645</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>-33479546.4745657</v>
-      </c>
+        <v>55195.85583602128</v>
+      </c>
+      <c r="BR8" t="inlineStr"/>
       <c r="BS8" t="n">
-        <v>-115.8571428571429</v>
+        <v>82610714.28571428</v>
       </c>
       <c r="BT8" t="n">
-        <v>-149285.7142857143</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>-12.45416666666667</v>
-      </c>
+        <v>31.42857142857144</v>
+      </c>
+      <c r="BU8" t="inlineStr"/>
       <c r="BV8" t="n">
-        <v>2.492857142857162</v>
+        <v>-3.807142857142857</v>
       </c>
       <c r="BW8" t="n">
-        <v>-84.28571428571428</v>
+        <v>-2.370214717665306</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>YmumZjET</t>
+          <t>xMovyDqH</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45605.47916666666</v>
+        <v>45606.64583333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">willenborg f 
+          <t xml:space="preserve">osmers h 
   ger </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">weserstadion
-  bremen </t>
+          <t xml:space="preserve">voith arena
+  heidenheim </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ig1f1fy3</t>
+          <t>KWixEVWi</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>63WsD2ei</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>A15eUM4C</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2VSFgl3c</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
         <v>59</v>
       </c>
-      <c r="H9" t="n">
+      <c r="J9" t="n">
         <v>591</v>
       </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
         <v>20242025</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>germany</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>M5BRZDsC</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>4ljanukM</t>
-        </is>
-      </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1028571428571425</v>
+        <v>-0.1066666666666669</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.2283333333333333</v>
+        <v>0.1343749999999997</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1499999999999999</v>
+        <v>0.1654411764705883</v>
       </c>
       <c r="T9" t="n">
-        <v>1.75</v>
+        <v>0.6666666666666674</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2000000000000002</v>
+        <v>0.1066176470588234</v>
       </c>
       <c r="V9" t="n">
-        <v>3.5</v>
+        <v>6.333333333333334</v>
       </c>
       <c r="W9" t="n">
-        <v>1.150000000000002</v>
+        <v>1.047794117647058</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>-1.666666666666667</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.1000000000000003</v>
+        <v>0.3639705882352942</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.875</v>
+        <v>-2</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.1500000000000001</v>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>0.1764705882352942</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>18.56914098972923</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>20.37702604864808</v>
       </c>
       <c r="AD9" t="n">
-        <v>-166.4404585061379</v>
+        <v>763.7367266984069</v>
       </c>
       <c r="AE9" t="n">
-        <v>-21.16803923184236</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>34</v>
-      </c>
+        <v>864.8234369854948</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="n">
-        <v>-6</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>10</v>
-      </c>
+        <v>-9.285714285714278</v>
+      </c>
+      <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="n">
-        <v>4.53846153846154</v>
+        <v>-3.719780219780219</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.75</v>
+        <v>5.666666666666671</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.800000000000004</v>
+        <v>-0.503676470588232</v>
       </c>
       <c r="AL9" t="n">
-        <v>8.25</v>
+        <v>10.66666666666667</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.2999999999999972</v>
+        <v>-0.9632352941176521</v>
       </c>
       <c r="AN9" t="n">
-        <v>162.7142857142858</v>
+        <v>161.3333333333334</v>
       </c>
       <c r="AO9" t="n">
-        <v>7.5</v>
+        <v>16.99166666666673</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-0.1710526315789471</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>-0.5</v>
-      </c>
+        <v>-1.036764705882353</v>
+      </c>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
-        <v>-1</v>
+        <v>-6.666666666666666</v>
       </c>
       <c r="AU9" t="n">
-        <v>-2.849999999999998</v>
+        <v>3.07720588235294</v>
       </c>
       <c r="AV9" t="n">
-        <v>12.20482815634518</v>
+        <v>5.171003915910536</v>
       </c>
       <c r="AW9" t="n">
-        <v>23.50885065874618</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>-0.06360022603714025</v>
-      </c>
+        <v>-13.27521214561568</v>
+      </c>
+      <c r="AX9" t="inlineStr"/>
       <c r="AY9" t="n">
-        <v>0.01255912972227</v>
+        <v>-0.01730730088726171</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>-0.6666666666666667</v>
       </c>
       <c r="BA9" t="n">
-        <v>-0.3</v>
+        <v>-0.003676470588235281</v>
       </c>
       <c r="BB9" t="n">
-        <v>-3.2525883838384</v>
+        <v>0.9093779791404835</v>
       </c>
       <c r="BC9" t="n">
-        <v>3934.688670168503</v>
+        <v>-3.909595624837209</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.4285714285714284</v>
+        <v>2.203156565656567</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.4285714285714284</v>
+        <v>-6.070304050604008</v>
       </c>
       <c r="BF9" t="n">
-        <v>3.51653808743697</v>
+        <v>-5.193139730639714</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.09772727272727288</v>
+        <v>-6041529.678057254</v>
       </c>
       <c r="BH9" t="n">
-        <v>7243.592171717173</v>
+        <v>-4</v>
       </c>
       <c r="BI9" t="n">
-        <v>-1.212872132158459</v>
+        <v>-7</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.8377209595959627</v>
+        <v>-197000</v>
       </c>
       <c r="BK9" t="n">
-        <v>0</v>
+        <v>-0.3076178451178448</v>
       </c>
       <c r="BL9" t="n">
-        <v>1.940461439542531</v>
+        <v>-2.616203703703704</v>
       </c>
       <c r="BM9" t="n">
-        <v>4.861363636363649</v>
+        <v>-0.3497862912847685</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.214285714285715</v>
+        <v>-13729.96632996634</v>
       </c>
       <c r="BO9" t="n">
-        <v>4073626.893939395</v>
+        <v>-342</v>
       </c>
       <c r="BP9" t="n">
-        <v>6114285.714285715</v>
+        <v>4</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.374202753053567</v>
+        <v>-13235.1108413253</v>
       </c>
       <c r="BR9" t="n">
-        <v>1537195.451264029</v>
+        <v>-6356085.858585859</v>
       </c>
       <c r="BS9" t="n">
-        <v>38</v>
+        <v>-66925000</v>
       </c>
       <c r="BT9" t="n">
-        <v>24428.57142857143</v>
+        <v>-327</v>
       </c>
       <c r="BU9" t="n">
-        <v>4.183901515151504</v>
+        <v>1.622979797979809</v>
       </c>
       <c r="BV9" t="n">
-        <v>-2.452380952380963</v>
+        <v>-1.238095238095241</v>
       </c>
       <c r="BW9" t="n">
-        <v>38.71428571428569</v>
+        <v>0.7908282380197704</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
+          <t>UkaNveph</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45606.5625</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">zwayer f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mhparena
+  stuttgart </t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>hAcTWKKN</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>UkPWzhq8</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>59</v>
+      </c>
+      <c r="J10" t="n">
+        <v>591</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.204166666666667</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.860955882352941</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.735294117647059</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U10" t="n">
+        <v>4.496732026143791</v>
+      </c>
+      <c r="V10" t="n">
+        <v>11</v>
+      </c>
+      <c r="W10" t="n">
+        <v>11.02941176470588</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2.205882352941177</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.784313725490196</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>17.38905385872297</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>16.45934007658951</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>787.1513569611509</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>817.4895263976072</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="n">
+        <v>55.45641025641024</v>
+      </c>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="n">
+        <v>32.07179487179487</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>9.13725490196078</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>23.84967320261438</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>235.2499999999999</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>341.4833333333333</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>-1.705882352941176</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>-3.702614379084965</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>-29.02808749664499</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>-8.78699609168757</v>
+      </c>
+      <c r="AX10" t="inlineStr"/>
+      <c r="AY10" t="n">
+        <v>-0.005533184991042016</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0.5751633986928105</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>1.513768479649865</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>1.59123839857682</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0.3305134680134643</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>-2.447670366913783</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>-1.725589225589218</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>2439717.465186602</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>7</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>90000</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>-0.208670033670034</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>-0.1446127946127973</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>0.07122063308208793</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>-6611.279461279468</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>320</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>1.523809523809518</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>-1537.794621206966</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>-476979.1666666698</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>45475000</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>301</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>0.5404040404040131</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>1.380952380952383</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>0.7802279736731919</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>UJQITUyi</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45606.47916666666</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stegemann s 
+  ger </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wwk arena
+  augsburg </t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>fTVNku3I</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>f3ddUIXs</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0jdIgO6t</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>59</v>
+      </c>
+      <c r="J11" t="n">
+        <v>591</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.289166666666667</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.223</v>
+      </c>
+      <c r="R11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.676470588235294</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3.106617647058823</v>
+      </c>
+      <c r="V11" t="n">
+        <v>15.13333333333333</v>
+      </c>
+      <c r="W11" t="n">
+        <v>9.477941176470589</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.533333333333333</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.8566176470588234</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.841911764705882</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>13.2782321817616</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>18.66272280446168</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>892.6713221519055</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>897.306983197559</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="n">
+        <v>17.61538461538461</v>
+      </c>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="n">
+        <v>25.38461538461538</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>8.866666666666674</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>5.746323529411768</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>-3.333333333333329</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>-4.852941176470594</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>-30.00000000000006</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>-61.19999999999999</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>-2.733333333333333</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>-0.9227941176470589</v>
+      </c>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="n">
+        <v>-1.166666666666667</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>-0.9333333333333353</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>2.580882352941174</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>-13.19656072533058</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>-18.43376579238556</v>
+      </c>
+      <c r="AX11" t="inlineStr"/>
+      <c r="AY11" t="n">
+        <v>0.02955273332125195</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>-0.3412669932406835</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>0.5826973921546283</v>
+      </c>
+      <c r="BD11" t="inlineStr"/>
+      <c r="BE11" t="n">
+        <v>-0.7226451545530495</v>
+      </c>
+      <c r="BF11" t="inlineStr"/>
+      <c r="BG11" t="n">
+        <v>-517740.6465975549</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>3</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>24000</v>
+      </c>
+      <c r="BK11" t="inlineStr"/>
+      <c r="BL11" t="inlineStr"/>
+      <c r="BM11" t="n">
+        <v>-0.1423175599984809</v>
+      </c>
+      <c r="BN11" t="inlineStr"/>
+      <c r="BO11" t="n">
+        <v>210</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>-1.857142857142861</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>-3782.336641793878</v>
+      </c>
+      <c r="BR11" t="inlineStr"/>
+      <c r="BS11" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>209</v>
+      </c>
+      <c r="BU11" t="inlineStr"/>
+      <c r="BV11" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>0.6380313947747709</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>j5mWxZE4</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45605.60416666666</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dingert c 
+  ger </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">red bull arena
+  leipzig </t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>IkCftsQm</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>4fuCGs9P</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>59</v>
+      </c>
+      <c r="J12" t="n">
+        <v>591</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.603333333333333</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.909450980392156</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.476973684210527</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U12" t="n">
+        <v>5.963815789473684</v>
+      </c>
+      <c r="V12" t="n">
+        <v>4</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11.95394736842105</v>
+      </c>
+      <c r="X12" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>2.059210526315789</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.950657894736842</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>22.96990381297447</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>19.51226557517918</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1004.403205834458</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>886.3328606689703</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="n">
+        <v>75.85128205128206</v>
+      </c>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="n">
+        <v>34.85641025641025</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>7.299342105263158</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>9.46052631578948</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>-43.00000000000006</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>168.0875</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>-1.6875</v>
+      </c>
+      <c r="AR12" t="inlineStr"/>
+      <c r="AS12" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>-2.230263157894736</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>19.98140856582549</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>-5.459871123422786</v>
+      </c>
+      <c r="AX12" t="inlineStr"/>
+      <c r="AY12" t="n">
+        <v>-0.006330959302539844</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0.4177631578947368</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>-0.3265257988466885</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>4.71436943766308</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>0.2128472222222229</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>4.678356317086511</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>6.126388888888883</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>15584271.31802334</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>-4</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>100000</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>0.895486111111111</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>5.640624999999986</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>0.6816601599033623</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>33696.52777777778</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>-277</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>-7.125</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>26736.88442447571</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>22125902.77777778</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>107775000</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>-248</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>-1.06701388888888</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>-0.625</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>2.591271312630198</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>biQrHC9r</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45605.47916666666</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hartmann r 
+  ger </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vonovia ruhrstadion
+  bochum </t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>UgdQz0fK</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>GzfvcwRj</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>59</v>
+      </c>
+      <c r="J13" t="n">
+        <v>591</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-1.943333333333333</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>-1.952941176470588</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-3</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-2.549019607843137</v>
+      </c>
+      <c r="T13" t="n">
+        <v>-3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-3.258169934640523</v>
+      </c>
+      <c r="V13" t="n">
+        <v>-0.3333333333333321</v>
+      </c>
+      <c r="W13" t="n">
+        <v>-6.91830065359477</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-3.333333333333334</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>-2.264705882352941</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-2.686274509803921</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>20.3277789748378</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>26.0338128196328</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>932.4043924967523</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1011.112198514533</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="n">
+        <v>-18.1875</v>
+      </c>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="n">
+        <v>-28.00892857142857</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>-9.333333333333339</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>-8.251633986928102</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>-4.666666666666671</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>-20.3202614379085</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>-110.6666666666667</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>-276.0441176470588</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.176470588235295</v>
+      </c>
+      <c r="AR13" t="inlineStr"/>
+      <c r="AS13" t="n">
+        <v>0.8333333333333333</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>4.000000000000002</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>3.352941176470589</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>-8.436918765944142</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>8.715934129360825</v>
+      </c>
+      <c r="AX13" t="inlineStr"/>
+      <c r="AY13" t="n">
+        <v>0.02721688433885941</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>-0.5620915032679739</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.776625471462843</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>-11.32112164037241</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>1.840425084175084</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>-10.66006282357974</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>-11.86222643097642</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>-36276816.4581707</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>-2</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>-173000</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>-2.023863636363636</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>-11.9101430976431</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>-1.364937584882438</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>-82257.76515151515</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>-26</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>-65353.74310595404</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>-46171269.99158249</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>-61325000</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>-32</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>1.498674242424244</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>2.963943170071417</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>nee3ysec</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45605.47916666666</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">badstubner f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mewa arena
+  mainz </t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>YZPE6Sx7</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>pfoInmcq</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>59</v>
+      </c>
+      <c r="J14" t="n">
+        <v>591</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.4325000000000001</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.044117647058824</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.473684210526316</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-0.2982456140350882</v>
+      </c>
+      <c r="V14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W14" t="n">
+        <v>6.649122807017545</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-0.05000000000000027</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.002923976608187218</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.6000000000000001</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>17.03056354877007</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>18.85966828711871</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>985.4970996554355</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>912.9167668298387</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="n">
+        <v>18.09523809523807</v>
+      </c>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="n">
+        <v>23.67619047619047</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>-8.049999999999997</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>3.435672514619881</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>-31.3</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>-16.38011695906434</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>-206.0833333333334</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>-148.1727941176471</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>-0.4000000000000004</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>4.251461988304095</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>-3.470410403866293</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1.596392480288987</v>
+      </c>
+      <c r="AX14" t="inlineStr"/>
+      <c r="AY14" t="n">
+        <v>0.01863225685802798</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>-0.1637426900584795</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0.6627883769137703</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>-5.808847598050377</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>0.3959595959595994</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>-5.331014088250924</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>-6.720202020202024</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>-18492191.47258186</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>-6</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>-16</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>-294000</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>-1.146085858585859</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>-7.30441919191918</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>-0.6958263249478418</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>-32590.78282828283</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>-512</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>2.125</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>-21240.47309115034</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>-30257335.85858586</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>-208700000</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>-478</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>-3.133080808080763</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>-0.03119675302340852</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>6HTjFjve</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45605.47916666666</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gerach t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">millerntor stadion
+  hamburg </t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>KUx4Q7x1</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>hpYJ6izc</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>59</v>
+      </c>
+      <c r="J15" t="n">
+        <v>591</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>-2.235</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>-0.6381568627450982</v>
+      </c>
+      <c r="R15" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="S15" t="n">
+        <v>-0.7052631578947368</v>
+      </c>
+      <c r="T15" t="n">
+        <v>-9.4</v>
+      </c>
+      <c r="U15" t="n">
+        <v>-1.463157894736841</v>
+      </c>
+      <c r="V15" t="n">
+        <v>-10.6</v>
+      </c>
+      <c r="W15" t="n">
+        <v>-0.1649122807017527</v>
+      </c>
+      <c r="X15" t="n">
+        <v>-4.8</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>-0.9052631578947368</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-0.1894736842105262</v>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="AD15" t="n">
+        <v>1284.140329487989</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1023.812081812265</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="n">
+        <v>6.283333333333331</v>
+      </c>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="n">
+        <v>5.449999999999999</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>2.466666666666661</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1.333333333333336</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>-40.53333333333332</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>-10.84912280701754</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>-575.6666666666666</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>-145.327731092437</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>-0.6507936507936507</v>
+      </c>
+      <c r="AR15" t="inlineStr"/>
+      <c r="AS15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>1.266666666666667</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>-0.7789473684210542</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>86.27191661538022</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>15.82364783047451</v>
+      </c>
+      <c r="AX15" t="inlineStr"/>
+      <c r="AY15" t="n">
+        <v>0.03587896681123888</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>-0.9333333333333333</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>-0.07719298245614031</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>-0.5115454076367385</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>-12.54221007481941</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>-0.5477272727272791</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>-12.08477758427934</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>-12.45416666666667</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>-33479546.4745657</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>-118000</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>-2.331944444444444</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>-12.86300505050505</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>-1.603642070863433</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>-65116.41414141414</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>20</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>-0.4666666666666686</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>-59535.90327944043</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>-47224346.59090909</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>-57210000</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>29</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>1.005681818181785</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>1.466666666666669</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>1.474570540935645</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>YmumZjET</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45605.47916666666</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">storks s 
+  ger </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">weserstadion
+  bremen </t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>M5BRZDsC</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>4ljanukM</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>59</v>
+      </c>
+      <c r="J16" t="n">
+        <v>591</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>-1.17</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-0.2746666666666666</v>
+      </c>
+      <c r="R16" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="S16" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-0.1666666666666665</v>
+      </c>
+      <c r="U16" t="n">
+        <v>-0.4862745098039212</v>
+      </c>
+      <c r="V16" t="n">
+        <v>-4.166666666666668</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.2549019607843128</v>
+      </c>
+      <c r="X16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>-1.03921568627451</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-1.282352941176471</v>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="AD16" t="n">
+        <v>944.0534735357809</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>934.5321134618432</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="n">
+        <v>-7.448717948717942</v>
+      </c>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="n">
+        <v>17.4102564102564</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>2.916666666666664</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>-0.6549019607843114</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>-4.166666666666671</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>-3.129411764705878</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>63.33333333333331</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>-44.19999999999993</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>-1.833333333333333</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>-0.5714285714285714</v>
+      </c>
+      <c r="AR16" t="inlineStr"/>
+      <c r="AS16" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>-5.083333333333332</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>-1.529411764705882</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>49.77988632550036</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>15.50885892048173</v>
+      </c>
+      <c r="AX16" t="inlineStr"/>
+      <c r="AY16" t="n">
+        <v>0.04790801418890725</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>-0.4166666666666666</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>-0.5529411764705882</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>-1.212872132158459</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>1.940461439542531</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>0.8377209595959627</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>3.51653808743697</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>4.183901515151504</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>1537195.451264029</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>28000</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>0.09772727272727288</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>4.861363636363649</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>7243.592171717173</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>17</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>3934.688670168503</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>4073626.893939395</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>12500000</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>16</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>-3.2525883838384</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>1.374202753053567</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
           <t>v3DAZKP9</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n">
+      <c r="B17" s="2" t="n">
         <v>45604.6875</v>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">brand b 
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reichel t 
   ger </t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t xml:space="preserve">stadion an der alten forsterei
   berlin </t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>pzHW4oaE</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>fiEQZ7C7</t>
         </is>
       </c>
-      <c r="G10" t="n">
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>hpYJ6izc</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>YZPE6Sx7</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
         <v>59</v>
       </c>
-      <c r="H10" t="n">
+      <c r="J17" t="n">
         <v>591</v>
       </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
         <v>20242025</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>germany</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>K6A2elS9</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>vZA6VYpf</t>
-        </is>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>-0.6914285714285713</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>-0.2672222222222222</v>
-      </c>
-      <c r="R10" t="n">
-        <v>-0.375</v>
-      </c>
-      <c r="S10" t="n">
-        <v>-0.2999999999999998</v>
-      </c>
-      <c r="T10" t="n">
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.2000000000000002</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.8047083333333329</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T17" t="n">
+        <v>-0.3333333333333326</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
+      </c>
+      <c r="V17" t="n">
         <v>-2</v>
       </c>
-      <c r="U10" t="n">
-        <v>-0.4500000000000002</v>
-      </c>
-      <c r="V10" t="n">
-        <v>-4</v>
-      </c>
-      <c r="W10" t="n">
-        <v>-0.4499999999999975</v>
-      </c>
-      <c r="X10" t="n">
-        <v>-0.625</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>-0.6000000000000001</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>-1.125</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>-0.45</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>-3.215237019924519</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>-2.990857979739559</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>16.99569098189153</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>36.49754953464293</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>-71</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>-10.46153846153845</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>-14</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>8.692307692307693</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>-9.125</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>-1.149999999999999</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>-23.25</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>-9.5</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>-327.7142857142857</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>-146.7222222222222</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>0.5026315789473685</v>
-      </c>
-      <c r="AR10" t="inlineStr"/>
-      <c r="AS10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>4.125</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>3.349999999999998</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>12.86345896707828</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>-1.910765312830016</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>0.006053378146401403</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>0.02433786762267351</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>-0.375</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>2.153409090909093</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>1801.547931772395</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>-2.285714285714286</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>-1.428571428571429</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>-1.098939720989293</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>-0.3114898989898991</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>-263.0050505050494</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>-0.3341039825888039</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>-0.3671717171717184</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>-0.263948390360929</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>-0.7742130225295796</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>-2.020833333333357</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>2.826190476190476</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>-5143674.242424242</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>-6442857.142857142</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>-1.158462607877937</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>-2229956.750443399</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>-169.2857142857143</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>-3714.285714285725</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>-1.304040404040407</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>-5.971428571428589</v>
-      </c>
-      <c r="BW10" t="n">
-        <v>-150.8571428571429</v>
+      <c r="W17" t="n">
+        <v>4.875</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>20.40057165057165</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>17.86354288690541</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>973.3942913420832</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>898.3403938393072</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="n">
+        <v>-14.84615384615385</v>
+      </c>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="n">
+        <v>16.23076923076923</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>-12.33333333333333</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>2.6875</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>-15.33333333333333</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>-1.875</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>-136.3333333333333</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>-35.86666666666667</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0.6666666666666665</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0.5446428571428572</v>
+      </c>
+      <c r="AR17" t="inlineStr"/>
+      <c r="AS17" t="inlineStr"/>
+      <c r="AT17" t="n">
+        <v>0.3333333333333339</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>2.125</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>16.28296066151853</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>-1.314627185485811</v>
+      </c>
+      <c r="AX17" t="inlineStr"/>
+      <c r="AY17" t="n">
+        <v>0.0238791355209734</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>-0.6666666666666666</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>-0.1875</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>2.232142857142858</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>0.6964285714285694</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>-0.009090909090911481</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>-1.982142857142861</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>-1.727272727272734</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>-585714.2857142859</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>-3</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>-2</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>-10000</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>-0.3363636363636364</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>-2.445454545454552</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>-0.1071428571428572</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>-763.636363636364</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>-226</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>-4.166666666666657</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>5053.571428571428</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>-5896363.636363637</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>-6000000</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>-198</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>1.718181818181819</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>3</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>-2.535714285714278</v>
       </c>
     </row>
   </sheetData>
